--- a/output_test_cases.xlsx
+++ b/output_test_cases.xlsx
@@ -431,1027 +431,1107 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>story_number</t>
+          <t>executive_summary</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>test_cases</t>
+          <t>user_story</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>edge_cases</t>
+          <t>happy_path_summary</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>shared_tests</t>
+          <t>scenario_table</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>regression_impact</t>
+          <t>detailed_test_cases</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>This user story enables Case Workers to initiate Medicaid eligibility processing by recording new applications with essential applicant information. It ensures proper capture of applicant details, system validation for required data, and reinforces data integrity and user role compliance.</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['Verify a case worker can access and open the new Medicaid application intake form.', 'Verify all required applicant detail fields (name, DOB, SSN, address, etc.) are present.', 'Check that submitting a completed form saves a new application record and assigns a unique identifier.', 'Validate that user permissions restrict intake to authorized case workers.', 'Verify successful creation is logged/audited.']</t>
+          <t>As a Case Worker, I want to intake a new Medicaid application so that I can begin the eligibility process. - Enable intake of new applications with basic applicant details.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Attempt submit with missing mandatory fields.', 'Enter special characters or non-ASCII in input fields.', 'Submit duplicate applications for the same SSN.', 'Enter an unrealistically long name/address.']</t>
+          <t>A Case Worker logs in, accesses the intake module, enters valid applicant information, saves the application, and receives a confirmation that the case is created and ready for further processing.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Ensure intake correctly interacts with ID verification (Story 2).', 'Ensure integration with income check (Story 3).', 'Check household composition recording (Story 4).', 'Confirm incomplete applications are flagged (Story 5).']</t>
+          <t>[{'Test Case ID': 'INTAKE-01', 'Brief Description': 'Successful intake of new Medicaid application with complete valid details'}, {'Test Case ID': 'INTAKE-02', 'Brief Description': 'Attempt intake with missing applicant mandatory fields'}, {'Test Case ID': 'INTAKE-03', 'Brief Description': 'Attempt intake with invalid format (e.g., invalid SSN or DOB)'}, {'Test Case ID': 'INTAKE-04', 'Brief Description': 'Verify only Case Worker roles have access to intake function'}, {'Test Case ID': 'INTAKE-05', 'Brief Description': 'Check system audit log records the intake event'}, {'Test Case ID': 'INTAKE-06', 'Brief Description': 'Verify application cannot be submitted twice with same SSN'}]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 5, 8, 9, 22, 26, 27, 31]</t>
+          <t>[{'Test Case ID': 'INTAKE-01', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Create New Application', 'Test Scenario Title': 'Intake with Complete Valid Applicant Data', 'Precondition': 'User logged in as Case Worker; Intake module accessible', 'Test Data': "{ 'Name': 'John Doe', 'DOB': '1980-01-01', 'SSN': '123-45-6789', 'Address': '123 Main St', ... }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker', "2. Navigate to 'Intake New Application'", '3. Enter all required applicant information in valid formats', '4. Submit application'], 'Expected Result': 'New application is created and case number assigned; confirmation displayed', 'Dependent Module/Process': 'Eligibility Workflow'}, {'Test Case ID': 'INTAKE-02', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Create New Application', 'Test Scenario Title': 'Missing Mandatory Fields', 'Precondition': 'User logged in as Case Worker; Intake module accessible', 'Test Data': "{ 'Name': 'John Doe', 'DOB': '', 'SSN': '', ... }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker', "2. Navigate to 'Intake New Application'", '3. Leave mandatory fields blank', '4. Attempt to submit application'], 'Expected Result': 'System displays error for missing required fields; user cannot proceed', 'Dependent Module/Process': None}, {'Test Case ID': 'INTAKE-03', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Create New Application', 'Test Scenario Title': 'Invalid Data Format', 'Precondition': 'User logged in as Case Worker; Intake module accessible', 'Test Data': "{ 'SSN': 'invalid', 'DOB': '99-99-9999' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker', "2. Navigate to 'Intake New Application'", '3. Enter invalid values (e.g., alphabetic SSN, malformed DOB)', '4. Attempt to submit application'], 'Expected Result': 'System displays format validation errors; application not saved', 'Dependent Module/Process': None}, {'Test Case ID': 'INTAKE-04', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role Validation', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Role Based Access Control - Intake Screen', 'Precondition': 'User logged in as non-Case Worker (e.g., Auditor, Public User)', 'Test Data': '{}', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor/Public User', 'Detailed Test Steps': ['1. Log in as non-Case Worker user', "2. Attempt to access 'Intake New Application' functionality"], 'Expected Result': 'User is denied access; sees error or is redirected', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'INTAKE-05', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Audit Logging', 'User Story': 'US-1', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Event Logging', 'Activity Title': 'Log Creation', 'Test Scenario Title': 'Audit Logging on Application Intake', 'Precondition': 'New application successfully submitted', 'Test Data': "{ 'Case Worker': 'user123', 'Timestamp': '&lt;date/time&gt;' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Complete application intake (see intake happy path)', '2. Query audit logs for recent activity'], 'Expected Result': 'Intake event logged with user ID, timestamp, and applicant reference', 'Dependent Module/Process': 'Audit Log System'}, {'Test Case ID': 'INTAKE-06', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Duplicate Check', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Duplicate Detection', 'Test Scenario Title': 'Duplicate SSN Submission Prevention', 'Precondition': 'Existing application with SSN 123-45-6789', 'Test Data': "{ 'SSN': '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Attempt to create new application with SSN already present in active system', '2. Submit application'], 'Expected Result': 'System prevents duplicate submission; error displayed regarding existing record', 'Dependent Module/Process': 'Duplicate Detection Service'}]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>This user story ensures that Medicaid applicant identity is verified against authoritative sources (such as DMV or SSA), preventing identity fraud and maintaining record accuracy in the eligibility process.</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>["Verify applicant government ID field accepts valid formats (e.g., driver's license, SSN).", 'Confirm correct API calls to DMV/SSA with sample applicant info.', 'Validate error is shown for invalid or non-matching IDs.', 'Check audit trail/log for ID verification attempts and results.', 'Verify handling and display for system/API unavailability.']</t>
+          <t>As a Case Worker, I want to verify applicant identity using government ID so that I can ensure accurate records. - Integrate ID verification with DMV or SSA databases.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['Submit expired or revoked ID.', 'Simulate DMV/SSA database timeout or error.', 'Use ID with similar data but different person (identity collision).']</t>
+          <t>Case Worker submits applicant's government ID information; system sends request to DMV/SSA; receives positive match and marks identity as verified.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['Verify intake must complete ID verification before advancing (Story 1).', 'Test error propagation to incomplete application flagging (Story 5).']</t>
+          <t>[{'Test Case ID': 'IDVER-01', 'Brief Description': 'Successfully verify applicant identity with valid government ID'}, {'Test Case ID': 'IDVER-02', 'Brief Description': 'Fail verification with invalid or mismatched government ID'}, {'Test Case ID': 'IDVER-03', 'Brief Description': 'Attempt to verify identity when external ID verification service is unavailable'}, {'Test Case ID': 'IDVER-04', 'Brief Description': 'Ensure only Case Workers may initiate ID verification'}, {'Test Case ID': 'IDVER-05', 'Brief Description': 'Audit logging of identity verification attempt'}, {'Test Case ID': 'IDVER-06', 'Brief Description': 'Compliance with data masking on government ID fields'}]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[1, 5, 9, 31]</t>
+          <t>[{'Test Case ID': 'IDVER-01', 'EPIC': 'Identity Verification', 'Feature': 'Government ID Validation', 'User Story': 'US-2', 'Business Process': 'Applicant Verification', 'Sub-Process Title': 'Identity Validation', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'Successful Government ID Verification', 'Precondition': 'Applicant data entered and saved; user is Case Worker', 'Test Data': "{ 'SSN': '234-56-7890', 'FullName': 'Jane Smith', 'DOB': '1990-02-20' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant in system', '2. Enter government ID information (e.g., SSN/DL)', '3. Initiate verification request', '4. Await system response'], 'Expected Result': "System confirms positive ID match; applicant identity marked as 'Verified'", 'Dependent Module/Process': 'External API to DMV/SSA'}, {'Test Case ID': 'IDVER-02', 'EPIC': 'Identity Verification', 'Feature': 'Government ID Validation', 'User Story': 'US-2', 'Business Process': 'Applicant Verification', 'Sub-Process Title': 'Identity Validation', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'Invalid or Mismatched Government ID', 'Precondition': 'Applicant data entered and saved; user is Case Worker', 'Test Data': "{ 'SSN': '111-22-3333', 'FullName': 'Not Matching', 'DOB': '1985-12-01' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Enter mismatched or invalid government ID information', '3. Submit verification request'], 'Expected Result': 'System displays verification failure and related message; identity not marked as verified', 'Dependent Module/Process': 'External API to DMV/SSA'}, {'Test Case ID': 'IDVER-03', 'EPIC': 'Identity Verification', 'Feature': 'Government ID Validation', 'User Story': 'US-2', 'Business Process': 'Applicant Verification', 'Sub-Process Title': 'Identity Validation', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'ID Verification Service Unavailable', 'Precondition': 'Applicant data entered and saved; external service is purposefully down', 'Test Data': "{ 'SSN': '222-33-4444' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Enter government ID information', '3. Submit verification request'], 'Expected Result': 'System notifies user that verification service is unavailable; identity remains unverified', 'Dependent Module/Process': 'External API to DMV/SSA'}, {'Test Case ID': 'IDVER-04', 'EPIC': 'Identity Verification', 'Feature': 'Access Control', 'User Story': 'US-2', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Verify Role Restriction', 'Test Scenario Title': 'Only Case Workers Can Submit ID Verification', 'Precondition': 'User logged in as non-Case Worker', 'Test Data': '{}', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor/Public User/Other Staff', 'Detailed Test Steps': ['1. Log in as an unauthorized user', '2. Attempt to access ID verification feature'], 'Expected Result': 'Access is denied; feature not visible or user receives error', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'IDVER-05', 'EPIC': 'Identity Verification', 'Feature': 'Audit Logging', 'User Story': 'US-2', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Event Logging', 'Activity Title': 'Log Verification Attempt', 'Test Scenario Title': 'Audit Logging for Identity Verification Attempt', 'Precondition': 'Verification attempt performed (success or failure)', 'Test Data': "{ 'user': 'cw01', 'applicant': 'xyz', 'timestamp': '&lt;date&gt;' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Perform a government ID verification attempt (success or failure)', '2. Query system audit logs', '3. Ensure entry has required details'], 'Expected Result': 'Audit log entry records user, timestamp, result, and applicant reference', 'Dependent Module/Process': 'Audit Log and Compliance Monitoring'}, {'Test Case ID': 'IDVER-06', 'EPIC': 'Identity Verification', 'Feature': 'Data Compliance', 'User Story': 'US-2', 'Business Process': 'Compliance (HIPAA, State Regs)', 'Sub-Process Title': 'Protected Data Handling', 'Activity Title': 'Data Display and Transmission', 'Test Scenario Title': 'PII Masking on Government ID During Verification', 'Precondition': 'Application with government ID entered', 'Test Data': "{ 'SSN': '867-53-0909' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. View government ID input and display fields during verification process', '2. Review UI and logs for PII exposure'], 'Expected Result': 'Government ID (SSN, DL#) is masked per compliance standards (e.g., last 4 digits only)', 'Dependent Module/Process': 'Data Masking/Compliance Engine'}]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>This user story enables Case Workers to determine Medicaid financial eligibility by integrating with wage data sources like The Work Number, allowing accurate application assessment based on verified income.</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['Verify a case worker can trigger income check using applicant data.', 'Validate connection to income system (e.g., The Work Number) sends correct payload and parses response.', 'Check workflow ensures financial qualification shows accurate eligibility.', 'Verify error message handling for income system downtime.', 'Test for storing and retrieving historical income check results.']</t>
+          <t>As a Case Worker, I want to check income eligibility using wage data so that I can determine financial qualification. - Connect to income verification systems like The Work Number.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['Income system returns ambiguous or multiple entries.', 'Applicant has no income record.', 'Income data returned is inconsistent (e.g., negative value).']</t>
+          <t>Case Worker initiates income check for an applicant; system queries The Work Number; returns income data; eligibility determination based on returned values.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['Validate income check step is accessible from application intake (Story 1).']</t>
+          <t>[{'Test Case ID': 'INCVER-01', 'Brief Description': 'Successful retrieval and processing of income data'}, {'Test Case ID': 'INCVER-02', 'Brief Description': 'Income eligibility fails - applicant income above threshold'}, {'Test Case ID': 'INCVER-03', 'Brief Description': 'No wage data found for applicant'}, {'Test Case ID': 'INCVER-04', 'Brief Description': 'External income verification system downtime'}, {'Test Case ID': 'INCVER-05', 'Brief Description': 'API returns unexpected/incomplete data'}, {'Test Case ID': 'INCVER-06', 'Brief Description': 'Access to income check restricted to Case Worker role'}, {'Test Case ID': 'INCVER-07', 'Brief Description': 'Verify audit logs record all income data access and eligibility decisions'}]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[1, 37]</t>
+          <t>[{'Test Case ID': 'INCVER-01', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Successful Wage Data Retrieval', 'Precondition': 'Applicant record exists; user as Case Worker', 'Test Data': "{ 'SSN': '345-67-8901', 'Employer': 'ABC Corp' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System sends request to The Work Number', '4. Receives valid income data'], 'Expected Result': 'Income data displayed; eligibility decision based on rules; status updated on application', 'Dependent Module/Process': 'Income API, Eligibility Engine'}, {'Test Case ID': 'INCVER-02', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Income Above Threshold', 'Precondition': 'Applicant record exists; user as Case Worker', 'Test Data': "{ 'Income': 50000, 'Threshold': 20000 }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System receives income data exceeding eligibility threshold'], 'Expected Result': 'System flags applicant as income-ineligible; displays explanatory alert; marks application as ineligible', 'Dependent Module/Process': 'Eligibility Engine'}, {'Test Case ID': 'INCVER-03', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'No Wage Data Found', 'Precondition': 'Applicant exists with valid SSN; no wage record in The Work Number', 'Test Data': "{ 'SSN': '999-99-9999' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', "3. System receives 'no data found' response"], 'Expected Result': 'System notifies user; allows for manual follow-up or document upload', 'Dependent Module/Process': 'Income API'}, {'Test Case ID': 'INCVER-04', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Income Verification Service Unavailable', 'Precondition': 'Applicant exists; income service is down', 'Test Data': "{ 'SSN': '456-78-9012' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System fails to receive response from The Work Number'], 'Expected Result': 'System displays error regarding service unavailability; prevents eligibility action until resolved', 'Dependent Module/Process': 'Income API'}, {'Test Case ID': 'INCVER-05', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Unexpected or Incomplete API Response', 'Precondition': 'Applicant record exists; API returns partial data', 'Test Data': "{ 'Employer': '', 'Income': null }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System receives incomplete API response'], 'Expected Result': 'System displays error/validation message for incomplete data; no eligibility determination made', 'Dependent Module/Process': 'Income API/Error Handling'}, {'Test Case ID': 'INCVER-06', 'EPIC': 'Income Verification', 'Feature': 'Access Control', 'User Story': 'US-3', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Verify Role Restriction', 'Test Scenario Title': 'Restrict Access to Income Verification to Case Workers', 'Precondition': 'User logged in as non-Case Worker', 'Test Data': '{}', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor/Public User/Other Staff', 'Detailed Test Steps': ['1. Log in as unauthorized user', '2. Attempt to access income verification feature'], 'Expected Result': 'Access is denied; feature not visible or user receives error', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'INCVER-07', 'EPIC': 'Income Verification', 'Feature': 'Audit Logging', 'User Story': 'US-3', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Event Logging', 'Activity Title': 'Log Income Checks', 'Test Scenario Title': 'Audit Logging of Income Data Requests', 'Precondition': 'Income check requested for applicant', 'Test Data': "{ 'User': 'cw01', 'Applicant': 'abc', 'Timestamp': '&lt;date/time&gt;' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Perform income check', '2. Query audit logs for recent activity'], 'Expected Result': 'Audit log captures requester ID, applicant reference, timestamp, and eligibility decision', 'Dependent Module/Process': 'Audit Log/Compliance System'}]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Workers can accurately record and maintain household composition, capturing household members and their relationships for eligibility assessment based on family size. Proper recording enables compliance with program and audit requirements.</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Verify adding household members, their ages, and relationships in the application.', 'Test upper and lower limits for number of household members.', 'Validate relationships (e.g., self, spouse, child, other) are accurate and saved.', 'Check changes to household reflect in eligibility assessment.']</t>
+          <t>As a Case Worker, I want to record household composition so that I can assess eligibility based on family size. - Capture household members and their relationships.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['Input invalid relationships or age values.', 'Household with only one member (edge minimal case).', 'Very large households (e.g., 15+ members).']</t>
+          <t>Case Worker logs in, opens a client case, navigates to the household composition section, adds all household members (with correct relationships), saves the data, and verifies system acceptance.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['Confirm household step is required for Medicaid application intake (Story 1).', 'Verify correct passing of household info to eligibility logic.']</t>
+          <t>[{'Test Case ID': 'US4_TC1', 'Brief Description': 'Add household members and relationships successfully (happy path)'}, {'Test Case ID': 'US4_TC2', 'Brief Description': 'Add a household member with missing required fields (negative)'}, {'Test Case ID': 'US4_TC3', 'Brief Description': 'Attempt to save household composition with invalid relationships (negative)'}, {'Test Case ID': 'US4_TC4', 'Brief Description': 'Attempt to add duplicate household members (negative)'}, {'Test Case ID': 'US4_TC5', 'Brief Description': 'Verify data is saved and displayed correctly upon reopening (functional/integration)'}, {'Test Case ID': 'US4_TC6', 'Brief Description': 'API: POST/PUT household composition with all valid fields'}, {'Test Case ID': 'US4_TC7', 'Brief Description': 'API: Reject incomplete/invalid household composition data'}]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[1, 27]</t>
+          <t>[{'Test Case ID': 'US4_TC1', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Add household members and relationships successfully', 'Precondition': 'Case Worker has a valid login; client case exists', 'Test Data': 'Case ID: 123; Members: John Smith (DOB: 1980-05-01, Relationship: Self), Mary Smith (DOB: 1982-03-10, Relationship: Spouse), Janet Smith (DOB: 2010-09-01, Relationship: Daughter)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Navigate to client case (ID: 123)', "Go to 'Household Composition' section", "Click 'Add Member', enter John Smith’s details and relationship 'Self', save", "Click 'Add Member', enter Mary Smith, relationship 'Spouse', save", "Click 'Add Member', enter Janet Smith, relationship 'Daughter', save", "Click 'Save' household composition"], 'Expected Result': 'All household members are listed with correct relationships. No errors. Data is persisted.', 'Dependent Module/Process': 'Client Case'}, {'Test Case ID': 'US4_TC2', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Add household member with missing required fields', 'Precondition': "Case Worker at 'Household Composition' section", 'Test Data': 'Name: (blank), DOB: 2012-04-23, Relationship: Son', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Attempt to add new household member, leave 'Name' blank, fill other fields", "Click 'Save'"], 'Expected Result': "System highlights missing 'Name' field and prevents save, user sees appropriate error message.", 'Dependent Module/Process': 'Client Case'}, {'Test Case ID': 'US4_TC3', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Save household member with invalid relationship', 'Precondition': 'At least one household member has been added', 'Test Data': 'Name: Jane Doe, Relationship: Alien', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Add a new household member Jane Doe', "Select 'Alien' as relationship", "Click 'Save'"], 'Expected Result': 'System displays validation error ‘Invalid relationship’ and save is blocked.', 'Dependent Module/Process': 'Validation Service'}, {'Test Case ID': 'US4_TC4', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Add duplicate household members', 'Precondition': 'Member John Smith (DOB:1980-05-01) already exists', 'Test Data': 'Name: John Smith, DOB: 1980-05-01, Relationship: Self', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to add John Smith with same DOB again', "Click 'Save'"], 'Expected Result': "System alerts 'Duplicate member detected' and prevents save.", 'Dependent Module/Process': 'Duplicate Checking'}, {'Test Case ID': 'US4_TC5', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Verify persistence', 'Test Scenario Title': 'Review household composition after save', 'Precondition': 'Household composition saved successfully', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Logout and login again', 'Navigate to client case', "Open 'Household Composition' section"], 'Expected Result': 'All previously added members and relationships appear correctly.', 'Dependent Module/Process': 'Persistence/Database'}, {'Test Case ID': 'US4_TC6', 'EPIC': 'Household Management', 'Feature': 'Household Composition API', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Create/Update Household Composition', 'Test Scenario Title': 'API accepts valid household composition submission', 'Precondition': 'API is accessible with valid credentials', 'Test Data': "{ household_id: 123, members: [{name: 'John Smith', dob: '1980-05-01', relationship: 'Self'}, ...] }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Send POST or PUT request to /api/household-compositions with valid payload'], 'Expected Result': 'API responds with 200 OK and reflects household data correctly.', 'Dependent Module/Process': 'API/Database'}, {'Test Case ID': 'US4_TC7', 'EPIC': 'Household Management', 'Feature': 'Household Composition API', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Create/Update Household Composition', 'Test Scenario Title': 'API rejects incomplete/invalid household composition submission', 'Precondition': 'API is accessible', 'Test Data': "{ household_id: 123, members: [{dob: '1982-05-23', relationship: 'Spouse'}] }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Send POST or PUT request to /api/household-compositions with incomplete member data'], 'Expected Result': "API responds with 400 Bad Request and validation message specifying missing 'name' field.", 'Dependent Module/Process': 'API Validation'}]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>This user story provides a means for Case Workers to identify and manage incomplete applications by flagging missing fields and documents, ensuring quicker follow-up and higher compliance rates.</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Submit incomplete application and verify required fields are highlighted.', 'Leave out required documentation and ensure flag is raised.', 'Test visual and filtering indicators for incomplete versus complete applications in the work queue.', 'Verify follow-up reminder is generated for flagged applications.', 'Ensure proper logging of incomplete application status.']</t>
+          <t>As a Case Worker, I want to flag incomplete applications so that I can follow up with applicants. - System should highlight missing fields and documents.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['Missing both fields and documents.', 'Flipping between states by consecutively completing and removing required information.', 'Submit with all optional information but missing just one required item.']</t>
+          <t>Case Worker reviews an application, system highlights missing fields/documents, Case Worker flags the application as incomplete, system updates application status for follow-up.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['Check flagging works when intake is incomplete (Story 1).', 'Verify IDs not verified trigger incomplete status (Story 2).']</t>
+          <t>[{'Test Case ID': 'US5_TC1', 'Brief Description': 'System auto-highlights incomplete applications (happy path)'}, {'Test Case ID': 'US5_TC2', 'Brief Description': 'Flag application as incomplete and initiate follow-up'}, {'Test Case ID': 'US5_TC3', 'Brief Description': 'Verify application with all fields and documents is not flagged'}, {'Test Case ID': 'US5_TC4', 'Brief Description': 'Attempt to flag application already marked complete (negative)'}, {'Test Case ID': 'US5_TC5', 'Brief Description': 'API: Retrieve list of incomplete applications'}, {'Test Case ID': 'US5_TC6', 'Brief Description': 'Permissions: Verify only Case Worker role can flag incomplete'}]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[1, 2, 11, 12, 22]</t>
+          <t>[{'Test Case ID': 'US5_TC1', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Field/Document Validation', 'Activity Title': 'Highlight Incomplete Fields/Docs', 'Test Scenario Title': 'System automatically detects and highlights missing fields/documents', 'Precondition': 'Application submitted with missing information (e.g., missing income proof)', 'Test Data': 'Application ID: 456, Document: Proof of income (missing), Field: Address (blank)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Navigate to Application ID: 456', 'Observe highlighted missing fields/documents on application page'], 'Expected Result': 'System visually highlights missing required fields and documents.', 'Dependent Module/Process': 'Validation Rules/Document Upload'}, {'Test Case ID': 'US5_TC2', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Mark and Follow-Up', 'Activity Title': 'Flag Incomplete Application', 'Test Scenario Title': 'Case Worker flags application as incomplete and initiates follow-up', 'Precondition': 'Incomplete application identified', 'Test Data': 'Application ID: 457', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["On incomplete application screen, click 'Flag as Incomplete'", 'Select reason for incompleteness from drop-down', 'Enter notes for follow-up', 'Save changes'], 'Expected Result': "Application status updated to 'Incomplete'; flagged for follow-up; appropriate audit trail generated.", 'Dependent Module/Process': 'Audit, Workflow'}, {'Test Case ID': 'US5_TC3', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Field/Document Validation', 'Activity Title': 'Flag Review', 'Test Scenario Title': 'Verify system does not flag complete application', 'Precondition': 'Application with all required information and documents submitted', 'Test Data': 'Application ID: 458; all fields provided', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open complete application (ID:458)', 'Verify that no fields or document sections are flagged as incomplete'], 'Expected Result': 'No highlighting or incomplete status is shown for the application.', 'Dependent Module/Process': 'Validation Rules'}, {'Test Case ID': 'US5_TC4', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Mark and Follow-Up', 'Activity Title': 'Invalid Flag Action', 'Test Scenario Title': "Attempt to flag application already marked 'Complete'", 'Precondition': "Application status is 'Complete'", 'Test Data': 'Application ID: 459', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to flag completed application (ID: 459) as incomplete'], 'Expected Result': 'System prevents action and displays appropriate error message.', 'Dependent Module/Process': 'Status Management'}, {'Test Case ID': 'US5_TC5', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management API', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Fetch Incomplete Applications', 'Test Scenario Title': 'API returns all incomplete applications assigned to the case worker', 'Precondition': 'API is accessible and applications exist', 'Test Data': 'GET /api/applications?status=incomplete', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Send GET request to /api/applications?status=incomplete'], 'Expected Result': 'API responds with list of all incomplete applications for the user.', 'Dependent Module/Process': 'API'}, {'Test Case ID': 'US5_TC6', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Role-based Action', 'Test Scenario Title': 'Only case workers can flag incomplete applications', 'Precondition': 'Other roles (e.g., Applicant) can access application view', 'Test Data': 'Role: Applicant; Application ID: 460', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ["Login as 'Applicant'", 'View own application (ID: 460)', "Attempt to flag as 'Incomplete'"], 'Expected Result': 'Flagging option is not visible or action is blocked for non-case workers.', 'Dependent Module/Process': 'Role Permissions'}]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>This user story enables Case Managers to monitor client eligibility status and renewal timelines using a dashboard to support proactive service planning and compliance. The dashboard must accurately reflect real-time data per role-based access standards.</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Log in as a Case Manager and view the dashboard; verify eligibility status displayed for all assigned clients', 'Verify dashboard displays correct eligibility status for clients with varying statuses (eligible, not eligible, pending)', 'Verify renewal dates are shown and match backend data', 'Filter/sort clients by eligibility status', 'Click on a client to view more details']</t>
+          <t>As a Case Manager, I want to view the eligibility status of my clients so that I can plan services accordingly. - Dashboard showing eligibility status and renewal dates.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['Client with missing or null eligibility status', 'Client with multiple eligibility records', 'Client with expired status but no renewal date', 'No clients assigned to Case Manager']</t>
+          <t>Case Manager accesses dashboard, sees the list of clients with current eligibility status and renewal dates, enabling clear planning of follow-up actions.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['Verify eligibility and renewal information matches data in stories 7 (alerts), 23, 25, 34']</t>
+          <t>[{'Test Case ID': 'US6_TC1', 'Brief Description': 'Dashboard displays eligibility status and renewal dates for all assigned clients (happy path)'}, {'Test Case ID': 'US6_TC2', 'Brief Description': 'Status and renewal information updates in real-time as eligibility changes (integration)'}, {'Test Case ID': 'US6_TC3', 'Brief Description': 'Access denied for unauthorized user roles (permissions compliance)'}, {'Test Case ID': 'US6_TC4', 'Brief Description': 'API: Retrieve eligibility status list for clients'}, {'Test Case ID': 'US6_TC5', 'Brief Description': 'Dashboard filters clients by eligibility status'}, {'Test Case ID': 'US6_TC6', 'Brief Description': 'Dashboard includes audit trail for eligibility changes (compliance/audit)'}]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['Story 7: Alerts for expiring eligibility', 'Story 23: Any client data sync features', 'Story 25: Dashboard client summation', 'Story 34: Client profile or service planning views']</t>
+          <t>[{'Test Case ID': 'US6_TC1', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Eligibility Overview', 'Activity Title': 'Eligibility Display', 'Test Scenario Title': 'Dashboard displays eligibility status and renewal dates for all assigned clients', 'Precondition': 'Case Manager assigned clients with eligibility data', 'Test Data': 'Clients: [Mark Lee, Status: Eligible, Renewal: 2024-08-10]; [Ella Green, Status: Ineligible, Renewal: 2025-02-01]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager', "Open 'Eligibility Dashboard'", 'Review client list with status and renewal columns'], 'Expected Result': 'Dashboard lists all assigned clients with accurate status and renewal dates.', 'Dependent Module/Process': 'Eligibility Determination'}, {'Test Case ID': 'US6_TC2', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Real-time Update', 'Activity Title': 'Status Refresh', 'Test Scenario Title': 'Eligibility status and renewal date reflect in dashboard real-time when updated', 'Precondition': 'Eligibility update occurs for a client', 'Test Data': 'Client: Mark Lee; Original status: Eligible; Renewal: 2024-08-10; Update to Ineligible', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Trigger eligibility update for Mark Lee (via back-end or UI)', 'Refresh dashboard as Case Manager'], 'Expected Result': 'Dashboard instantly shows new eligibility status and correct renewal date.', 'Dependent Module/Process': 'Eligibility Engine, Dashboard'}, {'Test Case ID': 'US6_TC3', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Role Permissions', 'Activity Title': 'Unauthorized Access', 'Test Scenario Title': 'Access denied for unauthorized roles', 'Precondition': 'User with non-Case Manager role (e.g., Applicant, Case Worker) attempts access', 'Test Data': 'User Role: Applicant', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Log in as Applicant', "Attempt to navigate to 'Eligibility Dashboard'"], 'Expected Result': "System denies access with message 'Access Denied' or redirects user.", 'Dependent Module/Process': 'Role-Based Access Control'}, {'Test Case ID': 'US6_TC4', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard API', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Fetch Client Status', 'Test Scenario Title': 'API endpoint returns eligibility status and renewal dates for assigned clients', 'Precondition': 'Case Manager with client assignments, API authentication', 'Test Data': 'GET /api/clients/eligibility?manager_id=789', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Call API with case manager credentials'], 'Expected Result': 'API response lists each client and includes eligibility status and renewal date fields.', 'Dependent Module/Process': 'API, Eligibility Service'}, {'Test Case ID': 'US6_TC5', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Dashboard Filtering', 'Activity Title': 'Filter Eligibility', 'Test Scenario Title': 'Dashboard client list filters by eligibility status', 'Precondition': 'Dashboard displays client list', 'Test Data': 'Statuses: [Eligible, Ineligible, Renewal Due]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open dashboard', "Select filter 'Eligible'", 'Verify only eligible clients are shown'], 'Expected Result': 'Filtered client list matches selected eligibility status.', 'Dependent Module/Process': 'Dashboard Filtering'}, {'Test Case ID': 'US6_TC6', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Track Eligibility Changes', 'Test Scenario Title': 'Eligibility dashboard records audit trail entries for status changes', 'Precondition': 'Eligibility status updated for a client by authorized process/user', 'Test Data': 'Client: Ella Green, Status before: Eligible, after: Ineligible', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Update eligibility status for Ella Green', 'Review audit trail/log for corresponding dashboard entry'], 'Expected Result': 'Audit log entry created with user, timestamp, previous and new status. Traceable for compliance.', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>This user story ensures that Case Managers receive timely, system-generated alerts when a client's eligibility is about to expire, enabling proactive redeterminations and service continuity.</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['Simulate eligibility status expiring in 30 days; verify alert appears for correct client', 'Verify alert timing (exactly 30 days before renewal date)', 'Dismiss an alert and check it is removed from view', 'Verify alerts appear for all clients with expiring eligibility', 'Test that no alert is generated when eligibility is not close to expiring']</t>
+          <t>As a Case Manager, I want to receive alerts when a client's eligibility is about to expire so that I can initiate redetermination. - System-generated alerts 30 days before expiration.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['Eligibility expires in less than 30 days (should alert immediately)', 'Eligibility with no expiry date', 'Multiple clients expiring the same day', 'Alert conditions overlap due to rapid changes']</t>
+          <t>When a client's eligibility is 30 days from expiration, the system automatically generates and delivers an alert to the assigned Case Manager.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['Alert details link back to dashboard (Story 6)', 'Eligibility and renewal date accuracy']</t>
+          <t>[{'Test Case ID': 'TC_07_01', 'Brief Description': 'System sends alert to Case Manager 30 days before eligibility expiration.'}, {'Test Case ID': 'TC_07_02', 'Brief Description': 'Verify no alert is sent if no eligibility is expiring within 30 days.'}, {'Test Case ID': 'TC_07_03', 'Brief Description': 'Case Manager receives only relevant alerts (permission check).'}, {'Test Case ID': 'TC_07_04', 'Brief Description': 'System does not duplicate alerts for the same case.'}, {'Test Case ID': 'TC_07_05', 'Brief Description': 'Audit log of alert generation and delivery is maintained.'}]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['Story 6: Dashboard eligibility and renewal date display', 'Story 34: Client status updates', 'Story 23: Any batch alert-related features']</t>
+          <t>[{'Test Case ID': 'TC_07_01', 'EPIC': 'Case Eligibility Management', 'Feature': 'Notifications &amp; Alerts', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'System Notification', 'Activity Title': 'Generate Eligibility Expiration Alert', 'Test Scenario Title': 'Happy Path: Alert generated and delivered', 'Precondition': 'Client eligibility record exists with an expiration date 30 days in the future; Case Manager is assigned.', 'Test Data': "{ 'client_id': '12345', 'eligibility_expiry': '2024-07-30', 'case_manager_id': 'CM_01'}", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["Set a client's eligibility expiration to 30 days in the future.", 'Wait for system batch job/cron to process expiration checks.', 'Login as assigned Case Manager.', 'Navigate to alert dashboard/inbox.'], 'Expected Result': "Alert regarding client's upcoming eligibility expiration is visible to the Case Manager.", 'Dependent Module/Process': 'Eligibility Management, Notification Service'}, {'Test Case ID': 'TC_07_02', 'EPIC': 'Case Eligibility Management', 'Feature': 'Notifications &amp; Alerts', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'System Notification', 'Activity Title': 'Filter Expiry Dates', 'Test Scenario Title': 'No alert for ineligible records', 'Precondition': 'All eligibility expiration dates are more than 30 days away.', 'Test Data': "{ 'client_id': '54321', 'eligibility_expiry': '2024-09-01', 'case_manager_id': 'CM_02'}", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Set all client records to have expiration &gt;30 days from today.', 'Wait for system batch job/cron.', 'Login as Case Manager.', 'Check for alerts.'], 'Expected Result': 'No new alerts are generated for eligibility expiration.', 'Dependent Module/Process': 'Eligibility Management, Notification Service'}, {'Test Case ID': 'TC_07_03', 'EPIC': 'Case Eligibility Management', 'Feature': 'Permissions', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'Security and Permissions', 'Activity Title': 'Alert Access Restriction', 'Test Scenario Title': 'Only assigned Case Manager receives alert', 'Precondition': 'Multiple Case Managers exist; one is assigned to client.', 'Test Data': "{ 'client_id': '202303', 'eligibility_expiry': '2024-07-30', 'case_manager_id': 'CM_01', 'other_manager_id': 'CM_03' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign client to Manager A.', 'Wait for alert generation.', 'Log in as Manager A: Check for alert.', 'Log in as Manager B: Check for alert.'], 'Expected Result': 'Only assigned Case Manager (Manager A) receives the alert; others do not.', 'Dependent Module/Process': 'User Management'}, {'Test Case ID': 'TC_07_04', 'EPIC': 'Case Eligibility Management', 'Feature': 'Notifications &amp; Alerts', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'System Notification', 'Activity Title': 'Alert Deduplication', 'Test Scenario Title': 'No duplicate alerts for same case', 'Precondition': 'Eligibility expiration date is not changed repeatedly.', 'Test Data': "{ 'client_id': '303404', 'eligibility_expiry': '2024-07-30', 'case_manager_id': 'CM_04' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Trigger alert generation.', 'Check alert history for the case.', 'Trigger cycle again without changing expiry date.', 'Check if additional alert is sent.'], 'Expected Result': 'Only one alert is sent per case for a given eligibility expiration date.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_07_05', 'EPIC': 'Case Eligibility Management', 'Feature': 'Compliance', 'User Story': '7', 'Business Process': 'Audit &amp; Reporting', 'Sub-Process Title': 'Logging', 'Activity Title': 'Alert Audit Trail', 'Test Scenario Title': 'Audit log of alert', 'Precondition': 'Alerts are being generated.', 'Test Data': "{ 'alert_id': 'A991', 'case_manager_id': 'CM_05', 'timestamp': '2024-06-01T09:30:00Z' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Trigger alert.', 'Access audit logs.', 'Verify alert generation and delivery is recorded.'], 'Expected Result': 'Alert event is traceable with timestamp, alert type, recipient, and client reference in audit log.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>This user story focuses on enabling Case Workers to upload various supporting documents (PDF, images, scans) to a client's case, ensuring comprehensive and compliant record-keeping.</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>["Upload valid PDF to a case and confirm it's attached/displayed", 'Upload valid image (JPEG/PNG) and scanned image and verify', 'Attempt upload of unsupported formats (e.g., .exe, .docx) and confirm rejection', "Delete an uploaded document and ensure it's removed", 'Verify upload size restrictions (if any) are enforced']</t>
+          <t>As a Case Worker, I want to upload supporting documents to a case so that I can maintain complete records. - Allow PDF, image, and scanned uploads to case files.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['Upload large files near maximum size', 'Corrupted image or PDF upload', 'Duplicate file uploads (same file name/content)', 'Uploading no file (empty upload)']</t>
+          <t>A Case Worker successfully uploads a PDF, image, or scanned file to an assigned case file, and the documents become accessible via the client's record.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['File access from other related functions (Stories 11, 12, 17, 21, 24, 29, 39)', 'Document visibility in audit/history (if implemented)']</t>
+          <t>[{'Test Case ID': 'TC_08_01', 'Brief Description': 'Case Worker uploads a supported document (PDF, image, scan) to a case.'}, {'Test Case ID': 'TC_08_02', 'Brief Description': 'Attempt to upload an unsupported file type.'}, {'Test Case ID': 'TC_08_03', 'Brief Description': 'Case Worker with insufficient permissions tries to upload a document.'}, {'Test Case ID': 'TC_08_04', 'Brief Description': 'Uploaded document is linked to the correct case and visible for audit.'}, {'Test Case ID': 'TC_08_05', 'Brief Description': 'Data privacy and compliance validation for file upload and storage.'}]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['Story 1: Case file creation/attachment', 'Stories 11, 12: Case document workflows', 'Story 17: Document management', 'Story 21: User access to documents', 'Story 24: Multi-file management', 'Story 29: Case closure with docs', 'Story 39: Reporting including document presence']</t>
+          <t>[{'Test Case ID': 'TC_08_01', 'EPIC': 'Case Document Management', 'Feature': 'File Upload', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Upload Supported Documents', 'Test Scenario Title': 'Happy Path: Supported document upload', 'Precondition': 'Case Worker is assigned to an active case; case file exists.', 'Test Data': "{ 'case_id': 'C123', 'user_id': 'CW_01', 'file': 'income_verification.pdf' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to assigned client's case file.", "Click 'Upload Document'.", 'Select a supported file (e.g., income_verification.pdf).', "Click 'Submit'."], 'Expected Result': "File is uploaded, linked to case, visible in client's documents.", 'Dependent Module/Process': 'Document Storage, Case Management'}, {'Test Case ID': 'TC_08_02', 'EPIC': 'Case Document Management', 'Feature': 'File Upload', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Reject Unsupported File Type', 'Test Scenario Title': 'Negative: Unsupported file type upload', 'Precondition': 'Case Worker tries to upload .exe file.', 'Test Data': "{ 'case_id': 'C124', 'user_id': 'CW_01', 'file': 'malware.exe' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to case file.', "Click 'Upload Document'.", 'Select file with unsupported extension (malware.exe).', "Click 'Submit'."], 'Expected Result': 'System prevents upload; error message displayed.', 'Dependent Module/Process': 'File Validation'}, {'Test Case ID': 'TC_08_03', 'EPIC': 'Case Document Management', 'Feature': 'Permissions', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict Upload Permissions', 'Test Scenario Title': 'Negative: Insufficient permissions', 'Precondition': 'User with read-only role accesses case.', 'Test Data': "{ 'case_id': 'C125', 'user_id': 'CW_ReadOnly' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker (read-only)', 'Detailed Test Steps': ['Login as Case Worker (read-only).', 'Navigate to case file.', "Check for presence of 'Upload Document' button."], 'Expected Result': "'Upload Document' button not present or access is denied on upload attempt.", 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'TC_08_04', 'EPIC': 'Case Document Management', 'Feature': 'Compliance &amp; Traceability', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Audit', 'Activity Title': 'Record Upload in Audit Log', 'Test Scenario Title': 'Document audit logging', 'Precondition': 'File uploaded successfully.', 'Test Data': "{ 'case_id': 'C126', 'user_id': 'CW_02', 'file': 'residence_proof.jpg' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Upload a document as Case Worker.', 'Access audit logs.', 'Search for the upload event.'], 'Expected Result': 'Audit log lists the file upload with timestamp, user, and case reference.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC_08_05', 'EPIC': 'Case Document Management', 'Feature': 'Compliance', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Data Privacy', 'Activity Title': 'Validate Upload Security', 'Test Scenario Title': 'Compliance and secure storage', 'Precondition': 'System configured for compliance (e.g., HIPAA).', 'Test Data': "{ 'case_id': 'C127', 'user_id': 'CW_03', 'file': 'medical_record.pdf' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Upload a sensitive document.', 'Attempt unauthorized access to the document.', 'Review encryption in storage.', 'Check compliance policy audit report.'], 'Expected Result': 'Only authorized users access the document; document is encrypted as per policy and access recorded in logs.', 'Dependent Module/Process': 'Security, Compliance Engine, Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Workers can efficiently search for existing applicants by name or SSN, utilizing fuzzy matching, to prevent duplicate entries and maintain data integrity.</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Search applicants by full name (exact match), verify results', 'Search by partial name (fuzzy match), confirm correct candidates returned', 'Search by SSN, verify exact matching only', 'No results for non-existent SSN/name', 'Attempt search with special characters']</t>
+          <t>As a Case Worker, I want to search for existing applicants by name or SSN so that I can avoid duplicate entries. - Search functionality with fuzzy matching.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['Applicants with same name, different SSN', 'SSN with leading zeros', 'Name fields with accents or non-Latin characters', 'Very large result set for common names']</t>
+          <t>Case Worker searches by name or SSN and receives relevant applicant records, including close/fuzzy matches, reducing the risk of duplicate entries.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['Duplicate-detection tests related to Story 1 or Story 2', 'Check proper search matching for Story 31']</t>
+          <t>[{'Test Case ID': 'TC_09_01', 'Brief Description': 'Search applicant by full name and receive expected results.'}, {'Test Case ID': 'TC_09_02', 'Brief Description': 'Search applicant by SSN and receive exact match results.'}, {'Test Case ID': 'TC_09_03', 'Brief Description': 'Fuzzy search returns partial or similar matches for misspelled names.'}, {'Test Case ID': 'TC_09_04', 'Brief Description': 'System prevents creation of duplicate applicant when a match is found.'}, {'Test Case ID': 'TC_09_05', 'Brief Description': 'Access control: Only authorized users can access applicant search functionality.'}]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['Story 1: Case creation/duplicate check', 'Story 2: New applicant workflows', 'Story 31: Applicant data retrieval or display']</t>
+          <t>[{'Test Case ID': 'TC_09_01', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Search by Name', 'Test Scenario Title': 'Full name search - happy path', 'Precondition': "Applicant 'John Smith' exists in system.", 'Test Data': "{ 'applicant_name': 'John Smith' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'Add Applicant' workflow.", "Enter full name 'John Smith' in search field.", 'Submit the search.'], 'Expected Result': "Applicant record for 'John Smith' appears in search results.", 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_09_02', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Search by SSN', 'Test Scenario Title': 'SSN search - happy path', 'Precondition': "Applicant with SSN '123-45-6789' exists.", 'Test Data': "{ 'ssn': '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'Add Applicant' workflow.", "Enter SSN '123-45-6789' in search field.", 'Submit the search.'], 'Expected Result': 'Applicant record appears with full details.', 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_09_03', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Fuzzy Search', 'Test Scenario Title': 'Partial/misspelled name returns fuzzy matches', 'Precondition': "Applicants with similar names exist (e.g., 'Jon Smyth').", 'Test Data': "{ 'applicant_name': 'Jonh Smit' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'Add Applicant'.", "Enter misspelled name 'Jonh Smit'.", 'Submit the search.'], 'Expected Result': "Search results include close matches like 'John Smith', 'Jon Smyth'.", 'Dependent Module/Process': 'Search Engine'}, {'Test Case ID': 'TC_09_04', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Prevent Duplicate Creation', 'Test Scenario Title': 'Prevent duplicate when match exists', 'Precondition': 'Applicant with provided name or SSN exists.', 'Test Data': "{ 'applicant_name': 'John Smith', 'ssn': '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Search for applicant by SSN/name.', 'Try to create new applicant record with same details.'], 'Expected Result': 'System blocks creation, shows error about duplicate entry.', 'Dependent Module/Process': 'Applicant Database, Duplicate Check'}, {'Test Case ID': 'TC_09_05', 'EPIC': 'Applicant Management', 'Feature': 'Permissions', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict Search Access', 'Test Scenario Title': 'Only authorized users can search applicants', 'Precondition': 'User is not in authorized role (e.g., guest).', 'Test Data': "{ 'user_id': 'Guest_01' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Not authorized', 'Detailed Test Steps': ['Login as unauthorized user.', 'Try to access applicant search screen.'], 'Expected Result': 'Applicant search functionality is not accessible.', 'Dependent Module/Process': 'User Role Management'}]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>This user story focuses on enabling Case Managers to efficiently distribute cases among team members, ensuring workload balance and providing both automated assignment rules and manual override capabilities.</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Assign case to team member with lowest workload, verify assignment', 'Test manual override to assign a case irrespective of workload', 'Re-assign case and ensure update reflected in all views', 'Verify reassignment history/tracking if implemented', 'Test case assignment on edge (e.g., team member at max workload)']</t>
+          <t>As a Case Manager, I want to assign cases to team members based on workload so that we can balance responsibilities. - Case assignment rules and manual override options.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['No team members available', 'Case assigned to member on leave (should block or warn)', 'Multiple team members with identical workload', 'Manual override used repeatedly for same case']</t>
+          <t>Case Manager logs in, system suggests case assignments based on current team workload, Manager reviews and accepts the automated assignment, or manually overrides to reassign cases as needed.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['Assignment logic applied in Stories 28, 40', 'Consistent update to assignment visible in dashboards and reports']</t>
+          <t>[{'Test Case ID': 'TC_10_01', 'Brief Description': 'Automated assignment of new cases using workload rules'}, {'Test Case ID': 'TC_10_02', 'Brief Description': 'Manual override to assign or reassign a case'}, {'Test Case ID': 'TC_10_03', 'Brief Description': 'Error handling when a case is assigned to a non-existent team member'}, {'Test Case ID': 'TC_10_04', 'Brief Description': 'Validation of permissions for assignment and override'}]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['Story 28: Team management assignments', 'Story 40: Any workload calculations or team member dashboards']</t>
+          <t>[{'Test Case ID': 'TC_10_01', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Automated Assignment', 'Test Scenario Title': 'System automatically assigns cases according to workload balancing rules', 'Precondition': 'Case Manager is logged in; at least one unassigned case exists; workload metrics available for all team members.', 'Test Data': '3 unassigned cases; team member workloads: Alice-5, Bob-2, Carol-3', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager navigates to unassigned cases view.', "Clicks 'Auto Assign' button.", 'System calculates current workloads for team members.', 'System assigns cases to team members with lowest workload.', 'Assignment details are displayed for review.'], 'Expected Result': 'Cases assigned to Bob (lowest workload first), followed by Carol, then Alice; assignment log updated.', 'Dependent Module/Process': 'Team member data; Case Management module'}, {'Test Case ID': 'TC_10_02', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Manual Override', 'Test Scenario Title': 'Case Manager manually overwrites a case assignment', 'Precondition': 'A case is already assigned to a team member.', 'Test Data': 'Case #123 assigned to Bob.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager selects Case #123.', "Clicks 'Reassign'.", 'Chooses Alice from the team list.', 'Confirms reassignment.'], 'Expected Result': 'Case #123 is now assigned to Alice; audit trail/log records change with timestamp and user info.', 'Dependent Module/Process': 'Case Management; Audit log'}, {'Test Case ID': 'TC_10_03', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Error Handling', 'Test Scenario Title': 'System prevents assignment to non-existent or inactive team member', 'Precondition': 'Case Manager attempts to assign a case.', 'Test Data': "Team member 'Dave' does not exist or is inactive.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager selects an unassigned case.', "Attempts to assign case to 'Dave'."], 'Expected Result': "Error message: 'Selected team member is not available.' Assignment prevented.", 'Dependent Module/Process': 'Access control; Team directory'}, {'Test Case ID': 'TC_10_04', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Only Case Managers can assign/reassign cases', 'Precondition': 'User is logged in as a non-Case Manager role (e.g., Case Worker).', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker attempts to assign or reassign a case.'], 'Expected Result': "UI controls are hidden/disabled or error: 'Access Denied.' No changes are committed.", 'Dependent Module/Process': 'User roles/permissions'}]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Case Workers can request missing documents from applicants, generating secure email or SMS notifications with upload links to facilitate efficient document collection.</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['Verify that a case worker can initiate a document request for an applicant.', 'Verify that an email notification is generated with a secure upload link and sent to the applicant.', 'Verify that an SMS notification is generated with a secure upload link and sent to the applicant.', 'Validate that generated upload links are unique and associated with the correct applicant and document request.', 'Verify that the upload link expires or becomes invalid after a specified time or after the document is uploaded.']</t>
+          <t>As a Case Worker, I want to send document requests to applicants so that they can upload missing items. - Generate email or SMS notifications with secure upload links.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['Applicant with invalid or missing contact information (email/SMS).', 'Attempt to reuse an expired or already used upload link.', 'Simultaneous document requests for multiple items for the same applicant.', 'Case worker cancels document request after notification sent.']</t>
+          <t>Case Worker selects missing documents, system generates and sends notification (email/SMS) with a secure upload link to the applicant.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['Verify document requests are correctly reflected in related document checklists/tracking (Story 12).', 'Ensure notifications are logged in communication logs (Story 14, if applicable for case workers).']</t>
+          <t>[{'Test Case ID': 'TC_11_01', 'Brief Description': 'Send document request via email with secure upload link'}, {'Test Case ID': 'TC_11_02', 'Brief Description': 'Send document request via SMS with secure upload link'}, {'Test Case ID': 'TC_11_03', 'Brief Description': 'Attempt to send request with missing contact info'}, {'Test Case ID': 'TC_11_04', 'Brief Description': 'Permission validation — Case Worker only'}]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['5: Applicant document upload functionality.', '8: Notification system.', '12: Document submission tracking.', '17: Overall applicant communications.', '21: Security for uploaded documents.']</t>
+          <t>[{'Test Case ID': 'TC_11_01', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send Email Request', 'Test Scenario Title': 'Case Worker sends a document request via email', 'Precondition': 'Applicant profile has a valid email.', 'Test Data': 'Applicant: John Doe, Missing documents: Proof of Address, Email: john@example.com', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker selects applicant with missing documents.', "Selects 'Send Document Request (Email)'.", 'Chooses missing documents to request.', 'Confirms and sends request.'], 'Expected Result': 'Applicant receives an email with secure upload link listing requested documents; system logs notification sent.', 'Dependent Module/Process': 'Email server; Applicant portal'}, {'Test Case ID': 'TC_11_02', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send SMS Request', 'Test Scenario Title': 'Case Worker sends a document request via SMS', 'Precondition': 'Applicant profile has a valid mobile number.', 'Test Data': 'Applicant: Jane Smith, Missing: ID Card, Mobile: +1234567890', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker selects applicant with missing document.', "Selects 'Send Document Request (SMS)'.", 'Chooses missing document.', 'Confirms and sends request.'], 'Expected Result': 'Applicant receives SMS with secure upload link; notification is logged.', 'Dependent Module/Process': 'SMS gateway; Applicant portal'}, {'Test Case ID': 'TC_11_03', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send Document Request', 'Test Scenario Title': 'Error handling when contact information is missing', 'Precondition': 'Applicant lacks valid email and mobile.', 'Test Data': 'Applicant: Bob Lee, No contact info', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker selects applicant missing required contact details.', 'Attempts to send document request.'], 'Expected Result': "System displays error: 'No valid contact information available. Cannot send request.'", 'Dependent Module/Process': 'Applicant directory'}, {'Test Case ID': 'TC_11_04', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Only Case Worker roles can send document requests', 'Precondition': 'User is not a Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Applicant logs in and tries to use the document request function.'], 'Expected Result': "'Send Document Request' option is not available or an 'Access Denied' error appears.", 'Dependent Module/Process': 'User roles/permissions'}]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Case Workers monitor document submission via an up-to-date checklist, with visual indicators reflecting current status for each required document. This enables timely follow-up for pending items.</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['Verify that all requested documents are listed in the checklist for each applicant.', "Validate that status indicators correctly show 'pending', 'submitted', 'approved', or 'rejected' for each document.", 'Verify case worker can filter or sort checklist by status.', 'Ensure status is updated when applicant uploads a document via secure link.', 'Verify that the checklist refreshes in real-time or after refresh when there is an update.']</t>
+          <t>As a Case Worker, I want to track document submission status so that I can follow up on pending items. - Document checklist with status indicators.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['Document is uploaded with the wrong file type or corrupted file.', 'Simultaneous uploads for the same document type.', 'Checklist shows extra or missing document types not relevant for an applicant.']</t>
+          <t>Case Worker views applicant profile, sees a checklist with status (Submitted, Pending, Rejected) for each required document, enabling targeted follow-up.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['Test submission tracking after sending document requests (Story 11).']</t>
+          <t>[{'Test Case ID': 'TC_12_01', 'Brief Description': 'Display document checklist with status indicators'}, {'Test Case ID': 'TC_12_02', 'Brief Description': 'Status updates after document upload'}, {'Test Case ID': 'TC_12_03', 'Brief Description': 'Handle status for rejected or invalid submissions'}, {'Test Case ID': 'TC_12_04', 'Brief Description': 'Permission validation — Case Worker only'}]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['5: Applicant document upload.', '8: Notification triggers for document updates.', '11: Document request and notification logic.', '17: Follow-up communication triggers.', '21: Document security and access.']</t>
+          <t>[{'Test Case ID': 'TC_12_01', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'View Status Checklist', 'Test Scenario Title': 'Case Worker sees checklist with status for each required document', 'Precondition': 'Applicant has a list of required documents in the system.', 'Test Data': 'Applicant: Emma, Required: Proof of Residence (Submitted), Proof of Income (Pending)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker opens applicant profile.', "Navigates to 'Documents' section.", 'Reviews checklist and status indicators.'], 'Expected Result': 'Checklist displays all required documents, each with a clear status indicator (e.g., color-coded, icons, text labels).', 'Dependent Module/Process': 'Document database; Applicant profile'}, {'Test Case ID': 'TC_12_02', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'Status Update', 'Test Scenario Title': 'Checklist updates after applicant uploads a document', 'Precondition': "A required document is marked as 'Pending'.", 'Test Data': 'Applicant: Alex, Uploads ID Card document.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Applicant uploads ID Card via secure link.', 'Case Worker refreshes or revisits checklist.'], 'Expected Result': "Status for ID Card changes from 'Pending' to 'Submitted'; timestamp of update visible.", 'Dependent Module/Process': 'Applicant portal; Document Management'}, {'Test Case ID': 'TC_12_03', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'Status Handling', 'Test Scenario Title': 'Checklist indicates rejected/invalid document submissions', 'Precondition': 'Applicant uploaded a document that was rejected by Case Worker.', 'Test Data': "Proof of Income marked as 'Rejected' for Applicant: Lily.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker reviews submitted document.', "Marks submission as 'Rejected' or 'Invalid'.", 'Checklist reflects rejection status, optionally with reason.'], 'Expected Result': "'Rejected' or 'Invalid' status shown, with rejection note/reason visible.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'TC_12_04', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Only Case Workers can see full document status checklist', 'Precondition': 'User is not a Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Applicant logs in and tries to access full checklist/status view.'], 'Expected Result': 'Applicant can only see their own submissions and statuses, not staff-level checklist details.', 'Dependent Module/Process': 'User roles/permissions'}]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>This user story focuses on equipping case workers with a tool to redact sensitive information (such as SSNs and addresses) from uploaded documents to ensure privacy and compliance with data protection regulations.</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Verify that the redaction tool is available for all uploaded documents.', 'Test that user can select and redact sensitive information like SSN, address, etc.', 'Validate that redacted areas cannot be revealed after saving.', 'Verify that the redacted document is used in place of the original for sharing/viewing.', 'Check audit logs for all redaction actions.']</t>
+          <t>As a Case Worker, I want to redact sensitive information in uploaded documents so that I can protect privacy.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['Uploaded documents with unusual formats or encrypted text.', 'Redacting the entire document or attempting to redact non-text content.', 'Multiple redactions made/removed before saving.']</t>
+          <t>A case worker selects a document, uses the redaction tool to mask sensitive information (like SSNs, addresses), saves the redacted version, and confirms that the masked information is not visible in the output.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['Ensure that redacted documents are correctly referenced in document checklists/tracking (Story 12).', 'Verify redacted documents are not exposed in notifications or document links (Story 11, 21).']</t>
+          <t>[{'Test Case ID': 'TC13-1', 'Brief Description': 'Redact SSN and addresses in a PDF document (happy path)'}, {'Test Case ID': 'TC13-2', 'Brief Description': 'Attempt redaction as an unauthorized user (negative)'}, {'Test Case ID': 'TC13-3', 'Brief Description': 'Test auto-detection failure when there is no sensitive data (negative)'}, {'Test Case ID': 'TC13-4', 'Brief Description': 'Audit log is generated for each redaction (compliance)'}]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['8: Uploading and accessing applicant documents.', '21: Document security, access controls.', '29: Workflows involving sensitive data.']</t>
+          <t>[{'Test Case ID': 'TC13-1', 'EPIC': 'Document Management', 'Feature': 'Redaction Tool', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redact Sensitive Information', 'Activity Title': 'Manual and auto redaction', 'Test Scenario Title': 'Happy path—successful redaction by authorized case worker', 'Precondition': 'Case worker is logged in and has upload permission; document with sensitive fields (SSN/address) is present.', 'Test Data': 'PDF file containing fake SSNs and addresses.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to the client’s_uploaded_doc page.', 'Open the uploaded document in the redaction tool interface.', "Select 'Auto-detect sensitive fields'.", 'Verify that detected fields (SSNs, addresses) are highlighted.', 'Apply redaction to all highlighted fields.', 'Save and view the redacted document.'], 'Expected Result': 'All sensitive data is obscured in the saved document; only allowed information is visible.', 'Dependent Module/Process': 'Document Management, Security/Compliance'}, {'Test Case ID': 'TC13-2', 'EPIC': 'Document Management', 'Feature': 'Redaction Tool', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redact Sensitive Information', 'Activity Title': 'Permission validation', 'Test Scenario Title': 'Negative test—unauthorized user attempts redaction', 'Precondition': 'User is logged in as a Clerk (no redact permission), document is uploaded.', 'Test Data': 'Any document.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Clerk', 'Detailed Test Steps': ['Navigate to the document page.', 'Attempt to launch the redaction tool.'], 'Expected Result': "Error message displayed: 'You do not have permission to redact documents.' No access to tool.", 'Dependent Module/Process': 'Authorization'}, {'Test Case ID': 'TC13-3', 'EPIC': 'Document Management', 'Feature': 'Redaction Tool', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redact Sensitive Information', 'Activity Title': 'Auto-detection validation', 'Test Scenario Title': 'Auto-detect finds no sensitive info', 'Precondition': 'Case worker logged in, document with no sensitive information uploaded.', 'Test Data': 'PDF with no PII/SSN/address.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open document in redaction tool.', "Click 'Auto-detect sensitive fields'."], 'Expected Result': 'No fields are highlighted. User can proceed manually. No accidental redaction.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'TC13-4', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Redaction Audit', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redaction Audit', 'Activity Title': 'Redaction event logging', 'Test Scenario Title': 'Audit log generated for every redaction', 'Precondition': 'Case worker completes redaction.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Redact any document using the tool.', 'Check the audit logs for a new entry referencing redaction action.'], 'Expected Result': 'Each redaction event is logged with user ID, timestamp, redaction type, and document reference.', 'Dependent Module/Process': 'Audit, Compliance, Document Management'}]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>This user story emphasizes providing case managers with communication logs embedded in each client's case profile, including records of emails, calls, and messages, to offer a holistic case timeline.</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['Verify that all emails, calls, and messages with a client are logged in the case timeline.', 'Check that logs include timestamp, type, sender/recipient, and summary/details.', 'Confirm that logs are correctly associated with the right case/client.', 'Test searching/filtering log entries by date, type, or participant.', 'Verify permissions: only authorized users can view/edit communication logs.']</t>
+          <t>As a Case Manager, I want to view communication logs with clients so that I can understand case history.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['Bulk communication events occurring close in time.', 'Missing or partial log data (e.g., call with no duration recorded).', 'Edit/delete attempts on logs; confirm audit or prevention.']</t>
+          <t>A case manager opens a case profile, selects the ‘Communication Logs’ tab, and reviews a chronological log of all correspondence with that client.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>['Check that document request notifications (Story 11) and tracking updates (Story 12) are logged when communication is sent/received, if integrated.']</t>
+          <t>[{'Test Case ID': 'TC14-1', 'Brief Description': 'Happy path—viewing logs for a client'}, {'Test Case ID': 'TC14-2', 'Brief Description': 'Negative—case manager tries to access logs for a case they do not manage'}, {'Test Case ID': 'TC14-3', 'Brief Description': 'API integration—ensure all emails, calls, messages are logged'}, {'Test Case ID': 'TC14-4', 'Brief Description': 'Compliance—ensure logs are immutable and audit trailed'}]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['6: General case notes and history logging.', '20: Related communication/logging modules.']</t>
+          <t>[{'Test Case ID': 'TC14-1', 'EPIC': 'Case Management', 'Feature': 'Communication Logs', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'View Communication History', 'Activity Title': 'Access communication logs', 'Test Scenario Title': 'Case manager views communication logs in the timeline (happy path)', 'Precondition': 'User is logged in as Case Manager and manages the selected case.', 'Test Data': 'Case with email, call, and message records.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to the case file.', "Click on the 'Communication Logs' tab.", 'Review the entries presented in reverse chronological order.'], 'Expected Result': 'All correspondence entries (emails, calls, messages) for the client are shown with correct details.', 'Dependent Module/Process': 'Case Management, Correspondence Subsystem'}, {'Test Case ID': 'TC14-2', 'EPIC': 'Case Management', 'Feature': 'Communication Logs', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'View Communication History', 'Activity Title': 'Permissions validation', 'Test Scenario Title': 'Case manager attempts to access communication logs for an unrelated case', 'Precondition': 'Case Manager does not manage/own the case.', 'Test Data': 'An unrelated case ID.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Attempt to access the 'Communication Logs' tab of an unassigned case."], 'Expected Result': 'Access denied message or no logs are available; sensitive log information is not exposed.', 'Dependent Module/Process': 'Case Management, Authorization'}, {'Test Case ID': 'TC14-3', 'EPIC': 'Case Management', 'Feature': 'Communication Logs', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'View Communication History', 'Activity Title': 'API Integration', 'Test Scenario Title': 'APIs correctly update log entries for different communication types', 'Precondition': 'Case exists. API integration for email/call/message logging is active.', 'Test Data': 'Trigger one email, one call, one message via API.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'System/Case Manager', 'Detailed Test Steps': ['Trigger sending an email to the client via the system.', 'Simulate an inbound call to the call logger API.', 'Send an internal message via messaging API.', 'Open case communication logs.'], 'Expected Result': 'Each action results in a log entry accurately reflecting the communication, timestamp, and user.', 'Dependent Module/Process': 'Correspondence, Telephony, Messaging APIs'}, {'Test Case ID': 'TC14-4', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Audit Trail', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'Log Immutability', 'Activity Title': 'Communication log audit compliance', 'Test Scenario Title': 'Audit log for communication entries is generated and modification is prevented', 'Precondition': 'Log entries exist for a case.', 'Test Data': 'Any communication log entry.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'Case Manager/Auditor', 'Detailed Test Steps': ['Attempt to edit or delete a communication log entry.', 'Check the system audit trail.'], 'Expected Result': 'Communication log entries are immutable and attempts to change them are logged with user ID and timestamp.', 'Dependent Module/Process': 'Audit Module, Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>This user story ensures case managers are able to coordinate with other agencies in cases involving dual eligibility by sharing notes and case flags, improving benefit delivery.</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['Verify that a case manager can create and view notes shared with other agencies.', 'Check that shared case flags can be added, edited, and removed.', 'Ensure shared notes are only visible to authorized agency staff.', 'Test notifications or visibility toggles when notes/flags are changed.', 'Verify accurate audit trail for all inter-agency actions.']</t>
+          <t>As a Case Manager, I want to coordinate with other agencies for dual eligibility cases so that clients receive all benefits.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['Multiple agencies making concurrent updates to shared notes.', 'Attempt to access/edit notes by unauthorized users/agencies.', 'Duplicate shared case flags for the same reason.']</t>
+          <t>A case reaches dual-eligibility status, the case manager adds inter-agency notes and sets shared flags, and these updates are visible to all collaborating parties.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'Test Case ID': 'TC15-1', 'Brief Description': 'Add inter-agency note and shared flag in dual-eligible case'}, {'Test Case ID': 'TC15-2', 'Brief Description': 'Negative—user from another agency attempts to edit unauthorized note'}, {'Test Case ID': 'TC15-3', 'Brief Description': 'Integration—note and flag sync across agencies/systems'}, {'Test Case ID': 'TC15-4', 'Brief Description': 'Compliance—logging and tracking all inter-agency actions'}]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['None explicitly listed, but may impact general note-sharing or case visibility features.']</t>
+          <t>[{'Test Case ID': 'TC15-1', 'EPIC': 'Case Collaboration', 'Feature': 'Dual Eligibility', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Inter-Agency Communication', 'Activity Title': 'Add notes and shared flags', 'Test Scenario Title': 'Case manager successfully adds an inter-agency note and flag (happy path)', 'Precondition': 'Case is flagged as dual-eligible. Logged in as authorized case manager.', 'Test Data': 'Dual-eligible case record.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open the dual-eligible case profile.', "Navigate to the 'Inter-Agency Notes' section.", 'Add a note referencing coordination details.', 'Set the shared flag (e.g., "Needs cross-agency review").', 'Save changes.'], 'Expected Result': 'Note and flag are persisted. Others with permission see them in real time.', 'Dependent Module/Process': 'Case Management, Inter-Agency Portal'}, {'Test Case ID': 'TC15-2', 'EPIC': 'Case Collaboration', 'Feature': 'Dual Eligibility', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Inter-Agency Communication', 'Activity Title': 'Permissions validation', 'Test Scenario Title': 'User from another agency tries to edit a note not their own', 'Precondition': 'Inter-agency note created by Agency A, user logged in as Agency B’s manager.', 'Test Data': 'Note created by Agency A.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager from Agency B', 'Detailed Test Steps': ['Navigate to the dual-eligible case profile.', 'Attempt to edit or delete a note authored by Agency A.'], 'Expected Result': 'Action denied. User is unable to change notes not their own; error displayed or edit option disabled.', 'Dependent Module/Process': 'Authorization, Inter-Agency Portal'}, {'Test Case ID': 'TC15-3', 'EPIC': 'Case Collaboration', 'Feature': 'Dual Eligibility', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Inter-Agency Communication', 'Activity Title': 'Integration sync', 'Test Scenario Title': 'Inter-agency note and shared flag are correctly synced with external agency systems', 'Precondition': 'Inter-agency note and flag created.', 'Test Data': 'Example note, flag value.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager/API', 'Detailed Test Steps': ['Create note/flag in System 1.', 'Trigger system sync/API push to System 2.', "Verify that the note and flag appear in System 2's dual-case interface."], 'Expected Result': 'Note/flag are present, with correct values and authorship, in all connected systems.', 'Dependent Module/Process': 'API Integration, External Agency System'}, {'Test Case ID': 'TC15-4', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Inter-Agency Coordination Audit', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Track all inter-agency actions', 'Test Scenario Title': 'Audit logging requirements for all actions on dual-eligible cases', 'Precondition': 'Inter-agency notes and flags updated.', 'Test Data': 'Any action (add/edit/delete note or flag).', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager/Auditor', 'Detailed Test Steps': ['Perform actions (add/edit/delete note, toggle flag) as a case manager.', 'Check audit logs for each action.'], 'Expected Result': 'All inter-agency actions are recorded in audit logs, including user ID, timestamp, agency, action type, and old/new values for compliance.', 'Dependent Module/Process': 'Audit, Logging, Case Management, Inter-Agency Portal'}]</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>This user story covers the generation and download of an auto-generated PDF summary report detailing eligibility findings. The summary is intended for submission or presentation to supervisors, requires correct data representation, and must be available only to authorized Case Workers.</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['Verify PDF is generated after triggering summary report for a case.', 'Check that PDF contains all relevant eligibility findings (status, reasons, date, etc.).', 'Validate download functionality of the generated PDF.', 'Ensure PDFs are generated only for authorized users (Case Workers).', 'Test proper naming convention for PDF files.', 'Ensure sensitive information is masked/obfuscated as necessary in the PDF.', 'Verify performance for large or complex cases in summary generation.']</t>
+          <t>16: As a Case Worker, I want to generate a summary report of eligibility findings so that I can present it to supervisors. - Auto-generated PDF summary of case findings.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['Case with no eligibility findings.', 'Case with maximum allowed number of eligibility findings.', 'Case with special characters or international characters in findings.', "Case in a 'deleted' or 'archived' state.", 'User tries to generate PDF for a case they do not have access to.']</t>
+          <t>The Case Worker selects an option to generate a report. The system compiles case data, formats it into a PDF, and makes it available for download or printing. The PDF contains all relevant eligibility findings and is correctly branded.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>['Verify eligibility findings data (source: stories 3, 4, 6, 25, 32, 35) is consistent in the PDF.', 'Cross-validate summary report content with eligibility and outcome data from related features.']</t>
+          <t>[{'Test Case ID': 'TC16.1', 'Brief Description': 'Generate PDF summary for a completed eligibility case (Valid Case Worker, complete data)'}, {'Test Case ID': 'TC16.2', 'Brief Description': 'Attempt PDF generation with incomplete/missing eligibility data'}, {'Test Case ID': 'TC16.3', 'Brief Description': 'Unauthorized user (not a Case Worker) tries to generate summary'}, {'Test Case ID': 'TC16.4', 'Brief Description': 'Verify that the PDF output matches the displayed case findings'}, {'Test Case ID': 'TC16.5', 'Brief Description': 'Verify PDF accessibility and compliance (e.g., Section 508)'}, {'Test Case ID': 'TC16.6', 'Brief Description': 'API endpoint for report generation returns expected response'}]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 25, 32, 35]</t>
+          <t>[{'Test Case ID': 'TC16.1', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'Generate PDF for complete eligibility case as Case Worker', 'Precondition': "User is logged in as Case Worker; case status is 'completed'; eligibility findings exist.", 'Test Data': {'CaseID': 'CASE1234', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Navigate to completed eligibility case (CASE1234)', "Click 'Generate Summary Report'", 'Wait for PDF to be generated', 'Download or preview report'], 'Expected Result': 'PDF is generated/downloaded. Content matches case data. File has correct branding, accessible format, timestamp.', 'Dependent Module/Process': 'Reporting Engine'}, {'Test Case ID': 'TC16.2', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'Handle cases with incomplete eligibility data', 'Precondition': 'User is logged in as Case Worker; case status is incomplete/missing key findings.', 'Test Data': {'CaseID': 'CASE5678', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Navigate to incomplete eligibility case (CASE5678)', 'Attempt to generate summary report'], 'Expected Result': 'System warns user of missing data. PDF is not produced or includes explicit note on missing info.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'TC16.3', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'Access control: Non-Case Worker attempts PDF generation', 'Precondition': 'User is logged in as Supervisor, Client, or other unauthorized role.', 'Test Data': {'CaseID': 'CASE3456', 'UserRole': 'Supervisor'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Login as Supervisor', 'Navigate to eligibility case (CASE3456)', 'Attempt to generate summary report'], 'Expected Result': 'Access denied; feature not available or error displayed.', 'Dependent Module/Process': 'Role-based Access Control'}, {'Test Case ID': 'TC16.4', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'PDF content accuracy and branding', 'Precondition': 'PDF generated for completed case', 'Test Data': {'CaseID': 'CASE1234', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open generated PDF', 'Cross-check data with screen/displayed case findings'], 'Expected Result': 'All data matches, layout meets standards, contains logo/legal statements.', 'Dependent Module/Process': 'PDF Rendering Service'}, {'Test Case ID': 'TC16.5', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'PDF accessibility and compliance check', 'Precondition': 'PDF generated', 'Test Data': {'CaseID': 'CASE1234'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Inspect PDF for accessibility features (tags, searchability, screen reader compatibility)', 'Check for Section 508 or local accessibility compliance'], 'Expected Result': 'PDF meets accessibility requirements.', 'Dependent Module/Process': 'Compliance Module'}, {'Test Case ID': 'TC16.6', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting API', 'Activity Title': 'API-based Generation', 'Test Scenario Title': 'API call returns PDF and correct status', 'Precondition': 'API endpoint available; valid session token.', 'Test Data': {'CaseID': 'CASE1234', 'APIToken': 'VALID_TOKEN'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (API)', 'Detailed Test Steps': ['Submit API request with valid case ID', 'Verify HTTP response code and PDF file in response'], 'Expected Result': 'API returns 200 OK, PDF file is valid.', 'Dependent Module/Process': 'API Gateway'}]</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>This user story ensures that Case Workers receive real-time notifications whenever a client uploads a document. The system must alert the appropriate Case Worker instantly and only for the cases they manage, with proper handling of unauthorized access and notification content.</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Verify notification is triggered when a client uploads a document.', 'Ensure alerts are received in near real-time by assigned Case Worker.', 'Check that link in alert leads to the correct document in the correct case.', 'Validate notifications are sent only to relevant Case Worker(s).', 'Check ability to dismiss/mark alert as read.', 'Ensure notifications appear only for new uploads (not for edits or deletes).']</t>
+          <t>17: As a Case Worker, I want to receive alerts when a document is uploaded by a client so that I can review it promptly. - Real-time notifications for document uploads.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['Multiple documents uploaded simultaneously.', 'Same document re-uploaded.', 'Upload by an unassigned or unverified client.', 'Network or connectivity interruptions during upload.']</t>
+          <t>A client uploads a document linked to their case. The Case Worker assigned receives an immediate alert via the notification channel (in-app, email, or SMS). Notification provides document and client info.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['Test document upload workflow (shared with stories 8, 11, 12, 39).', 'Validate notification system integration for other triggered alerts.']</t>
+          <t>[{'Test Case ID': 'TC17.1', 'Brief Description': 'Case Worker receives notification when client uploads document'}, {'Test Case ID': 'TC17.2', 'Brief Description': 'Case Worker does not receive notification for unrelated case document upload'}, {'Test Case ID': 'TC17.3', 'Brief Description': 'Unauthorized user does not receive document upload alert'}, {'Test Case ID': 'TC17.4', 'Brief Description': 'Notification content and usability (document ID, client info, timestamp)'}, {'Test Case ID': 'TC17.5', 'Brief Description': 'Test delay or failure in notification delivery'}, {'Test Case ID': 'TC17.6', 'Brief Description': 'Notification via API/WebSocket (integration with external notification service)'}]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[8, 11, 12, 39]</t>
+          <t>[{'Test Case ID': 'TC17.1', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Alert Generation', 'Activity Title': 'Client uploads document, Case Worker notified', 'Test Scenario Title': 'Case Worker receives alert for relevant case', 'Precondition': 'Client and Case Worker linked via case assignment.', 'Test Data': {'CaseID': 'CASE2345', 'ClientID': 'CLIENT123', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Client', 'Navigate to case (CASE2345)', 'Upload document (e.g., proof_of_income.pdf)', 'Ensure upload completion', 'Login (switch to) Case Worker assigned to CASE2345', 'Check notifications'], 'Expected Result': 'Case Worker receives real-time alert about document upload with correct info.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'TC17.2', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Alert Filtering', 'Activity Title': 'Only relevant Case Worker notified', 'Test Scenario Title': 'Case Worker is not notified for non-assigned case uploads', 'Precondition': 'Case Worker is *not* assigned to CASE3456.', 'Test Data': {'CaseID': 'CASE3456', 'ClientID': 'CLIENT456', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Client', 'Upload document for CASE3456', 'Login as unrelated Case Worker', 'Check notifications'], 'Expected Result': 'No notification received for unassigned case.', 'Dependent Module/Process': 'Access Control/Assignment Logic'}, {'Test Case ID': 'TC17.3', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Permission Checking', 'Activity Title': 'Notification only sent to authorized users', 'Test Scenario Title': 'Unauthorized user/non-Case Worker does not get notifications', 'Precondition': 'User logged in as Supervisor or Client.', 'Test Data': {'UserRole': 'Supervisor'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor/Client', 'Detailed Test Steps': ['Login as Client/Supervisor', 'Trigger document upload on any case', 'Monitor for notifications'], 'Expected Result': 'No notification appears for unauthorized roles.', 'Dependent Module/Process': 'Notification Filtering'}, {'Test Case ID': 'TC17.4', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Alert Content Verification', 'Activity Title': 'Correctness of alert content', 'Test Scenario Title': 'Notification textual accuracy and completeness', 'Precondition': 'Case Worker receives document upload alert.', 'Test Data': {'CaseID': 'CASE2345', 'DocName': 'proof_of_income.pdf'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Check notification content after upload', 'Verify presence of document name, upload time, client ID'], 'Expected Result': 'Alert details are accurate and complete.', 'Dependent Module/Process': 'Notification Formatting'}, {'Test Case ID': 'TC17.5', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Notification Delivery', 'Activity Title': 'Test response to notification service outage or delay', 'Test Scenario Title': 'Simulate notification delay/failure', 'Precondition': 'Notification system integration enabled.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger document upload', 'Simulate delay or downtime in notification service', 'Observe case worker notification panel'], 'Expected Result': 'Notifications delayed, error logged or fallback path invoked. No duplicate/malformed alerts.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC17.6', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'API/WebSocket Integration', 'Activity Title': 'Notification via API/WebSocket', 'Test Scenario Title': 'Verify notification API/WebSocket message arrives', 'Precondition': 'API endpoint available, Case Worker session WebSocket open.', 'Test Data': {'CaseID': 'CASE2345'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (API)', 'Detailed Test Steps': ['Initiate WebSocket/API listener as Case Worker', 'Upload document as Client for linked case', 'Validate receipt of message'], 'Expected Result': 'Notification payload received in real time.', 'Dependent Module/Process': 'Notification API/WebSocket Service'}]</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>This user story supports workload tracking by allowing Case Managers to record time spent on each case. The system should support both manual time entry and automated timers, restrict data visibility to authorized users, and ensure auditability of time logs for accurate reporting.</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Verify timer starts, pauses, and stops correctly for a case.', 'Test manual time entry and editing for a log.', 'Ensure time is recorded to the correct case and user.', 'Check reporting aggregates show correct totals for workload.', 'Test export or summary of time logs per case.']</t>
+          <t>18: As a Case Manager, I want to track the time spent on each case so that I can report on workload. - Timer or manual entry of time logs per case.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['Timers left running over session logouts or device changes.', 'Attempting to log zero or negative time.', 'Cases with extremely high or fragmented time logs.', 'Manual updates during an active timer.', 'Case is reassigned during logging.']</t>
+          <t>Case Manager opens a case, starts/stops a timer to log time or enters time manually. Log is saved and reflected in workload reports. Only the assigned or authorized Case Manager may record/view logs.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>['Consistency with overall case management (stories 6, 10, 32, 40).', 'Reporting logic shared with related case summary report features.']</t>
+          <t>[{'Test Case ID': 'TC18.1', 'Brief Description': 'Start and stop timer, verify time logged'}, {'Test Case ID': 'TC18.2', 'Brief Description': 'Manually enter time for a case'}, {'Test Case ID': 'TC18.3', 'Brief Description': 'Attempt to log/edit time as unauthorized user'}, {'Test Case ID': 'TC18.4', 'Brief Description': 'View summarized time logs in workload report'}, {'Test Case ID': 'TC18.5', 'Brief Description': 'API test: time log entry and retrieval'}, {'Test Case ID': 'TC18.6', 'Brief Description': 'Audit compliance: time log history is immutable and traceable'}]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[6, 10, 32, 40]</t>
+          <t>[{'Test Case ID': 'TC18.1', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'Active Timing', 'Activity Title': 'Start/Stop Timer', 'Test Scenario Title': 'Timer records elapsed work time correctly', 'Precondition': 'Case exists; Case Manager assigned.', 'Test Data': {'CaseID': 'CASE7890', 'UserRole': 'CaseManager'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to case (CASE7890)', "Click 'Start Timer'", 'Perform some work for several minutes', "Click 'Stop Timer'", 'Check time log entry'], 'Expected Result': 'Elapsed time is logged accurately; entry saved with timestamp and user info.', 'Dependent Module/Process': 'Time Logging Service'}, {'Test Case ID': 'TC18.2', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'Manual Entry', 'Activity Title': 'Manually log time', 'Test Scenario Title': 'Manual time entry for a case', 'Precondition': 'Case exists; user is Case Manager.', 'Test Data': {'CaseID': 'CASE7890', 'TimeSpent': '01:30'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Open CASE7890', "Select 'Manual Time Entry'", "Enter '1 hour 30 minutes'", 'Save log'], 'Expected Result': 'Time log created with entered value, timestamped, user attributed.', 'Dependent Module/Process': 'Time Logging Service'}, {'Test Case ID': 'TC18.3', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict time logging to authorized users', 'Test Scenario Title': 'Unauthorized user attempts to log/edit time', 'Precondition': 'User is not assigned Case Manager on CASE7890.', 'Test Data': {'CaseID': 'CASE7890', 'UserRole': 'Supervisor'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Login as Supervisor', 'Open CASE7890', 'Attempt to start timer or enter time manually'], 'Expected Result': 'Time logging/edit controls unavailable or action denied with error.', 'Dependent Module/Process': 'Role-based Access'}, {'Test Case ID': 'TC18.4', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Reporting', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Summarize case time logs', 'Test Scenario Title': 'View time logs in workload report', 'Precondition': 'Time logs recorded for several cases', 'Test Data': [{'CaseID': 'CASE7890', 'TimeLogged': '01:30'}, {'CaseID': 'CASE6789', 'TimeLogged': '02:15'}], 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Open workload report/dashboard', 'Review summary by case and total time'], 'Expected Result': 'Workload report accurately sums times from all entries.', 'Dependent Module/Process': 'Reporting'}, {'Test Case ID': 'TC18.5', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'API Integration', 'Activity Title': 'Time log via API', 'Test Scenario Title': 'Submit and retrieve time log using API', 'Precondition': 'Time Logging API available; valid API token.', 'Test Data': {'CaseID': 'CASE7890', 'TimeSpent': '00:45', 'APIToken': 'VALID'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager (API)', 'Detailed Test Steps': ['POST time log to API (CASE7890, 00:45)', 'GET time logs for CASE7890 via API'], 'Expected Result': 'API returns success, log retrievable and reflects correct data.', 'Dependent Module/Process': 'API Gateway'}, {'Test Case ID': 'TC18.6', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Immutability', 'Activity Title': 'Audit time log history', 'Test Scenario Title': 'Ensure logs are immutable, auditable', 'Precondition': 'Existing time logs for a case; audit log feature enabled.', 'Test Data': {'CaseID': 'CASE7890'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Admin', 'Detailed Test Steps': ['Login as Audit Admin', 'Retrieve time log history for CASE7890', 'Attempt to modify/delete existing entry', 'Review system audit trail'], 'Expected Result': 'Time logs are read-only after creation; audit trail captures all access and attempted edits.', 'Dependent Module/Process': 'Audit Log/Compliance Module'}]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>This story enables case workers to quickly generate and print client-facing checklists of required documents for specific case types, supporting clear guidance and streamlining the intake process for walk-in clients.</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Verify checklist is generated based on selected case type.', 'Confirm accuracy and completeness of required document list.', 'Test print functionality for the checklist output.', 'Check preview before printing.', 'Test generated checklist for various case types.']</t>
+          <t>19: As a Case Worker, I want to print a checklist of required documents so that I can provide it to walk-in clients.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['Case types with unusually long or short document lists.', 'Checklist with special formatting (long names, special characters).', 'Checklist generated after document requirements are updated.']</t>
+          <t>Case Worker selects a case type, views the corresponding checklist of required documents, and prints it for a walk-in client.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>['Check integration with required documents logic (stories 5, 8, 21, 26).', 'Test document upload and checklist synchronization.']</t>
+          <t>[{'Test Case ID': 'US19_TC01', 'Brief Description': 'Checklist generated and printed for selected case type (happy path)'}, {'Test Case ID': 'US19_TC02', 'Brief Description': 'Checklist generation fails with undefined or unsupported case type'}, {'Test Case ID': 'US19_TC03', 'Brief Description': 'Print preview and functionality works as expected'}, {'Test Case ID': 'US19_TC04', 'Brief Description': 'User tries to print without selecting a case type'}, {'Test Case ID': 'US19_TC05', 'Brief Description': 'User (not Case Worker) attempts to access/print checklist (permission denied)'}]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[5, 8, 21, 26]</t>
+          <t>[{'Test Case ID': 'US19_TC01', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Document Information Capture', 'Activity Title': 'Checklist Generation &amp; Printing', 'Test Scenario Title': 'Checklist is generated and printed for selected case type', 'Precondition': 'User is logged in as Case Worker; at least one case type with checklist exists.', 'Test Data': "{CaseType: 'Family Assistance', Checklist: ['Proof of ID', 'Proof of Income', 'Residence Verification']}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Checklist Feature.', "Select 'Family Assistance' as case type.", 'System displays printable checklist based on case type.', 'Click Print button.'], 'Expected Result': "Printable checklist is displayed; clicking 'Print' sends document to printer.", 'Dependent Module/Process': 'Document Templates, Role Permissions'}, {'Test Case ID': 'US19_TC02', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Document Information Capture', 'Activity Title': 'Checklist Generation', 'Test Scenario Title': 'Checklist generation fails for undefined or unsupported case type', 'Precondition': 'User is logged in as Case Worker.', 'Test Data': "{CaseType: 'Alien Registration', Checklist: null}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Checklist Feature.', "Select 'Alien Registration' as case type.", 'Attempt to generate checklist.'], 'Expected Result': "System displays message: 'Checklist for selected case type not available.' Print option is disabled.", 'Dependent Module/Process': 'Document Templates, Error Handling'}, {'Test Case ID': 'US19_TC03', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Checklist Printing', 'Activity Title': 'Checklist Print Preview', 'Test Scenario Title': 'Print preview and print functionality', 'Precondition': 'Checklist is generated; printer is connected.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ["With checklist generated, click 'Print'.", 'Preview is shown.', "Click 'Confirm' on preview dialog."], 'Expected Result': 'Checklist is printed as per preview. Document layout matches template.', 'Dependent Module/Process': 'Printing Service, Document Templates'}, {'Test Case ID': 'US19_TC04', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Checklist Validation', 'Activity Title': 'Print Attempt Without Selection', 'Test Scenario Title': 'Attempt to print without selecting case type', 'Precondition': 'User is on checklist screen, no case type selected.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Do not select case type.', "Click 'Print'."], 'Expected Result': "System displays validation message: 'Please select a case type.' Print action is blocked.", 'Dependent Module/Process': 'UI Validation'}, {'Test Case ID': 'US19_TC05', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Unauthorized Access Attempt', 'Test Scenario Title': 'Non-authorized user attempts to generate or print checklist', 'Precondition': 'User logged in as a role other than Case Worker.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Receptionist', 'Detailed Test Steps': ['Attempt to access Checklist feature.', 'Try to generate and print checklist.'], 'Expected Result': 'Access is denied; system logs attempt for audit.', 'Dependent Module/Process': 'Role Permissions, Security Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>This story provides a workflow for Case Managers to escalate urgent cases to supervisors, ensuring priority cases receive rapid attention through a formalized escalation and notification mechanism.</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['Verify urgent case marking and flag visibility.', 'Check case escalation workflow initiates from Case Manager.', 'Ensure supervisor receives prompt notification of escalation.', 'Track correct recording of escalation in case history/audit trail.', 'Test de-escalation or resolution workflow.']</t>
+          <t>20: As a Case Manager, I want to escalate urgent cases to supervisors so that they receive immediate attention.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['Multiple concurrent escalations by different managers.', 'Case flagged as urgent but already closed or archived.', 'Supervisor unavailable/unassigned.']</t>
+          <t>Case Manager marks a case as urgent and escalates it. Supervisor is notified and the case status updates accordingly.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>['Validate priority flag and notification processes (stories 14, 38).']</t>
+          <t>[{'Test Case ID': 'US20_TC01', 'Brief Description': 'Successful escalation of urgent case to supervisor'}, {'Test Case ID': 'US20_TC02', 'Brief Description': 'Non-urgent cases cannot be escalated'}, {'Test Case ID': 'US20_TC03', 'Brief Description': 'Supervisor receives notification upon escalation'}, {'Test Case ID': 'US20_TC04', 'Brief Description': 'User attempts escalation without sufficient permission'}, {'Test Case ID': 'US20_TC05', 'Brief Description': 'Escalation action fails due to system error (error handling)'}]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[14, 38]</t>
+          <t>[{'Test Case ID': 'US20_TC01', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Review', 'Activity Title': 'Mark &amp; Escalate Case', 'Test Scenario Title': 'Successful urgent case escalation', 'Precondition': "User is logged in as Case Manager; assigned case exists with status 'Open'.", 'Test Data': "{CaseID: 10234, Priority: 'Urgent'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to assigned case.', "Mark case as 'Urgent' using priority flag.", "Click 'Escalate to Supervisor'.", 'Confirm escalation.'], 'Expected Result': "Case status updated to 'Escalated.' Supervisor receives notification.", 'Dependent Module/Process': 'Notification Service, Case Workflows'}, {'Test Case ID': 'US20_TC02', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Review', 'Activity Title': 'Escalation Criteria Validation', 'Test Scenario Title': 'Attempt to escalate non-urgent case', 'Precondition': "User is logged in as Case Manager; assigned case exists with status 'Open'.", 'Test Data': "{CaseID: 10555, Priority: 'Normal'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to assigned case.', "Attempt to escalate case not marked as 'Urgent'."], 'Expected Result': 'Escalation option is disabled or warning message displayed.', 'Dependent Module/Process': 'UI Validation, Case Workflows'}, {'Test Case ID': 'US20_TC03', 'EPIC': 'Case Escalation', 'Feature': 'Supervisor Notification', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation Notification', 'Activity Title': 'Supervisor Notification Handling', 'Test Scenario Title': 'Supervisor receives real-time escalation notification', 'Precondition': 'Supervisor is logged in; escalation trigger generated.', 'Test Data': "{SupervisorID: 9902, CaseID: 11012, Escalation: 'Urgent'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Case Manager escalates case.', 'Check supervisor notifications panel.'], 'Expected Result': 'Supervisor receives notification with case details and urgency.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'US20_TC04', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Unauthorized Escalation Attempt', 'Test Scenario Title': 'User without escalation permission attempts to escalate', 'Precondition': 'Logged in as user with no escalation rights (e.g., Case Worker).', 'Test Data': '{CaseID: 12367}', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to escalate an open case.'], 'Expected Result': 'Escalation option not visible or access denied error shown and logged for audit.', 'Dependent Module/Process': 'Role Permissions, Security Logging'}, {'Test Case ID': 'US20_TC05', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation Error Handling', 'Activity Title': 'System Error During Escalation', 'Test Scenario Title': 'Escalation fails due to backend or system error', 'Precondition': 'Backend service temporarily unavailable.', 'Test Data': "{CaseID: 14991, Priority: 'Urgent'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Attempt to escalate urgent case.', 'Simulate backend outage or delay.'], 'Expected Result': 'Error is displayed, escalation is not processed, user is advised to retry. Error is logged for audit.', 'Dependent Module/Process': 'Error Handling, Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>This story automates the validation of uploaded documents through OCR and metadata checks, supporting a reduction in manual review time and improving accuracy at document intake.</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Verify OCR correctly extracts text from supported document files (PDF, JPEG, PNG)', 'Validate that required metadata fields are auto-checked upon upload', 'Ensure system flags documents missing key metadata or with unreadable OCR', 'Verify error message is shown when non-supported file type is uploaded', "Check that valid documents are marked as 'auto-validated' and alert generated for failures", 'Audit logs record all auto-validation results']</t>
+          <t>21: As a Case Worker, I want to auto-validate uploaded documents so that I can reduce manual review time.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['Low-resolution or skewed scans', 'Handwritten documents', 'Documents with large amounts of noise or watermarks', 'Multipart PDFs (containing both images and text)', 'Files with missing or corrupt metadata']</t>
+          <t>Case Worker uploads a document, the system performs OCR and metadata validation, and marks the document as valid if checks pass.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>['Upload and validation logic for documents (shared with stories 8, 11, 12, 13, 19, 24)', 'Permission enforcement for who can trigger uploads/validation']</t>
+          <t>[{'Test Case ID': 'US21_TC01', 'Brief Description': 'Successful OCR and metadata validation on acceptable document'}, {'Test Case ID': 'US21_TC02', 'Brief Description': 'Document fails validation due to missing/incorrect metadata'}, {'Test Case ID': 'US21_TC03', 'Brief Description': 'Uploaded file is unreadable/invalid format (OCR failure)'}, {'Test Case ID': 'US21_TC04', 'Brief Description': 'Unauthorized user attempts to upload/validate document'}, {'Test Case ID': 'US21_TC05', 'Brief Description': 'Audit log is created for every validation attempt (compliance)'}]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[8, 11, 12, 13, 19, 24]</t>
+          <t>[{'Test Case ID': 'US21_TC01', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Intake', 'Activity Title': 'Upload and Validate', 'Test Scenario Title': 'Successful OCR and metadata validation', 'Precondition': 'User logged in as Case Worker; auto-validation feature enabled.', 'Test Data': "{Filename: 'id_proof.pdf', Type: 'PDF', Metadata: {ClientID: 101, DateOfBirth: '1992-04-05'}}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to document upload screen.', "Upload 'id_proof.pdf' with required metadata.", 'System performs OCR and checks metadata matches client profile.', 'Validation status is displayed.'], 'Expected Result': 'Document is marked valid; system displays success message and stores document.', 'Dependent Module/Process': 'OCR Engine, Metadata Parser'}, {'Test Case ID': 'US21_TC02', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Intake', 'Activity Title': 'Metadata Error Handling', 'Test Scenario Title': 'Document fails validation due to missing or incorrect metadata', 'Precondition': 'User logged in as Case Worker.', 'Test Data': "{Filename: 'income_statement.pdf', Metadata: {ClientID: '', DateOfBirth: '01-01-2000'}}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload document missing required metadata.', 'System attempts metadata validation.'], 'Expected Result': 'Document rejected; clear error message citing missing/incorrect metadata.', 'Dependent Module/Process': 'Metadata Parser, Validation Rules'}, {'Test Case ID': 'US21_TC03', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Intake', 'Activity Title': 'OCR Failure Handling', 'Test Scenario Title': 'Uploaded file is unreadable or unsupported format (OCR failure)', 'Precondition': 'User logged in as Case Worker.', 'Test Data': "{Filename: 'scanned_doc.tiff', Type: 'TIFF', Metadata: {...}}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload an unsupported or corrupt file.', 'System performs OCR.'], 'Expected Result': "Document rejected with error: 'Unable to process file.' User is prompted to re-upload.", 'Dependent Module/Process': 'OCR Engine, Error Handling'}, {'Test Case ID': 'US21_TC04', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Unauthorized user attempts upload/validation', 'Precondition': 'User role does not include upload/validate rights.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Client', 'Detailed Test Steps': ['Attempt to upload a document.', 'Attempt to trigger validation.'], 'Expected Result': 'Action is denied; attempt is logged for audit.', 'Dependent Module/Process': 'Role Permissions, Security Logging'}, {'Test Case ID': 'US21_TC05', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Audit &amp; Compliance', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Every validation attempt is logged for audit (compliance)', 'Precondition': 'Audit logging feature enabled.', 'Test Data': "{Filename: 'sample.pdf', AttemptType: ['Success', 'Failure']}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload a valid and an invalid document.', 'Check system audit logs.'], 'Expected Result': 'Each validation attempt (success or failure) is logged with timestamp, user, and outcome for audit.', 'Dependent Module/Process': 'Audit Logging, Compliance Framework'}]</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>This user story focuses on leveraging AI-driven suggestions to help Case Workers efficiently complete application forms by highlighting and recommending content for missing fields.</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['System suggests completion options for blank or incomplete required fields', 'Clicking suggestion auto-fills field with AI-recommended values', 'Rejecting suggestion preserves user-entered value', 'Accuracy of suggestions is logged', 'User can request new suggestions after modifying application']</t>
+          <t>22: As a Case Worker, I want to receive suggestions for missing fields in applications so that I can complete them faster. - AI-based field completion suggestions. | Related: [1, 5, 19] | Group: [22]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['Applications with all fields filled (no suggestion expected)', 'Extremely minimal input (only one or two fields present)', 'Conflicting values between user entry and AI suggestion', 'Very large application forms with many missing fields']</t>
+          <t>A Case Worker views an incomplete application and the system suggests values for missing fields, enabling completion and submission of the application without errors.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>['Field validation, missing field detection (shared with stories 1, 5)', 'Audit tracking of suggestions']</t>
+          <t>[{'Test Case ID': 'US22_FT_01', 'Brief Description': 'AI suggestions appear for all required missing fields in an incomplete application.'}, {'Test Case ID': 'US22_FT_02', 'Brief Description': 'Case Worker accepts suggested values and successfully submits the completed application.'}, {'Test Case ID': 'US22_NT_01', 'Brief Description': 'AI does not suggest values for fields already completed by user.'}, {'Test Case ID': 'US22_NT_02', 'Brief Description': 'System handles applications with non-suggestable (unknown) missing fields correctly by prompting manual entry.'}, {'Test Case ID': 'US22_IR_01', 'Brief Description': 'Suggestions are not visible to users without sufficient permissions (Case Managers, external users).'}, {'Test Case ID': 'US22_COMP_01', 'Brief Description': 'AI suggestions comply with data privacy policies (do not leak confidential information).'}]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[1, 5]</t>
+          <t>[{'Test Case ID': 'US22_FT_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Review Incomplete Application', 'Activity Title': 'Field Completion Suggestion', 'Test Scenario Title': 'Display AI Suggestions for Missing Fields', 'Precondition': 'Case Worker has access to an incomplete application with missing required fields.', 'Test Data': "Sample application missing 'Address' and 'Income' fields.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to incomplete application.', 'Observe UI indicators for missing fields.', 'Trigger AI suggestion feature (either auto or on user click).'], 'Expected Result': 'The system displays valid AI-based suggestions for each missing field.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form'}, {'Test Case ID': 'US22_FT_02', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Complete and Submit Application', 'Activity Title': 'Accept AI Suggestions', 'Test Scenario Title': 'Accept and Apply Suggested Values', 'Precondition': 'AI suggestions are generated for required missing fields.', 'Test Data': "Suggestion: 'Address' =&gt; '123 Main St', 'Income' =&gt; '50000'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Review suggested values.', 'Accept all suggestions.', 'Submit the application.'], 'Expected Result': 'Suggested values are applied; submission is successful; all validations pass.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form, Submission Workflow'}, {'Test Case ID': 'US22_NT_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Prevent Duplicate Suggestions', 'Activity Title': 'Exclude Completed Fields', 'Test Scenario Title': 'No Suggestions for Already Filled Fields', 'Precondition': 'Some required fields already completed by user.', 'Test Data': "Application with 'Name', 'DOB' filled; 'Address' missing.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Open an incomplete application where 'Name' and 'DOB' are already filled.", 'Trigger AI suggestion.', 'Observe suggested fields.'], 'Expected Result': 'No suggestions are made for already completed fields.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form'}, {'Test Case ID': 'US22_NT_02', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Handle Unsupported Fields', 'Activity Title': 'Manual Input Prompt', 'Test Scenario Title': 'Prompt Manual Entry for Unsupported Fields', 'Precondition': 'Application contains required fields that are not supported by AI suggestion.', 'Test Data': "Unknown field: 'Special Accommodation Requirements'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt AI suggestion on application with unsupported field.', 'Observe system response.'], 'Expected Result': 'System prompts user to enter value manually; does not fail silently or crash.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form'}, {'Test Case ID': 'US22_IR_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Role-Based Visibility', 'Test Scenario Title': 'Restrict AI Suggestions to Case Workers', 'Precondition': 'Logged in as user without Case Worker permissions.', 'Test Data': 'Any incomplete application.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager/Unauthorized User', 'Detailed Test Steps': ['Login as Case Manager or another unauthorized role.', 'Access an incomplete application.', 'Attempt to trigger AI suggestion.'], 'Expected Result': 'AI suggestions feature is not visible or accessible.', 'Dependent Module/Process': 'Authentication, Role-based Access Control'}, {'Test Case ID': 'US22_COMP_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Compliance and Audit', 'Activity Title': 'Data Privacy', 'Test Scenario Title': 'Ensure AI Suggestions Respect Data Privacy', 'Precondition': 'AI model trained with current system data.', 'Test Data': 'Application with PII fields (Name, SSN, etc).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Review suggested values for sensitive fields.', 'Inspect logs/audit trail.', 'Review data lineage of suggestions.'], 'Expected Result': 'No unauthorized data exposure; data privacy and audit logging complies with GDPR/HIPAA/internal policies.', 'Dependent Module/Process': 'AI Suggestion Engine, Audit Logging, Compliance Framework'}]</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>This user story is about empowering Case Managers to filter and prioritize clients on their dashboard by eligibility status, thereby enhancing their outreach and workflow efficiency.</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['Apply each filter (pending, approved, expired) and verify displayed client list matches expected status', 'Multiple filters combined (if supported) reflect accurate results', 'Reset/clear filters returns full client list', 'Filtered results update client and eligibility counts']</t>
+          <t>23: As a Case Manager, I want to filter clients by eligibility status so that I can prioritize outreach. - Filter dashboard by status: pending, approved, expired. | Related: [6, 25, 32] | Group: [23]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['No clients meet filter (empty result)', 'All clients in same status', 'Rapidly switching filters', 'Clients with no eligibility status set']</t>
+          <t>A Case Manager applies the status filter on the dashboard and instantly sees clients grouped as pending, approved, or expired, enabling targeted action.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>['Eligibility status logic for clients (shared with 6, 25, 32)', 'Dashboard data integrity']</t>
+          <t>[{'Test Case ID': 'US23_FT_01', 'Brief Description': "Filter dashboard to display only 'pending' clients."}, {'Test Case ID': 'US23_FT_02', 'Brief Description': "Filter dashboard to show only 'approved' clients."}, {'Test Case ID': 'US23_FT_03', 'Brief Description': "Filter dashboard to display only 'expired' clients."}, {'Test Case ID': 'US23_NT_01', 'Brief Description': 'Applying an invalid or unsupported filter returns no results and displays an error.'}, {'Test Case ID': 'US23_IR_01', 'Brief Description': 'Unauthorized users cannot access or use filter functionality.'}, {'Test Case ID': 'US23_E2E_01', 'Brief Description': 'Dashboard filter returns up-to-date, integrated eligibility statuses from the backend API.'}]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[6, 25, 32]</t>
+          <t>[{'Test Case ID': 'US23_FT_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Prioritize by Status', 'Activity Title': 'Select Status Filter', 'Test Scenario Title': "Filter by 'Pending' Status", 'Precondition': 'Case Manager logged in with dashboard access; client data is available.', 'Test Data': 'Clients: [John Doe: Pending, Jane Roe: Approved, Sam Smith: Pending]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to dashboard.', "Select 'Pending' from status filter dropdown.", 'Observe client list refresh.'], 'Expected Result': "Dashboard displays only clients with 'Pending' status.", 'Dependent Module/Process': 'Dashboard UI, Eligibility Status API'}, {'Test Case ID': 'US23_FT_02', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Prioritize by Status', 'Activity Title': 'Select Status Filter', 'Test Scenario Title': "Filter by 'Approved' Status", 'Precondition': 'Dashboard shows multiple clients with various statuses.', 'Test Data': 'Clients: [John Doe: Pending, Jane Roe: Approved, Sam Smith: Expired]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Select 'Approved' status in filter.", 'Review dashboard results.'], 'Expected Result': "Only 'Approved' clients are displayed.", 'Dependent Module/Process': 'Dashboard UI, Eligibility Status API'}, {'Test Case ID': 'US23_FT_03', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Prioritize by Status', 'Activity Title': 'Select Status Filter', 'Test Scenario Title': "Filter by 'Expired' Status", 'Precondition': 'Clients exist in all status categories.', 'Test Data': 'Clients: [Sam Smith: Expired]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Apply 'Expired' status filter.", 'Compare displayed list against expected expired clients.'], 'Expected Result': "Only clients with status 'Expired' appear.", 'Dependent Module/Process': 'Eligibility Status Data, Dashboard UI'}, {'Test Case ID': 'US23_NT_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Handle Invalid Filter', 'Activity Title': 'Invalid Filter Graceful Handling', 'Test Scenario Title': 'Apply Unsupported Status Filter', 'Precondition': 'Dashboard has active filtering capability.', 'Test Data': "Invalid filter value: 'Under Review'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Attempt to filter clients with an unsupported status value.', 'Observe system behavior.'], 'Expected Result': 'Dashboard shows appropriate error or empty state; no crash.', 'Dependent Module/Process': 'Dashboard UI, Error Handling'}, {'Test Case ID': 'US23_IR_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Dashboard Access', 'Sub-Process Title': 'Permission Check', 'Activity Title': 'Restrict Filter UI', 'Test Scenario Title': 'Unauthorized User Cannot Filter', 'Precondition': 'Login as non-Case Manager role.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, External User', 'Detailed Test Steps': ['Login as a user without Case Manager privileges.', 'Navigate to client dashboard.', 'Look for status filter options.'], 'Expected Result': 'Status filter is not accessible or functional for unauthorized roles.', 'Dependent Module/Process': 'Authentication, Role-based Permissions'}, {'Test Case ID': 'US23_E2E_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Full System Integration', 'Activity Title': 'API and UI Sync', 'Test Scenario Title': 'Filter Reflects Latest Status from API', 'Precondition': 'API holds up-to-date eligibility data.', 'Test Data': 'Update status in backend (e.g., pending→approved), refresh dashboard.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Change status of one client in backend to 'Approved'.", "Refresh dashboard and apply 'Approved' filter.", 'Verify real-time update.'], 'Expected Result': 'Filter results match latest backend data.', 'Dependent Module/Process': 'Eligibility Status API, Dashboard UI'}]</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>This user story enhances Case Worker efficiency by enabling bulk document uploads with automatic matching to multiple cases, reducing manual effort and error.</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Upload multiple documents associated to distinct cases, verify correct case attachment', 'Upload batch with some invalid documents, verify only valid files processed', 'Bulk upload with mixture of supported/unsupported file types', 'UI feedback for batch progress and completion', 'Audit log records every upload and case association']</t>
+          <t>24: As a Case Worker, I want to bulk upload documents for multiple cases so that I can save time. - Batch upload with case matching logic. | Related: [8] | Group: [24]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['Very large batch (system limits, timeouts)', 'Files missing case identifiers', 'Multiple files for same case in one batch']</t>
+          <t>Case Worker uploads a batch of documents; the system automatically matches and attaches each document to the correct case, showing success.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>['Document upload pipeline (shared with 8, 21)', 'User permissions for batch operations']</t>
+          <t>[{'Test Case ID': 'US24_FT_01', 'Brief Description': 'Bulk upload successfully attaches documents to correct cases.'}, {'Test Case ID': 'US24_NT_01', 'Brief Description': 'Upload is partially successful with some documents unmatched; user receives actionable error/warning.'}, {'Test Case ID': 'US24_NT_02', 'Brief Description': 'Bulk upload fails if all documents lack matching data (e.g., invalid case IDs), system rolls back changes.'}, {'Test Case ID': 'US24_IR_01', 'Brief Description': 'Non-Case Worker users cannot access bulk upload functionality.'}, {'Test Case ID': 'US24_COMP_01', 'Brief Description': 'All uploads are logged for audit; file types and data comply with policy.'}]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[8, 21]</t>
+          <t>[{'Test Case ID': 'US24_FT_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Batch Document Upload', 'Activity Title': 'Upload Multiple Files', 'Test Scenario Title': 'Successful Bulk Upload and Case Matching', 'Precondition': 'Case Worker logged in; cases exist and are accessible.', 'Test Data': 'Files: [john_doe_id.pdf-&gt;Case 123, jane_roe_transcript.pdf-&gt;Case 456]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select bulk upload option.', 'Choose multiple files with valid naming/case identifier conventions.', 'Confirm upload.', 'Check attachment status for each case.'], 'Expected Result': 'All documents matched and attached to correct cases. Confirmation displayed.', 'Dependent Module/Process': 'Case Matching Logic, Document Storage'}, {'Test Case ID': 'US24_NT_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Batch Document Upload', 'Activity Title': 'Partial Match Handling', 'Test Scenario Title': 'Bulk Upload with Some Unmatched Documents', 'Precondition': 'Mixed-validity files selected for upload.', 'Test Data': 'Files: [good.pdf-&gt;Case 123, error.pdf-&gt;No match]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload files (one with no match).', 'Monitor system response.', 'Review result messages.'], 'Expected Result': 'Matched document attached; unmatched document flagged with actionable error. No data loss or corruption.', 'Dependent Module/Process': 'Case Matching Logic, Document Workflow'}, {'Test Case ID': 'US24_NT_02', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Batch Document Upload', 'Activity Title': 'Full Upload Failure Handling', 'Test Scenario Title': 'Bulk Upload Failure Due to No Match', 'Precondition': 'All selected files have invalid or missing identifiers.', 'Test Data': 'Files: [unknown1.pdf, unknown2.pdf]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload only invalid files.', 'Observe system processing.', 'Inspect error and rollback behavior.'], 'Expected Result': 'No documents attached. User receives a clear error. No partial state left in system.', 'Dependent Module/Process': 'Case Matching Logic, Transaction Rollback'}, {'Test Case ID': 'US24_IR_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Role Restriction', 'Test Scenario Title': 'Only Case Workers Can Bulk Upload', 'Precondition': 'Login as a user without Case Worker permissions.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Client, etc.', 'Detailed Test Steps': ['Attempt to access bulk upload screen as unauthorized user.', 'Try triggering upload functionality.'], 'Expected Result': 'Bulk upload UI and API endpoints inaccessible.', 'Dependent Module/Process': 'Authentication, Authorization'}, {'Test Case ID': 'US24_COMP_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Compliance and Audit', 'Activity Title': 'Logging and Validation', 'Test Scenario Title': 'Bulk Upload Meets Audit and Policy Requirements', 'Precondition': 'Bulk upload feature enabled; audit system active.', 'Test Data': 'Files: various types, including non-permitted if possible.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload a valid set of documents.', 'Attempt uploading unsupported file types.', 'Check audit logs for entries.', 'Verify compliance validation messages for blocked types.', 'Request or view audit trail/report.'], 'Expected Result': 'All uploads are logged with user, timestamp, and case info; unsupported files are blocked; compliance warnings shown as needed.', 'Dependent Module/Process': 'Audit Logging, Compliance System, File Storage'}]</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>This user story revolves around providing Case Managers with insights through an analytics dashboard, allowing them to view and analyze trends in eligibility denials. This capability aims to help identify systemic issues, enabling data-driven interventions and compliance with reporting requirements.</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['View eligibility denial trends over selectable date ranges', 'Denial reason breakdown shows correct count and percentage', 'Export analytics data to CSV', 'Drill down from trend graph to list of denied applications', 'Filter analytics results by caseworker, location']</t>
+          <t>As a Case Manager, I want to view trends in eligibility denials so that I can identify systemic issues.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['No denial data in period (empty graph)', 'Multiple denials with same reason in short period', 'Denial with missing or unknown reason code']</t>
+          <t>Case Manager logs in, navigates to the analytics dashboard, and views visualizations detailing denial patterns, including frequency, reasons, and trends over user-defined periods.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>['Eligibility determination and status logic (shared with 6, 16, 23)', 'Analytics dashboard usability']</t>
+          <t>[{'Test Case ID': 'US25-TC01', 'Brief Description': 'Case Manager views the denial trends dashboard with accurate, up-to-date data.'}, {'Test Case ID': 'US25-TC02', 'Brief Description': 'Case Manager filters dashboard by various criteria (date, reason, location).'}, {'Test Case ID': 'US25-TC03', 'Brief Description': 'Case Manager exports denial trends report for compliance/audit.'}, {'Test Case ID': 'US25-TC04', 'Brief Description': 'Unauthorized user attempts to access the dashboard.'}, {'Test Case ID': 'US25-TC05', 'Brief Description': 'Dashboard displays proper messages when there is no data.'}, {'Test Case ID': 'US25-TC06', 'Brief Description': 'API returns correct data for denial trends (integration testing).'}]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[6, 16, 23]</t>
+          <t>[{'Test Case ID': 'US25-TC01', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Reporting', 'Activity Title': 'View Denial Trends', 'Test Scenario Title': 'Case Manager views the denial trends dashboard with accurate data.', 'Precondition': 'Case Manager has account and dashboard permissions; denial data exists in the system.', 'Test Data': 'Sample denial records with varied reasons/dates/locations.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to Analytics -&gt; Denial Trends.', 'Observe displayed dashboard charts/tables.'], 'Expected Result': 'Dashboard loads successfully, displaying accurate visualizations of denial patterns matching test data.', 'Dependent Module/Process': 'Denials database, Authentication'}, {'Test Case ID': 'US25-TC02', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Reporting', 'Activity Title': 'Filter Dashboard', 'Test Scenario Title': 'Case Manager uses filtering options.', 'Precondition': 'Case Manager is on the denial trends dashboard.', 'Test Data': 'Diverse denials by date/reason/location.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Use dashboard filters for date, denial reason, and location.', 'Apply filter and observe results.'], 'Expected Result': 'Visualizations and data update accurately as per selected filters.', 'Dependent Module/Process': 'UI, Filter APIs'}, {'Test Case ID': 'US25-TC03', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Reporting', 'Activity Title': 'Export Reports', 'Test Scenario Title': 'Case Manager exports denial trends for compliance/audit.', 'Precondition': 'Denial trends are displayed on Dashboard.', 'Test Data': 'Sample denial records.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Click export/download button on dashboard.', 'Select file type (PDF, CSV, etc.)', 'Download the report.'], 'Expected Result': 'File is downloaded containing data matching dashboard, formatted for audit/compliance.', 'Dependent Module/Process': 'Export Service'}, {'Test Case ID': 'US25-TC04', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Security', 'Activity Title': 'Unauthorized Access Prevention', 'Test Scenario Title': 'Unauthorized user attempts dashboard access.', 'Precondition': 'User is not assigned Case Manager or higher permissions.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Other roles (e.g., Applicant)', 'Detailed Test Steps': ['Log in as non-authorized user.', 'Attempt to access denial trends dashboard URL/page.'], 'Expected Result': 'Access is denied; appropriate error or redirect is shown.', 'Dependent Module/Process': 'Authentication/Authorization'}, {'Test Case ID': 'US25-TC05', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics UX', 'Activity Title': 'No Data Handling', 'Test Scenario Title': 'Dashboard displays proper messages when no denial data exists.', 'Precondition': 'There are no denials in the database.', 'Test Data': 'Empty denial records.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in and navigate to dashboard when database is empty.'], 'Expected Result': '"No data available" message is shown; visualizations are empty/grayed out.', 'Dependent Module/Process': 'Analytics Data Layer'}, {'Test Case ID': 'US25-TC06', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Backend API', 'Activity Title': 'API Testing', 'Test Scenario Title': 'API returns accurate denial trend data.', 'Precondition': 'Denial data is seeded in backend.', 'Test Data': 'Known denial scenarios.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call API endpoint for denial trend data with different parameters.', 'Verify returned dataset matches expected results.'], 'Expected Result': 'API returns accurate summaries as per seeded data and filters.', 'Dependent Module/Process': 'Analytics API'}]</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>This user story focuses on improving efficiency for Case Workers by auto-filling new applications using data from past cases. The goal is to reduce manual data entry and potential input errors while maintaining data privacy and permissions boundaries.</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Verify that when creating a new application, available historical data from previous cases is automatically populated in matching fields.', 'Ensure that only relevant and correct fields are pre-filled based on the case type.', 'Check that users can manually overwrite any pre-filled data.', 'Validate that pre-filled data sources are accurate and up to date.', 'Confirm that there is an indication (highlight or info icon) that data was pre-filled from previous cases.']</t>
+          <t>As a Case Worker, I want to pre-fill application data from previous cases so that I can reduce data entry.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['Previous cases have incomplete or inaccurate data.', 'No previous cases exist for the applicant.', 'Previous data contains special characters or invalid format.', 'Multiple prior cases with conflicting values.']</t>
+          <t>Case Worker initiates a new application, the system suggests and pre-fills relevant fields with data from historical cases connected to the applicant, and the Case Worker reviews and modifies as necessary.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['Test pre-fill with initial application creation (from Story 1).', 'Test with multiple prior cases (related to Story 19, which may also reuse applicant data).']</t>
+          <t>[{'Test Case ID': 'US26-TC01', 'Brief Description': 'Auto-fill populates fields from prior cases when Case Worker initiates a new application.'}, {'Test Case ID': 'US26-TC02', 'Brief Description': 'Case Worker manually edits pre-filled data before submitting.'}, {'Test Case ID': 'US26-TC03', 'Brief Description': 'No prior case data exist; no fields are auto-filled.'}, {'Test Case ID': 'US26-TC04', 'Brief Description': 'Case Worker tries to pre-fill for a case not linked to their jurisdiction (permissions validation).'}, {'Test Case ID': 'US26-TC05', 'Brief Description': 'API returns accurate data when requested for auto-fill.'}, {'Test Case ID': 'US26-TC06', 'Brief Description': 'Audit log records auto-fill usages (compliance).'}]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Story 1 (basic application creation)', 'Story 19 (reuse of applicant data or case history)', 'Any form population or data entry features']</t>
+          <t>[{'Test Case ID': 'US26-TC01', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Auto-fill', 'Activity Title': 'Create Application', 'Test Scenario Title': 'Fields pre-filled from previous cases.', 'Precondition': 'Case Worker is assigned eligible applicant with prior cases in system.', 'Test Data': 'Prior case data in DB (address, household, income, etc.).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Start new application for applicant with historical data.', 'Observe auto-filled fields.'], 'Expected Result': 'Fields are automatically populated with prior data, accurately matching history.', 'Dependent Module/Process': 'Application Engine, Data Retrieval API'}, {'Test Case ID': 'US26-TC02', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Auto-fill', 'Activity Title': 'Edit Auto-Filled Data', 'Test Scenario Title': 'Case Worker edits pre-filled data before submitting.', 'Precondition': 'Fields are auto-filled on application form.', 'Test Data': 'Prior case data, new corrections.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Change information for one or more auto-filled fields.', 'Submit application.'], 'Expected Result': 'Edits are saved; final submission uses updated values.', 'Dependent Module/Process': 'Application Form Validation'}, {'Test Case ID': 'US26-TC03', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Auto-fill', 'Activity Title': 'No History Condition', 'Test Scenario Title': 'No prior data, nothing is auto-filled.', 'Precondition': 'Applicant has no prior case in DB.', 'Test Data': 'Empty prior case.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Start new application for applicant with no history.', 'Observe that all fields are empty.'], 'Expected Result': 'No fields are pre-populated; application starts blank.', 'Dependent Module/Process': 'Auto-fill Trigger'}, {'Test Case ID': 'US26-TC04', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Jurisdiction Validation', 'Test Scenario Title': 'Case Worker attempts pre-fill for a case outside their jurisdiction.', 'Precondition': 'Case Worker lacks permission for given applicant’s history.', 'Test Data': 'Applicant/case in different jurisdiction.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (unauthorized)', 'Detailed Test Steps': ['Start new application for applicant outside jurisdiction.', 'Attempt to trigger auto-fill.'], 'Expected Result': 'Auto-fill does not fetch data; appropriate error/warning is displayed.', 'Dependent Module/Process': 'Authorization, Jurisdiction Rules'}, {'Test Case ID': 'US26-TC05', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'Integration', 'Sub-Process Title': 'API', 'Activity Title': 'API Testing', 'Test Scenario Title': 'API returns correct auto-fill data.', 'Precondition': 'Test user/applicant with history exists.', 'Test Data': 'Historical records for test applicant.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Invoke auto-fill API for applicant ID.', 'Validate returned fields against database records.'], 'Expected Result': 'API returns correct, complete data for pre-fill.', 'Dependent Module/Process': 'Auto-fill API'}, {'Test Case ID': 'US26-TC06', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'Compliance/Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Auto-fill usage is logged for audit.', 'Precondition': 'System audit logging is enabled.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Trigger auto-fill on application.', 'Check audit log for entry with Case Worker’s activity.'], 'Expected Result': 'Auto-fill access is recorded in logs with user, applicant, and timestamp for compliance.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>This user story ensures integrity by alerting Case Workers when there are conflicting household data entries across linked applications, enabling timely resolution and maintaining data correctness for eligibility determinations.</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['Verify that conflicting household data across multiple applications is detected.', 'Ensure that system generates alerts when discrepancies are found.', 'Check that alerts provide clear, actionable information regarding discrepancies.', 'Test that resolving or dismissing an alert updates its status.', 'Confirm that non-conflicting applications do not generate false positives.']</t>
+          <t>As a Case Worker, I want to receive alerts for conflicting household data so that I can resolve discrepancies.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Household data changes in the middle of review.', 'Same household members with slightly different spellings or data formats.', 'Large number of applications with overlapping household data.', 'Missing or null household fields.']</t>
+          <t>Case Worker processes an application; the system scans for duplicate household data across records and prompts an alert if any conflicts are detected.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>['Test with household entered in new application flow (from Story 1).', 'Verify alert if data updated from other system modules (story 4 could be cross-checking).']</t>
+          <t>[{'Test Case ID': 'US27-TC01', 'Brief Description': 'Case Worker receives alert when household data conflict is detected during application submission.'}, {'Test Case ID': 'US27-TC02', 'Brief Description': 'Case Worker reviews and resolves conflicting household data following alert.'}, {'Test Case ID': 'US27-TC03', 'Brief Description': 'No conflict in household data; application proceeds with no alert.'}, {'Test Case ID': 'US27-TC04', 'Brief Description': 'API correctly flags/returns data conflicts for integration.'}, {'Test Case ID': 'US27-TC05', 'Brief Description': 'Case Worker attempts to ignore alert and proceed without resolution (negative path).'}, {'Test Case ID': 'US27-TC06', 'Brief Description': 'Alert/audit log is generated for each detected conflict (compliance).'}]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['Story 1 (application household data entry)', 'Story 4 (any data consistency checks)', 'Alert and notification system']</t>
+          <t>[{'Test Case ID': 'US27-TC01', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'Submit Application', 'Test Scenario Title': 'Household conflict triggers alert.', 'Precondition': 'Household data in new application conflicts with existing record.', 'Test Data': 'Duplicate or conflicting household details (e.g., same member with different DOB).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Enter household details in new application that conflict with another record.', 'Attempt to submit application.'], 'Expected Result': 'Pop-up or banner alert notifies Case Worker of data conflict, listing affected fields.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'US27-TC02', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'Resolve Data Conflict', 'Test Scenario Title': 'Case Worker resolves conflicting household data.', 'Precondition': 'System has flagged household conflict.', 'Test Data': 'Conflicting details; correct data available.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Observe conflict alert.', 'Edit household details to resolve discrepancy.', 'Re-submit application.'], 'Expected Result': 'System accepts update if no further conflict exists; no alert on re-submission.', 'Dependent Module/Process': 'Application Save Logic'}, {'Test Case ID': 'US27-TC03', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'No Conflict', 'Test Scenario Title': 'No alert is raised when data is unique.', 'Precondition': 'No conflicting household data in system.', 'Test Data': 'Unique household details.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Enter new, unique household details.', 'Submit application.'], 'Expected Result': 'Application is submitted with no alert.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'US27-TC04', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Integration', 'Sub-Process Title': 'Cross-Check API', 'Activity Title': 'API Testing', 'Test Scenario Title': 'API flags conflicting household data as expected.', 'Precondition': 'Conflicting and non-conflicting household data in source.', 'Test Data': 'Test endpoint with conflicting input household data.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call household data validation API with new application data.', 'Validate that response identifies conflicts accurately.'], 'Expected Result': 'API returns clear indication of any conflicts or passes if none.', 'Dependent Module/Process': 'Validation Microservice'}, {'Test Case ID': 'US27-TC05', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'Attempt Override', 'Test Scenario Title': 'Case Worker ignores alert and tries to proceed.', 'Precondition': 'Household conflict alert shown.', 'Test Data': 'Conflicting submission.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Dismiss conflict alert.', 'Attempt to submit application without resolving.'], 'Expected Result': 'System does not allow submission; persists alert and blocks progress until resolved.', 'Dependent Module/Process': 'Form Submission Validation'}, {'Test Case ID': 'US27-TC06', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Compliance/Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Alert Logging', 'Test Scenario Title': 'All conflict alerts and resolutions are audit-logged.', 'Precondition': 'System audit logging enabled.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Trigger household data conflict and resolve it.', 'Review audit log for entries including conflict, user, timestamps, and resolution actions.'], 'Expected Result': 'System logs all alerts and resolutions for audit/compliance.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>This user story ensures case managers can assign cases to caseworkers who have matching language proficiency, thereby enhancing client satisfaction and service quality.</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Confirm that a case can be assigned based on client language preference.', 'Validate that only caseworkers with matching language skills are displayed as assignable.', 'Check that assignment can be forced/overridden if required (permissions).', 'Ensure error is shown if no match is available.', 'Test updating caseworker or client language and observing assignment change.']</t>
+          <t>As a Case Manager, I want to assign cases based on language preference so that clients receive better service. - Match caseworker language skills with client preference.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['Client lists a rare language not covered by any caseworker.', 'Multiple caseworkers with matching skills (random/priority assignment?).', 'Caseworker updates skill list after assignment.', 'Client with multiple language preferences.']</t>
+          <t>Case Manager selects a case. The system allows assignment only to caseworkers with matching or higher language proficiency as per the client’s preference. Assignment is successful and notified.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>['Test with client/case creation (from Story 10, for initial assignment).']</t>
+          <t>[{'Test Case ID': 'US28_TC1', 'Brief Description': 'Assign case to a caseworker with matching language proficiency (positive test).'}, {'Test Case ID': 'US28_TC2', 'Brief Description': 'Attempt to assign case to a caseworker without required language (negative test).'}, {'Test Case ID': 'US28_TC3', 'Brief Description': 'System filtering caseworkers by language skill in assignment (functional test).'}, {'Test Case ID': 'US28_TC4', 'Brief Description': 'Audit log records language-based assignment action (compliance test).'}, {'Test Case ID': 'US28_TC5', 'Brief Description': 'Verify data synchronization between case assignment and user profile modules (integration test).'}]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Story 10 (case assignment)', 'Caseworker/client details management']</t>
+          <t>[{'Test Case ID': 'US28_TC1', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Cases', 'Activity Title': 'Assign based on language', 'Test Scenario Title': 'Successful assignment with language match', 'Precondition': 'Case manager and caseworker accounts exist; case has a required language; at least one caseworker with matching skill.', 'Test Data': {'Case ID': 'CASE123', 'Required Language': 'Spanish', 'Caseworker Skills': [{'User': 'CW001', 'Languages': ['Spanish', 'English']}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Open CASE123 with Spanish language preference.', "Click 'Assign Case'.", 'Select CW001 (Spanish, English) from eligible list.', 'Confirm assignment.'], 'Expected Result': 'Case is successfully assigned to CW001; assignment confirmation is displayed.', 'Dependent Module/Process': 'User Profile, Case Management'}, {'Test Case ID': 'US28_TC2', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Cases', 'Activity Title': 'Assign based on language', 'Test Scenario Title': 'Failed assignment when language skill missing', 'Precondition': 'Case manager and at least one caseworker without language skill; case specifies language.', 'Test Data': {'Case ID': 'CASE124', 'Required Language': 'Mandarin', 'Caseworker Skills': [{'User': 'CW002', 'Languages': ['English']}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Open CASE124 with Mandarin language preference.', "Click 'Assign Case'.", 'Attempt to select CW002 (English).', 'Confirm assignment.'], 'Expected Result': "System prevents assignment; error indicating 'Language skill mismatch'.", 'Dependent Module/Process': 'User Profile, Case Management'}, {'Test Case ID': 'US28_TC3', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Cases', 'Activity Title': 'Assign based on language', 'Test Scenario Title': 'Filter caseworkers by language dynamically', 'Precondition': 'Caseworker data with various language skills exists.', 'Test Data': {'Required Language': 'French', 'Available Caseworkers': [{'User': 'CW003', 'Languages': ['French', 'English']}, {'User': 'CW004', 'Languages': ['German']}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Attempt to assign case requiring French.', 'Observe displayed list of available caseworkers.'], 'Expected Result': 'Only CW003 (French) is displayed for selection; CW004 (German) is not.', 'Dependent Module/Process': 'User Profile'}, {'Test Case ID': 'US28_TC4', 'EPIC': 'Case Assignment', 'Feature': 'Audit', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignments', 'Activity Title': 'Audit trail', 'Test Scenario Title': 'Language-based assignment audit logged', 'Precondition': 'Case assignment occurs.', 'Test Data': {'Case ID': 'CASE125'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign CASE125 based on French preference.', 'Access audit logs.'], 'Expected Result': 'Audit log includes time, case ID, caseworker ID, assigning manager, and language filter details.', 'Dependent Module/Process': 'Audit, Logging'}, {'Test Case ID': 'US28_TC5', 'EPIC': 'Case Assignment', 'Feature': 'Integration', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignments', 'Activity Title': 'Data Synchronization', 'Test Scenario Title': 'Consistent language skill lookup between assignments and user profiles', 'Precondition': 'Caseworker language skills updated in profile service.', 'Test Data': {'CW005': 'Added Japanese'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Admin', 'Detailed Test Steps': ["As Admin, update CW005's profile: add Japanese.", 'As Case Manager, assign a Japanese language case.', 'Verify CW005 appears as eligible.'], 'Expected Result': 'CW005 is selectable after profile update, confirming real-time data sync.', 'Dependent Module/Process': 'User Profile, Case Assignment'}]</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>This user story enables case workers to preview documents before uploading them, reducing errors by allowing verification of scanned document accuracy.</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['Verify that document preview loads correctly in the upload dialog/pane.', 'Confirm that only supported file types render a preview; others display an appropriate message.', 'Ensure that the displayed preview matches the original document.', 'Check performance loading various file sizes.', 'Test cancelling or replacing documents before upload.']</t>
+          <t>As a Case Worker, I want to preview documents before uploading so that I can ensure accuracy. - Preview pane for scanned documents.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['Uploading a corrupt or unsupported file type.', 'Multi-page (PDF) or multi-image uploads.', 'Very large file uploads (performance/memory).', 'Files with malicious or non-standard content.']</t>
+          <t>Case Worker uploads a scanned document, previews it in a pane, confirms its correctness, and uploads or cancels as needed.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>['Document upload tests (from Story 8).', 'Review preview before submission (related to Story 13, likely integration with document review flow).']</t>
+          <t>[{'Test Case ID': 'US29_TC1', 'Brief Description': 'Preview and upload a valid scanned document (positive test).'}, {'Test Case ID': 'US29_TC2', 'Brief Description': 'Attempt to preview an unsupported file format (negative test).'}, {'Test Case ID': 'US29_TC3', 'Brief Description': 'Attempt to upload without previewing (control disabled).'}, {'Test Case ID': 'US29_TC4', 'Brief Description': 'Verify preview pane proper rendering for PDF and image files.'}, {'Test Case ID': 'US29_TC5', 'Brief Description': 'Audit logs record preview and upload action (compliance).'}]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['Story 8 (document upload)', 'Story 13 (document review/preview)', 'Any file handling or previewing libraries']</t>
+          <t>[{'Test Case ID': 'US29_TC1', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Preview and Confirm Upload', 'Test Scenario Title': 'Successful document preview and upload', 'Precondition': 'User logged in as Case Worker.', 'Test Data': {'Document': 'valid_scan.pdf'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to case documents section.', "Click 'Upload Document'.", "Select 'valid_scan.pdf' for upload.", 'Preview pane displays the document.', "Click 'Confirm Upload'."], 'Expected Result': "'valid_scan.pdf' is visible in case documents; successful upload notification displayed.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC2', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Error Handling', 'Test Scenario Title': 'Unsupported file format preview fails', 'Precondition': 'User logged in. Unsupported file available.', 'Test Data': {'Document': 'unknown.xyz'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Click 'Upload Document'.", "Select 'unknown.xyz' for upload.", 'System attempts to preview but fails.'], 'Expected Result': "Error message 'Unsupported file format' displayed; upload disabled.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC3', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Preview Enforcement', 'Test Scenario Title': 'Upload disabled until previewed', 'Precondition': 'User logged in.', 'Test Data': {'Document': 'large_image.jpg'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select 'Upload Document'.", "Choose 'large_image.jpg'.", 'Attempt to upload without completing preview.'], 'Expected Result': 'Upload button remains disabled until preview completes.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC4', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Multi-Format Preview', 'Test Scenario Title': 'Preview supports PDF and image files', 'Precondition': 'User logged in.', 'Test Data': {'PDF': 'scan.pdf', 'Image': 'photo.png'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Upload 'scan.pdf' and observe preview.", "Upload 'photo.png' and observe preview."], 'Expected Result': 'Both PDFs and images are rendered correctly in the preview pane.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC5', 'EPIC': 'Document Management', 'Feature': 'Audit', 'User Story': 'US29', 'Business Process': 'Document Management', 'Sub-Process Title': 'Preview and Upload', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Audit log for preview and upload', 'Precondition': 'User uploads document after preview.', 'Test Data': {'User': 'CW008', 'Document': 'confidential.pdf'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["CW008 previews and uploads 'confidential.pdf'.", 'Access audit logs.'], 'Expected Result': 'Audit log records user ID, document name, timestamp, and action: previewed/uploaded.', 'Dependent Module/Process': 'Audit, Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>This user story provides case managers with the functionality to export filtered case data to Excel/CSV, supporting offline analysis while ensuring data privacy compliance.</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Verify that users can export visible/filterable case data to Excel/CSV format.', 'Check that exported file is readable in Excel and data matches what is shown in the app.', 'Test exporting large volumes of records.', 'Ensure all selected/filter columns export correctly.', 'Test export with special characters and date/time fields.']</t>
+          <t>As a Case Manager, I want to export case data to Excel so that I can analyze it offline. - Export filtered case lists to CSV/Excel.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['No records returned by filter (empty export file).', 'Fields with Excel-reserved characters (commas, quotes, formulas).', 'Rapid repeated export submissions.', 'Data containing multi-line or binary content.']</t>
+          <t>Case Manager filters case list, clicks export, downloads a correctly formatted and complete Excel file of visible data only.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>['Test with filtering features (from Story 32).', 'Test with various export options/settings (from Story 23 if relevant).']</t>
+          <t>[{'Test Case ID': 'US30_TC1', 'Brief Description': 'Export filtered case list to Excel (positive test).'}, {'Test Case ID': 'US30_TC2', 'Brief Description': 'Attempt export with no data after applying filters (negative test).'}, {'Test Case ID': 'US30_TC3', 'Brief Description': 'Verify exported data does not include unauthorized data (permissions/compliance).'}, {'Test Case ID': 'US30_TC4', 'Brief Description': 'Validate audit trail for export operation (compliance, GDPR).'}, {'Test Case ID': 'US30_TC5', 'Brief Description': 'Verify API sends correct filter criteria during export (API/integration test).'}]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['Story 32 (data filtering)', 'Story 23 (data export/reporting)', 'Any data retrieval or reporting backends']</t>
+          <t>[{'Test Case ID': 'US30_TC1', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Case List Export', 'Activity Title': 'Filter and Export', 'Test Scenario Title': 'Successful export of filtered case data', 'Precondition': 'User logged in as Case Manager; cases exist; filter applied.', 'Test Data': {'Filter': 'Status = Open', 'Expected Export Rows': 5}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Apply filter: Status = Open.', "Click 'Export to Excel'.", 'Download the .xlsx file.', 'Open file to verify contents.'], 'Expected Result': 'Excel contains only 5 rows with Status = Open; format matches requirements.', 'Dependent Module/Process': 'Reporting, Export Module'}, {'Test Case ID': 'US30_TC2', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Case List Export', 'Activity Title': 'Filter and Export', 'Test Scenario Title': 'Attempt export with no data after filtering', 'Precondition': 'User logged in; cases exist; filter reduces visible list to 0.', 'Test Data': {'Filter': 'Status = Archived'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Apply filter: Status = Archived (no results expected).', "Click 'Export to Excel'."], 'Expected Result': "System displays message: 'No data to export.'; no file generated.", 'Dependent Module/Process': 'Reporting, Export Module'}, {'Test Case ID': 'US30_TC3', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Permissions and Data Privacy', 'Activity Title': 'Restricted Data Export', 'Test Scenario Title': 'Exported data excludes unauthorized information', 'Precondition': 'Case Manager does not have access to sensitive fields.', 'Test Data': {'Fields': ['Basic Info', 'Sensitive Info']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Filter and view cases with sensitive information field.', 'Export case list to Excel.', 'Open and review file.'], 'Expected Result': "Excel excludes unauthorized columns (e.g., 'Sensitive Info').", 'Dependent Module/Process': 'Data Privacy, Role Management'}, {'Test Case ID': 'US30_TC4', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Audit', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Audit log records export action', 'Precondition': 'Export action performed.', 'Test Data': {'User': 'CM010', 'Action': 'Export'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['CM010 filters case list and clicks export.', 'Access and review audit logs (download event).'], 'Expected Result': 'Audit log captures time, user, filters used, and confirmation of data file generation.', 'Dependent Module/Process': 'Audit, Export, Compliance'}, {'Test Case ID': 'US30_TC5', 'EPIC': 'Case Management Reporting', 'Feature': 'Export API', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'API', 'Activity Title': 'Export Invocation', 'Test Scenario Title': 'Correct filter passed to export API', 'Precondition': 'API logging enabled; filter applied.', 'Test Data': {'API Endpoint': '/api/cases/export', 'Filter Sent': 'Status = Open'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Apply filter (Status = Open) in UI.', 'Trigger export.', 'Monitor API request payload.'], 'Expected Result': "API request body includes applied filter ('Status = Open'); export reflects UI filter.", 'Dependent Module/Process': 'Export API, Reporting'}]</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>This user story focuses on improving data integrity and workload management by alerting case workers to duplicate application submissions, enabling them to merge records and maintain a single, authoritative client file.</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Create two applications with matching identifying information and verify alert for potential duplicate.', 'Create applications with similar (but not identical) data and check if duplicates are detected based on matching logic.', 'Review flagged duplicates list as a Case Worker to ensure visibility and correctness.', 'Merge flagged duplicate applications and verify accuracy and data integrity post-merge.', 'Verify alert is generated in real-time, not delayed.', 'Mark false positive as not duplicate and verify alerts are not repeated for that pair.']</t>
+          <t>As a Case Worker, I want to receive alerts for duplicate applications so that I can merge them. - System detects and flags potential duplicates.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['Applicants with common names but different addresses.', 'Same person applies with slight differences in spelling or typos.', 'Applications submitted from different channels (online and in-person).', 'Merged application with already merged records.', 'Bulk upload leading to multiple duplicates at once.']</t>
+          <t>When a new application is submitted, the system checks for existing applications with matching identifiers (e.g., name, date of birth, SSN). If matches are found, the system alerts the case worker, allowing them to review and merge duplicates.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>['Test that duplicate flagging and merging works after application creation (Related: [1, 2, 9]).']</t>
+          <t>[{'Test Case ID': '31-FUNC-01', 'Brief Description': 'Detect and alert on new duplicate application.'}, {'Test Case ID': '31-FUNC-02', 'Brief Description': 'System does not flag non-duplicates.'}, {'Test Case ID': '31-FUNC-03', 'Brief Description': 'Case worker merges duplicates successfully.'}, {'Test Case ID': '31-FUNC-04', 'Brief Description': 'Case worker attempts to merge non-duplicates.'}, {'Test Case ID': '31-API-01', 'Brief Description': 'API returns flagged duplicates for given input.'}, {'Test Case ID': '31-E2E-01', 'Brief Description': 'End-to-end: Submission, alert, review, and merge.'}, {'Test Case ID': '31-SEC-01', 'Brief Description': 'Case worker without merge permission attempts to merge.'}, {'Test Case ID': '31-COMP-01', 'Brief Description': 'Audit trail generated for merge operation.'}]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['Application submission/creation', 'Merge functionality in applications', 'Any application search and display screens']</t>
+          <t>[{'Test Case ID': '31-FUNC-01', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Application Detection', 'User Story': '31', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicate Check', 'Activity Title': 'Submit New Application', 'Test Scenario Title': 'Alert On Duplicate Application', 'Precondition': 'A similar application already exists in the system.', 'Test Data': 'Applicant with same name, DOB, and SSN as an existing record.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit a new application with matching identifiers.', 'System checks for duplicates.', 'System displays alert to user.'], 'Expected Result': 'Case worker receives a duplicate alert; application is flagged for review.', 'Dependent Module/Process': 'Database'}, {'Test Case ID': '31-FUNC-02', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Application Detection', 'User Story': '31', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicate Check', 'Activity Title': 'Submit Non-Duplicate Application', 'Test Scenario Title': 'No Alert On Unique Application', 'Precondition': 'No matching application in the system.', 'Test Data': 'Applicant with unique identifiers.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit a new application with unique identifiers.'], 'Expected Result': 'No duplicate alert; application proceeds normally.', 'Dependent Module/Process': 'Database'}, {'Test Case ID': '31-FUNC-03', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Management', 'User Story': '31', 'Business Process': 'Case Management', 'Sub-Process Title': 'Merge Records', 'Activity Title': 'Merge Duplicate Applications', 'Test Scenario Title': 'Successful Merge', 'Precondition': 'Duplicate applications flagged.', 'Test Data': 'Two applications flagged as duplicates.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to flagged duplicates.', 'Select merge option.', 'Resolve data conflicts if prompted.', 'Complete merge operation.'], 'Expected Result': 'Applications merged; single record retained; audit trail logged.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': '31-FUNC-04', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Management', 'User Story': '31', 'Business Process': 'Case Management', 'Sub-Process Title': 'Merge Records', 'Activity Title': 'Attempt Merge of Non-Duplicates', 'Test Scenario Title': 'Erroneous Merge Attempt Blocked', 'Precondition': 'Two clearly non-duplicate applications exist.', 'Test Data': 'Applications with unique identifiers.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Attempt to merge two unrelated applications.'], 'Expected Result': 'System blocks merge and shows error.', 'Dependent Module/Process': 'Validation Service'}, {'Test Case ID': '31-API-01', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Application Detection API', 'User Story': '31', 'Business Process': 'Backend Services', 'Sub-Process Title': 'API Call', 'Activity Title': 'Duplicate Check Service', 'Test Scenario Title': 'API Flags Duplicates', 'Precondition': 'API exposed for duplicate checking.', 'Test Data': "{ 'name': 'Jane Doe', 'dob': '1990-01-01', 'ssn': '123-45-6789' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call API with duplicate applicant data.'], 'Expected Result': 'API returns duplicate flag with matched record IDs.', 'Dependent Module/Process': 'API Gateway'}, {'Test Case ID': '31-E2E-01', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Processing', 'User Story': '31', 'Business Process': 'Application Submission to Merge', 'Sub-Process Title': 'End-to-End Flow', 'Activity Title': 'Duplicate Alert to Merge Completion', 'Test Scenario Title': 'E2E Duplicate Detection and Merge', 'Precondition': 'At least one duplicate exists in the database.', 'Test Data': 'Valid and duplicate applicant submissions.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit application.', 'System alerts on duplicate.', 'Review flagged application.', 'Merge duplicated records.'], 'Expected Result': 'User notified; records merged successfully; audit entry created.', 'Dependent Module/Process': 'Database, Audit'}, {'Test Case ID': '31-SEC-01', 'EPIC': 'Data Integrity', 'Feature': 'Role-Based Access', 'User Story': '31', 'Business Process': 'Permissions Enforcement', 'Sub-Process Title': 'Merge Authorization', 'Activity Title': 'Unauthorized User Attempts Merge', 'Test Scenario Title': 'Permission Enforcement', 'Precondition': 'User has view-only permission.', 'Test Data': 'Flagged duplicates present.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (No Merge Permission)', 'Detailed Test Steps': ['Login as user without merge rights.', 'Attempt to merge flagged applications.'], 'Expected Result': 'System denies merge; appropriate error displayed.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': '31-COMP-01', 'EPIC': 'Compliance', 'Feature': 'Audit Logging', 'User Story': '31', 'Business Process': 'Audit &amp; Monitoring', 'Sub-Process Title': 'Log Creation', 'Activity Title': 'Merge Operation Logged', 'Test Scenario Title': 'Audit Log Verification', 'Precondition': 'User merges duplicate applications.', 'Test Data': 'Duplicate merge event.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Merge duplicate applications.', 'Review audit logs.'], 'Expected Result': 'Audit log captures user, timestamp, and details of merge operation.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>This user story ensures that Case Managers can monitor and evaluate team performance efficiently by providing a flexible report builder to generate, filter, and export monthly activity reports based on worker and status.</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['Generate a monthly report by selecting specific worker and status filters; verify data accuracy.', 'Generate a monthly report without filters and verify all cases included.', 'Test report generation across different months and years.', 'Download/export generated report and confirm format (PDF, CSV, etc.).', 'Verify that only authorized Case Managers can access the report builder.', 'Test large data sets for performance issues.']</t>
+          <t>As a Case Manager, I want to generate monthly reports of case activity so that I can track team performance. - Report builder with filters by worker and status.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['Month or filter chosen with no case activity.', 'Worker with no cases assigned.', 'Deleted, reassigned, or inactive cases within the period.', 'Change reporting period while generating report.', 'Special characters in worker names or statuses.']</t>
+          <t>The Case Manager accesses the reporting tool, selects the required reporting period, applies filters such as worker and status, and generates a monthly report summarizing case activities.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>['Test report data accuracy where other stories filter by worker/status or export data (Related: [16, 18, 23, 30]).']</t>
+          <t>[{'Test Case ID': '32-FUNC-01', 'Brief Description': 'Generate unfiltered case activity report.'}, {'Test Case ID': '32-FUNC-02', 'Brief Description': 'Generate filtered report by worker.'}, {'Test Case ID': '32-FUNC-03', 'Brief Description': 'Generate filtered report by status.'}, {'Test Case ID': '32-FUNC-04', 'Brief Description': 'No results with unavailable filters.'}, {'Test Case ID': '32-API-01', 'Brief Description': 'API returns correct report data for query.'}, {'Test Case ID': '32-E2E-01', 'Brief Description': 'End-to-end: Report generation, export, and review.'}, {'Test Case ID': '32-SEC-01', 'Brief Description': 'Permission: Unprivileged user attempts report access.'}, {'Test Case ID': '32-COMP-01', 'Brief Description': 'Audit trail for report access and export.'}]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['Case activity logging', 'User role access controls', 'Existing or similar reporting features']</t>
+          <t>[{'Test Case ID': '32-FUNC-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Case Activity Report', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Generate Full Report', 'Test Scenario Title': 'Generate Monthly Case Report (All Filters)', 'Precondition': 'Cases exist in database for the reporting period.', 'Test Data': 'Case activity data for multiple workers and statuses.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to report builder.', 'Select current month.', 'Generate report without filters.'], 'Expected Result': 'System displays complete case activity report for the period.', 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-FUNC-02', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Report Filtering', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Filter By Worker', 'Test Scenario Title': 'Filter Report By Worker', 'Precondition': 'Cases assigned to different workers exist.', 'Test Data': 'Case activity records with assigned worker IDs.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to report builder.', 'Select worker from filter options.', 'Generate report.'], 'Expected Result': 'Report shows only cases assigned to selected worker.', 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-FUNC-03', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Report Filtering', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Filter By Status', 'Test Scenario Title': 'Filter Report By Status', 'Precondition': 'Cases with various statuses (e.g., open, closed) exist.', 'Test Data': "Case activity records with 'Open' and 'Closed' statuses.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to report builder.', "Select status filter (e.g., 'Open').", 'Generate report.'], 'Expected Result': 'Report shows only cases with selected status.', 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-FUNC-04', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Report Filtering', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Unavailable Filters', 'Test Scenario Title': 'No Results With Unavailable Filter', 'Precondition': 'No cases match filter criteria.', 'Test Data': 'No case for worker X in reporting period.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Apply filter with no matching cases.', 'Generate report.'], 'Expected Result': "Report shows 'No data available' or empty result.", 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-API-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Reporting API', 'User Story': '32', 'Business Process': 'Backend Reporting', 'Sub-Process Title': 'API Query', 'Activity Title': 'API Case Activity Report Query', 'Test Scenario Title': 'API Data Fetch and Filter', 'Precondition': 'API exposed for report queries.', 'Test Data': "{ 'period': '2024-05', 'worker': '123', 'status': 'Open' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call reporting API with selected filters.'], 'Expected Result': 'API returns correct filtered report data.', 'Dependent Module/Process': 'API, Reporting DB'}, {'Test Case ID': '32-E2E-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'End-to-End Reporting', 'User Story': '32', 'Business Process': 'Report Management', 'Sub-Process Title': 'E2E Flow', 'Activity Title': 'Report Generation to Export', 'Test Scenario Title': 'Full E2E Report Generation and Export', 'Precondition': 'Reporting module active and populated.', 'Test Data': 'All relevant case activity.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Generate monthly report.', 'Export report (e.g., CSV, PDF).', 'Review downloaded file.'], 'Expected Result': 'Report is generated, exported, and data matches on-screen results.', 'Dependent Module/Process': 'Export Service'}, {'Test Case ID': '32-SEC-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Permission Enforcement', 'User Story': '32', 'Business Process': 'Security', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Unauthorized Report Access', 'Test Scenario Title': 'Access Denied for Unprivileged User', 'Precondition': 'User assigned role without report access.', 'Test Data': 'N/A', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Attempt to access report builder.'], 'Expected Result': 'Access denied; error or redirect shown.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': '32-COMP-01', 'EPIC': 'Compliance', 'Feature': 'Audit Logging', 'User Story': '32', 'Business Process': 'Audit &amp; Reporting', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Report Generation Logging', 'Test Scenario Title': 'Audit Trail For Report Actions', 'Precondition': 'Case Manager generates and exports a report.', 'Test Data': 'Report event activity.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Generate and export report.', 'Review audit logs.'], 'Expected Result': 'Audit entry exists for report generation and export (timestamp, user, filters).', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>This user story provides important controls for compliance and operational accuracy by informing case workers of updates to eligibility rules, ensuring that assessments reflect current policies.</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['Trigger eligibility rule change and verify all relevant users receive timely notifications.', 'Check notification content for accuracy and clarity.', 'Verify dismissal and/or acknowledgment of notification.', 'Confirm new users receive notification if rule changed before their account creation.', 'Verify notification is only sent to Case Workers.']</t>
+          <t>As a Case Worker, I want to receive alerts when eligibility rules change so that I can adjust my assessments. - System notification of policy updates.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['Multiple eligibility rule changes in quick succession.', 'No recipients online/active at change time.', 'Rule changed, then rolled back.', 'User marked as inactive or deleted before notification.']</t>
+          <t>The system notifies all relevant case workers via dashboard alert, email, or in-app notification when an eligibility rule is updated, allowing timely review and adjustment of ongoing or new assessments.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'Test Case ID': '33-FUNC-01', 'Brief Description': 'Notification sent for eligibility rule update.'}, {'Test Case ID': '33-FUNC-02', 'Brief Description': 'Case Worker acknowledges alert.'}, {'Test Case ID': '33-FUNC-03', 'Brief Description': 'No alerts sent if no change.'}, {'Test Case ID': '33-E2E-01', 'Brief Description': 'End-to-end: Rule change triggers notification and case worker updates assessment.'}, {'Test Case ID': '33-SEC-01', 'Brief Description': 'Unauthorized user does not receive notifications.'}, {'Test Case ID': '33-COMP-01', 'Brief Description': 'Audit log of policy update and notifications.'}]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['Eligibility rule engine', 'User notification systems']</t>
+          <t>[{'Test Case ID': '33-FUNC-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'Rule Notifications', 'User Story': '33', 'Business Process': 'Policy Update Alerts', 'Sub-Process Title': 'Notification Distribution', 'Activity Title': 'Send Alert On Rule Change', 'Test Scenario Title': 'Notification Sent to Case Workers', 'Precondition': 'Eligibility rule is updated by administrator.', 'Test Data': 'Amend rule: Change income threshold from $1500 to $1400.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Admin updates eligibility rule.', 'System triggers notification event.', 'Case worker logs in to application.'], 'Expected Result': 'Case worker receives prompt notification of rule change.', 'Dependent Module/Process': 'Notifications, Policy Management'}, {'Test Case ID': '33-FUNC-02', 'EPIC': 'Eligibility Compliance', 'Feature': 'Alert Acknowledgement', 'User Story': '33', 'Business Process': 'Policy Update Alerts', 'Sub-Process Title': 'Acknowledgement', 'Activity Title': 'Acknowledge Policy Alert', 'Test Scenario Title': 'User Acknowledges Alert', 'Precondition': 'Case worker has received a policy update alert.', 'Test Data': 'Active user.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'View policy update alert.', 'Acknowledge (e.g., click "Acknowledge" button).'], 'Expected Result': 'Alert marked as read/acknowledged, recorded in user history.', 'Dependent Module/Process': 'User Notification Center'}, {'Test Case ID': '33-FUNC-03', 'EPIC': 'Eligibility Compliance', 'Feature': 'Rule Notifications', 'User Story': '33', 'Business Process': 'Policy Update Alerts', 'Sub-Process Title': 'Notification Logic', 'Activity Title': 'No-Change Scenario', 'Test Scenario Title': 'No Notification Sent', 'Precondition': 'No policy or rule changes.', 'Test Data': 'Unchanged eligibility rules for 30 days.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Check notifications panel for policy alerts.'], 'Expected Result': 'No new alerts present.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': '33-E2E-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'End-to-End Update Handling', 'User Story': '33', 'Business Process': 'Policy Management', 'Sub-Process Title': 'E2E Rule Update Procedure', 'Activity Title': 'Update Trigger to Assessment Adjustment', 'Test Scenario Title': 'E2E Rule Change &amp; Assessment Adjustment', 'Precondition': 'Active cases relying on eligible rules.', 'Test Data': 'Update rule; case in progress.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Update eligibility rule.', 'Case worker notified.', 'Case worker reviews open cases.', 'Adjust assessments per new rule.'], 'Expected Result': 'Notification received; assessments updated as required.', 'Dependent Module/Process': 'Assessment Engine, Notifications'}, {'Test Case ID': '33-SEC-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'RBAC - Notification Restrictions', 'User Story': '33', 'Business Process': 'Security', 'Sub-Process Title': 'Notification Permissions', 'Activity Title': 'Unauthorized User Notification Check', 'Test Scenario Title': 'Unauthorized User Is Not Notified', 'Precondition': 'Non-case worker user account exists.', 'Test Data': 'User with no eligibility assessment role.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest/Non-Case Worker', 'Detailed Test Steps': ['Login as unauthorized user.', 'Update eligibility rule as admin.', 'Check for notification.'], 'Expected Result': 'No notification sent to unauthorized user.', 'Dependent Module/Process': 'RBAC, Notifications'}, {'Test Case ID': '33-COMP-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'Audit Logging - Policy', 'User Story': '33', 'Business Process': 'Audit &amp; Notification', 'Sub-Process Title': 'Policy Update Logs', 'Activity Title': 'Audit Of Rule Change', 'Test Scenario Title': 'Audit Log Captures Policy Change And Alerts', 'Precondition': 'Policy update performed and alerts sent.', 'Test Data': 'Rule change event.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System Auditor', 'Detailed Test Steps': ['Trigger rule update and send notifications.', 'Review system audit logs.'], 'Expected Result': 'Log contains timestamp, author of change, notification recipients, and content.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>This user story focuses on enabling Case Managers to track overdue redeterminations, including listing all overdue cases with corresponding actionable follow-up items. Ensuring compliance and auditability is key.</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['List all overdue redetermination cases assigned to a Case Manager.', 'Perform follow-up action (e.g., send reminder) from overdue list, and verify outcome.', 'Sort and filter overdue cases (by priority, date, or worker).', 'Change case status and ensure overdue list refreshes.', 'Access control: only Case Managers can view overdue redeterminations.']</t>
+          <t>As a Case Manager, I want to track overdue redeterminations so that I can ensure compliance. - List of overdue cases with follow-up actions.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['No overdue cases in the system.', 'Case becomes overdue during current session.', 'Previously overdue case is resolved and reappears due to error.', 'Case reassigned while overdue.']</t>
+          <t>Case Manager logs in, navigates to the overdue redeterminations section, views a filtered list of overdue cases with follow-up actions, and initiates or records compliance activities.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>['Verify overdue determination calculation logic matches related determination features (Related: [6, 7]).']</t>
+          <t>[{'Test Case ID': 'US34_TC1', 'Brief Description': 'Display list of overdue redetermination cases with required follow-up actions (happy path)'}, {'Test Case ID': 'US34_TC2', 'Brief Description': 'No overdue cases present (edge case)'}, {'Test Case ID': 'US34_TC3', 'Brief Description': 'Follow-up action triggers compliance workflow'}, {'Test Case ID': 'US34_TC4', 'Brief Description': 'Case Manager with no permission attempts access'}, {'Test Case ID': 'US34_TC5', 'Brief Description': 'API returns incomplete/erroneous data (integration negative case)'}, {'Test Case ID': 'US34_TC6', 'Brief Description': 'Audit log properly records viewing and follow-up actions'}]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['Redetermination logic', 'Case assignment functionality', 'Overdue detection in other modules']</t>
+          <t>[{'Test Case ID': 'US34_TC1', 'EPIC': 'Redetermination Compliance', 'Feature': 'Overdue Redeterminations Tracking', 'User Story': 'US34', 'Business Process': 'Case Oversight', 'Sub-Process Title': 'Redetermination Compliance Monitoring', 'Activity Title': 'Review Overdue Redeterminations', 'Test Scenario Title': 'Display list of overdue redetermination cases with follow-up actions', 'Precondition': 'Case Manager account enabled and logged in; at least one case with an overdue redetermination exists.', 'Test Data': 'Case 103 | Redetermination Due: 2024-04-01 (overdue), Status: Pending follow-up.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', "Navigate to 'Overdue Redeterminations' section.", 'Verify system displays list of cases where redetermination due date is past today.', 'For each case, confirm relevant follow-up action(s) are displayed.'], 'Expected Result': 'List of overdue cases is presented with accurate follow-up actions; UI allows navigation to compliance actions.', 'Dependent Module/Process': 'Case Management, Compliance Module'}, {'Test Case ID': 'US34_TC2', 'EPIC': 'Redetermination Compliance', 'Feature': 'Overdue Redeterminations Tracking', 'User Story': 'US34', 'Business Process': 'Case Oversight', 'Sub-Process Title': 'Redetermination Compliance Monitoring', 'Activity Title': 'Review Overdue Redeterminations', 'Test Scenario Title': 'No overdue cases present', 'Precondition': 'Case Manager logged in; no cases with overdue redeterminations exist.', 'Test Data': 'No overdue cases in the database.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', "Navigate to 'Overdue Redeterminations' section."], 'Expected Result': 'System displays a message indicating that there are no overdue cases and disables follow-up actions.', 'Dependent Module/Process': 'Case Management'}, {'Test Case ID': 'US34_TC3', 'EPIC': 'Redetermination Compliance', 'Feature': 'Overdue Redeterminations Tracking', 'User Story': 'US34', 'Business Process': 'Case Oversight', 'Sub-Process Title': 'Redetermination Compliance Monitoring', 'Activity Title': 'Initiate Compliance Workflow', 'Test Scenario Title': 'Follow-up action triggers compliance workflow', 'Precondition': 'At least one overdue redetermination is listed for the Case Manager.', 'Test Data': 'Case 105, Overdue: 2024-04-12', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', "Navigate to 'Overdue Redeterminations' section.", 'Select an overdue case.', "Click on a follow-up action (e.g., 'Send Reminder')."], 'Expected Result': 'Compliance workflow is triggered (e.g., reminder is logged and/or sent, case note updated, audit trail updated).', 'Dependent Module/Process': 'Compliance Module, Notification Service'}, {'Test Case ID': 'US34_TC4', 'EPIC': 'Redetermination Compliance', 'Feature': 'Permissions &amp; Access Controls', 'User Story': 'US34', 'Business Process': 'Authorization', 'Sub-Process Title': 'User Role Validation', 'Activity Title': 'Enforce Role-Based Access', 'Test Scenario Title': 'Case Manager with no permission attempts access', 'Precondition': 'User account lacks Case Manager role.', 'Test Data': 'Regular User account', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Non-Case Manager', 'Detailed Test Steps': ['Log in as a user without Case Manager role (e.g., Case Worker).', "Attempt to navigate to 'Overdue Redeterminations' page."], 'Expected Result': 'System denies access with appropriate error message or redirects to insufficient permissions page.', 'Dependent Module/Process': 'Authentication, Authorization'}, {'Test Case ID': 'US34_TC5', 'EPIC': 'Redetermination Compliance', 'Feature': 'Integration &amp; API', 'User Story': 'US34', 'Business Process': 'System Integration', 'Sub-Process Title': 'API Communication', 'Activity Title': 'Handle Data Errors Gracefully', 'Test Scenario Title': 'API returns incomplete/erroneous data', 'Precondition': 'API mocks configured to return malformed data.', 'Test Data': 'Malformed JSON (missing required fields)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Trigger UI/API fetch for overdue redeterminations with simulated API error.', "Observe system's response."], 'Expected Result': 'Error message displayed; system logs error and avoids crashing; compliance/audit report unaffected.', 'Dependent Module/Process': 'API Gateway, Error Logging'}, {'Test Case ID': 'US34_TC6', 'EPIC': 'Redetermination Compliance', 'Feature': 'Audit &amp; Compliance', 'User Story': 'US34', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Compliance Auditing', 'Activity Title': 'Record User Actions', 'Test Scenario Title': 'Audit log records viewing and follow-up actions', 'Precondition': 'Audit logging is enabled in the system.', 'Test Data': 'Test actions by Case Manager.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'View an overdue redetermination case.', 'Initiate a follow-up action (e.g., send reminder).', 'Check audit log.'], 'Expected Result': 'Audit log contains entry for viewing the case and for executing follow-up action, including timestamp, user ID, and action type.', 'Dependent Module/Process': 'Audit Trail, Compliance Module'}]</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Workers can generate a printable summary of case notes for inclusion in physical files, supporting both digital and paper-based record-keeping and compliance.</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Print summary for a case with multiple notes and verify formatting/layout.', 'Print summary for case with no notes (empty state handling).', 'Ensure confidential/flagged notes are handled per policy.', 'Verify only authorized users can print case note summaries.', 'Check print/export in different browsers and devices.']</t>
+          <t>As a Case Worker, I want to print a summary of case notes so that I can include them in physical files. - Printable case note summary.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['Very large number of case notes.', 'Case notes with images, special formatting, or attachments.', 'Case notes in multiple languages.', 'Corrupted or partially-saved notes.']</t>
+          <t>Case Worker selects a case, chooses 'Print Summary', and receives a formatted, print-ready document containing the relevant case notes.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>['Consistency of printable output/data integrity with digital display/exported case notes (Related: [16]).']</t>
+          <t>[{'Test Case ID': 'US35_TC1', 'Brief Description': 'Generate and print summary for cases with notes (happy path)'}, {'Test Case ID': 'US35_TC2', 'Brief Description': 'Case with no notes (edge case)'}, {'Test Case ID': 'US35_TC3', 'Brief Description': 'User without print permission attempts to print'}, {'Test Case ID': 'US35_TC4', 'Brief Description': 'Printable summary meets format and compliance requirements'}, {'Test Case ID': 'US35_TC5', 'Brief Description': 'API error when generating summary (integration negative case)'}]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['Case note management/storage', 'Exporting/printing frameworks']</t>
+          <t>[{'Test Case ID': 'US35_TC1', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Print Case Notes Summary', 'Test Scenario Title': 'Generate and print summary for cases with notes', 'Precondition': 'Case Worker is logged in and has at least one case with saved notes.', 'Test Data': 'Case 202 | Case Notes: 3 entries', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Navigate to a specific case with notes.', "Select 'Print Summary' or equivalent option.", 'Preview or directly print the summary.'], 'Expected Result': 'Case note summary is generated accurately and formatted for printing; printable dialog or PDF is presented.', 'Dependent Module/Process': 'Case Management, Print Services'}, {'Test Case ID': 'US35_TC2', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Handle Cases with No Notes', 'Test Scenario Title': 'Case with no notes', 'Precondition': 'Case Worker is logged in; at least one case has no notes.', 'Test Data': 'Case 203 | No notes available.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Navigate to a case with no notes.', 'Attempt to print the summary.'], 'Expected Result': "System displays message 'No notes available to print', disables print function, or generates a blank (but formatted) summary.", 'Dependent Module/Process': 'Case Management'}, {'Test Case ID': 'US35_TC3', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Access Control', 'Sub-Process Title': 'User Role Validation', 'Activity Title': 'Enforce Print Permissions', 'Test Scenario Title': 'User without print permission attempts to print', 'Precondition': "User is not granted 'Print Case Notes' permission.", 'Test Data': 'Regular User account', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'User without Print Permission', 'Detailed Test Steps': ['Log in as user without print permission.', 'Navigate to case notes.', "Attempt to initiate 'Print Summary' action."], 'Expected Result': 'System prevents the action, shows an authorization error message or disables print button.', 'Dependent Module/Process': 'Authorization Module'}, {'Test Case ID': 'US35_TC4', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Compliance', 'Sub-Process Title': 'Format Validation', 'Activity Title': 'Printable Summary Format Validation', 'Test Scenario Title': 'Printable summary meets format and compliance requirements', 'Precondition': 'Case Worker is authorized and can print; template is set as per compliance rules.', 'Test Data': 'Case 202 | Notes with sensitive and non-sensitive info.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Generate printable summary for a case.', 'Review the document format and required disclosure/compliance elements (headers, confidentiality statement, redactions).'], 'Expected Result': 'Printable summary matches mandated format; confidential data is protected or omitted; compliance footer present.', 'Dependent Module/Process': 'Compliance/Legal'}, {'Test Case ID': 'US35_TC5', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'System Integration', 'Sub-Process Title': 'API Communication', 'Activity Title': 'Error Handling During Summary Generation', 'Test Scenario Title': 'API error when generating summary', 'Precondition': 'API mock or backend is configured to return error on summary request.', 'Test Data': 'N/A (force error response)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to print case notes when backend/API is failing.', 'Observe system behavior.'], 'Expected Result': 'User receives a meaningful error message and/or retry option; system logs error for audit.', 'Dependent Module/Process': 'API Gateway, Error Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>This user story describes a notification system for Case Managers, alerting them when a case is inactive for 60 days, including access to relevant case history for follow-up and compliance.</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['Receive alert when a case is inactive for exactly 60 days.', 'Alert contains relevant case history.', 'No alert is sent for cases inactive for less than 60 days.', 'Alert is sent only once per inactivity event.', 'Alert displays correct case manager and case information.']</t>
+          <t>As a Case Manager, I want to receive alerts when a case is inactive for 60 days so that I can follow up. - Inactivity alerts with case history.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['Case is updated at 59 days, then inactive — ensure timer resets.', 'Case marked inactive right before a leap day.', 'Multiple cases become inactive on the same day.', 'Case is reactivated and becomes inactive again.']</t>
+          <t>Case becomes inactive for 60 days, Case Manager receives alert, reviews case history, and performs follow-up actions or logs compliance.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>['Test alert notification system with story 40 (Workload alerts).']</t>
+          <t>[{'Test Case ID': 'US36_TC1', 'Brief Description': 'Trigger and display alert for case inactive for 60 days (happy path)'}, {'Test Case ID': 'US36_TC2', 'Brief Description': 'Case becomes active before 60 days (should not alert)'}, {'Test Case ID': 'US36_TC3', 'Brief Description': 'Case Manager with alert permission only receives relevant notifications'}, {'Test Case ID': 'US36_TC4', 'Brief Description': 'Alert includes sufficient case history for meaningful follow-up'}, {'Test Case ID': 'US36_TC5', 'Brief Description': 'Integration: Alert system fails to send notification (negative case)'}, {'Test Case ID': 'US36_TC6', 'Brief Description': 'Audit log records alert delivery and Case Manager action'}]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['Retest alert delivery system (shared with stories 40).', 'Verify alert history logging and display.']</t>
+          <t>[{'Test Case ID': 'US36_TC1', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Notification', 'Sub-Process Title': 'Inactivity Detection', 'Activity Title': 'Trigger Inactivity Alert', 'Test Scenario Title': 'Trigger and display alert for case inactive for 60 days', 'Precondition': 'Case has had no activity for exactly 60 days; Case Manager subscribes to alert notifications.', 'Test Data': "Case 301 | Last Activity: 2024-03-01; today's date: 2024-04-30.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Ensure case has had 59 days of inactivity.', 'Do not perform any activity for the 60th day.', 'Once 60 days pass, log in as Case Manager.', 'Verify notification is received regarding inactivity.'], 'Expected Result': 'Alert/notification is received by the Case Manager; alert is visible in dashboard and/or email as configured.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'US36_TC2', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Notification', 'Sub-Process Title': 'Inactivity Detection', 'Activity Title': 'Suppress Alert for Recently Active Case', 'Test Scenario Title': 'Case becomes active before 60 days (should not alert)', 'Precondition': 'Case has had recent activity within last 60 days.', 'Test Data': 'Case 302 | Last Activity: 2024-04-10.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Make at least one activity update on case within 59 days.', 'Check for alert at 60-day mark.'], 'Expected Result': 'No inactivity alert is issued for that case.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'US36_TC3', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Authorization', 'Sub-Process Title': 'User Role Validation', 'Activity Title': 'Permission-based Notification', 'Test Scenario Title': 'Case Manager with alert permission only receives relevant notifications', 'Precondition': 'System contains multiple users, some with and some without alert permissions.', 'Test Data': 'Case 303 | Inactive 60 days', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Non-Case Manager', 'Detailed Test Steps': ['Log in as Case Manager and as user without case oversight role.', 'Verify which users receive alerts.'], 'Expected Result': 'Only Case Managers with correct permissions receive inactivity alerts.', 'Dependent Module/Process': 'Authorization, Notification Engine'}, {'Test Case ID': 'US36_TC4', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Notification', 'Sub-Process Title': 'Alert Content Verification', 'Activity Title': 'Display Case History in Alert', 'Test Scenario Title': 'Alert includes sufficient case history for meaningful follow-up', 'Precondition': 'Inactivity alert triggered on case.', 'Test Data': 'Case 301 | Last Activity: 2024-03-01; Case History: all events last 6 months.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Receive inactivity alert.', 'Open alert details.', 'Review included case history.'], 'Expected Result': 'Alert contains a concise summary of relevant recent case history (e.g., last activity, responsible party, pending items).', 'Dependent Module/Process': 'Case History Module, Notification Engine'}, {'Test Case ID': 'US36_TC5', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'System Integration', 'Sub-Process Title': 'Notification Delivery', 'Activity Title': 'Handle Notification Failures', 'Test Scenario Title': 'Integration: Alert system fails to send notification', 'Precondition': 'Notification engine integration is simulated to fail.', 'Test Data': 'Simulated notification service downtime.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Simulate notification engine outage.', 'Inactivity threshold met for a case.', 'Log in as Case Manager.', 'Check alert delivery status.'], 'Expected Result': 'User does not receive alert, system logs delivery failure, and support/audit team notified as per compliance requirements.', 'Dependent Module/Process': 'Notification Engine, Logging'}, {'Test Case ID': 'US36_TC6', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Compliance Auditing', 'Activity Title': 'Audit Alert Delivery and Actions', 'Test Scenario Title': 'Audit log records alert delivery and Case Manager action', 'Precondition': 'Audit system is active; inactivity alert is triggered.', 'Test Data': 'Case 304 | 60 days inactive, alert delivered.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Receive inactivity alert as Case Manager.', 'Review and perform follow-up action.', 'Check audit log entries.'], 'Expected Result': 'Audit log reflects alert delivery timestamp, recipient, and records any subsequent follow-up activity for compliance and audit review.', 'Dependent Module/Process': 'Audit Trail, Notification Engine'}]</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>This user story addresses the need for Case Workers to be promptly notified when clients provide conflicting income information, enabling them to investigate and resolve inconsistencies in a timely manner. The focus is on generating alerts based on automated income data validation, ensuring data integrity and compliance.</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['Alert generated when new income data entry conflicts with existing records.', 'Alert states which data fields conflict.', 'Case Worker receives only relevant conflicting income alerts.', 'No duplicate alerts for same conflict.', 'Resolved conflicts are not repeatedly alerted.']</t>
+          <t>As a Case Worker, I want to receive alerts when a client submits conflicting income data so that I can investigate. - Income validation alerts.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['Multiple conflicting entries submitted simultaneously.', 'Income field left blank vs. zero.', 'Client edits same value back and forth before saving.', 'Edge values (e.g., maximum/minimum allowed income).']</t>
+          <t>A client submits income data that conflicts with existing records. The system automatically detects the inconsistency and generates an alert for the assigned Case Worker for timely investigation.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['Validation logic from story 3 if income validation is reused.']</t>
+          <t>[{'Test Case ID': 'TC_37_01', 'Brief Description': 'Alert triggers when client submits new income data that conflicts with previous data.'}, {'Test Case ID': 'TC_37_02', 'Brief Description': 'No alert is triggered when income data submitted is consistent with existing records.'}, {'Test Case ID': 'TC_37_03', 'Brief Description': 'Alert is only delivered to authorized Case Worker, not to unauthorized users.'}, {'Test Case ID': 'TC_37_04', 'Brief Description': 'System logs alert for compliance/audit purposes.'}, {'Test Case ID': 'TC_37_05', 'Brief Description': 'System fails gracefully if validation engine is down (negative test).'}, {'Test Case ID': 'TC_37_06', 'Brief Description': 'Alert correctly includes relevant client details and type of conflict.'}]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['Retest income validation (story 3).', 'Retest alert notification delivery.']</t>
+          <t>[{'Test Case ID': 'TC_37_01', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Intake &amp; Verification', 'Sub-Process Title': 'Income Submission', 'Activity Title': 'Income Data Validation', 'Test Scenario Title': 'Alert is triggered for conflicting income data', 'Precondition': 'Case Worker and client are registered in the system. Client has historical income record.', 'Test Data': {'ClientID': 'C10012', 'ExistingIncome': '$2000/month', 'SubmittedIncome': '$5000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as client.', '2. Navigate to income submission form.', '3. Submit new income value ($5000/month, when previous was $2000/month).', '4. System performs income data validation post-submission.', '5. System detects conflict.', '6. System generates and delivers alert to assigned Case Worker.'], 'Expected Result': 'Case Worker receives alert with client details, previous and current income values, and nature of conflict.', 'Dependent Module/Process': 'Notification Service, Data Validation Engine'}, {'Test Case ID': 'TC_37_02', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Intake &amp; Verification', 'Sub-Process Title': 'Income Submission', 'Activity Title': 'Consistent Data Submission', 'Test Scenario Title': 'No alert for non-conflicting income submission', 'Precondition': 'Client has existing income record consistent with new submission.', 'Test Data': {'ClientID': 'C10012', 'ExistingIncome': '$2000/month', 'SubmittedIncome': '$2000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as client.', '2. Submit income value identical to previous value.', '3. System performs validation.', '4. No conflict detected.'], 'Expected Result': 'No alert generated or delivered to Case Worker.', 'Dependent Module/Process': 'Notification Service, Data Validation Engine'}, {'Test Case ID': 'TC_37_03', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Notification', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Alert Delivery', 'Test Scenario Title': 'Alert goes only to assigned Case Worker', 'Precondition': 'Client submits conflicting income data.', 'Test Data': {'ClientID': 'C10012', 'AssignedCaseWorker': 'CW567'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Unassigned User', 'Detailed Test Steps': ['1. Client submits conflicting income data.', '2. System generates alert.', '3. Attempt to access alert as assigned Case Worker, another Case Worker, and unauthorized user.'], 'Expected Result': 'Alert visible only to assigned Case Worker, not to unauthorized users.', 'Dependent Module/Process': 'Access Control, Notification Service'}, {'Test Case ID': 'TC_37_04', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Logging', 'Activity Title': 'Alert Event Logging', 'Test Scenario Title': 'Alert is logged for compliance/audit', 'Precondition': 'System is configured for audit logging.', 'Test Data': {'ClientID': 'C10012', 'ConflictingIncome': True}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Auditor', 'Detailed Test Steps': ['1. Client submits conflicting income data.', '2. Alert is generated.', '3. Query audit log as Auditor.'], 'Expected Result': 'Audit log contains entry with client ID, alert time, case worker ID, and description of conflict.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}, {'Test Case ID': 'TC_37_05', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Exception Handling', 'Sub-Process Title': 'System Fault', 'Activity Title': 'Validation Engine Down', 'Test Scenario Title': 'System handles validation service outage gracefully', 'Precondition': 'Validation engine is non-operational.', 'Test Data': {'ClientID': 'C10012', 'SubmittedIncome': '$7000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Simulate income submission while validation engine is down.', '2. Monitor system response to submission.'], 'Expected Result': 'User receives error or information message; no false alerts are generated. Incident is logged.', 'Dependent Module/Process': 'Notification Service, Validation Engine'}, {'Test Case ID': 'TC_37_06', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Notification', 'Sub-Process Title': 'Alert Content Validation', 'Activity Title': 'Alert Content Check', 'Test Scenario Title': 'Alert content contains all required fields', 'Precondition': 'Case Worker with assigned client.', 'Test Data': {'ClientID': 'C10012', 'PreviousIncome': '$2500/month', 'SubmittedIncome': '$8000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Trigger conflict by submitting different income.', '2. Receive alert and inspect contents.'], 'Expected Result': 'Alert message includes client name/ID, both income values, timestamp, and nature of conflict.', 'Dependent Module/Process': 'Notification Service'}]</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>This user story ensures that Case Managers have visibility into the volume and urgency of escalated cases over time. The system must provide accurate metrics via a dashboard, supporting operational reporting and decision-making.</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['Dashboard displays count of currently escalated cases.', 'Dashboard updates when new case is escalated/de-escalated.', 'Access controls: only managers can see escalation metrics.', 'Escalation trend graph reflects historical data accurately.', 'Multiple escalations/de-escalations in quick succession are tracked correctly.']</t>
+          <t>As a Case Manager, I want to track the number of escalated cases so that I can report on urgency trends. - Escalation metrics dashboard.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['No cases escalated (dashboard shows zero).', 'Cases escalated and de-escalated within same reporting period.', 'Edge of reporting period (e.g., case escalated at midnight).', 'Large numbers of escalated cases (stress test).']</t>
+          <t>Case escalation events are captured in real time. The dashboard for Case Managers displays up-to-date counts of escalated cases, supports filtering and export, and ensures only authorized access.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['Escalation tracking logic (story 20) - if escalation is a shared attribute.']</t>
+          <t>[{'Test Case ID': 'TC_38_01', 'Brief Description': 'Escalated cases are reflected in dashboard metrics in real time.'}, {'Test Case ID': 'TC_38_02', 'Brief Description': 'Non-escalated cases are not included in escalated count.'}, {'Test Case ID': 'TC_38_03', 'Brief Description': 'Dashboard access is restricted to Case Managers.'}, {'Test Case ID': 'TC_38_04', 'Brief Description': 'Case Manager can export/report on escalation data.'}, {'Test Case ID': 'TC_38_05', 'Brief Description': 'Dashboard handles system errors gracefully (negative).'}, {'Test Case ID': 'TC_38_06', 'Brief Description': 'Dashboard includes historical data and filtering by date/urgency.'}]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['Retest escalation case workflow (story 20).', 'Retest reporting/dashboard modules.']</t>
+          <t>[{'Test Case ID': 'TC_38_01', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Escalations Tracking', 'Sub-Process Title': 'Dashboard Update', 'Activity Title': 'Real-Time Metrics Update', 'Test Scenario Title': 'Escalated case is instantly reflected in metrics', 'Precondition': 'Case is present and assigned to a worker.', 'Test Data': {'CaseID': 'E12345', 'EscalationFlag': 'True'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Escalate a case as a Case Worker.', '2. Log in as Case Manager.', '3. Open escalation dashboard.', '4. Check escalated case count.'], 'Expected Result': 'Dashboard shows increased count, including the newly escalated case.', 'Dependent Module/Process': 'Case Management, Dashboard Service'}, {'Test Case ID': 'TC_38_02', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Escalations Tracking', 'Sub-Process Title': 'Non-Escalated Case', 'Activity Title': 'Metrics Exclusion', 'Test Scenario Title': 'Non-escalated cases are not counted', 'Precondition': 'Non-escalated case exists.', 'Test Data': {'CaseID': 'NE54321', 'EscalationFlag': 'False'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Do not escalate case NE54321.', '2. View dashboard.', '3. Check escalated case count.'], 'Expected Result': 'Dashboard does not include non-escalated case in escalated metrics.', 'Dependent Module/Process': 'Case Management, Dashboard Service'}, {'Test Case ID': 'TC_38_03', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role Check', 'Activity Title': 'Dashboard Access Control', 'Test Scenario Title': 'Only Case Managers can access the dashboard', 'Precondition': 'Dashboard is configured. User roles assigned.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Case Worker', 'Detailed Test Steps': ['1. Attempt to log in as Case Manager; open dashboard.', '2. Attempt to log in as Case Worker; open dashboard.'], 'Expected Result': 'Dashboard is accessible only to users with Case Manager role.', 'Dependent Module/Process': 'User Management, Access Control'}, {'Test Case ID': 'TC_38_04', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Reporting', 'Sub-Process Title': 'Export Data', 'Activity Title': 'Dashboard Export', 'Test Scenario Title': 'Case Manager can export escalation metrics', 'Precondition': 'Escalation metrics dashboard is accessible.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Log in as Case Manager.', '2. Open escalation dashboard.', '3. Choose export option (CSV/XLS/PDF).'], 'Expected Result': 'Dashboard successfully exports correct data format containing escalated cases.', 'Dependent Module/Process': 'Dashboard Service, Export Service'}, {'Test Case ID': 'TC_38_05', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Exception Handling', 'Sub-Process Title': 'Dashboard Failure', 'Activity Title': 'Graceful Failure', 'Test Scenario Title': 'Dashboard handles failure gracefully', 'Precondition': 'Dashboard backend is offline or unavailable.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Simulate backend outage.', '2. Attempt to access dashboard.'], 'Expected Result': 'User receives appropriate error message; no incomplete or misleading data shown.', 'Dependent Module/Process': 'Dashboard Service, Exception Handler'}, {'Test Case ID': 'TC_38_06', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Reporting', 'Sub-Process Title': 'Filtering', 'Activity Title': 'Historical Data and Filters', 'Test Scenario Title': 'Dashboard supports filters by date and urgency', 'Precondition': 'Dashboard contains escalated case history.', 'Test Data': {'Dates': ['2023-05-01 to 2024-01-30'], 'UrgencyLevels': ['Low', 'High']}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Open escalation dashboard.', '2. Apply date range and urgency filters.', '3. View filtered results.'], 'Expected Result': 'Dashboard displays correct numbers for specified date range and urgency.', 'Dependent Module/Process': 'Dashboard Service'}]</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>This user story requires notifications for Case Workers when clients upload documents after normal business hours (e.g., 6PM-8AM). Such alerts help prioritize urgent, after-hours submissions and emphasize timely case management.</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['Alert sent when document upload occurs outside business hours.', 'Correct case worker receives after-hours upload alerts.', 'Alerts include correct document and client context.', 'Business hours are configurable and respected.', 'Multiple uploads after-hours trigger individual alerts.']</t>
+          <t>As a Case Worker, I want to receive alerts when a client uploads a document after business hours so that I can prioritize review. - After-hours upload alerts.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['Upload occurs on boundary time (exact close/open of business hours).', 'Client uploads multiple files quickly after hours.', 'Leap year/Daylight Saving Time changes on business hours.', 'Case Worker is on leave or changed assignment post-upload.']</t>
+          <t>A client uploads a document at 9:30PM. The system detects time of upload and immediately notifies assigned Case Worker. Alert contains document and client details for prioritization.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['Upload notification logic (stories 8 and 17).']</t>
+          <t>[{'Test Case ID': 'TC_39_01', 'Brief Description': 'Alert triggers for document uploaded outside business hours.'}, {'Test Case ID': 'TC_39_02', 'Brief Description': 'No alert triggers for document uploaded within business hours.'}, {'Test Case ID': 'TC_39_03', 'Brief Description': 'Only assigned Case Worker receives after-hours alert.'}, {'Test Case ID': 'TC_39_04', 'Brief Description': 'Alert includes client, document, and timestamp details.'}, {'Test Case ID': 'TC_39_05', 'Brief Description': 'System logs after-hours alert for compliance/audit.'}, {'Test Case ID': 'TC_39_06', 'Brief Description': 'System handles time-zone variance correctly.'}]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['Retest document upload workflow (stories 8 and 17).', 'Retest notification/alerting system.']</t>
+          <t>[{'Test Case ID': 'TC_39_01', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Document Handling', 'Sub-Process Title': 'Upload Monitoring', 'Activity Title': 'After-Hours Detection', 'Test Scenario Title': 'Alert for after-hours upload', 'Precondition': 'Client has assigned Case Worker. Upload allowed anytime.', 'Test Data': {'ClientID': 'C20021', 'DocumentType': 'Proof of Income', 'UploadTime': '21:30'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as client and upload document at 21:30.', '2. System detects time outside business hours.', '3. System triggers alert to assigned Case Worker.'], 'Expected Result': 'Case Worker receives alert including client, document, and timestamp details.', 'Dependent Module/Process': 'Notification Service, Upload Module'}, {'Test Case ID': 'TC_39_02', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Document Handling', 'Sub-Process Title': 'Upload Monitoring', 'Activity Title': 'Business Hours Upload', 'Test Scenario Title': 'No alert for uploads within business hours', 'Precondition': 'Business hours defined (e.g., 8AM-6PM). Client assigned.', 'Test Data': {'ClientID': 'C20021', 'UploadTime': '10:30'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Client uploads document at 10:30.', '2. System detects time within business hours.'], 'Expected Result': 'No after-hours alert triggered.', 'Dependent Module/Process': 'Notification Service, Upload Module'}, {'Test Case ID': 'TC_39_03', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Notification', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Restricted Delivery', 'Test Scenario Title': 'Only assigned Case Worker receives alert', 'Precondition': 'Client is assigned to a specific Case Worker.', 'Test Data': {'ClientID': 'C20021', 'AssignedCaseWorker': 'CW789'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Unauthorized User', 'Detailed Test Steps': ['1. Upload document after hours.', '2. System delivers alert.', '3. Attempt to access alert as assigned and unassigned users.'], 'Expected Result': 'Only assigned Case Worker can view alert; unauthorized users cannot.', 'Dependent Module/Process': 'Notification Service, Access Control'}, {'Test Case ID': 'TC_39_04', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Notification', 'Sub-Process Title': 'Alert Details', 'Activity Title': 'Alert Content Validation', 'Test Scenario Title': 'Alert includes key details', 'Precondition': 'Client uploads document after hours.', 'Test Data': {'ClientID': 'C20021', 'DocumentName': 'Proof of Residency.pdf', 'UploadTime': '19:45'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Inspect the received alert.', '2. Review client and document information.'], 'Expected Result': 'Alert includes client name/ID, document name/type, upload timestamp.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_39_05', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Logging', 'Activity Title': 'Alert Auditing', 'Test Scenario Title': 'After-hours alerts are audit-logged', 'Precondition': 'Audit log enabled.', 'Test Data': {'ClientID': 'C20021', 'UploadTime': '22:00'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor', 'Detailed Test Steps': ['1. Trigger after-hours alert by uploading document.', '2. Reviewer queries audit log.'], 'Expected Result': 'Log contains: alert type, timestamp, client ID, document type, Case Worker ID.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}, {'Test Case ID': 'TC_39_06', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Configuration', 'Sub-Process Title': 'Time Zone Handling', 'Activity Title': 'Time Zone Configuration', 'Test Scenario Title': 'System accounts for time-zone differences', 'Precondition': 'Users in multiple time zones.', 'Test Data': {'ClientID': 'C20021', 'UploadTimeUTC': '02:00', 'CaseWorkerTimeZone': 'EST', 'ClientTimeZone': 'PST'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Client in PST uploads document at 6PM PST.', '2. System calculates local business hours based on Case Worker time zone (EST).', '3. Determine if alert should trigger.'], 'Expected Result': "Alert is based on business hours in assigned Case Worker's time zone; time calculations validated.", 'Dependent Module/Process': 'Notification Service, User Profile Service'}]</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>This user story requires the implementation of automated workload threshold alerts for Case Managers, enabling them to proactively manage and reassign cases when a caseworker is overloaded. The test coverage will focus on correct alert generation, delivery, role restrictions, integration with thresholds, audit requirements, and negative scenarios such as missing thresholds or unauthorized access.</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['Alert sent to Case Manager when Case Worker is assigned above workload threshold.', 'Accurate calculation of workload (e.g., number of cases, complexity weighting).', 'Alert includes list of overloaded Case Workers and their assigned cases.', 'Alert is not sent when workload is below threshold.', 'Case reassignment clears previous overload alert.']</t>
+          <t>As a Case Manager, I want to receive alerts when a caseworker is overloaded so that I can reassign cases. (Workload threshold alerts)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['Worker receives cases above threshold and then cases are closed rapidly.', 'Threshold change after assignment (e.g., lowered).', 'Simultaneous reassignment among multiple workers.', 'Very high number of concurrent overloads.']</t>
+          <t>When a caseworker's assigned case count exceeds a pre-defined threshold, the system automatically generates and sends an alert notification to the responsible Case Manager, who can then access the system to review and act on the alert.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['Alert notification system (shared with story 36).']</t>
+          <t>[{'Test Case ID': 'TC40-001', 'Brief Description': 'Caseworker exceeds workload threshold; alert sent to assigned Case Manager (Positive/Functional)'}, {'Test Case ID': 'TC40-002', 'Brief Description': 'Threshold not crossed; no alert generated (Negative/Functional)'}, {'Test Case ID': 'TC40-003', 'Brief Description': 'Verify only Case Managers receive alerts for their own teams (Negative/User Role &amp; Permissions)'}, {'Test Case ID': 'TC40-004', 'Brief Description': 'Workload threshold changed; system uses updated threshold for alert generation (Integration/Functional)'}, {'Test Case ID': 'TC40-005', 'Brief Description': 'API returns correct workload alert status for dashboard (API/Integration)'}, {'Test Case ID': 'TC40-006', 'Brief Description': 'Audit log entry created when alert is sent (Compliance/Audit)'}, {'Test Case ID': 'TC40-007', 'Brief Description': 'Case Manager can access alert details and reassign cases (E2E/Functional)'}, {'Test Case ID': 'TC40-008', 'Brief Description': 'Unauthorized user attempts to access alert details (Negative/Security/Permissions)'}, {'Test Case ID': 'TC40-009', 'Brief Description': 'System unavailable during threshold breach; alert generated after recovery (Negative/Recovery/Integration)'}]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['Retest alert delivery (story 36).', 'Retest case assignment logic (stories 10, 18).']</t>
+          <t>[{'Test Case ID': 'TC40-001', 'EPIC': 'Case Management', 'Feature': 'Workload Monitoring', 'User Story': 'US-40', 'Business Process': 'Case Allocation', 'Sub-Process Title': 'Workload Assessment', 'Activity Title': 'Threshold Alert Generation', 'Test Scenario Title': 'Caseworker exceeds workload threshold; alert sent to Case Manager', 'Precondition': 'Caseworker assigned to at least N cases (N is the configured threshold); Case Manager is linked to caseworker; Notification system is operational.', 'Test Data': {'CaseworkerID': 'CW1234', 'CaseManagerID': 'CM4678', 'Threshold': 15, 'CurrentAssignedCases': 16}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Admin and set workload threshold for caseworkers to 15.', 'Assign 16 active cases to CW1234.', "Wait for system's workload evaluation job to run.", 'Log in as Case Manager CM4678.', "Navigate to 'Workload Alerts' or notification center."], 'Expected Result': 'Alert is displayed to CM4678 indicating CW1234 has exceeded the workload threshold. Alert content includes caseworker name, assigned cases count, timestamp, and actionable link to reassign.', 'Dependent Module/Process': 'Notification system, Caseworker assignment, User roles/permissions'}, {'Test Case ID': 'TC40-002', 'EPIC': 'Case Management', 'Feature': 'Workload Monitoring', 'User Story': 'US-40', 'Business Process': 'Case Allocation', 'Sub-Process Title': 'Workload Assessment', 'Activity Title': 'No Alert When Threshold Not Crossed', 'Test Scenario Title': 'Caseworker under workload threshold; no alert should be sent', 'Precondition': 'Caseworker below threshold; Threshold configured; Notification system operational.', 'Test Data': {'CaseworkerID': 'CW5678', 'Threshold': 15, 'CurrentAssignedCases': 14}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Set workload threshold for caseworkers to 15.', 'Assign 14 active cases to CW5678.', 'Force workload evaluation run if necessary.', 'Log in as case manager for CW5678.', 'Check for new workload alerts.'], 'Expected Result': 'No alert should be generated or visible to any Case Manager for CW5678.', 'Dependent Module/Process': 'Notification system, User roles/permissions'}, {'Test Case ID': 'TC40-003', 'EPIC': 'Security &amp; Compliance', 'Feature': 'Role-Based Access Control', 'User Story': 'US-40', 'Business Process': 'Alert Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict Alert Visibility by Role', 'Test Scenario Title': 'Only authorized Case Managers can receive alerts', 'Precondition': 'Workload threshold exceeded for a caseworker; Multiple Case Managers exist (some unrelated); Notification system operational.', 'Test Data': {'CaseworkerID': 'CW1234', 'AuthorizedManagerID': 'CM4678', 'UnauthorizedManagerID': 'CM9898', 'Threshold': 10, 'CurrentAssignedCases': 12}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Other Manager', 'Detailed Test Steps': ['Assign 12 cases to CW1234, assigned to CM4678.', 'Ensure CM9898 is not linked to CW1234.', 'Run workload evaluation.', 'Log in as CM9898 (unauthorized).', 'Navigate to workload alerts and check for any alert regarding CW1234.'], 'Expected Result': 'CM9898 does not receive any alert for CW1234. Only CM4678 is notified.', 'Dependent Module/Process': 'Notification system, User management'}, {'Test Case ID': 'TC40-004', 'EPIC': 'Case Management', 'Feature': 'Workload Monitoring', 'User Story': 'US-40', 'Business Process': 'Threshold Configuration', 'Sub-Process Title': 'Threshold Management', 'Activity Title': 'Alert Generation with Updated Thresholds', 'Test Scenario Title': 'System responds to threshold changes for future alerts', 'Precondition': 'Initial threshold set; Caseworker close to threshold.', 'Test Data': {'CaseworkerID': 'CW2345', 'OldThreshold': 10, 'NewThreshold': 15, 'CurrentAssignedCases': 12}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Set threshold to 10, assign 12 cases (alert should trigger).', 'Reset threshold to 15.', 'Run workload evaluation.', 'Log in as assigned Case Manager, review alerts.'], 'Expected Result': 'No new alert is generated for CW2345 after threshold increased, unless actual cases exceed new threshold.', 'Dependent Module/Process': 'Threshold config, Notification system'}, {'Test Case ID': 'TC40-005', 'EPIC': 'Workload API', 'Feature': 'Alert Status Delivery', 'User Story': 'US-40', 'Business Process': 'Data Integration', 'Sub-Process Title': 'API Availability', 'Activity Title': 'Provide Alert Status via API', 'Test Scenario Title': 'API call retrieves accurate workload alert status', 'Precondition': 'Threshold breached for a caseworker; alert has been generated.', 'Test Data': {'CaseworkerID': 'CW3456', 'AlertStatus': 'Active'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'API Consumer (Dashboard/App)', 'Detailed Test Steps': ['Trigger a threshold breach for CW3456.', 'Call the relevant API endpoint (GET /api/alerts/workloads?caseworker=CW3456).'], 'Expected Result': "API returns JSON payload showing 'Active' alert for CW3456, including timestamp and related info.", 'Dependent Module/Process': 'API Gateway, Notification system, Workload module'}, {'Test Case ID': 'TC40-006', 'EPIC': 'Case Management Audit', 'Feature': 'Compliance Logging', 'User Story': 'US-40', 'Business Process': 'Audit &amp; Reporting', 'Sub-Process Title': 'Alert Event Logging', 'Activity Title': 'Audit Entry for Alert Sent', 'Test Scenario Title': 'Audit record created when alert is sent', 'Precondition': 'Alert generated for threshold breach.', 'Test Data': {'CaseworkerID': 'CW4444', 'CaseManagerID': 'CM5555', 'Threshold': 15}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Administrator', 'Detailed Test Steps': ['Trigger alert by assigning 16 cases to CW4444.', 'Access audit log as Audit Admin.', 'Search for alert generation event for CW4444.'], 'Expected Result': 'Audit log includes entry: caseworker ID, manager ID, alert timestamp, threshold crossed, action taken.', 'Dependent Module/Process': 'Audit log, Notification system'}, {'Test Case ID': 'TC40-007', 'EPIC': 'Case Management', 'Feature': 'Case Reassignment', 'User Story': 'US-40', 'Business Process': 'End-to-End Allocation', 'Sub-Process Title': 'Alert Response', 'Activity Title': 'Reassign after Alert', 'Test Scenario Title': 'Case Manager acts on alert, reassigns case', 'Precondition': 'Alert for overloaded caseworker is active; Case Manager in system.', 'Test Data': {'CaseworkerID': 'CW5555', 'CaseManagerID': 'CM1234', 'AlternateCaseworkerID': 'CW8888'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Caseworker CW5555 exceeds threshold; alert generated.', 'CM1234 opens alert details.', 'CM1234 selects one case and assigns to CW8888.', 'System confirms case reassignment.'], 'Expected Result': 'Case is reassigned from CW5555 to CW8888. Alert details update to reflect action. Audit log records action.', 'Dependent Module/Process': 'Case assignment, Alert system, Audit log'}, {'Test Case ID': 'TC40-008', 'EPIC': 'Security &amp; Compliance', 'Feature': 'Access Control', 'User Story': 'US-40', 'Business Process': 'Alert Management', 'Sub-Process Title': 'Alert Details Security', 'Activity Title': 'Unauthorized Access Attempt', 'Test Scenario Title': 'Unauthorized user cannot access alert details', 'Precondition': 'Alert generated for workload breach.', 'Test Data': {'CaseworkerID': 'CW2323', 'UnauthorizedUserID': 'USR9999'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Line Staff (not a Case Manager)', 'Detailed Test Steps': ['Alert generated for overloaded CW2323.', 'User USR9999 attempts to access alert details URL directly.'], 'Expected Result': 'System denies access and displays appropriate error message (e.g., 403 Forbidden). No data disclosed.', 'Dependent Module/Process': 'Authorization module, Notification system'}, {'Test Case ID': 'TC40-009', 'EPIC': 'System Reliability', 'Feature': 'Recovery Mode', 'User Story': 'US-40', 'Business Process': 'Background Processing', 'Sub-Process Title': 'Service Resiliency', 'Activity Title': 'Deferred Alert Generation After Outage', 'Test Scenario Title': 'Alert generated after system outage', 'Precondition': 'System temporarily unavailable during threshold breach; system recovery imminent.', 'Test Data': {'CaseworkerID': 'CW8888', 'CaseManagerID': 'CM0001', 'Threshold': 5, 'CurrentAssignedCases': 6}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Take notification system offline.', 'Assign 6 cases to CW8888 (threshold 5).', 'Restore notification system.', 'Run workload evaluation process.', 'Log in as CM0001 and check for alerts.'], 'Expected Result': 'After system recovery, alert is generated and visible to CM0001, including accurate timestamp of actual threshold breach.', 'Dependent Module/Process': 'Notification system, Background jobs'}]</t>
         </is>
       </c>
     </row>

--- a/output_test_cases.xlsx
+++ b/output_test_cases.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['Verify a case worker can access and open the new Medicaid application intake form.', 'Verify all required applicant detail fields (name, DOB, SSN, address, etc.) are present.', 'Check that submitting a completed form saves a new application record and assigns a unique identifier.', 'Validate that user permissions restrict intake to authorized case workers.', 'Verify successful creation is logged/audited.']</t>
+          <t>['Submit a new Medicaid application with all mandatory fields completed.', 'Submit a new application omitting one optional field.', 'Submit a new application with invalid applicant data format (e.g., date of birth as text).', 'Attempt to submit a duplicate application for the same applicant.', 'Save an application as a draft before submission.', 'View application details after successful submission.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Attempt submit with missing mandatory fields.', 'Enter special characters or non-ASCII in input fields.', 'Submit duplicate applications for the same SSN.', 'Enter an unrealistically long name/address.']</t>
+          <t>['Applicant name with special characters or Unicode.', 'Applicant with extremely long address or name fields.', 'Applicant birthdate set to future/past improbable dates.', 'No internet connection during application submission.', 'Simultaneous submissions from two case workers.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Ensure intake correctly interacts with ID verification (Story 2).', 'Ensure integration with income check (Story 3).', 'Check household composition recording (Story 4).', 'Confirm incomplete applications are flagged (Story 5).']</t>
+          <t>['Verification that details submitted in intake are available for identity and income verification (related to Stories 2 and 3).']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 5, 8, 9, 22, 26, 27, 31]</t>
+          <t>[2, 3, 4, 5, 8, 9, 11, 12, 19, 22, 26, 31]</t>
         </is>
       </c>
     </row>
@@ -486,22 +486,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>["Verify applicant government ID field accepts valid formats (e.g., driver's license, SSN).", 'Confirm correct API calls to DMV/SSA with sample applicant info.', 'Validate error is shown for invalid or non-matching IDs.', 'Check audit trail/log for ID verification attempts and results.', 'Verify handling and display for system/API unavailability.']</t>
+          <t>['Verify identity using a valid government ID (realistic sample).', 'Reject identity with a mismatched government ID.', 'Verify identity with an expired ID.', 'System timeout or error in response from DMV/SSA database.', 'Log each verification attempt and result.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['Submit expired or revoked ID.', 'Simulate DMV/SSA database timeout or error.', 'Use ID with similar data but different person (identity collision).']</t>
+          <t>['Applicant uses ID issued out of state or country.', 'ID contains special characters (hyphens, apostrophes).', 'Network interruption during database check.', 'Multiple IDs submitted for one applicant.']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['Verify intake must complete ID verification before advancing (Story 1).', 'Test error propagation to incomplete application flagging (Story 5).']</t>
+          <t>['Cross-check that applicant data from intake (Story 1) matches the ID verification request.', 'Verify that identity verification locks out other processes on failure (may extend to Stories 1, 3).']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[1, 5, 9, 31]</t>
+          <t>[1, 3, 33]</t>
         </is>
       </c>
     </row>
@@ -511,22 +511,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['Verify a case worker can trigger income check using applicant data.', 'Validate connection to income system (e.g., The Work Number) sends correct payload and parses response.', 'Check workflow ensures financial qualification shows accurate eligibility.', 'Verify error message handling for income system downtime.', 'Test for storing and retrieving historical income check results.']</t>
+          <t>['Check income eligibility with accurate matched wage data.', 'Handle missing or partial wage data.', 'Handle mismatched SSN or applicant record.', 'Display error on integration failure with income verification system.', 'Manually override income after failed automatic check (if permitted).']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['Income system returns ambiguous or multiple entries.', 'Applicant has no income record.', 'Income data returned is inconsistent (e.g., negative value).']</t>
+          <t>['Applicant with multiple employers or multiple wage records for same period.', 'Applicant with zero wage earnings.', 'Income data in foreign currency or unusual frequency.', 'Rapid repeated queries for same applicant.']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['Validate income check step is accessible from application intake (Story 1).']</t>
+          <t>['Ensure application retrieved from intake (Story 1) is the same used for income check.', 'Compare ID verification status from Story 2 with wage verification process.']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[1, 37]</t>
+          <t>[1, 2, 37]</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Verify adding household members, their ages, and relationships in the application.', 'Test upper and lower limits for number of household members.', 'Validate relationships (e.g., self, spouse, child, other) are accurate and saved.', 'Check changes to household reflect in eligibility assessment.']</t>
+          <t>['Add household members with relationships specified (parent, spouse, child, etc.).', 'Edit or remove a household member from application.', 'Attempt to submit household data with missing relationships.', 'Display household summary and calculated family size.', 'Reject adding duplicate household members.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['Input invalid relationships or age values.', 'Household with only one member (edge minimal case).', 'Very large households (e.g., 15+ members).']</t>
+          <t>['Household member with same name as applicant.', 'Circular relationships (e.g., both members listed as parent and child of each other).', 'Unusually large households (e.g., 15+ members).']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['Confirm household step is required for Medicaid application intake (Story 1).', 'Verify correct passing of household info to eligibility logic.']</t>
+          <t>['Ensure household info links back to correct application from intake (Story 1).', 'Test impact on eligibility calculations requiring family size.']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -561,22 +561,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Submit incomplete application and verify required fields are highlighted.', 'Leave out required documentation and ensure flag is raised.', 'Test visual and filtering indicators for incomplete versus complete applications in the work queue.', 'Verify follow-up reminder is generated for flagged applications.', 'Ensure proper logging of incomplete application status.']</t>
+          <t>['Submit a partially complete application and verify that it is flagged as incomplete.', 'Attempt to submit without any required documents to check flagging behavior.', 'Fill out all required fields and documents, confirm that flag is removed.', 'System generates a follow-up notification/reminder to case worker/applicant.', 'View dashboard/list of all flagged incomplete applications.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['Missing both fields and documents.', 'Flipping between states by consecutively completing and removing required information.', 'Submit with all optional information but missing just one required item.']</t>
+          <t>['All optional fields left blank; only required missing.', 'Rapidly toggling between incomplete and complete states.', 'Application flagged as incomplete then deleted or withdrawn.']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['Check flagging works when intake is incomplete (Story 1).', 'Verify IDs not verified trigger incomplete status (Story 2).']</t>
+          <t>['Integration with Story 1 intake process to ensure correct flagging upon submission.', 'Interaction with document upload and completeness checks (Stories 11, 12, 22).']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[1, 2, 11, 12, 22]</t>
+          <t>[1, 12, 11, 22]</t>
         </is>
       </c>
     </row>
@@ -586,22 +586,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Log in as a Case Manager and view the dashboard; verify eligibility status displayed for all assigned clients', 'Verify dashboard displays correct eligibility status for clients with varying statuses (eligible, not eligible, pending)', 'Verify renewal dates are shown and match backend data', 'Filter/sort clients by eligibility status', 'Click on a client to view more details']</t>
+          <t>['Login as Case Manager and access dashboard.', 'Verify eligibility status is displayed for each assigned client.', 'Verify renewal dates are displayed and accurate.', 'Check that clients with various eligibility states (e.g., eligible, expired, pending renewal) are correctly represented.', 'Ensure correct behavior for clients not assigned to the Case Manager (they should not be visible).']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['Client with missing or null eligibility status', 'Client with multiple eligibility records', 'Client with expired status but no renewal date', 'No clients assigned to Case Manager']</t>
+          <t>['Clients with missing or malformed eligibility data.', 'Clients with eligibility expiring today.', 'Clients with multiple eligibility programs (multi-line status).', 'Case Manager with no assigned clients.', 'Client whose eligibility was updated in another session during view.']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['Verify eligibility and renewal information matches data in stories 7 (alerts), 23, 25, 34']</t>
+          <t>['Shared with 7: Test eligibility status consistency and updates reflected in both dashboard view and alerts.', 'Shared with 23, 25, 30, 32, 34, 36: Test eligibility display when related functionalities such as alerts, updates, or renewals are triggered.']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['Story 7: Alerts for expiring eligibility', 'Story 23: Any client data sync features', 'Story 25: Dashboard client summation', 'Story 34: Client profile or service planning views']</t>
+          <t>['7 (alerts on eligibility)', '23, 25, 30, 32, 34, 36 (all features displaying or using eligibility status or dates)', 'Any functionality displaying, updating, or using client dashboard data']</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['Simulate eligibility status expiring in 30 days; verify alert appears for correct client', 'Verify alert timing (exactly 30 days before renewal date)', 'Dismiss an alert and check it is removed from view', 'Verify alerts appear for all clients with expiring eligibility', 'Test that no alert is generated when eligibility is not close to expiring']</t>
+          <t>['Simulate eligibility nearing expiration (29,30,31 days) and confirm alert appears.', 'Verify alert timing (exactly 30 days prior).', 'Ensure that once eligibility is renewed, alert is dismissed.', 'Check alert content for accuracy and clarity.', 'Login as different Case Manager and verify only appropriate clients trigger alerts.', 'Confirm system does not send duplicate alerts daily.']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['Eligibility expires in less than 30 days (should alert immediately)', 'Eligibility with no expiry date', 'Multiple clients expiring the same day', 'Alert conditions overlap due to rapid changes']</t>
+          <t>['Eligibility expiring on leap day (Feb 29).', 'Eligibility expiring at end of month (e.g., April 30).', 'Eligibility status manually altered to expired/renewed during alert window.', 'Eligibility with no expiration date set.', 'Multiple clients expiring the same day.']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['Alert details link back to dashboard (Story 6)', 'Eligibility and renewal date accuracy']</t>
+          <t>['Shared with 6: Confirm that eligible statuses triggering alerts are the same as those shown on the dashboard.', 'Shared with 34, 36: Involve scenarios where eligibility changes affect both alerts and dashboard displays.']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['Story 6: Dashboard eligibility and renewal date display', 'Story 34: Client status updates', 'Story 23: Any batch alert-related features']</t>
+          <t>['6 (dashboard eligibility display)', '34, 36 (other stories that trigger or display eligibility alerts)', 'Any notification/alarm/alerting features across the platform']</t>
         </is>
       </c>
     </row>
@@ -636,22 +636,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>["Upload valid PDF to a case and confirm it's attached/displayed", 'Upload valid image (JPEG/PNG) and scanned image and verify', 'Attempt upload of unsupported formats (e.g., .exe, .docx) and confirm rejection', "Delete an uploaded document and ensure it's removed", 'Verify upload size restrictions (if any) are enforced']</t>
+          <t>['Upload PDF, JPEG, PNG, and scanned images to a case; confirm success for each.', 'Attempt to upload an unsupported file type (e.g., .exe), and confirm rejection.', 'Verify that uploaded documents are linked to the correct case.', 'Check file size limits and upload behavior for large files.', 'Test access permissions for uploads (case worker vs non-case worker).', 'Download/view uploaded documents and verify integrity.']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['Upload large files near maximum size', 'Corrupted image or PDF upload', 'Duplicate file uploads (same file name/content)', 'Uploading no file (empty upload)']</t>
+          <t>['File with a corrupted header or empty file.', 'Mass upload (multiple files or rapid succession).', 'Files with special/unicode characters in filename.', 'Simultaneous uploads by two users to same case.', 'Network interruption during upload.']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['File access from other related functions (Stories 11, 12, 17, 21, 24, 29, 39)', 'Document visibility in audit/history (if implemented)']</t>
+          <t>['Shared with 1, 11, 12, 13, 17, 21, 24, 29, 39: Test document upload, retrieval, linking, access rights, and integrity across features requiring file/document management.']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['Story 1: Case file creation/attachment', 'Stories 11, 12: Case document workflows', 'Story 17: Document management', 'Story 21: User access to documents', 'Story 24: Multi-file management', 'Story 29: Case closure with docs', 'Story 39: Reporting including document presence']</t>
+          <t>['1, 11, 12, 13, 17, 21, 24, 29, 39 (any other feature that uses file/document upload or management)', 'Any reports or exports involving uploaded documents']</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Search applicants by full name (exact match), verify results', 'Search by partial name (fuzzy match), confirm correct candidates returned', 'Search by SSN, verify exact matching only', 'No results for non-existent SSN/name', 'Attempt search with special characters']</t>
+          <t>['Search by full name and verify correct applicants are listed.', 'Search by partial name (test fuzzy matching).', 'Search by SSN (with/without dashes).', 'Attempt duplicate entry with existing name/SSN and verify prevention.', 'Check search performance with large applicant list.', 'Verify search results are restricted by user permissions.']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['Applicants with same name, different SSN', 'SSN with leading zeros', 'Name fields with accents or non-Latin characters', 'Very large result set for common names']</t>
+          <t>['Applicants with identical names but different SSNs.', 'Special characters in names (e.g., O’Connor, José).', 'Very short input (&lt; 2 chars).', 'Applicants with missing or invalid SSNs.', 'Search performed during system sync or backup.']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['Duplicate-detection tests related to Story 1 or Story 2', 'Check proper search matching for Story 31']</t>
+          <t>['Shared with 1, 31: Validate duplicate detection, search performance, and permission checks.']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['Story 1: Case creation/duplicate check', 'Story 2: New applicant workflows', 'Story 31: Applicant data retrieval or display']</t>
+          <t>['1 (if it involves applicant entry or search)', '31 (any other module using search or duplicate prevention functionality)', 'Any onboarding/registration or deduplication workflow']</t>
         </is>
       </c>
     </row>
@@ -686,22 +686,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Assign case to team member with lowest workload, verify assignment', 'Test manual override to assign a case irrespective of workload', 'Re-assign case and ensure update reflected in all views', 'Verify reassignment history/tracking if implemented', 'Test case assignment on edge (e.g., team member at max workload)']</t>
+          <t>['Assign case automatically based on workload and verify distribution among team members.', 'Override and manually assign/reassign a case; verify assignment.', 'Attempt to assign to inactive or overloaded team member.', 'Ensure notification/confirmation upon assignment.', 'Verify case status is updated post-assignment.']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['No team members available', 'Case assigned to member on leave (should block or warn)', 'Multiple team members with identical workload', 'Manual override used repeatedly for same case']</t>
+          <t>['All team members at maximum capacity.', 'New case created while assignment in progress.', 'Team member removed from system after assignment.', 'Manual override to self-assigned case.', 'Very large team or batch assignment.']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['Assignment logic applied in Stories 28, 40', 'Consistent update to assignment visible in dashboards and reports']</t>
+          <t>['Shared with 28, 40: Test for assignment rules, overrides, reassignment, and notifications across all case-control/management modules.']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['Story 28: Team management assignments', 'Story 40: Any workload calculations or team member dashboards']</t>
+          <t>['28, 40 (all related to team assignment, workload balancing, and reassignment)', 'Any user notification or workload report module']</t>
         </is>
       </c>
     </row>
@@ -711,22 +711,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['Verify that a case worker can initiate a document request for an applicant.', 'Verify that an email notification is generated with a secure upload link and sent to the applicant.', 'Verify that an SMS notification is generated with a secure upload link and sent to the applicant.', 'Validate that generated upload links are unique and associated with the correct applicant and document request.', 'Verify that the upload link expires or becomes invalid after a specified time or after the document is uploaded.']</t>
+          <t>['Generate email with correct applicant and missing document references.', 'Generate SMS with secure upload link.', 'Secure upload link is unique to applicant and document request.', 'Link expiration feature works as expected.', 'Notification is sent upon request initiation.', 'Retry/resend notification if first delivery fails.', 'Log notification delivery status.']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['Applicant with invalid or missing contact information (email/SMS).', 'Attempt to reuse an expired or already used upload link.', 'Simultaneous document requests for multiple items for the same applicant.', 'Case worker cancels document request after notification sent.']</t>
+          <t>['Applicant does not have a valid email or mobile number.', 'Applicant receives multiple requests simultaneously.', 'Upload link expires before applicant can act.', 'Wrong/malformed upload link sent.', 'Spam filter blocks notification.']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['Verify document requests are correctly reflected in related document checklists/tracking (Story 12).', 'Ensure notifications are logged in communication logs (Story 14, if applicable for case workers).']</t>
+          <t>['Document upload integration from related stories 5 and 8.', 'Validation of secure links with document submission (story 12).']</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['5: Applicant document upload functionality.', '8: Notification system.', '12: Document submission tracking.', '17: Overall applicant communications.', '21: Security for uploaded documents.']</t>
+          <t>[1, 5, 8, 12, 17]</t>
         </is>
       </c>
     </row>
@@ -736,22 +736,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['Verify that all requested documents are listed in the checklist for each applicant.', "Validate that status indicators correctly show 'pending', 'submitted', 'approved', or 'rejected' for each document.", 'Verify case worker can filter or sort checklist by status.', 'Ensure status is updated when applicant uploads a document via secure link.', 'Verify that the checklist refreshes in real-time or after refresh when there is an update.']</t>
+          <t>['Document status is updated upon applicant upload.', 'Case worker is able to see all pending, submitted, and verified items.', 'Checklist loads correctly for all applicants.', 'Status indicators are accurate and reflect backend status.', 'Manual overrides by Case Worker update status.', 'Notifications triggered for pending items.']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['Document is uploaded with the wrong file type or corrupted file.', 'Simultaneous uploads for the same document type.', 'Checklist shows extra or missing document types not relevant for an applicant.']</t>
+          <t>['Multiple applicants uploading the same document.', 'Corrupted document upload.', 'Status stuck in pending after successful upload.', 'Checklist refreshes with incomplete status after system crash.']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['Test submission tracking after sending document requests (Story 11).']</t>
+          <t>['Document upload workflow from stories 5, 8, 11, 17.', 'Checklist visibility after document request sending (story 11).']</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['5: Applicant document upload.', '8: Notification triggers for document updates.', '11: Document request and notification logic.', '17: Follow-up communication triggers.', '21: Document security and access.']</t>
+          <t>[5, 8, 11, 17]</t>
         </is>
       </c>
     </row>
@@ -761,22 +761,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Verify that the redaction tool is available for all uploaded documents.', 'Test that user can select and redact sensitive information like SSN, address, etc.', 'Validate that redacted areas cannot be revealed after saving.', 'Verify that the redacted document is used in place of the original for sharing/viewing.', 'Check audit logs for all redaction actions.']</t>
+          <t>['Uploaded document scanned for sensitive fields (e.g., SSN, addresses).', 'Redaction tool marks and masks sensitive data correctly.', 'Case Worker can preview and adjust redactions before saving.', 'Redacted documents are stored and replace originals in case file.', 'Unauthorized users cannot access unredacted originals.']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['Uploaded documents with unusual formats or encrypted text.', 'Redacting the entire document or attempting to redact non-text content.', 'Multiple redactions made/removed before saving.']</t>
+          <t>['Document contains non-standard formatting (e.g., handwriting, scanned images).', 'Redaction fails to detect all sensitive information.', 'Manual redaction overrides auto-detected fields.', 'User attempts to download original unredacted version.']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['Ensure that redacted documents are correctly referenced in document checklists/tracking (Story 12).', 'Verify redacted documents are not exposed in notifications or document links (Story 11, 21).']</t>
+          <t>['Document upload and storage handling from story 8.']</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['8: Uploading and accessing applicant documents.', '21: Document security, access controls.', '29: Workflows involving sensitive data.']</t>
+          <t>[8]</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['Verify that all emails, calls, and messages with a client are logged in the case timeline.', 'Check that logs include timestamp, type, sender/recipient, and summary/details.', 'Confirm that logs are correctly associated with the right case/client.', 'Test searching/filtering log entries by date, type, or participant.', 'Verify permissions: only authorized users can view/edit communication logs.']</t>
+          <t>['All communication types (email, call, SMS, portal message) logged with timestamps.', 'Logs display correct chronology and metadata.', 'Case Manager can filter logs by type or date.', 'Privacy restrictions apply to sensitive communications.', 'Audit log captures log edits or deletions.']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['Bulk communication events occurring close in time.', 'Missing or partial log data (e.g., call with no duration recorded).', 'Edit/delete attempts on logs; confirm audit or prevention.']</t>
+          <t>['Duplicated entries in log due to system error.', 'Log entry missing sender or content details.', 'Bulk imported communications from legacy systems.', 'Very high volume of logs for a single case.']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>['Check that document request notifications (Story 11) and tracking updates (Story 12) are logged when communication is sent/received, if integrated.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['6: General case notes and history logging.', '20: Related communication/logging modules.']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['Verify that a case manager can create and view notes shared with other agencies.', 'Check that shared case flags can be added, edited, and removed.', 'Ensure shared notes are only visible to authorized agency staff.', 'Test notifications or visibility toggles when notes/flags are changed.', 'Verify accurate audit trail for all inter-agency actions.']</t>
+          <t>['Dual eligibility case shows correct agency flags.', 'Notes shared between agencies are visible to authorized users only.', 'Case Manager can add/edit/remove inter-agency notes.', 'Update of case status in one agency propagates to connected agencies.', 'Alerts for benefit overlaps or conflicts are generated.']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['Multiple agencies making concurrent updates to shared notes.', 'Attempt to access/edit notes by unauthorized users/agencies.', 'Duplicate shared case flags for the same reason.']</t>
+          <t>['Agency connection lost during update.', 'Conflicting notes or flags from two agencies.', 'User lacks permission to see flags.', 'Simultaneous updates from multiple agencies.']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['None explicitly listed, but may impact general note-sharing or case visibility features.']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -836,22 +836,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['Verify PDF is generated after triggering summary report for a case.', 'Check that PDF contains all relevant eligibility findings (status, reasons, date, etc.).', 'Validate download functionality of the generated PDF.', 'Ensure PDFs are generated only for authorized users (Case Workers).', 'Test proper naming convention for PDF files.', 'Ensure sensitive information is masked/obfuscated as necessary in the PDF.', 'Verify performance for large or complex cases in summary generation.']</t>
+          <t>['Verify that the case worker can generate a PDF summary for a given case.', 'Verify that the generated PDF contains all eligibility findings for the selected case.', 'Check the formatting and readability of the generated PDF.', 'Verify the PDF can be saved/downloaded.', 'Verify that the PDF content matches the data present in the case system.']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['Case with no eligibility findings.', 'Case with maximum allowed number of eligibility findings.', 'Case with special characters or international characters in findings.', "Case in a 'deleted' or 'archived' state.", 'User tries to generate PDF for a case they do not have access to.']</t>
+          <t>['Generate a summary for a case with no eligibility findings.', 'Generate a summary for a case with very large number of eligibility findings (e.g., 100+).', 'Check PDF generation for a case with special or non-ASCII characters in findings.', 'Check for timeout or failure if PDF generation fails.']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>['Verify eligibility findings data (source: stories 3, 4, 6, 25, 32, 35) is consistent in the PDF.', 'Cross-validate summary report content with eligibility and outcome data from related features.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 25, 32, 35]</t>
+          <t>['Any other features generating or exporting PDFs in the system', 'Eligibility findings data model and reporting']</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Verify notification is triggered when a client uploads a document.', 'Ensure alerts are received in near real-time by assigned Case Worker.', 'Check that link in alert leads to the correct document in the correct case.', 'Validate notifications are sent only to relevant Case Worker(s).', 'Check ability to dismiss/mark alert as read.', 'Ensure notifications appear only for new uploads (not for edits or deletes).']</t>
+          <t>['Upload a document as a client and verify the case worker immediately receives an alert.', 'Verify the notification contains case identifier and uploader information.', 'Verify the alert is visible on both web and mobile (if applicable).', 'Ensure duplicate alerts are not generated for the same upload.', 'Check that alerts are only sent to case workers assigned to the case.', 'Check that the alert links to the uploaded document and relevant case.']</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['Multiple documents uploaded simultaneously.', 'Same document re-uploaded.', 'Upload by an unassigned or unverified client.', 'Network or connectivity interruptions during upload.']</t>
+          <t>['Document uploaded during system downtime—test notification delivery post-recovery.', 'Simultaneous uploads by multiple clients on one case.', 'Uploads by unauthorized users (should not trigger alerts).', 'Non-standard file types or extremely large files.']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['Test document upload workflow (shared with stories 8, 11, 12, 39).', 'Validate notification system integration for other triggered alerts.']</t>
+          <t>['Verify notifications for document uploads (Shared with stories 8, 11, 12, 39).']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[8, 11, 12, 39]</t>
+          <t>['Notification system (all types)', 'Document upload workflow', 'Access control for alerts']</t>
         </is>
       </c>
     </row>
@@ -886,22 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Verify timer starts, pauses, and stops correctly for a case.', 'Test manual time entry and editing for a log.', 'Ensure time is recorded to the correct case and user.', 'Check reporting aggregates show correct totals for workload.', 'Test export or summary of time logs per case.']</t>
+          <t>['Verify that case manager can start and stop a timer per case.', 'Verify manual entry of time logs is possible and accurate.', 'Check that time logged appears correctly in workload reports.', 'Edit or delete time logs and verify changes reflect in case and reports.', 'Ensure time logs are attributed to the correct case and user.']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['Timers left running over session logouts or device changes.', 'Attempting to log zero or negative time.', 'Cases with extremely high or fragmented time logs.', 'Manual updates during an active timer.', 'Case is reassigned during logging.']</t>
+          <t>['Attempt to log negative or zero minutes/hours.', 'Simultaneous timer sessions by same user on different cases.', 'Very large durations (e.g., timer left running for a week).', 'Manual entry with future or implausible past dates.']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>['Consistency with overall case management (stories 6, 10, 32, 40).', 'Reporting logic shared with related case summary report features.']</t>
+          <t>['Time tracking and reporting interactions (Shared with stories 32, 40).']</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[6, 10, 32, 40]</t>
+          <t>['All workload reporting features', 'UI for case detail and reporting', 'Historical case data aggregation']</t>
         </is>
       </c>
     </row>
@@ -911,22 +911,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Verify checklist is generated based on selected case type.', 'Confirm accuracy and completeness of required document list.', 'Test print functionality for the checklist output.', 'Check preview before printing.', 'Test generated checklist for various case types.']</t>
+          <t>['Verify that a checklist can be generated and printed for any case type.', 'Check that the checklist contains correct document requirements for the chosen case type.', 'Verify printable output (formatting, page breaks, etc.).', 'Print-preview functionality validation.', 'Checklist printing with various browsers/printers.']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['Case types with unusually long or short document lists.', 'Checklist with special formatting (long names, special characters).', 'Checklist generated after document requirements are updated.']</t>
+          <t>['Case types with no required documents.', 'Checklist with very large number of required documents.', 'Printing in portrait vs. landscape mode.', 'Very long document names or special characters.']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>['Check integration with required documents logic (stories 5, 8, 21, 26).', 'Test document upload and checklist synchronization.']</t>
+          <t>['Checklist generation and printing (Shared with stories 1, 5, 26).']</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[5, 8, 21, 26]</t>
+          <t>['Document management features', 'Case type configuration', 'Related print/export features']</t>
         </is>
       </c>
     </row>
@@ -936,22 +936,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['Verify urgent case marking and flag visibility.', 'Check case escalation workflow initiates from Case Manager.', 'Ensure supervisor receives prompt notification of escalation.', 'Track correct recording of escalation in case history/audit trail.', 'Test de-escalation or resolution workflow.']</t>
+          <t>['Verify that a case manager can flag a case as urgent and escalate to a supervisor.', 'Verify that escalated cases are visible to supervisors immediately.', 'Check that priority flags are visually distinct in case lists.', 'Test notification to supervisor upon escalation.', 'Verify tracking/audit log records the escalation event.']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['Multiple concurrent escalations by different managers.', 'Case flagged as urgent but already closed or archived.', 'Supervisor unavailable/unassigned.']</t>
+          <t>['Escalating the same case multiple times.', 'Multiple simultaneous escalations of different cases.', 'Escalation and de-escalation (if supported).', 'Escalating cases without supervisors assigned.']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>['Validate priority flag and notification processes (stories 14, 38).']</t>
+          <t>['Escalation workflow (Shared with story 38).']</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[14, 38]</t>
+          <t>['Supervisor alert and case assignment systems', 'Case list filtering and sorting', 'Notification and audit features']</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Verify OCR correctly extracts text from supported document files (PDF, JPEG, PNG)', 'Validate that required metadata fields are auto-checked upon upload', 'Ensure system flags documents missing key metadata or with unreadable OCR', 'Verify error message is shown when non-supported file type is uploaded', "Check that valid documents are marked as 'auto-validated' and alert generated for failures", 'Audit logs record all auto-validation results']</t>
+          <t>['Verify OCR is triggered for each uploaded document.', 'Check that metadata (date, type, owner) is extracted from various document formats (PDF, JPG, PNG).', 'Validate that documents with unreadable text trigger error or warning messages.', 'Test that successfully validated documents bypass manual review queue.', 'Confirm that validation errors are logged and visible to the Case Worker.']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['Low-resolution or skewed scans', 'Handwritten documents', 'Documents with large amounts of noise or watermarks', 'Multipart PDFs (containing both images and text)', 'Files with missing or corrupt metadata']</t>
+          <t>['Upload a corrupted or password-protected file.', 'Use a document with no readable text (blank page).', 'Upload an image with handwritten or distorted text.', 'File with incorrect or missing metadata.', 'Supported file type with unusual encoding or orientation.']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>['Upload and validation logic for documents (shared with stories 8, 11, 12, 13, 19, 24)', 'Permission enforcement for who can trigger uploads/validation']</t>
+          <t>['Test document upload workflow used in story 8 (if 8 covers document upload core logic).', 'Bulk or batch upload validation process from story 24.']</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[8, 11, 12, 13, 19, 24]</t>
+          <t>['Story 8 (document upload and processing core logic)', 'Story 24 (bulk upload if validation also applies per file)']</t>
         </is>
       </c>
     </row>
@@ -986,22 +986,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['System suggests completion options for blank or incomplete required fields', 'Clicking suggestion auto-fills field with AI-recommended values', 'Rejecting suggestion preserves user-entered value', 'Accuracy of suggestions is logged', 'User can request new suggestions after modifying application']</t>
+          <t>['Submit an incomplete application and verify field suggestions are generated.', 'Ensure suggested fields are contextually relevant based on AI analysis.', 'Check performance for large/complex applications.', 'Ensure suggestions update live as fields are completed.', 'Dismiss a suggestion and verify it does not reappear unless context changes.']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['Applications with all fields filled (no suggestion expected)', 'Extremely minimal input (only one or two fields present)', 'Conflicting values between user entry and AI suggestion', 'Very large application forms with many missing fields']</t>
+          <t>['All fields already completed (should return no suggestions).', 'Application with unusual or rare data types.', 'Fields intentionally left blank (e.g., applicant chooses not to answer).', 'Application with conflicting or ambiguous data.']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>['Field validation, missing field detection (shared with stories 1, 5)', 'Audit tracking of suggestions']</t>
+          <t>['Field validation and completion logic from story 1 (which may handle basic missing fields).', 'Checks for required field logic from story 5 (if related to field requirement completeness).']</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[1, 5]</t>
+          <t>['Story 1 (field validation, error handling)', 'Story 5 (required fields and application completeness logic)']</t>
         </is>
       </c>
     </row>
@@ -1011,22 +1011,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['Apply each filter (pending, approved, expired) and verify displayed client list matches expected status', 'Multiple filters combined (if supported) reflect accurate results', 'Reset/clear filters returns full client list', 'Filtered results update client and eligibility counts']</t>
+          <t>["Apply filter for 'pending' status and verify only correct clients are shown.", "Filter by 'approved' and 'expired', review that only appropriate clients display.", 'Reset/remove filter and confirm full client list returns.', 'Check multi-status filters (if supported).', 'Verify filters persist or reset as per requirements on navigation.']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['No clients meet filter (empty result)', 'All clients in same status', 'Rapidly switching filters', 'Clients with no eligibility status set']</t>
+          <t>['No clients in a chosen status.', 'Client with invalid/unknown status.', 'Large client lists to test performance of filtering.', 'Rapidly toggling between statuses.']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>['Eligibility status logic for clients (shared with 6, 25, 32)', 'Dashboard data integrity']</t>
+          <t>['Client dashboard rendering and status logic from story 6 (if story 6 covers client status tracking).']</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[6, 25, 32]</t>
+          <t>['Story 6 (client status tracking and dashboard filtering logic)']</t>
         </is>
       </c>
     </row>
@@ -1036,22 +1036,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Upload multiple documents associated to distinct cases, verify correct case attachment', 'Upload batch with some invalid documents, verify only valid files processed', 'Bulk upload with mixture of supported/unsupported file types', 'UI feedback for batch progress and completion', 'Audit log records every upload and case association']</t>
+          <t>['Bulk upload multiple documents and verify each is assigned to the correct case.', 'Attempt batch upload with one or more unsupported file types.', 'Check for error reporting on failed uploads within a batch.', 'Test simultaneous bulk uploads by multiple users.', 'Validate performance for large batches.']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['Very large batch (system limits, timeouts)', 'Files missing case identifiers', 'Multiple files for same case in one batch']</t>
+          <t>['Batch with a mix of valid and invalid files.', 'Batch with duplicate or conflicting case identifiers.', 'Documents for nonexistent cases.', 'Extremely large file sizes.']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>['Document upload pipeline (shared with 8, 21)', 'User permissions for batch operations']</t>
+          <t>['Document processing and validation logic from story 8 (core upload).', 'Auto-validation process from story 21 (if auto-validation also applies to bulk uploads).']</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[8, 21]</t>
+          <t>['Story 8 (general document upload)', 'Story 21 (if auto-validation is used by bulk upload process)']</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['View eligibility denial trends over selectable date ranges', 'Denial reason breakdown shows correct count and percentage', 'Export analytics data to CSV', 'Drill down from trend graph to list of denied applications', 'Filter analytics results by caseworker, location']</t>
+          <t>['Access analytics dashboard and verify trends for different denial reasons.', 'Confirm data matches underlying client/application records.', 'Filter analytics by time period, region, or other available facets.', 'Check graphical and numeric representations are consistent.', 'Download/export report and verify data integrity.']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['No denial data in period (empty graph)', 'Multiple denials with same reason in short period', 'Denial with missing or unknown reason code']</t>
+          <t>['No denials in selected period (empty trend).', 'Multiple denials for single client (duplicate handling).', 'Denial reason field is blank or contains unusual text.', 'Huge volume of denial records – stress/performance.']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>['Eligibility determination and status logic (shared with 6, 16, 23)', 'Analytics dashboard usability']</t>
+          <t>['Eligibility status and case status logic from story 6 (if analytics source is same status used for filtering in story 23).']</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[6, 16, 23]</t>
+          <t>['Story 6 (eligibility status logic impacts dashboard analytics)', 'Story 23 (dashboard filtering features if dashboard code is shared)']</t>
         </is>
       </c>
     </row>
@@ -1086,22 +1086,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Verify that when creating a new application, available historical data from previous cases is automatically populated in matching fields.', 'Ensure that only relevant and correct fields are pre-filled based on the case type.', 'Check that users can manually overwrite any pre-filled data.', 'Validate that pre-filled data sources are accurate and up to date.', 'Confirm that there is an indication (highlight or info icon) that data was pre-filled from previous cases.']</t>
+          <t>['Verify that application forms are automatically pre-filled with data from the applicant’s previous cases.', 'Verify that correct and relevant fields are populated based on historical records.', 'Check that manual edits to pre-filled data are possible and saved correctly.', 'Check audit logs to see if auto-filled information is tracked.', 'Verify functionality when no previous case exists (should show blank fields).', 'Test that data is pulled from the most recent previous case.']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['Previous cases have incomplete or inaccurate data.', 'No previous cases exist for the applicant.', 'Previous data contains special characters or invalid format.', 'Multiple prior cases with conflicting values.']</t>
+          <t>['Previous data has missing or invalid formats.', 'Applicant has multiple previous cases with conflicting data.', 'Very large previous case data sets (performance, completeness).', 'Previous cases contain special characters or non-standard input.']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['Test pre-fill with initial application creation (from Story 1).', 'Test with multiple prior cases (related to Story 19, which may also reuse applicant data).']</t>
+          <t>['Related to [1, 19]: Test data shared/refreshed across linked applications.']</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Story 1 (basic application creation)', 'Story 19 (reuse of applicant data or case history)', 'Any form population or data entry features']</t>
+          <t>['Story 1 (initial application creation and data entry)', 'Story 19 (data duplication or reuse elsewhere)', 'Any form pre-fill/autofill functionality']</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['Verify that conflicting household data across multiple applications is detected.', 'Ensure that system generates alerts when discrepancies are found.', 'Check that alerts provide clear, actionable information regarding discrepancies.', 'Test that resolving or dismissing an alert updates its status.', 'Confirm that non-conflicting applications do not generate false positives.']</t>
+          <t>['Cross-check household data (e.g., names, SSN, DOB) across all existing applications for a new or updated entry.', 'Trigger and display alert when conflicting household data is detected.', 'Ensure alert displays relevant information for resolving discrepancies.', 'Test dismissal and resolution workflow for the alert.', 'Confirm no alert is shown when there are no conflicts.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Household data changes in the middle of review.', 'Same household members with slightly different spellings or data formats.', 'Large number of applications with overlapping household data.', 'Missing or null household fields.']</t>
+          <t>['Household data differs by single character or whitespace.', 'Multiple conflicting records found for same household.', 'Same household member appears under different spellings or identifiers.', 'Household data includes non-English alphabets or symbols.']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>['Test with household entered in new application flow (from Story 1).', 'Verify alert if data updated from other system modules (story 4 could be cross-checking).']</t>
+          <t>['Related to [4]: Shared data validation, conflict resolution workflow.']</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['Story 1 (application household data entry)', 'Story 4 (any data consistency checks)', 'Alert and notification system']</t>
+          <t>['Story 4 (data quality checks or duplicate detection)', 'Any household member verification features']</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Confirm that a case can be assigned based on client language preference.', 'Validate that only caseworkers with matching language skills are displayed as assignable.', 'Check that assignment can be forced/overridden if required (permissions).', 'Ensure error is shown if no match is available.', 'Test updating caseworker or client language and observing assignment change.']</t>
+          <t>['Assign case to a caseworker based on client’s language preference.', 'Verify that only caseworkers with the relevant language skill are selectable/assigned.', 'Provide alternative assignment when no caseworker matches the language preference.', 'Allow re-assignment and confirm language preference is preserved.', 'Display language skill of each caseworker in the assignment interface.']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['Client lists a rare language not covered by any caseworker.', 'Multiple caseworkers with matching skills (random/priority assignment?).', 'Caseworker updates skill list after assignment.', 'Client with multiple language preferences.']</t>
+          <t>["Client's preferred language not supported by any caseworker.", 'Caseworker has multiple language skills.', 'Clients specify multiple or ambiguous language preferences.', 'Case assignment for large numbers of simultaneous incoming cases.']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>['Test with client/case creation (from Story 10, for initial assignment).']</t>
+          <t>['Related to [10]: Test general case assignment logic and override processes.']</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Story 10 (case assignment)', 'Caseworker/client details management']</t>
+          <t>['Story 10 (case assignment workflow)', 'Any assignment/matching functionality']</t>
         </is>
       </c>
     </row>
@@ -1161,22 +1161,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['Verify that document preview loads correctly in the upload dialog/pane.', 'Confirm that only supported file types render a preview; others display an appropriate message.', 'Ensure that the displayed preview matches the original document.', 'Check performance loading various file sizes.', 'Test cancelling or replacing documents before upload.']</t>
+          <t>['Upload a document and verify that an accurate preview is shown before confirming upload.', 'Test the preview with different formats (PDF, JPG, PNG, DOCX, etc.).', 'Check user actions (zoom, rotate, page through multi-page files) in preview pane.', 'Attempt to upload a corrupt or unsupported file and verify error handling.', 'Ensure preview does not save file until confirmed.']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['Uploading a corrupt or unsupported file type.', 'Multi-page (PDF) or multi-image uploads.', 'Very large file uploads (performance/memory).', 'Files with malicious or non-standard content.']</t>
+          <t>['Large files, multi-page documents, or high-resolution images.', 'Empty or blank documents.', 'Password-protected or encrypted documents.', 'File with malicious content.']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>['Document upload tests (from Story 8).', 'Review preview before submission (related to Story 13, likely integration with document review flow).']</t>
+          <t>['Related to [8]: Shared document upload, validation, and error messaging.']</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['Story 8 (document upload)', 'Story 13 (document review/preview)', 'Any file handling or previewing libraries']</t>
+          <t>['Story 8 (document upload, validation, error handling)', 'Any file handling workflow']</t>
         </is>
       </c>
     </row>
@@ -1186,22 +1186,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Verify that users can export visible/filterable case data to Excel/CSV format.', 'Check that exported file is readable in Excel and data matches what is shown in the app.', 'Test exporting large volumes of records.', 'Ensure all selected/filter columns export correctly.', 'Test export with special characters and date/time fields.']</t>
+          <t>['Export filtered case lists to CSV and Excel formats.', 'Verify data completeness and correct formatting in exported files.', 'Check that filters (date range, status, worker, etc.) are respected in export.', 'Test export functionality for large numbers of cases (performance test).', 'Open exported file in Excel and verify readability and column structure.']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['No records returned by filter (empty export file).', 'Fields with Excel-reserved characters (commas, quotes, formulas).', 'Rapid repeated export submissions.', 'Data containing multi-line or binary content.']</t>
+          <t>['Exporting with no filters (all cases).', 'Exporting with filters that return no results.', 'Very large datasets (row limits, memory).', 'Special characters or Unicode in data fields.']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>['Test with filtering features (from Story 32).', 'Test with various export options/settings (from Story 23 if relevant).']</t>
+          <t>['Related to [6]: Data filtering logic and general export features.']</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['Story 32 (data filtering)', 'Story 23 (data export/reporting)', 'Any data retrieval or reporting backends']</t>
+          <t>['Story 6 (export logic, data filters)', 'Any case data reporting functionality']</t>
         </is>
       </c>
     </row>
@@ -1211,22 +1211,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Create two applications with matching identifying information and verify alert for potential duplicate.', 'Create applications with similar (but not identical) data and check if duplicates are detected based on matching logic.', 'Review flagged duplicates list as a Case Worker to ensure visibility and correctness.', 'Merge flagged duplicate applications and verify accuracy and data integrity post-merge.', 'Verify alert is generated in real-time, not delayed.', 'Mark false positive as not duplicate and verify alerts are not repeated for that pair.']</t>
+          <t>['Submit two applications with matching key identifiers (e.g. name, DOB, SSN) and verify that both are flagged as duplicates.', 'View a list of flagged duplicates and confirm that potential matches are displayed to the case worker.', 'Attempt to merge flagged applications and verify that the merge process works as expected.', 'Test alert/notification delivery for duplicate detection (e.g. email, dashboard alert).', 'Verify that cases not matching duplicate criteria are not flagged.', 'Audit log records when a duplicate is detected or merged.']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['Applicants with common names but different addresses.', 'Same person applies with slight differences in spelling or typos.', 'Applications submitted from different channels (online and in-person).', 'Merged application with already merged records.', 'Bulk upload leading to multiple duplicates at once.']</t>
+          <t>['Applications with slight variations (e.g. one has a typo in the name).', 'Applications submitted in rapid succession versus hours apart.', 'Cases with missing or partial identification fields.', 'Extremely large batches of applications submitted at once.', 'Applications flagged as duplicates, but on review, are not the same person.']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>['Test that duplicate flagging and merging works after application creation (Related: [1, 2, 9]).']</t>
+          <t>['Review alert/flag system mechanics as in stories 1 and 9 (e.g., notification handling, display in work queues).']</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['Application submission/creation', 'Merge functionality in applications', 'Any application search and display screens']</t>
+          <t>[1, 9]</t>
         </is>
       </c>
     </row>
@@ -1236,22 +1236,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['Generate a monthly report by selecting specific worker and status filters; verify data accuracy.', 'Generate a monthly report without filters and verify all cases included.', 'Test report generation across different months and years.', 'Download/export generated report and confirm format (PDF, CSV, etc.).', 'Verify that only authorized Case Managers can access the report builder.', 'Test large data sets for performance issues.']</t>
+          <t>['Generate monthly report for all case activities.', 'Filter report by individual worker and verify the output matches database records.', 'Filter report by case status (open, closed, overdue) and verify data.', 'Export report and confirm downloaded file matches visible data.', 'Test report generation for months with no activity to verify handling of empty datasets.', 'Verify only Case Managers have access to this report function.']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['Month or filter chosen with no case activity.', 'Worker with no cases assigned.', 'Deleted, reassigned, or inactive cases within the period.', 'Change reporting period while generating report.', 'Special characters in worker names or statuses.']</t>
+          <t>['Generate report for a non-existent worker.', 'Extremely high number of cases (performance and correctness).', 'Case activities spanning multiple months for the same case.', 'Statuses with zero cases in the selected period.']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>['Test report data accuracy where other stories filter by worker/status or export data (Related: [16, 18, 23, 30]).']</t>
+          <t>['Filter selection and report validation logic similar to stories 6 and 18 (e.g. ensure filter and date logic is consistent across reporting modules).']</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['Case activity logging', 'User role access controls', 'Existing or similar reporting features']</t>
+          <t>[6, 18]</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['Trigger eligibility rule change and verify all relevant users receive timely notifications.', 'Check notification content for accuracy and clarity.', 'Verify dismissal and/or acknowledgment of notification.', 'Confirm new users receive notification if rule changed before their account creation.', 'Verify notification is only sent to Case Workers.']</t>
+          <t>['Trigger an eligibility rule change and verify that all relevant case workers receive notifications.', 'Check that the notification includes clear information about the policy update.', 'Verify that only affected case workers receive the alert (based on assignment/responsibility).', 'Test acknowledgment or dismissal of the notification.', 'Audit notification delivery and read history.']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['Multiple eligibility rule changes in quick succession.', 'No recipients online/active at change time.', 'Rule changed, then rolled back.', 'User marked as inactive or deleted before notification.']</t>
+          <t>['Multiple rules changing in quick succession.', 'Case Worker is offline or logged out when the rule changes.', 'Rules reverted back to the original after notification sent.', 'Edge case workers with very high or low caseloads for notification delivery.']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Notification and alerting system testing as used in story 2 (notification delivery, display, persistence, etc.)']</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['Eligibility rule engine', 'User notification systems']</t>
+          <t>[2]</t>
         </is>
       </c>
     </row>
@@ -1286,22 +1286,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['List all overdue redetermination cases assigned to a Case Manager.', 'Perform follow-up action (e.g., send reminder) from overdue list, and verify outcome.', 'Sort and filter overdue cases (by priority, date, or worker).', 'Change case status and ensure overdue list refreshes.', 'Access control: only Case Managers can view overdue redeterminations.']</t>
+          <t>['List all cases with overdue redeterminations and verify accuracy against database.', "Change a case's redetermination date to overdue and confirm it appears on the list.", 'Select a case and initiate follow-up actions, checking state transitions and recording.', 'Ensure overdue count is recalculated as cases are resolved or new overdue cases appear.', 'Check notifications or reminders sent for overdue cases.']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['No overdue cases in the system.', 'Case becomes overdue during current session.', 'Previously overdue case is resolved and reappears due to error.', 'Case reassigned while overdue.']</t>
+          <t>['Cases that become overdue during business logic execution (race conditions).', 'Very old or recently closed cases that should/should not appear.', 'Cases with missing/invalid redetermination dates.', 'Bulk transitions where many cases become overdue at once.']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>['Verify overdue determination calculation logic matches related determination features (Related: [6, 7]).']</t>
+          <t>['Case listing, filter, and status update logic as seen in stories 6 and 7 (consistency of list/filter/action functionality).']</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['Redetermination logic', 'Case assignment functionality', 'Overdue detection in other modules']</t>
+          <t>[6, 7]</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Print summary for a case with multiple notes and verify formatting/layout.', 'Print summary for case with no notes (empty state handling).', 'Ensure confidential/flagged notes are handled per policy.', 'Verify only authorized users can print case note summaries.', 'Check print/export in different browsers and devices.']</t>
+          <t>['Select a case and generate a printable summary of its notes.', 'Verify that all case notes are present and accurate in print view.', 'Check print formatting for readability and professional appearance.', 'Print to PDF/physical printer and confirm output fidelity.', 'Test accessibility of print function for different user roles.']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['Very large number of case notes.', 'Case notes with images, special formatting, or attachments.', 'Case notes in multiple languages.', 'Corrupted or partially-saved notes.']</t>
+          <t>['Cases with no notes (empty summary).', 'Cases with extremely long, multi-page notes.', 'Notes containing special characters, non-English text, or attachments.', 'Concurrent changes to notes while printing.']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>['Consistency of printable output/data integrity with digital display/exported case notes (Related: [16]).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['Case note management/storage', 'Exporting/printing frameworks']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['Receive alert when a case is inactive for exactly 60 days.', 'Alert contains relevant case history.', 'No alert is sent for cases inactive for less than 60 days.', 'Alert is sent only once per inactivity event.', 'Alert displays correct case manager and case information.']</t>
+          <t>['Verify that a case becomes eligible for inactivity alert after 60 days of no updates.', 'Confirm the alert is sent to the assigned Case Manager.', 'Check that alert includes relevant case history details.', 'Ensure the alert is not sent if there is activity within the 60-day window.', 'Check user interface for displaying inactivity alerts.']</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['Case is updated at 59 days, then inactive — ensure timer resets.', 'Case marked inactive right before a leap day.', 'Multiple cases become inactive on the same day.', 'Case is reactivated and becomes inactive again.']</t>
+          <t>['Case updated 59 days ago—no alert should be sent.', 'Case updated at exactly the 60th day—alert should trigger.', 'A case with backdated activity that brings last activity within 60 days.', 'Multiple cases becoming inactive simultaneously.']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>['Test alert notification system with story 40 (Workload alerts).']</t>
+          <t>['Validate alert notification mechanism used in stories 6 and 7 (since related).']</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['Retest alert delivery system (shared with stories 40).', 'Verify alert history logging and display.']</t>
+          <t>['Stories 6, 7 (other alert scenarios for Case Managers).', 'Any alert delivery or notification systems used for case alerts.']</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['Alert generated when new income data entry conflicts with existing records.', 'Alert states which data fields conflict.', 'Case Worker receives only relevant conflicting income alerts.', 'No duplicate alerts for same conflict.', 'Resolved conflicts are not repeatedly alerted.']</t>
+          <t>['Check detection of conflicting income data on client submission.', 'Verify alert is generated for the assigned Case Worker on valid conflict.', 'Confirm alert includes both previous and submitted income data.', 'Verify no alert is generated for non-conflicting submissions.', 'UI/UX confirmation of alert receipt by Case Worker.']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['Multiple conflicting entries submitted simultaneously.', 'Income field left blank vs. zero.', 'Client edits same value back and forth before saving.', 'Edge values (e.g., maximum/minimum allowed income).']</t>
+          <t>['Multiple income entries submitted in quick succession with mixed conflicts.', "Edge of a threshold (e.g., $1 difference); system's conflict tolerance.", 'Duplicate income entries (identical values).', 'Income data submitted via different channels (e.g., web/phone).']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['Validation logic from story 3 if income validation is reused.']</t>
+          <t>['Income data validation logic tests shared with story 3.']</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['Retest income validation (story 3).', 'Retest alert notification delivery.']</t>
+          <t>['Story 3 (income validation logic).', 'Alert delivery systems for Case Workers.']</t>
         </is>
       </c>
     </row>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['Dashboard displays count of currently escalated cases.', 'Dashboard updates when new case is escalated/de-escalated.', 'Access controls: only managers can see escalation metrics.', 'Escalation trend graph reflects historical data accurately.', 'Multiple escalations/de-escalations in quick succession are tracked correctly.']</t>
+          <t>['Verify that escalated cases are tracked in the dashboard.', 'Check metrics update in real time as new cases are escalated.', 'Verify counting logic: only actual escalations count toward metrics.', 'Confirm UI displays escalation trend over selected time period.', 'Test filtering/sorting by urgency in the dashboard.']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['No cases escalated (dashboard shows zero).', 'Cases escalated and de-escalated within same reporting period.', 'Edge of reporting period (e.g., case escalated at midnight).', 'Large numbers of escalated cases (stress test).']</t>
+          <t>['No escalated cases—dashboard should show zero or appropriate message.', 'Large number of escalated cases for one or more periods.', 'Case status toggled from escalated to non-escalated and vice versa.']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['Escalation tracking logic (story 20) - if escalation is a shared attribute.']</t>
+          <t>['Escalation status consistency tests with story 20.', 'Metric aggregation and dashboard rendering logic.']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['Retest escalation case workflow (story 20).', 'Retest reporting/dashboard modules.']</t>
+          <t>['Story 20 (escalation status tracking).', 'Dashboard/reporting features.']</t>
         </is>
       </c>
     </row>
@@ -1411,22 +1411,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['Alert sent when document upload occurs outside business hours.', 'Correct case worker receives after-hours upload alerts.', 'Alerts include correct document and client context.', 'Business hours are configurable and respected.', 'Multiple uploads after-hours trigger individual alerts.']</t>
+          <t>['Verify that an alert is generated when a document is uploaded outside business hours.', 'Check that the alert is sent to the correct Case Worker.', 'Test configuring business hours and their impact on alert logic.', 'Ensure alerts are not generated for uploads during business hours.', 'UI displays after-hours upload alerts properly.']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['Upload occurs on boundary time (exact close/open of business hours).', 'Client uploads multiple files quickly after hours.', 'Leap year/Daylight Saving Time changes on business hours.', 'Case Worker is on leave or changed assignment post-upload.']</t>
+          <t>['Upload takes place exactly at the edge (start/end) of business hours.', 'Multiple uploads in rapid succession (bulk uploads) after hours.', 'Uploads by different clients to the same caseworker after hours.']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['Upload notification logic (stories 8 and 17).']</t>
+          <t>['Document upload detection logic with stories 8 and 17.', 'Alert notification mechanism.']</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['Retest document upload workflow (stories 8 and 17).', 'Retest notification/alerting system.']</t>
+          <t>['Stories 8, 17 (document upload feature and related alerts).', 'Alert delivery/notification systems.']</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1436,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['Alert sent to Case Manager when Case Worker is assigned above workload threshold.', 'Accurate calculation of workload (e.g., number of cases, complexity weighting).', 'Alert includes list of overloaded Case Workers and their assigned cases.', 'Alert is not sent when workload is below threshold.', 'Case reassignment clears previous overload alert.']</t>
+          <t>['Verify alert is generated when a Case Worker exceeds the workload threshold.', 'Alert is received by the Case Manager responsible for reassignment.', 'Test the calculation logic for workload (e.g., number and type of cases handled).', 'Check that reducing workload below threshold removes or resolves alert.', 'UI/UX for generating, viewing, and acting on overload alerts.']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['Worker receives cases above threshold and then cases are closed rapidly.', 'Threshold change after assignment (e.g., lowered).', 'Simultaneous reassignment among multiple workers.', 'Very high number of concurrent overloads.']</t>
+          <t>['Workload exactly at the threshold (should not trigger alert).', 'Rapid changes in workload (cases assigned/closed in quick succession).', 'Simultaneous overloads across multiple caseworkers.']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['Alert notification system (shared with story 36).']</t>
+          <t>['Workload calculation and threshold comparison logic with stories 10 and 18.', 'Alert notification routine.']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['Retest alert delivery (story 36).', 'Retest case assignment logic (stories 10, 18).']</t>
+          <t>['Stories 10, 18 (workload calculation and reassignment flows).', 'Alert and notification systems.']</t>
         </is>
       </c>
     </row>

--- a/output_test_cases.xlsx
+++ b/output_test_cases.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,169 +458,172 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>This user story enables Case Workers to initiate Medicaid eligibility processing by recording new applications with essential applicant information. It ensures proper capture of applicant details, system validation for required data, and reinforces data integrity and user role compliance.</t>
+          <t>This user story enables Case Workers to intake a new Medicaid application, serving as the foundational step for eligibility determination. The process involves collecting basic applicant information, creating an application record, and ensuring smooth progression to subsequent eligibility checks.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to intake a new Medicaid application so that I can begin the eligibility process. - Enable intake of new applications with basic applicant details.</t>
+          <t>As a Case Worker, I want to intake a new Medicaid application so that I can begin the eligibility process.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A Case Worker logs in, accesses the intake module, enters valid applicant information, saves the application, and receives a confirmation that the case is created and ready for further processing.</t>
+          <t>A Case Worker logs in, accesses the intake module, enters all required applicant details (name, DOB, address, contact, SSN, etc.), submits the application, and receives confirmation with a unique application ID.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'INTAKE-01', 'Brief Description': 'Successful intake of new Medicaid application with complete valid details'}, {'Test Case ID': 'INTAKE-02', 'Brief Description': 'Attempt intake with missing applicant mandatory fields'}, {'Test Case ID': 'INTAKE-03', 'Brief Description': 'Attempt intake with invalid format (e.g., invalid SSN or DOB)'}, {'Test Case ID': 'INTAKE-04', 'Brief Description': 'Verify only Case Worker roles have access to intake function'}, {'Test Case ID': 'INTAKE-05', 'Brief Description': 'Check system audit log records the intake event'}, {'Test Case ID': 'INTAKE-06', 'Brief Description': 'Verify application cannot be submitted twice with same SSN'}]</t>
+          <t>[{'Test Case ID': 'US1_TC1', 'Brief Description': 'Intake new Medicaid application with valid details (Happy Path)'}, {'Test Case ID': 'US1_TC2', 'Brief Description': 'Attempt intake with missing mandatory fields (Negative)'}, {'Test Case ID': 'US1_TC3', 'Brief Description': 'Attempt intake with invalid data formats (Negative)'}, {'Test Case ID': 'US1_TC4', 'Brief Description': 'Verify application cannot be submitted by unauthorized user role (Negative, Permissions)'}, {'Test Case ID': 'US1_TC5', 'Brief Description': 'Verify audit log records application intake (Compliance, Audit)'}, {'Test Case ID': 'US1_TC6', 'Brief Description': 'Verify API endpoint for application creation returns correct response (API)'}, {'Test Case ID': 'US1_TC7', 'Brief Description': 'Verify integration to downstream modules (e.g., eligibility process trigger)'}]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'INTAKE-01', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Create New Application', 'Test Scenario Title': 'Intake with Complete Valid Applicant Data', 'Precondition': 'User logged in as Case Worker; Intake module accessible', 'Test Data': "{ 'Name': 'John Doe', 'DOB': '1980-01-01', 'SSN': '123-45-6789', 'Address': '123 Main St', ... }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker', "2. Navigate to 'Intake New Application'", '3. Enter all required applicant information in valid formats', '4. Submit application'], 'Expected Result': 'New application is created and case number assigned; confirmation displayed', 'Dependent Module/Process': 'Eligibility Workflow'}, {'Test Case ID': 'INTAKE-02', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Create New Application', 'Test Scenario Title': 'Missing Mandatory Fields', 'Precondition': 'User logged in as Case Worker; Intake module accessible', 'Test Data': "{ 'Name': 'John Doe', 'DOB': '', 'SSN': '', ... }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker', "2. Navigate to 'Intake New Application'", '3. Leave mandatory fields blank', '4. Attempt to submit application'], 'Expected Result': 'System displays error for missing required fields; user cannot proceed', 'Dependent Module/Process': None}, {'Test Case ID': 'INTAKE-03', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Create New Application', 'Test Scenario Title': 'Invalid Data Format', 'Precondition': 'User logged in as Case Worker; Intake module accessible', 'Test Data': "{ 'SSN': 'invalid', 'DOB': '99-99-9999' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker', "2. Navigate to 'Intake New Application'", '3. Enter invalid values (e.g., alphabetic SSN, malformed DOB)', '4. Attempt to submit application'], 'Expected Result': 'System displays format validation errors; application not saved', 'Dependent Module/Process': None}, {'Test Case ID': 'INTAKE-04', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Application Intake UI', 'User Story': 'US-1', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role Validation', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Role Based Access Control - Intake Screen', 'Precondition': 'User logged in as non-Case Worker (e.g., Auditor, Public User)', 'Test Data': '{}', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor/Public User', 'Detailed Test Steps': ['1. Log in as non-Case Worker user', "2. Attempt to access 'Intake New Application' functionality"], 'Expected Result': 'User is denied access; sees error or is redirected', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'INTAKE-05', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Audit Logging', 'User Story': 'US-1', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Event Logging', 'Activity Title': 'Log Creation', 'Test Scenario Title': 'Audit Logging on Application Intake', 'Precondition': 'New application successfully submitted', 'Test Data': "{ 'Case Worker': 'user123', 'Timestamp': '&lt;date/time&gt;' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Complete application intake (see intake happy path)', '2. Query audit logs for recent activity'], 'Expected Result': 'Intake event logged with user ID, timestamp, and applicant reference', 'Dependent Module/Process': 'Audit Log System'}, {'Test Case ID': 'INTAKE-06', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Duplicate Check', 'User Story': 'US-1', 'Business Process': 'Medicaid Eligibility Determination', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Duplicate Detection', 'Test Scenario Title': 'Duplicate SSN Submission Prevention', 'Precondition': 'Existing application with SSN 123-45-6789', 'Test Data': "{ 'SSN': '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Attempt to create new application with SSN already present in active system', '2. Submit application'], 'Expected Result': 'System prevents duplicate submission; error displayed regarding existing record', 'Dependent Module/Process': 'Duplicate Detection Service'}]</t>
+          <t>[{'Test Case ID': 'US1_TC1', 'EPIC': 'Medicaid Application Intake', 'Feature': 'New Application Intake', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Enter Applicant Details', 'Test Scenario Title': 'Successful Medicaid application intake', 'Precondition': "Case Worker is logged in and has 'Case Worker' role assigned. Intake system is available.", 'Test Data': {'First Name': 'Jane', 'Last Name': 'Doe', 'DOB': '1980-01-01', 'Address': '123 Main St', 'SSN': '123-45-6789', 'Contact': '555-1111'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Navigate to 'Application Intake' page.", 'Enter all required applicant details.', 'Submit the form.'], 'Expected Result': "System confirms successful intake, generates unique application ID, and status is set to 'Intake Complete'.", 'Dependent Module/Process': 'Eligibility module (post-intake)'}, {'Test Case ID': 'US1_TC2', 'EPIC': 'Medicaid Application Intake', 'Feature': 'New Application Intake', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Enter Applicant Details', 'Test Scenario Title': 'Attempt intake with missing mandatory fields', 'Precondition': "User is logged in as 'Case Worker'.", 'Test Data': {'First Name': '', 'Last Name': 'Doe', 'DOB': '1980-01-01', 'Address': '', 'SSN': ''}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Go to 'Application Intake'.", 'Leave mandatory fields empty or incomplete.', 'Attempt to submit.'], 'Expected Result': 'System displays field-level validation errors, does not proceed to intake submission.', 'Dependent Module/Process': None}, {'Test Case ID': 'US1_TC3', 'EPIC': 'Medicaid Application Intake', 'Feature': 'New Application Intake', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Enter Applicant Details', 'Test Scenario Title': 'Invalid data format field', 'Precondition': "User is logged in as 'Case Worker'.", 'Test Data': {'First Name': 'Jane', 'Last Name': 'Doe', 'DOB': '01-01-1980x', 'Address': 'Example Lane', 'SSN': 'not-a-ssn'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to intake page.', 'Enter fields with invalid formats (text in date, incorrect SSN).', 'Submit application.'], 'Expected Result': 'System rejects submission; relevant fields display format error messages.', 'Dependent Module/Process': None}, {'Test Case ID': 'US1_TC4', 'EPIC': 'Medicaid Application Intake', 'Feature': 'New Application Intake', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'Application Intake', 'Activity Title': 'Access Intake', 'Test Scenario Title': 'Intake by unauthorized user role', 'Precondition': "User logged in as Viewer or with no 'Case Worker' privileges.", 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Viewer/Other', 'Detailed Test Steps': ['Attempt to access intake module.', 'Try to submit an application.'], 'Expected Result': "System denies access with a 'Permission Denied' message; no submission allowed.", 'Dependent Module/Process': 'User Roles and Permissions'}, {'Test Case ID': 'US1_TC5', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Compliance and Auditing', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'Audit and Compliance', 'Activity Title': 'Record Audit Trail', 'Test Scenario Title': 'Audit log creation after application intake', 'Precondition': 'Application intake completed.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Complete an application intake (as per US1_TC1).', 'Access system audit logs.'], 'Expected Result': 'Audit log contains relevant details (timestamp, user, action, application ID) per regulatory requirements.', 'Dependent Module/Process': 'Audit Logging Module'}, {'Test Case ID': 'US1_TC6', 'EPIC': 'Medicaid Application Intake', 'Feature': 'API Integration', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'API Submission', 'Activity Title': 'Call API Endpoint', 'Test Scenario Title': 'Validate API endpoint for application intake', 'Precondition': 'API credentials available; system ready.', 'Test Data': {'payload': {'firstName': 'Jane', 'lastName': 'Doe', 'dob': '1980-01-01', 'address': '123 Main St', 'ssn': '123-45-6789'}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Send POST request to /applications endpoint with payload.'], 'Expected Result': 'API returns 201 Created, response body contains application ID and intake status.', 'Dependent Module/Process': 'API Gateway'}, {'Test Case ID': 'US1_TC7', 'EPIC': 'Medicaid Application Intake', 'Feature': 'Integration Testing', 'User Story': 'US1', 'Business Process': 'Medicaid Eligibility', 'Sub-Process Title': 'Downstream Processing', 'Activity Title': 'Post-intake Eligibility Trigger', 'Test Scenario Title': 'Verify eligibility process is triggered after successful intake', 'Precondition': 'Application intake is completed successfully.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit new application.', 'Monitor system for eligibility process initiation.'], 'Expected Result': 'Eligibility process/status is updated and initiated per design.', 'Dependent Module/Process': 'Eligibility Determination'}]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>This user story ensures that Medicaid applicant identity is verified against authoritative sources (such as DMV or SSA), preventing identity fraud and maintaining record accuracy in the eligibility process.</t>
+          <t>This user story covers the integration of external government identity verification (e.g., DMV, SSA), allowing Case Workers to confirm Medicaid applicants’ identities and maintain accurate administration records.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to verify applicant identity using government ID so that I can ensure accurate records. - Integrate ID verification with DMV or SSA databases.</t>
+          <t>As a Case Worker, I want to verify applicant identity using government ID so that I can ensure accurate records.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Case Worker submits applicant's government ID information; system sends request to DMV/SSA; receives positive match and marks identity as verified.</t>
+          <t>Case Worker enters applicant's government ID, system queries external database (DMV/SSA), identity is successfully verified and marked as validated in the system.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'IDVER-01', 'Brief Description': 'Successfully verify applicant identity with valid government ID'}, {'Test Case ID': 'IDVER-02', 'Brief Description': 'Fail verification with invalid or mismatched government ID'}, {'Test Case ID': 'IDVER-03', 'Brief Description': 'Attempt to verify identity when external ID verification service is unavailable'}, {'Test Case ID': 'IDVER-04', 'Brief Description': 'Ensure only Case Workers may initiate ID verification'}, {'Test Case ID': 'IDVER-05', 'Brief Description': 'Audit logging of identity verification attempt'}, {'Test Case ID': 'IDVER-06', 'Brief Description': 'Compliance with data masking on government ID fields'}]</t>
+          <t>[{'Test Case ID': 'US2_TC1', 'Brief Description': 'Verify identity with valid government ID (Happy Path)'}, {'Test Case ID': 'US2_TC2', 'Brief Description': 'Fail to verify identity with invalid or expired ID (Negative)'}, {'Test Case ID': 'US2_TC3', 'Brief Description': 'Simulate unavailable external system (Negative, Integration)'}, {'Test Case ID': 'US2_TC4', 'Brief Description': 'Verify only authorized users may perform verification (Permissions)'}, {'Test Case ID': 'US2_TC5', 'Brief Description': 'System logs verification request and response (Audit &amp; Compliance)'}, {'Test Case ID': 'US2_TC6', 'Brief Description': 'API response for identity verification endpoint (API)'}]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'IDVER-01', 'EPIC': 'Identity Verification', 'Feature': 'Government ID Validation', 'User Story': 'US-2', 'Business Process': 'Applicant Verification', 'Sub-Process Title': 'Identity Validation', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'Successful Government ID Verification', 'Precondition': 'Applicant data entered and saved; user is Case Worker', 'Test Data': "{ 'SSN': '234-56-7890', 'FullName': 'Jane Smith', 'DOB': '1990-02-20' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant in system', '2. Enter government ID information (e.g., SSN/DL)', '3. Initiate verification request', '4. Await system response'], 'Expected Result': "System confirms positive ID match; applicant identity marked as 'Verified'", 'Dependent Module/Process': 'External API to DMV/SSA'}, {'Test Case ID': 'IDVER-02', 'EPIC': 'Identity Verification', 'Feature': 'Government ID Validation', 'User Story': 'US-2', 'Business Process': 'Applicant Verification', 'Sub-Process Title': 'Identity Validation', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'Invalid or Mismatched Government ID', 'Precondition': 'Applicant data entered and saved; user is Case Worker', 'Test Data': "{ 'SSN': '111-22-3333', 'FullName': 'Not Matching', 'DOB': '1985-12-01' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Enter mismatched or invalid government ID information', '3. Submit verification request'], 'Expected Result': 'System displays verification failure and related message; identity not marked as verified', 'Dependent Module/Process': 'External API to DMV/SSA'}, {'Test Case ID': 'IDVER-03', 'EPIC': 'Identity Verification', 'Feature': 'Government ID Validation', 'User Story': 'US-2', 'Business Process': 'Applicant Verification', 'Sub-Process Title': 'Identity Validation', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'ID Verification Service Unavailable', 'Precondition': 'Applicant data entered and saved; external service is purposefully down', 'Test Data': "{ 'SSN': '222-33-4444' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Enter government ID information', '3. Submit verification request'], 'Expected Result': 'System notifies user that verification service is unavailable; identity remains unverified', 'Dependent Module/Process': 'External API to DMV/SSA'}, {'Test Case ID': 'IDVER-04', 'EPIC': 'Identity Verification', 'Feature': 'Access Control', 'User Story': 'US-2', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Verify Role Restriction', 'Test Scenario Title': 'Only Case Workers Can Submit ID Verification', 'Precondition': 'User logged in as non-Case Worker', 'Test Data': '{}', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor/Public User/Other Staff', 'Detailed Test Steps': ['1. Log in as an unauthorized user', '2. Attempt to access ID verification feature'], 'Expected Result': 'Access is denied; feature not visible or user receives error', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'IDVER-05', 'EPIC': 'Identity Verification', 'Feature': 'Audit Logging', 'User Story': 'US-2', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Event Logging', 'Activity Title': 'Log Verification Attempt', 'Test Scenario Title': 'Audit Logging for Identity Verification Attempt', 'Precondition': 'Verification attempt performed (success or failure)', 'Test Data': "{ 'user': 'cw01', 'applicant': 'xyz', 'timestamp': '&lt;date&gt;' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Perform a government ID verification attempt (success or failure)', '2. Query system audit logs', '3. Ensure entry has required details'], 'Expected Result': 'Audit log entry records user, timestamp, result, and applicant reference', 'Dependent Module/Process': 'Audit Log and Compliance Monitoring'}, {'Test Case ID': 'IDVER-06', 'EPIC': 'Identity Verification', 'Feature': 'Data Compliance', 'User Story': 'US-2', 'Business Process': 'Compliance (HIPAA, State Regs)', 'Sub-Process Title': 'Protected Data Handling', 'Activity Title': 'Data Display and Transmission', 'Test Scenario Title': 'PII Masking on Government ID During Verification', 'Precondition': 'Application with government ID entered', 'Test Data': "{ 'SSN': '867-53-0909' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. View government ID input and display fields during verification process', '2. Review UI and logs for PII exposure'], 'Expected Result': 'Government ID (SSN, DL#) is masked per compliance standards (e.g., last 4 digits only)', 'Dependent Module/Process': 'Data Masking/Compliance Engine'}]</t>
+          <t>[{'Test Case ID': 'US2_TC1', 'EPIC': 'Applicant Identity Verification', 'Feature': 'DMV/SSA Integration', 'User Story': 'US2', 'Business Process': 'Identity Management', 'Sub-Process Title': 'Government ID Verification', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'Successful government ID verification', 'Precondition': 'Applicant has valid government-issued ID; Case Worker is logged in and has necessary permissions.', 'Test Data': {'ID Type': "Driver's License", 'ID Number': 'D1234567', 'DOB': '1980-01-01'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to the verification section of the application.', 'Enter government ID details.', 'Submit for verification.'], 'Expected Result': "System validates ID with DMV/SSA, applicant record is marked as 'Verified.'", 'Dependent Module/Process': 'DMV/SSA external system'}, {'Test Case ID': 'US2_TC2', 'EPIC': 'Applicant Identity Verification', 'Feature': 'DMV/SSA Integration', 'User Story': 'US2', 'Business Process': 'Identity Management', 'Sub-Process Title': 'Government ID Verification', 'Activity Title': 'Submit ID for Verification', 'Test Scenario Title': 'Fail verification with invalid ID', 'Precondition': 'Applicant provides expired or incorrect government ID.', 'Test Data': {'ID Type': 'State ID', 'ID Number': 'INVALID123', 'DOB': '1980-01-01'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Enter invalid government ID details.', 'Submit for verification.'], 'Expected Result': "System displays 'Identity could not be verified.' Record remains unverified.", 'Dependent Module/Process': 'DMV/SSA external system'}, {'Test Case ID': 'US2_TC3', 'EPIC': 'Applicant Identity Verification', 'Feature': 'DMV/SSA Integration', 'User Story': 'US2', 'Business Process': 'Identity Management', 'Sub-Process Title': 'Government ID Verification', 'Activity Title': 'External Service Availability', 'Test Scenario Title': 'External system unavailable during verification', 'Precondition': 'DMV/SSA service is offline or unreachable.', 'Test Data': {'ID Type': "Driver's License", 'ID Number': 'D1234567', 'DOB': '1980-01-01'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit ID for verification while simulated outage is active.'], 'Expected Result': 'System displays connection or service unavailable error; record is not updated.', 'Dependent Module/Process': 'DMV/SSA external system'}, {'Test Case ID': 'US2_TC4', 'EPIC': 'Applicant Identity Verification', 'Feature': 'Permissions and Access Control', 'User Story': 'US2', 'Business Process': 'Identity Management', 'Sub-Process Title': 'Government ID Verification', 'Activity Title': 'Authorization', 'Test Scenario Title': 'Unauthorized user attempts verification', 'Precondition': "User is logged in but does not have 'Case Worker' or 'ID Verifier' role.", 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Viewer/Other', 'Detailed Test Steps': ['Attempt to access ID verification feature.'], 'Expected Result': 'System denies access with appropriate error message.', 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'US2_TC5', 'EPIC': 'Applicant Identity Verification', 'Feature': 'Compliance and Audit', 'User Story': 'US2', 'Business Process': 'Identity Management', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Log Verification Attempts', 'Test Scenario Title': 'Audit logging for ID verification actions', 'Precondition': 'ID verification request performed.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit ID for verification.', 'Review audit logs.'], 'Expected Result': 'Audit logs capture user, timestamp, applicant, verification request, and response for compliance.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'US2_TC6', 'EPIC': 'Applicant Identity Verification', 'Feature': 'API Contract Validation', 'User Story': 'US2', 'Business Process': 'Identity Management', 'Sub-Process Title': 'API Integration', 'Activity Title': 'Verify API Response', 'Test Scenario Title': 'API validation for identity verification', 'Precondition': 'API endpoint is deployed and accessible.', 'Test Data': {'payload': {'idType': "Driver's License", 'idNumber': 'D1234567', 'dob': '1980-01-01'}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Send POST to /verify-identity with valid payload.'], 'Expected Result': "API responds with 200 and verificationStatus: 'Verified'.", 'Dependent Module/Process': 'API Gateway, DMV/SSA'}]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>This user story enables Case Workers to determine Medicaid financial eligibility by integrating with wage data sources like The Work Number, allowing accurate application assessment based on verified income.</t>
+          <t>This user story enables Case Workers to determine an applicant's financial qualification for Medicaid by verifying income data through connection with trusted sources like The Work Number or state wage databases.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to check income eligibility using wage data so that I can determine financial qualification. - Connect to income verification systems like The Work Number.</t>
+          <t>As a Case Worker, I want to check income eligibility using wage data so that I can determine financial qualification.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Case Worker initiates income check for an applicant; system queries The Work Number; returns income data; eligibility determination based on returned values.</t>
+          <t>Case Worker inputs applicant details, system automatically queries connected wage databases for employment and income verification, and receives/integrates verified wage information for eligibility assessment.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'INCVER-01', 'Brief Description': 'Successful retrieval and processing of income data'}, {'Test Case ID': 'INCVER-02', 'Brief Description': 'Income eligibility fails - applicant income above threshold'}, {'Test Case ID': 'INCVER-03', 'Brief Description': 'No wage data found for applicant'}, {'Test Case ID': 'INCVER-04', 'Brief Description': 'External income verification system downtime'}, {'Test Case ID': 'INCVER-05', 'Brief Description': 'API returns unexpected/incomplete data'}, {'Test Case ID': 'INCVER-06', 'Brief Description': 'Access to income check restricted to Case Worker role'}, {'Test Case ID': 'INCVER-07', 'Brief Description': 'Verify audit logs record all income data access and eligibility decisions'}]</t>
+          <t>[{'Test Case ID': 'US3_TC1', 'Brief Description': 'Check income eligibility with valid wage data returned (Happy Path)'}, {'Test Case ID': 'US3_TC2', 'Brief Description': 'Fail income verification due to no record found (Negative)'}, {'Test Case ID': 'US3_TC3', 'Brief Description': 'Income below and above Medicaid threshold (Boundary, Compliance)'}, {'Test Case ID': 'US3_TC4', 'Brief Description': 'Simulate wage source system unavailable (Negative, Integration)'}, {'Test Case ID': 'US3_TC5', 'Brief Description': 'User without permission attempts income check (Permissions)'}, {'Test Case ID': 'US3_TC6', 'Brief Description': 'Verify audit logging for income verification (Audit &amp; Compliance)'}, {'Test Case ID': 'US3_TC7', 'Brief Description': 'Validate API contract for wage data query (API)'}]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'INCVER-01', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Successful Wage Data Retrieval', 'Precondition': 'Applicant record exists; user as Case Worker', 'Test Data': "{ 'SSN': '345-67-8901', 'Employer': 'ABC Corp' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System sends request to The Work Number', '4. Receives valid income data'], 'Expected Result': 'Income data displayed; eligibility decision based on rules; status updated on application', 'Dependent Module/Process': 'Income API, Eligibility Engine'}, {'Test Case ID': 'INCVER-02', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Income Above Threshold', 'Precondition': 'Applicant record exists; user as Case Worker', 'Test Data': "{ 'Income': 50000, 'Threshold': 20000 }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System receives income data exceeding eligibility threshold'], 'Expected Result': 'System flags applicant as income-ineligible; displays explanatory alert; marks application as ineligible', 'Dependent Module/Process': 'Eligibility Engine'}, {'Test Case ID': 'INCVER-03', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'No Wage Data Found', 'Precondition': 'Applicant exists with valid SSN; no wage record in The Work Number', 'Test Data': "{ 'SSN': '999-99-9999' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', "3. System receives 'no data found' response"], 'Expected Result': 'System notifies user; allows for manual follow-up or document upload', 'Dependent Module/Process': 'Income API'}, {'Test Case ID': 'INCVER-04', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Income Verification Service Unavailable', 'Precondition': 'Applicant exists; income service is down', 'Test Data': "{ 'SSN': '456-78-9012' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System fails to receive response from The Work Number'], 'Expected Result': 'System displays error regarding service unavailability; prevents eligibility action until resolved', 'Dependent Module/Process': 'Income API'}, {'Test Case ID': 'INCVER-05', 'EPIC': 'Income Verification', 'Feature': 'Wage Data Integration', 'User Story': 'US-3', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Income Assessment', 'Activity Title': 'Query Income Data', 'Test Scenario Title': 'Unexpected or Incomplete API Response', 'Precondition': 'Applicant record exists; API returns partial data', 'Test Data': "{ 'Employer': '', 'Income': null }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Select applicant', '2. Initiate income check', '3. System receives incomplete API response'], 'Expected Result': 'System displays error/validation message for incomplete data; no eligibility determination made', 'Dependent Module/Process': 'Income API/Error Handling'}, {'Test Case ID': 'INCVER-06', 'EPIC': 'Income Verification', 'Feature': 'Access Control', 'User Story': 'US-3', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Verify Role Restriction', 'Test Scenario Title': 'Restrict Access to Income Verification to Case Workers', 'Precondition': 'User logged in as non-Case Worker', 'Test Data': '{}', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor/Public User/Other Staff', 'Detailed Test Steps': ['1. Log in as unauthorized user', '2. Attempt to access income verification feature'], 'Expected Result': 'Access is denied; feature not visible or user receives error', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'INCVER-07', 'EPIC': 'Income Verification', 'Feature': 'Audit Logging', 'User Story': 'US-3', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Event Logging', 'Activity Title': 'Log Income Checks', 'Test Scenario Title': 'Audit Logging of Income Data Requests', 'Precondition': 'Income check requested for applicant', 'Test Data': "{ 'User': 'cw01', 'Applicant': 'abc', 'Timestamp': '&lt;date/time&gt;' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Perform income check', '2. Query audit logs for recent activity'], 'Expected Result': 'Audit log captures requester ID, applicant reference, timestamp, and eligibility decision', 'Dependent Module/Process': 'Audit Log/Compliance System'}]</t>
+          <t>[{'Test Case ID': 'US3_TC1', 'EPIC': 'Income Eligibility Verification', 'Feature': 'Wage Data Connection', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'Query Wage Databases', 'Test Scenario Title': 'Successful wage data retrieval and eligibility check', 'Precondition': 'Case Worker is logged in and has eligibility determination role. Wage data system is online.', 'Test Data': {'Applicant Name': 'Jane Doe', 'SSN': '123-45-6789'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to income eligibility section.', 'Input applicant details and request wage verification.', 'System queries The Work Number or appropriate wage source.'], 'Expected Result': 'System returns verified wage data and eligibility status based on Medicaid thresholds.', 'Dependent Module/Process': 'Wage Data Source'}, {'Test Case ID': 'US3_TC2', 'EPIC': 'Income Eligibility Verification', 'Feature': 'Wage Data Connection', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'Query Wage Databases', 'Test Scenario Title': 'No wage record found', 'Precondition': 'Wage system is online, applicant not present in database.', 'Test Data': {'Applicant Name': 'John Smith', 'SSN': '000-00-0000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit wage verification for applicant not in system.'], 'Expected Result': "System returns 'No record found'; eligibility cannot be determined from wage database.", 'Dependent Module/Process': 'Wage Data Source'}, {'Test Case ID': 'US3_TC3', 'EPIC': 'Income Eligibility Verification', 'Feature': 'Wage Data Connection', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'Compliance with Income Thresholds', 'Test Scenario Title': 'Applicants with income above/below threshold', 'Precondition': 'Case Worker is logged in.', 'Test Data': [{'Applicant': 'Alice Low', 'SSN': '222-22-2222', 'Annual Income': 10000}, {'Applicant': 'Bob High', 'SSN': '333-33-3333', 'Annual Income': 60000}], 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit wage verification for both test applicants.'], 'Expected Result': 'System determines Alice Low is eligible, Bob High is ineligible as per Medicaid guidelines.', 'Dependent Module/Process': 'Wage Data Source, Compliance Rules'}, {'Test Case ID': 'US3_TC4', 'EPIC': 'Income Eligibility Verification', 'Feature': 'Integration Fault Handling', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'Handle Wage Data System Outage', 'Test Scenario Title': 'Wage data source unavailable', 'Precondition': 'Wage source system is offline/unreachable.', 'Test Data': {'Applicant Name': 'Jane Doe', 'SSN': '123-45-6789'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt wage verification while source system is down.'], 'Expected Result': 'System displays error and blocks eligibility decision; option for manual override per policy.', 'Dependent Module/Process': 'Wage Data Source'}, {'Test Case ID': 'US3_TC5', 'EPIC': 'Income Eligibility Verification', 'Feature': 'Permission Enforcement', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'Access Controls', 'Test Scenario Title': 'Unauthorized role attempts income check', 'Precondition': 'User with no income check privileges.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Viewer/Other', 'Detailed Test Steps': ['Attempt access to wage verification feature.'], 'Expected Result': 'System denies access per role permissions.', 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': 'US3_TC6', 'EPIC': 'Income Eligibility Verification', 'Feature': 'Audit &amp; Compliance', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Audit trail for all wage verification actions', 'Precondition': 'Wage verification action performed.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Perform income eligibility check.', 'Review audit logs.'], 'Expected Result': 'Audit log records user, timestamp, query details, and response for compliance checking.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'US3_TC7', 'EPIC': 'Income Eligibility Verification', 'Feature': 'API Contract Validation', 'User Story': 'US3', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Income Check', 'Activity Title': 'API Validation', 'Test Scenario Title': 'Income verification API response', 'Precondition': 'API is accessible and test credentials are available.', 'Test Data': {'payload': {'applicantName': 'Jane Doe', 'ssn': '123-45-6789'}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Send POST to /income-verification with applicant data.'], 'Expected Result': 'API responds with 200, wage data, and eligibility status.', 'Dependent Module/Process': 'Wage Data Source'}]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>This user story ensures Case Workers can accurately record and maintain household composition, capturing household members and their relationships for eligibility assessment based on family size. Proper recording enables compliance with program and audit requirements.</t>
+          <t>This story addresses the need for Case Workers to record detailed household composition, crucial for eligibility assessment. The system must allow entry and management of household members, capture their relationships, and ensure data integrity for regulatory compliance and auditability.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to record household composition so that I can assess eligibility based on family size. - Capture household members and their relationships.</t>
+          <t>As a Case Worker, I want to record household composition so that I can assess eligibility based on family size.
+- Capture household members and their relationships.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Case Worker logs in, opens a client case, navigates to the household composition section, adds all household members (with correct relationships), saves the data, and verifies system acceptance.</t>
+          <t>Case Worker successfully adds, edits, and reviews household members with appropriate relationships; the system stores all data, supports eligibility calculations, and logs all changes for audit.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US4_TC1', 'Brief Description': 'Add household members and relationships successfully (happy path)'}, {'Test Case ID': 'US4_TC2', 'Brief Description': 'Add a household member with missing required fields (negative)'}, {'Test Case ID': 'US4_TC3', 'Brief Description': 'Attempt to save household composition with invalid relationships (negative)'}, {'Test Case ID': 'US4_TC4', 'Brief Description': 'Attempt to add duplicate household members (negative)'}, {'Test Case ID': 'US4_TC5', 'Brief Description': 'Verify data is saved and displayed correctly upon reopening (functional/integration)'}, {'Test Case ID': 'US4_TC6', 'Brief Description': 'API: POST/PUT household composition with all valid fields'}, {'Test Case ID': 'US4_TC7', 'Brief Description': 'API: Reject incomplete/invalid household composition data'}]</t>
+          <t>[{'Test Case ID': '4.1', 'Brief Description': 'Add household members with valid data and relationships.'}, {'Test Case ID': '4.2', 'Brief Description': 'Edit household member data and relationships.'}, {'Test Case ID': '4.3', 'Brief Description': 'Attempt to add a household member with missing or invalid fields (negative).'}, {'Test Case ID': '4.4', 'Brief Description': 'View and verify household composition summary.'}, {'Test Case ID': '4.5', 'Brief Description': 'Check audit log and compliance traces for data entry and edits.'}]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US4_TC1', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Add household members and relationships successfully', 'Precondition': 'Case Worker has a valid login; client case exists', 'Test Data': 'Case ID: 123; Members: John Smith (DOB: 1980-05-01, Relationship: Self), Mary Smith (DOB: 1982-03-10, Relationship: Spouse), Janet Smith (DOB: 2010-09-01, Relationship: Daughter)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Navigate to client case (ID: 123)', "Go to 'Household Composition' section", "Click 'Add Member', enter John Smith’s details and relationship 'Self', save", "Click 'Add Member', enter Mary Smith, relationship 'Spouse', save", "Click 'Add Member', enter Janet Smith, relationship 'Daughter', save", "Click 'Save' household composition"], 'Expected Result': 'All household members are listed with correct relationships. No errors. Data is persisted.', 'Dependent Module/Process': 'Client Case'}, {'Test Case ID': 'US4_TC2', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Add household member with missing required fields', 'Precondition': "Case Worker at 'Household Composition' section", 'Test Data': 'Name: (blank), DOB: 2012-04-23, Relationship: Son', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Attempt to add new household member, leave 'Name' blank, fill other fields", "Click 'Save'"], 'Expected Result': "System highlights missing 'Name' field and prevents save, user sees appropriate error message.", 'Dependent Module/Process': 'Client Case'}, {'Test Case ID': 'US4_TC3', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Save household member with invalid relationship', 'Precondition': 'At least one household member has been added', 'Test Data': 'Name: Jane Doe, Relationship: Alien', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Add a new household member Jane Doe', "Select 'Alien' as relationship", "Click 'Save'"], 'Expected Result': 'System displays validation error ‘Invalid relationship’ and save is blocked.', 'Dependent Module/Process': 'Validation Service'}, {'Test Case ID': 'US4_TC4', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Add duplicate household members', 'Precondition': 'Member John Smith (DOB:1980-05-01) already exists', 'Test Data': 'Name: John Smith, DOB: 1980-05-01, Relationship: Self', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to add John Smith with same DOB again', "Click 'Save'"], 'Expected Result': "System alerts 'Duplicate member detected' and prevents save.", 'Dependent Module/Process': 'Duplicate Checking'}, {'Test Case ID': 'US4_TC5', 'EPIC': 'Household Management', 'Feature': 'Household Composition', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'Household Record', 'Activity Title': 'Verify persistence', 'Test Scenario Title': 'Review household composition after save', 'Precondition': 'Household composition saved successfully', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Logout and login again', 'Navigate to client case', "Open 'Household Composition' section"], 'Expected Result': 'All previously added members and relationships appear correctly.', 'Dependent Module/Process': 'Persistence/Database'}, {'Test Case ID': 'US4_TC6', 'EPIC': 'Household Management', 'Feature': 'Household Composition API', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Create/Update Household Composition', 'Test Scenario Title': 'API accepts valid household composition submission', 'Precondition': 'API is accessible with valid credentials', 'Test Data': "{ household_id: 123, members: [{name: 'John Smith', dob: '1980-05-01', relationship: 'Self'}, ...] }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Send POST or PUT request to /api/household-compositions with valid payload'], 'Expected Result': 'API responds with 200 OK and reflects household data correctly.', 'Dependent Module/Process': 'API/Database'}, {'Test Case ID': 'US4_TC7', 'EPIC': 'Household Management', 'Feature': 'Household Composition API', 'User Story': 'US4', 'Business Process': 'Eligibility Assessment', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Create/Update Household Composition', 'Test Scenario Title': 'API rejects incomplete/invalid household composition submission', 'Precondition': 'API is accessible', 'Test Data': "{ household_id: 123, members: [{dob: '1982-05-23', relationship: 'Spouse'}] }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Send POST or PUT request to /api/household-compositions with incomplete member data'], 'Expected Result': "API responds with 400 Bad Request and validation message specifying missing 'name' field.", 'Dependent Module/Process': 'API Validation'}]</t>
+          <t>[{'Test Case ID': '4.1', 'EPIC': 'Household Management', 'Feature': 'Household Composition Capture', 'User Story': '4', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Household Data Entry', 'Activity Title': 'Add Household Member', 'Test Scenario Title': 'Successfully add a new household member with all required data', 'Precondition': 'Case Worker is logged in and has access permissions; client case is open.', 'Test Data': {'Full Name': 'Jane Doe', 'DOB': '2015-05-05', 'Relationship': 'Child', 'Gender': 'F'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Navigate to the Household Composition section of the client's record.", "Click 'Add Member'.", 'Enter all required fields (Full Name, DOB, Relationship, Gender).', "Click 'Save'."], 'Expected Result': 'The new household member is displayed in the household list and relationship is correctly captured.', 'Dependent Module/Process': 'Eligibility Calculation'}, {'Test Case ID': '4.2', 'EPIC': 'Household Management', 'Feature': 'Household Composition Capture', 'User Story': '4', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Household Data Edit', 'Activity Title': 'Edit Household Member', 'Test Scenario Title': 'Edit data for an existing household member', 'Precondition': 'At least one household member is recorded.', 'Test Data': {'Full Name': 'Jane Doe', 'DOB': '2015-05-05', 'Relationship': 'Stepchild'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select an existing household member from the list.', "Click 'Edit'.", 'Modify the Relationship field.', "Click 'Save'."], 'Expected Result': 'Household member’s relationship is updated; change is logged for audit.', 'Dependent Module/Process': 'Audit Log, Eligibility Calculation'}, {'Test Case ID': '4.3', 'EPIC': 'Household Management', 'Feature': 'Household Composition Capture', 'User Story': '4', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Validation', 'Activity Title': 'Validate Required Fields', 'Test Scenario Title': 'Attempt to add household member with missing required data', 'Precondition': 'Case Worker is on the Add Member form.', 'Test Data': {'Full Name': '', 'DOB': '2012-03-01', 'Relationship': 'Child'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Leave 'Full Name' blank.", 'Enter other required fields.', "Click 'Save'."], 'Expected Result': 'System displays a validation error indicating the missing field and prevents saving.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': '4.4', 'EPIC': 'Household Management', 'Feature': 'Household Composition Capture', 'User Story': '4', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Review', 'Activity Title': 'View Household Summary', 'Test Scenario Title': 'View and verify accuracy of household composition', 'Precondition': 'Multiple household members exist.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to household summary page.', 'Review all listed members and their relationships.'], 'Expected Result': 'All household information is accurate and up-to-date.', 'Dependent Module/Process': 'Eligibility Calculation'}, {'Test Case ID': '4.5', 'EPIC': 'Household Management', 'Feature': 'Compliance and Audit Trail', 'User Story': '4', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Audit Compliance', 'Activity Title': 'Review Audit Log', 'Test Scenario Title': 'Check that all edits and additions are logged for audit purposes', 'Precondition': 'At least one add/edit household action performed.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Compliance Officer', 'Detailed Test Steps': ['Access audit log for a client case.', 'Review recent household composition changes.'], 'Expected Result': 'Audit log shows date/time, user, and details of all changes.', 'Dependent Module/Process': 'Audit Log'}]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>This user story provides a means for Case Workers to identify and manage incomplete applications by flagging missing fields and documents, ensuring quicker follow-up and higher compliance rates.</t>
+          <t>This story ensures Case Workers can quickly identify and follow up on incomplete applications. The system must validate data entry, highlight missing fields and required documents, and support compliance through audit logs for follow-up actions.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to flag incomplete applications so that I can follow up with applicants. - System should highlight missing fields and documents.</t>
+          <t>As a Case Worker, I want to flag incomplete applications so that I can follow up with applicants.
+- System should highlight missing fields and documents.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Case Worker reviews an application, system highlights missing fields/documents, Case Worker flags the application as incomplete, system updates application status for follow-up.</t>
+          <t>Case Worker reviews an application, missing fields are clearly identified and flagged, and incomplete applications can be tracked and followed up consistently.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US5_TC1', 'Brief Description': 'System auto-highlights incomplete applications (happy path)'}, {'Test Case ID': 'US5_TC2', 'Brief Description': 'Flag application as incomplete and initiate follow-up'}, {'Test Case ID': 'US5_TC3', 'Brief Description': 'Verify application with all fields and documents is not flagged'}, {'Test Case ID': 'US5_TC4', 'Brief Description': 'Attempt to flag application already marked complete (negative)'}, {'Test Case ID': 'US5_TC5', 'Brief Description': 'API: Retrieve list of incomplete applications'}, {'Test Case ID': 'US5_TC6', 'Brief Description': 'Permissions: Verify only Case Worker role can flag incomplete'}]</t>
+          <t>[{'Test Case ID': '5.1', 'Brief Description': 'Submit application with all fields and documents completed.'}, {'Test Case ID': '5.2', 'Brief Description': 'Attempt to submit application with missing required fields (negative).'}, {'Test Case ID': '5.3', 'Brief Description': 'Attempt to submit application with missing required documents (negative).'}, {'Test Case ID': '5.4', 'Brief Description': 'View list of flagged incomplete applications.'}, {'Test Case ID': '5.5', 'Brief Description': 'Check audit trail for application status changes.'}]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US5_TC1', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Field/Document Validation', 'Activity Title': 'Highlight Incomplete Fields/Docs', 'Test Scenario Title': 'System automatically detects and highlights missing fields/documents', 'Precondition': 'Application submitted with missing information (e.g., missing income proof)', 'Test Data': 'Application ID: 456, Document: Proof of income (missing), Field: Address (blank)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Navigate to Application ID: 456', 'Observe highlighted missing fields/documents on application page'], 'Expected Result': 'System visually highlights missing required fields and documents.', 'Dependent Module/Process': 'Validation Rules/Document Upload'}, {'Test Case ID': 'US5_TC2', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Mark and Follow-Up', 'Activity Title': 'Flag Incomplete Application', 'Test Scenario Title': 'Case Worker flags application as incomplete and initiates follow-up', 'Precondition': 'Incomplete application identified', 'Test Data': 'Application ID: 457', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["On incomplete application screen, click 'Flag as Incomplete'", 'Select reason for incompleteness from drop-down', 'Enter notes for follow-up', 'Save changes'], 'Expected Result': "Application status updated to 'Incomplete'; flagged for follow-up; appropriate audit trail generated.", 'Dependent Module/Process': 'Audit, Workflow'}, {'Test Case ID': 'US5_TC3', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Field/Document Validation', 'Activity Title': 'Flag Review', 'Test Scenario Title': 'Verify system does not flag complete application', 'Precondition': 'Application with all required information and documents submitted', 'Test Data': 'Application ID: 458; all fields provided', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open complete application (ID:458)', 'Verify that no fields or document sections are flagged as incomplete'], 'Expected Result': 'No highlighting or incomplete status is shown for the application.', 'Dependent Module/Process': 'Validation Rules'}, {'Test Case ID': 'US5_TC4', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Mark and Follow-Up', 'Activity Title': 'Invalid Flag Action', 'Test Scenario Title': "Attempt to flag application already marked 'Complete'", 'Precondition': "Application status is 'Complete'", 'Test Data': 'Application ID: 459', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to flag completed application (ID: 459) as incomplete'], 'Expected Result': 'System prevents action and displays appropriate error message.', 'Dependent Module/Process': 'Status Management'}, {'Test Case ID': 'US5_TC5', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management API', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Fetch Incomplete Applications', 'Test Scenario Title': 'API returns all incomplete applications assigned to the case worker', 'Precondition': 'API is accessible and applications exist', 'Test Data': 'GET /api/applications?status=incomplete', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Send GET request to /api/applications?status=incomplete'], 'Expected Result': 'API responds with list of all incomplete applications for the user.', 'Dependent Module/Process': 'API'}, {'Test Case ID': 'US5_TC6', 'EPIC': 'Application Processing', 'Feature': 'Incomplete Application Management', 'User Story': 'US5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Role-based Action', 'Test Scenario Title': 'Only case workers can flag incomplete applications', 'Precondition': 'Other roles (e.g., Applicant) can access application view', 'Test Data': 'Role: Applicant; Application ID: 460', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ["Login as 'Applicant'", 'View own application (ID: 460)', "Attempt to flag as 'Incomplete'"], 'Expected Result': 'Flagging option is not visible or action is blocked for non-case workers.', 'Dependent Module/Process': 'Role Permissions'}]</t>
+          <t>[{'Test Case ID': '5.1', 'EPIC': 'Application Management', 'Feature': 'Application Completeness Validation', 'User Story': '5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Data Entry Validation', 'Activity Title': 'Submit Complete Application', 'Test Scenario Title': 'Successfully submit an application with all fields and documents provided', 'Precondition': 'Case Worker is logged in; all information is gathered.', 'Test Data': {'Fields Completed': 'All', 'Documents Uploaded': 'All'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Fill in all required fields on the application form.', 'Upload all required documents.', 'Submit the application.'], 'Expected Result': 'Application submission succeeds; no missing field or document warnings are displayed.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': '5.2', 'EPIC': 'Application Management', 'Feature': 'Application Completeness Validation', 'User Story': '5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Field Validation', 'Activity Title': 'Validation of Required Fields', 'Test Scenario Title': 'Application submission with missing required fields', 'Precondition': 'Application is partially filled.', 'Test Data': {'Fields Completed': 'Some', 'Documents Uploaded': 'All'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Leave one or more required fields empty.', 'Upload all required documents.', 'Submit the application.'], 'Expected Result': 'System highlights the missing fields, displays an error message, and prevents submission.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': '5.3', 'EPIC': 'Application Management', 'Feature': 'Application Completeness Validation', 'User Story': '5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Validation', 'Activity Title': 'Validation of Required Documents', 'Test Scenario Title': 'Application submission with missing required documents', 'Precondition': 'All fields are filled, but not all documents uploaded.', 'Test Data': {'Fields Completed': 'All', 'Documents Uploaded': 'Some'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Complete all required fields.', 'Omit one or more required documents.', 'Submit the application.'], 'Expected Result': 'System highlights the missing documents, displays an error message, and prevents submission.', 'Dependent Module/Process': 'Document Management, Validation Engine'}, {'Test Case ID': '5.4', 'EPIC': 'Application Management', 'Feature': 'Application Tracking', 'User Story': '5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Application Monitoring', 'Activity Title': 'View Flagged Applications', 'Test Scenario Title': 'View and filter applications flagged as incomplete', 'Precondition': 'At least one incomplete application is in the system.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in and navigate to the application tracking dashboard.', 'Filter or search for flagged/incomplete applications.'], 'Expected Result': 'All incomplete/flagged applications are listed with highlighted missing information.', 'Dependent Module/Process': 'Reporting'}, {'Test Case ID': '5.5', 'EPIC': 'Application Management', 'Feature': 'Compliance and Audit Trail', 'User Story': '5', 'Business Process': 'Application Review', 'Sub-Process Title': 'Audit Compliance', 'Activity Title': 'Review Application Status Changes', 'Test Scenario Title': 'Audit trail logs all status changes and flagging actions', 'Precondition': 'Application status has changed due to flagging.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Compliance Officer', 'Detailed Test Steps': ['Access audit log for a flagged application.', 'Review all status change events, including user and timestamps.'], 'Expected Result': 'Audit log records all flag and status changes for regulatory/audit review.', 'Dependent Module/Process': 'Audit Log'}]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>This user story enables Case Managers to monitor client eligibility status and renewal timelines using a dashboard to support proactive service planning and compliance. The dashboard must accurately reflect real-time data per role-based access standards.</t>
+          <t>This story enables Case Managers to efficiently plan client services by viewing up-to-date eligibility statuses and renewal dates for all clients via a dashboard, following all privacy, data security, and audit requirements.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to view the eligibility status of my clients so that I can plan services accordingly. - Dashboard showing eligibility status and renewal dates.</t>
+          <t>As a Case Manager, I want to view the eligibility status of my clients so that I can plan services accordingly.
+- Dashboard showing eligibility status and renewal dates.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Case Manager accesses dashboard, sees the list of clients with current eligibility status and renewal dates, enabling clear planning of follow-up actions.</t>
+          <t>Case Manager logs in and sees an accurate, real-time dashboard of all assigned clients with their eligibility status and date of eligibility renewal.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US6_TC1', 'Brief Description': 'Dashboard displays eligibility status and renewal dates for all assigned clients (happy path)'}, {'Test Case ID': 'US6_TC2', 'Brief Description': 'Status and renewal information updates in real-time as eligibility changes (integration)'}, {'Test Case ID': 'US6_TC3', 'Brief Description': 'Access denied for unauthorized user roles (permissions compliance)'}, {'Test Case ID': 'US6_TC4', 'Brief Description': 'API: Retrieve eligibility status list for clients'}, {'Test Case ID': 'US6_TC5', 'Brief Description': 'Dashboard filters clients by eligibility status'}, {'Test Case ID': 'US6_TC6', 'Brief Description': 'Dashboard includes audit trail for eligibility changes (compliance/audit)'}]</t>
+          <t>[{'Test Case ID': '6.1', 'Brief Description': 'View dashboard with current eligibility status and renewal dates for multiple clients.'}, {'Test Case ID': '6.2', 'Brief Description': 'Verify data refresh on dashboard after an eligibility status change (integration).'}, {'Test Case ID': '6.3', 'Brief Description': 'Case Manager without permissions attempts to access dashboard (negative).'}, {'Test Case ID': '6.4', 'Brief Description': 'Ensure compliance: all dashboard views are audit-logged and PII is protected.'}]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US6_TC1', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Eligibility Overview', 'Activity Title': 'Eligibility Display', 'Test Scenario Title': 'Dashboard displays eligibility status and renewal dates for all assigned clients', 'Precondition': 'Case Manager assigned clients with eligibility data', 'Test Data': 'Clients: [Mark Lee, Status: Eligible, Renewal: 2024-08-10]; [Ella Green, Status: Ineligible, Renewal: 2025-02-01]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager', "Open 'Eligibility Dashboard'", 'Review client list with status and renewal columns'], 'Expected Result': 'Dashboard lists all assigned clients with accurate status and renewal dates.', 'Dependent Module/Process': 'Eligibility Determination'}, {'Test Case ID': 'US6_TC2', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Real-time Update', 'Activity Title': 'Status Refresh', 'Test Scenario Title': 'Eligibility status and renewal date reflect in dashboard real-time when updated', 'Precondition': 'Eligibility update occurs for a client', 'Test Data': 'Client: Mark Lee; Original status: Eligible; Renewal: 2024-08-10; Update to Ineligible', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Trigger eligibility update for Mark Lee (via back-end or UI)', 'Refresh dashboard as Case Manager'], 'Expected Result': 'Dashboard instantly shows new eligibility status and correct renewal date.', 'Dependent Module/Process': 'Eligibility Engine, Dashboard'}, {'Test Case ID': 'US6_TC3', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Role Permissions', 'Activity Title': 'Unauthorized Access', 'Test Scenario Title': 'Access denied for unauthorized roles', 'Precondition': 'User with non-Case Manager role (e.g., Applicant, Case Worker) attempts access', 'Test Data': 'User Role: Applicant', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Log in as Applicant', "Attempt to navigate to 'Eligibility Dashboard'"], 'Expected Result': "System denies access with message 'Access Denied' or redirects user.", 'Dependent Module/Process': 'Role-Based Access Control'}, {'Test Case ID': 'US6_TC4', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard API', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'API Interaction', 'Activity Title': 'Fetch Client Status', 'Test Scenario Title': 'API endpoint returns eligibility status and renewal dates for assigned clients', 'Precondition': 'Case Manager with client assignments, API authentication', 'Test Data': 'GET /api/clients/eligibility?manager_id=789', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Integration', 'Detailed Test Steps': ['Call API with case manager credentials'], 'Expected Result': 'API response lists each client and includes eligibility status and renewal date fields.', 'Dependent Module/Process': 'API, Eligibility Service'}, {'Test Case ID': 'US6_TC5', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Dashboard Filtering', 'Activity Title': 'Filter Eligibility', 'Test Scenario Title': 'Dashboard client list filters by eligibility status', 'Precondition': 'Dashboard displays client list', 'Test Data': 'Statuses: [Eligible, Ineligible, Renewal Due]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open dashboard', "Select filter 'Eligible'", 'Verify only eligible clients are shown'], 'Expected Result': 'Filtered client list matches selected eligibility status.', 'Dependent Module/Process': 'Dashboard Filtering'}, {'Test Case ID': 'US6_TC6', 'EPIC': 'Eligibility Tracking', 'Feature': 'Eligibility Dashboard', 'User Story': 'US6', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Track Eligibility Changes', 'Test Scenario Title': 'Eligibility dashboard records audit trail entries for status changes', 'Precondition': 'Eligibility status updated for a client by authorized process/user', 'Test Data': 'Client: Ella Green, Status before: Eligible, after: Ineligible', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Update eligibility status for Ella Green', 'Review audit trail/log for corresponding dashboard entry'], 'Expected Result': 'Audit log entry created with user, timestamp, previous and new status. Traceable for compliance.', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
+          <t>[{'Test Case ID': '6.1', 'EPIC': 'Eligibility Planning', 'Feature': 'Eligibility Dashboard', 'User Story': '6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Eligibility Review', 'Activity Title': 'View Client Eligibility Status', 'Test Scenario Title': 'Dashboard displays eligibility statuses and renewal dates for assigned clients', 'Precondition': 'Case Manager is assigned clients and logged into the system.', 'Test Data': {'Clients': [{'Name': 'Sam Lee', 'Eligibility Status': 'Active', 'Renewal Date': '2024-09-01'}, {'Name': 'Alex Chen', 'Eligibility Status': 'Pending', 'Renewal Date': '2024-07-15'}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to the eligibility dashboard.', 'Review listed clients, their eligibility status, and renewal dates.'], 'Expected Result': 'Dashboard displays a list of assigned clients with accurate eligibility status and renewal dates.', 'Dependent Module/Process': 'Eligibility Engine, Data Warehouse'}, {'Test Case ID': '6.2', 'EPIC': 'Eligibility Planning', 'Feature': 'Eligibility Dashboard', 'User Story': '6', 'Business Process': 'Service Planning', 'Sub-Process Title': 'Eligibility Maintenance', 'Activity Title': 'Dashboard Data Refresh', 'Test Scenario Title': 'Dashboard updates when a client’s eligibility status changes', 'Precondition': 'Eligibility status of a client changes in backend system.', 'Test Data': {'Client': 'Alex Chen', 'Old Status': 'Pending', 'New Status': 'Active'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Change eligibility status in backend/admin tool.', 'Refresh the eligibility dashboard as Case Manager.'], 'Expected Result': 'Dashboard reflects updated eligibility status ("Active") and maintains correct renewal date.', 'Dependent Module/Process': 'Eligibility Engine, API Gateway'}, {'Test Case ID': '6.3', 'EPIC': 'Eligibility Planning', 'Feature': 'Eligibility Dashboard', 'User Story': '6', 'Business Process': 'Security and Permissions', 'Sub-Process Title': 'Role Validation', 'Activity Title': 'Access Control', 'Test Scenario Title': 'Case Manager without permissions attempts dashboard access', 'Precondition': "User does not have 'Case Manager' role.", 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Other Staff', 'Detailed Test Steps': ['Log in as a user without Case Manager permissions.', 'Attempt to access the eligibility dashboard.'], 'Expected Result': 'Access denied, dashboard is not shown; security event is logged.', 'Dependent Module/Process': 'Access Control, Audit Log'}, {'Test Case ID': '6.4', 'EPIC': 'Eligibility Planning', 'Feature': 'Eligibility Dashboard', 'User Story': '6', 'Business Process': 'Compliance', 'Sub-Process Title': 'PII Protection and Audit', 'Activity Title': 'Audit Log and Privacy Review', 'Test Scenario Title': 'Audit each dashboard view/access and ensure PII is masked/protected', 'Precondition': 'PII data is displayed on dashboard; logging enabled.', 'Test Data': {'Client': 'Sam Lee', 'Eligibility Status': 'Active'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Compliance Officer', 'Detailed Test Steps': ['Access the audit log after dashboard view events.', 'Review that all user access to PII is logged with date/time/user.', 'Verify no unmasked PII appears in logs, screens, or exports.'], 'Expected Result': 'All dashboard access is logged for audit; PII exposure complies with relevant data privacy regulations.', 'Dependent Module/Process': 'Audit Log, Data Privacy Module'}]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>This user story ensures that Case Managers receive timely, system-generated alerts when a client's eligibility is about to expire, enabling proactive redeterminations and service continuity.</t>
+          <t>This user story ensures that Case Managers receive timely, system-generated alerts 30 days prior to a client's eligibility expiration, enabling timely redetermination and compliance with eligibility management requirements.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -630,24 +633,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>When a client's eligibility is 30 days from expiration, the system automatically generates and delivers an alert to the assigned Case Manager.</t>
+          <t>When a client's eligibility is set to expire in 30 days, the system automatically sends an alert to the assigned Case Manager, who is then able to access details and initiate the redetermination process.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_07_01', 'Brief Description': 'System sends alert to Case Manager 30 days before eligibility expiration.'}, {'Test Case ID': 'TC_07_02', 'Brief Description': 'Verify no alert is sent if no eligibility is expiring within 30 days.'}, {'Test Case ID': 'TC_07_03', 'Brief Description': 'Case Manager receives only relevant alerts (permission check).'}, {'Test Case ID': 'TC_07_04', 'Brief Description': 'System does not duplicate alerts for the same case.'}, {'Test Case ID': 'TC_07_05', 'Brief Description': 'Audit log of alert generation and delivery is maintained.'}]</t>
+          <t>[{'Test Case ID': 'US7_TC1', 'Brief Description': 'System generates alert for clients 30 days before eligibility expiration (happy path).'}, {'Test Case ID': 'US7_TC2', 'Brief Description': 'No alert generated if eligibility expiration is more than 30 days away (negative).'}, {'Test Case ID': 'US7_TC3', 'Brief Description': 'No alert generated if eligibility has already expired (negative).'}, {'Test Case ID': 'US7_TC4', 'Brief Description': 'Alert is only sent to assigned Case Manager, not unassigned users (permissions).'}, {'Test Case ID': 'US7_TC5', 'Brief Description': 'Multiple alerts are not sent for the same client (compliance/audit).'}]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_07_01', 'EPIC': 'Case Eligibility Management', 'Feature': 'Notifications &amp; Alerts', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'System Notification', 'Activity Title': 'Generate Eligibility Expiration Alert', 'Test Scenario Title': 'Happy Path: Alert generated and delivered', 'Precondition': 'Client eligibility record exists with an expiration date 30 days in the future; Case Manager is assigned.', 'Test Data': "{ 'client_id': '12345', 'eligibility_expiry': '2024-07-30', 'case_manager_id': 'CM_01'}", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["Set a client's eligibility expiration to 30 days in the future.", 'Wait for system batch job/cron to process expiration checks.', 'Login as assigned Case Manager.', 'Navigate to alert dashboard/inbox.'], 'Expected Result': "Alert regarding client's upcoming eligibility expiration is visible to the Case Manager.", 'Dependent Module/Process': 'Eligibility Management, Notification Service'}, {'Test Case ID': 'TC_07_02', 'EPIC': 'Case Eligibility Management', 'Feature': 'Notifications &amp; Alerts', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'System Notification', 'Activity Title': 'Filter Expiry Dates', 'Test Scenario Title': 'No alert for ineligible records', 'Precondition': 'All eligibility expiration dates are more than 30 days away.', 'Test Data': "{ 'client_id': '54321', 'eligibility_expiry': '2024-09-01', 'case_manager_id': 'CM_02'}", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Set all client records to have expiration &gt;30 days from today.', 'Wait for system batch job/cron.', 'Login as Case Manager.', 'Check for alerts.'], 'Expected Result': 'No new alerts are generated for eligibility expiration.', 'Dependent Module/Process': 'Eligibility Management, Notification Service'}, {'Test Case ID': 'TC_07_03', 'EPIC': 'Case Eligibility Management', 'Feature': 'Permissions', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'Security and Permissions', 'Activity Title': 'Alert Access Restriction', 'Test Scenario Title': 'Only assigned Case Manager receives alert', 'Precondition': 'Multiple Case Managers exist; one is assigned to client.', 'Test Data': "{ 'client_id': '202303', 'eligibility_expiry': '2024-07-30', 'case_manager_id': 'CM_01', 'other_manager_id': 'CM_03' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign client to Manager A.', 'Wait for alert generation.', 'Log in as Manager A: Check for alert.', 'Log in as Manager B: Check for alert.'], 'Expected Result': 'Only assigned Case Manager (Manager A) receives the alert; others do not.', 'Dependent Module/Process': 'User Management'}, {'Test Case ID': 'TC_07_04', 'EPIC': 'Case Eligibility Management', 'Feature': 'Notifications &amp; Alerts', 'User Story': '7', 'Business Process': 'Eligibility Redetermination', 'Sub-Process Title': 'System Notification', 'Activity Title': 'Alert Deduplication', 'Test Scenario Title': 'No duplicate alerts for same case', 'Precondition': 'Eligibility expiration date is not changed repeatedly.', 'Test Data': "{ 'client_id': '303404', 'eligibility_expiry': '2024-07-30', 'case_manager_id': 'CM_04' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Trigger alert generation.', 'Check alert history for the case.', 'Trigger cycle again without changing expiry date.', 'Check if additional alert is sent.'], 'Expected Result': 'Only one alert is sent per case for a given eligibility expiration date.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_07_05', 'EPIC': 'Case Eligibility Management', 'Feature': 'Compliance', 'User Story': '7', 'Business Process': 'Audit &amp; Reporting', 'Sub-Process Title': 'Logging', 'Activity Title': 'Alert Audit Trail', 'Test Scenario Title': 'Audit log of alert', 'Precondition': 'Alerts are being generated.', 'Test Data': "{ 'alert_id': 'A991', 'case_manager_id': 'CM_05', 'timestamp': '2024-06-01T09:30:00Z' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Trigger alert.', 'Access audit logs.', 'Verify alert generation and delivery is recorded.'], 'Expected Result': 'Alert event is traceable with timestamp, alert type, recipient, and client reference in audit log.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}]</t>
+          <t>[{'Test Case ID': 'US7_TC1', 'EPIC': 'Eligibility Management', 'Feature': 'Eligibility Expiry Alerts', 'User Story': 'US7', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Send Expiry Alert', 'Test Scenario Title': 'Generate alert 30 days before eligibility expiration', 'Precondition': "Client's eligibility expiration date is within 30 days; Case Manager is assigned to the client.", 'Test Data': 'Client record with eligibility expiring in 30 days', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Log in as Case Manager.', '2. Ensure client eligibility expiration is set 30 days from today.', '3. Trigger alert generation process (automated/scheduled job).', '4. Check Case Manager notifications.'], 'Expected Result': 'System sends a notification/alert to the Case Manager about the pending eligibility expiration.', 'Dependent Module/Process': 'Notification System'}, {'Test Case ID': 'US7_TC2', 'EPIC': 'Eligibility Management', 'Feature': 'Eligibility Expiry Alerts', 'User Story': 'US7', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Prevent premature alerts', 'Test Scenario Title': 'Do not generate alerts when eligibility expiration is more than 30 days away', 'Precondition': "Client's eligibility expiration date is more than 30 days from today.", 'Test Data': 'Client record with eligibility expiring in 45 days', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Log in as Case Manager.', '2. Verify eligibility expiration date is set beyond 30 days.', '3. Trigger alert generation process.', '4. Check notifications.'], 'Expected Result': 'No alert is generated and no notification is sent.', 'Dependent Module/Process': 'Notification System'}, {'Test Case ID': 'US7_TC3', 'EPIC': 'Eligibility Management', 'Feature': 'Eligibility Expiry Alerts', 'User Story': 'US7', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Prevent expired alerts', 'Test Scenario Title': 'Ensure no alerts for already expired eligibility', 'Precondition': "Client's eligibility expiration date has already passed.", 'Test Data': 'Client record with expired eligibility', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Log in as Case Manager.', '2. Review expired client eligibility.', '3. Trigger alert generation process.', '4. Check notifications.'], 'Expected Result': 'No alert is generated for already expired eligibility.', 'Dependent Module/Process': 'Notification System'}, {'Test Case ID': 'US7_TC4', 'EPIC': 'Eligibility Management', 'Feature': 'Eligibility Expiry Alerts', 'User Story': 'US7', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'User Permissions for Alerts', 'Test Scenario Title': 'Alert is delivered only to assigned Case Manager', 'Precondition': 'A client is assigned to a Case Manager.', 'Test Data': 'Assignment data mapping client to specific Case Manager', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Other Users', 'Detailed Test Steps': ['1. Assign client with expiring eligibility to Case Manager A.', '2. Trigger alert generation process.', '3. Check notifications for Case Manager A and other users.'], 'Expected Result': 'Only the assigned Case Manager receives the alert notification.', 'Dependent Module/Process': 'User Role/Permissions, Notification System'}, {'Test Case ID': 'US7_TC5', 'EPIC': 'Eligibility Management', 'Feature': 'Eligibility Expiry Alerts', 'User Story': 'US7', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Multiple Alerts Prevention', 'Test Scenario Title': 'No duplicate alerts sent for same client within 30-day window', 'Precondition': 'Alert has already been generated once for the 30-day window.', 'Test Data': 'Client record with eligibility within 30 days; alert log includes existing alert record', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Confirm alert has been sent for a client 30 days before expiration.', '2. Trigger alert generation process again during the 30-day window.', '3. Check notification and system logs.'], 'Expected Result': 'No additional/duplicate alerts are sent for the same client within the alert period.', 'Dependent Module/Process': 'Notification System, Audit/Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>This user story focuses on enabling Case Workers to upload various supporting documents (PDF, images, scans) to a client's case, ensuring comprehensive and compliant record-keeping.</t>
+          <t>This user story ensures that Case Workers can upload various types of supporting documents (PDFs, images, scanned files) to case files, supporting full documentation compliance.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,24 +660,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A Case Worker successfully uploads a PDF, image, or scanned file to an assigned case file, and the documents become accessible via the client's record.</t>
+          <t>Case Worker uploads a valid PDF, image, or scanned document which is correctly attached to the client's record, ensuring the case file is complete and retrievable.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_08_01', 'Brief Description': 'Case Worker uploads a supported document (PDF, image, scan) to a case.'}, {'Test Case ID': 'TC_08_02', 'Brief Description': 'Attempt to upload an unsupported file type.'}, {'Test Case ID': 'TC_08_03', 'Brief Description': 'Case Worker with insufficient permissions tries to upload a document.'}, {'Test Case ID': 'TC_08_04', 'Brief Description': 'Uploaded document is linked to the correct case and visible for audit.'}, {'Test Case ID': 'TC_08_05', 'Brief Description': 'Data privacy and compliance validation for file upload and storage.'}]</t>
+          <t>[{'Test Case ID': 'US8_TC1', 'Brief Description': 'Upload supported file types (PDF, JPG, PNG, scanned images) to case file (happy path).'}, {'Test Case ID': 'US8_TC2', 'Brief Description': 'Fail to upload unsupported file types (e.g., .exe, .zip) (negative).'}, {'Test Case ID': 'US8_TC3', 'Brief Description': 'Upload with missing, corrupted, or empty file (negative).'}, {'Test Case ID': 'US8_TC4', 'Brief Description': 'Verify file access is restricted to permitted users only (permissions/compliance).'}, {'Test Case ID': 'US8_TC5', 'Brief Description': 'Audit log is updated with upload action for compliance.'}]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_08_01', 'EPIC': 'Case Document Management', 'Feature': 'File Upload', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Upload Supported Documents', 'Test Scenario Title': 'Happy Path: Supported document upload', 'Precondition': 'Case Worker is assigned to an active case; case file exists.', 'Test Data': "{ 'case_id': 'C123', 'user_id': 'CW_01', 'file': 'income_verification.pdf' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to assigned client's case file.", "Click 'Upload Document'.", 'Select a supported file (e.g., income_verification.pdf).', "Click 'Submit'."], 'Expected Result': "File is uploaded, linked to case, visible in client's documents.", 'Dependent Module/Process': 'Document Storage, Case Management'}, {'Test Case ID': 'TC_08_02', 'EPIC': 'Case Document Management', 'Feature': 'File Upload', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Reject Unsupported File Type', 'Test Scenario Title': 'Negative: Unsupported file type upload', 'Precondition': 'Case Worker tries to upload .exe file.', 'Test Data': "{ 'case_id': 'C124', 'user_id': 'CW_01', 'file': 'malware.exe' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to case file.', "Click 'Upload Document'.", 'Select file with unsupported extension (malware.exe).', "Click 'Submit'."], 'Expected Result': 'System prevents upload; error message displayed.', 'Dependent Module/Process': 'File Validation'}, {'Test Case ID': 'TC_08_03', 'EPIC': 'Case Document Management', 'Feature': 'Permissions', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict Upload Permissions', 'Test Scenario Title': 'Negative: Insufficient permissions', 'Precondition': 'User with read-only role accesses case.', 'Test Data': "{ 'case_id': 'C125', 'user_id': 'CW_ReadOnly' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker (read-only)', 'Detailed Test Steps': ['Login as Case Worker (read-only).', 'Navigate to case file.', "Check for presence of 'Upload Document' button."], 'Expected Result': "'Upload Document' button not present or access is denied on upload attempt.", 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'TC_08_04', 'EPIC': 'Case Document Management', 'Feature': 'Compliance &amp; Traceability', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Audit', 'Activity Title': 'Record Upload in Audit Log', 'Test Scenario Title': 'Document audit logging', 'Precondition': 'File uploaded successfully.', 'Test Data': "{ 'case_id': 'C126', 'user_id': 'CW_02', 'file': 'residence_proof.jpg' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Upload a document as Case Worker.', 'Access audit logs.', 'Search for the upload event.'], 'Expected Result': 'Audit log lists the file upload with timestamp, user, and case reference.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC_08_05', 'EPIC': 'Case Document Management', 'Feature': 'Compliance', 'User Story': '8', 'Business Process': 'Case Maintenance', 'Sub-Process Title': 'Data Privacy', 'Activity Title': 'Validate Upload Security', 'Test Scenario Title': 'Compliance and secure storage', 'Precondition': 'System configured for compliance (e.g., HIPAA).', 'Test Data': "{ 'case_id': 'C127', 'user_id': 'CW_03', 'file': 'medical_record.pdf' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Upload a sensitive document.', 'Attempt unauthorized access to the document.', 'Review encryption in storage.', 'Check compliance policy audit report.'], 'Expected Result': 'Only authorized users access the document; document is encrypted as per policy and access recorded in logs.', 'Dependent Module/Process': 'Security, Compliance Engine, Audit Logging'}]</t>
+          <t>[{'Test Case ID': 'US8_TC1', 'EPIC': 'Case Documentation', 'Feature': 'Document Upload', 'User Story': 'US8', 'Business Process': 'Case File Management', 'Sub-Process Title': 'Attach Document', 'Activity Title': 'Upload Supported Files', 'Test Scenario Title': 'Upload allowed document types', 'Precondition': 'User is authenticated and has write access to the case file.', 'Test Data': 'Sample PDF, JPG, PNG, scanned TIFF files', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker.', "2. Navigate to client's case file.", "3. Click 'Upload Document'.", '4. Select each supported file type in turn (PDF, JPG, PNG, TIFF).', '5. Confirm upload.'], 'Expected Result': "Each file is successfully uploaded and listed in the client's case file with proper metadata.", 'Dependent Module/Process': 'File Storage, Case Management System'}, {'Test Case ID': 'US8_TC2', 'EPIC': 'Case Documentation', 'Feature': 'Document Upload', 'User Story': 'US8', 'Business Process': 'Case File Management', 'Sub-Process Title': 'Attach Document', 'Activity Title': 'Reject Unsupported Files', 'Test Scenario Title': 'Attempt upload of unsupported file types', 'Precondition': 'User is authenticated and has write access.', 'Test Data': 'Sample .exe, .zip, .bat files', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker.', "2. Navigate to client's case file upload dialog.", '3. Attempt to upload unsupported file types.'], 'Expected Result': 'System displays an error message; upload is not completed.', 'Dependent Module/Process': 'File Validation, Security'}, {'Test Case ID': 'US8_TC3', 'EPIC': 'Case Documentation', 'Feature': 'Document Upload', 'User Story': 'US8', 'Business Process': 'Case File Management', 'Sub-Process Title': 'File Validation', 'Activity Title': 'Handle Missing or Corrupt Files', 'Test Scenario Title': 'Attempt upload with invalid input (empty or corrupted file)', 'Precondition': 'User is authenticated.', 'Test Data': 'Empty file, corrupted PDF, incomplete image file', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in.', '2. Attempt upload with a zero-byte file.', '3. Attempt upload with a corrupted PDF.', '4. Attempt upload with incomplete image file.'], 'Expected Result': 'System shows error message describing upload failure. File is not attached to case.', 'Dependent Module/Process': 'File Validation'}, {'Test Case ID': 'US8_TC4', 'EPIC': 'Case Documentation', 'Feature': 'Document Upload', 'User Story': 'US8', 'Business Process': 'Case File Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'File Permission Enforcement', 'Test Scenario Title': 'Non-authorized roles cannot upload or view documents', 'Precondition': 'User does not have document upload or case access permission.', 'Test Data': 'N/A', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Other User Roles (e.g., Viewer)', 'Detailed Test Steps': ['1. Log in as a user without upload or view rights.', '2. Access the case file page.', '3. Attempt to upload or view documents.'], 'Expected Result': 'Upload and/or view options are disabled or inaccessible; system logs access attempt.', 'Dependent Module/Process': 'Authorization, Audit'}, {'Test Case ID': 'US8_TC5', 'EPIC': 'Case Documentation', 'Feature': 'Document Upload', 'User Story': 'US8', 'Business Process': 'Case File Management', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Record Upload Actions', 'Test Scenario Title': 'Audit log records file upload event', 'Precondition': 'User uploads file to case.', 'Test Data': 'Any supported document file', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Complete the file upload as in US8_TC1.', '2. Access the audit log as an admin or via API.', '3. Search for recent upload event.'], 'Expected Result': 'Audit trail contains accurate file upload metadata (user, timestamp, file type, case ID).', 'Dependent Module/Process': 'Audit/Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>This user story ensures Case Workers can efficiently search for existing applicants by name or SSN, utilizing fuzzy matching, to prevent duplicate entries and maintain data integrity.</t>
+          <t>This user story ensures the Case Worker can search for applicants by name or SSN, supporting fuzzy matching, to prevent duplicate records and improve case data integrity.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -684,854 +687,773 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Case Worker searches by name or SSN and receives relevant applicant records, including close/fuzzy matches, reducing the risk of duplicate entries.</t>
+          <t>Case Worker enters name or SSN in the search field. The system returns a relevant list of matching applicants, utilizing fuzzy matching to catch close matches and prevent duplicates.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_09_01', 'Brief Description': 'Search applicant by full name and receive expected results.'}, {'Test Case ID': 'TC_09_02', 'Brief Description': 'Search applicant by SSN and receive exact match results.'}, {'Test Case ID': 'TC_09_03', 'Brief Description': 'Fuzzy search returns partial or similar matches for misspelled names.'}, {'Test Case ID': 'TC_09_04', 'Brief Description': 'System prevents creation of duplicate applicant when a match is found.'}, {'Test Case ID': 'TC_09_05', 'Brief Description': 'Access control: Only authorized users can access applicant search functionality.'}]</t>
+          <t>[{'Test Case ID': 'US9_TC1', 'Brief Description': 'Search for an applicant by exact name/SSN returns correct results (happy path).'}, {'Test Case ID': 'US9_TC2', 'Brief Description': 'Search using fuzzy name matching returns similar results (functional/fuzzy).'}, {'Test Case ID': 'US9_TC3', 'Brief Description': 'Search returns no match for new/unique applicants (negative).'}, {'Test Case ID': 'US9_TC4', 'Brief Description': 'Unauthorized user cannot access applicant search (permissions).'}, {'Test Case ID': 'US9_TC5', 'Brief Description': 'APIs return appropriate results and handle invalid input (API/edge cases).'}]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_09_01', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Search by Name', 'Test Scenario Title': 'Full name search - happy path', 'Precondition': "Applicant 'John Smith' exists in system.", 'Test Data': "{ 'applicant_name': 'John Smith' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'Add Applicant' workflow.", "Enter full name 'John Smith' in search field.", 'Submit the search.'], 'Expected Result': "Applicant record for 'John Smith' appears in search results.", 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_09_02', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Search by SSN', 'Test Scenario Title': 'SSN search - happy path', 'Precondition': "Applicant with SSN '123-45-6789' exists.", 'Test Data': "{ 'ssn': '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'Add Applicant' workflow.", "Enter SSN '123-45-6789' in search field.", 'Submit the search.'], 'Expected Result': 'Applicant record appears with full details.', 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_09_03', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Fuzzy Search', 'Test Scenario Title': 'Partial/misspelled name returns fuzzy matches', 'Precondition': "Applicants with similar names exist (e.g., 'Jon Smyth').", 'Test Data': "{ 'applicant_name': 'Jonh Smit' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'Add Applicant'.", "Enter misspelled name 'Jonh Smit'.", 'Submit the search.'], 'Expected Result': "Search results include close matches like 'John Smith', 'Jon Smyth'.", 'Dependent Module/Process': 'Search Engine'}, {'Test Case ID': 'TC_09_04', 'EPIC': 'Applicant Management', 'Feature': 'Search Functionality', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Prevent Duplicate Creation', 'Test Scenario Title': 'Prevent duplicate when match exists', 'Precondition': 'Applicant with provided name or SSN exists.', 'Test Data': "{ 'applicant_name': 'John Smith', 'ssn': '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Search for applicant by SSN/name.', 'Try to create new applicant record with same details.'], 'Expected Result': 'System blocks creation, shows error about duplicate entry.', 'Dependent Module/Process': 'Applicant Database, Duplicate Check'}, {'Test Case ID': 'TC_09_05', 'EPIC': 'Applicant Management', 'Feature': 'Permissions', 'User Story': '9', 'Business Process': 'New Applicant Intake', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict Search Access', 'Test Scenario Title': 'Only authorized users can search applicants', 'Precondition': 'User is not in authorized role (e.g., guest).', 'Test Data': "{ 'user_id': 'Guest_01' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Not authorized', 'Detailed Test Steps': ['Login as unauthorized user.', 'Try to access applicant search screen.'], 'Expected Result': 'Applicant search functionality is not accessible.', 'Dependent Module/Process': 'User Role Management'}]</t>
+          <t>[{'Test Case ID': 'US9_TC1', 'EPIC': 'Applicant Data Integrity', 'Feature': 'Search Applicants', 'User Story': 'US9', 'Business Process': 'Applicant Screening', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Exact Search', 'Test Scenario Title': 'Return exact matches for name or SSN', 'Precondition': 'Applicant records exist with unique names/SSNs.', 'Test Data': 'Applicant: John Doe, SSN: 123-45-6789', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker.', '2. Navigate to applicant search page.', '3. Enter full name or full SSN and submit search.'], 'Expected Result': 'Applicant matching the exact search query is returned in the results.', 'Dependent Module/Process': 'Search Engine, Applicant DB'}, {'Test Case ID': 'US9_TC2', 'EPIC': 'Applicant Data Integrity', 'Feature': 'Search Applicants', 'User Story': 'US9', 'Business Process': 'Applicant Screening', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'Fuzzy Search', 'Test Scenario Title': 'Fuzzy matching returns close matches', 'Precondition': 'Similar applicant names or SSNs exist in the database.', 'Test Data': 'Applicant: Jon D, John Doe, Jonathan Doe, SSNs with minor variations.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker.', "2. Search with partial or slightly misspelled name ('Jon Doe', 'Jhn Doe').", '3. Search with SSN containing a typo.'], 'Expected Result': 'System returns list of similar or close matching applicants, suggesting possible duplicates.', 'Dependent Module/Process': 'Search Engine, Fuzzy Logic Module'}, {'Test Case ID': 'US9_TC3', 'EPIC': 'Applicant Data Integrity', 'Feature': 'Search Applicants', 'User Story': 'US9', 'Business Process': 'Applicant Screening', 'Sub-Process Title': 'Applicant Search', 'Activity Title': 'No Match Handling', 'Test Scenario Title': 'No results returned for unique/new queries', 'Precondition': 'Database does not have a matching applicant.', 'Test Data': "Name: 'Zyphus Quill', SSN: 999-99-9999", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in.', "2. Search by name 'Zyphus Quill' or SSN '999-99-9999'."], 'Expected Result': "System displays 'No applicants found' or similar message.", 'Dependent Module/Process': 'Search Engine'}, {'Test Case ID': 'US9_TC4', 'EPIC': 'Applicant Data Integrity', 'Feature': 'Search Applicants', 'User Story': 'US9', 'Business Process': 'Applicant Screening', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Access Control', 'Test Scenario Title': 'Non-authorized user access is denied', 'Precondition': 'User has no applicant search permission.', 'Test Data': 'N/A', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Viewer or other restricted role', 'Detailed Test Steps': ['1. Log in as non-Case Worker.', '2. Attempt to access applicant search page or API.'], 'Expected Result': 'Access is denied; an error or insufficient permissions message is displayed. Attempt is logged.', 'Dependent Module/Process': 'Authorization, Audit'}, {'Test Case ID': 'US9_TC5', 'EPIC': 'Applicant Data Integrity', 'Feature': 'Search Applicants (API)', 'User Story': 'US9', 'Business Process': 'Applicant Screening', 'Sub-Process Title': 'API Testing', 'Activity Title': 'Test Search API', 'Test Scenario Title': 'API returns correct search results and handles edge cases', 'Precondition': 'Search API is accessible.', 'Test Data': 'Exact, fuzzy, invalid, and blank search inputs', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'API Client (Case Worker context)', 'Detailed Test Steps': ['1. Send API request with correct name/SSN.', '2. Send API request with partial/fuzzy input.', '3. Send request with invalid data (e.g., invalid SSN format, empty request).', '4. Send request without proper authentication.'], 'Expected Result': 'API returns proper results, empty set, or error messages as appropriate; permissions are enforced.', 'Dependent Module/Process': 'API Layer, Search Engine, Auth'}]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>This user story focuses on enabling Case Managers to efficiently distribute cases among team members, ensuring workload balance and providing both automated assignment rules and manual override capabilities.</t>
+          <t>This user story focuses on enabling Case Managers to assign cases to team members according to workload, with both automated rules and manual override. This supports balanced case allocation and operational efficiency for the team.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to assign cases to team members based on workload so that we can balance responsibilities. - Case assignment rules and manual override options.</t>
+          <t>10: As a Case Manager, I want to assign cases to team members based on workload so that we can balance responsibilities. - Case assignment rules and manual override options.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Case Manager logs in, system suggests case assignments based on current team workload, Manager reviews and accepts the automated assignment, or manually overrides to reassign cases as needed.</t>
+          <t>Case Manager logs in, reviews unassigned cases, uses automated assignment (based on workload metrics), with option to manually override case-team member assignments; assignments update team member workload, and audit trail captures all changes.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_10_01', 'Brief Description': 'Automated assignment of new cases using workload rules'}, {'Test Case ID': 'TC_10_02', 'Brief Description': 'Manual override to assign or reassign a case'}, {'Test Case ID': 'TC_10_03', 'Brief Description': 'Error handling when a case is assigned to a non-existent team member'}, {'Test Case ID': 'TC_10_04', 'Brief Description': 'Validation of permissions for assignment and override'}]</t>
+          <t>[{'Test Case ID': 'TC10-1', 'Brief Description': 'Auto-assign case based on workload rules'}, {'Test Case ID': 'TC10-2', 'Brief Description': 'Manual override of auto-assignment'}, {'Test Case ID': 'TC10-3', 'Brief Description': 'Attempt to assign to inactive/overloaded member'}, {'Test Case ID': 'TC10-4', 'Brief Description': 'Verify audit log records all assignments and overrides'}, {'Test Case ID': 'TC10-5', 'Brief Description': 'API assignment endpoint validation'}, {'Test Case ID': 'TC10-6', 'Brief Description': 'Permission check: Only Case Manager can assign'}]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_10_01', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Automated Assignment', 'Test Scenario Title': 'System automatically assigns cases according to workload balancing rules', 'Precondition': 'Case Manager is logged in; at least one unassigned case exists; workload metrics available for all team members.', 'Test Data': '3 unassigned cases; team member workloads: Alice-5, Bob-2, Carol-3', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager navigates to unassigned cases view.', "Clicks 'Auto Assign' button.", 'System calculates current workloads for team members.', 'System assigns cases to team members with lowest workload.', 'Assignment details are displayed for review.'], 'Expected Result': 'Cases assigned to Bob (lowest workload first), followed by Carol, then Alice; assignment log updated.', 'Dependent Module/Process': 'Team member data; Case Management module'}, {'Test Case ID': 'TC_10_02', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Manual Override', 'Test Scenario Title': 'Case Manager manually overwrites a case assignment', 'Precondition': 'A case is already assigned to a team member.', 'Test Data': 'Case #123 assigned to Bob.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager selects Case #123.', "Clicks 'Reassign'.", 'Chooses Alice from the team list.', 'Confirms reassignment.'], 'Expected Result': 'Case #123 is now assigned to Alice; audit trail/log records change with timestamp and user info.', 'Dependent Module/Process': 'Case Management; Audit log'}, {'Test Case ID': 'TC_10_03', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Error Handling', 'Test Scenario Title': 'System prevents assignment to non-existent or inactive team member', 'Precondition': 'Case Manager attempts to assign a case.', 'Test Data': "Team member 'Dave' does not exist or is inactive.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager selects an unassigned case.', "Attempts to assign case to 'Dave'."], 'Expected Result': "Error message: 'Selected team member is not available.' Assignment prevented.", 'Dependent Module/Process': 'Access control; Team directory'}, {'Test Case ID': 'TC_10_04', 'EPIC': 'Case Distribution', 'Feature': 'Case Assignment', 'User Story': 'US-10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignment', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Only Case Managers can assign/reassign cases', 'Precondition': 'User is logged in as a non-Case Manager role (e.g., Case Worker).', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker attempts to assign or reassign a case.'], 'Expected Result': "UI controls are hidden/disabled or error: 'Access Denied.' No changes are committed.", 'Dependent Module/Process': 'User roles/permissions'}]</t>
+          <t>[{'Test Case ID': 'TC10-1', 'EPIC': 'Case Assignment', 'Feature': 'Automated Case Allocation', 'User Story': '10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Assignment', 'Activity Title': 'Auto-Assignment', 'Test Scenario Title': 'Verify auto-assignment based on workload', 'Precondition': 'Cases exist in the unassigned queue; team members with varying workload are active.', 'Test Data': {'Cases': ['CaseA', 'CaseB'], 'TeamMembers': [{'id': 'tm1', 'CurrentLoad': 3}, {'id': 'tm2', 'CurrentLoad': 1}]}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to unassigned cases view', "Select 'Auto-Assign' for CaseA", 'System selects team member with lowest workload (tm2)', "Assignment is reflected in both case and member's workload list"], 'Expected Result': "CaseA assigned to tm2; tm2's workload increased, system displays assignment, and audit log is updated.", 'Dependent Module/Process': 'User Management; Case Management'}, {'Test Case ID': 'TC10-2', 'EPIC': 'Case Assignment', 'Feature': 'Manual Assignment Override', 'User Story': '10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Assignment', 'Activity Title': 'Manual Override', 'Test Scenario Title': 'Manual assignment override after auto-assignment', 'Precondition': 'Case was auto-assigned to a team member.', 'Test Data': {'Case': 'CaseA', 'CurrentAssignedMember': 'tm2', 'OverrideMember': 'tm1'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'View assigned CaseA', "Select 'Reassign' option", 'Manually select tm1 for CaseA', 'Confirm override'], 'Expected Result': "CaseA is reassigned to tm1; both members' workloads are updated; audit log captures override including before/after assignment.", 'Dependent Module/Process': 'Case Management'}, {'Test Case ID': 'TC10-3', 'EPIC': 'Case Assignment', 'Feature': 'Assignment Validation', 'User Story': '10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Assignment', 'Activity Title': 'Assignment Integrity', 'Test Scenario Title': 'Assign to inactive or overloaded member (negative)', 'Precondition': 'A team member is marked as inactive or at maximum load.', 'Test Data': {'Case': 'CaseB', 'TeamMember': {'id': 'tm3', 'Active': False}, 'TeamMember2': {'id': 'tm4', 'CurrentLoad': 10, 'MaxLoad': 10}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Attempt to assign CaseB to tm3 (inactive)', 'Observe error message', 'Attempt to assign CaseB to tm4 (max load)', 'Observe error message'], 'Expected Result': 'System prevents assignment and displays relevant messages; audit log not updated for failed attempts.', 'Dependent Module/Process': 'User Management'}, {'Test Case ID': 'TC10-4', 'EPIC': 'Case Assignment', 'Feature': 'Audit Trail', 'User Story': '10', 'Business Process': 'Case Management', 'Sub-Process Title': 'Compliance &amp; Audit', 'Activity Title': 'Audit Verification', 'Test Scenario Title': 'Verify audit trail of assignments and overrides', 'Precondition': 'Cases have been assigned and reassigned.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Officer', 'Detailed Test Steps': ['Login as Audit Officer', 'Navigate to audit log for case assignments', 'Review records for assignment and override actions'], 'Expected Result': 'Audit log contains user, timestamp, case ID, previous member, and new member for each assign/reassign action.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC10-5', 'EPIC': 'Case Assignment', 'Feature': 'API Assignment Endpoint', 'User Story': '10', 'Business Process': 'Case Management', 'Sub-Process Title': 'API Integration', 'Activity Title': 'Assignment API', 'Test Scenario Title': 'Validate API for case assignment (positive/negative)', 'Precondition': 'API endpoint is available and documented.', 'Test Data': {'APIRequest': {'caseId': 'CaseC', 'assigneeId': 'tm2'}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Integration Test', 'Detailed Test Steps': ['Submit valid POST request to assignment API', 'Verify HTTP 200 and expected payload', 'Attempt POST with invalid or inactive assignee', 'Verify HTTP 400 or 403 with error payload'], 'Expected Result': 'Valid assignments succeed; invalid assignments are blocked with proper error responses.', 'Dependent Module/Process': 'API Layer'}, {'Test Case ID': 'TC10-6', 'EPIC': 'Case Assignment', 'Feature': 'User Role Permission', 'User Story': '10', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Role-based Assignment', 'Test Scenario Title': 'Only Case Manager can assign cases', 'Precondition': 'Case Worker and Case Manager roles both exist.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Attempt to access assignment features', 'Observe UI/API behavior'], 'Expected Result': 'Case Worker is denied access to assignment actions.', 'Dependent Module/Process': 'Access Control'}]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Case Workers can request missing documents from applicants, generating secure email or SMS notifications with upload links to facilitate efficient document collection.</t>
+          <t>This user story enables Case Workers to request documents from applicants, automatically generating secure notifications (email or SMS) with upload links for applicants to submit missing information.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to send document requests to applicants so that they can upload missing items. - Generate email or SMS notifications with secure upload links.</t>
+          <t>11: As a Case Worker, I want to send document requests to applicants so that they can upload missing items. - Generate email or SMS notifications with secure upload links.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Case Worker selects missing documents, system generates and sends notification (email/SMS) with a secure upload link to the applicant.</t>
+          <t>Case Worker selects missing documents, system generates document request, applicant receives secure email/SMS with upload link, and uploads document.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_11_01', 'Brief Description': 'Send document request via email with secure upload link'}, {'Test Case ID': 'TC_11_02', 'Brief Description': 'Send document request via SMS with secure upload link'}, {'Test Case ID': 'TC_11_03', 'Brief Description': 'Attempt to send request with missing contact info'}, {'Test Case ID': 'TC_11_04', 'Brief Description': 'Permission validation — Case Worker only'}]</t>
+          <t>[{'Test Case ID': 'TC11-1', 'Brief Description': 'Send email document request with valid applicant address'}, {'Test Case ID': 'TC11-2', 'Brief Description': 'Send SMS document request with valid applicant phone'}, {'Test Case ID': 'TC11-3', 'Brief Description': 'Receive secure upload link as applicant'}, {'Test Case ID': 'TC11-4', 'Brief Description': 'Attempt to send request to applicant with missing contact info (negative)'}, {'Test Case ID': 'TC11-5', 'Brief Description': 'Upload process from applicant POV (E2E test)'}, {'Test Case ID': 'TC11-6', 'Brief Description': 'Verify only Case Worker role can send requests'}, {'Test Case ID': 'TC11-7', 'Brief Description': 'Audit log contains all sent document requests'}]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_11_01', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send Email Request', 'Test Scenario Title': 'Case Worker sends a document request via email', 'Precondition': 'Applicant profile has a valid email.', 'Test Data': 'Applicant: John Doe, Missing documents: Proof of Address, Email: john@example.com', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker selects applicant with missing documents.', "Selects 'Send Document Request (Email)'.", 'Chooses missing documents to request.', 'Confirms and sends request.'], 'Expected Result': 'Applicant receives an email with secure upload link listing requested documents; system logs notification sent.', 'Dependent Module/Process': 'Email server; Applicant portal'}, {'Test Case ID': 'TC_11_02', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send SMS Request', 'Test Scenario Title': 'Case Worker sends a document request via SMS', 'Precondition': 'Applicant profile has a valid mobile number.', 'Test Data': 'Applicant: Jane Smith, Missing: ID Card, Mobile: +1234567890', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker selects applicant with missing document.', "Selects 'Send Document Request (SMS)'.", 'Chooses missing document.', 'Confirms and sends request.'], 'Expected Result': 'Applicant receives SMS with secure upload link; notification is logged.', 'Dependent Module/Process': 'SMS gateway; Applicant portal'}, {'Test Case ID': 'TC_11_03', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send Document Request', 'Test Scenario Title': 'Error handling when contact information is missing', 'Precondition': 'Applicant lacks valid email and mobile.', 'Test Data': 'Applicant: Bob Lee, No contact info', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker selects applicant missing required contact details.', 'Attempts to send document request.'], 'Expected Result': "System displays error: 'No valid contact information available. Cannot send request.'", 'Dependent Module/Process': 'Applicant directory'}, {'Test Case ID': 'TC_11_04', 'EPIC': 'Document Management', 'Feature': 'Document Request', 'User Story': 'US-11', 'Business Process': 'Applicant Communication', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Only Case Worker roles can send document requests', 'Precondition': 'User is not a Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Applicant logs in and tries to use the document request function.'], 'Expected Result': "'Send Document Request' option is not available or an 'Access Denied' error appears.", 'Dependent Module/Process': 'User roles/permissions'}]</t>
+          <t>[{'Test Case ID': 'TC11-1', 'EPIC': 'Case Documentation', 'Feature': 'Document Requests', 'User Story': '11', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Request', 'Activity Title': 'Send Email Request', 'Test Scenario Title': 'Send document request by email (positive)', 'Precondition': 'Applicant has valid email; required document identified as missing.', 'Test Data': {'Applicant': {'id': 'app1', 'email': 'valid@email.com'}, 'Documents': ['Proof of ID']}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Open applicant case', "Select 'Request Document' &gt; choose 'Proof of ID'", 'Select communication: Email', 'Send request'], 'Expected Result': 'Applicant receives email with secure upload link; request logged in case history.', 'Dependent Module/Process': 'Email Service'}, {'Test Case ID': 'TC11-2', 'EPIC': 'Case Documentation', 'Feature': 'Document Requests', 'User Story': '11', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Request', 'Activity Title': 'Send SMS Request', 'Test Scenario Title': 'Send document request by SMS (positive)', 'Precondition': 'Applicant has valid phone number.', 'Test Data': {'Applicant': {'id': 'app2', 'phone': '+14445556666'}, 'Documents': ['Birth Certificate']}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', "Identify missing 'Birth Certificate' for app2", 'Choose SMS as notification method', 'Send request'], 'Expected Result': 'Applicant receives SMS with secure upload link; event recorded in case log.', 'Dependent Module/Process': 'SMS Service'}, {'Test Case ID': 'TC11-3', 'EPIC': 'Case Documentation', 'Feature': 'Document Submission', 'User Story': '11', 'Business Process': 'Applicant Interaction', 'Sub-Process Title': 'Secure Upload', 'Activity Title': 'Receive Upload Link', 'Test Scenario Title': 'Applicant receives and opens secure upload link', 'Precondition': 'Document request was sent and applicant has received the link.', 'Test Data': {'UploadLink': 'securelink123'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Open email or SMS with link', 'Click link', 'Arrive at secure upload portal'], 'Expected Result': 'Portal loads, prompting authentication (if applicable) or direct upload screen.', 'Dependent Module/Process': 'Applicant Portal'}, {'Test Case ID': 'TC11-4', 'EPIC': 'Case Documentation', 'Feature': 'Document Requests', 'User Story': '11', 'Business Process': 'Document Management', 'Sub-Process Title': 'Request Validation', 'Activity Title': 'Missing Contact Info', 'Test Scenario Title': 'Attempt to send request to applicant with missing email/phone (negative)', 'Precondition': 'Applicant record lacks both phone and email.', 'Test Data': {'Applicant': {'id': 'app3', 'email': '', 'phone': ''}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open applicant app3', "Choose 'Request Document'", 'Attempt to proceed to notification'], 'Expected Result': "System blocks request and displays error: 'No valid contact information on file'.", 'Dependent Module/Process': 'Data Validation'}, {'Test Case ID': 'TC11-5', 'EPIC': 'Case Documentation', 'Feature': 'Applicant Submission', 'User Story': '11', 'Business Process': 'End-to-End Process', 'Sub-Process Title': 'Document Request Fulfillment', 'Activity Title': 'Applicant Upload', 'Test Scenario Title': 'Applicant uploads document from link (E2E)', 'Precondition': 'Applicant has access to secure upload link.', 'Test Data': {'UploadFile': 'scan.pdf'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Click upload link in notification', "Upload 'scan.pdf' file", 'Confirm upload'], 'Expected Result': "'Document Uploaded' confirmation is displayed to applicant, file status in case updated to 'Received'.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'TC11-6', 'EPIC': 'Case Documentation', 'Feature': 'Role Enforcement', 'User Story': '11', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Request Permissions', 'Test Scenario Title': 'Verify only Case Worker can send document requests', 'Precondition': 'User with Applicant role logged in.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Login as Applicant', "Attempt to access 'Send Document Request' feature"], 'Expected Result': 'Applicant cannot see or use the document request function.', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'TC11-7', 'EPIC': 'Case Documentation', 'Feature': 'Audit Compliance', 'User Story': '11', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Request Logging', 'Activity Title': 'Audit Log Verification', 'Test Scenario Title': 'All document requests recorded in audit logs', 'Precondition': 'Document request(s) made by Case Worker', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Officer', 'Detailed Test Steps': ['Login as Audit Officer', 'Check audit logs for requests sent', 'Verify presence of case/worker/applicant/data/time'], 'Expected Result': 'Audit logs contain all relevant document request actions and metadata.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Case Workers monitor document submission via an up-to-date checklist, with visual indicators reflecting current status for each required document. This enables timely follow-up for pending items.</t>
+          <t>This user story ensures that Case Workers can monitor which documents for an applicant have been submitted or are missing, using a status-indicated checklist to support timely follow-up and tracking.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to track document submission status so that I can follow up on pending items. - Document checklist with status indicators.</t>
+          <t>12: As a Case Worker, I want to track document submission status so that I can follow up on pending items. - Document checklist with status indicators.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Case Worker views applicant profile, sees a checklist with status (Submitted, Pending, Rejected) for each required document, enabling targeted follow-up.</t>
+          <t>Case Worker opens case, views checklist with real-time status (uploaded/pending/missing) for all required documents, and follows up on pending items.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_12_01', 'Brief Description': 'Display document checklist with status indicators'}, {'Test Case ID': 'TC_12_02', 'Brief Description': 'Status updates after document upload'}, {'Test Case ID': 'TC_12_03', 'Brief Description': 'Handle status for rejected or invalid submissions'}, {'Test Case ID': 'TC_12_04', 'Brief Description': 'Permission validation — Case Worker only'}]</t>
+          <t>[{'Test Case ID': 'TC12-1', 'Brief Description': 'Checklist displays correct status for each document'}, {'Test Case ID': 'TC12-2', 'Brief Description': "Status changes to 'Received' after applicant uploads"}, {'Test Case ID': 'TC12-3', 'Brief Description': 'Status does not update on upload failure (negative)'}, {'Test Case ID': 'TC12-4', 'Brief Description': 'Case Worker attempts follow-up for pending item'}, {'Test Case ID': 'TC12-5', 'Brief Description': 'Checklist updates in real time (integration test)'}, {'Test Case ID': 'TC12-6', 'Brief Description': 'Checklist not visible to unauthorized roles'}, {'Test Case ID': 'TC12-7', 'Brief Description': 'Verify compliance/audit log of status changes'}]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_12_01', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'View Status Checklist', 'Test Scenario Title': 'Case Worker sees checklist with status for each required document', 'Precondition': 'Applicant has a list of required documents in the system.', 'Test Data': 'Applicant: Emma, Required: Proof of Residence (Submitted), Proof of Income (Pending)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker opens applicant profile.', "Navigates to 'Documents' section.", 'Reviews checklist and status indicators.'], 'Expected Result': 'Checklist displays all required documents, each with a clear status indicator (e.g., color-coded, icons, text labels).', 'Dependent Module/Process': 'Document database; Applicant profile'}, {'Test Case ID': 'TC_12_02', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'Status Update', 'Test Scenario Title': 'Checklist updates after applicant uploads a document', 'Precondition': "A required document is marked as 'Pending'.", 'Test Data': 'Applicant: Alex, Uploads ID Card document.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Applicant uploads ID Card via secure link.', 'Case Worker refreshes or revisits checklist.'], 'Expected Result': "Status for ID Card changes from 'Pending' to 'Submitted'; timestamp of update visible.", 'Dependent Module/Process': 'Applicant portal; Document Management'}, {'Test Case ID': 'TC_12_03', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'Status Handling', 'Test Scenario Title': 'Checklist indicates rejected/invalid document submissions', 'Precondition': 'Applicant uploaded a document that was rejected by Case Worker.', 'Test Data': "Proof of Income marked as 'Rejected' for Applicant: Lily.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker reviews submitted document.', "Marks submission as 'Rejected' or 'Invalid'.", 'Checklist reflects rejection status, optionally with reason.'], 'Expected Result': "'Rejected' or 'Invalid' status shown, with rejection note/reason visible.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'TC_12_04', 'EPIC': 'Document Management', 'Feature': 'Document Status Tracking', 'User Story': 'US-12', 'Business Process': 'Application Review', 'Sub-Process Title': 'Document Collection', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Only Case Workers can see full document status checklist', 'Precondition': 'User is not a Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Applicant logs in and tries to access full checklist/status view.'], 'Expected Result': 'Applicant can only see their own submissions and statuses, not staff-level checklist details.', 'Dependent Module/Process': 'User roles/permissions'}]</t>
+          <t>[{'Test Case ID': 'TC12-1', 'EPIC': 'Document Tracking', 'Feature': 'Checklist Display', 'User Story': '12', 'Business Process': 'Document Management', 'Sub-Process Title': 'Status Tracking', 'Activity Title': 'Checklist View', 'Test Scenario Title': 'Checklist displays correct document statuses', 'Precondition': 'Applicant case exists with at least one required document uploaded and one pending.', 'Test Data': {'RequiredDocuments': [{'type': 'ID', 'status': 'Received'}, {'type': 'Proof of Address', 'status': 'Pending'}]}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Open the checklist view for the case', "Observe each document's status column"], 'Expected Result': "Checklist clearly indicates status ('Received', 'Pending', 'Missing') for each required document.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'TC12-2', 'EPIC': 'Document Tracking', 'Feature': 'Checklist Update', 'User Story': '12', 'Business Process': 'Document Management', 'Sub-Process Title': 'Checklist Automation', 'Activity Title': 'Status Update', 'Test Scenario Title': "Status changes to 'Received' after document upload", 'Precondition': 'Checklist displayed; applicant uploads a document.', 'Test Data': {'Document': {'type': 'Proof of Address', 'status': 'Pending'}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ["Upload 'Proof of Address' as applicant", 'Case Worker refreshes checklist'], 'Expected Result': "Status for 'Proof of Address' updates to 'Received'; timestamp of receipt displayed.", 'Dependent Module/Process': 'Applicant Portal'}, {'Test Case ID': 'TC12-3', 'EPIC': 'Document Tracking', 'Feature': 'Checklist Robustness', 'User Story': '12', 'Business Process': 'Document Management', 'Sub-Process Title': 'Status Verification', 'Activity Title': 'Upload Failure Handling', 'Test Scenario Title': 'Status does not update on document upload failure (negative)', 'Precondition': 'Checklist displayed; applicant attempts to upload but upload is interrupted or rejected.', 'Test Data': {'Document': {'type': 'ID', 'status': 'Pending'}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ["Attempt to upload 'ID' document", 'Simulate network failure or blocked file type', 'Refresh checklist as Case Worker'], 'Expected Result': "Checklist continues to show 'Pending' for 'ID'; error logged in applicant portal.", 'Dependent Module/Process': 'Network/File Validation'}, {'Test Case ID': 'TC12-4', 'EPIC': 'Document Tracking', 'Feature': 'Follow-up Action', 'User Story': '12', 'Business Process': 'Document Management', 'Sub-Process Title': 'Follow-Up', 'Activity Title': 'Follow-Up Action', 'Test Scenario Title': 'Case Worker follows up on pending document', 'Precondition': "At least one document remains in 'Pending' status.", 'Test Data': {'Document': {'type': 'Birth Certificate', 'status': 'Pending'}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['View checklist', "Click 'Follow-Up' or 'Remind' on the pending item"], 'Expected Result': 'System logs follow-up action and can trigger a new notification to applicant.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC12-5', 'EPIC': 'Document Tracking', 'Feature': 'Checklist-Portal Integration', 'User Story': '12', 'Business Process': 'Document Management', 'Sub-Process Title': 'Real Time Update', 'Activity Title': 'Integration', 'Test Scenario Title': 'Checklist updates in real time after applicant upload', 'Precondition': 'Applicant portal and case worker checklist both open for same case.', 'Test Data': {'Document': {'type': 'Utility Bill'}}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant, Case Worker', 'Detailed Test Steps': ['Applicant uploads Utility Bill', 'Observe checklist instantly (or after defined interval) updates status', 'Verify timestamp and document link availability'], 'Expected Result': "Checklist status for 'Utility Bill' moves to 'Received' in real time without manual refresh.", 'Dependent Module/Process': 'Real-Time Data Service'}, {'Test Case ID': 'TC12-6', 'EPIC': 'Document Tracking', 'Feature': 'Access Control', 'User Story': '12', 'Business Process': 'User Management', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Unauthorized Access Test', 'Test Scenario Title': 'Checklist not visible to unauthorized users', 'Precondition': 'Applicant logged in to portal.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Login as Applicant', 'Attempt to access case worker checklist page'], 'Expected Result': "Applicant receives 'Access Denied' or does not see checklist feature.", 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'TC12-7', 'EPIC': 'Document Tracking', 'Feature': 'Audit Logging', 'User Story': '12', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Status Change Logging', 'Activity Title': 'Audit Log Review', 'Test Scenario Title': 'Audit log of all status changes', 'Precondition': 'Checklist status has changed via upload/follow-up.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Officer', 'Detailed Test Steps': ['Login as Audit Officer', 'Open audit log for applicant case', 'Search for status change records'], 'Expected Result': 'Audit log includes who made the change, document, previous and new status, timestamp.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>This user story focuses on equipping case workers with a tool to redact sensitive information (such as SSNs and addresses) from uploaded documents to ensure privacy and compliance with data protection regulations.</t>
+          <t>This user story focuses on enabling Case Workers to generate a PDF summary report of eligibility findings for cases they manage. The report should be auto-generated, accurate, and suitable for sharing with supervisors. Coverage includes permissions, format compliance, content validation, and integration with the case management system.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to redact sensitive information in uploaded documents so that I can protect privacy.</t>
+          <t>As a Case Worker, I want to generate a summary report of eligibility findings so that I can present it to supervisors. (Auto-generated PDF summary of case findings.)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A case worker selects a document, uses the redaction tool to mask sensitive information (like SSNs, addresses), saves the redacted version, and confirms that the masked information is not visible in the output.</t>
+          <t>Case Worker initiates report generation from a case file, and the system produces a downloadable PDF summary containing accurate eligibility findings.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC13-1', 'Brief Description': 'Redact SSN and addresses in a PDF document (happy path)'}, {'Test Case ID': 'TC13-2', 'Brief Description': 'Attempt redaction as an unauthorized user (negative)'}, {'Test Case ID': 'TC13-3', 'Brief Description': 'Test auto-detection failure when there is no sensitive data (negative)'}, {'Test Case ID': 'TC13-4', 'Brief Description': 'Audit log is generated for each redaction (compliance)'}]</t>
+          <t>[{'Test Case ID': 'TC16-01', 'Brief Description': 'Generate eligibility summary report successfully (PDF generated, proper data included).'}, {'Test Case ID': 'TC16-02', 'Brief Description': 'Attempt to generate report without proper case selection (no eligible case).'}, {'Test Case ID': 'TC16-03', 'Brief Description': 'Review PDF format and data accuracy for compliance.'}, {'Test Case ID': 'TC16-04', 'Brief Description': 'Unauthorised role attempts to generate report (permission denied).'}, {'Test Case ID': 'TC16-05', 'Brief Description': 'System/network error during report generation.'}]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC13-1', 'EPIC': 'Document Management', 'Feature': 'Redaction Tool', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redact Sensitive Information', 'Activity Title': 'Manual and auto redaction', 'Test Scenario Title': 'Happy path—successful redaction by authorized case worker', 'Precondition': 'Case worker is logged in and has upload permission; document with sensitive fields (SSN/address) is present.', 'Test Data': 'PDF file containing fake SSNs and addresses.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to the client’s_uploaded_doc page.', 'Open the uploaded document in the redaction tool interface.', "Select 'Auto-detect sensitive fields'.", 'Verify that detected fields (SSNs, addresses) are highlighted.', 'Apply redaction to all highlighted fields.', 'Save and view the redacted document.'], 'Expected Result': 'All sensitive data is obscured in the saved document; only allowed information is visible.', 'Dependent Module/Process': 'Document Management, Security/Compliance'}, {'Test Case ID': 'TC13-2', 'EPIC': 'Document Management', 'Feature': 'Redaction Tool', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redact Sensitive Information', 'Activity Title': 'Permission validation', 'Test Scenario Title': 'Negative test—unauthorized user attempts redaction', 'Precondition': 'User is logged in as a Clerk (no redact permission), document is uploaded.', 'Test Data': 'Any document.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Clerk', 'Detailed Test Steps': ['Navigate to the document page.', 'Attempt to launch the redaction tool.'], 'Expected Result': "Error message displayed: 'You do not have permission to redact documents.' No access to tool.", 'Dependent Module/Process': 'Authorization'}, {'Test Case ID': 'TC13-3', 'EPIC': 'Document Management', 'Feature': 'Redaction Tool', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redact Sensitive Information', 'Activity Title': 'Auto-detection validation', 'Test Scenario Title': 'Auto-detect finds no sensitive info', 'Precondition': 'Case worker logged in, document with no sensitive information uploaded.', 'Test Data': 'PDF with no PII/SSN/address.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open document in redaction tool.', "Click 'Auto-detect sensitive fields'."], 'Expected Result': 'No fields are highlighted. User can proceed manually. No accidental redaction.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'TC13-4', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Redaction Audit', 'User Story': '13', 'Business Process': 'Case Document Handling', 'Sub-Process Title': 'Redaction Audit', 'Activity Title': 'Redaction event logging', 'Test Scenario Title': 'Audit log generated for every redaction', 'Precondition': 'Case worker completes redaction.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZREDACTDOC1', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Redact any document using the tool.', 'Check the audit logs for a new entry referencing redaction action.'], 'Expected Result': 'Each redaction event is logged with user ID, timestamp, redaction type, and document reference.', 'Dependent Module/Process': 'Audit, Compliance, Document Management'}]</t>
+          <t>[{'Test Case ID': 'TC16-01', 'EPIC': 'Reporting', 'Feature': 'Case Summary Reporting', 'User Story': '16', 'Business Process': 'Case Management', 'Sub-Process Title': 'Eligibility Assessment', 'Activity Title': 'Generate Summary Report', 'Test Scenario Title': 'Generate eligibility summary report successfully', 'Precondition': 'Case Worker is logged in and has access to a completed eligibility case.', 'Test Data': {'Case ID': 'CASE1234', 'Eligibility Findings': 'Eligible, criteria A, B met'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as a Case Worker', "Navigate to 'Cases' and select CASE1234", "Click 'Generate Report' or equivalent button", 'Wait for the PDF to be generated and click to download/view'], 'Expected Result': 'PDF file is generated, content includes all eligibility findings, formatted correctly, ready for presentation.', 'Dependent Module/Process': 'Document Generation Service'}, {'Test Case ID': 'TC16-02', 'EPIC': 'Reporting', 'Feature': 'Case Summary Reporting', 'User Story': '16', 'Business Process': 'Case Management', 'Sub-Process Title': 'Eligibility Assessment', 'Activity Title': 'Generate Summary Report', 'Test Scenario Title': 'Generate report with no eligible case selected', 'Precondition': 'Case Worker is logged in but no case is selected/not eligible for reporting.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Do not select a case or select an ineligible case', "Click 'Generate Report'"], 'Expected Result': "System displays 'No eligible case selected' or appropriate error message, prevents report generation.", 'Dependent Module/Process': 'Case Selection'}, {'Test Case ID': 'TC16-03', 'EPIC': 'Reporting', 'Feature': 'Case Summary Reporting', 'User Story': '16', 'Business Process': 'Case Management', 'Sub-Process Title': 'Eligibility Assessment', 'Activity Title': 'Generate Summary Report', 'Test Scenario Title': 'Compliance - PDF format and content accuracy', 'Precondition': 'Case Worker successfully generated a summary report.', 'Test Data': {'Expected Fields': ['Case ID', 'Client Name', 'Eligibility Conclusion', 'Criteria Met/Unmet', 'Date of Assessment']}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open generated PDF report', 'Check if all required fields are present', 'Review formatting, section headers, page numbers', 'Compare data with source system'], 'Expected Result': 'PDF matches all compliance and data accuracy requirements; audit fields (date/time, author) are present.', 'Dependent Module/Process': 'Compliance Standards, Audit Logs'}, {'Test Case ID': 'TC16-04', 'EPIC': 'Reporting', 'Feature': 'Case Summary Reporting', 'User Story': '16', 'Business Process': 'Case Management', 'Sub-Process Title': 'Eligibility Assessment', 'Activity Title': 'Generate Summary Report', 'Test Scenario Title': 'Permission - Unauthorised role cannot generate', 'Precondition': 'User with Supervisor role logged in (no permission to generate reports).', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Log in as Supervisor', 'Navigate to a case', "Attempt to click 'Generate Report'"], 'Expected Result': "'Generate Report' button not visible or action is denied with proper error message.", 'Dependent Module/Process': 'Authorization Service'}, {'Test Case ID': 'TC16-05', 'EPIC': 'Reporting', 'Feature': 'Case Summary Reporting', 'User Story': '16', 'Business Process': 'Case Management', 'Sub-Process Title': 'Eligibility Assessment', 'Activity Title': 'Generate Summary Report', 'Test Scenario Title': 'Error Handling - Service/Network Interruption', 'Precondition': 'Case with eligibility findings, network instability or reporting service down.', 'Test Data': {'Service Response': '500 error or timeout'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to generate report during simulated network/service failure'], 'Expected Result': "User receives error notification: 'Unable to generate report at this time.' Log entry created for support.", 'Dependent Module/Process': 'Document Generation Service, Error Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>This user story emphasizes providing case managers with communication logs embedded in each client's case profile, including records of emails, calls, and messages, to offer a holistic case timeline.</t>
+          <t>Case Workers need immediate notification when clients upload documents to ensure prompt review, improving case turnaround times. Tests cover notification delivery, real-time updates, permissions, API/webhook integrations, and compliance.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to view communication logs with clients so that I can understand case history.</t>
+          <t>As a Case Worker, I want to receive alerts when a document is uploaded by a client so that I can review it promptly. (Real-time notifications for document uploads.)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A case manager opens a case profile, selects the ‘Communication Logs’ tab, and reviews a chronological log of all correspondence with that client.</t>
+          <t>Client uploads a document; the system instantly notifies the assigned Case Worker via the application and/or email.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC14-1', 'Brief Description': 'Happy path—viewing logs for a client'}, {'Test Case ID': 'TC14-2', 'Brief Description': 'Negative—case manager tries to access logs for a case they do not manage'}, {'Test Case ID': 'TC14-3', 'Brief Description': 'API integration—ensure all emails, calls, messages are logged'}, {'Test Case ID': 'TC14-4', 'Brief Description': 'Compliance—ensure logs are immutable and audit trailed'}]</t>
+          <t>[{'Test Case ID': 'TC17-01', 'Brief Description': 'Case Worker receives real-time notification when a document is uploaded.'}, {'Test Case ID': 'TC17-02', 'Brief Description': 'Case Worker does not receive notification if not assigned to the case.'}, {'Test Case ID': 'TC17-03', 'Brief Description': 'Client uploads an unsupported file type (error message).'}, {'Test Case ID': 'TC17-04', 'Brief Description': 'Case Worker receives duplicate notifications for same upload (should not happen).'}, {'Test Case ID': 'TC17-05', 'Brief Description': 'Notification content meets compliance/audit requirements.'}]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC14-1', 'EPIC': 'Case Management', 'Feature': 'Communication Logs', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'View Communication History', 'Activity Title': 'Access communication logs', 'Test Scenario Title': 'Case manager views communication logs in the timeline (happy path)', 'Precondition': 'User is logged in as Case Manager and manages the selected case.', 'Test Data': 'Case with email, call, and message records.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to the case file.', "Click on the 'Communication Logs' tab.", 'Review the entries presented in reverse chronological order.'], 'Expected Result': 'All correspondence entries (emails, calls, messages) for the client are shown with correct details.', 'Dependent Module/Process': 'Case Management, Correspondence Subsystem'}, {'Test Case ID': 'TC14-2', 'EPIC': 'Case Management', 'Feature': 'Communication Logs', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'View Communication History', 'Activity Title': 'Permissions validation', 'Test Scenario Title': 'Case manager attempts to access communication logs for an unrelated case', 'Precondition': 'Case Manager does not manage/own the case.', 'Test Data': 'An unrelated case ID.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Attempt to access the 'Communication Logs' tab of an unassigned case."], 'Expected Result': 'Access denied message or no logs are available; sensitive log information is not exposed.', 'Dependent Module/Process': 'Case Management, Authorization'}, {'Test Case ID': 'TC14-3', 'EPIC': 'Case Management', 'Feature': 'Communication Logs', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'View Communication History', 'Activity Title': 'API Integration', 'Test Scenario Title': 'APIs correctly update log entries for different communication types', 'Precondition': 'Case exists. API integration for email/call/message logging is active.', 'Test Data': 'Trigger one email, one call, one message via API.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'System/Case Manager', 'Detailed Test Steps': ['Trigger sending an email to the client via the system.', 'Simulate an inbound call to the call logger API.', 'Send an internal message via messaging API.', 'Open case communication logs.'], 'Expected Result': 'Each action results in a log entry accurately reflecting the communication, timestamp, and user.', 'Dependent Module/Process': 'Correspondence, Telephony, Messaging APIs'}, {'Test Case ID': 'TC14-4', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Audit Trail', 'User Story': '14', 'Business Process': 'Case Review', 'Sub-Process Title': 'Log Immutability', 'Activity Title': 'Communication log audit compliance', 'Test Scenario Title': 'Audit log for communication entries is generated and modification is prevented', 'Precondition': 'Log entries exist for a case.', 'Test Data': 'Any communication log entry.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZCOMMLOGS', 'User Role': 'Case Manager/Auditor', 'Detailed Test Steps': ['Attempt to edit or delete a communication log entry.', 'Check the system audit trail.'], 'Expected Result': 'Communication log entries are immutable and attempts to change them are logged with user ID and timestamp.', 'Dependent Module/Process': 'Audit Module, Logging'}]</t>
+          <t>[{'Test Case ID': 'TC17-01', 'EPIC': 'Notifications', 'Feature': 'Document Upload Alert', 'User Story': '17', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Management', 'Activity Title': 'Document Upload Notification', 'Test Scenario Title': 'Real-time notification on document upload', 'Precondition': 'Case Worker is logged in and assigned to a case; client has access to upload.', 'Test Data': {'User': 'client1', 'Case Worker': 'workerA', 'Document': 'income_proof.pdf', 'Case ID': 'CASE5678'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker logs in and monitors notification area.', 'Client1 logs in, uploads income_proof.pdf to CASE5678.', 'Observe if real-time notification appears for workerA.'], 'Expected Result': "Notification for new document upload appears instantly in Case Worker's interface and/or via configured channels.", 'Dependent Module/Process': 'Notification Service, Document Management'}, {'Test Case ID': 'TC17-02', 'EPIC': 'Notifications', 'Feature': 'Document Upload Alert', 'User Story': '17', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Management', 'Activity Title': 'Document Upload Notification', 'Test Scenario Title': 'No notification for unassigned Case Worker', 'Precondition': 'Case Worker is logged in but not assigned to relevant case.', 'Test Data': {'User': 'client2', 'Case Worker': 'workerB (not assigned)', 'Document': 'identity_card.pdf', 'Case ID': 'CASE7890'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['workerB logs in and monitors notification area.', 'client2 uploads identity_card.pdf to CASE7890.', 'Observe notification panel for workerB.'], 'Expected Result': 'No notification is delivered to workerB; system respects assignment permissions.', 'Dependent Module/Process': 'Notification Service, User Permissions'}, {'Test Case ID': 'TC17-03', 'EPIC': 'Notifications', 'Feature': 'Document Upload Alert', 'User Story': '17', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Management', 'Activity Title': 'Document Upload Notification', 'Test Scenario Title': 'Unsupported file type upload', 'Precondition': 'Client has access to document upload interface.', 'Test Data': {'User': 'client1', 'File': 'malware.exe'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Client', 'Detailed Test Steps': ['client1 attempts to upload malware.exe.'], 'Expected Result': "System rejects upload, displays 'Unsupported file type' error, and does not send alert to Case Worker.", 'Dependent Module/Process': 'File Validation'}, {'Test Case ID': 'TC17-04', 'EPIC': 'Notifications', 'Feature': 'Document Upload Alert', 'User Story': '17', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Management', 'Activity Title': 'Document Upload Notification', 'Test Scenario Title': 'Duplicate notification prevention', 'Precondition': 'Case Worker is assigned; system monitored for duplicate events.', 'Test Data': {'User': 'client1', 'Document': 'income_proof.pdf'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger document upload and ensure notification delivered.', 'Repeat trigger for same document (simulate retry or duplicate event).'], 'Expected Result': 'Only one notification per unique upload event is received.', 'Dependent Module/Process': 'Notification Deduplication'}, {'Test Case ID': 'TC17-05', 'EPIC': 'Notifications', 'Feature': 'Document Upload Alert', 'User Story': '17', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Management', 'Activity Title': 'Document Upload Notification', 'Test Scenario Title': 'Notification compliance and audit attributes', 'Precondition': 'Document successfully uploaded and notification is generated.', 'Test Data': {'Expected Notification Fields': ['Uploader Name', 'Upload Timestamp', 'Document Type', 'Case Reference']}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Inspect details of received notification.', 'Verify inclusion of uploader, timestamp, document, and case ID.'], 'Expected Result': 'Notification includes all compliance/audit fields for traceability in logs.', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>This user story ensures case managers are able to coordinate with other agencies in cases involving dual eligibility by sharing notes and case flags, improving benefit delivery.</t>
+          <t>The system must allow Case Managers to log or track time spent on each case – either via an active timer or manual entry – enabling accurate workload reporting. Test coverage includes timer functionality, manual time logging, permissions, reporting, editing logs, and audit trails.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to coordinate with other agencies for dual eligibility cases so that clients receive all benefits.</t>
+          <t>As a Case Manager, I want to track the time spent on each case so that I can report on workload. (Timer or manual entry of time logs per case.)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A case reaches dual-eligibility status, the case manager adds inter-agency notes and sets shared flags, and these updates are visible to all collaborating parties.</t>
+          <t>Case Manager starts/stops a timer or enters worked hours manually for a case. The system records this time, displays it in the case log, and includes it in workload reports.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC15-1', 'Brief Description': 'Add inter-agency note and shared flag in dual-eligible case'}, {'Test Case ID': 'TC15-2', 'Brief Description': 'Negative—user from another agency attempts to edit unauthorized note'}, {'Test Case ID': 'TC15-3', 'Brief Description': 'Integration—note and flag sync across agencies/systems'}, {'Test Case ID': 'TC15-4', 'Brief Description': 'Compliance—logging and tracking all inter-agency actions'}]</t>
+          <t>[{'Test Case ID': 'TC18-01', 'Brief Description': 'Start and stop timer logs time correctly for a case.'}, {'Test Case ID': 'TC18-02', 'Brief Description': 'Manually add a time log entry for a case.'}, {'Test Case ID': 'TC18-03', 'Brief Description': 'Edit or delete a previously logged time entry.'}, {'Test Case ID': 'TC18-04', 'Brief Description': 'Unauthorized user attempts to enter or modify time logs.'}, {'Test Case ID': 'TC18-05', 'Brief Description': 'Workload report includes all time log entries for a case.'}]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC15-1', 'EPIC': 'Case Collaboration', 'Feature': 'Dual Eligibility', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Inter-Agency Communication', 'Activity Title': 'Add notes and shared flags', 'Test Scenario Title': 'Case manager successfully adds an inter-agency note and flag (happy path)', 'Precondition': 'Case is flagged as dual-eligible. Logged in as authorized case manager.', 'Test Data': 'Dual-eligible case record.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open the dual-eligible case profile.', "Navigate to the 'Inter-Agency Notes' section.", 'Add a note referencing coordination details.', 'Set the shared flag (e.g., "Needs cross-agency review").', 'Save changes.'], 'Expected Result': 'Note and flag are persisted. Others with permission see them in real time.', 'Dependent Module/Process': 'Case Management, Inter-Agency Portal'}, {'Test Case ID': 'TC15-2', 'EPIC': 'Case Collaboration', 'Feature': 'Dual Eligibility', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Inter-Agency Communication', 'Activity Title': 'Permissions validation', 'Test Scenario Title': 'User from another agency tries to edit a note not their own', 'Precondition': 'Inter-agency note created by Agency A, user logged in as Agency B’s manager.', 'Test Data': 'Note created by Agency A.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager from Agency B', 'Detailed Test Steps': ['Navigate to the dual-eligible case profile.', 'Attempt to edit or delete a note authored by Agency A.'], 'Expected Result': 'Action denied. User is unable to change notes not their own; error displayed or edit option disabled.', 'Dependent Module/Process': 'Authorization, Inter-Agency Portal'}, {'Test Case ID': 'TC15-3', 'EPIC': 'Case Collaboration', 'Feature': 'Dual Eligibility', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Inter-Agency Communication', 'Activity Title': 'Integration sync', 'Test Scenario Title': 'Inter-agency note and shared flag are correctly synced with external agency systems', 'Precondition': 'Inter-agency note and flag created.', 'Test Data': 'Example note, flag value.', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager/API', 'Detailed Test Steps': ['Create note/flag in System 1.', 'Trigger system sync/API push to System 2.', "Verify that the note and flag appear in System 2's dual-case interface."], 'Expected Result': 'Note/flag are present, with correct values and authorship, in all connected systems.', 'Dependent Module/Process': 'API Integration, External Agency System'}, {'Test Case ID': 'TC15-4', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Inter-Agency Coordination Audit', 'User Story': '15', 'Business Process': 'Benefits Coordination', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Track all inter-agency actions', 'Test Scenario Title': 'Audit logging requirements for all actions on dual-eligible cases', 'Precondition': 'Inter-agency notes and flags updated.', 'Test Data': 'Any action (add/edit/delete note or flag).', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'ZDUALCASE', 'User Role': 'Case Manager/Auditor', 'Detailed Test Steps': ['Perform actions (add/edit/delete note, toggle flag) as a case manager.', 'Check audit logs for each action.'], 'Expected Result': 'All inter-agency actions are recorded in audit logs, including user ID, timestamp, agency, action type, and old/new values for compliance.', 'Dependent Module/Process': 'Audit, Logging, Case Management, Inter-Agency Portal'}]</t>
+          <t>[{'Test Case ID': 'TC18-01', 'EPIC': 'Time Tracking', 'Feature': 'Case Time Logs', 'User Story': '18', 'Business Process': 'Case Management', 'Sub-Process Title': 'Time Tracking', 'Activity Title': 'Log Time via Timer', 'Test Scenario Title': 'Start and stop timer logs time', 'Precondition': 'Case Manager is logged in and assigned to a case.', 'Test Data': {'Case ID': 'CASE2222', 'Manager': 'manager1'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['manager1 logs in.', 'Navigates to CASE2222.', "Clicks 'Start Timer' at 09:00.", 'Performs work for 30 minutes.', "Clicks 'Stop Timer' at 09:30.", 'Views time log entry.'], 'Expected Result': 'A time log entry of 30 minutes is recorded against CASE2222 with correct timestamps and user information.', 'Dependent Module/Process': 'Time Logging Module'}, {'Test Case ID': 'TC18-02', 'EPIC': 'Time Tracking', 'Feature': 'Case Time Logs', 'User Story': '18', 'Business Process': 'Case Management', 'Sub-Process Title': 'Time Tracking', 'Activity Title': 'Manual Time Logging', 'Test Scenario Title': 'Manually add a time log entry', 'Precondition': 'Case Manager is assigned to a case.', 'Test Data': {'Manual Time': '45 minutes', 'Date': '2024-06-15'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to CASE2222.', "Click 'Add Time Log'.", 'Enter 45 minutes for 2024-06-15.', 'Save entry.'], 'Expected Result': "45-minute manual log appears in the case's time log history with date and user info.", 'Dependent Module/Process': 'Time Logging Module'}, {'Test Case ID': 'TC18-03', 'EPIC': 'Time Tracking', 'Feature': 'Case Time Logs', 'User Story': '18', 'Business Process': 'Case Management', 'Sub-Process Title': 'Time Tracking', 'Activity Title': 'Edit or Delete Time Log', 'Test Scenario Title': 'Modify or delete a time log entry', 'Precondition': 'Case Manager has previously logged time for CASE2222.', 'Test Data': {'Time Log Entry ID': 'TL123', 'Original Time': '30 minutes'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to CASE2222 time logs.', 'Select time log TL123.', "Click 'Edit' and change to 25 minutes.", "Alternatively, click 'Delete'."], 'Expected Result': 'Edited time log is updated or, if deleted, is removed. All changes are audited.', 'Dependent Module/Process': 'Time Logging, Audit Trail'}, {'Test Case ID': 'TC18-04', 'EPIC': 'Time Tracking', 'Feature': 'Case Time Logs', 'User Story': '18', 'Business Process': 'Case Management', 'Sub-Process Title': 'Time Tracking', 'Activity Title': 'Unauthorized Time Log', 'Test Scenario Title': 'Attempt entry by unauthorized user', 'Precondition': 'User with Clerk role (no time logging permission) is logged in.', 'Test Data': {'Role': 'Clerk'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Clerk', 'Detailed Test Steps': ['Clerk logs in.', 'Navigates to a case.', 'Tries to log or edit time.'], 'Expected Result': "System denies access—'Action not permitted' message appears and no changes are made.", 'Dependent Module/Process': 'Role Permissions'}, {'Test Case ID': 'TC18-05', 'EPIC': 'Time Tracking', 'Feature': 'Case Time Logs', 'User Story': '18', 'Business Process': 'Case Management', 'Sub-Process Title': 'Time Tracking', 'Activity Title': 'Time Reporting', 'Test Scenario Title': 'Include all logs in workload report', 'Precondition': 'Multiple time logs recorded for several cases.', 'Test Data': {'Reports': 'Workload per case for June 2024'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Run workload report for June 2024.', 'Review per-case and per-user time totals.'], 'Expected Result': 'Report includes all logged times (manual and timer-based) for selected period, traceable to each case and user.', 'Dependent Module/Process': 'Reporting Module, Time Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>This user story covers the generation and download of an auto-generated PDF summary report detailing eligibility findings. The summary is intended for submission or presentation to supervisors, requires correct data representation, and must be available only to authorized Case Workers.</t>
+          <t>This user story aims to allow Case Workers to generate and print a checklist of required documents for different case types. This checklist can be provided to walk-in clients to guide them on necessary documents for their cases.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16: As a Case Worker, I want to generate a summary report of eligibility findings so that I can present it to supervisors. - Auto-generated PDF summary of case findings.</t>
+          <t>As a Case Worker, I want to print a checklist of required documents so that I can provide it to walk-in clients.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Case Worker selects an option to generate a report. The system compiles case data, formats it into a PDF, and makes it available for download or printing. The PDF contains all relevant eligibility findings and is correctly branded.</t>
+          <t>Case Worker selects a case type, generates the checklist, and prints it for the client.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC16.1', 'Brief Description': 'Generate PDF summary for a completed eligibility case (Valid Case Worker, complete data)'}, {'Test Case ID': 'TC16.2', 'Brief Description': 'Attempt PDF generation with incomplete/missing eligibility data'}, {'Test Case ID': 'TC16.3', 'Brief Description': 'Unauthorized user (not a Case Worker) tries to generate summary'}, {'Test Case ID': 'TC16.4', 'Brief Description': 'Verify that the PDF output matches the displayed case findings'}, {'Test Case ID': 'TC16.5', 'Brief Description': 'Verify PDF accessibility and compliance (e.g., Section 508)'}, {'Test Case ID': 'TC16.6', 'Brief Description': 'API endpoint for report generation returns expected response'}]</t>
+          <t>[{'Test Case ID': 'TC19-1', 'Brief Description': 'Checklist can be generated and printed for valid case types.'}, {'Test Case ID': 'TC19-2', 'Brief Description': 'Checklist shows correct documents based on case type.'}, {'Test Case ID': 'TC19-3', 'Brief Description': 'Checklist generation fails if invalid/unsupported case type is selected.'}, {'Test Case ID': 'TC19-4', 'Brief Description': 'Permissions restrict checklist printing to authorized Case Workers.'}, {'Test Case ID': 'TC19-5', 'Brief Description': 'Accessibility and printable format compliance (PDF, large font, etc.).'}]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC16.1', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'Generate PDF for complete eligibility case as Case Worker', 'Precondition': "User is logged in as Case Worker; case status is 'completed'; eligibility findings exist.", 'Test Data': {'CaseID': 'CASE1234', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Navigate to completed eligibility case (CASE1234)', "Click 'Generate Summary Report'", 'Wait for PDF to be generated', 'Download or preview report'], 'Expected Result': 'PDF is generated/downloaded. Content matches case data. File has correct branding, accessible format, timestamp.', 'Dependent Module/Process': 'Reporting Engine'}, {'Test Case ID': 'TC16.2', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'Handle cases with incomplete eligibility data', 'Precondition': 'User is logged in as Case Worker; case status is incomplete/missing key findings.', 'Test Data': {'CaseID': 'CASE5678', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker', 'Navigate to incomplete eligibility case (CASE5678)', 'Attempt to generate summary report'], 'Expected Result': 'System warns user of missing data. PDF is not produced or includes explicit note on missing info.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'TC16.3', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'Access control: Non-Case Worker attempts PDF generation', 'Precondition': 'User is logged in as Supervisor, Client, or other unauthorized role.', 'Test Data': {'CaseID': 'CASE3456', 'UserRole': 'Supervisor'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Login as Supervisor', 'Navigate to eligibility case (CASE3456)', 'Attempt to generate summary report'], 'Expected Result': 'Access denied; feature not available or error displayed.', 'Dependent Module/Process': 'Role-based Access Control'}, {'Test Case ID': 'TC16.4', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'PDF content accuracy and branding', 'Precondition': 'PDF generated for completed case', 'Test Data': {'CaseID': 'CASE1234', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open generated PDF', 'Cross-check data with screen/displayed case findings'], 'Expected Result': 'All data matches, layout meets standards, contains logo/legal statements.', 'Dependent Module/Process': 'PDF Rendering Service'}, {'Test Case ID': 'TC16.5', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Generate Eligibility Summary PDF', 'Test Scenario Title': 'PDF accessibility and compliance check', 'Precondition': 'PDF generated', 'Test Data': {'CaseID': 'CASE1234'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Inspect PDF for accessibility features (tags, searchability, screen reader compatibility)', 'Check for Section 508 or local accessibility compliance'], 'Expected Result': 'PDF meets accessibility requirements.', 'Dependent Module/Process': 'Compliance Module'}, {'Test Case ID': 'TC16.6', 'EPIC': 'Eligibility Determination', 'Feature': 'Reporting', 'User Story': '16', 'Business Process': 'Eligibility Review', 'Sub-Process Title': 'Reporting API', 'Activity Title': 'API-based Generation', 'Test Scenario Title': 'API call returns PDF and correct status', 'Precondition': 'API endpoint available; valid session token.', 'Test Data': {'CaseID': 'CASE1234', 'APIToken': 'VALID_TOKEN'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (API)', 'Detailed Test Steps': ['Submit API request with valid case ID', 'Verify HTTP response code and PDF file in response'], 'Expected Result': 'API returns 200 OK, PDF file is valid.', 'Dependent Module/Process': 'API Gateway'}]</t>
+          <t>[{'Test Case ID': 'TC19-1', 'EPIC': 'Document Management', 'Feature': 'Checklist Generation', 'User Story': 'US19', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Provision', 'Activity Title': 'Checklist Printing', 'Test Scenario Title': 'Generate and print checklist for valid case type', 'Precondition': 'Case Worker is logged in and is on the Document Checklist module.', 'Test Data': "Case Type: 'Housing Assistance'; Required documents configured in the system.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Document Checklist module.', "Select 'Housing Assistance' from case type dropdown.", "Click 'Generate Checklist'.", "Click 'Print' button."], 'Expected Result': 'Checklist displays all required documents for Housing Assistance and is sent to the printer in proper format.', 'Dependent Module/Process': 'Case Type Configuration'}, {'Test Case ID': 'TC19-2', 'EPIC': 'Document Management', 'Feature': 'Checklist Generation', 'User Story': 'US19', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Provision', 'Activity Title': 'Checklist Printing', 'Test Scenario Title': 'Checklist content matches configured documents for selected case type', 'Precondition': 'At least two case types are configured with different document requirements.', 'Test Data': "Case Type1: 'Housing Assistance'; Documents: A, B, C. Case Type2: 'Child Care'; Documents: X, Y.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Generate checklist for 'Housing Assistance' and inspect document list.", "Generate checklist for 'Child Care' and inspect document list."], 'Expected Result': 'Each checklist contains only the documents configured for the selected case type.', 'Dependent Module/Process': 'Case Type Configuration'}, {'Test Case ID': 'TC19-3', 'EPIC': 'Document Management', 'Feature': 'Checklist Generation', 'User Story': 'US19', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Provision', 'Activity Title': 'Checklist Printing', 'Test Scenario Title': 'Error on invalid/unsupported case type selection', 'Precondition': 'User is on Document Checklist module.', 'Test Data': "Case Type: 'Unrecognized Type'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Enter or select an invalid case type.', "Click 'Generate Checklist'."], 'Expected Result': 'Error message indicates unsupported type. Checklist is not generated.', 'Dependent Module/Process': 'Error Handling'}, {'Test Case ID': 'TC19-4', 'EPIC': 'Document Management', 'Feature': 'Checklist Generation', 'User Story': 'US19', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Provision', 'Activity Title': 'Checklist Printing', 'Test Scenario Title': 'Permission enforcement for printing', 'Precondition': 'User with insufficient permissions tries to access/print checklist.', 'Test Data': 'User role: Guest, unauthorized Case Worker.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest/Unauthorized', 'Detailed Test Steps': ['Log in as Guest or unauthorized user.', 'Attempt to access Document Checklist module or print checklist.'], 'Expected Result': 'Access denied message; checklist generation/printing is blocked.', 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'TC19-5', 'EPIC': 'Document Management', 'Feature': 'Checklist Generation', 'User Story': 'US19', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Provision', 'Activity Title': 'Checklist Printing', 'Test Scenario Title': 'Compliance with accessibility and print format requirements', 'Precondition': 'User is authorized to print checklist.', 'Test Data': 'Case Type: Any', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Generate and print checklist.', 'Check for ADA-compliant font size and logical structure in PDF/printout.'], 'Expected Result': 'Printed checklist meets accessibility (e.g., large print, PDF tags) and formatting standards.', 'Dependent Module/Process': 'Compliance Module'}]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>This user story ensures that Case Workers receive real-time notifications whenever a client uploads a document. The system must alert the appropriate Case Worker instantly and only for the cases they manage, with proper handling of unauthorized access and notification content.</t>
+          <t>This user story implements escalation of urgent cases with priority flags, allowing Case Managers to ensure supervisors are immediately notified and can act accordingly.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17: As a Case Worker, I want to receive alerts when a document is uploaded by a client so that I can review it promptly. - Real-time notifications for document uploads.</t>
+          <t>As a Case Manager, I want to escalate urgent cases to supervisors so that they receive immediate attention.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A client uploads a document linked to their case. The Case Worker assigned receives an immediate alert via the notification channel (in-app, email, or SMS). Notification provides document and client info.</t>
+          <t>Case Manager marks a case as urgent and escalates it, triggering notification to the assigned supervisor.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC17.1', 'Brief Description': 'Case Worker receives notification when client uploads document'}, {'Test Case ID': 'TC17.2', 'Brief Description': 'Case Worker does not receive notification for unrelated case document upload'}, {'Test Case ID': 'TC17.3', 'Brief Description': 'Unauthorized user does not receive document upload alert'}, {'Test Case ID': 'TC17.4', 'Brief Description': 'Notification content and usability (document ID, client info, timestamp)'}, {'Test Case ID': 'TC17.5', 'Brief Description': 'Test delay or failure in notification delivery'}, {'Test Case ID': 'TC17.6', 'Brief Description': 'Notification via API/WebSocket (integration with external notification service)'}]</t>
+          <t>[{'Test Case ID': 'TC20-1', 'Brief Description': 'Urgent case escalation triggers supervisor notification and priority flag.'}, {'Test Case ID': 'TC20-2', 'Brief Description': 'Only Case Managers can escalate cases; permissions enforced.'}, {'Test Case ID': 'TC20-3', 'Brief Description': 'Audit trail created for each escalation action.'}, {'Test Case ID': 'TC20-4', 'Brief Description': 'Cannot escalate already escalated/closed cases (negative).'}, {'Test Case ID': 'TC20-5', 'Brief Description': 'API call for escalation status returns correct priority flag and audit metadata.'}]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC17.1', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Alert Generation', 'Activity Title': 'Client uploads document, Case Worker notified', 'Test Scenario Title': 'Case Worker receives alert for relevant case', 'Precondition': 'Client and Case Worker linked via case assignment.', 'Test Data': {'CaseID': 'CASE2345', 'ClientID': 'CLIENT123', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Client', 'Navigate to case (CASE2345)', 'Upload document (e.g., proof_of_income.pdf)', 'Ensure upload completion', 'Login (switch to) Case Worker assigned to CASE2345', 'Check notifications'], 'Expected Result': 'Case Worker receives real-time alert about document upload with correct info.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'TC17.2', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Alert Filtering', 'Activity Title': 'Only relevant Case Worker notified', 'Test Scenario Title': 'Case Worker is not notified for non-assigned case uploads', 'Precondition': 'Case Worker is *not* assigned to CASE3456.', 'Test Data': {'CaseID': 'CASE3456', 'ClientID': 'CLIENT456', 'UserRole': 'CaseWorker'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Client', 'Upload document for CASE3456', 'Login as unrelated Case Worker', 'Check notifications'], 'Expected Result': 'No notification received for unassigned case.', 'Dependent Module/Process': 'Access Control/Assignment Logic'}, {'Test Case ID': 'TC17.3', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Permission Checking', 'Activity Title': 'Notification only sent to authorized users', 'Test Scenario Title': 'Unauthorized user/non-Case Worker does not get notifications', 'Precondition': 'User logged in as Supervisor or Client.', 'Test Data': {'UserRole': 'Supervisor'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor/Client', 'Detailed Test Steps': ['Login as Client/Supervisor', 'Trigger document upload on any case', 'Monitor for notifications'], 'Expected Result': 'No notification appears for unauthorized roles.', 'Dependent Module/Process': 'Notification Filtering'}, {'Test Case ID': 'TC17.4', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Alert Content Verification', 'Activity Title': 'Correctness of alert content', 'Test Scenario Title': 'Notification textual accuracy and completeness', 'Precondition': 'Case Worker receives document upload alert.', 'Test Data': {'CaseID': 'CASE2345', 'DocName': 'proof_of_income.pdf'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Check notification content after upload', 'Verify presence of document name, upload time, client ID'], 'Expected Result': 'Alert details are accurate and complete.', 'Dependent Module/Process': 'Notification Formatting'}, {'Test Case ID': 'TC17.5', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Notification Delivery', 'Activity Title': 'Test response to notification service outage or delay', 'Test Scenario Title': 'Simulate notification delay/failure', 'Precondition': 'Notification system integration enabled.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger document upload', 'Simulate delay or downtime in notification service', 'Observe case worker notification panel'], 'Expected Result': 'Notifications delayed, error logged or fallback path invoked. No duplicate/malformed alerts.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC17.6', 'EPIC': 'Document Management', 'Feature': 'Notifications', 'User Story': '17', 'Business Process': 'Document Upload', 'Sub-Process Title': 'API/WebSocket Integration', 'Activity Title': 'Notification via API/WebSocket', 'Test Scenario Title': 'Verify notification API/WebSocket message arrives', 'Precondition': 'API endpoint available, Case Worker session WebSocket open.', 'Test Data': {'CaseID': 'CASE2345'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (API)', 'Detailed Test Steps': ['Initiate WebSocket/API listener as Case Worker', 'Upload document as Client for linked case', 'Validate receipt of message'], 'Expected Result': 'Notification payload received in real time.', 'Dependent Module/Process': 'Notification API/WebSocket Service'}]</t>
+          <t>[{'Test Case ID': 'TC20-1', 'EPIC': 'Case Handling', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Escalation', 'Activity Title': 'Escalate Urgent Case', 'Test Scenario Title': 'Escalation of urgent cases triggers supervisor notification', 'Precondition': 'Case Manager is logged in and viewing a case eligible for escalation.', 'Test Data': 'Case ID: 12345; Status: Open; Supervisor ID: S5678.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to case 12345 details.', "Click 'Escalate' button.", 'Set urgency flag and confirm escalation.'], 'Expected Result': 'Case displays as escalated. Supervisor S5678 receives real-time notification with priority indicator.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC20-2', 'EPIC': 'Case Handling', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Role Permissions', 'Activity Title': 'Enforce Escalation Rights', 'Test Scenario Title': 'Only Case Managers can escalate cases', 'Precondition': 'User is logged in with various roles.', 'Test Data': 'Roles: Case Worker, Case Manager, Supervisor', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Multiple', 'Detailed Test Steps': ['Log in as Case Worker. Attempt to escalate a case.', 'Log in as Supervisor. Attempt to escalate a case.', 'Log in as Case Manager. Attempt to escalate a case.'], 'Expected Result': "Only Case Manager can access and use the 'Escalate' functionality.", 'Dependent Module/Process': 'User Permissions'}, {'Test Case ID': 'TC20-3', 'EPIC': 'Case Handling', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Log Escalation Actions', 'Test Scenario Title': 'Audit log is created for every escalation event', 'Precondition': 'Audit trail module enabled.', 'Test Data': 'Case ID: Any', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Escalate a case.', 'Retrieve audit logs for the case.'], 'Expected Result': 'Audit trail logs timestamp, user ID, case ID, and action details for escalation.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC20-4', 'EPIC': 'Case Handling', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Business Logic Validation', 'Activity Title': 'Enforce Escalation Constraints', 'Test Scenario Title': 'Cannot escalate already escalated or closed cases', 'Precondition': 'Case already escalated or status = closed.', 'Test Data': 'Case ID: Closed or escalated', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Attempt to escalate case with status 'Closed' or 'Escalated'."], 'Expected Result': 'System displays error indicating escalation not permitted.', 'Dependent Module/Process': 'Case Status Validation'}, {'Test Case ID': 'TC20-5', 'EPIC': 'Case Handling', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management API', 'Sub-Process Title': 'Get Escalation Status', 'Activity Title': 'API Check', 'Test Scenario Title': 'API returns priority flag and audit details for escalated cases', 'Precondition': 'Escalated case exists; API endpoint accessible.', 'Test Data': 'Case ID: Escalated', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'API Client (Service)', 'Detailed Test Steps': ['Call GET /cases/{id} API.', 'Check response for escalation priority flag and audit metadata.'], 'Expected Result': 'API response includes priority flag and audit/log meta.', 'Dependent Module/Process': 'API, Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>This user story supports workload tracking by allowing Case Managers to record time spent on each case. The system should support both manual time entry and automated timers, restrict data visibility to authorized users, and ensure auditability of time logs for accurate reporting.</t>
+          <t>This user story enables automated validation of uploaded documents using OCR and metadata checks, helping Case Workers reduce manual effort, catch errors, and ensure file integrity and conformity.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18: As a Case Manager, I want to track the time spent on each case so that I can report on workload. - Timer or manual entry of time logs per case.</t>
+          <t>As a Case Worker, I want to auto-validate uploaded documents so that I can reduce manual review time.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Case Manager opens a case, starts/stops a timer to log time or enters time manually. Log is saved and reflected in workload reports. Only the assigned or authorized Case Manager may record/view logs.</t>
+          <t>Case Worker uploads a correctly formatted document; OCR and metadata validation succeed; document marked as valid.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC18.1', 'Brief Description': 'Start and stop timer, verify time logged'}, {'Test Case ID': 'TC18.2', 'Brief Description': 'Manually enter time for a case'}, {'Test Case ID': 'TC18.3', 'Brief Description': 'Attempt to log/edit time as unauthorized user'}, {'Test Case ID': 'TC18.4', 'Brief Description': 'View summarized time logs in workload report'}, {'Test Case ID': 'TC18.5', 'Brief Description': 'API test: time log entry and retrieval'}, {'Test Case ID': 'TC18.6', 'Brief Description': 'Audit compliance: time log history is immutable and traceable'}]</t>
+          <t>[{'Test Case ID': 'TC21-1', 'Brief Description': 'Valid document passes OCR and metadata checks; accepted automatically.'}, {'Test Case ID': 'TC21-2', 'Brief Description': 'Invalid format document (corrupt/unsupported) is rejected with error.'}, {'Test Case ID': 'TC21-3', 'Brief Description': 'Document fails OCR (unreadable/scanned poorly); flagged for manual review.'}, {'Test Case ID': 'TC21-4', 'Brief Description': 'Document missing required metadata is rejected.'}, {'Test Case ID': 'TC21-5', 'Brief Description': 'Audit log records validation outcome and user actions for compliance.'}]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC18.1', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'Active Timing', 'Activity Title': 'Start/Stop Timer', 'Test Scenario Title': 'Timer records elapsed work time correctly', 'Precondition': 'Case exists; Case Manager assigned.', 'Test Data': {'CaseID': 'CASE7890', 'UserRole': 'CaseManager'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to case (CASE7890)', "Click 'Start Timer'", 'Perform some work for several minutes', "Click 'Stop Timer'", 'Check time log entry'], 'Expected Result': 'Elapsed time is logged accurately; entry saved with timestamp and user info.', 'Dependent Module/Process': 'Time Logging Service'}, {'Test Case ID': 'TC18.2', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'Manual Entry', 'Activity Title': 'Manually log time', 'Test Scenario Title': 'Manual time entry for a case', 'Precondition': 'Case exists; user is Case Manager.', 'Test Data': {'CaseID': 'CASE7890', 'TimeSpent': '01:30'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Open CASE7890', "Select 'Manual Time Entry'", "Enter '1 hour 30 minutes'", 'Save log'], 'Expected Result': 'Time log created with entered value, timestamped, user attributed.', 'Dependent Module/Process': 'Time Logging Service'}, {'Test Case ID': 'TC18.3', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict time logging to authorized users', 'Test Scenario Title': 'Unauthorized user attempts to log/edit time', 'Precondition': 'User is not assigned Case Manager on CASE7890.', 'Test Data': {'CaseID': 'CASE7890', 'UserRole': 'Supervisor'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Login as Supervisor', 'Open CASE7890', 'Attempt to start timer or enter time manually'], 'Expected Result': 'Time logging/edit controls unavailable or action denied with error.', 'Dependent Module/Process': 'Role-based Access'}, {'Test Case ID': 'TC18.4', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Reporting', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Summarize case time logs', 'Test Scenario Title': 'View time logs in workload report', 'Precondition': 'Time logs recorded for several cases', 'Test Data': [{'CaseID': 'CASE7890', 'TimeLogged': '01:30'}, {'CaseID': 'CASE6789', 'TimeLogged': '02:15'}], 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Open workload report/dashboard', 'Review summary by case and total time'], 'Expected Result': 'Workload report accurately sums times from all entries.', 'Dependent Module/Process': 'Reporting'}, {'Test Case ID': 'TC18.5', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Case Work Tracking', 'Sub-Process Title': 'API Integration', 'Activity Title': 'Time log via API', 'Test Scenario Title': 'Submit and retrieve time log using API', 'Precondition': 'Time Logging API available; valid API token.', 'Test Data': {'CaseID': 'CASE7890', 'TimeSpent': '00:45', 'APIToken': 'VALID'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager (API)', 'Detailed Test Steps': ['POST time log to API (CASE7890, 00:45)', 'GET time logs for CASE7890 via API'], 'Expected Result': 'API returns success, log retrievable and reflects correct data.', 'Dependent Module/Process': 'API Gateway'}, {'Test Case ID': 'TC18.6', 'EPIC': 'Workload Management', 'Feature': 'Time Tracking', 'User Story': '18', 'Business Process': 'Audit/Compliance', 'Sub-Process Title': 'Immutability', 'Activity Title': 'Audit time log history', 'Test Scenario Title': 'Ensure logs are immutable, auditable', 'Precondition': 'Existing time logs for a case; audit log feature enabled.', 'Test Data': {'CaseID': 'CASE7890'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Admin', 'Detailed Test Steps': ['Login as Audit Admin', 'Retrieve time log history for CASE7890', 'Attempt to modify/delete existing entry', 'Review system audit trail'], 'Expected Result': 'Time logs are read-only after creation; audit trail captures all access and attempted edits.', 'Dependent Module/Process': 'Audit Log/Compliance Module'}]</t>
+          <t>[{'Test Case ID': 'TC21-1', 'EPIC': 'Document Management', 'Feature': 'Auto-Validation of Documents', 'User Story': 'US21', 'Business Process': 'Document Submission', 'Sub-Process Title': 'Upload', 'Activity Title': 'Auto Validation', 'Test Scenario Title': 'Valid document passes OCR and metadata checks', 'Precondition': 'Case Worker logged in; Upload module accessible.', 'Test Data': 'PDF file, with valid text content and complete metadata (name, date, type).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Browse and select valid PDF file.', 'Upload document via upload module.', 'Wait for auto-validation feedback.'], 'Expected Result': 'System validates document using OCR and metadata checks; document is automatically marked as valid and available for further processing.', 'Dependent Module/Process': 'OCR Engine, Metadata Validation'}, {'Test Case ID': 'TC21-2', 'EPIC': 'Document Management', 'Feature': 'Auto-Validation of Documents', 'User Story': 'US21', 'Business Process': 'Document Submission', 'Sub-Process Title': 'Upload', 'Activity Title': 'Auto Validation', 'Test Scenario Title': 'Corrupt or unsupported file format is rejected', 'Precondition': 'Case Worker logged in.', 'Test Data': 'File: corrupt.docx or unsupported format (e.g., .exe).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to upload corrupt or unsupported file.', 'Observe validation feedback.'], 'Expected Result': 'System shows error and does not accept the file.', 'Dependent Module/Process': 'File Type Validation'}, {'Test Case ID': 'TC21-3', 'EPIC': 'Document Management', 'Feature': 'Auto-Validation of Documents', 'User Story': 'US21', 'Business Process': 'Document Submission', 'Sub-Process Title': 'Upload', 'Activity Title': 'Auto Validation', 'Test Scenario Title': 'Poorly scanned or OCR-unreadable document flagged for review', 'Precondition': 'OCR engine is online.', 'Test Data': 'PDF image scan with low resolution/blurry text.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload low-quality scanned PDF document.', 'Wait for OCR and metadata validation.', 'Check system output/flag.'], 'Expected Result': "System flags document as 'Needs manual review', logs OCR issue.", 'Dependent Module/Process': 'OCR Engine'}, {'Test Case ID': 'TC21-4', 'EPIC': 'Document Management', 'Feature': 'Auto-Validation of Documents', 'User Story': 'US21', 'Business Process': 'Document Submission', 'Sub-Process Title': 'Upload', 'Activity Title': 'Auto Validation', 'Test Scenario Title': 'Missing mandatory metadata triggers rejection', 'Precondition': 'Case Worker logged in.', 'Test Data': 'PDF without required metadata field (e.g., document type missing).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload PDF with incomplete metadata.', 'Observe feedback.'], 'Expected Result': 'System rejects document, displays error indicating missing metadata.', 'Dependent Module/Process': 'Metadata Validation'}, {'Test Case ID': 'TC21-5', 'EPIC': 'Document Management', 'Feature': 'Auto-Validation of Documents', 'User Story': 'US21', 'Business Process': 'Document Submission', 'Sub-Process Title': 'Upload', 'Activity Title': 'Auto Validation', 'Test Scenario Title': 'Audit log captures validation actions for compliance', 'Precondition': 'Audit log module enabled.', 'Test Data': 'Any upload event.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload a document (valid/invalid).', 'Retrieve related audit logs.'], 'Expected Result': 'Audit log records user ID, upload timestamp, validation result, and action taken (accepted, flagged, rejected).', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>This story enables case workers to quickly generate and print client-facing checklists of required documents for specific case types, supporting clear guidance and streamlining the intake process for walk-in clients.</t>
+          <t>This user story focuses on enhancing efficiency for Case Workers by providing AI-driven suggestions for missing fields in applications, enabling quicker and more accurate completion.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19: As a Case Worker, I want to print a checklist of required documents so that I can provide it to walk-in clients.</t>
+          <t>As a Case Worker, I want to receive suggestions for missing fields in applications so that I can complete them faster. (AI-based field completion suggestions)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Case Worker selects a case type, views the corresponding checklist of required documents, and prints it for a walk-in client.</t>
+          <t>Case Worker opens an incomplete application and receives intelligent suggestions for missing fields, which can be reviewed and approved.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US19_TC01', 'Brief Description': 'Checklist generated and printed for selected case type (happy path)'}, {'Test Case ID': 'US19_TC02', 'Brief Description': 'Checklist generation fails with undefined or unsupported case type'}, {'Test Case ID': 'US19_TC03', 'Brief Description': 'Print preview and functionality works as expected'}, {'Test Case ID': 'US19_TC04', 'Brief Description': 'User tries to print without selecting a case type'}, {'Test Case ID': 'US19_TC05', 'Brief Description': 'User (not Case Worker) attempts to access/print checklist (permission denied)'}]</t>
+          <t>[{'Test Case ID': '22-FUNC-1', 'Brief Description': 'AI displays suggestions for all missing mandatory fields when editing an application.'}, {'Test Case ID': '22-FUNC-2', 'Brief Description': 'AI does not display suggestions for already-completed fields.'}, {'Test Case ID': '22-FUNC-3', 'Brief Description': 'Case Worker can accept or reject a suggestion.'}, {'Test Case ID': '22-FUNC-4', 'Brief Description': 'System logs all AI-generated suggestions for audit purposes.'}, {'Test Case ID': '22-NEG-1', 'Brief Description': 'No suggestions are displayed if the AI model is unavailable; application editing is still possible.'}, {'Test Case ID': '22-PERM-1', 'Brief Description': 'Only Case Worker roles can access and apply AI suggestions.'}, {'Test Case ID': '22-API-1', 'Brief Description': 'System sends incomplete application data to AI API and receives suggestions.'}]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US19_TC01', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Document Information Capture', 'Activity Title': 'Checklist Generation &amp; Printing', 'Test Scenario Title': 'Checklist is generated and printed for selected case type', 'Precondition': 'User is logged in as Case Worker; at least one case type with checklist exists.', 'Test Data': "{CaseType: 'Family Assistance', Checklist: ['Proof of ID', 'Proof of Income', 'Residence Verification']}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Checklist Feature.', "Select 'Family Assistance' as case type.", 'System displays printable checklist based on case type.', 'Click Print button.'], 'Expected Result': "Printable checklist is displayed; clicking 'Print' sends document to printer.", 'Dependent Module/Process': 'Document Templates, Role Permissions'}, {'Test Case ID': 'US19_TC02', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Document Information Capture', 'Activity Title': 'Checklist Generation', 'Test Scenario Title': 'Checklist generation fails for undefined or unsupported case type', 'Precondition': 'User is logged in as Case Worker.', 'Test Data': "{CaseType: 'Alien Registration', Checklist: null}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Checklist Feature.', "Select 'Alien Registration' as case type.", 'Attempt to generate checklist.'], 'Expected Result': "System displays message: 'Checklist for selected case type not available.' Print option is disabled.", 'Dependent Module/Process': 'Document Templates, Error Handling'}, {'Test Case ID': 'US19_TC03', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Checklist Printing', 'Activity Title': 'Checklist Print Preview', 'Test Scenario Title': 'Print preview and print functionality', 'Precondition': 'Checklist is generated; printer is connected.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ["With checklist generated, click 'Print'.", 'Preview is shown.', "Click 'Confirm' on preview dialog."], 'Expected Result': 'Checklist is printed as per preview. Document layout matches template.', 'Dependent Module/Process': 'Printing Service, Document Templates'}, {'Test Case ID': 'US19_TC04', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Checklist Validation', 'Activity Title': 'Print Attempt Without Selection', 'Test Scenario Title': 'Attempt to print without selecting case type', 'Precondition': 'User is on checklist screen, no case type selected.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Do not select case type.', "Click 'Print'."], 'Expected Result': "System displays validation message: 'Please select a case type.' Print action is blocked.", 'Dependent Module/Process': 'UI Validation'}, {'Test Case ID': 'US19_TC05', 'EPIC': 'Client Intake', 'Feature': 'Document Checklist', 'User Story': 'US19', 'Business Process': 'Client Onboarding', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Unauthorized Access Attempt', 'Test Scenario Title': 'Non-authorized user attempts to generate or print checklist', 'Precondition': 'User logged in as a role other than Case Worker.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CHECKLIST_PRINT', 'User Role': 'Receptionist', 'Detailed Test Steps': ['Attempt to access Checklist feature.', 'Try to generate and print checklist.'], 'Expected Result': 'Access is denied; system logs attempt for audit.', 'Dependent Module/Process': 'Role Permissions, Security Logging'}]</t>
+          <t>[{'Test Case ID': '22-FUNC-1', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'Application Data Entry', 'Sub-Process Title': 'Edit Application', 'Activity Title': 'Receive AI Suggestions', 'Test Scenario Title': 'Display suggestions for missing mandatory fields', 'Precondition': 'User is logged in as Case Worker and has access to an incomplete application.', 'Test Data': 'Application with several empty mandatory fields; Case Worker credentials.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker.', '2. Open an incomplete application.', '3. Observe suggestions for missing fields appear via UI popover or sidebar.', '4. Review suggested values.'], 'Expected Result': 'Field suggestions are displayed for all missing mandatory fields. Only empty/invalid fields are suggested.', 'Dependent Module/Process': 'AI Engine / Backend Suggestions API'}, {'Test Case ID': '22-FUNC-2', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'Application Data Entry', 'Sub-Process Title': 'Edit Application', 'Activity Title': 'Receive AI Suggestions', 'Test Scenario Title': 'No suggestions for already completed or valid fields', 'Precondition': 'User is editing an application with some or all fields completed.', 'Test Data': 'Completed application.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as Case Worker.', '2. Open a completed application.', '3. Verify no suggestions are shown for completed fields.'], 'Expected Result': 'No field suggestions are provided for already-completed or valid fields.', 'Dependent Module/Process': 'AI Engine'}, {'Test Case ID': '22-FUNC-3', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'Application Data Entry', 'Sub-Process Title': 'Edit Application', 'Activity Title': 'Receive AI Suggestions', 'Test Scenario Title': 'Accept or reject AI suggestion', 'Precondition': 'User is presented with AI suggestions.', 'Test Data': 'Incomplete application.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Review suggestions for missing fields.', '2. Accept a suggestion for a given field.', '3. Confirm the field is completed with AI value.', '4. Reject a suggestion for another field.', '5. Verify the field remains blank.'], 'Expected Result': 'Accepted suggestion populates the field; rejected suggestion does not alter application.', 'Dependent Module/Process': 'Application Form UI'}, {'Test Case ID': '22-FUNC-4', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'Application Data Entry', 'Sub-Process Title': 'Edit Application', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Audit suggestion logs', 'Precondition': 'User interacts with AI suggestions.', 'Test Data': 'Case Worker accepts and rejects suggestions.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Accept and reject several suggestions.', '2. Access audit logs.', '3. Search for suggestion actions.'], 'Expected Result': 'Audit log records actions: suggestions shown, accepted, or rejected, with timestamp and user ID (for regulatory compliance).', 'Dependent Module/Process': 'Audit/Logging Engine'}, {'Test Case ID': '22-NEG-1', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'Application Data Entry', 'Sub-Process Title': 'Edit Application', 'Activity Title': 'AI Suggestion Failure', 'Test Scenario Title': 'No suggestions if AI service is unavailable', 'Precondition': 'AI backend is offline or unreachable.', 'Test Data': 'Any incomplete application.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Open incomplete application.', '2. Observe system behaviour.', '3. Try to submit application.'], 'Expected Result': 'AI suggestions are not displayed; regular editing is still available (with error notification displayed).', 'Dependent Module/Process': 'AI Service'}, {'Test Case ID': '22-PERM-1', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role Validation', 'Activity Title': 'Enforce permissions', 'Test Scenario Title': 'Restrict AI suggestions to Case Worker role', 'Precondition': 'User is not a Case Worker.', 'Test Data': 'Other user roles: Case Manager, Admin.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager, Admin', 'Detailed Test Steps': ['1. Log in as Case Manager or Admin.', '2. Open incomplete application.', '3. Verify AI suggestions are not available.'], 'Expected Result': 'AI suggestions are not shown to unauthorized roles.', 'Dependent Module/Process': 'Authorization'}, {'Test Case ID': '22-API-1', 'EPIC': 'AI-Assisted Case Management', 'Feature': 'Field Completion Suggestions', 'User Story': '22', 'Business Process': 'API Integration', 'Sub-Process Title': 'Suggest Fields', 'Activity Title': 'AI Suggestion API', 'Test Scenario Title': 'Application invokes AI API correctly', 'Precondition': 'Application is incomplete; service is running.', 'Test Data': 'Incomplete application JSON.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Submit incomplete application record to suggestion API.', '2. Capture input/output payload.', '3. Validate returned suggestions correspondence.'], 'Expected Result': 'API receives correct incomplete data, returns relevant suggestions for only missing fields.', 'Dependent Module/Process': 'AI Suggestion API'}]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>This story provides a workflow for Case Managers to escalate urgent cases to supervisors, ensuring priority cases receive rapid attention through a formalized escalation and notification mechanism.</t>
+          <t>This user story enhances the Case Manager dashboard, enabling users to filter clients by eligibility status (pending, approved, expired) to streamline outreach prioritization.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20: As a Case Manager, I want to escalate urgent cases to supervisors so that they receive immediate attention.</t>
+          <t>As a Case Manager, I want to filter clients by eligibility status so that I can prioritize outreach. (Filter dashboard by status: pending, approved, expired)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Case Manager marks a case as urgent and escalates it. Supervisor is notified and the case status updates accordingly.</t>
+          <t>Case Manager views the dashboard, applies 'approved' filter, and sees only approved clients listed, improving focus for outreach.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US20_TC01', 'Brief Description': 'Successful escalation of urgent case to supervisor'}, {'Test Case ID': 'US20_TC02', 'Brief Description': 'Non-urgent cases cannot be escalated'}, {'Test Case ID': 'US20_TC03', 'Brief Description': 'Supervisor receives notification upon escalation'}, {'Test Case ID': 'US20_TC04', 'Brief Description': 'User attempts escalation without sufficient permission'}, {'Test Case ID': 'US20_TC05', 'Brief Description': 'Escalation action fails due to system error (error handling)'}]</t>
+          <t>[{'Test Case ID': '23-FUNC-1', 'Brief Description': "Case Manager filters dashboard by 'pending' status and sees only pending clients."}, {'Test Case ID': '23-FUNC-2', 'Brief Description': "Case Manager filters dashboard by 'approved' status and sees only approved clients."}, {'Test Case ID': '23-FUNC-3', 'Brief Description': "Case Manager filters dashboard by 'expired' status and sees only expired clients."}, {'Test Case ID': '23-NEG-1', 'Brief Description': 'Applying a filter when no clients match shows an empty result set with informative message.'}, {'Test Case ID': '23-PERM-1', 'Brief Description': 'Only Case Manager can access and use the eligibility status filters.'}, {'Test Case ID': '23-API-1', 'Brief Description': 'Filter criteria are sent correctly to backend API and results match filter.'}, {'Test Case ID': '23-E2E-1', 'Brief Description': 'Full process: changing eligibility status and verifying dashboard updates accordingly.'}]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US20_TC01', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Review', 'Activity Title': 'Mark &amp; Escalate Case', 'Test Scenario Title': 'Successful urgent case escalation', 'Precondition': "User is logged in as Case Manager; assigned case exists with status 'Open'.", 'Test Data': "{CaseID: 10234, Priority: 'Urgent'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to assigned case.', "Mark case as 'Urgent' using priority flag.", "Click 'Escalate to Supervisor'.", 'Confirm escalation.'], 'Expected Result': "Case status updated to 'Escalated.' Supervisor receives notification.", 'Dependent Module/Process': 'Notification Service, Case Workflows'}, {'Test Case ID': 'US20_TC02', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Review', 'Activity Title': 'Escalation Criteria Validation', 'Test Scenario Title': 'Attempt to escalate non-urgent case', 'Precondition': "User is logged in as Case Manager; assigned case exists with status 'Open'.", 'Test Data': "{CaseID: 10555, Priority: 'Normal'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to assigned case.', "Attempt to escalate case not marked as 'Urgent'."], 'Expected Result': 'Escalation option is disabled or warning message displayed.', 'Dependent Module/Process': 'UI Validation, Case Workflows'}, {'Test Case ID': 'US20_TC03', 'EPIC': 'Case Escalation', 'Feature': 'Supervisor Notification', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation Notification', 'Activity Title': 'Supervisor Notification Handling', 'Test Scenario Title': 'Supervisor receives real-time escalation notification', 'Precondition': 'Supervisor is logged in; escalation trigger generated.', 'Test Data': "{SupervisorID: 9902, CaseID: 11012, Escalation: 'Urgent'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Case Manager escalates case.', 'Check supervisor notifications panel.'], 'Expected Result': 'Supervisor receives notification with case details and urgency.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'US20_TC04', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Unauthorized Escalation Attempt', 'Test Scenario Title': 'User without escalation permission attempts to escalate', 'Precondition': 'Logged in as user with no escalation rights (e.g., Case Worker).', 'Test Data': '{CaseID: 12367}', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to escalate an open case.'], 'Expected Result': 'Escalation option not visible or access denied error shown and logged for audit.', 'Dependent Module/Process': 'Role Permissions, Security Logging'}, {'Test Case ID': 'US20_TC05', 'EPIC': 'Case Escalation', 'Feature': 'Escalation Workflow', 'User Story': 'US20', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation Error Handling', 'Activity Title': 'System Error During Escalation', 'Test Scenario Title': 'Escalation fails due to backend or system error', 'Precondition': 'Backend service temporarily unavailable.', 'Test Data': "{CaseID: 14991, Priority: 'Urgent'}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_CASE_MANAGE', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Attempt to escalate urgent case.', 'Simulate backend outage or delay.'], 'Expected Result': 'Error is displayed, escalation is not processed, user is advised to retry. Error is logged for audit.', 'Dependent Module/Process': 'Error Handling, Logging'}]</t>
+          <t>[{'Test Case ID': '23-FUNC-1', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Review', 'Sub-Process Title': 'Dashboard Filtering', 'Activity Title': 'Apply pending filter', 'Test Scenario Title': 'Filter by pending status', 'Precondition': 'Case Manager is logged in; dashboard contains clients with multiple statuses.', 'Test Data': 'Clients with statuses: pending, approved, expired.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Log in as Case Manager.', '2. Go to client dashboard.', "3. Click 'Filter' and select 'Pending'.", '4. Observe resulting client list.'], 'Expected Result': "Only clients with 'pending' status are visible.", 'Dependent Module/Process': 'Dashboard Filter Backend API'}, {'Test Case ID': '23-FUNC-2', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Review', 'Sub-Process Title': 'Dashboard Filtering', 'Activity Title': 'Apply approved filter', 'Test Scenario Title': 'Filter by approved status', 'Precondition': "Clients exist with 'approved' status.", 'Test Data': "Clients with status 'approved'.", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["1. Select 'Approved' in the filter options.", '2. Observe displayed client list.', '3. Optionally, cross-reference with records.'], 'Expected Result': "Only 'approved' status clients are shown.", 'Dependent Module/Process': 'Dashboard Filter Backend API'}, {'Test Case ID': '23-FUNC-3', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Review', 'Sub-Process Title': 'Dashboard Filtering', 'Activity Title': 'Apply expired filter', 'Test Scenario Title': 'Filter by expired status', 'Precondition': "Clients exist with 'expired' status.", 'Test Data': "Clients with status 'expired'.", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["1. Select 'Expired' filter.", '2. Verify resulting client list.', '3. Cross-reference with expected records.'], 'Expected Result': "Only 'expired' status records are visible.", 'Dependent Module/Process': 'Dashboard Filter Backend API'}, {'Test Case ID': '23-NEG-1', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Review', 'Sub-Process Title': 'Dashboard Filtering', 'Activity Title': 'Empty filter result', 'Test Scenario Title': 'No clients for a selected status', 'Precondition': 'All clients are not in selected status.', 'Test Data': "No clients with status 'pending'.", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["1. Apply filter for a status not present (e.g., 'pending').", '2. Observe dashboard.', '3. Review message shown.'], 'Expected Result': "Empty dashboard with message like 'No clients found for this status.'", 'Dependent Module/Process': 'Dashboard Filter UI logic'}, {'Test Case ID': '23-PERM-1', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role Permissions', 'Activity Title': 'Enforce filter permissions', 'Test Scenario Title': 'Restrict filters to Case Manager role', 'Precondition': 'User with non-Case Manager role.', 'Test Data': 'Other roles (Case Worker, Admin).', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker, Admin', 'Detailed Test Steps': ['1. Attempt to access dashboard filters as other user roles.', '2. Observe filter availability.', '3. Try applying a filter if possible.'], 'Expected Result': 'Eligibility status filters are disabled or hidden for unauthorized roles.', 'Dependent Module/Process': 'Authorization'}, {'Test Case ID': '23-API-1', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'API Integration', 'Sub-Process Title': 'Filter Clients', 'Activity Title': 'Filter API Request', 'Test Scenario Title': 'API receives and processes filter correctly', 'Precondition': 'Backend API for filtering is operational.', 'Test Data': "API call filter: status='approved'.", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["1. Apply 'approved' filter in UI.", '2. Capture network request.', '3. Inspect query parameters/payload.', '4. Verify API response matches filter.'], 'Expected Result': "Filter parameter 'status=approved' is sent; response contains only matching clients.", 'Dependent Module/Process': 'Dashboard API'}, {'Test Case ID': '23-E2E-1', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'End-to-End Client Status Update', 'Sub-Process Title': 'Change Status', 'Activity Title': 'Verify dashboard update', 'Test Scenario Title': 'End-to-end status change reflects in filter results', 'Precondition': "At least one client is in 'pending' status.", 'Test Data': 'Client with mutable status.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["1. Change client status from 'pending' to 'approved' in appropriate module.", "2. Revisit dashboard and apply 'approved' filter.", "3. Confirm client is now listed under 'approved'.", "4. Apply 'pending' filter to ensure client no longer appears."], 'Expected Result': 'Dashboard accurately reflects status changes through filter.', 'Dependent Module/Process': 'Status Update Module'}]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>This story automates the validation of uploaded documents through OCR and metadata checks, supporting a reduction in manual review time and improving accuracy at document intake.</t>
+          <t>This user story enables Case Workers to upload multiple documents at once for multiple cases, improving efficiency with a robust matching logic for document-to-case association.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21: As a Case Worker, I want to auto-validate uploaded documents so that I can reduce manual review time.</t>
+          <t>As a Case Worker, I want to bulk upload documents for multiple cases so that I can save time. (Batch upload with case matching logic)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Case Worker uploads a document, the system performs OCR and metadata validation, and marks the document as valid if checks pass.</t>
+          <t>Case Worker selects and uploads multiple documents, the system matches documents to relevant cases, and uploads succeed in batch.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US21_TC01', 'Brief Description': 'Successful OCR and metadata validation on acceptable document'}, {'Test Case ID': 'US21_TC02', 'Brief Description': 'Document fails validation due to missing/incorrect metadata'}, {'Test Case ID': 'US21_TC03', 'Brief Description': 'Uploaded file is unreadable/invalid format (OCR failure)'}, {'Test Case ID': 'US21_TC04', 'Brief Description': 'Unauthorized user attempts to upload/validate document'}, {'Test Case ID': 'US21_TC05', 'Brief Description': 'Audit log is created for every validation attempt (compliance)'}]</t>
+          <t>[{'Test Case ID': '24-FUNC-1', 'Brief Description': 'Case Worker uploads batch files, system matches each document to correct case.'}, {'Test Case ID': '24-FUNC-2', 'Brief Description': 'Case Worker receives summary of upload: successful and failed matches.'}, {'Test Case ID': '24-FUNC-3', 'Brief Description': 'System allows user to manually reassign unmatched documents.'}, {'Test Case ID': '24-NEG-1', 'Brief Description': 'System handles invalid or corrupted documents gracefully, not blocking other uploads.'}, {'Test Case ID': '24-PERM-1', 'Brief Description': 'Bulk upload option only appears for Case Workers.'}, {'Test Case ID': '24-API-1', 'Brief Description': 'Bulk upload API processes multi-file payloads and returns detailed result.'}, {'Test Case ID': '24-COMP-1', 'Brief Description': 'Audit log records all bulk document uploads with file metadata for compliance.'}]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US21_TC01', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Intake', 'Activity Title': 'Upload and Validate', 'Test Scenario Title': 'Successful OCR and metadata validation', 'Precondition': 'User logged in as Case Worker; auto-validation feature enabled.', 'Test Data': "{Filename: 'id_proof.pdf', Type: 'PDF', Metadata: {ClientID: 101, DateOfBirth: '1992-04-05'}}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to document upload screen.', "Upload 'id_proof.pdf' with required metadata.", 'System performs OCR and checks metadata matches client profile.', 'Validation status is displayed.'], 'Expected Result': 'Document is marked valid; system displays success message and stores document.', 'Dependent Module/Process': 'OCR Engine, Metadata Parser'}, {'Test Case ID': 'US21_TC02', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Intake', 'Activity Title': 'Metadata Error Handling', 'Test Scenario Title': 'Document fails validation due to missing or incorrect metadata', 'Precondition': 'User logged in as Case Worker.', 'Test Data': "{Filename: 'income_statement.pdf', Metadata: {ClientID: '', DateOfBirth: '01-01-2000'}}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload document missing required metadata.', 'System attempts metadata validation.'], 'Expected Result': 'Document rejected; clear error message citing missing/incorrect metadata.', 'Dependent Module/Process': 'Metadata Parser, Validation Rules'}, {'Test Case ID': 'US21_TC03', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Intake', 'Activity Title': 'OCR Failure Handling', 'Test Scenario Title': 'Uploaded file is unreadable or unsupported format (OCR failure)', 'Precondition': 'User logged in as Case Worker.', 'Test Data': "{Filename: 'scanned_doc.tiff', Type: 'TIFF', Metadata: {...}}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload an unsupported or corrupt file.', 'System performs OCR.'], 'Expected Result': "Document rejected with error: 'Unable to process file.' User is prompted to re-upload.", 'Dependent Module/Process': 'OCR Engine, Error Handling'}, {'Test Case ID': 'US21_TC04', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Unauthorized user attempts upload/validation', 'Precondition': 'User role does not include upload/validate rights.', 'Test Data': 'N/A', 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Client', 'Detailed Test Steps': ['Attempt to upload a document.', 'Attempt to trigger validation.'], 'Expected Result': 'Action is denied; attempt is logged for audit.', 'Dependent Module/Process': 'Role Permissions, Security Logging'}, {'Test Case ID': 'US21_TC05', 'EPIC': 'Document Capture &amp; Validation', 'Feature': 'Auto Validation via OCR/Metadata', 'User Story': 'US21', 'Business Process': 'Document Management', 'Sub-Process Title': 'Audit &amp; Compliance', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Every validation attempt is logged for audit (compliance)', 'Precondition': 'Audit logging feature enabled.', 'Test Data': "{Filename: 'sample.pdf', AttemptType: ['Success', 'Failure']}", 'T-Code': 'N/A', 'SAP Fiori Application ID': 'F_APP_DOC_UPLOAD', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload a valid and an invalid document.', 'Check system audit logs.'], 'Expected Result': 'Each validation attempt (success or failure) is logged with timestamp, user, and outcome for audit.', 'Dependent Module/Process': 'Audit Logging, Compliance Framework'}]</t>
+          <t>[{'Test Case ID': '24-FUNC-1', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Bulk Upload', 'Activity Title': 'Batch file import', 'Test Scenario Title': 'Batch document upload and automatic case matching', 'Precondition': 'Case Worker has multiple documents and case records exist.', 'Test Data': 'Multiple PDF files, each named with case ID or client name; Case Worker user.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Navigate to bulk upload interface.', '2. Select and upload multiple documents.', '3. Monitor upload process; observe progress screen.', '4. View document-to-case assignments.'], 'Expected Result': 'Documents are uploaded in batch; each is matched to correct case if possible.', 'Dependent Module/Process': 'Case Matching Engine'}, {'Test Case ID': '24-FUNC-2', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Bulk Upload', 'Activity Title': 'Summary Feedback', 'Test Scenario Title': 'Provide upload summary results', 'Precondition': 'Bulk upload includes both matchable and unmatched documents.', 'Test Data': 'Some files with unresolvable names, others with clear case IDs.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Complete bulk upload.', '2. Review upload summary dialog.', '3. Note counts of successful and failed uploads.'], 'Expected Result': 'User sees which documents succeeded, which failed, and why (e.g., unmatched).', 'Dependent Module/Process': 'Bulk Upload UI'}, {'Test Case ID': '24-FUNC-3', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Bulk Upload', 'Activity Title': 'Manual Matching', 'Test Scenario Title': 'Allow manual case assignment for unmatched documents', 'Precondition': 'Bulk upload included unmatched documents.', 'Test Data': 'Files with ambiguous or missing identifiers.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. After upload, view unmatched list.', '2. Select a document to assign manually.', '3. Search for and select appropriate case.', '4. Confirm assignment.'], 'Expected Result': 'Unmatched document is successfully associated after manual assignment.', 'Dependent Module/Process': 'Case Search'}, {'Test Case ID': '24-NEG-1', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Bulk Upload', 'Activity Title': 'Handle Invalid Inputs', 'Test Scenario Title': 'Invalid/corrupt document handling in bulk upload', 'Precondition': 'Batch includes valid and invalid/corrupted documents.', 'Test Data': 'At least one zero-byte or corrupted file.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Attempt batch upload including invalid files.', '2. Review process and result summary.'], 'Expected Result': 'Corrupt/invalid files are rejected with error message; other uploads continue normally.', 'Dependent Module/Process': 'Bulk Upload Service'}, {'Test Case ID': '24-PERM-1', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Access Control', 'Sub-Process Title': 'Bulk Upload Permission', 'Activity Title': 'Show/Hide Bulk Upload', 'Test Scenario Title': 'Bulk upload available to Case Worker only', 'Precondition': 'Logged in as non-Case Worker role.', 'Test Data': 'Admin, Case Manager logins.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Admin, Case Manager', 'Detailed Test Steps': ['1. Attempt to access bulk upload UI.', '2. Observe access.', '3. Try uploading if possible.'], 'Expected Result': 'Bulk upload feature is hidden or access is denied to unauthorized users.', 'Dependent Module/Process': 'Authorization'}, {'Test Case ID': '24-API-1', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'API Integration', 'Sub-Process Title': 'Bulk Upload API', 'Activity Title': 'API Batch Upload', 'Test Scenario Title': 'Backend processes and acknowledges bulk upload', 'Precondition': 'Bulk upload API is enabled.', 'Test Data': 'API request: multi-part files, including case ID metadata.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Send API batch upload request.', '2. Receive and validate API response.', '3. Cross-reference API result with files sent.'], 'Expected Result': 'API returns success/error details for each file, reflecting upload and case match results.', 'Dependent Module/Process': 'Bulk Upload API'}, {'Test Case ID': '24-COMP-1', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Logging', 'Activity Title': 'Bulk Upload Audit', 'Test Scenario Title': 'Audit trail created for bulk upload action', 'Precondition': 'Completed bulk upload.', 'Test Data': 'Bulk upload batch (various files).', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Complete bulk document upload.', '2. Access audit logs as permitted user.', '3. Search for upload event and its file/case assignments.'], 'Expected Result': 'Audit log entries contain file name, user, timestamp, case assignment and error status (for regulatory traceability).', 'Dependent Module/Process': 'Audit Log Service'}]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>This user story focuses on leveraging AI-driven suggestions to help Case Workers efficiently complete application forms by highlighting and recommending content for missing fields.</t>
+          <t>This user story enables Case Managers to monitor trends in eligibility denials via an analytics dashboard with granular breakdowns by denial reasons. It supports early identification of systemic issues and compliance with internal monitoring standards.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22: As a Case Worker, I want to receive suggestions for missing fields in applications so that I can complete them faster. - AI-based field completion suggestions. | Related: [1, 5, 19] | Group: [22]</t>
+          <t>As a Case Manager, I want to view trends in eligibility denials so that I can identify systemic issues.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A Case Worker views an incomplete application and the system suggests values for missing fields, enabling completion and submission of the application without errors.</t>
+          <t>Case Manager logs in, accesses the analytics dashboard, and views accurate graphical and tabular representations of denial trends, including detailed breakdowns by reason and time period.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US22_FT_01', 'Brief Description': 'AI suggestions appear for all required missing fields in an incomplete application.'}, {'Test Case ID': 'US22_FT_02', 'Brief Description': 'Case Worker accepts suggested values and successfully submits the completed application.'}, {'Test Case ID': 'US22_NT_01', 'Brief Description': 'AI does not suggest values for fields already completed by user.'}, {'Test Case ID': 'US22_NT_02', 'Brief Description': 'System handles applications with non-suggestable (unknown) missing fields correctly by prompting manual entry.'}, {'Test Case ID': 'US22_IR_01', 'Brief Description': 'Suggestions are not visible to users without sufficient permissions (Case Managers, external users).'}, {'Test Case ID': 'US22_COMP_01', 'Brief Description': 'AI suggestions comply with data privacy policies (do not leak confidential information).'}]</t>
+          <t>[{'Test Case ID': 'US25_TC1', 'Brief Description': 'Case Manager views denial trends dashboard displaying expected denial reasons'}, {'Test Case ID': 'US25_TC2', 'Brief Description': 'Case Manager applies filters (date range, program type) and sees correct data reflections'}, {'Test Case ID': 'US25_TC3', 'Brief Description': 'Access denied to dashboard for unauthorized users'}, {'Test Case ID': 'US25_TC4', 'Brief Description': 'Dashboard handles empty or delayed data sources gracefully'}, {'Test Case ID': 'US25_TC5', 'Brief Description': 'Audit trail captures dashboard access for compliance'}]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US22_FT_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Review Incomplete Application', 'Activity Title': 'Field Completion Suggestion', 'Test Scenario Title': 'Display AI Suggestions for Missing Fields', 'Precondition': 'Case Worker has access to an incomplete application with missing required fields.', 'Test Data': "Sample application missing 'Address' and 'Income' fields.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to incomplete application.', 'Observe UI indicators for missing fields.', 'Trigger AI suggestion feature (either auto or on user click).'], 'Expected Result': 'The system displays valid AI-based suggestions for each missing field.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form'}, {'Test Case ID': 'US22_FT_02', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Complete and Submit Application', 'Activity Title': 'Accept AI Suggestions', 'Test Scenario Title': 'Accept and Apply Suggested Values', 'Precondition': 'AI suggestions are generated for required missing fields.', 'Test Data': "Suggestion: 'Address' =&gt; '123 Main St', 'Income' =&gt; '50000'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Review suggested values.', 'Accept all suggestions.', 'Submit the application.'], 'Expected Result': 'Suggested values are applied; submission is successful; all validations pass.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form, Submission Workflow'}, {'Test Case ID': 'US22_NT_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Prevent Duplicate Suggestions', 'Activity Title': 'Exclude Completed Fields', 'Test Scenario Title': 'No Suggestions for Already Filled Fields', 'Precondition': 'Some required fields already completed by user.', 'Test Data': "Application with 'Name', 'DOB' filled; 'Address' missing.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Open an incomplete application where 'Name' and 'DOB' are already filled.", 'Trigger AI suggestion.', 'Observe suggested fields.'], 'Expected Result': 'No suggestions are made for already completed fields.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form'}, {'Test Case ID': 'US22_NT_02', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Handle Unsupported Fields', 'Activity Title': 'Manual Input Prompt', 'Test Scenario Title': 'Prompt Manual Entry for Unsupported Fields', 'Precondition': 'Application contains required fields that are not supported by AI suggestion.', 'Test Data': "Unknown field: 'Special Accommodation Requirements'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt AI suggestion on application with unsupported field.', 'Observe system response.'], 'Expected Result': 'System prompts user to enter value manually; does not fail silently or crash.', 'Dependent Module/Process': 'AI Suggestion Engine, Application Form'}, {'Test Case ID': 'US22_IR_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Role-Based Visibility', 'Test Scenario Title': 'Restrict AI Suggestions to Case Workers', 'Precondition': 'Logged in as user without Case Worker permissions.', 'Test Data': 'Any incomplete application.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager/Unauthorized User', 'Detailed Test Steps': ['Login as Case Manager or another unauthorized role.', 'Access an incomplete application.', 'Attempt to trigger AI suggestion.'], 'Expected Result': 'AI suggestions feature is not visible or accessible.', 'Dependent Module/Process': 'Authentication, Role-based Access Control'}, {'Test Case ID': 'US22_COMP_01', 'EPIC': 'Intelligent Assistance', 'Feature': 'AI Field Suggestion', 'User Story': '22', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Compliance and Audit', 'Activity Title': 'Data Privacy', 'Test Scenario Title': 'Ensure AI Suggestions Respect Data Privacy', 'Precondition': 'AI model trained with current system data.', 'Test Data': 'Application with PII fields (Name, SSN, etc).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Review suggested values for sensitive fields.', 'Inspect logs/audit trail.', 'Review data lineage of suggestions.'], 'Expected Result': 'No unauthorized data exposure; data privacy and audit logging complies with GDPR/HIPAA/internal policies.', 'Dependent Module/Process': 'AI Suggestion Engine, Audit Logging, Compliance Framework'}]</t>
+          <t>[{'Test Case ID': 'US25_TC1', 'EPIC': 'Analytics &amp; Reporting', 'Feature': 'Eligibility Denial Trends', 'User Story': '25', 'Business Process': 'Monitoring', 'Sub-Process Title': 'Eligibility Trends Analytics', 'Activity Title': 'View Denial Trends Dashboard', 'Test Scenario Title': 'Positive trend visualization with all denial reasons', 'Precondition': 'Case Manager credentials; historic denial data available', 'Test Data': {'Case Denials': [{'date': '2023-12-01', 'reason': 'Income over limit'}, {'date': '2024-01-15', 'reason': 'Missing documentation'}]}, 'T-Code': '', 'SAP Fiori Application ID': 'F1234', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log into the system as Case Manager', 'Navigate to Analytics &gt; Denial Trends Dashboard', 'Observe displayed denial reasons, counts, and trend over time'], 'Expected Result': 'Dashboard displays correct trend graphs and breakdown by denial reason', 'Dependent Module/Process': 'Eligibility, Analytics Service'}, {'Test Case ID': 'US25_TC2', 'EPIC': 'Analytics &amp; Reporting', 'Feature': 'Eligibility Denial Trends', 'User Story': '25', 'Business Process': 'Monitoring', 'Sub-Process Title': 'Eligibility Trends Analytics', 'Activity Title': 'Apply Trend Filters', 'Test Scenario Title': 'Date and type filters affect dashboard correctly', 'Precondition': 'Case Manager logged in; sufficient denial data across categories', 'Test Data': {'Filter': 'Program Type = SNAP', 'Date Range': '2024-01-01 to 2024-06-30'}, 'T-Code': '', 'SAP Fiori Application ID': 'F1234', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to Denial Trends Dashboard', 'Apply Program Type: SNAP filter', 'Apply Date range: 2024-01-01 to 2024-06-30', 'Review updated chart/table view'], 'Expected Result': 'Displayed trends match filtered data set; no other programs or time periods shown', 'Dependent Module/Process': 'Analytics Service, Filters'}, {'Test Case ID': 'US25_TC3', 'EPIC': 'Analytics &amp; Reporting', 'Feature': 'Eligibility Denial Trends', 'User Story': '25', 'Business Process': 'Security &amp; Access', 'Sub-Process Title': 'Role-based Access', 'Activity Title': 'Restrict Unauthorized Dashboard Access', 'Test Scenario Title': 'Access denied for users without Case Manager role', 'Precondition': "User logged in as 'Case Worker' or another role; dashboard configured to restrict access", 'Test Data': {'User Role': 'Case Worker'}, 'T-Code': '', 'SAP Fiori Application ID': 'F1234', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Navigate to Analytics &gt; Denial Trends Dashboard'], 'Expected Result': 'User receives an access denied message or does not see the dashboard menu option', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'US25_TC4', 'EPIC': 'Analytics &amp; Reporting', 'Feature': 'Eligibility Denial Trends', 'User Story': '25', 'Business Process': 'Monitoring', 'Sub-Process Title': 'Data Quality', 'Activity Title': 'Dashboard Robustness', 'Test Scenario Title': 'Empty or delayed data handling', 'Precondition': 'Dashboard linked to empty or delayed data source', 'Test Data': {'Case Denials': []}, 'T-Code': '', 'SAP Fiori Application ID': 'F1234', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to Denial Trends Dashboard', 'Observe system response when no data is available'], 'Expected Result': "Dashboard indicates 'No Data Available' or similar friendly message and does not crash", 'Dependent Module/Process': 'Analytics Data Layer'}, {'Test Case ID': 'US25_TC5', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Access Logging', 'User Story': '25', 'Business Process': 'Audit', 'Sub-Process Title': 'Access Log &amp; Review', 'Activity Title': 'Dashboard Access Logging', 'Test Scenario Title': 'Audit entry created on dashboard access', 'Precondition': 'User with Case Manager privileges; audit trail enabled', 'Test Data': {'Case Manager ID': 'CM12345'}, 'T-Code': '', 'SAP Fiori Application ID': 'F1234', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Access the Denial Trends Dashboard as Case Manager', 'Review system-generated audit logs for access record'], 'Expected Result': 'Audit log entry records access with timestamp, user ID, and dashboard ID', 'Dependent Module/Process': 'Audit Logging Service'}]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>This user story is about empowering Case Managers to filter and prioritize clients on their dashboard by eligibility status, thereby enhancing their outreach and workflow efficiency.</t>
+          <t>This user story enables Case Workers to streamline new application entry by automatically pre-filling data fields from previous cases for the same client, reducing manual workload and data entry errors.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23: As a Case Manager, I want to filter clients by eligibility status so that I can prioritize outreach. - Filter dashboard by status: pending, approved, expired. | Related: [6, 25, 32] | Group: [23]</t>
+          <t>As a Case Worker, I want to pre-fill application data from previous cases so that I can reduce data entry.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A Case Manager applies the status filter on the dashboard and instantly sees clients grouped as pending, approved, or expired, enabling targeted action.</t>
+          <t>Case Worker searches for an applicant, creates a new application, and sees certain fields (e.g., Name, Address, Household Members) pre-filled from historical data, which are editable as needed.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US23_FT_01', 'Brief Description': "Filter dashboard to display only 'pending' clients."}, {'Test Case ID': 'US23_FT_02', 'Brief Description': "Filter dashboard to show only 'approved' clients."}, {'Test Case ID': 'US23_FT_03', 'Brief Description': "Filter dashboard to display only 'expired' clients."}, {'Test Case ID': 'US23_NT_01', 'Brief Description': 'Applying an invalid or unsupported filter returns no results and displays an error.'}, {'Test Case ID': 'US23_IR_01', 'Brief Description': 'Unauthorized users cannot access or use filter functionality.'}, {'Test Case ID': 'US23_E2E_01', 'Brief Description': 'Dashboard filter returns up-to-date, integrated eligibility statuses from the backend API.'}]</t>
+          <t>[{'Test Case ID': 'US26_TC1', 'Brief Description': 'Case Worker sees previous case data auto-filled in new application'}, {'Test Case ID': 'US26_TC2', 'Brief Description': 'Case Worker edits pre-filled data without errors'}, {'Test Case ID': 'US26_TC3', 'Brief Description': 'No previous data results in blank application fields'}, {'Test Case ID': 'US26_TC4', 'Brief Description': 'Unauthorized role cannot see or trigger auto-fill'}, {'Test Case ID': 'US26_TC5', 'Brief Description': 'Audit logs record case data retrieval'}, {'Test Case ID': 'US26_TC6', 'Brief Description': 'Data pre-fill complies with data privacy controls'}]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US23_FT_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Prioritize by Status', 'Activity Title': 'Select Status Filter', 'Test Scenario Title': "Filter by 'Pending' Status", 'Precondition': 'Case Manager logged in with dashboard access; client data is available.', 'Test Data': 'Clients: [John Doe: Pending, Jane Roe: Approved, Sam Smith: Pending]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to dashboard.', "Select 'Pending' from status filter dropdown.", 'Observe client list refresh.'], 'Expected Result': "Dashboard displays only clients with 'Pending' status.", 'Dependent Module/Process': 'Dashboard UI, Eligibility Status API'}, {'Test Case ID': 'US23_FT_02', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Prioritize by Status', 'Activity Title': 'Select Status Filter', 'Test Scenario Title': "Filter by 'Approved' Status", 'Precondition': 'Dashboard shows multiple clients with various statuses.', 'Test Data': 'Clients: [John Doe: Pending, Jane Roe: Approved, Sam Smith: Expired]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Select 'Approved' status in filter.", 'Review dashboard results.'], 'Expected Result': "Only 'Approved' clients are displayed.", 'Dependent Module/Process': 'Dashboard UI, Eligibility Status API'}, {'Test Case ID': 'US23_FT_03', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Prioritize by Status', 'Activity Title': 'Select Status Filter', 'Test Scenario Title': "Filter by 'Expired' Status", 'Precondition': 'Clients exist in all status categories.', 'Test Data': 'Clients: [Sam Smith: Expired]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Apply 'Expired' status filter.", 'Compare displayed list against expected expired clients.'], 'Expected Result': "Only clients with status 'Expired' appear.", 'Dependent Module/Process': 'Eligibility Status Data, Dashboard UI'}, {'Test Case ID': 'US23_NT_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Handle Invalid Filter', 'Activity Title': 'Invalid Filter Graceful Handling', 'Test Scenario Title': 'Apply Unsupported Status Filter', 'Precondition': 'Dashboard has active filtering capability.', 'Test Data': "Invalid filter value: 'Under Review'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Attempt to filter clients with an unsupported status value.', 'Observe system behavior.'], 'Expected Result': 'Dashboard shows appropriate error or empty state; no crash.', 'Dependent Module/Process': 'Dashboard UI, Error Handling'}, {'Test Case ID': 'US23_IR_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Dashboard Access', 'Sub-Process Title': 'Permission Check', 'Activity Title': 'Restrict Filter UI', 'Test Scenario Title': 'Unauthorized User Cannot Filter', 'Precondition': 'Login as non-Case Manager role.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, External User', 'Detailed Test Steps': ['Login as a user without Case Manager privileges.', 'Navigate to client dashboard.', 'Look for status filter options.'], 'Expected Result': 'Status filter is not accessible or functional for unauthorized roles.', 'Dependent Module/Process': 'Authentication, Role-based Permissions'}, {'Test Case ID': 'US23_E2E_01', 'EPIC': 'Client Management', 'Feature': 'Dashboard Filtering', 'User Story': '23', 'Business Process': 'Client Outreach', 'Sub-Process Title': 'Full System Integration', 'Activity Title': 'API and UI Sync', 'Test Scenario Title': 'Filter Reflects Latest Status from API', 'Precondition': 'API holds up-to-date eligibility data.', 'Test Data': 'Update status in backend (e.g., pending→approved), refresh dashboard.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ["Change status of one client in backend to 'Approved'.", "Refresh dashboard and apply 'Approved' filter.", 'Verify real-time update.'], 'Expected Result': 'Filter results match latest backend data.', 'Dependent Module/Process': 'Eligibility Status API, Dashboard UI'}]</t>
+          <t>[{'Test Case ID': 'US26_TC1', 'EPIC': 'Case Intake Automation', 'Feature': 'Application Pre-fill', 'User Story': '26', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Case Creation', 'Activity Title': 'Pre-fill Fields from Previous Cases', 'Test Scenario Title': 'Auto-populate with historical applicant data', 'Precondition': 'Case Worker assigned; applicant with previous cases exists', 'Test Data': {'Applicant': 'Jane Smith', 'Historical Cases': [{'name': 'Jane Smith', 'address': '1234 Maple Ave', 'household': '3'}]}, 'T-Code': '', 'SAP Fiori Application ID': 'F2345', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', "Search for existing applicant 'Jane Smith'", 'Initiate new application', 'Observe pre-filled fields: Name, Address, Household'], 'Expected Result': 'Fields populated with most recent historical data; fields remain editable', 'Dependent Module/Process': 'Case Database, Application Forms'}, {'Test Case ID': 'US26_TC2', 'EPIC': 'Case Intake Automation', 'Feature': 'Application Pre-fill', 'User Story': '26', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Data Modification', 'Activity Title': 'Edit Pre-filled Data', 'Test Scenario Title': 'Case Worker can overwrite pre-filled data', 'Precondition': 'Case Worker creating new pre-filled application', 'Test Data': {'Applicant': 'Jane Smith', 'Initial Address': '1234 Maple Ave', 'New Address': '5678 Oak St'}, 'T-Code': '', 'SAP Fiori Application ID': 'F2345', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Follow TC1 steps to access pre-filled application', "Edit the Address field to '5678 Oak St'", 'Save and view application'], 'Expected Result': 'Data saves with updated values; audit captures change', 'Dependent Module/Process': 'Application Forms, Audit Logging'}, {'Test Case ID': 'US26_TC3', 'EPIC': 'Case Intake Automation', 'Feature': 'Application Pre-fill', 'User Story': '26', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Case Creation - No History', 'Activity Title': 'No Data Pre-fill', 'Test Scenario Title': 'No prior case data found', 'Precondition': 'Case Worker; applicant with no prior cases', 'Test Data': {'Applicant': 'Mark Bell', 'Historical Cases': []}, 'T-Code': '', 'SAP Fiori Application ID': 'F2345', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', "Search for new applicant 'Mark Bell'", 'Start new application'], 'Expected Result': 'No fields pre-filled; application form blank', 'Dependent Module/Process': 'Case Database'}, {'Test Case ID': 'US26_TC4', 'EPIC': 'Case Intake Automation', 'Feature': 'Application Pre-fill', 'User Story': '26', 'Business Process': 'Security &amp; Access', 'Sub-Process Title': 'Role Restriction', 'Activity Title': 'Unauthorized Role Auto-fill Restriction', 'Test Scenario Title': 'Other user roles cannot trigger pre-fill', 'Precondition': 'User logged in as Guest', 'Test Data': {'User Role': 'Guest'}, 'T-Code': '', 'SAP Fiori Application ID': 'F2345', 'User Role': 'Guest', 'Detailed Test Steps': ['Log in as Guest user', 'Attempt to generate a new application for an existing applicant'], 'Expected Result': 'Auto-fill not triggered; user sees blank fields or receives error', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'US26_TC5', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Pre-fill Data Audit', 'User Story': '26', 'Business Process': 'Audit', 'Sub-Process Title': 'Data Retrieval Logging', 'Activity Title': 'Audit Logging for Pre-fill', 'Test Scenario Title': 'Audit trail for historical data access', 'Precondition': 'Case Worker accesses pre-fill feature; audit enabled', 'Test Data': {'Applicant': 'Jane Smith'}, 'T-Code': '', 'SAP Fiori Application ID': 'F2345', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger auto-fill on application creation', 'Check audit log for data retrieval event'], 'Expected Result': 'Audit log includes user, timestamp, data access details', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'US26_TC6', 'EPIC': 'Data Privacy', 'Feature': 'Pre-fill Compliance', 'User Story': '26', 'Business Process': 'Compliance', 'Sub-Process Title': 'Data Privacy Controls', 'Activity Title': 'Ensure Authorized Data Pre-fill Only', 'Test Scenario Title': 'Data pre-fill respects privacy and access policies', 'Precondition': 'Legal constraints (e.g., GDPR/HIPAA); system configured for only authorized data retrieval', 'Test Data': {'Applicant': 'Sensitive Data Case'}, 'T-Code': '', 'SAP Fiori Application ID': 'F2345', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt pre-fill for an applicant restricted under privacy policy', 'Review if sensitive fields are masked/omitted'], 'Expected Result': 'Data pre-fill omits or masks restricted fields; compliance maintained', 'Dependent Module/Process': 'Compliance, GDPR/HIPAA Module'}]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>This user story enhances Case Worker efficiency by enabling bulk document uploads with automatic matching to multiple cases, reducing manual effort and error.</t>
+          <t>This user story introduces real-time alerts for Case Workers when conflicting household information is detected across applications for the same household, supporting quick discrepancy resolution and data integrity.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24: As a Case Worker, I want to bulk upload documents for multiple cases so that I can save time. - Batch upload with case matching logic. | Related: [8] | Group: [24]</t>
+          <t>As a Case Worker, I want to receive alerts for conflicting household data so that I can resolve discrepancies.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Case Worker uploads a batch of documents; the system automatically matches and attaches each document to the correct case, showing success.</t>
+          <t>Case Worker enters household data for an application; system cross-checks with existing records and, if a conflict is found (e.g., household member count mismatch), an alert pops up prompting review and resolution.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US24_FT_01', 'Brief Description': 'Bulk upload successfully attaches documents to correct cases.'}, {'Test Case ID': 'US24_NT_01', 'Brief Description': 'Upload is partially successful with some documents unmatched; user receives actionable error/warning.'}, {'Test Case ID': 'US24_NT_02', 'Brief Description': 'Bulk upload fails if all documents lack matching data (e.g., invalid case IDs), system rolls back changes.'}, {'Test Case ID': 'US24_IR_01', 'Brief Description': 'Non-Case Worker users cannot access bulk upload functionality.'}, {'Test Case ID': 'US24_COMP_01', 'Brief Description': 'All uploads are logged for audit; file types and data comply with policy.'}]</t>
+          <t>[{'Test Case ID': 'US27_TC1', 'Brief Description': 'Case Worker receives conflict alert when entering different household data'}, {'Test Case ID': 'US27_TC2', 'Brief Description': 'Case Worker chooses to review and resolve conflict via guided UI flow'}, {'Test Case ID': 'US27_TC3', 'Brief Description': 'No alert when data matches across applications'}, {'Test Case ID': 'US27_TC4', 'Brief Description': 'User without permission cannot see household conflict alerts'}, {'Test Case ID': 'US27_TC5', 'Brief Description': 'Alert triggers are logged for compliance/audit'}]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US24_FT_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Batch Document Upload', 'Activity Title': 'Upload Multiple Files', 'Test Scenario Title': 'Successful Bulk Upload and Case Matching', 'Precondition': 'Case Worker logged in; cases exist and are accessible.', 'Test Data': 'Files: [john_doe_id.pdf-&gt;Case 123, jane_roe_transcript.pdf-&gt;Case 456]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select bulk upload option.', 'Choose multiple files with valid naming/case identifier conventions.', 'Confirm upload.', 'Check attachment status for each case.'], 'Expected Result': 'All documents matched and attached to correct cases. Confirmation displayed.', 'Dependent Module/Process': 'Case Matching Logic, Document Storage'}, {'Test Case ID': 'US24_NT_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Batch Document Upload', 'Activity Title': 'Partial Match Handling', 'Test Scenario Title': 'Bulk Upload with Some Unmatched Documents', 'Precondition': 'Mixed-validity files selected for upload.', 'Test Data': 'Files: [good.pdf-&gt;Case 123, error.pdf-&gt;No match]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload files (one with no match).', 'Monitor system response.', 'Review result messages.'], 'Expected Result': 'Matched document attached; unmatched document flagged with actionable error. No data loss or corruption.', 'Dependent Module/Process': 'Case Matching Logic, Document Workflow'}, {'Test Case ID': 'US24_NT_02', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Batch Document Upload', 'Activity Title': 'Full Upload Failure Handling', 'Test Scenario Title': 'Bulk Upload Failure Due to No Match', 'Precondition': 'All selected files have invalid or missing identifiers.', 'Test Data': 'Files: [unknown1.pdf, unknown2.pdf]', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload only invalid files.', 'Observe system processing.', 'Inspect error and rollback behavior.'], 'Expected Result': 'No documents attached. User receives a clear error. No partial state left in system.', 'Dependent Module/Process': 'Case Matching Logic, Transaction Rollback'}, {'Test Case ID': 'US24_IR_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Role Restriction', 'Test Scenario Title': 'Only Case Workers Can Bulk Upload', 'Precondition': 'Login as a user without Case Worker permissions.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Client, etc.', 'Detailed Test Steps': ['Attempt to access bulk upload screen as unauthorized user.', 'Try triggering upload functionality.'], 'Expected Result': 'Bulk upload UI and API endpoints inaccessible.', 'Dependent Module/Process': 'Authentication, Authorization'}, {'Test Case ID': 'US24_COMP_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '24', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Compliance and Audit', 'Activity Title': 'Logging and Validation', 'Test Scenario Title': 'Bulk Upload Meets Audit and Policy Requirements', 'Precondition': 'Bulk upload feature enabled; audit system active.', 'Test Data': 'Files: various types, including non-permitted if possible.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload a valid set of documents.', 'Attempt uploading unsupported file types.', 'Check audit logs for entries.', 'Verify compliance validation messages for blocked types.', 'Request or view audit trail/report.'], 'Expected Result': 'All uploads are logged with user, timestamp, and case info; unsupported files are blocked; compliance warnings shown as needed.', 'Dependent Module/Process': 'Audit Logging, Compliance System, File Storage'}]</t>
+          <t>[{'Test Case ID': 'US27_TC1', 'EPIC': 'Data Integrity Assurance', 'Feature': 'Household Data Validation', 'User Story': '27', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Household Data Entry', 'Activity Title': 'Detect Household Data Conflicts', 'Test Scenario Title': 'Alert upon conflicting data detected', 'Precondition': 'Applicant with existing household data; Case Worker role', 'Test Data': {'Application 1': {'household_count': 3}, 'Application 2': {'household_count': 5}}, 'T-Code': '', 'SAP Fiori Application ID': 'F3456', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Open application for applicant with existing household data', "Enter 'household_count' = 5 where previous was 3", 'Submit entry'], 'Expected Result': 'System displays real-time alert regarding inconsistent household data', 'Dependent Module/Process': 'Cross-Application Data Checker'}, {'Test Case ID': 'US27_TC2', 'EPIC': 'Data Integrity Assurance', 'Feature': 'Household Data Validation', 'User Story': '27', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Conflict Resolution', 'Activity Title': 'Resolve Data Conflict', 'Test Scenario Title': 'Guided conflict resolution upon alert', 'Precondition': 'Active conflict detected as in TC1', 'Test Data': {'Case IDs': ['A100', 'A101'], 'Conflicting Field': 'household_count'}, 'T-Code': '', 'SAP Fiori Application ID': 'F3456', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Receive alert from TC1', "Choose 'Review Conflicts'", 'Access summary of conflicting records', 'Edit or confirm the correct data point', 'Save changes'], 'Expected Result': 'System records resolution choice; household data aligned; audit trail updated', 'Dependent Module/Process': 'Conflict Resolution UI, Audit Logging'}, {'Test Case ID': 'US27_TC3', 'EPIC': 'Data Integrity Assurance', 'Feature': 'Household Data Validation', 'User Story': '27', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Data Entry Validation', 'Activity Title': 'Normal Entry, No Conflict', 'Test Scenario Title': 'No alert when no conflict exists', 'Precondition': 'All historical household data matches new entry', 'Test Data': {'Previous Data': {'household_count': 3}, 'Current Entry': {'household_count': 3}}, 'T-Code': '', 'SAP Fiori Application ID': 'F3456', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker', 'Create or update application with household count matching existing records', 'Save entry'], 'Expected Result': 'No conflict alert triggered; data entry proceeds without warning', 'Dependent Module/Process': 'Cross-Application Data Checker'}, {'Test Case ID': 'US27_TC4', 'EPIC': 'Data Integrity Assurance', 'Feature': 'Household Data Validation', 'User Story': '27', 'Business Process': 'Security &amp; Access', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Alert Visibility', 'Test Scenario Title': 'Unauthorized role cannot view conflict warnings', 'Precondition': 'User logged in as viewer/guest; role does not have intake or conflict resolution permissions', 'Test Data': {'User Role': 'Viewer'}, 'T-Code': '', 'SAP Fiori Application ID': 'F3456', 'User Role': 'Viewer', 'Detailed Test Steps': ['Log in as Viewer', 'Attempt to create/update application with conflicting household data'], 'Expected Result': 'No alert shown; user cannot access or act on conflict feature', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'US27_TC5', 'EPIC': 'Audit &amp; Compliance', 'Feature': 'Alert Trigger Audit', 'User Story': '27', 'Business Process': 'Audit', 'Sub-Process Title': 'Alert Logging', 'Activity Title': 'Household Conflict Alert Logging', 'Test Scenario Title': 'System logs every alert and resolution', 'Precondition': 'Audit logging enabled; Case Worker role', 'Test Data': {'Conflict': {'applications': ['A100', 'A101']}}, 'T-Code': '', 'SAP Fiori Application ID': 'F3456', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger a household conflict as per TC1', 'Resolve or dismiss the alert', 'Check audit logs'], 'Expected Result': 'Audit logs include user, timestamp, nature of conflict, and resolution or dismissal details', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>This user story revolves around providing Case Managers with insights through an analytics dashboard, allowing them to view and analyze trends in eligibility denials. This capability aims to help identify systemic issues, enabling data-driven interventions and compliance with reporting requirements.</t>
+          <t>This user story ensures clients receive services in their preferred language by enabling case managers to assign cases based on the language skills of caseworkers. Functional, integration, role-permission, and compliance aspects are considered, including edge cases (e.g., no language match found), access control, and potential audit requirements.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to view trends in eligibility denials so that I can identify systemic issues.</t>
+          <t>As a Case Manager, I want to assign cases based on language preference so that clients receive better service. - Match caseworker language skills with client preference.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Case Manager logs in, navigates to the analytics dashboard, and views visualizations detailing denial patterns, including frequency, reasons, and trends over user-defined periods.</t>
+          <t>Case Manager selects a client case with a specified language preference and is shown a filtered list of caseworkers with matching language skills. The manager assigns the case, and the assignment is logged.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US25-TC01', 'Brief Description': 'Case Manager views the denial trends dashboard with accurate, up-to-date data.'}, {'Test Case ID': 'US25-TC02', 'Brief Description': 'Case Manager filters dashboard by various criteria (date, reason, location).'}, {'Test Case ID': 'US25-TC03', 'Brief Description': 'Case Manager exports denial trends report for compliance/audit.'}, {'Test Case ID': 'US25-TC04', 'Brief Description': 'Unauthorized user attempts to access the dashboard.'}, {'Test Case ID': 'US25-TC05', 'Brief Description': 'Dashboard displays proper messages when there is no data.'}, {'Test Case ID': 'US25-TC06', 'Brief Description': 'API returns correct data for denial trends (integration testing).'}]</t>
+          <t>[{'Test Case ID': '28-1', 'Brief Description': 'Assign case to a caseworker matching the client language preference.'}, {'Test Case ID': '28-2', 'Brief Description': 'Attempt to assign case when no caseworker matches the language preference.'}, {'Test Case ID': '28-3', 'Brief Description': 'Verify that only Case Managers have case assignment permissions.'}, {'Test Case ID': '28-4', 'Brief Description': 'Audit trail: ensure assignments are logged with language match details.'}]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US25-TC01', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Reporting', 'Activity Title': 'View Denial Trends', 'Test Scenario Title': 'Case Manager views the denial trends dashboard with accurate data.', 'Precondition': 'Case Manager has account and dashboard permissions; denial data exists in the system.', 'Test Data': 'Sample denial records with varied reasons/dates/locations.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to Analytics -&gt; Denial Trends.', 'Observe displayed dashboard charts/tables.'], 'Expected Result': 'Dashboard loads successfully, displaying accurate visualizations of denial patterns matching test data.', 'Dependent Module/Process': 'Denials database, Authentication'}, {'Test Case ID': 'US25-TC02', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Reporting', 'Activity Title': 'Filter Dashboard', 'Test Scenario Title': 'Case Manager uses filtering options.', 'Precondition': 'Case Manager is on the denial trends dashboard.', 'Test Data': 'Diverse denials by date/reason/location.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Use dashboard filters for date, denial reason, and location.', 'Apply filter and observe results.'], 'Expected Result': 'Visualizations and data update accurately as per selected filters.', 'Dependent Module/Process': 'UI, Filter APIs'}, {'Test Case ID': 'US25-TC03', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Reporting', 'Activity Title': 'Export Reports', 'Test Scenario Title': 'Case Manager exports denial trends for compliance/audit.', 'Precondition': 'Denial trends are displayed on Dashboard.', 'Test Data': 'Sample denial records.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Click export/download button on dashboard.', 'Select file type (PDF, CSV, etc.)', 'Download the report.'], 'Expected Result': 'File is downloaded containing data matching dashboard, formatted for audit/compliance.', 'Dependent Module/Process': 'Export Service'}, {'Test Case ID': 'US25-TC04', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics Security', 'Activity Title': 'Unauthorized Access Prevention', 'Test Scenario Title': 'Unauthorized user attempts dashboard access.', 'Precondition': 'User is not assigned Case Manager or higher permissions.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Other roles (e.g., Applicant)', 'Detailed Test Steps': ['Log in as non-authorized user.', 'Attempt to access denial trends dashboard URL/page.'], 'Expected Result': 'Access is denied; appropriate error or redirect is shown.', 'Dependent Module/Process': 'Authentication/Authorization'}, {'Test Case ID': 'US25-TC05', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Analytics UX', 'Activity Title': 'No Data Handling', 'Test Scenario Title': 'Dashboard displays proper messages when no denial data exists.', 'Precondition': 'There are no denials in the database.', 'Test Data': 'Empty denial records.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in and navigate to dashboard when database is empty.'], 'Expected Result': '"No data available" message is shown; visualizations are empty/grayed out.', 'Dependent Module/Process': 'Analytics Data Layer'}, {'Test Case ID': 'US25-TC06', 'EPIC': 'Eligibility Analytics', 'Feature': 'Denial Trends Dashboard', 'User Story': '#25', 'Business Process': 'Eligibility Analysis', 'Sub-Process Title': 'Backend API', 'Activity Title': 'API Testing', 'Test Scenario Title': 'API returns accurate denial trend data.', 'Precondition': 'Denial data is seeded in backend.', 'Test Data': 'Known denial scenarios.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call API endpoint for denial trend data with different parameters.', 'Verify returned dataset matches expected results.'], 'Expected Result': 'API returns accurate summaries as per seeded data and filters.', 'Dependent Module/Process': 'Analytics API'}]</t>
+          <t>[{'Test Case ID': '28-1', 'EPIC': 'Case Assignment', 'Feature': 'Language Preference Matching', 'User Story': '28', 'Business Process': 'Service Assignment', 'Sub-Process Title': 'Case Allocation', 'Activity Title': 'Assign Case by Language', 'Test Scenario Title': 'Assign case with language match available', 'Precondition': 'Case Manager is logged in; case has a language preference indicated; at least one caseworker with matching skills is available.', 'Test Data': {'ClientLanguage': 'Spanish', 'CaseworkerSkills': ['Spanish', 'English']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to pending cases list.', 'Select a case with ClientLanguage = Spanish.', "Click 'Assign Case'.", "Observe/filter caseworker list for those with 'Spanish' skills.", 'Select a caseworker and confirm assignment.'], 'Expected Result': "Case is assigned to a caseworker with 'Spanish' language skills. Assignment is logged.", 'Dependent Module/Process': 'User Management (caseworker skills), Case Management'}, {'Test Case ID': '28-2', 'EPIC': 'Case Assignment', 'Feature': 'Language Preference Matching', 'User Story': '28', 'Business Process': 'Service Assignment', 'Sub-Process Title': 'Case Allocation', 'Activity Title': 'Assign Case by Language', 'Test Scenario Title': 'Handle no language match available', 'Precondition': 'Case Manager is logged in; no caseworker has the required language skill for the case.', 'Test Data': {'ClientLanguage': 'Mandarin', 'CaseworkerSkills': ['Spanish', 'English']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to pending cases list.', 'Select a case with ClientLanguage = Mandarin.', "Click 'Assign Case'.", 'Observe caseworker list (should not show any with matching skill).'], 'Expected Result': "System displays message: 'No caseworkers available with the required language skills.' Assignment is not possible.", 'Dependent Module/Process': 'User Management (caseworker skills), Case Management'}, {'Test Case ID': '28-3', 'EPIC': 'Case Assignment', 'Feature': 'Language Preference Matching', 'User Story': '28', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role-Based Authorization', 'Activity Title': 'Restrict Assignment', 'Test Scenario Title': 'Verify permission for assignment', 'Precondition': 'User is logged in as Case Worker (not Case Manager).', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Attempt to assign a pending case.'], 'Expected Result': "System denies access, showing 'Insufficient permissions' error.", 'Dependent Module/Process': 'Role Management'}, {'Test Case ID': '28-4', 'EPIC': 'Case Assignment', 'Feature': 'Audit and Compliance', 'User Story': '28', 'Business Process': 'Service Assignment', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Log Assignment', 'Test Scenario Title': 'Validate audit logging for assignment', 'Precondition': 'Case assigned to a caseworker with matching language.', 'Test Data': {'CaseID': 'C1234', 'AssignedTo': 'Jane Doe', 'Language': 'French'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['After assignment, access system audit logs.', 'Search by CaseID.', 'Review log entry for assignment, including language match.'], 'Expected Result': 'Audit log shows timestamp, assigner, assignee, client language preference, and matched skill.', 'Dependent Module/Process': 'Audit Logging, Case Management'}]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>This user story focuses on improving efficiency for Case Workers by auto-filling new applications using data from past cases. The goal is to reduce manual data entry and potential input errors while maintaining data privacy and permissions boundaries.</t>
+          <t>This user story enables a Case Worker to preview uploaded documents before submission, reducing document errors and improving data quality. Functional and negative cases (unsupported formats, corrupted files), role-based access, and compliance with data integrity are covered.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to pre-fill application data from previous cases so that I can reduce data entry.</t>
+          <t>As a Case Worker, I want to preview documents before uploading so that I can ensure accuracy. - Preview pane for scanned documents.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Case Worker initiates a new application, the system suggests and pre-fills relevant fields with data from historical cases connected to the applicant, and the Case Worker reviews and modifies as necessary.</t>
+          <t>Case Worker selects a document for upload, is shown a preview, and can choose to proceed or cancel.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US26-TC01', 'Brief Description': 'Auto-fill populates fields from prior cases when Case Worker initiates a new application.'}, {'Test Case ID': 'US26-TC02', 'Brief Description': 'Case Worker manually edits pre-filled data before submitting.'}, {'Test Case ID': 'US26-TC03', 'Brief Description': 'No prior case data exist; no fields are auto-filled.'}, {'Test Case ID': 'US26-TC04', 'Brief Description': 'Case Worker tries to pre-fill for a case not linked to their jurisdiction (permissions validation).'}, {'Test Case ID': 'US26-TC05', 'Brief Description': 'API returns accurate data when requested for auto-fill.'}, {'Test Case ID': 'US26-TC06', 'Brief Description': 'Audit log records auto-fill usages (compliance).'}]</t>
+          <t>[{'Test Case ID': '29-1', 'Brief Description': 'Successfully preview and upload a document.'}, {'Test Case ID': '29-2', 'Brief Description': 'Attempt to preview an unsupported file format.'}, {'Test Case ID': '29-3', 'Brief Description': 'Attempt to preview a corrupted file.'}, {'Test Case ID': '29-4', 'Brief Description': 'Non-authorized user attempts document upload.'}]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US26-TC01', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Auto-fill', 'Activity Title': 'Create Application', 'Test Scenario Title': 'Fields pre-filled from previous cases.', 'Precondition': 'Case Worker is assigned eligible applicant with prior cases in system.', 'Test Data': 'Prior case data in DB (address, household, income, etc.).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Start new application for applicant with historical data.', 'Observe auto-filled fields.'], 'Expected Result': 'Fields are automatically populated with prior data, accurately matching history.', 'Dependent Module/Process': 'Application Engine, Data Retrieval API'}, {'Test Case ID': 'US26-TC02', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Auto-fill', 'Activity Title': 'Edit Auto-Filled Data', 'Test Scenario Title': 'Case Worker edits pre-filled data before submitting.', 'Precondition': 'Fields are auto-filled on application form.', 'Test Data': 'Prior case data, new corrections.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Change information for one or more auto-filled fields.', 'Submit application.'], 'Expected Result': 'Edits are saved; final submission uses updated values.', 'Dependent Module/Process': 'Application Form Validation'}, {'Test Case ID': 'US26-TC03', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Auto-fill', 'Activity Title': 'No History Condition', 'Test Scenario Title': 'No prior data, nothing is auto-filled.', 'Precondition': 'Applicant has no prior case in DB.', 'Test Data': 'Empty prior case.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Start new application for applicant with no history.', 'Observe that all fields are empty.'], 'Expected Result': 'No fields are pre-populated; application starts blank.', 'Dependent Module/Process': 'Auto-fill Trigger'}, {'Test Case ID': 'US26-TC04', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'New Application Creation', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Jurisdiction Validation', 'Test Scenario Title': 'Case Worker attempts pre-fill for a case outside their jurisdiction.', 'Precondition': 'Case Worker lacks permission for given applicant’s history.', 'Test Data': 'Applicant/case in different jurisdiction.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (unauthorized)', 'Detailed Test Steps': ['Start new application for applicant outside jurisdiction.', 'Attempt to trigger auto-fill.'], 'Expected Result': 'Auto-fill does not fetch data; appropriate error/warning is displayed.', 'Dependent Module/Process': 'Authorization, Jurisdiction Rules'}, {'Test Case ID': 'US26-TC05', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'Integration', 'Sub-Process Title': 'API', 'Activity Title': 'API Testing', 'Test Scenario Title': 'API returns correct auto-fill data.', 'Precondition': 'Test user/applicant with history exists.', 'Test Data': 'Historical records for test applicant.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Invoke auto-fill API for applicant ID.', 'Validate returned fields against database records.'], 'Expected Result': 'API returns correct, complete data for pre-fill.', 'Dependent Module/Process': 'Auto-fill API'}, {'Test Case ID': 'US26-TC06', 'EPIC': 'Application Workflow', 'Feature': 'Auto-fill from History', 'User Story': '#26', 'Business Process': 'Compliance/Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Auto-fill usage is logged for audit.', 'Precondition': 'System audit logging is enabled.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Trigger auto-fill on application.', 'Check audit log for entry with Case Worker’s activity.'], 'Expected Result': 'Auto-fill access is recorded in logs with user, applicant, and timestamp for compliance.', 'Dependent Module/Process': 'Audit Logging'}]</t>
+          <t>[{'Test Case ID': '29-1', 'EPIC': 'Case Documents', 'Feature': 'Document Preview Before Upload', 'User Story': '29', 'Business Process': 'Document Management', 'Sub-Process Title': 'Upload', 'Activity Title': 'Preview &amp; Upload', 'Test Scenario Title': 'Preview and upload supported document', 'Precondition': 'Case Worker is logged in; supported document is available (e.g., PDF, JPG).', 'Test Data': {'DocumentName': 'ClientIDProof.pdf', 'DocumentType': 'PDF'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to case document upload section.', "Click 'Select File' and choose 'ClientIDProof.pdf'.", 'Preview pane displays the document.', "Verify contents, then click 'Upload'."], 'Expected Result': 'Document is correctly displayed in preview and uploaded to the case file.', 'Dependent Module/Process': 'Document Management, Case Management'}, {'Test Case ID': '29-2', 'EPIC': 'Case Documents', 'Feature': 'Document Preview Before Upload', 'User Story': '29', 'Business Process': 'Document Management', 'Sub-Process Title': 'Upload', 'Activity Title': 'Preview Unsupported File', 'Test Scenario Title': 'Preview unsupported format', 'Precondition': 'Case Worker is logged in; unsupported file (e.g., .exe or .zip) is available.', 'Test Data': {'DocumentName': 'UnsupportedFile.zip', 'DocumentType': 'ZIP'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to case document upload section.', "Select 'UnsupportedFile.zip'.", 'System attempts to preview.'], 'Expected Result': "System displays error: 'File type not supported for preview.' Upload button is disabled.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': '29-3', 'EPIC': 'Case Documents', 'Feature': 'Document Preview Before Upload', 'User Story': '29', 'Business Process': 'Document Management', 'Sub-Process Title': 'Upload', 'Activity Title': 'Preview Corrupted File', 'Test Scenario Title': 'Preview corrupted file', 'Precondition': 'Case Worker is logged in; corrupted file present.', 'Test Data': {'DocumentName': 'CorruptedID.pdf', 'DocumentType': 'PDF'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select 'CorruptedID.pdf' for upload.", 'System tries to generate document preview.'], 'Expected Result': "Preview pane displays error: 'Unable to display document. File may be corrupted.' Upload is disabled.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': '29-4', 'EPIC': 'Case Documents', 'Feature': 'Document Preview Before Upload', 'User Story': '29', 'Business Process': 'Authorization', 'Sub-Process Title': 'Role-Based Access', 'Activity Title': 'Restrict Upload', 'Test Scenario Title': 'Authorization restriction on upload', 'Precondition': 'User is not a Case Worker (e.g., basic user) and attempts upload.', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Basic User', 'Detailed Test Steps': ['Login as a Basic User.', 'Navigate to document upload section.', 'Attempt to upload any file.'], 'Expected Result': "System displays 'Access denied' or upload button is hidden.", 'Dependent Module/Process': 'Role Management'}]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>This user story ensures integrity by alerting Case Workers when there are conflicting household data entries across linked applications, enabling timely resolution and maintaining data correctness for eligibility determinations.</t>
+          <t>This user story allows Case Managers to export filtered case lists to Excel/CSV for offline analysis, supporting operational needs and potential audit/compliance requirements. The test plan considers successful export, access control, export of selected fields, and error handling.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to receive alerts for conflicting household data so that I can resolve discrepancies.</t>
+          <t>As a Case Manager, I want to export case data to Excel so that I can analyze it offline. - Export filtered case lists to CSV/Excel.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Case Worker processes an application; the system scans for duplicate household data across records and prompts an alert if any conflicts are detected.</t>
+          <t>Case Manager filters cases, clicks export, and receives a correctly-formatted Excel/CSV file containing the relevant records and headers.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US27-TC01', 'Brief Description': 'Case Worker receives alert when household data conflict is detected during application submission.'}, {'Test Case ID': 'US27-TC02', 'Brief Description': 'Case Worker reviews and resolves conflicting household data following alert.'}, {'Test Case ID': 'US27-TC03', 'Brief Description': 'No conflict in household data; application proceeds with no alert.'}, {'Test Case ID': 'US27-TC04', 'Brief Description': 'API correctly flags/returns data conflicts for integration.'}, {'Test Case ID': 'US27-TC05', 'Brief Description': 'Case Worker attempts to ignore alert and proceed without resolution (negative path).'}, {'Test Case ID': 'US27-TC06', 'Brief Description': 'Alert/audit log is generated for each detected conflict (compliance).'}]</t>
+          <t>[{'Test Case ID': '30-1', 'Brief Description': 'Successful export of filtered case data by a Case Manager.'}, {'Test Case ID': '30-2', 'Brief Description': 'Attempt export with no data (empty filter result).'}, {'Test Case ID': '30-3', 'Brief Description': 'Verify that unauthorized users cannot export case data.'}, {'Test Case ID': '30-4', 'Brief Description': 'Audit that all exports are logged.'}]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US27-TC01', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'Submit Application', 'Test Scenario Title': 'Household conflict triggers alert.', 'Precondition': 'Household data in new application conflicts with existing record.', 'Test Data': 'Duplicate or conflicting household details (e.g., same member with different DOB).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Enter household details in new application that conflict with another record.', 'Attempt to submit application.'], 'Expected Result': 'Pop-up or banner alert notifies Case Worker of data conflict, listing affected fields.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'US27-TC02', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'Resolve Data Conflict', 'Test Scenario Title': 'Case Worker resolves conflicting household data.', 'Precondition': 'System has flagged household conflict.', 'Test Data': 'Conflicting details; correct data available.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Observe conflict alert.', 'Edit household details to resolve discrepancy.', 'Re-submit application.'], 'Expected Result': 'System accepts update if no further conflict exists; no alert on re-submission.', 'Dependent Module/Process': 'Application Save Logic'}, {'Test Case ID': 'US27-TC03', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'No Conflict', 'Test Scenario Title': 'No alert is raised when data is unique.', 'Precondition': 'No conflicting household data in system.', 'Test Data': 'Unique household details.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Enter new, unique household details.', 'Submit application.'], 'Expected Result': 'Application is submitted with no alert.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'US27-TC04', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Integration', 'Sub-Process Title': 'Cross-Check API', 'Activity Title': 'API Testing', 'Test Scenario Title': 'API flags conflicting household data as expected.', 'Precondition': 'Conflicting and non-conflicting household data in source.', 'Test Data': 'Test endpoint with conflicting input household data.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call household data validation API with new application data.', 'Validate that response identifies conflicts accurately.'], 'Expected Result': 'API returns clear indication of any conflicts or passes if none.', 'Dependent Module/Process': 'Validation Microservice'}, {'Test Case ID': 'US27-TC05', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Application Processing', 'Sub-Process Title': 'Validation', 'Activity Title': 'Attempt Override', 'Test Scenario Title': 'Case Worker ignores alert and tries to proceed.', 'Precondition': 'Household conflict alert shown.', 'Test Data': 'Conflicting submission.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Dismiss conflict alert.', 'Attempt to submit application without resolving.'], 'Expected Result': 'System does not allow submission; persists alert and blocks progress until resolved.', 'Dependent Module/Process': 'Form Submission Validation'}, {'Test Case ID': 'US27-TC06', 'EPIC': 'Data Integrity', 'Feature': 'Conflict Detection', 'User Story': '#27', 'Business Process': 'Compliance/Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Alert Logging', 'Test Scenario Title': 'All conflict alerts and resolutions are audit-logged.', 'Precondition': 'System audit logging enabled.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Trigger household data conflict and resolve it.', 'Review audit log for entries including conflict, user, timestamps, and resolution actions.'], 'Expected Result': 'System logs all alerts and resolutions for audit/compliance.', 'Dependent Module/Process': 'Audit Logging'}]</t>
+          <t>[{'Test Case ID': '30-1', 'EPIC': 'Case Data Export', 'Feature': 'Export Functionality', 'User Story': '30', 'Business Process': 'Analytics/Reporting', 'Sub-Process Title': 'Data Export', 'Activity Title': 'Export Filtered Case List', 'Test Scenario Title': 'Successful export to Excel/CSV', 'Precondition': 'Case Manager is logged in; cases available; filter applied.', 'Test Data': {'Filter': 'Open cases assigned to team A'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Navigate to case list view.', 'Apply filter: Team = A, Status = Open.', "Click 'Export to Excel'.", 'Download and open resulting file.'], 'Expected Result': 'Excel/CSV file contains only open cases assigned to Team A, with accurate and well-formatted columns.', 'Dependent Module/Process': 'Case Management, Data Export'}, {'Test Case ID': '30-2', 'EPIC': 'Case Data Export', 'Feature': 'Export Functionality', 'User Story': '30', 'Business Process': 'Analytics/Reporting', 'Sub-Process Title': 'Data Export', 'Activity Title': 'Export Empty Result', 'Test Scenario Title': 'Export with empty filter result', 'Precondition': 'Case Manager is logged in; filter applied yields zero cases.', 'Test Data': {'Filter': 'Status = Closed, Date = Future'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Apply filter: Status = Closed, Date in future (no match).', "Click 'Export to Excel'."], 'Expected Result': "Excel/CSV file is generated with headers and no data rows, or a message: 'No data to export.'", 'Dependent Module/Process': 'Case Management, Data Export'}, {'Test Case ID': '30-3', 'EPIC': 'Case Data Export', 'Feature': 'Export Functionality', 'User Story': '30', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role-Based Authorization', 'Activity Title': 'Restrict Export', 'Test Scenario Title': 'Unauthorized user export attempt', 'Precondition': 'User is not a Case Manager (e.g., Case Worker or Basic User).', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Basic User', 'Detailed Test Steps': ['Login as Basic User.', 'Navigate to case list.', "Attempt to find or use 'Export to Excel' feature."], 'Expected Result': "'Export to Excel' is not available; if accessed via direct URL or API, system denies with 'Unauthorized' message.", 'Dependent Module/Process': 'Role Management, Data Export'}, {'Test Case ID': '30-4', 'EPIC': 'Case Data Export', 'Feature': 'Audit Logging', 'User Story': '30', 'Business Process': 'Compliance', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Log Export Event', 'Test Scenario Title': 'Audit export actions', 'Precondition': 'Case Manager has exported case data.', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['After export, access system audit logs.', 'Search for export event by username or timestamp.'], 'Expected Result': 'Audit log displays username, time, filter criteria, and whether export was successful.', 'Dependent Module/Process': 'Audit Logging, Data Export'}]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>This user story ensures case managers can assign cases to caseworkers who have matching language proficiency, thereby enhancing client satisfaction and service quality.</t>
+          <t>This user story ensures that Case Workers are notified when the system detects potential duplicate client applications, enabling effective data management and deduplication by merging them. This addresses data quality and process efficiency concerns.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to assign cases based on language preference so that clients receive better service. - Match caseworker language skills with client preference.</t>
+          <t>31: As a Case Worker, I want to receive alerts for duplicate applications so that I can merge them. - System detects and flags potential duplicates.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Case Manager selects a case. The system allows assignment only to caseworkers with matching or higher language proficiency as per the client’s preference. Assignment is successful and notified.</t>
+          <t>The Case Worker submits a new application. The system detects that the data matches another existing record, triggers an alert, and offers the option to review and merge the applications.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US28_TC1', 'Brief Description': 'Assign case to a caseworker with matching language proficiency (positive test).'}, {'Test Case ID': 'US28_TC2', 'Brief Description': 'Attempt to assign case to a caseworker without required language (negative test).'}, {'Test Case ID': 'US28_TC3', 'Brief Description': 'System filtering caseworkers by language skill in assignment (functional test).'}, {'Test Case ID': 'US28_TC4', 'Brief Description': 'Audit log records language-based assignment action (compliance test).'}, {'Test Case ID': 'US28_TC5', 'Brief Description': 'Verify data synchronization between case assignment and user profile modules (integration test).'}]</t>
+          <t>[{'Test Case ID': '31-01', 'Brief Description': 'System successfully detects duplicate application and notifies Case Worker'}, {'Test Case ID': '31-02', 'Brief Description': 'Case Worker reviews and merges duplicate applications'}, {'Test Case ID': '31-03', 'Brief Description': 'System does not detect duplicates for unique applications'}, {'Test Case ID': '31-04', 'Brief Description': 'System mistakenly flags a non-duplicate as duplicate (false positive)'}, {'Test Case ID': '31-05', 'Brief Description': 'User without merge permissions attempts to merge applications'}]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US28_TC1', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Cases', 'Activity Title': 'Assign based on language', 'Test Scenario Title': 'Successful assignment with language match', 'Precondition': 'Case manager and caseworker accounts exist; case has a required language; at least one caseworker with matching skill.', 'Test Data': {'Case ID': 'CASE123', 'Required Language': 'Spanish', 'Caseworker Skills': [{'User': 'CW001', 'Languages': ['Spanish', 'English']}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Open CASE123 with Spanish language preference.', "Click 'Assign Case'.", 'Select CW001 (Spanish, English) from eligible list.', 'Confirm assignment.'], 'Expected Result': 'Case is successfully assigned to CW001; assignment confirmation is displayed.', 'Dependent Module/Process': 'User Profile, Case Management'}, {'Test Case ID': 'US28_TC2', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Cases', 'Activity Title': 'Assign based on language', 'Test Scenario Title': 'Failed assignment when language skill missing', 'Precondition': 'Case manager and at least one caseworker without language skill; case specifies language.', 'Test Data': {'Case ID': 'CASE124', 'Required Language': 'Mandarin', 'Caseworker Skills': [{'User': 'CW002', 'Languages': ['English']}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Open CASE124 with Mandarin language preference.', "Click 'Assign Case'.", 'Attempt to select CW002 (English).', 'Confirm assignment.'], 'Expected Result': "System prevents assignment; error indicating 'Language skill mismatch'.", 'Dependent Module/Process': 'User Profile, Case Management'}, {'Test Case ID': 'US28_TC3', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Cases', 'Activity Title': 'Assign based on language', 'Test Scenario Title': 'Filter caseworkers by language dynamically', 'Precondition': 'Caseworker data with various language skills exists.', 'Test Data': {'Required Language': 'French', 'Available Caseworkers': [{'User': 'CW003', 'Languages': ['French', 'English']}, {'User': 'CW004', 'Languages': ['German']}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Attempt to assign case requiring French.', 'Observe displayed list of available caseworkers.'], 'Expected Result': 'Only CW003 (French) is displayed for selection; CW004 (German) is not.', 'Dependent Module/Process': 'User Profile'}, {'Test Case ID': 'US28_TC4', 'EPIC': 'Case Assignment', 'Feature': 'Audit', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignments', 'Activity Title': 'Audit trail', 'Test Scenario Title': 'Language-based assignment audit logged', 'Precondition': 'Case assignment occurs.', 'Test Data': {'Case ID': 'CASE125'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign CASE125 based on French preference.', 'Access audit logs.'], 'Expected Result': 'Audit log includes time, case ID, caseworker ID, assigning manager, and language filter details.', 'Dependent Module/Process': 'Audit, Logging'}, {'Test Case ID': 'US28_TC5', 'EPIC': 'Case Assignment', 'Feature': 'Integration', 'User Story': 'US28', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assignments', 'Activity Title': 'Data Synchronization', 'Test Scenario Title': 'Consistent language skill lookup between assignments and user profiles', 'Precondition': 'Caseworker language skills updated in profile service.', 'Test Data': {'CW005': 'Added Japanese'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Admin', 'Detailed Test Steps': ["As Admin, update CW005's profile: add Japanese.", 'As Case Manager, assign a Japanese language case.', 'Verify CW005 appears as eligible.'], 'Expected Result': 'CW005 is selectable after profile update, confirming real-time data sync.', 'Dependent Module/Process': 'User Profile, Case Assignment'}]</t>
+          <t>[{'Test Case ID': '31-01', 'EPIC': 'Application Processing', 'Feature': 'Duplicate Detection', 'User Story': '31', 'Business Process': 'Case Intake', 'Sub-Process Title': 'Application Submission', 'Activity Title': 'Duplicate Detection and Alert', 'Test Scenario Title': 'System detects and alerts on duplicate applications', 'Precondition': 'Case Worker has access to submit applications; duplicate detection rules configured.', 'Test Data': 'Application with data identical to an existing application (same SSN, DOB, Name, Address).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit a new application with data that matches an existing case.', 'Wait for system to process the application.', 'Observe if an alert/notification regarding a duplicate is received.'], 'Expected Result': 'System flags the application as a potential duplicate and notifies the Case Worker with relevant details.', 'Dependent Module/Process': 'Notification Service, Master Data Management'}, {'Test Case ID': '31-02', 'EPIC': 'Application Processing', 'Feature': 'Duplicate Resolution', 'User Story': '31', 'Business Process': 'Case Intake', 'Sub-Process Title': 'Application Review', 'Activity Title': 'Merging Duplicate Applications', 'Test Scenario Title': 'Case Worker merges flagged duplicate applications', 'Precondition': 'Duplicate applications are flagged; Case Worker has merge permissions.', 'Test Data': 'Two applications with overlapping personal information, flagged as duplicates.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Go to the duplicate alert screen.', 'Select duplicate applications.', 'Review overlap information.', 'Use the merge action as prompted.', 'Confirm and submit merge action.'], 'Expected Result': 'Applications are successfully merged; a single case record is retained; audit log is updated.', 'Dependent Module/Process': 'Case Record Management, Audit Logging'}, {'Test Case ID': '31-03', 'EPIC': 'Application Processing', 'Feature': 'Duplicate Detection', 'User Story': '31', 'Business Process': 'Case Intake', 'Sub-Process Title': 'Application Submission', 'Activity Title': 'Unique Application Handling', 'Test Scenario Title': 'System does not flag unique applications as duplicates', 'Precondition': 'No similar application exists in the database.', 'Test Data': 'Application with unique identifier data.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit a new application with unique personal data.', "Wait for system's duplicate check.", "Observe the application's status."], 'Expected Result': 'System does not create duplicate alerts or flags.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': '31-04', 'EPIC': 'Application Processing', 'Feature': 'Duplicate Detection', 'User Story': '31', 'Business Process': 'Case Intake', 'Sub-Process Title': 'Duplicate Checking', 'Activity Title': 'Handle False Positive Duplicates', 'Test Scenario Title': 'System incorrectly flags a unique application as duplicate', 'Precondition': 'Unique applications exist; duplicate detection threshold may be too sensitive.', 'Test Data': 'Applications with similar but not identical data.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit an application with data similar but not identical to an existing application.', 'Observe whether a duplicate alert is triggered.', 'Review system flagged duplicates.'], 'Expected Result': 'System may incorrectly flag; allows Case Worker to dismiss false duplicate.', 'Dependent Module/Process': 'Notification Service, Data Matching Logic'}, {'Test Case ID': '31-05', 'EPIC': 'Application Processing', 'Feature': 'Duplicate Resolution Security', 'User Story': '31', 'Business Process': 'Case Intake', 'Sub-Process Title': 'Application Review', 'Activity Title': 'Permissions Check', 'Test Scenario Title': 'Enforce permissions for merge action', 'Precondition': 'User without permission attempts to merge.', 'Test Data': 'Duplicate application flagged.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Observer', 'Detailed Test Steps': ['Login as Case Observer (read-only user).', 'Attempt to merge flagged duplicate applications.', 'Review error or system message.'], 'Expected Result': 'System denies merge attempt and displays appropriate error message.', 'Dependent Module/Process': 'Permissions Management'}]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>This user story enables case workers to preview documents before uploading them, reducing errors by allowing verification of scanned document accuracy.</t>
+          <t>This user story empowers Case Managers to monitor and track team activity and performance through customized, filterable monthly case reports, supporting accountability and resource management.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to preview documents before uploading so that I can ensure accuracy. - Preview pane for scanned documents.</t>
+          <t>32: As a Case Manager, I want to generate monthly reports of case activity so that I can track team performance. - Report builder with filters by worker and status.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case Worker uploads a scanned document, previews it in a pane, confirms its correctness, and uploads or cancels as needed.</t>
+          <t>Case Manager logs in, accesses the report builder, sets the date, worker, and status filters, and generates a downloadable monthly activity report.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US29_TC1', 'Brief Description': 'Preview and upload a valid scanned document (positive test).'}, {'Test Case ID': 'US29_TC2', 'Brief Description': 'Attempt to preview an unsupported file format (negative test).'}, {'Test Case ID': 'US29_TC3', 'Brief Description': 'Attempt to upload without previewing (control disabled).'}, {'Test Case ID': 'US29_TC4', 'Brief Description': 'Verify preview pane proper rendering for PDF and image files.'}, {'Test Case ID': 'US29_TC5', 'Brief Description': 'Audit logs record preview and upload action (compliance).'}]</t>
+          <t>[{'Test Case ID': '32-01', 'Brief Description': 'Case Manager generates a complete report for all workers and statuses.'}, {'Test Case ID': '32-02', 'Brief Description': 'Case Manager generates a filtered report by worker and/or status.'}, {'Test Case ID': '32-03', 'Brief Description': 'Case Manager attempts to generate a report without sufficient permissions.'}, {'Test Case ID': '32-04', 'Brief Description': 'System handles report generation for a month with no cases.'}, {'Test Case ID': '32-05', 'Brief Description': 'Case Manager exports or downloads the generated report.'}, {'Test Case ID': '32-06', 'Brief Description': 'Report reflects changes after status updates or case reassignment.'}]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US29_TC1', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Preview and Confirm Upload', 'Test Scenario Title': 'Successful document preview and upload', 'Precondition': 'User logged in as Case Worker.', 'Test Data': {'Document': 'valid_scan.pdf'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to case documents section.', "Click 'Upload Document'.", "Select 'valid_scan.pdf' for upload.", 'Preview pane displays the document.', "Click 'Confirm Upload'."], 'Expected Result': "'valid_scan.pdf' is visible in case documents; successful upload notification displayed.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC2', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Error Handling', 'Test Scenario Title': 'Unsupported file format preview fails', 'Precondition': 'User logged in. Unsupported file available.', 'Test Data': {'Document': 'unknown.xyz'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Click 'Upload Document'.", "Select 'unknown.xyz' for upload.", 'System attempts to preview but fails.'], 'Expected Result': "Error message 'Unsupported file format' displayed; upload disabled.", 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC3', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Preview Enforcement', 'Test Scenario Title': 'Upload disabled until previewed', 'Precondition': 'User logged in.', 'Test Data': {'Document': 'large_image.jpg'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select 'Upload Document'.", "Choose 'large_image.jpg'.", 'Attempt to upload without completing preview.'], 'Expected Result': 'Upload button remains disabled until preview completes.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC4', 'EPIC': 'Document Management', 'Feature': 'Document Upload &amp; Preview', 'User Story': 'US29', 'Business Process': 'Document Upload', 'Sub-Process Title': 'Preview Document', 'Activity Title': 'Multi-Format Preview', 'Test Scenario Title': 'Preview supports PDF and image files', 'Precondition': 'User logged in.', 'Test Data': {'PDF': 'scan.pdf', 'Image': 'photo.png'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Upload 'scan.pdf' and observe preview.", "Upload 'photo.png' and observe preview."], 'Expected Result': 'Both PDFs and images are rendered correctly in the preview pane.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US29_TC5', 'EPIC': 'Document Management', 'Feature': 'Audit', 'User Story': 'US29', 'Business Process': 'Document Management', 'Sub-Process Title': 'Preview and Upload', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Audit log for preview and upload', 'Precondition': 'User uploads document after preview.', 'Test Data': {'User': 'CW008', 'Document': 'confidential.pdf'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["CW008 previews and uploads 'confidential.pdf'.", 'Access audit logs.'], 'Expected Result': 'Audit log records user ID, document name, timestamp, and action: previewed/uploaded.', 'Dependent Module/Process': 'Audit, Logging'}]</t>
+          <t>[{'Test Case ID': '32-01', 'EPIC': 'Reporting', 'Feature': 'Monthly Activity Reporting', 'User Story': '32', 'Business Process': 'Performance Monitoring', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Full Report Generation', 'Test Scenario Title': 'Generate a complete monthly report for all cases', 'Precondition': 'Monthly case data is available; Case Manager has reporting permissions.', 'Test Data': 'Case activities from multiple workers across different statuses for the selected month.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to Report Builder.', 'Select the reporting month.', 'Leave worker and status filters as default (all).', 'Generate the report.', 'Review report content.'], 'Expected Result': 'Report displays activities for all workers and statuses within the selected month; data is accurate.', 'Dependent Module/Process': 'Case Management DB, Reporting Service'}, {'Test Case ID': '32-02', 'EPIC': 'Reporting', 'Feature': 'Monthly Activity Reporting', 'User Story': '32', 'Business Process': 'Performance Monitoring', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Filtered Report Generation', 'Test Scenario Title': 'Filter report by worker and/or case status', 'Precondition': 'Case activity data includes various workers and statuses.', 'Test Data': 'Cases by Worker A, Worker B; statuses: Open, Closed.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to Report Builder.', 'Select reporting month.', "Select Worker A and status 'Open'.", 'Generate the report.', 'Review report for correct filtering.'], 'Expected Result': "Report displays only cases handled by Worker A with status 'Open' for the selected month.", 'Dependent Module/Process': 'Case Assignment, Reporting Filters'}, {'Test Case ID': '32-03', 'EPIC': 'Reporting', 'Feature': 'Permissions', 'User Story': '32', 'Business Process': 'Performance Monitoring', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Permissions Check', 'Test Scenario Title': 'Non-manager user attempts report generation', 'Precondition': 'User with no report permissions.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Attempt to access Report Builder.', 'Try to generate a report.', 'Observe system response.'], 'Expected Result': 'Access is denied; system displays a permissions error.', 'Dependent Module/Process': 'Permissions/Access Control'}, {'Test Case ID': '32-04', 'EPIC': 'Reporting', 'Feature': 'Monthly Activity Reporting', 'User Story': '32', 'Business Process': 'Performance Monitoring', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Empty Data Handling', 'Test Scenario Title': 'Report for month with zero case activity', 'Precondition': 'Reporting period contains no case activity.', 'Test Data': 'Empty case data for entire month.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Select an empty month in Report Builder.', 'Generate the report.', 'Review the report.'], 'Expected Result': "Report generates successfully with 'No cases found' message.", 'Dependent Module/Process': 'Reporting Service'}, {'Test Case ID': '32-05', 'EPIC': 'Reporting', 'Feature': 'Export/Download', 'User Story': '32', 'Business Process': 'Performance Monitoring', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Exporting Reports', 'Test Scenario Title': 'Download or export generated report', 'Precondition': 'Report successfully generated.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Generate a report in Report Builder.', 'Click the export/download button.', 'Select format (e.g., PDF, CSV).', 'Save the file.'], 'Expected Result': 'Report is downloaded in selected format and opens correctly.', 'Dependent Module/Process': 'Export Module'}, {'Test Case ID': '32-06', 'EPIC': 'Reporting', 'Feature': 'Data Accuracy', 'User Story': '32', 'Business Process': 'Performance Monitoring', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'data consistency', 'Test Scenario Title': 'Report reflects updated data after status change', 'Precondition': 'At least one case status or assignment changed during the reporting period.', 'Test Data': 'Case status update on 5th of month.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Change status of a case during the month.', 'Generate report for that month for all statuses.', 'Verify that the report accurately reflects the status change.'], 'Expected Result': 'Report accurately matches the updated data.', 'Dependent Module/Process': 'Case Management System'}]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>This user story provides case managers with the functionality to export filtered case data to Excel/CSV, supporting offline analysis while ensuring data privacy compliance.</t>
+          <t>This user story ensures that Case Workers receive timely notifications about updates to eligibility rules, supporting consistent and compliant assessments and safeguarding the program against outdated evaluations.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to export case data to Excel so that I can analyze it offline. - Export filtered case lists to CSV/Excel.</t>
+          <t>33: As a Case Worker, I want to receive alerts when eligibility rules change so that I can adjust my assessments. - System notification of policy updates.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Case Manager filters case list, clicks export, downloads a correctly formatted and complete Excel file of visible data only.</t>
+          <t>System administrator updates eligibility rules. All relevant Case Workers receive notifications or alerts. Case Worker acknowledges the notification before proceeding with assessments.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US30_TC1', 'Brief Description': 'Export filtered case list to Excel (positive test).'}, {'Test Case ID': 'US30_TC2', 'Brief Description': 'Attempt export with no data after applying filters (negative test).'}, {'Test Case ID': 'US30_TC3', 'Brief Description': 'Verify exported data does not include unauthorized data (permissions/compliance).'}, {'Test Case ID': 'US30_TC4', 'Brief Description': 'Validate audit trail for export operation (compliance, GDPR).'}, {'Test Case ID': 'US30_TC5', 'Brief Description': 'Verify API sends correct filter criteria during export (API/integration test).'}]</t>
+          <t>[{'Test Case ID': '33-01', 'Brief Description': 'Case Worker receives notification immediately after eligibility rule change.'}, {'Test Case ID': '33-02', 'Brief Description': 'Case Worker acknowledges notification and continues assessment.'}, {'Test Case ID': '33-03', 'Brief Description': 'Case Worker attempts to proceed without acknowledging rule change notification.'}, {'Test Case ID': '33-04', 'Brief Description': 'Case Worker account not in alert recipient group does not receive notification.'}, {'Test Case ID': '33-05', 'Brief Description': 'System logs alerts for auditing purposes (compliance).'}]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US30_TC1', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Case List Export', 'Activity Title': 'Filter and Export', 'Test Scenario Title': 'Successful export of filtered case data', 'Precondition': 'User logged in as Case Manager; cases exist; filter applied.', 'Test Data': {'Filter': 'Status = Open', 'Expected Export Rows': 5}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Apply filter: Status = Open.', "Click 'Export to Excel'.", 'Download the .xlsx file.', 'Open file to verify contents.'], 'Expected Result': 'Excel contains only 5 rows with Status = Open; format matches requirements.', 'Dependent Module/Process': 'Reporting, Export Module'}, {'Test Case ID': 'US30_TC2', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Case List Export', 'Activity Title': 'Filter and Export', 'Test Scenario Title': 'Attempt export with no data after filtering', 'Precondition': 'User logged in; cases exist; filter reduces visible list to 0.', 'Test Data': {'Filter': 'Status = Archived'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Apply filter: Status = Archived (no results expected).', "Click 'Export to Excel'."], 'Expected Result': "System displays message: 'No data to export.'; no file generated.", 'Dependent Module/Process': 'Reporting, Export Module'}, {'Test Case ID': 'US30_TC3', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Permissions and Data Privacy', 'Activity Title': 'Restricted Data Export', 'Test Scenario Title': 'Exported data excludes unauthorized information', 'Precondition': 'Case Manager does not have access to sensitive fields.', 'Test Data': {'Fields': ['Basic Info', 'Sensitive Info']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Filter and view cases with sensitive information field.', 'Export case list to Excel.', 'Open and review file.'], 'Expected Result': "Excel excludes unauthorized columns (e.g., 'Sensitive Info').", 'Dependent Module/Process': 'Data Privacy, Role Management'}, {'Test Case ID': 'US30_TC4', 'EPIC': 'Case Management Reporting', 'Feature': 'Export to Excel', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'Audit', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Audit log records export action', 'Precondition': 'Export action performed.', 'Test Data': {'User': 'CM010', 'Action': 'Export'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['CM010 filters case list and clicks export.', 'Access and review audit logs (download event).'], 'Expected Result': 'Audit log captures time, user, filters used, and confirmation of data file generation.', 'Dependent Module/Process': 'Audit, Export, Compliance'}, {'Test Case ID': 'US30_TC5', 'EPIC': 'Case Management Reporting', 'Feature': 'Export API', 'User Story': 'US30', 'Business Process': 'Export', 'Sub-Process Title': 'API', 'Activity Title': 'Export Invocation', 'Test Scenario Title': 'Correct filter passed to export API', 'Precondition': 'API logging enabled; filter applied.', 'Test Data': {'API Endpoint': '/api/cases/export', 'Filter Sent': 'Status = Open'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Apply filter (Status = Open) in UI.', 'Trigger export.', 'Monitor API request payload.'], 'Expected Result': "API request body includes applied filter ('Status = Open'); export reflects UI filter.", 'Dependent Module/Process': 'Export API, Reporting'}]</t>
+          <t>[{'Test Case ID': '33-01', 'EPIC': 'Policy Management', 'Feature': 'Eligibility Rule Update', 'User Story': '33', 'Business Process': 'Assessment', 'Sub-Process Title': 'Policy Broadcast', 'Activity Title': 'Eligibility Rule Change Notification', 'Test Scenario Title': 'Case Worker is promptly notified of eligibility rule change', 'Precondition': 'Eligibility rules exist; system allows for rule updates; user has notification permissions.', 'Test Data': 'Eligibility rule updated by System Admin.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['System Admin updates eligibility rule.', 'Case Worker logs into the system within notification window.', 'Review notification center or alert area.'], 'Expected Result': 'Case Worker receives in-app and/or email notification of eligibility rule change.', 'Dependent Module/Process': 'Notification Service, Policy Management'}, {'Test Case ID': '33-02', 'EPIC': 'Policy Management', 'Feature': 'Eligibility Rule Update', 'User Story': '33', 'Business Process': 'Assessment', 'Sub-Process Title': 'Policy Broadcast', 'Activity Title': 'Acknowledge Notification', 'Test Scenario Title': 'Case Worker acknowledges receipt of update before proceeding', 'Precondition': 'Eligibility rule change notification is displayed to Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker receives rule update notification.', 'Review content of policy update.', 'Acknowledge notification via confirmation action.', 'Proceed to case assessment.'], 'Expected Result': 'Acknowledge recorded in system. Case Worker can proceed with assessment using new rules.', 'Dependent Module/Process': 'Notification System, Assessment Module'}, {'Test Case ID': '33-03', 'EPIC': 'Policy Management', 'Feature': 'Eligibility Rule Update', 'User Story': '33', 'Business Process': 'Assessment', 'Sub-Process Title': 'Policy Broadcast', 'Activity Title': 'Block Actions Until Acknowledgement', 'Test Scenario Title': 'Prevent assessments until notification is acknowledged', 'Precondition': 'New eligibility rule has been published; user has not acknowledged notification.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker logs in post-rule change.', 'Attempts to start or complete a case assessment.', 'Observe if access is blocked by pending notification.'], 'Expected Result': 'Assessment or actions are blocked until notification is acknowledged.', 'Dependent Module/Process': 'Notification Handling, UI Controls'}, {'Test Case ID': '33-04', 'EPIC': 'Policy Management', 'Feature': 'Eligibility Rule Update', 'User Story': '33', 'Business Process': 'Assessment', 'Sub-Process Title': 'Policy Broadcast', 'Activity Title': 'Notification Recipient Control', 'Test Scenario Title': 'Users without Case Worker role do not receive eligibility alerts', 'Precondition': 'Eligibility rule is updated; some users are not in alert recipient group.', 'Test Data': 'User with different role (e.g., Case Observer).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Observer', 'Detailed Test Steps': ['Update eligibility rule as System Admin.', 'Login as Case Observer.', 'Check notification center/alert inbox.', 'Verify absence of eligibility rule update alert.'], 'Expected Result': 'No notification shown to Case Observer or irrelevant roles.', 'Dependent Module/Process': 'Notification Service, Role Management'}, {'Test Case ID': '33-05', 'EPIC': 'Policy Management', 'Feature': 'Audit and Compliance', 'User Story': '33', 'Business Process': 'Assessment', 'Sub-Process Title': 'Compliance Logging', 'Activity Title': 'Notification and Acknowledgement Audit', 'Test Scenario Title': 'System logs notifications and acknowledgements for audit purposes', 'Precondition': 'Rule update occurs; Case Worker acknowledges notification.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Admin', 'Detailed Test Steps': ['Perform eligibility rule update as Admin.', 'Receive and acknowledge notification as Case Worker.', 'Audit Admin accesses logs/audit trail.', 'Review entries related to rule update, notification issuance, and acknowledgment.'], 'Expected Result': 'Audit trail captures rule update, notification delivery, and acknowledgment events with timestamps and user IDs.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>This user story focuses on improving data integrity and workload management by alerting case workers to duplicate application submissions, enabling them to merge records and maintain a single, authoritative client file.</t>
+          <t>This user story ensures Case Managers can monitor overdue redetermination cases with follow-up actions, ensuring regulatory compliance and audit readiness.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to receive alerts for duplicate applications so that I can merge them. - System detects and flags potential duplicates.</t>
+          <t>As a Case Manager, I want to track overdue redeterminations so that I can ensure compliance. - List of overdue cases with follow-up actions.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>When a new application is submitted, the system checks for existing applications with matching identifiers (e.g., name, date of birth, SSN). If matches are found, the system alerts the case worker, allowing them to review and merge duplicates.</t>
+          <t>Case Manager logs in, views a list of overdue redeterminations, reviews suggested follow-up actions, and records a follow-up.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': '31-FUNC-01', 'Brief Description': 'Detect and alert on new duplicate application.'}, {'Test Case ID': '31-FUNC-02', 'Brief Description': 'System does not flag non-duplicates.'}, {'Test Case ID': '31-FUNC-03', 'Brief Description': 'Case worker merges duplicates successfully.'}, {'Test Case ID': '31-FUNC-04', 'Brief Description': 'Case worker attempts to merge non-duplicates.'}, {'Test Case ID': '31-API-01', 'Brief Description': 'API returns flagged duplicates for given input.'}, {'Test Case ID': '31-E2E-01', 'Brief Description': 'End-to-end: Submission, alert, review, and merge.'}, {'Test Case ID': '31-SEC-01', 'Brief Description': 'Case worker without merge permission attempts to merge.'}, {'Test Case ID': '31-COMP-01', 'Brief Description': 'Audit trail generated for merge operation.'}]</t>
+          <t>[{'Test Case ID': '34-FUNC-01', 'Brief Description': 'Display list of overdue redeterminations with follow-up actions for valid Case Manager.'}, {'Test Case ID': '34-FUNC-02', 'Brief Description': 'No overdue redeterminations results in empty state with appropriate message.'}, {'Test Case ID': '34-NEG-01', 'Brief Description': 'User without Case Manager role attempts to access overdue redeterminations list.'}, {'Test Case ID': '34-API-01', 'Brief Description': 'API returns accurate and complete list of overdue redeterminations.'}, {'Test Case ID': '34-E2E-01', 'Brief Description': 'Case Manager follows up on an overdue redetermination and action is logged.'}, {'Test Case ID': '34-COMP-01', 'Brief Description': 'List is audit logged and meets compliance requirements.'}]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': '31-FUNC-01', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Application Detection', 'User Story': '31', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicate Check', 'Activity Title': 'Submit New Application', 'Test Scenario Title': 'Alert On Duplicate Application', 'Precondition': 'A similar application already exists in the system.', 'Test Data': 'Applicant with same name, DOB, and SSN as an existing record.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit a new application with matching identifiers.', 'System checks for duplicates.', 'System displays alert to user.'], 'Expected Result': 'Case worker receives a duplicate alert; application is flagged for review.', 'Dependent Module/Process': 'Database'}, {'Test Case ID': '31-FUNC-02', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Application Detection', 'User Story': '31', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicate Check', 'Activity Title': 'Submit Non-Duplicate Application', 'Test Scenario Title': 'No Alert On Unique Application', 'Precondition': 'No matching application in the system.', 'Test Data': 'Applicant with unique identifiers.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Submit a new application with unique identifiers.'], 'Expected Result': 'No duplicate alert; application proceeds normally.', 'Dependent Module/Process': 'Database'}, {'Test Case ID': '31-FUNC-03', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Management', 'User Story': '31', 'Business Process': 'Case Management', 'Sub-Process Title': 'Merge Records', 'Activity Title': 'Merge Duplicate Applications', 'Test Scenario Title': 'Successful Merge', 'Precondition': 'Duplicate applications flagged.', 'Test Data': 'Two applications flagged as duplicates.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to flagged duplicates.', 'Select merge option.', 'Resolve data conflicts if prompted.', 'Complete merge operation.'], 'Expected Result': 'Applications merged; single record retained; audit trail logged.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': '31-FUNC-04', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Management', 'User Story': '31', 'Business Process': 'Case Management', 'Sub-Process Title': 'Merge Records', 'Activity Title': 'Attempt Merge of Non-Duplicates', 'Test Scenario Title': 'Erroneous Merge Attempt Blocked', 'Precondition': 'Two clearly non-duplicate applications exist.', 'Test Data': 'Applications with unique identifiers.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Attempt to merge two unrelated applications.'], 'Expected Result': 'System blocks merge and shows error.', 'Dependent Module/Process': 'Validation Service'}, {'Test Case ID': '31-API-01', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Application Detection API', 'User Story': '31', 'Business Process': 'Backend Services', 'Sub-Process Title': 'API Call', 'Activity Title': 'Duplicate Check Service', 'Test Scenario Title': 'API Flags Duplicates', 'Precondition': 'API exposed for duplicate checking.', 'Test Data': "{ 'name': 'Jane Doe', 'dob': '1990-01-01', 'ssn': '123-45-6789' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call API with duplicate applicant data.'], 'Expected Result': 'API returns duplicate flag with matched record IDs.', 'Dependent Module/Process': 'API Gateway'}, {'Test Case ID': '31-E2E-01', 'EPIC': 'Data Integrity', 'Feature': 'Duplicate Processing', 'User Story': '31', 'Business Process': 'Application Submission to Merge', 'Sub-Process Title': 'End-to-End Flow', 'Activity Title': 'Duplicate Alert to Merge Completion', 'Test Scenario Title': 'E2E Duplicate Detection and Merge', 'Precondition': 'At least one duplicate exists in the database.', 'Test Data': 'Valid and duplicate applicant submissions.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit application.', 'System alerts on duplicate.', 'Review flagged application.', 'Merge duplicated records.'], 'Expected Result': 'User notified; records merged successfully; audit entry created.', 'Dependent Module/Process': 'Database, Audit'}, {'Test Case ID': '31-SEC-01', 'EPIC': 'Data Integrity', 'Feature': 'Role-Based Access', 'User Story': '31', 'Business Process': 'Permissions Enforcement', 'Sub-Process Title': 'Merge Authorization', 'Activity Title': 'Unauthorized User Attempts Merge', 'Test Scenario Title': 'Permission Enforcement', 'Precondition': 'User has view-only permission.', 'Test Data': 'Flagged duplicates present.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (No Merge Permission)', 'Detailed Test Steps': ['Login as user without merge rights.', 'Attempt to merge flagged applications.'], 'Expected Result': 'System denies merge; appropriate error displayed.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': '31-COMP-01', 'EPIC': 'Compliance', 'Feature': 'Audit Logging', 'User Story': '31', 'Business Process': 'Audit &amp; Monitoring', 'Sub-Process Title': 'Log Creation', 'Activity Title': 'Merge Operation Logged', 'Test Scenario Title': 'Audit Log Verification', 'Precondition': 'User merges duplicate applications.', 'Test Data': 'Duplicate merge event.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Merge duplicate applications.', 'Review audit logs.'], 'Expected Result': 'Audit log captures user, timestamp, and details of merge operation.', 'Dependent Module/Process': 'Audit Logging'}]</t>
+          <t>[{'Test Case ID': '34-FUNC-01', 'EPIC': 'Redetermination Tracking', 'Feature': 'Overdue Case Management', 'User Story': '34', 'Business Process': 'Case Compliance and Tracking', 'Sub-Process Title': 'Overdue Redeterminations', 'Activity Title': 'Display Overdue Redeterminations', 'Test Scenario Title': 'Display overdue list to authorized user', 'Precondition': 'At least one overdue redetermination exists in the system; user is logged in as Case Manager.', 'Test Data': 'Overdue case records populated in test environment.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to Overdue Redeterminations screen.', 'Observe the list and available follow-up actions.'], 'Expected Result': 'A list of overdue redeterminations is displayed with correct details and actionable items.', 'Dependent Module/Process': 'Case Management Module'}, {'Test Case ID': '34-NEG-01', 'EPIC': 'Redetermination Tracking', 'Feature': 'Overdue Case Management', 'User Story': '34', 'Business Process': 'Case Compliance and Tracking', 'Sub-Process Title': 'Overdue Redeterminations', 'Activity Title': 'Restrict Unauthorized Access', 'Test Scenario Title': 'Restrict non-Case Manager access', 'Precondition': 'Valid user account with insufficient privileges.', 'Test Data': 'None required.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Attempt to access Overdue Redeterminations screen.'], 'Expected Result': 'User receives access denied error or does not see the menu item.', 'Dependent Module/Process': 'Authentication/Authorization'}, {'Test Case ID': '34-API-01', 'EPIC': 'Redetermination Tracking', 'Feature': 'Overdue Case Management API', 'User Story': '34', 'Business Process': 'External System Integration', 'Sub-Process Title': 'API', 'Activity Title': 'API returns correct overdue list', 'Test Scenario Title': 'Validate overdue redeterminations API', 'Precondition': 'Overdue cases seeded.', 'Test Data': 'Sample overdue cases in the backend.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Service Account', 'Detailed Test Steps': ['Send GET request to /redeterminations/overdue endpoint.', 'Verify the response schema and data content.'], 'Expected Result': 'API returns a correct, complete list of overdue redeterminations.', 'Dependent Module/Process': 'API Gateway, Backend'}, {'Test Case ID': '34-E2E-01', 'EPIC': 'Redetermination Tracking', 'Feature': 'Overdue Case Management', 'User Story': '34', 'Business Process': 'Compliance Management', 'Sub-Process Title': 'Follow-up Actions', 'Activity Title': 'Follow-up on Overdue Redetermination', 'Test Scenario Title': 'Perform and log follow-up action', 'Precondition': 'Overdue case present for Case Manager.', 'Test Data': 'Case with overdue redetermination.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to overdue redeterminations list.', 'Select an overdue case.', 'Perform a follow-up action (e.g., send reminder, log a note).'], 'Expected Result': 'Follow-up action is recorded, timestamped, and visible in case history.', 'Dependent Module/Process': 'Case Management, Audit Log'}, {'Test Case ID': '34-COMP-01', 'EPIC': 'Redetermination Tracking', 'Feature': 'Compliance and Audit', 'User Story': '34', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Audit', 'Activity Title': 'Ensure Compliance Logging', 'Test Scenario Title': 'Overdue list is audit logged', 'Precondition': 'Overdue redetermination cases exist.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit/Compliance User', 'Detailed Test Steps': ['Perform actions on overdue redetermination list as Case Manager.', 'Review system audit logs as Audit user.'], 'Expected Result': 'All access and actions on overdue redeterminations are recorded per compliance policies.', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>This user story ensures that Case Managers can monitor and evaluate team performance efficiently by providing a flexible report builder to generate, filter, and export monthly activity reports based on worker and status.</t>
+          <t>This user story ensures Case Workers can print clear, accurate summaries of case notes for inclusion in physical records, supporting audits and workflows.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to generate monthly reports of case activity so that I can track team performance. - Report builder with filters by worker and status.</t>
+          <t>As a Case Worker, I want to print a summary of case notes so that I can include them in physical files. - Printable case note summary.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Case Manager accesses the reporting tool, selects the required reporting period, applies filters such as worker and status, and generates a monthly report summarizing case activities.</t>
+          <t>Case Worker selects a case, clicks 'Print Summary', and receives a formatted, printable summary with all relevant case notes.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': '32-FUNC-01', 'Brief Description': 'Generate unfiltered case activity report.'}, {'Test Case ID': '32-FUNC-02', 'Brief Description': 'Generate filtered report by worker.'}, {'Test Case ID': '32-FUNC-03', 'Brief Description': 'Generate filtered report by status.'}, {'Test Case ID': '32-FUNC-04', 'Brief Description': 'No results with unavailable filters.'}, {'Test Case ID': '32-API-01', 'Brief Description': 'API returns correct report data for query.'}, {'Test Case ID': '32-E2E-01', 'Brief Description': 'End-to-end: Report generation, export, and review.'}, {'Test Case ID': '32-SEC-01', 'Brief Description': 'Permission: Unprivileged user attempts report access.'}, {'Test Case ID': '32-COMP-01', 'Brief Description': 'Audit trail for report access and export.'}]</t>
+          <t>[{'Test Case ID': '35-FUNC-01', 'Brief Description': 'Print button displays printable case summary as Case Worker.'}, {'Test Case ID': '35-FUNC-02', 'Brief Description': 'Printable summary contains accurate, current, and complete case notes.'}, {'Test Case ID': '35-NEG-01', 'Brief Description': 'Unauthorized user attempts to print case note summary.'}, {'Test Case ID': '35-NEG-02', 'Brief Description': 'Attempt to print a summary for a case with no case notes.'}, {'Test Case ID': '35-E2E-01', 'Brief Description': 'Case note summary is generated, displayed, and sent to the printer.'}, {'Test Case ID': '35-COMP-01', 'Brief Description': 'Printed notes conform to information security and privacy regulations.'}]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': '32-FUNC-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Case Activity Report', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Generate Full Report', 'Test Scenario Title': 'Generate Monthly Case Report (All Filters)', 'Precondition': 'Cases exist in database for the reporting period.', 'Test Data': 'Case activity data for multiple workers and statuses.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to report builder.', 'Select current month.', 'Generate report without filters.'], 'Expected Result': 'System displays complete case activity report for the period.', 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-FUNC-02', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Report Filtering', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Filter By Worker', 'Test Scenario Title': 'Filter Report By Worker', 'Precondition': 'Cases assigned to different workers exist.', 'Test Data': 'Case activity records with assigned worker IDs.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to report builder.', 'Select worker from filter options.', 'Generate report.'], 'Expected Result': 'Report shows only cases assigned to selected worker.', 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-FUNC-03', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Report Filtering', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Filter By Status', 'Test Scenario Title': 'Filter Report By Status', 'Precondition': 'Cases with various statuses (e.g., open, closed) exist.', 'Test Data': "Case activity records with 'Open' and 'Closed' statuses.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to report builder.', "Select status filter (e.g., 'Open').", 'Generate report.'], 'Expected Result': 'Report shows only cases with selected status.', 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-FUNC-04', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Report Filtering', 'User Story': '32', 'Business Process': 'Performance Tracking', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Unavailable Filters', 'Test Scenario Title': 'No Results With Unavailable Filter', 'Precondition': 'No cases match filter criteria.', 'Test Data': 'No case for worker X in reporting period.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Apply filter with no matching cases.', 'Generate report.'], 'Expected Result': "Report shows 'No data available' or empty result.", 'Dependent Module/Process': 'Reporting Module'}, {'Test Case ID': '32-API-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Reporting API', 'User Story': '32', 'Business Process': 'Backend Reporting', 'Sub-Process Title': 'API Query', 'Activity Title': 'API Case Activity Report Query', 'Test Scenario Title': 'API Data Fetch and Filter', 'Precondition': 'API exposed for report queries.', 'Test Data': "{ 'period': '2024-05', 'worker': '123', 'status': 'Open' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System', 'Detailed Test Steps': ['Call reporting API with selected filters.'], 'Expected Result': 'API returns correct filtered report data.', 'Dependent Module/Process': 'API, Reporting DB'}, {'Test Case ID': '32-E2E-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'End-to-End Reporting', 'User Story': '32', 'Business Process': 'Report Management', 'Sub-Process Title': 'E2E Flow', 'Activity Title': 'Report Generation to Export', 'Test Scenario Title': 'Full E2E Report Generation and Export', 'Precondition': 'Reporting module active and populated.', 'Test Data': 'All relevant case activity.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Generate monthly report.', 'Export report (e.g., CSV, PDF).', 'Review downloaded file.'], 'Expected Result': 'Report is generated, exported, and data matches on-screen results.', 'Dependent Module/Process': 'Export Service'}, {'Test Case ID': '32-SEC-01', 'EPIC': 'Reporting &amp; Analytics', 'Feature': 'Permission Enforcement', 'User Story': '32', 'Business Process': 'Security', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Unauthorized Report Access', 'Test Scenario Title': 'Access Denied for Unprivileged User', 'Precondition': 'User assigned role without report access.', 'Test Data': 'N/A', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Attempt to access report builder.'], 'Expected Result': 'Access denied; error or redirect shown.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': '32-COMP-01', 'EPIC': 'Compliance', 'Feature': 'Audit Logging', 'User Story': '32', 'Business Process': 'Audit &amp; Reporting', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Report Generation Logging', 'Test Scenario Title': 'Audit Trail For Report Actions', 'Precondition': 'Case Manager generates and exports a report.', 'Test Data': 'Report event activity.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Generate and export report.', 'Review audit logs.'], 'Expected Result': 'Audit entry exists for report generation and export (timestamp, user, filters).', 'Dependent Module/Process': 'Audit Logging'}]</t>
+          <t>[{'Test Case ID': '35-FUNC-01', 'EPIC': 'Case Documentation', 'Feature': 'Printable Case Notes', 'User Story': '35', 'Business Process': 'Case Documentation Handling', 'Sub-Process Title': 'Print Case Notes', 'Activity Title': 'Display Print Option', 'Test Scenario Title': 'Verify print option displays printable summary', 'Precondition': 'Case with existing notes; user logged in as Case Worker.', 'Test Data': 'Case with multiple notes present.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Open a case with notes.', "Click 'Print Summary'."], 'Expected Result': 'System displays printable, well-formatted case note summary.', 'Dependent Module/Process': 'Case Notes Module'}, {'Test Case ID': '35-FUNC-02', 'EPIC': 'Case Documentation', 'Feature': 'Printable Case Notes', 'User Story': '35', 'Business Process': 'Case Documentation Handling', 'Sub-Process Title': 'Print Case Notes', 'Activity Title': 'Print Content Verification', 'Test Scenario Title': 'Printable summary content validation', 'Precondition': 'Case with diverse notes.', 'Test Data': 'Case with multiple, multi-format notes (text, date/time, author).', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Print the case note summary.', 'Verify all notes are present, in correct order, with all reference data.'], 'Expected Result': 'Printable summary contains all case notes, metadata, and is up-to-date.', 'Dependent Module/Process': 'Case Notes, Document Formatting'}, {'Test Case ID': '35-NEG-01', 'EPIC': 'Case Documentation', 'Feature': 'Printable Case Notes', 'User Story': '35', 'Business Process': 'Case Documentation Handling', 'Sub-Process Title': 'Print Case Notes', 'Activity Title': 'Access Control', 'Test Scenario Title': 'Unauthorized print attempt', 'Precondition': 'Valid user without printing permission.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'External Viewer', 'Detailed Test Steps': ['Log in as unauthorized user.', 'Navigate to a case.', 'Attempt to access or use the print summary option.'], 'Expected Result': 'Print functionality is not visible or is blocked with an error.', 'Dependent Module/Process': 'Authorization/Permissions'}, {'Test Case ID': '35-NEG-02', 'EPIC': 'Case Documentation', 'Feature': 'Printable Case Notes', 'User Story': '35', 'Business Process': 'Case Documentation Handling', 'Sub-Process Title': 'Print Case Notes', 'Activity Title': 'Edge Case Handling', 'Test Scenario Title': 'Print with no case notes', 'Precondition': 'Case exists but has no notes.', 'Test Data': 'Case with zero notes.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select a case with no notes.', "Click 'Print Summary'."], 'Expected Result': "User receives message 'No case notes to print' or prints a blank/empty summary.", 'Dependent Module/Process': 'UI, Case Notes'}, {'Test Case ID': '35-E2E-01', 'EPIC': 'Case Documentation', 'Feature': 'Printable Case Notes', 'User Story': '35', 'Business Process': 'Physical Documentation', 'Sub-Process Title': 'Printing', 'Activity Title': 'End-to-End Print Flow', 'Test Scenario Title': 'Full workflow for printing summary', 'Precondition': 'Case with notes; printer available.', 'Test Data': 'Case with test notes.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select case and open summary.', "Click 'Print Summary'.", 'Send print job to printer.', 'Retrieve physical printout.'], 'Expected Result': 'Physical summary matches displayed/expected content and formatting.', 'Dependent Module/Process': 'Case Notes, Print Service'}, {'Test Case ID': '35-COMP-01', 'EPIC': 'Case Documentation', 'Feature': 'Printable Case Notes', 'User Story': '35', 'Business Process': 'Compliance', 'Sub-Process Title': 'Security/Privacy', 'Activity Title': 'Regulatory Compliance', 'Test Scenario Title': 'Printout meets security/privacy requirements', 'Precondition': 'Printing sensitive data.', 'Test Data': 'Sensitive case note examples.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Compliance Officer', 'Detailed Test Steps': ['Print case summaries containing personal/confidential data.', 'Verify compliance marking (e.g., watermarks, access restrictions, mandatory audit logs).'], 'Expected Result': 'Printout complies with applicable information security and privacy standards (e.g., PII redaction, logs are kept).', 'Dependent Module/Process': 'Compliance, Print Service'}]</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>This user story provides important controls for compliance and operational accuracy by informing case workers of updates to eligibility rules, ensuring that assessments reflect current policies.</t>
+          <t>This user story provides Case Managers with timely alerts on case inactivity (60 days), supporting proactive follow-up and audit/compliance readiness.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to receive alerts when eligibility rules change so that I can adjust my assessments. - System notification of policy updates.</t>
+          <t>As a Case Manager, I want to receive alerts when a case is inactive for 60 days so that I can follow up. - Inactivity alerts with case history.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The system notifies all relevant case workers via dashboard alert, email, or in-app notification when an eligibility rule is updated, allowing timely review and adjustment of ongoing or new assessments.</t>
+          <t>Case Manager is automatically alerted (email or in-app) for each case inactive for 60 days and follows the provided link to review and take action.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': '33-FUNC-01', 'Brief Description': 'Notification sent for eligibility rule update.'}, {'Test Case ID': '33-FUNC-02', 'Brief Description': 'Case Worker acknowledges alert.'}, {'Test Case ID': '33-FUNC-03', 'Brief Description': 'No alerts sent if no change.'}, {'Test Case ID': '33-E2E-01', 'Brief Description': 'End-to-end: Rule change triggers notification and case worker updates assessment.'}, {'Test Case ID': '33-SEC-01', 'Brief Description': 'Unauthorized user does not receive notifications.'}, {'Test Case ID': '33-COMP-01', 'Brief Description': 'Audit log of policy update and notifications.'}]</t>
+          <t>[{'Test Case ID': '36-FUNC-01', 'Brief Description': 'Case Manager receives alert for 60-day inactive case.'}, {'Test Case ID': '36-FUNC-02', 'Brief Description': 'Each alert includes case history link/information.'}, {'Test Case ID': '36-NEG-01', 'Brief Description': 'Non-Case Manager does not receive inactivity alerts.'}, {'Test Case ID': '36-API-01', 'Brief Description': 'API delivers notification for each 60-day inactive case.'}, {'Test Case ID': '36-E2E-01', 'Brief Description': 'Case Manager receives alert, reviews case, and records a follow-up.'}, {'Test Case ID': '36-COMP-01', 'Brief Description': 'Alert activity and follow-up are audit logged and meet compliance.'}]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': '33-FUNC-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'Rule Notifications', 'User Story': '33', 'Business Process': 'Policy Update Alerts', 'Sub-Process Title': 'Notification Distribution', 'Activity Title': 'Send Alert On Rule Change', 'Test Scenario Title': 'Notification Sent to Case Workers', 'Precondition': 'Eligibility rule is updated by administrator.', 'Test Data': 'Amend rule: Change income threshold from $1500 to $1400.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Admin updates eligibility rule.', 'System triggers notification event.', 'Case worker logs in to application.'], 'Expected Result': 'Case worker receives prompt notification of rule change.', 'Dependent Module/Process': 'Notifications, Policy Management'}, {'Test Case ID': '33-FUNC-02', 'EPIC': 'Eligibility Compliance', 'Feature': 'Alert Acknowledgement', 'User Story': '33', 'Business Process': 'Policy Update Alerts', 'Sub-Process Title': 'Acknowledgement', 'Activity Title': 'Acknowledge Policy Alert', 'Test Scenario Title': 'User Acknowledges Alert', 'Precondition': 'Case worker has received a policy update alert.', 'Test Data': 'Active user.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'View policy update alert.', 'Acknowledge (e.g., click "Acknowledge" button).'], 'Expected Result': 'Alert marked as read/acknowledged, recorded in user history.', 'Dependent Module/Process': 'User Notification Center'}, {'Test Case ID': '33-FUNC-03', 'EPIC': 'Eligibility Compliance', 'Feature': 'Rule Notifications', 'User Story': '33', 'Business Process': 'Policy Update Alerts', 'Sub-Process Title': 'Notification Logic', 'Activity Title': 'No-Change Scenario', 'Test Scenario Title': 'No Notification Sent', 'Precondition': 'No policy or rule changes.', 'Test Data': 'Unchanged eligibility rules for 30 days.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Check notifications panel for policy alerts.'], 'Expected Result': 'No new alerts present.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': '33-E2E-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'End-to-End Update Handling', 'User Story': '33', 'Business Process': 'Policy Management', 'Sub-Process Title': 'E2E Rule Update Procedure', 'Activity Title': 'Update Trigger to Assessment Adjustment', 'Test Scenario Title': 'E2E Rule Change &amp; Assessment Adjustment', 'Precondition': 'Active cases relying on eligible rules.', 'Test Data': 'Update rule; case in progress.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Update eligibility rule.', 'Case worker notified.', 'Case worker reviews open cases.', 'Adjust assessments per new rule.'], 'Expected Result': 'Notification received; assessments updated as required.', 'Dependent Module/Process': 'Assessment Engine, Notifications'}, {'Test Case ID': '33-SEC-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'RBAC - Notification Restrictions', 'User Story': '33', 'Business Process': 'Security', 'Sub-Process Title': 'Notification Permissions', 'Activity Title': 'Unauthorized User Notification Check', 'Test Scenario Title': 'Unauthorized User Is Not Notified', 'Precondition': 'Non-case worker user account exists.', 'Test Data': 'User with no eligibility assessment role.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest/Non-Case Worker', 'Detailed Test Steps': ['Login as unauthorized user.', 'Update eligibility rule as admin.', 'Check for notification.'], 'Expected Result': 'No notification sent to unauthorized user.', 'Dependent Module/Process': 'RBAC, Notifications'}, {'Test Case ID': '33-COMP-01', 'EPIC': 'Eligibility Compliance', 'Feature': 'Audit Logging - Policy', 'User Story': '33', 'Business Process': 'Audit &amp; Notification', 'Sub-Process Title': 'Policy Update Logs', 'Activity Title': 'Audit Of Rule Change', 'Test Scenario Title': 'Audit Log Captures Policy Change And Alerts', 'Precondition': 'Policy update performed and alerts sent.', 'Test Data': 'Rule change event.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System Auditor', 'Detailed Test Steps': ['Trigger rule update and send notifications.', 'Review system audit logs.'], 'Expected Result': 'Log contains timestamp, author of change, notification recipients, and content.', 'Dependent Module/Process': 'Audit Logging'}]</t>
+          <t>[{'Test Case ID': '36-FUNC-01', 'EPIC': 'Case Inactivity Monitoring', 'Feature': 'Alerting System', 'User Story': '36', 'Business Process': 'Case Management', 'Sub-Process Title': 'Inactivity Alerts', 'Activity Title': 'Trigger Alert', 'Test Scenario Title': 'Send 60-day inactivity alert to Case Manager', 'Precondition': 'At least one case with no activity for 60 days assigned to Case Manager.', 'Test Data': 'Case with last activity timestamp older than 60 days.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Simulate time lapse or set last activity to 60+ days ago.', 'Verify alert is sent to assigned Case Manager via configured channel.'], 'Expected Result': 'Case Manager receives alert with case identification.', 'Dependent Module/Process': 'Alert Engine, Case Management'}, {'Test Case ID': '36-FUNC-02', 'EPIC': 'Case Inactivity Monitoring', 'Feature': 'Alerting System', 'User Story': '36', 'Business Process': 'Case Management', 'Sub-Process Title': 'Inactivity Alerts', 'Activity Title': 'Include Case History', 'Test Scenario Title': 'Alert contains link to case history', 'Precondition': 'Alert template configured.', 'Test Data': 'Case with 60 days inactivity.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Receive inactivity alert.', 'Open link or embedded summary to review case history.'], 'Expected Result': 'Alert includes direct access or embedded summary of case history.', 'Dependent Module/Process': 'Alert Engine, Case Viewer'}, {'Test Case ID': '36-NEG-01', 'EPIC': 'Case Inactivity Monitoring', 'Feature': 'Alerting System', 'User Story': '36', 'Business Process': 'Case Management', 'Sub-Process Title': 'Inactivity Alerts', 'Activity Title': 'Restrict Alert Recipients', 'Test Scenario Title': 'Non-Case Manager does not receive alert', 'Precondition': 'User is not assigned as Case Manager.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Check notification center/email for inactivity alerts.'], 'Expected Result': 'No alert received for inactive case.', 'Dependent Module/Process': 'Alert Engine, User Roles'}, {'Test Case ID': '36-API-01', 'EPIC': 'Case Inactivity Monitoring', 'Feature': 'Alerting System', 'User Story': '36', 'Business Process': 'Automated Processes', 'Sub-Process Title': 'Notifications', 'Activity Title': 'API Alert Delivery', 'Test Scenario Title': 'Notification API triggers on 60-day inactivity', 'Precondition': 'Simulated or real case with 60 days inactivity.', 'Test Data': 'Case last updated 60+ days ago.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Service Account', 'Detailed Test Steps': ['Trigger backend process that checks inactivity.', 'Observe API call to notification channel/user.', 'Verify correctness of alert payload (case ID, history link).'], 'Expected Result': 'API call is made for each 60-day inactive case with appropriate details.', 'Dependent Module/Process': 'Backend, Notification API'}, {'Test Case ID': '36-E2E-01', 'EPIC': 'Case Inactivity Monitoring', 'Feature': 'Alerting System', 'User Story': '36', 'Business Process': 'Case Management', 'Sub-Process Title': 'Alert to Follow-up', 'Activity Title': 'Proactive Case Handling', 'Test Scenario Title': 'End to end alert to action workflow', 'Precondition': 'Case is inactive for 60 days; alerts are enabled.', 'Test Data': 'Case and Case Manager assigned.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case inactivity period exceeds 60 days.', 'Receive and open alert.', 'Review case history.', 'Log a follow-up action (contact client, update status, note rationale).'], 'Expected Result': 'Alert is acted upon and follow-up is logged in case history.', 'Dependent Module/Process': 'Case Management, Alerting, Audit Log'}, {'Test Case ID': '36-COMP-01', 'EPIC': 'Case Inactivity Monitoring', 'Feature': 'Alerting System', 'User Story': '36', 'Business Process': 'Compliance', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Regulatory Compliance', 'Test Scenario Title': 'Alert and follow-up actions are audit logged', 'Precondition': 'Alert is received for 60-day inactive case.', 'Test Data': 'Audit log policy configured.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit/Compliance', 'Detailed Test Steps': ['Trigger an alert for an inactive case.', 'Log a follow-up as Case Manager.', 'Review audit log for timestamps, user IDs, and actions.'], 'Expected Result': 'Complete record of alerts and follow-ups are present in audit log for regulatory compliance.', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>This user story focuses on enabling Case Managers to track overdue redeterminations, including listing all overdue cases with corresponding actionable follow-up items. Ensuring compliance and auditability is key.</t>
+          <t>This user story ensures that Case Workers are informed via alerts whenever a client submits income data inconsistent with previous or supporting records. Timely alerts help Case Workers investigate and resolve discrepancies efficiently, improving data integrity and compliance.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to track overdue redeterminations so that I can ensure compliance. - List of overdue cases with follow-up actions.</t>
+          <t>As a Case Worker, I want to receive alerts when a client submits conflicting income data so that I can investigate. - Income validation alerts.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Case Manager logs in, navigates to the overdue redeterminations section, views a filtered list of overdue cases with follow-up actions, and initiates or records compliance activities.</t>
+          <t>When a client enters income data that does not align with previously submitted records or supporting documents, the system automatically notifies the assigned Case Worker with an alert containing relevant details for investigation.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US34_TC1', 'Brief Description': 'Display list of overdue redetermination cases with required follow-up actions (happy path)'}, {'Test Case ID': 'US34_TC2', 'Brief Description': 'No overdue cases present (edge case)'}, {'Test Case ID': 'US34_TC3', 'Brief Description': 'Follow-up action triggers compliance workflow'}, {'Test Case ID': 'US34_TC4', 'Brief Description': 'Case Manager with no permission attempts access'}, {'Test Case ID': 'US34_TC5', 'Brief Description': 'API returns incomplete/erroneous data (integration negative case)'}, {'Test Case ID': 'US34_TC6', 'Brief Description': 'Audit log properly records viewing and follow-up actions'}]</t>
+          <t>[{'Test Case ID': 'US37-TC1', 'Brief Description': 'Receive alert when conflicting income data is submitted by client.'}, {'Test Case ID': 'US37-TC2', 'Brief Description': 'No alert generated when income data is consistent.'}, {'Test Case ID': 'US37-TC3', 'Brief Description': 'Alert contains accurate and actionable information.'}, {'Test Case ID': 'US37-TC4', 'Brief Description': 'No alert sent to unauthorized roles.'}, {'Test Case ID': 'US37-TC5', 'Brief Description': 'Alert generated when conflicting data is detected via API integration.'}, {'Test Case ID': 'US37-TC6', 'Brief Description': 'Audit log records creation and delivery of alert (compliance).'}]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US34_TC1', 'EPIC': 'Redetermination Compliance', 'Feature': 'Overdue Redeterminations Tracking', 'User Story': 'US34', 'Business Process': 'Case Oversight', 'Sub-Process Title': 'Redetermination Compliance Monitoring', 'Activity Title': 'Review Overdue Redeterminations', 'Test Scenario Title': 'Display list of overdue redetermination cases with follow-up actions', 'Precondition': 'Case Manager account enabled and logged in; at least one case with an overdue redetermination exists.', 'Test Data': 'Case 103 | Redetermination Due: 2024-04-01 (overdue), Status: Pending follow-up.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', "Navigate to 'Overdue Redeterminations' section.", 'Verify system displays list of cases where redetermination due date is past today.', 'For each case, confirm relevant follow-up action(s) are displayed.'], 'Expected Result': 'List of overdue cases is presented with accurate follow-up actions; UI allows navigation to compliance actions.', 'Dependent Module/Process': 'Case Management, Compliance Module'}, {'Test Case ID': 'US34_TC2', 'EPIC': 'Redetermination Compliance', 'Feature': 'Overdue Redeterminations Tracking', 'User Story': 'US34', 'Business Process': 'Case Oversight', 'Sub-Process Title': 'Redetermination Compliance Monitoring', 'Activity Title': 'Review Overdue Redeterminations', 'Test Scenario Title': 'No overdue cases present', 'Precondition': 'Case Manager logged in; no cases with overdue redeterminations exist.', 'Test Data': 'No overdue cases in the database.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', "Navigate to 'Overdue Redeterminations' section."], 'Expected Result': 'System displays a message indicating that there are no overdue cases and disables follow-up actions.', 'Dependent Module/Process': 'Case Management'}, {'Test Case ID': 'US34_TC3', 'EPIC': 'Redetermination Compliance', 'Feature': 'Overdue Redeterminations Tracking', 'User Story': 'US34', 'Business Process': 'Case Oversight', 'Sub-Process Title': 'Redetermination Compliance Monitoring', 'Activity Title': 'Initiate Compliance Workflow', 'Test Scenario Title': 'Follow-up action triggers compliance workflow', 'Precondition': 'At least one overdue redetermination is listed for the Case Manager.', 'Test Data': 'Case 105, Overdue: 2024-04-12', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', "Navigate to 'Overdue Redeterminations' section.", 'Select an overdue case.', "Click on a follow-up action (e.g., 'Send Reminder')."], 'Expected Result': 'Compliance workflow is triggered (e.g., reminder is logged and/or sent, case note updated, audit trail updated).', 'Dependent Module/Process': 'Compliance Module, Notification Service'}, {'Test Case ID': 'US34_TC4', 'EPIC': 'Redetermination Compliance', 'Feature': 'Permissions &amp; Access Controls', 'User Story': 'US34', 'Business Process': 'Authorization', 'Sub-Process Title': 'User Role Validation', 'Activity Title': 'Enforce Role-Based Access', 'Test Scenario Title': 'Case Manager with no permission attempts access', 'Precondition': 'User account lacks Case Manager role.', 'Test Data': 'Regular User account', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Non-Case Manager', 'Detailed Test Steps': ['Log in as a user without Case Manager role (e.g., Case Worker).', "Attempt to navigate to 'Overdue Redeterminations' page."], 'Expected Result': 'System denies access with appropriate error message or redirects to insufficient permissions page.', 'Dependent Module/Process': 'Authentication, Authorization'}, {'Test Case ID': 'US34_TC5', 'EPIC': 'Redetermination Compliance', 'Feature': 'Integration &amp; API', 'User Story': 'US34', 'Business Process': 'System Integration', 'Sub-Process Title': 'API Communication', 'Activity Title': 'Handle Data Errors Gracefully', 'Test Scenario Title': 'API returns incomplete/erroneous data', 'Precondition': 'API mocks configured to return malformed data.', 'Test Data': 'Malformed JSON (missing required fields)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Trigger UI/API fetch for overdue redeterminations with simulated API error.', "Observe system's response."], 'Expected Result': 'Error message displayed; system logs error and avoids crashing; compliance/audit report unaffected.', 'Dependent Module/Process': 'API Gateway, Error Logging'}, {'Test Case ID': 'US34_TC6', 'EPIC': 'Redetermination Compliance', 'Feature': 'Audit &amp; Compliance', 'User Story': 'US34', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Compliance Auditing', 'Activity Title': 'Record User Actions', 'Test Scenario Title': 'Audit log records viewing and follow-up actions', 'Precondition': 'Audit logging is enabled in the system.', 'Test Data': 'Test actions by Case Manager.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'View an overdue redetermination case.', 'Initiate a follow-up action (e.g., send reminder).', 'Check audit log.'], 'Expected Result': 'Audit log contains entry for viewing the case and for executing follow-up action, including timestamp, user ID, and action type.', 'Dependent Module/Process': 'Audit Trail, Compliance Module'}]</t>
+          <t>[{'Test Case ID': 'US37-TC1', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': 'US37', 'Business Process': 'Case Processing', 'Sub-Process Title': 'Income Data Entry', 'Activity Title': 'Income Submission', 'Test Scenario Title': 'Alert generated on conflicting income data', 'Precondition': 'Client has previously submitted valid income data or supporting documents. Case Worker is assigned to client case.', 'Test Data': 'Previous income: $2500/month; New submission: $3500/month (no supporting document for new value).', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client logs in and submits new income data.', 'System cross-validates new data with historical records and supporting documents.', 'System detects a mismatch (amount differs by more than allowed threshold).', 'System generates an alert and sends to assigned Case Worker.'], 'Expected Result': 'Case Worker receives alert specifying client, submission time, and details of conflicting income.', 'Dependent Module/Process': 'Alerts/Notifications, Data Validation'}, {'Test Case ID': 'US37-TC2', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': 'US37', 'Business Process': 'Case Processing', 'Sub-Process Title': 'Income Data Entry', 'Activity Title': 'Income Submission', 'Test Scenario Title': 'No alert on consistent income data', 'Precondition': 'Case with prior income data on file.', 'Test Data': 'Previous income: $2500/month; New submission: $2500/month (with matching paystub).', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client submits new income data identical to previous data with valid support.', 'System cross-validates submission.', 'No validation rules trigger.'], 'Expected Result': 'No alert is sent to Case Worker.', 'Dependent Module/Process': 'Data Validation'}, {'Test Case ID': 'US37-TC3', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': 'US37', 'Business Process': 'Case Processing', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Alert Review', 'Test Scenario Title': 'Alert content validation', 'Precondition': 'Conflicting income detected and alert generated.', 'Test Data': 'Alert with fields: client name, time, old vs new income, link to case.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker receives alert.', 'Opens alert and reviews content.'], 'Expected Result': 'Alert contains necessary client details, timestamps, nature of conflict, and case link.', 'Dependent Module/Process': 'Alerts/Notifications'}, {'Test Case ID': 'US37-TC4', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': 'US37', 'Business Process': 'Case Processing', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Unauthorized user cannot access alerts', 'Precondition': 'Conflicting submission exists.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Other (e.g., Client, Analyst)', 'Detailed Test Steps': ['Log in as a user who is not assigned as Case Worker.', 'Attempt to access or receive income data conflict alert.'], 'Expected Result': 'No alert visible or delivered to unassigned users.', 'Dependent Module/Process': 'Access Management'}, {'Test Case ID': 'US37-TC5', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': 'US37', 'Business Process': 'Case Processing', 'Sub-Process Title': 'API Income Update', 'Activity Title': 'Data Integration', 'Test Scenario Title': 'API submission triggers alert on conflict', 'Precondition': 'API integration enabled; client submits income via API.', 'Test Data': 'API payload: income = $5,000/month, previous = $2500/month.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Simulate API call with conflicting income data.', 'System detects mismatch.', 'Alert generated and sent to Case Worker.'], 'Expected Result': 'Case Worker receives alert as per specifications.', 'Dependent Module/Process': 'API Gateway, Alerts'}, {'Test Case ID': 'US37-TC6', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': 'US37', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Alert Logging', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Alert actions logged for audit', 'Precondition': 'System generates alert for conflicting income.', 'Test Data': 'Alert creation event details.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Internal Auditor', 'Detailed Test Steps': ['Submit conflicting data to trigger alert.', 'Access audit logs.', 'Review that alert creation, delivery, and user access are logged.'], 'Expected Result': 'Audit log contains immutable entries for alert creation, notification delivery, and access per regulatory requirements.', 'Dependent Module/Process': 'Compliance, Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>This user story ensures Case Workers can generate a printable summary of case notes for inclusion in physical files, supporting both digital and paper-based record-keeping and compliance.</t>
+          <t>This user story delivers a metrics dashboard that enables Case Managers to track and report on the number of escalated cases, empowering them to assess urgency trends and optimize resource allocation.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to print a summary of case notes so that I can include them in physical files. - Printable case note summary.</t>
+          <t>As a Case Manager, I want to track the number of escalated cases so that I can report on urgency trends. - Escalation metrics dashboard.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Case Worker selects a case, chooses 'Print Summary', and receives a formatted, print-ready document containing the relevant case notes.</t>
+          <t>Case Manager accesses a dashboard displaying up-to-date statistics on escalated cases, allowing filtering, export, and reporting by defined periods and categories.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US35_TC1', 'Brief Description': 'Generate and print summary for cases with notes (happy path)'}, {'Test Case ID': 'US35_TC2', 'Brief Description': 'Case with no notes (edge case)'}, {'Test Case ID': 'US35_TC3', 'Brief Description': 'User without print permission attempts to print'}, {'Test Case ID': 'US35_TC4', 'Brief Description': 'Printable summary meets format and compliance requirements'}, {'Test Case ID': 'US35_TC5', 'Brief Description': 'API error when generating summary (integration negative case)'}]</t>
+          <t>[{'Test Case ID': 'US38-TC1', 'Brief Description': 'Dashboard shows correct count of escalated cases.'}, {'Test Case ID': 'US38-TC2', 'Brief Description': 'Case escalation impacts dashboard metrics in real-time.'}, {'Test Case ID': 'US38-TC3', 'Brief Description': 'Unauthorized users cannot access escalation metrics dashboard.'}, {'Test Case ID': 'US38-TC4', 'Brief Description': 'Case Manager can filter metrics by time period and case type.'}, {'Test Case ID': 'US38-TC5', 'Brief Description': 'Metrics export function works as expected (CSV, PDF).'}, {'Test Case ID': 'US38-TC6', 'Brief Description': 'Dashboard access and metric changes are logged for audits (compliance).'}]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US35_TC1', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Print Case Notes Summary', 'Test Scenario Title': 'Generate and print summary for cases with notes', 'Precondition': 'Case Worker is logged in and has at least one case with saved notes.', 'Test Data': 'Case 202 | Case Notes: 3 entries', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Navigate to a specific case with notes.', "Select 'Print Summary' or equivalent option.", 'Preview or directly print the summary.'], 'Expected Result': 'Case note summary is generated accurately and formatted for printing; printable dialog or PDF is presented.', 'Dependent Module/Process': 'Case Management, Print Services'}, {'Test Case ID': 'US35_TC2', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Handle Cases with No Notes', 'Test Scenario Title': 'Case with no notes', 'Precondition': 'Case Worker is logged in; at least one case has no notes.', 'Test Data': 'Case 203 | No notes available.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Navigate to a case with no notes.', 'Attempt to print the summary.'], 'Expected Result': "System displays message 'No notes available to print', disables print function, or generates a blank (but formatted) summary.", 'Dependent Module/Process': 'Case Management'}, {'Test Case ID': 'US35_TC3', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Access Control', 'Sub-Process Title': 'User Role Validation', 'Activity Title': 'Enforce Print Permissions', 'Test Scenario Title': 'User without print permission attempts to print', 'Precondition': "User is not granted 'Print Case Notes' permission.", 'Test Data': 'Regular User account', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'User without Print Permission', 'Detailed Test Steps': ['Log in as user without print permission.', 'Navigate to case notes.', "Attempt to initiate 'Print Summary' action."], 'Expected Result': 'System prevents the action, shows an authorization error message or disables print button.', 'Dependent Module/Process': 'Authorization Module'}, {'Test Case ID': 'US35_TC4', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'Compliance', 'Sub-Process Title': 'Format Validation', 'Activity Title': 'Printable Summary Format Validation', 'Test Scenario Title': 'Printable summary meets format and compliance requirements', 'Precondition': 'Case Worker is authorized and can print; template is set as per compliance rules.', 'Test Data': 'Case 202 | Notes with sensitive and non-sensitive info.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Generate printable summary for a case.', 'Review the document format and required disclosure/compliance elements (headers, confidentiality statement, redactions).'], 'Expected Result': 'Printable summary matches mandated format; confidential data is protected or omitted; compliance footer present.', 'Dependent Module/Process': 'Compliance/Legal'}, {'Test Case ID': 'US35_TC5', 'EPIC': 'Documentation &amp; Case Management', 'Feature': 'Case Note Print Function', 'User Story': 'US35', 'Business Process': 'System Integration', 'Sub-Process Title': 'API Communication', 'Activity Title': 'Error Handling During Summary Generation', 'Test Scenario Title': 'API error when generating summary', 'Precondition': 'API mock or backend is configured to return error on summary request.', 'Test Data': 'N/A (force error response)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to print case notes when backend/API is failing.', 'Observe system behavior.'], 'Expected Result': 'User receives a meaningful error message and/or retry option; system logs error for audit.', 'Dependent Module/Process': 'API Gateway, Error Logging'}]</t>
+          <t>[{'Test Case ID': 'US38-TC1', 'EPIC': 'Performance Analytics', 'Feature': 'Escalation Dashboard', 'User Story': 'US38', 'Business Process': 'Case Monitoring', 'Sub-Process Title': 'Escalation Metrics', 'Activity Title': 'Dashboard Viewing', 'Test Scenario Title': 'Dashboard displays accurate escalation count', 'Precondition': 'Cases exist, with a known subset escalated. Case Manager has access rights.', 'Test Data': '10 total cases, 4 escalated.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to Escalation Metrics dashboard.', 'Verify count of escalated cases.'], 'Expected Result': "Dashboard displays '4 escalated cases' out of '10 total cases.'", 'Dependent Module/Process': 'Case Database, Dashboard UI'}, {'Test Case ID': 'US38-TC2', 'EPIC': 'Performance Analytics', 'Feature': 'Escalation Dashboard', 'User Story': 'US38', 'Business Process': 'Case Monitoring', 'Sub-Process Title': 'Escalation Metrics', 'Activity Title': 'Real-time Updates', 'Test Scenario Title': 'Escalation updates reflect immediately', 'Precondition': 'Case Manager on Escalation Metrics dashboard.', 'Test Data': 'Case #7 escalated while dashboard open.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['While viewing dashboard, escalate a non-escalated case.', 'Observe dashboard update.'], 'Expected Result': 'Escalated case count increases by one in real-time.', 'Dependent Module/Process': 'Dashboard, Case Workflow'}, {'Test Case ID': 'US38-TC3', 'EPIC': 'Performance Analytics', 'Feature': 'Escalation Dashboard', 'User Story': 'US38', 'Business Process': 'Case Monitoring', 'Sub-Process Title': 'Escalation Metrics', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Restrict dashboard access to Case Managers', 'Precondition': 'User logged in as non-Case Manager.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Other (e.g. Case Worker, Client)', 'Detailed Test Steps': ['Attempt to access Escalation Metrics dashboard as unauthorized user.'], 'Expected Result': 'Access denied message or dashboard not visible.', 'Dependent Module/Process': 'Access Management'}, {'Test Case ID': 'US38-TC4', 'EPIC': 'Performance Analytics', 'Feature': 'Escalation Dashboard', 'User Story': 'US38', 'Business Process': 'Case Monitoring', 'Sub-Process Title': 'Escalation Metrics', 'Activity Title': 'Dashboard Filters', 'Test Scenario Title': 'Dashboard filter by period/case type functions', 'Precondition': 'Escalated cases exist with varied types and dates.', 'Test Data': 'Escalations by date and type.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Use dashboard controls to filter by time period (last month).', "Use dashboard controls to filter by case type (e.g. 'Urgent')."], 'Expected Result': 'Displayed metrics reflect only cases within selected criteria.', 'Dependent Module/Process': 'Dashboard UI'}, {'Test Case ID': 'US38-TC5', 'EPIC': 'Performance Analytics', 'Feature': 'Escalation Dashboard', 'User Story': 'US38', 'Business Process': 'Case Monitoring', 'Sub-Process Title': 'Escalation Metrics', 'Activity Title': 'Data Export', 'Test Scenario Title': 'Export of escalation metrics works', 'Precondition': 'Metrics dashboard is populated.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Click export to CSV.', 'Click export to PDF.'], 'Expected Result': 'Corresponding file downloads containing displayed metrics.', 'Dependent Module/Process': 'Dashboard, Export Service'}, {'Test Case ID': 'US38-TC6', 'EPIC': 'Performance Analytics', 'Feature': 'Escalation Dashboard', 'User Story': 'US38', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Dashboard and metric access logged for audit', 'Precondition': 'Case Manager accesses dashboard or exports metrics.', 'Test Data': 'User access event, data export event.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Internal Auditor', 'Detailed Test Steps': ['Access metrics dashboard.', 'Export dataset.', 'Review audit logs for access and export events.'], 'Expected Result': 'Audit log reflects dashboard access, metric updates, and exports per compliance needs.', 'Dependent Module/Process': 'Dashboard, Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>This user story describes a notification system for Case Managers, alerting them when a case is inactive for 60 days, including access to relevant case history for follow-up and compliance.</t>
+          <t>This user story ensures that Case Workers receive timely alerts if clients upload case-related documents outside of business hours, enabling them to prioritize such reviews and adhere to service-level agreements.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>As a Case Manager, I want to receive alerts when a case is inactive for 60 days so that I can follow up. - Inactivity alerts with case history.</t>
+          <t>As a Case Worker, I want to receive alerts when a client uploads a document after business hours so that I can prioritize review. - After-hours upload alerts.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Case becomes inactive for 60 days, Case Manager receives alert, reviews case history, and performs follow-up actions or logs compliance.</t>
+          <t>When a client uploads a document outside defined business hours, an alert is generated and sent to the assigned Case Worker with relevant client and document details.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US36_TC1', 'Brief Description': 'Trigger and display alert for case inactive for 60 days (happy path)'}, {'Test Case ID': 'US36_TC2', 'Brief Description': 'Case becomes active before 60 days (should not alert)'}, {'Test Case ID': 'US36_TC3', 'Brief Description': 'Case Manager with alert permission only receives relevant notifications'}, {'Test Case ID': 'US36_TC4', 'Brief Description': 'Alert includes sufficient case history for meaningful follow-up'}, {'Test Case ID': 'US36_TC5', 'Brief Description': 'Integration: Alert system fails to send notification (negative case)'}, {'Test Case ID': 'US36_TC6', 'Brief Description': 'Audit log records alert delivery and Case Manager action'}]</t>
+          <t>[{'Test Case ID': 'US39-TC1', 'Brief Description': 'Alert sent when document uploaded after business hours.'}, {'Test Case ID': 'US39-TC2', 'Brief Description': 'No alert sent for uploads within business hours.'}, {'Test Case ID': 'US39-TC3', 'Brief Description': 'Alert contains client and document metadata.'}, {'Test Case ID': 'US39-TC4', 'Brief Description': 'Unauthorized users cannot access after-hours upload alerts.'}, {'Test Case ID': 'US39-TC5', 'Brief Description': 'API uploads after hours trigger alerts for Case Worker.'}, {'Test Case ID': 'US39-TC6', 'Brief Description': 'Audit log records all after-hours alert actions for compliance.'}]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'US36_TC1', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Notification', 'Sub-Process Title': 'Inactivity Detection', 'Activity Title': 'Trigger Inactivity Alert', 'Test Scenario Title': 'Trigger and display alert for case inactive for 60 days', 'Precondition': 'Case has had no activity for exactly 60 days; Case Manager subscribes to alert notifications.', 'Test Data': "Case 301 | Last Activity: 2024-03-01; today's date: 2024-04-30.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Ensure case has had 59 days of inactivity.', 'Do not perform any activity for the 60th day.', 'Once 60 days pass, log in as Case Manager.', 'Verify notification is received regarding inactivity.'], 'Expected Result': 'Alert/notification is received by the Case Manager; alert is visible in dashboard and/or email as configured.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'US36_TC2', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Notification', 'Sub-Process Title': 'Inactivity Detection', 'Activity Title': 'Suppress Alert for Recently Active Case', 'Test Scenario Title': 'Case becomes active before 60 days (should not alert)', 'Precondition': 'Case has had recent activity within last 60 days.', 'Test Data': 'Case 302 | Last Activity: 2024-04-10.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Make at least one activity update on case within 59 days.', 'Check for alert at 60-day mark.'], 'Expected Result': 'No inactivity alert is issued for that case.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'US36_TC3', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Authorization', 'Sub-Process Title': 'User Role Validation', 'Activity Title': 'Permission-based Notification', 'Test Scenario Title': 'Case Manager with alert permission only receives relevant notifications', 'Precondition': 'System contains multiple users, some with and some without alert permissions.', 'Test Data': 'Case 303 | Inactive 60 days', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Non-Case Manager', 'Detailed Test Steps': ['Log in as Case Manager and as user without case oversight role.', 'Verify which users receive alerts.'], 'Expected Result': 'Only Case Managers with correct permissions receive inactivity alerts.', 'Dependent Module/Process': 'Authorization, Notification Engine'}, {'Test Case ID': 'US36_TC4', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Notification', 'Sub-Process Title': 'Alert Content Verification', 'Activity Title': 'Display Case History in Alert', 'Test Scenario Title': 'Alert includes sufficient case history for meaningful follow-up', 'Precondition': 'Inactivity alert triggered on case.', 'Test Data': 'Case 301 | Last Activity: 2024-03-01; Case History: all events last 6 months.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Receive inactivity alert.', 'Open alert details.', 'Review included case history.'], 'Expected Result': 'Alert contains a concise summary of relevant recent case history (e.g., last activity, responsible party, pending items).', 'Dependent Module/Process': 'Case History Module, Notification Engine'}, {'Test Case ID': 'US36_TC5', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'System Integration', 'Sub-Process Title': 'Notification Delivery', 'Activity Title': 'Handle Notification Failures', 'Test Scenario Title': 'Integration: Alert system fails to send notification', 'Precondition': 'Notification engine integration is simulated to fail.', 'Test Data': 'Simulated notification service downtime.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Simulate notification engine outage.', 'Inactivity threshold met for a case.', 'Log in as Case Manager.', 'Check alert delivery status.'], 'Expected Result': 'User does not receive alert, system logs delivery failure, and support/audit team notified as per compliance requirements.', 'Dependent Module/Process': 'Notification Engine, Logging'}, {'Test Case ID': 'US36_TC6', 'EPIC': 'Case Oversight', 'Feature': 'Inactivity Alerts', 'User Story': 'US36', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Compliance Auditing', 'Activity Title': 'Audit Alert Delivery and Actions', 'Test Scenario Title': 'Audit log records alert delivery and Case Manager action', 'Precondition': 'Audit system is active; inactivity alert is triggered.', 'Test Data': 'Case 304 | 60 days inactive, alert delivered.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Receive inactivity alert as Case Manager.', 'Review and perform follow-up action.', 'Check audit log entries.'], 'Expected Result': 'Audit log reflects alert delivery timestamp, recipient, and records any subsequent follow-up activity for compliance and audit review.', 'Dependent Module/Process': 'Audit Trail, Notification Engine'}]</t>
+          <t>[{'Test Case ID': 'US39-TC1', 'EPIC': 'Case Management', 'Feature': 'Document Handling', 'User Story': 'US39', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'After-hours Document Upload', 'Test Scenario Title': 'Alert on after-hours document upload', 'Precondition': 'Client is assigned to Case Worker; business hours are defined (e.g., 9AM-5PM).', 'Test Data': 'Upload time: 8:30PM.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client logs in after business hours and uploads document.', 'System detects upload timestamp outside business hours.', 'System generates alert for assigned Case Worker.'], 'Expected Result': 'Case Worker receives alert with client and document details.', 'Dependent Module/Process': 'Alerts/Notifications, Document Management'}, {'Test Case ID': 'US39-TC2', 'EPIC': 'Case Management', 'Feature': 'Document Handling', 'User Story': 'US39', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'In-hours Document Upload', 'Test Scenario Title': 'No alert in business hours', 'Precondition': 'Business hours defined.', 'Test Data': 'Upload time: 10:00AM.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client uploads document during business hours.', 'System checks timestamp.'], 'Expected Result': 'No alert sent to Case Worker.', 'Dependent Module/Process': 'Document Management'}, {'Test Case ID': 'US39-TC3', 'EPIC': 'Case Management', 'Feature': 'Document Handling', 'User Story': 'US39', 'Business Process': 'Document Management', 'Sub-Process Title': 'Alert Handling', 'Activity Title': 'Alert Review', 'Test Scenario Title': 'Alert content includes accurate details', 'Precondition': 'After-hours document upload alert generated.', 'Test Data': 'Alert includes: client name, document type, upload time, link to document.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Case Worker receives alert.', 'Open and review alert information.'], 'Expected Result': 'Alert displays client name/ID, document type, upload time, and link for quick access.', 'Dependent Module/Process': 'Alerts/Notifications'}, {'Test Case ID': 'US39-TC4', 'EPIC': 'Case Management', 'Feature': 'Document Handling', 'User Story': 'US39', 'Business Process': 'Document Management', 'Sub-Process Title': 'Alert Handling', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'No alert for unauthorized users', 'Precondition': 'After-hours document upload occurred.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Other (e.g. Client, Analyst)', 'Detailed Test Steps': ['Log in as user not assigned as Case Worker.', 'Attempt to view after-hours alerts.'], 'Expected Result': 'After-hours upload alerts are not visible or accessible.', 'Dependent Module/Process': 'Access Management'}, {'Test Case ID': 'US39-TC5', 'EPIC': 'Case Management', 'Feature': 'Document Handling', 'User Story': 'US39', 'Business Process': 'Document Management', 'Sub-Process Title': 'Document Upload via API', 'Activity Title': 'External Document Integration', 'Test Scenario Title': 'API upload after hours triggers alert', 'Precondition': 'API integration for document upload is active.', 'Test Data': 'API upload payload at 11:30PM.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger document upload via API after business hours.', 'System checks and generates alert if out-of-hours.', 'Alert is sent to Case Worker.'], 'Expected Result': 'Case Worker receives after-hours alert as per requirements.', 'Dependent Module/Process': 'API Gateway, Alerts'}, {'Test Case ID': 'US39-TC6', 'EPIC': 'Case Management', 'Feature': 'Document Handling', 'User Story': 'US39', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Alert Logging', 'Activity Title': 'Audit Logging', 'Test Scenario Title': 'Audit records for after-hours alerts', 'Precondition': 'After-hours upload alert generated.', 'Test Data': 'Alert creation and delivery events.', 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Internal Auditor', 'Detailed Test Steps': ['Generate after-hours upload and corresponding alert.', 'Access and review audit logs for alert lifecycle events.'], 'Expected Result': 'Audit logs include records of alert creation and delivery per compliance standards.', 'Dependent Module/Process': 'Audit Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>This user story addresses the need for Case Workers to be promptly notified when clients provide conflicting income information, enabling them to investigate and resolve inconsistencies in a timely manner. The focus is on generating alerts based on automated income data validation, ensuring data integrity and compliance.</t>
+          <t>This user story ensures that Case Managers are promptly notified when a caseworker's workload exceeds a predefined threshold, allowing timely reassignment of cases to maintain balance and service quality.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>As a Case Worker, I want to receive alerts when a client submits conflicting income data so that I can investigate. - Income validation alerts.</t>
+          <t>As a Case Manager, I want to receive alerts when a caseworker is overloaded so that I can reassign cases.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A client submits income data that conflicts with existing records. The system automatically detects the inconsistency and generates an alert for the assigned Case Worker for timely investigation.</t>
+          <t>When a caseworker’s assigned cases exceed the set threshold, the system generates an alert to the Case Manager. The Case Manager receives this alert and is able to initiate a reassignment process.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_37_01', 'Brief Description': 'Alert triggers when client submits new income data that conflicts with previous data.'}, {'Test Case ID': 'TC_37_02', 'Brief Description': 'No alert is triggered when income data submitted is consistent with existing records.'}, {'Test Case ID': 'TC_37_03', 'Brief Description': 'Alert is only delivered to authorized Case Worker, not to unauthorized users.'}, {'Test Case ID': 'TC_37_04', 'Brief Description': 'System logs alert for compliance/audit purposes.'}, {'Test Case ID': 'TC_37_05', 'Brief Description': 'System fails gracefully if validation engine is down (negative test).'}, {'Test Case ID': 'TC_37_06', 'Brief Description': 'Alert correctly includes relevant client details and type of conflict.'}]</t>
+          <t>[{'Test Case ID': 'TC40-01', 'Brief Description': "Verify alert is generated for Case Manager when a caseworker's workload exceeds threshold."}, {'Test Case ID': 'TC40-02', 'Brief Description': 'Verify alert is not generated when workload is below threshold.'}, {'Test Case ID': 'TC40-03', 'Brief Description': 'Verify multiple caseworker overloads trigger separate alerts.'}, {'Test Case ID': 'TC40-04', 'Brief Description': 'Validate Case Manager can view and act on alert.'}, {'Test Case ID': 'TC40-05', 'Brief Description': 'Verify alert is not sent to users without the Case Manager role.'}, {'Test Case ID': 'TC40-06', 'Brief Description': 'Negative: System does not generate duplicate alerts for same overload event.'}, {'Test Case ID': 'TC40-07', 'Brief Description': 'API: Test alert endpoint triggers as per business rules.'}, {'Test Case ID': 'TC40-08', 'Brief Description': 'Compliance: Audit log records overload alert generation and actions taken.'}]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[{'Test Case ID': 'TC_37_01', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Intake &amp; Verification', 'Sub-Process Title': 'Income Submission', 'Activity Title': 'Income Data Validation', 'Test Scenario Title': 'Alert is triggered for conflicting income data', 'Precondition': 'Case Worker and client are registered in the system. Client has historical income record.', 'Test Data': {'ClientID': 'C10012', 'ExistingIncome': '$2000/month', 'SubmittedIncome': '$5000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as client.', '2. Navigate to income submission form.', '3. Submit new income value ($5000/month, when previous was $2000/month).', '4. System performs income data validation post-submission.', '5. System detects conflict.', '6. System generates and delivers alert to assigned Case Worker.'], 'Expected Result': 'Case Worker receives alert with client details, previous and current income values, and nature of conflict.', 'Dependent Module/Process': 'Notification Service, Data Validation Engine'}, {'Test Case ID': 'TC_37_02', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Intake &amp; Verification', 'Sub-Process Title': 'Income Submission', 'Activity Title': 'Consistent Data Submission', 'Test Scenario Title': 'No alert for non-conflicting income submission', 'Precondition': 'Client has existing income record consistent with new submission.', 'Test Data': {'ClientID': 'C10012', 'ExistingIncome': '$2000/month', 'SubmittedIncome': '$2000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as client.', '2. Submit income value identical to previous value.', '3. System performs validation.', '4. No conflict detected.'], 'Expected Result': 'No alert generated or delivered to Case Worker.', 'Dependent Module/Process': 'Notification Service, Data Validation Engine'}, {'Test Case ID': 'TC_37_03', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Notification', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Alert Delivery', 'Test Scenario Title': 'Alert goes only to assigned Case Worker', 'Precondition': 'Client submits conflicting income data.', 'Test Data': {'ClientID': 'C10012', 'AssignedCaseWorker': 'CW567'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Unassigned User', 'Detailed Test Steps': ['1. Client submits conflicting income data.', '2. System generates alert.', '3. Attempt to access alert as assigned Case Worker, another Case Worker, and unauthorized user.'], 'Expected Result': 'Alert visible only to assigned Case Worker, not to unauthorized users.', 'Dependent Module/Process': 'Access Control, Notification Service'}, {'Test Case ID': 'TC_37_04', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Logging', 'Activity Title': 'Alert Event Logging', 'Test Scenario Title': 'Alert is logged for compliance/audit', 'Precondition': 'System is configured for audit logging.', 'Test Data': {'ClientID': 'C10012', 'ConflictingIncome': True}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Auditor', 'Detailed Test Steps': ['1. Client submits conflicting income data.', '2. Alert is generated.', '3. Query audit log as Auditor.'], 'Expected Result': 'Audit log contains entry with client ID, alert time, case worker ID, and description of conflict.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}, {'Test Case ID': 'TC_37_05', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Exception Handling', 'Sub-Process Title': 'System Fault', 'Activity Title': 'Validation Engine Down', 'Test Scenario Title': 'System handles validation service outage gracefully', 'Precondition': 'Validation engine is non-operational.', 'Test Data': {'ClientID': 'C10012', 'SubmittedIncome': '$7000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Simulate income submission while validation engine is down.', '2. Monitor system response to submission.'], 'Expected Result': 'User receives error or information message; no false alerts are generated. Incident is logged.', 'Dependent Module/Process': 'Notification Service, Validation Engine'}, {'Test Case ID': 'TC_37_06', 'EPIC': 'Case Management', 'Feature': 'Income Validation', 'User Story': '37', 'Business Process': 'Notification', 'Sub-Process Title': 'Alert Content Validation', 'Activity Title': 'Alert Content Check', 'Test Scenario Title': 'Alert content contains all required fields', 'Precondition': 'Case Worker with assigned client.', 'Test Data': {'ClientID': 'C10012', 'PreviousIncome': '$2500/month', 'SubmittedIncome': '$8000/month'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Trigger conflict by submitting different income.', '2. Receive alert and inspect contents.'], 'Expected Result': 'Alert message includes client name/ID, both income values, timestamp, and nature of conflict.', 'Dependent Module/Process': 'Notification Service'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>This user story ensures that Case Managers have visibility into the volume and urgency of escalated cases over time. The system must provide accurate metrics via a dashboard, supporting operational reporting and decision-making.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>As a Case Manager, I want to track the number of escalated cases so that I can report on urgency trends. - Escalation metrics dashboard.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Case escalation events are captured in real time. The dashboard for Case Managers displays up-to-date counts of escalated cases, supports filtering and export, and ensures only authorized access.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>[{'Test Case ID': 'TC_38_01', 'Brief Description': 'Escalated cases are reflected in dashboard metrics in real time.'}, {'Test Case ID': 'TC_38_02', 'Brief Description': 'Non-escalated cases are not included in escalated count.'}, {'Test Case ID': 'TC_38_03', 'Brief Description': 'Dashboard access is restricted to Case Managers.'}, {'Test Case ID': 'TC_38_04', 'Brief Description': 'Case Manager can export/report on escalation data.'}, {'Test Case ID': 'TC_38_05', 'Brief Description': 'Dashboard handles system errors gracefully (negative).'}, {'Test Case ID': 'TC_38_06', 'Brief Description': 'Dashboard includes historical data and filtering by date/urgency.'}]</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>[{'Test Case ID': 'TC_38_01', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Escalations Tracking', 'Sub-Process Title': 'Dashboard Update', 'Activity Title': 'Real-Time Metrics Update', 'Test Scenario Title': 'Escalated case is instantly reflected in metrics', 'Precondition': 'Case is present and assigned to a worker.', 'Test Data': {'CaseID': 'E12345', 'EscalationFlag': 'True'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Escalate a case as a Case Worker.', '2. Log in as Case Manager.', '3. Open escalation dashboard.', '4. Check escalated case count.'], 'Expected Result': 'Dashboard shows increased count, including the newly escalated case.', 'Dependent Module/Process': 'Case Management, Dashboard Service'}, {'Test Case ID': 'TC_38_02', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Escalations Tracking', 'Sub-Process Title': 'Non-Escalated Case', 'Activity Title': 'Metrics Exclusion', 'Test Scenario Title': 'Non-escalated cases are not counted', 'Precondition': 'Non-escalated case exists.', 'Test Data': {'CaseID': 'NE54321', 'EscalationFlag': 'False'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Do not escalate case NE54321.', '2. View dashboard.', '3. Check escalated case count.'], 'Expected Result': 'Dashboard does not include non-escalated case in escalated metrics.', 'Dependent Module/Process': 'Case Management, Dashboard Service'}, {'Test Case ID': 'TC_38_03', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role Check', 'Activity Title': 'Dashboard Access Control', 'Test Scenario Title': 'Only Case Managers can access the dashboard', 'Precondition': 'Dashboard is configured. User roles assigned.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Case Worker', 'Detailed Test Steps': ['1. Attempt to log in as Case Manager; open dashboard.', '2. Attempt to log in as Case Worker; open dashboard.'], 'Expected Result': 'Dashboard is accessible only to users with Case Manager role.', 'Dependent Module/Process': 'User Management, Access Control'}, {'Test Case ID': 'TC_38_04', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Reporting', 'Sub-Process Title': 'Export Data', 'Activity Title': 'Dashboard Export', 'Test Scenario Title': 'Case Manager can export escalation metrics', 'Precondition': 'Escalation metrics dashboard is accessible.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Log in as Case Manager.', '2. Open escalation dashboard.', '3. Choose export option (CSV/XLS/PDF).'], 'Expected Result': 'Dashboard successfully exports correct data format containing escalated cases.', 'Dependent Module/Process': 'Dashboard Service, Export Service'}, {'Test Case ID': 'TC_38_05', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Exception Handling', 'Sub-Process Title': 'Dashboard Failure', 'Activity Title': 'Graceful Failure', 'Test Scenario Title': 'Dashboard handles failure gracefully', 'Precondition': 'Dashboard backend is offline or unavailable.', 'Test Data': {}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Simulate backend outage.', '2. Attempt to access dashboard.'], 'Expected Result': 'User receives appropriate error message; no incomplete or misleading data shown.', 'Dependent Module/Process': 'Dashboard Service, Exception Handler'}, {'Test Case ID': 'TC_38_06', 'EPIC': 'Case Management', 'Feature': 'Escalation Metrics', 'User Story': '38', 'Business Process': 'Reporting', 'Sub-Process Title': 'Filtering', 'Activity Title': 'Historical Data and Filters', 'Test Scenario Title': 'Dashboard supports filters by date and urgency', 'Precondition': 'Dashboard contains escalated case history.', 'Test Data': {'Dates': ['2023-05-01 to 2024-01-30'], 'UrgencyLevels': ['Low', 'High']}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['1. Open escalation dashboard.', '2. Apply date range and urgency filters.', '3. View filtered results.'], 'Expected Result': 'Dashboard displays correct numbers for specified date range and urgency.', 'Dependent Module/Process': 'Dashboard Service'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>This user story requires notifications for Case Workers when clients upload documents after normal business hours (e.g., 6PM-8AM). Such alerts help prioritize urgent, after-hours submissions and emphasize timely case management.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>As a Case Worker, I want to receive alerts when a client uploads a document after business hours so that I can prioritize review. - After-hours upload alerts.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>A client uploads a document at 9:30PM. The system detects time of upload and immediately notifies assigned Case Worker. Alert contains document and client details for prioritization.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>[{'Test Case ID': 'TC_39_01', 'Brief Description': 'Alert triggers for document uploaded outside business hours.'}, {'Test Case ID': 'TC_39_02', 'Brief Description': 'No alert triggers for document uploaded within business hours.'}, {'Test Case ID': 'TC_39_03', 'Brief Description': 'Only assigned Case Worker receives after-hours alert.'}, {'Test Case ID': 'TC_39_04', 'Brief Description': 'Alert includes client, document, and timestamp details.'}, {'Test Case ID': 'TC_39_05', 'Brief Description': 'System logs after-hours alert for compliance/audit.'}, {'Test Case ID': 'TC_39_06', 'Brief Description': 'System handles time-zone variance correctly.'}]</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[{'Test Case ID': 'TC_39_01', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Document Handling', 'Sub-Process Title': 'Upload Monitoring', 'Activity Title': 'After-Hours Detection', 'Test Scenario Title': 'Alert for after-hours upload', 'Precondition': 'Client has assigned Case Worker. Upload allowed anytime.', 'Test Data': {'ClientID': 'C20021', 'DocumentType': 'Proof of Income', 'UploadTime': '21:30'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Log in as client and upload document at 21:30.', '2. System detects time outside business hours.', '3. System triggers alert to assigned Case Worker.'], 'Expected Result': 'Case Worker receives alert including client, document, and timestamp details.', 'Dependent Module/Process': 'Notification Service, Upload Module'}, {'Test Case ID': 'TC_39_02', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Document Handling', 'Sub-Process Title': 'Upload Monitoring', 'Activity Title': 'Business Hours Upload', 'Test Scenario Title': 'No alert for uploads within business hours', 'Precondition': 'Business hours defined (e.g., 8AM-6PM). Client assigned.', 'Test Data': {'ClientID': 'C20021', 'UploadTime': '10:30'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Client uploads document at 10:30.', '2. System detects time within business hours.'], 'Expected Result': 'No after-hours alert triggered.', 'Dependent Module/Process': 'Notification Service, Upload Module'}, {'Test Case ID': 'TC_39_03', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Notification', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Restricted Delivery', 'Test Scenario Title': 'Only assigned Case Worker receives alert', 'Precondition': 'Client is assigned to a specific Case Worker.', 'Test Data': {'ClientID': 'C20021', 'AssignedCaseWorker': 'CW789'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Unauthorized User', 'Detailed Test Steps': ['1. Upload document after hours.', '2. System delivers alert.', '3. Attempt to access alert as assigned and unassigned users.'], 'Expected Result': 'Only assigned Case Worker can view alert; unauthorized users cannot.', 'Dependent Module/Process': 'Notification Service, Access Control'}, {'Test Case ID': 'TC_39_04', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Notification', 'Sub-Process Title': 'Alert Details', 'Activity Title': 'Alert Content Validation', 'Test Scenario Title': 'Alert includes key details', 'Precondition': 'Client uploads document after hours.', 'Test Data': {'ClientID': 'C20021', 'DocumentName': 'Proof of Residency.pdf', 'UploadTime': '19:45'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Inspect the received alert.', '2. Review client and document information.'], 'Expected Result': 'Alert includes client name/ID, document name/type, upload timestamp.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_39_05', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Audit &amp; Compliance', 'Sub-Process Title': 'Logging', 'Activity Title': 'Alert Auditing', 'Test Scenario Title': 'After-hours alerts are audit-logged', 'Precondition': 'Audit log enabled.', 'Test Data': {'ClientID': 'C20021', 'UploadTime': '22:00'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor', 'Detailed Test Steps': ['1. Trigger after-hours alert by uploading document.', '2. Reviewer queries audit log.'], 'Expected Result': 'Log contains: alert type, timestamp, client ID, document type, Case Worker ID.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}, {'Test Case ID': 'TC_39_06', 'EPIC': 'Case Management', 'Feature': 'After-Hours Alerts', 'User Story': '39', 'Business Process': 'Configuration', 'Sub-Process Title': 'Time Zone Handling', 'Activity Title': 'Time Zone Configuration', 'Test Scenario Title': 'System accounts for time-zone differences', 'Precondition': 'Users in multiple time zones.', 'Test Data': {'ClientID': 'C20021', 'UploadTimeUTC': '02:00', 'CaseWorkerTimeZone': 'EST', 'ClientTimeZone': 'PST'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['1. Client in PST uploads document at 6PM PST.', '2. System calculates local business hours based on Case Worker time zone (EST).', '3. Determine if alert should trigger.'], 'Expected Result': "Alert is based on business hours in assigned Case Worker's time zone; time calculations validated.", 'Dependent Module/Process': 'Notification Service, User Profile Service'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>This user story requires the implementation of automated workload threshold alerts for Case Managers, enabling them to proactively manage and reassign cases when a caseworker is overloaded. The test coverage will focus on correct alert generation, delivery, role restrictions, integration with thresholds, audit requirements, and negative scenarios such as missing thresholds or unauthorized access.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>As a Case Manager, I want to receive alerts when a caseworker is overloaded so that I can reassign cases. (Workload threshold alerts)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>When a caseworker's assigned case count exceeds a pre-defined threshold, the system automatically generates and sends an alert notification to the responsible Case Manager, who can then access the system to review and act on the alert.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>[{'Test Case ID': 'TC40-001', 'Brief Description': 'Caseworker exceeds workload threshold; alert sent to assigned Case Manager (Positive/Functional)'}, {'Test Case ID': 'TC40-002', 'Brief Description': 'Threshold not crossed; no alert generated (Negative/Functional)'}, {'Test Case ID': 'TC40-003', 'Brief Description': 'Verify only Case Managers receive alerts for their own teams (Negative/User Role &amp; Permissions)'}, {'Test Case ID': 'TC40-004', 'Brief Description': 'Workload threshold changed; system uses updated threshold for alert generation (Integration/Functional)'}, {'Test Case ID': 'TC40-005', 'Brief Description': 'API returns correct workload alert status for dashboard (API/Integration)'}, {'Test Case ID': 'TC40-006', 'Brief Description': 'Audit log entry created when alert is sent (Compliance/Audit)'}, {'Test Case ID': 'TC40-007', 'Brief Description': 'Case Manager can access alert details and reassign cases (E2E/Functional)'}, {'Test Case ID': 'TC40-008', 'Brief Description': 'Unauthorized user attempts to access alert details (Negative/Security/Permissions)'}, {'Test Case ID': 'TC40-009', 'Brief Description': 'System unavailable during threshold breach; alert generated after recovery (Negative/Recovery/Integration)'}]</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>[{'Test Case ID': 'TC40-001', 'EPIC': 'Case Management', 'Feature': 'Workload Monitoring', 'User Story': 'US-40', 'Business Process': 'Case Allocation', 'Sub-Process Title': 'Workload Assessment', 'Activity Title': 'Threshold Alert Generation', 'Test Scenario Title': 'Caseworker exceeds workload threshold; alert sent to Case Manager', 'Precondition': 'Caseworker assigned to at least N cases (N is the configured threshold); Case Manager is linked to caseworker; Notification system is operational.', 'Test Data': {'CaseworkerID': 'CW1234', 'CaseManagerID': 'CM4678', 'Threshold': 15, 'CurrentAssignedCases': 16}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Admin and set workload threshold for caseworkers to 15.', 'Assign 16 active cases to CW1234.', "Wait for system's workload evaluation job to run.", 'Log in as Case Manager CM4678.', "Navigate to 'Workload Alerts' or notification center."], 'Expected Result': 'Alert is displayed to CM4678 indicating CW1234 has exceeded the workload threshold. Alert content includes caseworker name, assigned cases count, timestamp, and actionable link to reassign.', 'Dependent Module/Process': 'Notification system, Caseworker assignment, User roles/permissions'}, {'Test Case ID': 'TC40-002', 'EPIC': 'Case Management', 'Feature': 'Workload Monitoring', 'User Story': 'US-40', 'Business Process': 'Case Allocation', 'Sub-Process Title': 'Workload Assessment', 'Activity Title': 'No Alert When Threshold Not Crossed', 'Test Scenario Title': 'Caseworker under workload threshold; no alert should be sent', 'Precondition': 'Caseworker below threshold; Threshold configured; Notification system operational.', 'Test Data': {'CaseworkerID': 'CW5678', 'Threshold': 15, 'CurrentAssignedCases': 14}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Set workload threshold for caseworkers to 15.', 'Assign 14 active cases to CW5678.', 'Force workload evaluation run if necessary.', 'Log in as case manager for CW5678.', 'Check for new workload alerts.'], 'Expected Result': 'No alert should be generated or visible to any Case Manager for CW5678.', 'Dependent Module/Process': 'Notification system, User roles/permissions'}, {'Test Case ID': 'TC40-003', 'EPIC': 'Security &amp; Compliance', 'Feature': 'Role-Based Access Control', 'User Story': 'US-40', 'Business Process': 'Alert Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Restrict Alert Visibility by Role', 'Test Scenario Title': 'Only authorized Case Managers can receive alerts', 'Precondition': 'Workload threshold exceeded for a caseworker; Multiple Case Managers exist (some unrelated); Notification system operational.', 'Test Data': {'CaseworkerID': 'CW1234', 'AuthorizedManagerID': 'CM4678', 'UnauthorizedManagerID': 'CM9898', 'Threshold': 10, 'CurrentAssignedCases': 12}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager, Other Manager', 'Detailed Test Steps': ['Assign 12 cases to CW1234, assigned to CM4678.', 'Ensure CM9898 is not linked to CW1234.', 'Run workload evaluation.', 'Log in as CM9898 (unauthorized).', 'Navigate to workload alerts and check for any alert regarding CW1234.'], 'Expected Result': 'CM9898 does not receive any alert for CW1234. Only CM4678 is notified.', 'Dependent Module/Process': 'Notification system, User management'}, {'Test Case ID': 'TC40-004', 'EPIC': 'Case Management', 'Feature': 'Workload Monitoring', 'User Story': 'US-40', 'Business Process': 'Threshold Configuration', 'Sub-Process Title': 'Threshold Management', 'Activity Title': 'Alert Generation with Updated Thresholds', 'Test Scenario Title': 'System responds to threshold changes for future alerts', 'Precondition': 'Initial threshold set; Caseworker close to threshold.', 'Test Data': {'CaseworkerID': 'CW2345', 'OldThreshold': 10, 'NewThreshold': 15, 'CurrentAssignedCases': 12}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Set threshold to 10, assign 12 cases (alert should trigger).', 'Reset threshold to 15.', 'Run workload evaluation.', 'Log in as assigned Case Manager, review alerts.'], 'Expected Result': 'No new alert is generated for CW2345 after threshold increased, unless actual cases exceed new threshold.', 'Dependent Module/Process': 'Threshold config, Notification system'}, {'Test Case ID': 'TC40-005', 'EPIC': 'Workload API', 'Feature': 'Alert Status Delivery', 'User Story': 'US-40', 'Business Process': 'Data Integration', 'Sub-Process Title': 'API Availability', 'Activity Title': 'Provide Alert Status via API', 'Test Scenario Title': 'API call retrieves accurate workload alert status', 'Precondition': 'Threshold breached for a caseworker; alert has been generated.', 'Test Data': {'CaseworkerID': 'CW3456', 'AlertStatus': 'Active'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'API Consumer (Dashboard/App)', 'Detailed Test Steps': ['Trigger a threshold breach for CW3456.', 'Call the relevant API endpoint (GET /api/alerts/workloads?caseworker=CW3456).'], 'Expected Result': "API returns JSON payload showing 'Active' alert for CW3456, including timestamp and related info.", 'Dependent Module/Process': 'API Gateway, Notification system, Workload module'}, {'Test Case ID': 'TC40-006', 'EPIC': 'Case Management Audit', 'Feature': 'Compliance Logging', 'User Story': 'US-40', 'Business Process': 'Audit &amp; Reporting', 'Sub-Process Title': 'Alert Event Logging', 'Activity Title': 'Audit Entry for Alert Sent', 'Test Scenario Title': 'Audit record created when alert is sent', 'Precondition': 'Alert generated for threshold breach.', 'Test Data': {'CaseworkerID': 'CW4444', 'CaseManagerID': 'CM5555', 'Threshold': 15}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Audit Administrator', 'Detailed Test Steps': ['Trigger alert by assigning 16 cases to CW4444.', 'Access audit log as Audit Admin.', 'Search for alert generation event for CW4444.'], 'Expected Result': 'Audit log includes entry: caseworker ID, manager ID, alert timestamp, threshold crossed, action taken.', 'Dependent Module/Process': 'Audit log, Notification system'}, {'Test Case ID': 'TC40-007', 'EPIC': 'Case Management', 'Feature': 'Case Reassignment', 'User Story': 'US-40', 'Business Process': 'End-to-End Allocation', 'Sub-Process Title': 'Alert Response', 'Activity Title': 'Reassign after Alert', 'Test Scenario Title': 'Case Manager acts on alert, reassigns case', 'Precondition': 'Alert for overloaded caseworker is active; Case Manager in system.', 'Test Data': {'CaseworkerID': 'CW5555', 'CaseManagerID': 'CM1234', 'AlternateCaseworkerID': 'CW8888'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Caseworker CW5555 exceeds threshold; alert generated.', 'CM1234 opens alert details.', 'CM1234 selects one case and assigns to CW8888.', 'System confirms case reassignment.'], 'Expected Result': 'Case is reassigned from CW5555 to CW8888. Alert details update to reflect action. Audit log records action.', 'Dependent Module/Process': 'Case assignment, Alert system, Audit log'}, {'Test Case ID': 'TC40-008', 'EPIC': 'Security &amp; Compliance', 'Feature': 'Access Control', 'User Story': 'US-40', 'Business Process': 'Alert Management', 'Sub-Process Title': 'Alert Details Security', 'Activity Title': 'Unauthorized Access Attempt', 'Test Scenario Title': 'Unauthorized user cannot access alert details', 'Precondition': 'Alert generated for workload breach.', 'Test Data': {'CaseworkerID': 'CW2323', 'UnauthorizedUserID': 'USR9999'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Line Staff (not a Case Manager)', 'Detailed Test Steps': ['Alert generated for overloaded CW2323.', 'User USR9999 attempts to access alert details URL directly.'], 'Expected Result': 'System denies access and displays appropriate error message (e.g., 403 Forbidden). No data disclosed.', 'Dependent Module/Process': 'Authorization module, Notification system'}, {'Test Case ID': 'TC40-009', 'EPIC': 'System Reliability', 'Feature': 'Recovery Mode', 'User Story': 'US-40', 'Business Process': 'Background Processing', 'Sub-Process Title': 'Service Resiliency', 'Activity Title': 'Deferred Alert Generation After Outage', 'Test Scenario Title': 'Alert generated after system outage', 'Precondition': 'System temporarily unavailable during threshold breach; system recovery imminent.', 'Test Data': {'CaseworkerID': 'CW8888', 'CaseManagerID': 'CM0001', 'Threshold': 5, 'CurrentAssignedCases': 6}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Take notification system offline.', 'Assign 6 cases to CW8888 (threshold 5).', 'Restore notification system.', 'Run workload evaluation process.', 'Log in as CM0001 and check for alerts.'], 'Expected Result': 'After system recovery, alert is generated and visible to CM0001, including accurate timestamp of actual threshold breach.', 'Dependent Module/Process': 'Notification system, Background jobs'}]</t>
+          <t>[{'Test Case ID': 'TC40-01', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Case Assignment Management', 'Sub-Process Title': 'Monitoring Workload', 'Activity Title': 'Generate and Send Alert', 'Test Scenario Title': 'Workload crosses threshold; alert sent to Case Manager', 'Precondition': 'Caseworker is assigned to cases and workload monitoring is active. Threshold (e.g., 15 cases) is defined.', 'Test Data': {'Caseworker_ID': 'CW12345', 'Assigned_Cases_Before': 15, 'New_Assignment': 'CaseX'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as admin and set workload threshold to 15.', 'Log in as system and assign 15 cases to Caseworker CW12345.', 'Assign 1 additional case to CW12345.', 'Wait for the workload monitoring job/process to execute.', 'Log in as Case Manager and check notifications/alerts.'], 'Expected Result': 'Case Manager receives a clear alert stating CW12345 has exceeded the workload threshold.', 'Dependent Module/Process': 'Case Assignment, Notification Service'}, {'Test Case ID': 'TC40-02', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Case Assignment Management', 'Sub-Process Title': 'Monitoring Workload', 'Activity Title': 'Suppress Alert', 'Test Scenario Title': 'Workload remains below threshold; no alert sent', 'Precondition': 'Caseworker is close to threshold but not exceeded.', 'Test Data': {'Caseworker_ID': 'CW67890', 'Assigned_Cases': 14}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Ensure Caseworker CW67890 has 14 assigned cases (with threshold at 15).', 'Observe alert/notification module for any alerts.'], 'Expected Result': 'No alert is generated or received by Case Manager.', 'Dependent Module/Process': 'Case Assignment, Notification Service'}, {'Test Case ID': 'TC40-03', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Case Assignment Management', 'Sub-Process Title': 'Monitoring Workload', 'Activity Title': 'Generate Alerts for Multiple Overloaded Caseworkers', 'Test Scenario Title': 'Multiple caseworkers overloaded; Case Manager receives alerts for each', 'Precondition': 'Multiple caseworkers, with at least two about to exceed the threshold.', 'Test Data': {'Caseworker_1_ID': 'CW10001', 'Caseworker_2_ID': 'CW10002', 'Assigned_Cases_1': 15, 'Assigned_Cases_2': 15, 'Threshold': 15}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign cases so both CW10001 and CW10002 just exceed threshold.', 'Trigger workload monitoring.', 'Log in as Case Manager and view alerts.'], 'Expected Result': 'Case Manager receives separate alerts for each overloaded caseworker.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC40-04', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Case Assignment Management', 'Sub-Process Title': 'Respond to Alerts', 'Activity Title': 'Case Reassignment', 'Test Scenario Title': 'Case Manager acts on alert to reassign case', 'Precondition': 'At least one overload alert exists for a caseworker.', 'Test Data': {'Caseworker_ID': 'CW30123'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'View received overload alert for CW30123.', 'Initiate the reassignment process for one of the overloaded cases.', 'Confirm reassignment.'], 'Expected Result': "Case is reassigned successfully and alert shows as 'acted upon' or 'resolved'.", 'Dependent Module/Process': 'Case Reassignment'}, {'Test Case ID': 'TC40-05', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Access Control', 'Sub-Process Title': 'Permission Enforcement', 'Activity Title': 'Role-Based Restrictions', 'Test Scenario Title': 'Only Case Managers receive overload alerts', 'Precondition': 'System has users with roles: Case Manager, Caseworker, Auditor.', 'Test Data': {'Caseworker_ID': 'CW00011', 'Role_Users': ['Case Manager', 'Caseworker', 'Auditor']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'All', 'Detailed Test Steps': ['Simulate overload for CW00011.', 'Log in as Case Manager and verify alert receipt.', 'Log in as Caseworker and Auditor; check for alert visibility.'], 'Expected Result': 'Only the Case Manager receives the overload alert.', 'Dependent Module/Process': 'Authentication, Notification Access Control'}, {'Test Case ID': 'TC40-06', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Case Assignment Management', 'Sub-Process Title': 'Monitoring Workload', 'Activity Title': 'Duplicate Alert Prevention', 'Test Scenario Title': 'System prevents duplicate alerts for the same event', 'Precondition': 'Caseworker CW00234 is already flagged as overloaded.', 'Test Data': {'Caseworker_ID': 'CW00234', 'Current_Alert_Flag': 'True'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Ensure CW00234 is already marked as overloaded and alert exists.', 'Attempt to re-trigger overload (e.g., assign another case).', 'Monitor alert section for duplicate/identical new alerts.'], 'Expected Result': 'No duplicate alert is generated for the same overload event.', 'Dependent Module/Process': 'Notification De-duplication Logic'}, {'Test Case ID': 'TC40-07', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'API Integration', 'Sub-Process Title': 'Notification API', 'Activity Title': 'API Trigger', 'Test Scenario Title': 'Notification alert API correctly triggers on overload', 'Precondition': 'Notification API is enabled and authentication in place.', 'Test Data': {'API_Endpoint': '/api/alerts/overload', 'Payload': {'CaseworkerID': 'CW99876', 'CurrentLoad': 16, 'Threshold': 15}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'System', 'Detailed Test Steps': ['Simulate POST to /api/alerts/overload with payload indicating overload.', 'Observe Case Manager notifications.', 'Query alert status via API GET.'], 'Expected Result': 'Alert is triggered and visible to intended Case Manager; API response confirms alert creation.', 'Dependent Module/Process': 'Notification Service, API Gateway'}, {'Test Case ID': 'TC40-08', 'EPIC': 'Case Load Monitoring', 'Feature': 'Overload Alert Notification', 'User Story': 'US40', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Audit Alert Actions', 'Test Scenario Title': 'Audit log records alert creation and reassignment actions', 'Precondition': 'Audit logging enabled. Overload event occurs.', 'Test Data': {'Caseworker_ID': 'CW24680'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Trigger overload and alert for CW24680.', 'Reassign a case due to overload.', 'Access audit log as an Auditor.', 'Search for entries related to overload alert and reassignment.'], 'Expected Result': 'Audit log contains timestamped entries of alert generation, delivery, and actions taken (including user IDs).', 'Dependent Module/Process': 'Audit Log Service, Notification Service, Reassignment Module'}]</t>
         </is>
       </c>
     </row>

--- a/output_test_cases.xlsx
+++ b/output_test_cases.xlsx
@@ -457,1001 +457,1001 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>22895813</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['Submit a new Medicaid application with all mandatory fields completed.', 'Submit a new application omitting one optional field.', 'Submit a new application with invalid applicant data format (e.g., date of birth as text).', 'Attempt to submit a duplicate application for the same applicant.', 'Save an application as a draft before submission.', 'View application details after successful submission.']</t>
+          <t>['Verify that the Case Manager can access the eligibility status view for assigned clients.', 'Verify the eligibility status is displayed accurately for each client (eligible, ineligible, pending).', 'Verify filtering/sorting of clients by eligibility status.', 'Verify the date/time of the eligibility status is shown (if present).', 'Verify that eligibility status updates are reflected in real-time or after refresh.', 'Verify proper access control so only the Case Manager can view his/her clients.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Applicant name with special characters or Unicode.', 'Applicant with extremely long address or name fields.', 'Applicant birthdate set to future/past improbable dates.', 'No internet connection during application submission.', 'Simultaneous submissions from two case workers.']</t>
+          <t>['Clients with no eligibility assessment data.', 'Clients with multiple or conflicting eligibility statuses.', 'Rapid changes in eligibility (simultaneous updates).', 'Case Manager with a very large number of clients.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Verification that details submitted in intake are available for identity and income verification (related to Stories 2 and 3).']</t>
+          <t>['Test eligibility data rendering, as shared with 22895823 (report generation), 22895814, and 22895832.', 'Verify consistency between eligibility status view and summary report (22895823).']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 5, 8, 9, 11, 12, 19, 22, 26, 31]</t>
+          <t>['Eligibility data model (shared with 22895823, 22895832, 22895814, 22895841).', 'Case/Client access controls.']</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>22895831</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['Verify identity using a valid government ID (realistic sample).', 'Reject identity with a mismatched government ID.', 'Verify identity with an expired ID.', 'System timeout or error in response from DMV/SSA database.', 'Log each verification attempt and result.']</t>
+          <t>['Verify that the Case Worker can select multiple cases for document upload.', 'Verify that multiple document files can be selected and are associated with the correct cases.', 'Verify progress/status indicator during bulk upload.', 'Verify successful upload displays confirmation.', 'Verify failed uploads display error information per case/file.', 'Verify uploaded documents are retrievable under the correct cases.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['Applicant uses ID issued out of state or country.', 'ID contains special characters (hyphens, apostrophes).', 'Network interruption during database check.', 'Multiple IDs submitted for one applicant.']</t>
+          <t>['Uploading documents with invalid file types.', 'Uploading more documents/files than allowed limit.', 'Files with duplicate names across different cases.', 'Case is locked or not found during upload.', 'Network failure during bulk upload.']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['Cross-check that applicant data from intake (Story 1) matches the ID verification request.', 'Verify that identity verification locks out other processes on failure (may extend to Stories 1, 3).']</t>
+          <t>['File upload validation and association with cases (shared with 22895836: document preview before upload).']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[1, 3, 33]</t>
+          <t>['Document management and storage components (shared with 22895836, 22895828, 22895815).', "Cases' document association logic."]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>22895823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['Check income eligibility with accurate matched wage data.', 'Handle missing or partial wage data.', 'Handle mismatched SSN or applicant record.', 'Display error on integration failure with income verification system.', 'Manually override income after failed automatic check (if permitted).']</t>
+          <t>['Verify Case Worker can generate summary report for selected cases/clients.', 'Verify report includes accurate eligibility findings for all selected clients.', 'Verify report format (fields, layout) matches requirements.', 'Verify report export/download (PDF, Excel, etc.) is available.', 'Verify permission checks on report generation.']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['Applicant with multiple employers or multiple wage records for same period.', 'Applicant with zero wage earnings.', 'Income data in foreign currency or unusual frequency.', 'Rapid repeated queries for same applicant.']</t>
+          <t>['Generating a report for clients with no eligibility data.', 'Huge number of clients in report.', 'Eligibility data updates during/after report is running.']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['Ensure application retrieved from intake (Story 1) is the same used for income check.', 'Compare ID verification status from Story 2 with wage verification process.']</t>
+          <t>['Test eligibility data integrity and consistency (shared with 22895813, 22895832).', 'Test report export/download process.']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[1, 2, 37]</t>
+          <t>['Eligibility calculation logic (shared with 22895813, 22895832, 22895839).', 'Eligibility summary report features.']</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>22895836</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Add household members with relationships specified (parent, spouse, child, etc.).', 'Edit or remove a household member from application.', 'Attempt to submit household data with missing relationships.', 'Display household summary and calculated family size.', 'Reject adding duplicate household members.']</t>
+          <t>['Verify that Case Worker can initiate document preview before upload.', 'Verify correct rendering of supported file types (PDF, images, docs).', 'Verify error message upon trying to preview unsupported/corrupted files.', 'Verify preview matches the actual document content.', 'Verify ability to cancel upload after preview.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['Household member with same name as applicant.', 'Circular relationships (e.g., both members listed as parent and child of each other).', 'Unusually large households (e.g., 15+ members).']</t>
+          <t>['Attempting preview of large files or files with unsupported formats.', 'Previewing files with malware or embedded scripts.', 'Multiple previews in quick succession.']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['Ensure household info links back to correct application from intake (Story 1).', 'Test impact on eligibility calculations requiring family size.']</t>
+          <t>['File type/size validation logic (shared with 22895831, 22895828, 22895815).']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[1, 27]</t>
+          <t>['Document upload component (shared with 22895831, 22895828, 22895815).', 'Preview rendering component.']</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>22895834</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Submit a partially complete application and verify that it is flagged as incomplete.', 'Attempt to submit without any required documents to check flagging behavior.', 'Fill out all required fields and documents, confirm that flag is removed.', 'System generates a follow-up notification/reminder to case worker/applicant.', 'View dashboard/list of all flagged incomplete applications.']</t>
+          <t>['Verify Case Worker is notified when household data is conflicting.', 'Verify conflicting fields (e.g., addresses, relationships) are clearly highlighted.', 'Verify alert message is clear and actionable.', 'Verify notifications trigger only for actual conflicts.', 'Verify resolution instructions or links are provided.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['All optional fields left blank; only required missing.', 'Rapidly toggling between incomplete and complete states.', 'Application flagged as incomplete then deleted or withdrawn.']</t>
+          <t>['Multiple conflicts in a single household.', 'Rapid updates causing intermittent or resolved conflicts.', 'Edge case where conflict is due to data from external system.']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['Integration with Story 1 intake process to ensure correct flagging upon submission.', 'Interaction with document upload and completeness checks (Stories 11, 12, 22).']</t>
+          <t>['Testing notification/alert mechanism (shared with related stories 22895811, 22895844, 22895816 as per notification pattern).']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[1, 12, 11, 22]</t>
+          <t>['Household data model and validation rules.', 'Notification/alert infrastructure affecting related stories.']</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>22895846</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Login as Case Manager and access dashboard.', 'Verify eligibility status is displayed for each assigned client.', 'Verify renewal dates are displayed and accurate.', 'Check that clients with various eligibility states (e.g., eligible, expired, pending renewal) are correctly represented.', 'Ensure correct behavior for clients not assigned to the Case Manager (they should not be visible).']</t>
+          <t>['Verify that an alert is sent to the case worker when a client uploads a document after business hours.', 'Check that the alert includes client, document, and timestamp information.', 'Ensure an alert is NOT sent if a document is uploaded during business hours.', 'Validate the business hours definition (e.g., 9am-5pm configurable).', 'Review alert delivery mechanisms (email, dashboard, etc.).']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['Clients with missing or malformed eligibility data.', 'Clients with eligibility expiring today.', 'Clients with multiple eligibility programs (multi-line status).', 'Case Manager with no assigned clients.', 'Client whose eligibility was updated in another session during view.']</t>
+          <t>['Document uploaded at exactly the start or end of business hours.', 'Case worker divided across multiple time zones.', 'Multiple documents uploaded in quick succession after hours.', 'Document upload crosses business hours threshold (e.g., starts upload before, finishes after hours).']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['Shared with 7: Test eligibility status consistency and updates reflected in both dashboard view and alerts.', 'Shared with 23, 25, 30, 32, 34, 36: Test eligibility display when related functionalities such as alerts, updates, or renewals are triggered.']</t>
+          <t>['Check that alerts are triggered for document upload (shared with 22895824).', 'Test alert notifications for clients uploading documents during or after business hours.']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['7 (alerts on eligibility)', '23, 25, 30, 32, 34, 36 (all features displaying or using eligibility status or dates)', 'Any functionality displaying, updating, or using client dashboard data']</t>
+          <t>['22895824: Document upload alerting.', 'Any notification infrastructure (e.g., alert delivery used in other features).']</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>22895824</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['Simulate eligibility nearing expiration (29,30,31 days) and confirm alert appears.', 'Verify alert timing (exactly 30 days prior).', 'Ensure that once eligibility is renewed, alert is dismissed.', 'Check alert content for accuracy and clarity.', 'Login as different Case Manager and verify only appropriate clients trigger alerts.', 'Confirm system does not send duplicate alerts daily.']</t>
+          <t>['Verify that an alert is sent to a case worker whenever a client uploads a document.', 'Check the alert contains correct document, client, and timestamp details.', 'Ensure alerts are sent regardless of business hours.', 'Validate the system handles simultaneous uploads by multiple clients.']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['Eligibility expiring on leap day (Feb 29).', 'Eligibility expiring at end of month (e.g., April 30).', 'Eligibility status manually altered to expired/renewed during alert window.', 'Eligibility with no expiration date set.', 'Multiple clients expiring the same day.']</t>
+          <t>['Document uploaded by two clients at nearly the same time.', 'Upload fails halfway—no alert should be sent.', 'Document metadata is incomplete.']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['Shared with 6: Confirm that eligible statuses triggering alerts are the same as those shown on the dashboard.', 'Shared with 34, 36: Involve scenarios where eligibility changes affect both alerts and dashboard displays.']</t>
+          <t>['Validate alert notification format and delivery (shared with 22895846).', 'Test alert batching/deduplication logic (if any).']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['6 (dashboard eligibility display)', '34, 36 (other stories that trigger or display eligibility alerts)', 'Any notification/alarm/alerting features across the platform']</t>
+          <t>['22895846: After-hours alerting.', 'Notification systems used across application.']</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>22895829</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['Upload PDF, JPEG, PNG, and scanned images to a case; confirm success for each.', 'Attempt to upload an unsupported file type (e.g., .exe), and confirm rejection.', 'Verify that uploaded documents are linked to the correct case.', 'Check file size limits and upload behavior for large files.', 'Test access permissions for uploads (case worker vs non-case worker).', 'Download/view uploaded documents and verify integrity.']</t>
+          <t>['Verify that missing required fields in an application are detected.', 'Check that suggestions for completing missing fields are accurate and actionable.', 'Validate that case workers can access and apply suggestions easily.', 'Ensure suggestions do not expose sensitive information.']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['File with a corrupted header or empty file.', 'Mass upload (multiple files or rapid succession).', 'Files with special/unicode characters in filename.', 'Simultaneous uploads by two users to same case.', 'Network interruption during upload.']</t>
+          <t>['Applications with all fields completed—no suggestion shown.', 'Application missing multiple required fields.', 'Unrecognized or unexpected application fields.']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['Shared with 1, 11, 12, 13, 17, 21, 24, 29, 39: Test document upload, retrieval, linking, access rights, and integrity across features requiring file/document management.']</t>
+          <t>['Suggestion mechanism for data input (potentially shared with 22895812, 22895833).']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['1, 11, 12, 13, 17, 21, 24, 29, 39 (any other feature that uses file/document upload or management)', 'Any reports or exports involving uploaded documents']</t>
+          <t>['22895812, 22895833: If suggestion or field-checking logic changes.', 'Data validation components.']</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>22895811</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Search by full name and verify correct applicants are listed.', 'Search by partial name (test fuzzy matching).', 'Search by SSN (with/without dashes).', 'Attempt duplicate entry with existing name/SSN and verify prevention.', 'Check search performance with large applicant list.', 'Verify search results are restricted by user permissions.']</t>
+          <t>['Verify that household composition can be recorded and saved for a case.', 'Check that family size calculations are accurate and include all designated members.', 'Ensure household changes are tracked historically.', 'Validate that eligibility logic uses household composition correctly.']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['Applicants with identical names but different SSNs.', 'Special characters in names (e.g., O’Connor, José).', 'Very short input (&lt; 2 chars).', 'Applicants with missing or invalid SSNs.', 'Search performed during system sync or backup.']</t>
+          <t>['Household with zero members.', 'Large household (maximum supported size).', 'Editing/removing members after initial entry.', 'Duplicate household member entries.']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['Shared with 1, 31: Validate duplicate detection, search performance, and permission checks.']</t>
+          <t>['Eligibility assessment based on composition (possibly shared with eligibility stories 22895834, 22895810).']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['1 (if it involves applicant entry or search)', '31 (any other module using search or duplicate prevention functionality)', 'Any onboarding/registration or deduplication workflow']</t>
+          <t>['22895834, 22895810: Eligibility determination features.', 'Client information data structures.']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>22895820</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Assign case automatically based on workload and verify distribution among team members.', 'Override and manually assign/reassign a case; verify assignment.', 'Attempt to assign to inactive or overloaded team member.', 'Ensure notification/confirmation upon assignment.', 'Verify case status is updated post-assignment.']</t>
+          <t>['Verify sensitive information is detected and redacted in uploaded documents.', 'Check that non-sensitive documents are not altered.', 'Validate case worker can view redacted and original versions if permitted.', 'Ensure redaction is applied before document alerts are sent.']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['All team members at maximum capacity.', 'New case created while assignment in progress.', 'Team member removed from system after assignment.', 'Manual override to self-assigned case.', 'Very large team or batch assignment.']</t>
+          <t>['Documents with unusual formats (handwritten, images).', 'Partially detected sensitive information.', 'Multiple types of sensitive data in one document.', 'Large/complex documents with many pages.']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['Shared with 28, 40: Test for assignment rules, overrides, reassignment, and notifications across all case-control/management modules.']</t>
+          <t>['Redaction logic (shared with 22895815, 22895831).', 'End-to-end document upload and alert process.']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['28, 40 (all related to team assignment, workload balancing, and reassignment)', 'Any user notification or workload report module']</t>
+          <t>['22895815, 22895831: Redaction and privacy features.', 'Document upload, notification, and alert stories (22895824, 22895846).']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>22895816</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['Generate email with correct applicant and missing document references.', 'Generate SMS with secure upload link.', 'Secure upload link is unique to applicant and document request.', 'Link expiration feature works as expected.', 'Notification is sent upon request initiation.', 'Retry/resend notification if first delivery fails.', 'Log notification delivery status.']</t>
+          <t>['Search by full name returns correct applicant(s)', 'Search by partial name returns appropriate results', 'Search by full SSN returns the correct applicant', 'Search with invalid or nonexistent SSN returns no results', 'Search with blank input returns appropriate message or all applicants (if designed)', 'Search results update if applicant data is changed', 'Ensure search prevents duplicate entries based on existing applicants']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['Applicant does not have a valid email or mobile number.', 'Applicant receives multiple requests simultaneously.', 'Upload link expires before applicant can act.', 'Wrong/malformed upload link sent.', 'Spam filter blocks notification.']</t>
+          <t>['Search by name with leading, trailing, or multiple spaces', 'Search by name with different capitalizations', 'Search by name with special characters or accents', 'Search by SSN with dashes, spaces, or invalid formats', 'Multiple applicants with similar names', 'SSN with fewer/more than 9 digits']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['Document upload integration from related stories 5 and 8.', 'Validation of secure links with document submission (story 12).']</t>
+          <t>['Verify that applicant search functionality integrates with add/edit applicant workflows (related: 22895834, 22895838, 22895808)']</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[1, 5, 8, 12, 17]</t>
+          <t>['22895834', '22895838', '22895808']</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>22895818</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['Document status is updated upon applicant upload.', 'Case worker is able to see all pending, submitted, and verified items.', 'Checklist loads correctly for all applicants.', 'Status indicators are accurate and reflect backend status.', 'Manual overrides by Case Worker update status.', 'Notifications triggered for pending items.']</t>
+          <t>['Send document request to a single applicant', 'Send requests for multiple document types', 'Applicant receives notification for document request', 'Document request appears in applicant’s portal/dashboard', 'Case Worker sees status of document requests (pending/completed)', 'Error shown if trying to send request for unsupported document type']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['Multiple applicants uploading the same document.', 'Corrupted document upload.', 'Status stuck in pending after successful upload.', 'Checklist refreshes with incomplete status after system crash.']</t>
+          <t>['Send request to invalid or inactive applicant', 'Send duplicate requests for the same document', 'Request with blank or missing document types', 'Large batch of requests sent at once', 'Applicant with no email/contact info']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['Document upload workflow from stories 5, 8, 11, 17.', 'Checklist visibility after document request sending (story 11).']</t>
+          <t>['Test communication/notification logic (related: 22895819, 22895824, 22895826)']</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[5, 8, 11, 17]</t>
+          <t>['22895819', '22895824', '22895826']</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>22895815</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Uploaded document scanned for sensitive fields (e.g., SSN, addresses).', 'Redaction tool marks and masks sensitive data correctly.', 'Case Worker can preview and adjust redactions before saving.', 'Redacted documents are stored and replace originals in case file.', 'Unauthorized users cannot access unredacted originals.']</t>
+          <t>['Upload a single document to a case', 'Upload multiple documents to a single case', 'Support various file types (PDF, JPG, DOCX, etc.)', 'Restrict file upload size as per requirements', 'Case Worker can view uploaded documents after upload', 'Document upload fails gracefully with invalid file format']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['Document contains non-standard formatting (e.g., handwriting, scanned images).', 'Redaction fails to detect all sensitive information.', 'Manual redaction overrides auto-detected fields.', 'User attempts to download original unredacted version.']</t>
+          <t>['Upload with corrupted file', 'Upload extremely large file', 'Upload file with special characters in name', 'Simultaneous uploads of the same document', 'Upload to a non-existent or closed case']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['Document upload and storage handling from story 8.']</t>
+          <t>['Document view and retrieval (related: 22895831, 22895836, 22895820)']</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[8]</t>
+          <t>['22895831', '22895836', '22895820']</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>22895809</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['All communication types (email, call, SMS, portal message) logged with timestamps.', 'Logs display correct chronology and metadata.', 'Case Manager can filter logs by type or date.', 'Privacy restrictions apply to sensitive communications.', 'Audit log captures log edits or deletions.']</t>
+          <t>['Enter valid government ID returns verified status', 'Enter invalid or expired government ID returns error/failed status', 'Case Worker can review ID details before finalizing verification', 'Store verification status on applicant record', 'Attempt verification without required fields triggers error']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['Duplicated entries in log due to system error.', 'Log entry missing sender or content details.', 'Bulk imported communications from legacy systems.', 'Very high volume of logs for a single case.']</t>
+          <t>['ID with special characters or unusual formats', 'Two applicants with the same government ID', 'Upload blurry or partial ID image', 'Very long or very short ID numbers', 'Verification when system is offline or external service fails']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ID verification process consistency (related: 22895810)']</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22895810']</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>22895835</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['Dual eligibility case shows correct agency flags.', 'Notes shared between agencies are visible to authorized users only.', 'Case Manager can add/edit/remove inter-agency notes.', 'Update of case status in one agency propagates to connected agencies.', 'Alerts for benefit overlaps or conflicts are generated.']</t>
+          <t>['Assign case based on specified language preference', 'Automatic assignment when multiple agents have matching language skills', 'Fallback assignment when no agent has matching language', 'Update language preference and re-assign case', 'Display case assignments with assigned language clearly to case managers']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['Agency connection lost during update.', 'Conflicting notes or flags from two agencies.', 'User lacks permission to see flags.', 'Simultaneous updates from multiple agencies.']</t>
+          <t>['Applicant specifies a rare or unsupported language', 'No available case managers at time of assignment', 'Change in agent language skills after assignment', 'Simultaneous new cases with identical preferences', 'Applicant with multiple language preferences selected']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Case assignment rules consistency across case manager workflow (related: 22895817, 22895847)']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22895817', '22895847']</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>22895817</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['Verify that the case worker can generate a PDF summary for a given case.', 'Verify that the generated PDF contains all eligibility findings for the selected case.', 'Check the formatting and readability of the generated PDF.', 'Verify the PDF can be saved/downloaded.', 'Verify that the PDF content matches the data present in the case system.']</t>
+          <t>['Assign a new case to a team member with the lowest workload', 'Assign a case to a team member with manually adjusted workload', 'Attempt to assign a case when all members have reached their maximum case limit', 'Reassign an existing case to another team member', 'View summary of cases per team member post-assignment to verify workload balance']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['Generate a summary for a case with no eligibility findings.', 'Generate a summary for a case with very large number of eligibility findings (e.g., 100+).', 'Check PDF generation for a case with special or non-ASCII characters in findings.', 'Check for timeout or failure if PDF generation fails.']</t>
+          <t>['Assign case when one or more team members are marked as unavailable', 'Assign case when team workload information is incomplete or delayed', 'Assign multiple cases at once to test bulk assignment logic', 'Assign a case to a member with 0 workload versus those with several assignments']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Test interactions with story 22895827 (escalation) to ensure assigned cases can be escalated', 'Verify assignment changes for cases that are to be exported (story 22895837)', 'Test efficiency when cases are filtered by eligibility (story 22895830) prior to assignment']</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['Any other features generating or exporting PDFs in the system', 'Eligibility findings data model and reporting']</t>
+          <t>['22895827 (case escalation)', '22895837 (case export)', '22895825 (if relates to case reallocation/assignment logic)']</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>22895822</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Upload a document as a client and verify the case worker immediately receives an alert.', 'Verify the notification contains case identifier and uploader information.', 'Verify the alert is visible on both web and mobile (if applicable).', 'Ensure duplicate alerts are not generated for the same upload.', 'Check that alerts are only sent to case workers assigned to the case.', 'Check that the alert links to the uploaded document and relevant case.']</t>
+          <t>['Initiate coordination with another agency for a dual eligibility case', 'Log communication history with partnering agency for an eligible client', "Verify protocol followed for agencies' responses (accepted, declined, no response)"]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['Document uploaded during system downtime—test notification delivery post-recovery.', 'Simultaneous uploads by multiple clients on one case.', 'Uploads by unauthorized users (should not trigger alerts).', 'Non-standard file types or extremely large files.']</t>
+          <t>['Coordinate with an agency that is not yet in the system', 'Coordinate when agency response times out or fails', 'Dual eligibility for more than two agencies']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['Verify notifications for document uploads (Shared with stories 8, 11, 12, 39).']</t>
+          <t>['Test filtering of dual eligible cases (shared with 22895830), then coordinating', 'Verify that exporting dual eligibility cases (22895837) includes coordination status']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['Notification system (all types)', 'Document upload workflow', 'Access control for alerts']</t>
+          <t>['22895830 (filtering eligibility status)', '22895813 (related communication/coordination features)', '22895837 (case export including agency coordination details)']</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>22895827</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Verify that case manager can start and stop a timer per case.', 'Verify manual entry of time logs is possible and accurate.', 'Check that time logged appears correctly in workload reports.', 'Edit or delete time logs and verify changes reflect in case and reports.', 'Ensure time logs are attributed to the correct case and user.']</t>
+          <t>['Escalate an urgent case to a supervisor and verify notification', 'Track escalation status and resolution outcome', 'Attempt escalation for cases already handled or closed', 'Escalate both assigned and unassigned (or recently reassigned) cases']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['Attempt to log negative or zero minutes/hours.', 'Simultaneous timer sessions by same user on different cases.', 'Very large durations (e.g., timer left running for a week).', 'Manual entry with future or implausible past dates.']</t>
+          <t>['Escalate a case currently being assigned to another team member', 'Escalate multiple cases at once', 'Escalate a case with incomplete data']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>['Time tracking and reporting interactions (Shared with stories 32, 40).']</t>
+          <t>['Test with various case assignment conditions (22895817)', 'Verify escalation events are reflected in case data export (22895837)']</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['All workload reporting features', 'UI for case detail and reporting', 'Historical case data aggregation']</t>
+          <t>['22895817 (case assignment)', '22895825 (if case reassignment or escalation flows overlap)', '22895837 (case export including escalation status)']</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>22895837</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Verify that a checklist can be generated and printed for any case type.', 'Check that the checklist contains correct document requirements for the chosen case type.', 'Verify printable output (formatting, page breaks, etc.).', 'Print-preview functionality validation.', 'Checklist printing with various browsers/printers.']</t>
+          <t>['Export single case data to Excel and verify format/fields', 'Export filtered case list (by eligibility, priority, assigned member, etc.)', 'Export large number of cases and verify performance/limits', 'Export during concurrent case assignment or escalation actions']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['Case types with no required documents.', 'Checklist with very large number of required documents.', 'Printing in portrait vs. landscape mode.', 'Very long document names or special characters.']</t>
+          <t>['Export when no cases are present or filtered set is empty', 'Export with cases containing non-ASCII/unusual characters', 'Export when connection is interrupted']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>['Checklist generation and printing (Shared with stories 1, 5, 26).']</t>
+          <t>['Ensure exported data includes assignment (22895817), escalation (22895827), and eligibility coordination (22895822, 22895830) statuses', 'Export after bulk updates or changes']</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['Document management features', 'Case type configuration', 'Related print/export features']</t>
+          <t>['22895817, 22895827, 22895822, 22895830 (any field or status change should reflect in exported data)']</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>22895830</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['Verify that a case manager can flag a case as urgent and escalate to a supervisor.', 'Verify that escalated cases are visible to supervisors immediately.', 'Check that priority flags are visually distinct in case lists.', 'Test notification to supervisor upon escalation.', 'Verify tracking/audit log records the escalation event.']</t>
+          <t>['Filter clients by eligible status and verify result list', 'Filter by ineligible or pending status', 'Filter when no clients meet criteria', 'Combine filters (status + assigned case manager, etc.)']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['Escalating the same case multiple times.', 'Multiple simultaneous escalations of different cases.', 'Escalation and de-escalation (if supported).', 'Escalating cases without supervisors assigned.']</t>
+          <t>['Eligibility status is updated during filtering', 'Client with multiple eligibility types or pending changes', 'Filtering on very large client lists']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>['Escalation workflow (Shared with story 38).']</t>
+          <t>['Filtering followed by assignment (22895817)', 'Filtering for dual eligible cases and coordinating (22895822)', 'Filtering and exporting results (22895837)']</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['Supervisor alert and case assignment systems', 'Case list filtering and sorting', 'Notification and audit features']</t>
+          <t>['22895822 (dual eligibility coordination)', '22895837 (case export)', '22895817 (case assignment based on filter)']</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>22895843</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Verify OCR is triggered for each uploaded document.', 'Check that metadata (date, type, owner) is extracted from various document formats (PDF, JPG, PNG).', 'Validate that documents with unreadable text trigger error or warning messages.', 'Test that successfully validated documents bypass manual review queue.', 'Confirm that validation errors are logged and visible to the Case Worker.']</t>
+          <t>['Verify alert is generated when a case is inactive for exactly 60 days.', 'Verify alert includes relevant case details and notification to the correct Case Manager.', 'Confirm alert is not triggered for cases with activity in the last 59 days.', 'Verify alert is sent only once per inactivity period per case.', 'Confirm alert method (email, UI notification, etc.) per requirements.', 'Verify correct handling of cases that become active after an alert.', 'Test alert generation for different Case Managers, with multiple assigned cases.']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['Upload a corrupted or password-protected file.', 'Use a document with no readable text (blank page).', 'Upload an image with handwritten or distorted text.', 'File with incorrect or missing metadata.', 'Supported file type with unusual encoding or orientation.']</t>
+          <t>['Case inactive for 59 days, activity occurs, then another period of inactivity.', 'Case with no recorded activity at opening.', 'System downtime on scheduled alert day.', 'Case closed before 60 days ends.']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>['Test document upload workflow used in story 8 (if 8 covers document upload core logic).', 'Bulk or batch upload validation process from story 24.']</t>
+          <t>['Test alert delivery and notification logic shared with 22895841 and 22895814 (alert mechanisms and recipient validation).', 'Test alert list filtering/multiple alert types together (relates to 22895841 and 22895814).']</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['Story 8 (document upload and processing core logic)', 'Story 24 (bulk upload if validation also applies per file)']</t>
+          <t>['22895841 (overdue redeterminations alert logic)', '22895814 (eligibility expiration alert logic)']</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>22895847</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['Submit an incomplete application and verify field suggestions are generated.', 'Ensure suggested fields are contextually relevant based on AI analysis.', 'Check performance for large/complex applications.', 'Ensure suggestions update live as fields are completed.', 'Dismiss a suggestion and verify it does not reappear unless context changes.']</t>
+          <t>["Verify alert triggers when a caseworker's assigned cases meet or exceed the overload threshold.", 'Verify alerts are only sent to Case Managers, not caseworkers.', 'Confirm alert contains relevant details: overloaded caseworker, number of cases, list of case IDs.', 'Test alert triggers when crossing threshold due to reassignment or new cases.', 'Test for cases where multiple caseworkers become overloaded at once.', 'Ensure notifications stop if cases are reassigned below threshold.']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['All fields already completed (should return no suggestions).', 'Application with unusual or rare data types.', 'Fields intentionally left blank (e.g., applicant chooses not to answer).', 'Application with conflicting or ambiguous data.']</t>
+          <t>['Caseworker assigned just below threshold, receives several new cases at once.', 'Threshold changed in settings: verify system re-evaluates current assignments.', 'Caseworker becomes unavailable (on leave) while overloaded.', 'Multiple alerts for the same caseworker in short succession.']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>['Field validation and completion logic from story 1 (which may handle basic missing fields).', 'Checks for required field logic from story 5 (if related to field requirement completeness).']</t>
+          <t>['Test alert delivery &amp; notification channel logic shared with other alert stories (ensure consistent implementation across user roles).']</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['Story 1 (field validation, error handling)', 'Story 5 (required fields and application completeness logic)']</t>
+          <t>['Related stories 22895817, 22895835 involving case assignment logic or caseworker workload.']</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22895814</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>["Apply filter for 'pending' status and verify only correct clients are shown.", "Filter by 'approved' and 'expired', review that only appropriate clients display.", 'Reset/remove filter and confirm full client list returns.', 'Check multi-status filters (if supported).', 'Verify filters persist or reset as per requirements on navigation.']</t>
+          <t>["Verify alert triggers when client's eligibility is within notification window (e.g., 30 days before expiration).", 'Confirm alert includes client details, expiration date, and next steps.', 'Alert is sent only to relevant Case Manager.', 'No alert if eligibility already redetermined or extended.', 'Alert cancels if client eligibility is updated before expiration.', 'Multiple clients expiring simultaneously handled correctly.']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['No clients in a chosen status.', 'Client with invalid/unknown status.', 'Large client lists to test performance of filtering.', 'Rapidly toggling between statuses.']</t>
+          <t>['Client eligibility expiring on a holiday/weekend.', 'Eligibility extended minutes before alert is due.', 'Multiple eligibility windows per client (multiple programs).', 'Eligibility manually overridden by admin.']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>['Client dashboard rendering and status logic from story 6 (if story 6 covers client status tracking).']</t>
+          <t>['Test alert generation and recipient correctness shared with 22895841 and 22895843.', 'Multiple concurrent alerts of different types (test alert queue/rendering).']</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['Story 6 (client status tracking and dashboard filtering logic)']</t>
+          <t>['22895841 (overdue redetermination and alert flow), 22895843 (alert mechanics).']</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>22895841</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Bulk upload multiple documents and verify each is assigned to the correct case.', 'Attempt batch upload with one or more unsupported file types.', 'Check for error reporting on failed uploads within a batch.', 'Test simultaneous bulk uploads by multiple users.', 'Validate performance for large batches.']</t>
+          <t>['Verify overdue redeterminations are correctly flagged after eligibility expiration.', 'Alert sent only once per client per overdue period.', 'Multiple overdue clients flagged in dashboard/report.', 'Redetermination completed should remove overdue flag.', 'Accurate calculation of overdue status based on eligibility date.']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['Batch with a mix of valid and invalid files.', 'Batch with duplicate or conflicting case identifiers.', 'Documents for nonexistent cases.', 'Extremely large file sizes.']</t>
+          <t>['Redetermination completed immediately after becoming overdue.', 'Multiple overdue periods tracked for same client.', 'Eligibility date modified after becoming overdue.', 'Client is transferred between Case Managers while overdue.']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>['Document processing and validation logic from story 8 (core upload).', 'Auto-validation process from story 21 (if auto-validation also applies to bulk uploads).']</t>
+          <t>['Alerts tested for delivery, content, and recipient logic with 22895843 and 22895814.', 'Test updates to dashboard/status shared with other alerting stories.']</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['Story 8 (general document upload)', 'Story 21 (if auto-validation is used by bulk upload process)']</t>
+          <t>['22895814 (eligibility expiration alerts), 22895843 (inactivity alerts)']</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>22895845</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['Access analytics dashboard and verify trends for different denial reasons.', 'Confirm data matches underlying client/application records.', 'Filter analytics by time period, region, or other available facets.', 'Check graphical and numeric representations are consistent.', 'Download/export report and verify data integrity.']</t>
+          <t>['Verify escalated case count matches number of cases with escalation flag.', 'Count and summary appear correctly on reporting dashboard.', 'Trend reporting accurately reflects changes in escalated case volume over time.', 'Cases can be escalated and de-escalated and counts update accordingly.', 'Multiple escalation reasons are handled correctly.']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['No denials in selected period (empty trend).', 'Multiple denials for single client (duplicate handling).', 'Denial reason field is blank or contains unusual text.', 'Huge volume of denial records – stress/performance.']</t>
+          <t>['Case escalated, de-escalated, then escalated again; ensure correct historical trends.', 'Bulk escalation or de-escalation events.', 'Escalated case is closed or reassigned.']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>['Eligibility status and case status logic from story 6 (if analytics source is same status used for filtering in story 23).']</t>
+          <t>['Test dashboard/reporting rendering and refresh across data changes (may overlap with related escalation/urgency stories).', 'Validation of escalation flag logic could be shared if escalation is used in other stories.']</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['Story 6 (eligibility status logic impacts dashboard analytics)', 'Story 23 (dashboard filtering features if dashboard code is shared)']</t>
+          <t>['22895827 (if escalated case logic or reporting is reused), any reporting dashboards using escalated case count.']</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>22895825</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Verify that application forms are automatically pre-filled with data from the applicant’s previous cases.', 'Verify that correct and relevant fields are populated based on historical records.', 'Check that manual edits to pre-filled data are possible and saved correctly.', 'Check audit logs to see if auto-filled information is tracked.', 'Verify functionality when no previous case exists (should show blank fields).', 'Test that data is pulled from the most recent previous case.']</t>
+          <t>['Start tracking time when a case is opened.', 'Pause and resume time tracking on a single case.', 'Stop time tracking when a case is closed.', 'Log manual time entry/edit for a case.', 'Access time reports filtered by case, case manager, and date range.', 'Validate that time records persist across sessions.']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['Previous data has missing or invalid formats.', 'Applicant has multiple previous cases with conflicting data.', 'Very large previous case data sets (performance, completeness).', 'Previous cases contain special characters or non-standard input.']</t>
+          <t>['Multiple cases open concurrently and time tracked simultaneously.', 'Unusually long or negative time entries.', 'Time tracking interrupted by system crash or logout.', 'Leap year and daylight saving time changes during tracking.']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['Related to [1, 19]: Test data shared/refreshed across linked applications.']</t>
+          <t>['Integration with workload reporting (potential overlap with related stories 22895817, 22895837).']</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Story 1 (initial application creation and data entry)', 'Story 19 (data duplication or reuse elsewhere)', 'Any form pre-fill/autofill functionality']</t>
+          <t>['Any workload or time reporting features (related: 22895817, 22895837).']</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>22895832</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['Cross-check household data (e.g., names, SSN, DOB) across all existing applications for a new or updated entry.', 'Trigger and display alert when conflicting household data is detected.', 'Ensure alert displays relevant information for resolving discrepancies.', 'Test dismissal and resolution workflow for the alert.', 'Confirm no alert is shown when there are no conflicts.']</t>
+          <t>['View eligibility denial trends over different time periods (week, month, year).', 'Filter trend data by case type, program, or region.', 'Export or print trend reports.', 'Identify ‘spikes’ or anomalies in denial trends.', 'Display systemic issues or common denial reasons.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Household data differs by single character or whitespace.', 'Multiple conflicting records found for same household.', 'Same household member appears under different spellings or identifiers.', 'Household data includes non-English alphabets or symbols.']</t>
+          <t>['Periods with zero denials.', 'Sudden unexplained surge or drop in denials.', 'Incomplete or corrupted trend data.', 'Very large data sets (performance).']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>['Related to [4]: Shared data validation, conflict resolution workflow.']</t>
+          <t>['Testing eligibility denial logic with stories 22895813, 22895823.']</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['Story 4 (data quality checks or duplicate detection)', 'Any household member verification features']</t>
+          <t>['Eligibility logic and reporting (22895813, 22895823).']</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>22895828</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Assign case to a caseworker based on client’s language preference.', 'Verify that only caseworkers with the relevant language skill are selectable/assigned.', 'Provide alternative assignment when no caseworker matches the language preference.', 'Allow re-assignment and confirm language preference is preserved.', 'Display language skill of each caseworker in the assignment interface.']</t>
+          <t>['Upload a document and confirm it is auto-validated correctly.', 'Reject a clearly invalid/incorrect document.', 'Review validation results and override if necessary.', 'Log/document the validation process.', 'Display validation errors clearly to the user.']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>["Client's preferred language not supported by any caseworker.", 'Caseworker has multiple language skills.', 'Clients specify multiple or ambiguous language preferences.', 'Case assignment for large numbers of simultaneous incoming cases.']</t>
+          <t>['Unsupported or corrupted file formats.', 'Oversized files or files with ambiguous content.', 'Network interruption during upload.', 'Simultaneous uploads of multiple documents.']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>['Related to [10]: Test general case assignment logic and override processes.']</t>
+          <t>['Integration with document management features (see related: 22895831, 22895836).']</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Story 10 (case assignment workflow)', 'Any assignment/matching functionality']</t>
+          <t>['Document upload/validation flows, manual review features (22895831, 22895836).']</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>22895810</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['Upload a document and verify that an accurate preview is shown before confirming upload.', 'Test the preview with different formats (PDF, JPG, PNG, DOCX, etc.).', 'Check user actions (zoom, rotate, page through multi-page files) in preview pane.', 'Attempt to upload a corrupt or unsupported file and verify error handling.', 'Ensure preview does not save file until confirmed.']</t>
+          <t>['Check income eligibility with valid wage data.', 'Handle missing or incomplete wage data gracefully.', 'Validate proper calculation per current eligibility rules.', 'View income eligibility history for a case.', 'Manual override or note addition to income eligibility determination.']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['Large files, multi-page documents, or high-resolution images.', 'Empty or blank documents.', 'Password-protected or encrypted documents.', 'File with malicious content.']</t>
+          <t>['Conflicting sources of wage data.', 'Applicants at edge of eligibility income limits.', 'Negative, zero, or extremely high wages.', 'Eligibility checks during year-end or policy changes.']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>['Related to [8]: Shared document upload, validation, and error messaging.']</t>
+          <t>['Eligibility processing (overlap with 22895813, 22895809, 22895811).']</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['Story 8 (document upload, validation, error handling)', 'Any file handling workflow']</t>
+          <t>['Eligibility and qualification modules (22895811, 22895809, 22895813).']</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>22895812</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Export filtered case lists to CSV and Excel formats.', 'Verify data completeness and correct formatting in exported files.', 'Check that filters (date range, status, worker, etc.) are respected in export.', 'Test export functionality for large numbers of cases (performance test).', 'Open exported file in Excel and verify readability and column structure.']</t>
+          <t>['Flag an application as incomplete when mandatory fields are missing.', 'Remove the incomplete flag when fields are filled.', 'Generate notifications or alerts for incomplete applications.', 'Case Worker can view, filter, and sort by incomplete status.', 'Report on incomplete applications over a time period.']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['Exporting with no filters (all cases).', 'Exporting with filters that return no results.', 'Very large datasets (row limits, memory).', 'Special characters or Unicode in data fields.']</t>
+          <t>['Fields that become mandatory conditionally.', 'Rapid user edits (flag must update in real time).', 'Network or save failures after flagging.']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>['Related to [6]: Data filtering logic and general export features.']</t>
+          <t>['Application completeness and notification features (related: 22895829, 22895818).']</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['Story 6 (export logic, data filters)', 'Any case data reporting functionality']</t>
+          <t>['Application processing, notification, and status features (22895829, 22895818).']</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>22895808</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Submit two applications with matching key identifiers (e.g. name, DOB, SSN) and verify that both are flagged as duplicates.', 'View a list of flagged duplicates and confirm that potential matches are displayed to the case worker.', 'Attempt to merge flagged applications and verify that the merge process works as expected.', 'Test alert/notification delivery for duplicate detection (e.g. email, dashboard alert).', 'Verify that cases not matching duplicate criteria are not flagged.', 'Audit log records when a duplicate is detected or merged.']</t>
+          <t>['Verify that the Case Worker can access the Medicaid application intake screen.', 'Validate all required fields are presented and labeled correctly.', 'Test that fields accept and validate proper data formats (e.g. SSN, DOB, income).', 'Ensure successful saving/submission of a new Medicaid application.', 'Check that a new application record appears in the system after submission.', 'Ensure error messages display for required fields if left blank.']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['Applications with slight variations (e.g. one has a typo in the name).', 'Applications submitted in rapid succession versus hours apart.', 'Cases with missing or partial identification fields.', 'Extremely large batches of applications submitted at once.', 'Applications flagged as duplicates, but on review, are not the same person.']</t>
+          <t>['Submissions with special characters in name or address fields.', 'Very large numbers or out-of-range values for income, household size etc.', 'Simultaneous submissions for the same client.', 'Submitting incomplete or invalid application data.']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>['Review alert/flag system mechanics as in stories 1 and 9 (e.g., notification handling, display in work queues).']</t>
+          <t>['Test creation of a new application (also relevant if intake triggers duplicate alerts, see 22895838).', 'Field validation (should be shared if 22895808 or 22895838 adjust the intake process).']</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[1, 9]</t>
+          <t>['22895816 - If the intake process changes, any downstream steps related to the eligibility process.', '22895838 - Duplicate detection (alerts/merges).']</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>22895826</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['Generate monthly report for all case activities.', 'Filter report by individual worker and verify the output matches database records.', 'Filter report by case status (open, closed, overdue) and verify data.', 'Export report and confirm downloaded file matches visible data.', 'Test report generation for months with no activity to verify handling of empty datasets.', 'Verify only Case Managers have access to this report function.']</t>
+          <t>['Verify availability of the print checklist function.', 'Ensure that checklist includes all document types and correct items based on application type.', 'Test printing from different browsers/OS.', 'Validate downloaded/printed checklist output format.', 'Check that user can print for different client scenarios (new/renewal application, household size variations).']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['Generate report for a non-existent worker.', 'Extremely high number of cases (performance and correctness).', 'Case activities spanning multiple months for the same case.', 'Statuses with zero cases in the selected period.']</t>
+          <t>['Checklist for applications with unusual requirements (e.g. multiple languages, guardianships).', 'Very large family or household size resulting in long lists.', 'Checklist printing attempts for incomplete or incorrect application data.']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>['Filter selection and report validation logic similar to stories 6 and 18 (e.g. ensure filter and date logic is consistent across reporting modules).']</t>
+          <t>['Print checklist UI and functionality (also applies to 22895842 for printing summary).']</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[6, 18]</t>
+          <t>['22895818 - If document requirements change, it might impact the checklist.', '22895842 - Shared print functionality.']</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>22895842</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['Trigger an eligibility rule change and verify that all relevant case workers receive notifications.', 'Check that the notification includes clear information about the policy update.', 'Verify that only affected case workers receive the alert (based on assignment/responsibility).', 'Test acknowledgment or dismissal of the notification.', 'Audit notification delivery and read history.']</t>
+          <t>['Verify user can select and print case notes summary for a given client.', 'Test that selected notes appear accurately and in order.', 'Check that formatting of printed summary is correct.', 'Ensure different note types (manual entries, system logs) display properly.', 'Test print from multiple browsers/OS.']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['Multiple rules changing in quick succession.', 'Case Worker is offline or logged out when the rule changes.', 'Rules reverted back to the original after notification sent.', 'Edge case workers with very high or low caseloads for notification delivery.']</t>
+          <t>['Notes for clients with a large number of entries.', 'Very long individual notes (multi-page).', 'Case with no notes.']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>['Notification and alerting system testing as used in story 2 (notification delivery, display, persistence, etc.)']</t>
+          <t>['Print UI and compatibility testing (overlaps with 22895826 - printing checklist).']</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>['22895826 - Changes in print functionality.', 'Shared printing service or template module.']</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>22895838</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['List all cases with overdue redeterminations and verify accuracy against database.', "Change a case's redetermination date to overdue and confirm it appears on the list.", 'Select a case and initiate follow-up actions, checking state transitions and recording.', 'Ensure overdue count is recalculated as cases are resolved or new overdue cases appear.', 'Check notifications or reminders sent for overdue cases.']</t>
+          <t>['Test inputting a duplicate Medicaid application and verify that the system triggers an alert.', 'Validate detection logic for variations in client names/IDs.', 'Check that alert allows the Case Worker to view/merge duplicates.', 'Ensure alert is not triggered for non-duplicate applications.', 'Confirm merge action results in a single, unified application.']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['Cases that become overdue during business logic execution (race conditions).', 'Very old or recently closed cases that should/should not appear.', 'Cases with missing/invalid redetermination dates.', 'Bulk transitions where many cases become overdue at once.']</t>
+          <t>['Near-duplicates (typos, transposed digits in SSN).', 'Concurrency: Multiple workers submitting overlapping applications at the same time.', 'Merging applications with conflicting data.']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>['Case listing, filter, and status update logic as seen in stories 6 and 7 (consistency of list/filter/action functionality).']</t>
+          <t>['Application intake and validation (shared with 22895808).']</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[6, 7]</t>
+          <t>['22895808 - Changes in intake could affect duplicate logic.', '22895816, 22895833 - Any workflow that relies on accurate unique application records.']</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>22895844</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Select a case and generate a printable summary of its notes.', 'Verify that all case notes are present and accurate in print view.', 'Check print formatting for readability and professional appearance.', 'Print to PDF/physical printer and confirm output fidelity.', 'Test accessibility of print function for different user roles.']</t>
+          <t>['Submit application with conflicting income data and verify alert is presented.', 'Ensure alert content is clear and directs worker actions.', 'Test alert persistence and resolution process.', 'Check system identifies and flags all standard income data discrepancies.', 'Ensure no alert for consistent, valid data.']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['Cases with no notes (empty summary).', 'Cases with extremely long, multi-page notes.', 'Notes containing special characters, non-English text, or attachments.', 'Concurrent changes to notes while printing.']</t>
+          <t>['Rapidly updated applications (income updated multiple times).', 'Clients with multiple sources of income.', 'Partial/incomplete income data resulting in ambiguous conflicts.']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Alert UI and workflow for Case Workers (if similar approaches used for 22895838).']</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22895834 - If income data definitions change.', '22895810 - If data ingestion logic changes.']</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>22895840</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['Verify that a case becomes eligible for inactivity alert after 60 days of no updates.', 'Confirm the alert is sent to the assigned Case Manager.', 'Check that alert includes relevant case history details.', 'Ensure the alert is not sent if there is activity within the 60-day window.', 'Check user interface for displaying inactivity alerts.']</t>
+          <t>['Verify that a case worker receives an alert when an eligibility rule is changed.', 'Verify the alert contains information about what rule was changed and when.', 'Test if the alert is not sent for unrelated rule changes.', 'Check notification delivery (in-app, email, SMS if supported).', 'Verify that multiple eligibility rule changes trigger the correct number of alerts.', 'Check that dismissing/acknowledging an alert marks it as read.']</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['Case updated 59 days ago—no alert should be sent.', 'Case updated at exactly the 60th day—alert should trigger.', 'A case with backdated activity that brings last activity within 60 days.', 'Multiple cases becoming inactive simultaneously.']</t>
+          <t>['Multiple eligibility rules changed simultaneously.', 'Eligibility rule changed and then reverted before alert delivery.', 'Case worker has notification settings disabled.', 'Old/inactive case worker accounts.']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>['Validate alert notification mechanism used in stories 6 and 7 (since related).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['Stories 6, 7 (other alert scenarios for Case Managers).', 'Any alert delivery or notification systems used for case alerts.']</t>
+          <t>['Alerts and notifications module.', 'Case assessment workflows depending on eligibility rules.']</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>22895819</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['Check detection of conflicting income data on client submission.', 'Verify alert is generated for the assigned Case Worker on valid conflict.', 'Confirm alert includes both previous and submitted income data.', 'Verify no alert is generated for non-conflicting submissions.', 'UI/UX confirmation of alert receipt by Case Worker.']</t>
+          <t>['Verify that a case worker can see the submission status of each required document per case.', 'Ensure the status updates immediately after a document is submitted.', 'Test filtering or sorting cases by document status.', 'Check that pending documents can be easily identified.', 'Verify that following up action can be triggered from status view.', 'Test notifications/reminders for pending items.']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['Multiple income entries submitted in quick succession with mixed conflicts.', "Edge of a threshold (e.g., $1 difference); system's conflict tolerance.", 'Duplicate income entries (identical values).', 'Income data submitted via different channels (e.g., web/phone).']</t>
+          <t>['Documents submitted partially (e.g., multiple required files for one item, only some uploaded).', 'Simultaneous updates by different users.', 'Large volume of pending documents.', 'Document submitted by error, then withdrawn.']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['Income data validation logic tests shared with story 3.']</t>
+          <t>['22895818: Any shared UI or API endpoints for document status.', '22895824: Interactions when document requirements change.', '22895846: Shared tracking or notification features for documents.']</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['Story 3 (income validation logic).', 'Alert delivery systems for Case Workers.']</t>
+          <t>['Document management and uploads.', 'Case overview/dashboard.', 'Notification/reminder system for documents.']</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>22895839</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['Verify that escalated cases are tracked in the dashboard.', 'Check metrics update in real time as new cases are escalated.', 'Verify counting logic: only actual escalations count toward metrics.', 'Confirm UI displays escalation trend over selected time period.', 'Test filtering/sorting by urgency in the dashboard.']</t>
+          <t>['Generate a monthly report for case activity and verify accuracy with raw data.', 'Confirm the report includes all relevant fields (e.g., case opened/closed, activity logs).', 'Check report formatting for readability and exports (e.g., PDF, CSV).', 'Test for correct team-based access and report visibility.', 'Verify filter options (e.g., by team member, date range).']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['No escalated cases—dashboard should show zero or appropriate message.', 'Large number of escalated cases for one or more periods.', 'Case status toggled from escalated to non-escalated and vice versa.']</t>
+          <t>['Month with zero activity.', 'Large volume of activity data.', 'Cases transferred between managers or teams during the reporting period.']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['Escalation status consistency tests with story 20.', 'Metric aggregation and dashboard rendering logic.']</t>
+          <t>['22895837: Verify report data consistency if activity log format changes.', '22895823: Consistency with other case activity reports.']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['Story 20 (escalation status tracking).', 'Dashboard/reporting features.']</t>
+          <t>['Reporting module.', 'Case activity logging functionalities.']</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>22895821</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['Verify that an alert is generated when a document is uploaded outside business hours.', 'Check that the alert is sent to the correct Case Worker.', 'Test configuring business hours and their impact on alert logic.', 'Ensure alerts are not generated for uploads during business hours.', 'UI displays after-hours upload alerts properly.']</t>
+          <t>['Verify that case managers can access and view all communication logs for a case.', 'Ensure sorting/filtering of logs by date, client, or type is correct.', 'Test visibility permissions (only authorized users can view certain logs).', 'Check if attachment and message contents are displayed correctly.', 'Confirm integration with other case history records.']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['Upload takes place exactly at the edge (start/end) of business hours.', 'Multiple uploads in rapid succession (bulk uploads) after hours.', 'Uploads by different clients to the same caseworker after hours.']</t>
+          <t>['Very large number of communications in a single case.', 'Corrupted or missing log entries.', 'Communication logs linked to merged/split cases.']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['Document upload detection logic with stories 8 and 17.', 'Alert notification mechanism.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['Stories 8, 17 (document upload feature and related alerts).', 'Alert delivery/notification systems.']</t>
+          <t>['Communication logging features.', 'Case history aggregation and display.']</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>22895833</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['Verify alert is generated when a Case Worker exceeds the workload threshold.', 'Alert is received by the Case Manager responsible for reassignment.', 'Test the calculation logic for workload (e.g., number and type of cases handled).', 'Check that reducing workload below threshold removes or resolves alert.', 'UI/UX for generating, viewing, and acting on overload alerts.']</t>
+          <t>['Verify that a case worker can select and pre-fill data from previous cases into a new application.', 'Check that only authorized/eligible data is pre-filled.', 'Test the ability to edit or override pre-filled fields.', 'Ensure proper loading and performance for large historical datasets.', 'Check error handling if previous case data is inconsistent or missing.']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['Workload exactly at the threshold (should not trigger alert).', 'Rapid changes in workload (cases assigned/closed in quick succession).', 'Simultaneous overloads across multiple caseworkers.']</t>
+          <t>['Previous case data contains invalid or outdated fields.', 'Multiple previous cases for the same client with conflicting information.', 'No previous cases available for pre-fill.']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['Workload calculation and threshold comparison logic with stories 10 and 18.', 'Alert notification routine.']</t>
+          <t>['22895829: Shared code/data fetching for historical records.', '22895838: Data transformation and mapping logic.']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['Stories 10, 18 (workload calculation and reassignment flows).', 'Alert and notification systems.']</t>
+          <t>['New case/application workflows.', 'Historical data management.', 'Data privacy and authorization.']</t>
         </is>
       </c>
     </row>

--- a/output_test_cases.xlsx
+++ b/output_test_cases.xlsx
@@ -431,1027 +431,1107 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>story_number</t>
+          <t>executive_summary</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>test_cases</t>
+          <t>user_story</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>edge_cases</t>
+          <t>happy_path_summary</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>shared_tests</t>
+          <t>scenario_table</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>regression_impact</t>
+          <t>detailed_test_cases</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>22895813</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>This user story enables Case Workers to receive alerts when there are conflicting household data entries, helping them efficiently resolve data discrepancies and ensure record accuracy.</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['Verify that the Case Manager can access the eligibility status view for assigned clients.', 'Verify the eligibility status is displayed accurately for each client (eligible, ineligible, pending).', 'Verify filtering/sorting of clients by eligibility status.', 'Verify the date/time of the eligibility status is shown (if present).', 'Verify that eligibility status updates are reflected in real-time or after refresh.', 'Verify proper access control so only the Case Manager can view his/her clients.']</t>
+          <t>22895834: As a Case Worker, I want to receive alerts for conflicting household data so that I can resolve discrepancies.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Clients with no eligibility assessment data.', 'Clients with multiple or conflicting eligibility statuses.', 'Rapid changes in eligibility (simultaneous updates).', 'Case Manager with a very large number of clients.']</t>
+          <t>When a conflict is detected in household data, the system triggers an alert to the assigned Case Worker, who reviews and resolves the discrepancy.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Test eligibility data rendering, as shared with 22895823 (report generation), 22895814, and 22895832.', 'Verify consistency between eligibility status view and summary report (22895823).']</t>
+          <t>[{'Test Case ID': 'TC_22895834_01', 'Brief Description': 'Verify Case Worker receives an alert when conflicting data is detected.'}, {'Test Case ID': 'TC_22895834_02', 'Brief Description': 'Verify alert is not generated if data is consistent.'}, {'Test Case ID': 'TC_22895834_03', 'Brief Description': 'Ensure that alerts are not sent to unauthorized users.'}, {'Test Case ID': 'TC_22895834_04', 'Brief Description': 'Check system logs record the alert for audit compliance.'}, {'Test Case ID': 'TC_22895834_05', 'Brief Description': 'Verify the Case Worker can resolve the discrepancy from the alert.'}, {'Test Case ID': 'TC_22895834_06', 'Brief Description': 'API: Validate alert creation when data conflict is submitted.'}, {'Test Case ID': 'TC_22895834_07', 'Brief Description': 'Negative: Alert is not sent if Case Worker’s permissions are revoked.'}]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['Eligibility data model (shared with 22895823, 22895832, 22895814, 22895841).', 'Case/Client access controls.']</t>
+          <t>[{'Test Case ID': 'TC_22895834_01', 'EPIC': 'Household Data Integrity', 'Feature': 'Conflict Alerting', 'User Story': '22895834', 'Business Process': 'Case Management', 'Sub-Process Title': 'Data Consistency Validation', 'Activity Title': 'Alert Notification', 'Test Scenario Title': 'Receive alert on data conflict', 'Precondition': 'Case Worker is assigned to at least one household; conflicting data is entered in the household records.', 'Test Data': 'Household A: Member1 SSN=1234, DOB=01/01/2000 in one source, DOB=02/02/2000 in another.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Ensure household data is present and consistent.', 'Simulate entry of conflicting data for a household member.', 'Wait for system to process conflict.', 'Check alert center or email/notification system for new alert.'], 'Expected Result': 'Case Worker is notified with a clear alert indicating the conflict details.', 'Dependent Module/Process': 'Data Validation Engine, Notification Service'}, {'Test Case ID': 'TC_22895834_02', 'EPIC': 'Household Data Integrity', 'Feature': 'Conflict Alerting', 'User Story': '22895834', 'Business Process': 'Case Management', 'Sub-Process Title': 'Data Consistency Validation', 'Activity Title': 'Alert Notification', 'Test Scenario Title': 'No alert when data is consistent', 'Precondition': 'Consistent household data present.', 'Test Data': 'Household B: Member1 SSN=5678, DOB=03/03/2000 in all sources.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Validate household data consistency.', 'Observe alert center or notification system.'], 'Expected Result': 'No alert is received by the Case Worker.', 'Dependent Module/Process': 'Data Validation Engine'}, {'Test Case ID': 'TC_22895834_03', 'EPIC': 'Household Data Integrity', 'Feature': 'Conflict Alerting', 'User Story': '22895834', 'Business Process': 'Case Management', 'Sub-Process Title': 'Data Consistency Validation', 'Activity Title': 'Alert Notification', 'Test Scenario Title': 'Unauthorized user should not receive alert', 'Precondition': "Conflicting data present; user role does not have 'Case Worker' permissions.", 'Test Data': "Same as TC_22895834_01, but login as 'Guest' or another role.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest', 'Detailed Test Steps': ['Log in as non-Case Worker user.', 'Check for alerts regarding household conflicts.'], 'Expected Result': 'No alert is presented to unauthorized users.', 'Dependent Module/Process': 'User Role Management, Notification Service'}, {'Test Case ID': 'TC_22895834_04', 'EPIC': 'Audit / Compliance', 'Feature': 'Alert Logging', 'User Story': '22895834', 'Business Process': 'Case Management', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Alert Event Logging', 'Test Scenario Title': 'Alert event is logged for audit', 'Precondition': 'Alert for conflict is triggered.', 'Test Data': 'From TC_22895834_01', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger a conflict alert as in positive test.', 'Access system log with audit permissions.', 'Search for alert event log.'], 'Expected Result': 'Alert event is recorded with timestamp, case worker ID, and details of the conflict.', 'Dependent Module/Process': 'Audit Trail / Logging Module'}, {'Test Case ID': 'TC_22895834_05', 'EPIC': 'Household Data Integrity', 'Feature': 'Conflict Resolution', 'User Story': '22895834', 'Business Process': 'Case Management', 'Sub-Process Title': 'Conflict Resolution', 'Activity Title': 'Alert Handling', 'Test Scenario Title': 'Case Worker resolves discrepancy from alert', 'Precondition': 'Alert for household data conflict active in system.', 'Test Data': 'Household with conflicting member DOBs.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Navigate to alerts.', 'Open conflict alert.', 'Follow system workflow to resolve conflict (choose correct data/source, enter notes, mark as resolved).'], 'Expected Result': 'Discrepancy is resolved, alert is cleared, resolution is logged for audit.', 'Dependent Module/Process': 'Case Management UI, Audit Log'}, {'Test Case ID': 'TC_22895834_06', 'EPIC': 'Household Data Integrity', 'Feature': 'API - Alerting', 'User Story': '22895834', 'Business Process': 'API Integration', 'Sub-Process Title': 'Conflict Detection API', 'Activity Title': 'Alert API Response', 'Test Scenario Title': 'Alert generated when conflict via API', 'Precondition': 'API endpoint to submit household data is accessible.', 'Test Data': 'POST data with conflicting household member fields.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System Integration', 'Detailed Test Steps': ['Call POST /household-data with conflicting data.', "Check API response for 'conflict detected' flag.", 'Query notifications of Case Worker via API.'], 'Expected Result': 'API response confirms alert; alert exists in Case Worker inbox.', 'Dependent Module/Process': 'Notification API'}, {'Test Case ID': 'TC_22895834_07', 'EPIC': 'Security / Permissions', 'Feature': 'Alerting', 'User Story': '22895834', 'Business Process': 'User Management', 'Sub-Process Title': 'Role Permission Check', 'Activity Title': 'Alert Suppression', 'Test Scenario Title': 'Alert not sent if permissions revoked', 'Precondition': 'Case Worker’s alert permission has been revoked.', 'Test Data': 'Trigger household data conflict.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (permission revoked)', 'Detailed Test Steps': ['Revoke alert permission for Case Worker.', 'Trigger a data conflict.', 'Check for alert in notification center.'], 'Expected Result': 'No alert is delivered; event is logged for compliance.', 'Dependent Module/Process': 'User Management, Notification Service'}]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>22895831</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Workers are promptly notified when clients upload documents after official business hours, facilitating workload management and timely review.</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['Verify that the Case Worker can select multiple cases for document upload.', 'Verify that multiple document files can be selected and are associated with the correct cases.', 'Verify progress/status indicator during bulk upload.', 'Verify successful upload displays confirmation.', 'Verify failed uploads display error information per case/file.', 'Verify uploaded documents are retrievable under the correct cases.']</t>
+          <t>22895846: As a Case Worker, I want to receive alerts when a client uploads a document after business hours so that I can prioritize review.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['Uploading documents with invalid file types.', 'Uploading more documents/files than allowed limit.', 'Files with duplicate names across different cases.', 'Case is locked or not found during upload.', 'Network failure during bulk upload.']</t>
+          <t>If a document is uploaded after business hours, the assigned Case Worker receives an alert including the client, document type, and timestamp.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['File upload validation and association with cases (shared with 22895836: document preview before upload).']</t>
+          <t>[{'Test Case ID': 'TC_22895846_01', 'Brief Description': 'Verify alert is sent to Case Worker when document is uploaded after business hours.'}, {'Test Case ID': 'TC_22895846_02', 'Brief Description': 'No alert is sent for uploads during business hours.'}, {'Test Case ID': 'TC_22895846_03', 'Brief Description': 'Compliance: Ensure alert event is logged.'}, {'Test Case ID': 'TC_22895846_04', 'Brief Description': 'Negative: Alert is not sent if permissions are missing.'}, {'Test Case ID': 'TC_22895846_05', 'Brief Description': 'API: Alert creation on after-hours document upload via API.'}]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['Document management and storage components (shared with 22895836, 22895828, 22895815).', "Cases' document association logic."]</t>
+          <t>[{'Test Case ID': 'TC_22895846_01', 'EPIC': 'Document Management', 'Feature': 'After-hours Alerting', 'User Story': '22895846', 'Business Process': 'Case Management', 'Sub-Process Title': 'Document Uploads', 'Activity Title': 'After-hours Notification', 'Test Scenario Title': 'Receive alert for after-hours upload', 'Precondition': 'Document upload feature is enabled; Case Worker is assigned to client.', 'Test Data': 'Client ID: 1001, Upload Time: 8:30PM, Document: Proof of Income.pdf', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as client.', 'Upload a document after 5PM local time.', 'Case Worker checks for new notifications.'], 'Expected Result': 'Case Worker receives alert with client, document, and timestamp details.', 'Dependent Module/Process': 'Document Upload, Notification Service'}, {'Test Case ID': 'TC_22895846_02', 'EPIC': 'Document Management', 'Feature': 'After-hours Alerting', 'User Story': '22895846', 'Business Process': 'Case Management', 'Sub-Process Title': 'Document Uploads', 'Activity Title': 'Within Business Hours', 'Test Scenario Title': 'No alert for uploads during business hours', 'Precondition': 'Standard business hours are configured (e.g., 9AM-5PM).', 'Test Data': 'Upload at 10:00AM.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as client.', 'Upload a document at 10:00AM.', 'Case Worker checks alert center.'], 'Expected Result': 'No after-hours alert is received.', 'Dependent Module/Process': 'Notification Logic'}, {'Test Case ID': 'TC_22895846_03', 'EPIC': 'Audit / Compliance', 'Feature': 'Alert Logging', 'User Story': '22895846', 'Business Process': 'Case Management', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'After-hours Event Logging', 'Test Scenario Title': 'Audit log records after-hours alert event', 'Precondition': 'After-hours upload and alert generated.', 'Test Data': 'From TC_22895846_01', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload document after hours.', 'Check audit log as auditor or admin.', 'Search for alert event.'], 'Expected Result': 'Audit log records alert with timestamp and Case Worker/Client IDs.', 'Dependent Module/Process': 'Audit Trail'}, {'Test Case ID': 'TC_22895846_04', 'EPIC': 'Security / Permissions', 'Feature': 'Alert Permissions', 'User Story': '22895846', 'Business Process': 'User Management', 'Sub-Process Title': 'Permission Check', 'Activity Title': 'Alert Suppression', 'Test Scenario Title': 'Alert not sent without permissions', 'Precondition': 'Case Worker’s alert permission is revoked.', 'Test Data': 'Document upload after hours.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker (permissions revoked)', 'Detailed Test Steps': ['Revoke after-hours alert permissions.', 'Client uploads a document after hours.', 'Case Worker checks alert center.'], 'Expected Result': 'No alert is received by Case Worker.', 'Dependent Module/Process': 'User Management, Notification Service'}, {'Test Case ID': 'TC_22895846_05', 'EPIC': 'Document Management', 'Feature': 'API Integration', 'User Story': '22895846', 'Business Process': 'API Integration', 'Sub-Process Title': 'Document Upload API', 'Activity Title': 'API-triggered Alerts', 'Test Scenario Title': 'API triggers after-hours alert', 'Precondition': 'API enabled for uploads.', 'Test Data': 'POST /documents/upload with UploadTime=8:45PM', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System/Case Worker', 'Detailed Test Steps': ['Call document upload API with after-hours timestamp.', 'Query Case Worker notifications via API.', 'Validate receipt of alert.'], 'Expected Result': 'Alert generated and retrievable via API.', 'Dependent Module/Process': 'Document Upload API, Notification API'}]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>22895823</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Case Workers are proactively informed about missing fields in applications, allowing them to quickly complete and process applications with system-driven suggestions.</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['Verify Case Worker can generate summary report for selected cases/clients.', 'Verify report includes accurate eligibility findings for all selected clients.', 'Verify report format (fields, layout) matches requirements.', 'Verify report export/download (PDF, Excel, etc.) is available.', 'Verify permission checks on report generation.']</t>
+          <t>22895829: As a Case Worker, I want to receive suggestions for missing fields in applications so that I can complete them faster.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['Generating a report for clients with no eligibility data.', 'Huge number of clients in report.', 'Eligibility data updates during/after report is running.']</t>
+          <t>System scans application, identifies missing mandatory fields, and notifies Case Worker with suggestions and instructions to complete the application.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['Test eligibility data integrity and consistency (shared with 22895813, 22895832).', 'Test report export/download process.']</t>
+          <t>[{'Test Case ID': 'TC_22895829_01', 'Brief Description': 'Verify suggestion is shown when fields are missing.'}, {'Test Case ID': 'TC_22895829_02', 'Brief Description': 'No suggestions shown if application is complete.'}, {'Test Case ID': 'TC_22895829_03', 'Brief Description': 'Suggestions are provided only to authorized Case Workers.'}, {'Test Case ID': 'TC_22895829_04', 'Brief Description': 'API: System flags missing fields on submission.'}, {'Test Case ID': 'TC_22895829_05', 'Brief Description': 'Negative: Suggestions not visible due to permission issue.'}]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['Eligibility calculation logic (shared with 22895813, 22895832, 22895839).', 'Eligibility summary report features.']</t>
+          <t>[{'Test Case ID': 'TC_22895829_01', 'EPIC': 'Application Processing', 'Feature': 'Field Suggestion Engine', 'User Story': '22895829', 'Business Process': 'Application Review', 'Sub-Process Title': 'Field Completeness Check', 'Activity Title': 'Suggestion Notification', 'Test Scenario Title': 'Missing field suggestions are displayed', 'Precondition': 'Incomplete application exists; Case Worker logged in.', 'Test Data': "Application: missing 'phone number', 'income'.", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Open incomplete application.', 'Observe suggestions/recommendations panel.'], 'Expected Result': 'Suggestions show required missing fields and hints to complete.', 'Dependent Module/Process': 'Field Validation Engine'}, {'Test Case ID': 'TC_22895829_02', 'EPIC': 'Application Processing', 'Feature': 'Validation Feedback', 'User Story': '22895829', 'Business Process': 'Application Review', 'Sub-Process Title': 'Completeness Verification', 'Activity Title': 'Suggestion Suppression', 'Test Scenario Title': 'No suggestions when application is complete', 'Precondition': 'All required fields present.', 'Test Data': 'Application: All mandatory fields filled.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open fully completed application.', 'Look for suggestions panel.', 'Submit application.'], 'Expected Result': 'No missing field suggestions are displayed.', 'Dependent Module/Process': 'Field Validation Engine'}, {'Test Case ID': 'TC_22895829_03', 'EPIC': 'Application Processing', 'Feature': 'Permissions', 'User Story': '22895829', 'Business Process': 'User Management', 'Sub-Process Title': 'Role Permissions', 'Activity Title': 'Suggestion Notification', 'Test Scenario Title': 'Only authorized Case Workers see suggestions', 'Precondition': 'Case Worker role enabled; compare with unauthorized user.', 'Test Data': 'Incomplete application.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker, Guest', 'Detailed Test Steps': ['Log in as Case Worker: verify suggestions shown.', 'Log in as Guest: verify no suggestions shown.'], 'Expected Result': 'Suggestions appear only for Case Workers.', 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'TC_22895829_04', 'EPIC': 'Application Processing', 'Feature': 'API Submission', 'User Story': '22895829', 'Business Process': 'API Integration', 'Sub-Process Title': 'Application API', 'Activity Title': 'Field Suggestion API Response', 'Test Scenario Title': 'API flags missing fields on submit', 'Precondition': 'API endpoint available; incomplete application submitted.', 'Test Data': 'POST with omitted fields.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System / Case Worker', 'Detailed Test Steps': ['Call API to submit an incomplete application.', 'Check API response for missing fields suggestions.', 'Log in as Case Worker and verify UI suggestions.'], 'Expected Result': 'API returns list of missing fields with hints.', 'Dependent Module/Process': 'Application API, Field Validation Engine'}, {'Test Case ID': 'TC_22895829_05', 'EPIC': 'Security / Permissions', 'Feature': 'Suggestion Visibility', 'User Story': '22895829', 'Business Process': 'User Management', 'Sub-Process Title': 'Permissions Check', 'Activity Title': 'Suggestion Suppression', 'Test Scenario Title': 'Suggestions not visible to unauthorized user', 'Precondition': 'User role does not have permission for suggestions.', 'Test Data': 'Incomplete application.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest / Other', 'Detailed Test Steps': ['Login as user without suggestion permission.', 'Open incomplete application.', 'Look for suggestion panel.'], 'Expected Result': 'No suggestions appear; event is logged for compliance.', 'Dependent Module/Process': 'User Role Management, Audit Log'}]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>22895836</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>This user story allows Case Workers to search for existing applicants using name or SSN, reducing the risk of duplicate entries and promoting clean data practices.</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Verify that Case Worker can initiate document preview before upload.', 'Verify correct rendering of supported file types (PDF, images, docs).', 'Verify error message upon trying to preview unsupported/corrupted files.', 'Verify preview matches the actual document content.', 'Verify ability to cancel upload after preview.']</t>
+          <t>22895816: As a Case Worker, I want to search for existing applicants by name or SSN so that I can avoid duplicate entries.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['Attempting preview of large files or files with unsupported formats.', 'Previewing files with malware or embedded scripts.', 'Multiple previews in quick succession.']</t>
+          <t>Case Worker enters applicant’s name or SSN, system displays matching applicants to prevent duplicates.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['File type/size validation logic (shared with 22895831, 22895828, 22895815).']</t>
+          <t>[{'Test Case ID': 'TC_22895816_01', 'Brief Description': 'Search returns matching applicants by name.'}, {'Test Case ID': 'TC_22895816_02', 'Brief Description': 'Search returns matching applicants by SSN.'}, {'Test Case ID': 'TC_22895816_03', 'Brief Description': 'No results returned when applicant does not exist.'}, {'Test Case ID': 'TC_22895816_04', 'Brief Description': 'Negative: Search by SSN returns error for unauthorized users.'}, {'Test Case ID': 'TC_22895816_05', 'Brief Description': 'API: Search endpoint returns correct response for name or SSN.'}, {'Test Case ID': 'TC_22895816_06', 'Brief Description': 'Compliance: All search queries are logged for audit.'}]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['Document upload component (shared with 22895831, 22895828, 22895815).', 'Preview rendering component.']</t>
+          <t>[{'Test Case ID': 'TC_22895816_01', 'EPIC': 'Applicant Management', 'Feature': 'Applicant Search', 'User Story': '22895816', 'Business Process': 'Applicant Search', 'Sub-Process Title': 'By Name', 'Activity Title': 'Name-based Search', 'Test Scenario Title': 'Search applicants by name', 'Precondition': 'Applications exist in system; Case Worker logged in.', 'Test Data': "Search term: 'Jane Doe'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Go to applicant search screen.', "Enter 'Jane Doe' in search box.", 'Click search.'], 'Expected Result': "List of all applicants named 'Jane Doe' is displayed.", 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_22895816_02', 'EPIC': 'Applicant Management', 'Feature': 'Applicant Search', 'User Story': '22895816', 'Business Process': 'Applicant Search', 'Sub-Process Title': 'By SSN', 'Activity Title': 'SSN-based Search', 'Test Scenario Title': 'Search applicants by SSN', 'Precondition': "Applicant with SSN '123-45-6789' exists.", 'Test Data': "Search term: '123-45-6789'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', "Enter SSN '123-45-6789' in search box.", 'Click search.'], 'Expected Result': 'Single matching applicant is shown.', 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_22895816_03', 'EPIC': 'Applicant Management', 'Feature': 'Applicant Search', 'User Story': '22895816', 'Business Process': 'Applicant Search', 'Sub-Process Title': 'No Results', 'Activity Title': 'Negative Name/SSN Search', 'Test Scenario Title': 'No applicant found for non-existent criteria', 'Precondition': "No applicant with name 'John Xyz' or SSN '999-99-9999'.", 'Test Data': "Search terms: 'John Xyz', '999-99-9999'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', "Enter 'John Xyz' in search.", 'Click search.', "Repeat with SSN '999-99-9999'."], 'Expected Result': 'Search results indicate no matches found.', 'Dependent Module/Process': 'Applicant Database'}, {'Test Case ID': 'TC_22895816_04', 'EPIC': 'Security / Compliance', 'Feature': 'Search Permissions', 'User Story': '22895816', 'Business Process': 'User Management', 'Sub-Process Title': 'Permissions Check', 'Activity Title': 'SSN Search Restriction', 'Test Scenario Title': 'SSN search by unauthorized user fails', 'Precondition': 'User logged in without permission for SSN search.', 'Test Data': "Search term: '123-45-6789'", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest', 'Detailed Test Steps': ['Log in as user without SSN search access.', 'Attempt to search by SSN.', 'Observe result.'], 'Expected Result': 'Search fails with error or permission denied.', 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'TC_22895816_05', 'EPIC': 'Applicant Management', 'Feature': 'API Search', 'User Story': '22895816', 'Business Process': 'API Integration', 'Sub-Process Title': 'Applicant API', 'Activity Title': 'API-based Search', 'Test Scenario Title': 'API returns matching results by name/SSN', 'Precondition': 'API endpoint available.', 'Test Data': 'GET /applicants?name=Jane+Doe or SSN=123-45-6789', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System / Case Worker', 'Detailed Test Steps': ['Call GET /applicants?name=Jane+Doe.', 'Check for correct response.', 'Call GET /applicants?ssn=123-45-6789.', 'Check for correct response.'], 'Expected Result': 'API response matches search logic in UI.', 'Dependent Module/Process': 'Applicant API'}, {'Test Case ID': 'TC_22895816_06', 'EPIC': 'Compliance / Audit', 'Feature': 'Search Logging', 'User Story': '22895816', 'Business Process': 'Applicant Search', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Search Event Logging', 'Test Scenario Title': 'Search queries are logged for compliance', 'Precondition': 'Any search performed (UI or API).', 'Test Data': 'Any search query.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor', 'Detailed Test Steps': ['Perform search as Case Worker.', 'Log in as Auditor.', 'Check search event logs.', 'Verify search term, user, timestamp logged.'], 'Expected Result': 'All search terms and access details captured in audit logs.', 'Dependent Module/Process': 'Audit Trail'}]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>22895834</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cases are assigned by Case Managers based on clients’ language preferences, improving service by matching clients with linguistically capable workers.</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Verify Case Worker is notified when household data is conflicting.', 'Verify conflicting fields (e.g., addresses, relationships) are clearly highlighted.', 'Verify alert message is clear and actionable.', 'Verify notifications trigger only for actual conflicts.', 'Verify resolution instructions or links are provided.']</t>
+          <t>22895835: As a Case Manager, I want to assign cases based on language preference so that clients receive better service.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['Multiple conflicts in a single household.', 'Rapid updates causing intermittent or resolved conflicts.', 'Edge case where conflict is due to data from external system.']</t>
+          <t>Case Manager assigns a case to a Case Worker with matching language skills as per the client’s preference.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['Testing notification/alert mechanism (shared with related stories 22895811, 22895844, 22895816 as per notification pattern).']</t>
+          <t>[{'Test Case ID': 'TC_22895835_01', 'Brief Description': 'Assign case to Case Worker with matching language.'}, {'Test Case ID': 'TC_22895835_02', 'Brief Description': 'Warning shown if no workers available for language.'}, {'Test Case ID': 'TC_22895835_03', 'Brief Description': 'Compliance: Assignment event is logged for audit.'}, {'Test Case ID': 'TC_22895835_04', 'Brief Description': 'Negative: Assignment fails if Case Manager lacks permission.'}, {'Test Case ID': 'TC_22895835_05', 'Brief Description': 'API: Assign via integration; ensure language is respected.'}]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['Household data model and validation rules.', 'Notification/alert infrastructure affecting related stories.']</t>
+          <t>[{'Test Case ID': 'TC_22895835_01', 'EPIC': 'Case Assignment', 'Feature': 'Language-based Assignment', 'User Story': '22895835', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Assignment', 'Activity Title': 'Assign Case', 'Test Scenario Title': 'Assign based on language preference', 'Precondition': 'Case Manager logged in; list of Case Workers with languages known.', 'Test Data': 'Client: prefers Spanish, Worker A: English; Worker B: Spanish.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Open unassigned case for client preferring Spanish.', "Choose 'assign' option.", 'Select worker with Spanish skills.', 'Confirm assignment.'], 'Expected Result': 'Case assigned to worker with matching language; both parties notified.', 'Dependent Module/Process': 'Case Assignment Engine'}, {'Test Case ID': 'TC_22895835_02', 'EPIC': 'Case Assignment', 'Feature': 'Language Matching', 'User Story': '22895835', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Assignment', 'Activity Title': 'No Available Worker', 'Test Scenario Title': 'Warning if no workers for client language', 'Precondition': 'No Case Workers available for specified language.', 'Test Data': 'Client prefers Mandarin; no workers have Mandarin.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Open case with Mandarin preference.', 'Try to assign.', 'Observe UI feedback.'], 'Expected Result': 'System warns that no workers available for client’s language.', 'Dependent Module/Process': 'Case Assignment Engine'}, {'Test Case ID': 'TC_22895835_03', 'EPIC': 'Audit / Compliance', 'Feature': 'Assignment Logging', 'User Story': '22895835', 'Business Process': 'Case Management', 'Sub-Process Title': 'Audit Logging', 'Activity Title': 'Assignment Event Logging', 'Test Scenario Title': 'Assignment events are logged for audit', 'Precondition': 'Case assignment performed.', 'Test Data': 'Any assignment event.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor', 'Detailed Test Steps': ['Perform assignment as Case Manager.', 'Log in as Auditor.', 'Check audit logs for assignment event.', 'Verify language, case, and user captured.'], 'Expected Result': 'All assignment details captured in audit logs for traceability.', 'Dependent Module/Process': 'Audit Trail'}, {'Test Case ID': 'TC_22895835_04', 'EPIC': 'Security / Permissions', 'Feature': 'Assignment Permissions', 'User Story': '22895835', 'Business Process': 'User Management', 'Sub-Process Title': 'Permission Checks', 'Activity Title': 'Assignment Restriction', 'Test Scenario Title': 'Assignment fails without permission', 'Precondition': 'Case Manager permissions revoked.', 'Test Data': 'Attempted assignment.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager (permissions revoked)', 'Detailed Test Steps': ['Remove assignment privileges.', 'Attempt assignment of case.', 'Observe system response.'], 'Expected Result': 'Assignment cannot be completed; error message displayed.', 'Dependent Module/Process': 'User Role Management'}, {'Test Case ID': 'TC_22895835_05', 'EPIC': 'Case Assignment', 'Feature': 'API Integration', 'User Story': '22895835', 'Business Process': 'API Integration', 'Sub-Process Title': 'Assignment API', 'Activity Title': 'API-based Assignment', 'Test Scenario Title': 'API assigns case using language', 'Precondition': 'Assignment API enabled.', 'Test Data': "POST /cases/assign { caseId, workerId, language: 'Spanish' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System / Case Manager', 'Detailed Test Steps': ['Call /cases/assign API with language preference.', 'Check assignment in system.', 'Query assigned worker details.', 'Check notifications.'], 'Expected Result': 'API assigns case only to suitable worker; system and notification reflect assignment.', 'Dependent Module/Process': 'Assignment API'}]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>22895846</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>This user story focuses on enabling Case Managers to escalate urgent cases to supervisors, ensuring immediate visibility and attention for high-priority issues. The test coverage will validate the escalation mechanism, role-based permissions, notification capabilities, integration points, and audit trail/compliance requirements.</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Verify that an alert is sent to the case worker when a client uploads a document after business hours.', 'Check that the alert includes client, document, and timestamp information.', 'Ensure an alert is NOT sent if a document is uploaded during business hours.', 'Validate the business hours definition (e.g., 9am-5pm configurable).', 'Review alert delivery mechanisms (email, dashboard, etc.).']</t>
+          <t>22895827: As a Case Manager, I want to escalate urgent cases to supervisors so that they receive immediate attention.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['Document uploaded at exactly the start or end of business hours.', 'Case worker divided across multiple time zones.', 'Multiple documents uploaded in quick succession after hours.', 'Document upload crosses business hours threshold (e.g., starts upload before, finishes after hours).']</t>
+          <t>Case Manager selects an urgent case and successfully escalates it via the application; the supervisor is immediately notified, and the case status is updated.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['Check that alerts are triggered for document upload (shared with 22895824).', 'Test alert notifications for clients uploading documents during or after business hours.']</t>
+          <t>[{'Test Case ID': 'TC_CM_ESCALATE_001', 'Brief Description': 'Escalate an urgent case as Case Manager – successful path'}, {'Test Case ID': 'TC_CM_ESCALATE_002', 'Brief Description': 'Case Manager attempts to escalate a non-urgent case – system blocks action'}, {'Test Case ID': 'TC_CM_ESCALATE_003', 'Brief Description': 'Supervisor receives escalation alert/notification'}, {'Test Case ID': 'TC_CM_ESCALATE_004', 'Brief Description': 'Audit log records escalation action'}, {'Test Case ID': 'TC_CM_ESCALATE_005', 'Brief Description': 'User without Case Manager role tries to escalate – action unauthorized'}, {'Test Case ID': 'TC_CM_ESCALATE_006', 'Brief Description': 'Integration: Escalated case updates are reflected in Supervisor’s queue'}]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['22895824: Document upload alerting.', 'Any notification infrastructure (e.g., alert delivery used in other features).']</t>
+          <t>[{'Test Case ID': 'TC_CM_ESCALATE_001', 'EPIC': 'Urgent Case Management', 'Feature': 'Case Escalation', 'User Story': '22895827', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation', 'Activity Title': 'Escalate Urgent Case', 'Test Scenario Title': 'Case Manager successfully escalates urgent case', 'Precondition': "Case exists and is marked as 'urgent'. Case Manager has appropriate permissions.", 'Test Data': 'Case ID: C12345, Urgency: Urgent', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to the urgent case with ID C12345', "Select 'Escalate to Supervisor' action", 'Confirm the escalation'], 'Expected Result': "Case is updated to 'Escalated'; Supervisor is notified; audit log reflects the action.", 'Dependent Module/Process': 'Notification, Audit Logging, Supervisor Dashboard'}, {'Test Case ID': 'TC_CM_ESCALATE_002', 'EPIC': 'Urgent Case Management', 'Feature': 'Case Escalation', 'User Story': '22895827', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation', 'Activity Title': 'Block Escalation for Non-urgent Case', 'Test Scenario Title': 'System blocks attempt to escalate non-urgent case', 'Precondition': "Case exists and is not marked 'urgent'.", 'Test Data': 'Case ID: C54321, Urgency: Routine', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to the routine case with ID C54321', 'Attempt to escalate to supervisor'], 'Expected Result': 'System blocks action; error message displayed.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'TC_CM_ESCALATE_003', 'EPIC': 'Urgent Case Management', 'Feature': 'Case Escalation', 'User Story': '22895827', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation Notification', 'Activity Title': 'Send Notification to Supervisor', 'Test Scenario Title': 'Supervisor receives escalation alert', 'Precondition': 'Case escalated by Case Manager.', 'Test Data': 'Escalated Case ID: C12345', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Login as Supervisor', 'Check notifications/alerts queue'], 'Expected Result': 'Escalation alert received with case details.', 'Dependent Module/Process': 'Notification'}, {'Test Case ID': 'TC_CM_ESCALATE_004', 'EPIC': 'Urgent Case Management', 'Feature': 'Case Escalation Audit', 'User Story': '22895827', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalation Audit Log', 'Activity Title': 'Record Escalation', 'Test Scenario Title': 'Audit log is updated when case is escalated', 'Precondition': 'Case escalated to supervisor.', 'Test Data': 'Escalated Case ID: C12345', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor/System Admin', 'Detailed Test Steps': ['Query audit logs for action on Case ID C12345'], 'Expected Result': "Audit log shows timestamped entry: 'Case escalated to supervisor' with user details.", 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC_CM_ESCALATE_005', 'EPIC': 'Urgent Case Management', 'Feature': 'Case Escalation', 'User Story': '22895827', 'Business Process': 'Case Management', 'Sub-Process Title': 'Permission Validation', 'Activity Title': 'Validate Escalation Action', 'Test Scenario Title': 'User without Case Manager role tries to escalate', 'Precondition': "User role is not 'Case Manager'.", 'Test Data': 'Case ID: C12345', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Standard User/Clerk', 'Detailed Test Steps': ['Login as Standard User', 'Navigate to urgent case', 'Attempt to escalate case'], 'Expected Result': 'Escalate action not available or action blocked with an error.', 'Dependent Module/Process': 'Role/Permission Control'}, {'Test Case ID': 'TC_CM_ESCALATE_006', 'EPIC': 'Urgent Case Management', 'Feature': 'Supervisor Integration', 'User Story': '22895827', 'Business Process': 'Case Management', 'Sub-Process Title': 'Escalated Cases View', 'Activity Title': 'Integration of Escalated Case', 'Test Scenario Title': 'Escalated case appears in Supervisor’s queue', 'Precondition': 'Case has been escalated.', 'Test Data': 'Case ID: C12345', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Supervisor', 'Detailed Test Steps': ['Login as Supervisor', 'Open Escalated Cases queue', 'Verify presence of Case ID C12345'], 'Expected Result': 'Case appears in Supervisor’s escalated cases list.', 'Dependent Module/Process': 'Supervisor Dashboard'}]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>22895824</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>This story requires that Case Managers are alerted when a case has been inactive for 60 days, enabling timely follow-up and preventing lapses. Tests will confirm alert logic, user interface behavior, role-based notifications, and compliance with periodic review policies.</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['Verify that an alert is sent to a case worker whenever a client uploads a document.', 'Check the alert contains correct document, client, and timestamp details.', 'Ensure alerts are sent regardless of business hours.', 'Validate the system handles simultaneous uploads by multiple clients.']</t>
+          <t>22895843: As a Case Manager, I want to receive alerts when a case is inactive for 60 days so that I can follow up.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['Document uploaded by two clients at nearly the same time.', 'Upload fails halfway—no alert should be sent.', 'Document metadata is incomplete.']</t>
+          <t>Case remains inactive for 60 days; Case Manager receives and views alert, takes follow-up action.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['Validate alert notification format and delivery (shared with 22895846).', 'Test alert batching/deduplication logic (if any).']</t>
+          <t>[{'Test Case ID': 'TC_CM_ALERT_001', 'Brief Description': 'Case Manager receives alert after 60 days of inactivity'}, {'Test Case ID': 'TC_CM_ALERT_002', 'Brief Description': 'No alert generated for case with activity before 60 days'}, {'Test Case ID': 'TC_CM_ALERT_003', 'Brief Description': 'Case Manager clicks alert and is taken to the relevant case'}, {'Test Case ID': 'TC_CM_ALERT_004', 'Brief Description': 'Non-Case Manager does not receive alert'}]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['22895846: After-hours alerting.', 'Notification systems used across application.']</t>
+          <t>[{'Test Case ID': 'TC_CM_ALERT_001', 'EPIC': 'Case Follow-up and Alerts', 'Feature': 'Inactivity Alerting', 'User Story': '22895843', 'Business Process': 'Case Management', 'Sub-Process Title': 'Inactivity Monitoring', 'Activity Title': 'Generate Alert for Inactive Case', 'Test Scenario Title': 'Alert generated for case inactive 60 days', 'Precondition': 'Case has had no updates for 60 days.', 'Test Data': 'Case ID: C88777, Last Updated: 60+ days ago', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Ensure there is an inactive case (C88777) with last update 60+ days ago', 'Check notification or alert section'], 'Expected Result': 'Alert for inactivity is displayed with case details.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'TC_CM_ALERT_002', 'EPIC': 'Case Follow-up and Alerts', 'Feature': 'Inactivity Alerting', 'User Story': '22895843', 'Business Process': 'Case Management', 'Sub-Process Title': 'Inactivity Monitoring', 'Activity Title': 'Do not Alert for Active Case', 'Test Scenario Title': 'No alert generated for cases with recent activity', 'Precondition': 'Case updated within last 60 days.', 'Test Data': 'Case ID: C55443, Last Updated: 14 days ago', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Check alert section for Case ID: C55443'], 'Expected Result': 'No inactivity alert is displayed.', 'Dependent Module/Process': 'Notification Engine'}, {'Test Case ID': 'TC_CM_ALERT_003', 'EPIC': 'Case Follow-up and Alerts', 'Feature': 'Inactivity Alerting', 'User Story': '22895843', 'Business Process': 'Case Management', 'Sub-Process Title': 'Alert Navigation', 'Activity Title': 'Follow Up from Alert', 'Test Scenario Title': 'Case Manager clicks alert to access inactive case', 'Precondition': 'Inactivity alert present.', 'Test Data': 'Case ID: C88777', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'View alert for Case ID: C88777', 'Click on the alert'], 'Expected Result': 'User is taken to detailed view of that case.', 'Dependent Module/Process': 'Case Management UI'}, {'Test Case ID': 'TC_CM_ALERT_004', 'EPIC': 'Case Follow-up and Alerts', 'Feature': 'Inactivity Alerting', 'User Story': '22895843', 'Business Process': 'Case Management', 'Sub-Process Title': 'Role Permissions', 'Activity Title': 'Restrict Alert Visibility', 'Test Scenario Title': 'Non-Case Manager does not see inactivity alert', 'Precondition': 'Inactive case exists. User is not a Case Manager.', 'Test Data': 'Case ID: C88777', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Clerk or Supervisor', 'Detailed Test Steps': ['Login as Clerk/Supervisor', 'Check alerts/notifications'], 'Expected Result': 'No inactivity alert for case is visible.', 'Dependent Module/Process': 'Role Permissions'}]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>22895829</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Managers can track overdue redeterminations, thus maintaining compliance with policy deadlines. Test cases will validate overdue tracking mechanisms, UI updates, role access, reporting, and audit trail for regulatory compliance.</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['Verify that missing required fields in an application are detected.', 'Check that suggestions for completing missing fields are accurate and actionable.', 'Validate that case workers can access and apply suggestions easily.', 'Ensure suggestions do not expose sensitive information.']</t>
+          <t>22895841: As a Case Manager, I want to track overdue redeterminations so that I can ensure compliance.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['Applications with all fields completed—no suggestion shown.', 'Application missing multiple required fields.', 'Unrecognized or unexpected application fields.']</t>
+          <t>Case Manager sees list of clients with overdue redeterminations and views detailed compliance status per client.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['Suggestion mechanism for data input (potentially shared with 22895812, 22895833).']</t>
+          <t>[{'Test Case ID': 'TC_CM_OVERDUE_001', 'Brief Description': 'Overdue redeterminations are listed on Case Manager dashboard'}, {'Test Case ID': 'TC_CM_OVERDUE_002', 'Brief Description': 'Case Manager opens overdue record and views client details'}, {'Test Case ID': 'TC_CM_OVERDUE_003', 'Brief Description': 'System flags future-due redeterminations as not overdue'}, {'Test Case ID': 'TC_CM_OVERDUE_004', 'Brief Description': 'Audit trail for redetermination updates'}]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['22895812, 22895833: If suggestion or field-checking logic changes.', 'Data validation components.']</t>
+          <t>[{'Test Case ID': 'TC_CM_OVERDUE_001', 'EPIC': 'Compliance Management', 'Feature': 'Redetermination Tracking', 'User Story': '22895841', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Redetermination', 'Activity Title': 'View Overdue Redeterminations', 'Test Scenario Title': 'Dashboard lists overdue redeterminations', 'Precondition': 'Client records with overdue redeterminations exist.', 'Test Data': 'Client ID: CL876, Redetermination Due: 10 days ago', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to Compliance/Redeterminations section', 'Review overdue client list'], 'Expected Result': 'All clients with overdue redeterminations are listed with due dates.', 'Dependent Module/Process': 'Compliance Tracking'}, {'Test Case ID': 'TC_CM_OVERDUE_002', 'EPIC': 'Compliance Management', 'Feature': 'Redetermination Tracking', 'User Story': '22895841', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Redetermination', 'Activity Title': 'View Client Compliance Details', 'Test Scenario Title': 'Open overdue redetermination record', 'Precondition': 'Overdue record exists.', 'Test Data': 'Client ID: CL876', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Go to overdue redeterminations', 'Select a specific client (CL876)', 'View compliance details'], 'Expected Result': 'Detailed view shows redetermination date, overdue status, and client eligibility impact.', 'Dependent Module/Process': 'Compliance Tracking'}, {'Test Case ID': 'TC_CM_OVERDUE_003', 'EPIC': 'Compliance Management', 'Feature': 'Redetermination Tracking', 'User Story': '22895841', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Redetermination', 'Activity Title': 'Validate Not Overdue Status', 'Test Scenario Title': 'System does not list not-yet-due redeterminations', 'Precondition': 'Redetermination due in the future.', 'Test Data': 'Client ID: CL490, Due Date: +30 days', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'View overdue redeterminations list'], 'Expected Result': 'Client (CL490) is not listed.', 'Dependent Module/Process': 'Compliance Tracking'}, {'Test Case ID': 'TC_CM_OVERDUE_004', 'EPIC': 'Compliance Management', 'Feature': 'Redetermination Tracking', 'User Story': '22895841', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Redetermination Audit Trail', 'Activity Title': 'Verify Audit Trail', 'Test Scenario Title': 'Redetermination timeline tracked for auditability', 'Precondition': 'Redetermination action performed on overdue case.', 'Test Data': 'Client ID: CL876, Action: Redetermination Submitted', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor/Case Manager', 'Detailed Test Steps': ['Login as Auditor', 'Retrieve audit log for client CL876', 'Examine redetermination action entries'], 'Expected Result': 'Audit trail is complete and accurate with timestamps and user actions.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>22895811</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Case Managers need visibility into the number and types of escalated cases for reporting on urgency trends. The test suite will verify that all escalated cases are tracked accurately, visible to authorized users, and that escalations for metrics and reporting are properly counted.</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Verify that household composition can be recorded and saved for a case.', 'Check that family size calculations are accurate and include all designated members.', 'Ensure household changes are tracked historically.', 'Validate that eligibility logic uses household composition correctly.']</t>
+          <t>22895845: As a Case Manager, I want to track the number of escalated cases so that I can report on urgency trends.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['Household with zero members.', 'Large household (maximum supported size).', 'Editing/removing members after initial entry.', 'Duplicate household member entries.']</t>
+          <t>Case Manager accesses dashboard or report summarizing escalated case metrics; data reflects current state and trends.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['Eligibility assessment based on composition (possibly shared with eligibility stories 22895834, 22895810).']</t>
+          <t>[{'Test Case ID': 'TC_CM_ESC_TRACK_001', 'Brief Description': 'Case Manager views total number of escalated cases'}, {'Test Case ID': 'TC_CM_ESC_TRACK_002', 'Brief Description': 'Data refreshes in real-time after new escalation'}, {'Test Case ID': 'TC_CM_ESC_TRACK_003', 'Brief Description': 'Unauthorized user cannot access escalation report'}, {'Test Case ID': 'TC_CM_ESC_TRACK_004', 'Brief Description': 'Escalation statistics can be exported for reporting'}]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['22895834, 22895810: Eligibility determination features.', 'Client information data structures.']</t>
+          <t>[{'Test Case ID': 'TC_CM_ESC_TRACK_001', 'EPIC': 'Case Reporting and Trends', 'Feature': 'Escalation Metrics', 'User Story': '22895845', 'Business Process': 'Case Management Reporting', 'Sub-Process Title': 'Urgency Trend Reporting', 'Activity Title': 'View Escalated Case Count', 'Test Scenario Title': 'Case Manager views total number of escalated cases', 'Precondition': 'System contains escalated cases.', 'Test Data': 'Escalated Cases: C777, C888, C999', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to escalation report/dashboard', 'View total escalated cases count'], 'Expected Result': 'Displayed count matches current number of escalated cases.', 'Dependent Module/Process': 'Reporting Engine'}, {'Test Case ID': 'TC_CM_ESC_TRACK_002', 'EPIC': 'Case Reporting and Trends', 'Feature': 'Escalation Metrics', 'User Story': '22895845', 'Business Process': 'Case Management Reporting', 'Sub-Process Title': 'Urgency Trend Reporting', 'Activity Title': 'Validate Real-time Reporting', 'Test Scenario Title': 'Escalation report updates instantly after new escalation', 'Precondition': 'At least one new case escalated.', 'Test Data': 'Pre: 3 escalated cases, Action: escalate C1000', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Check initial escalated case count', 'Trigger escalation for case C1000', 'Refresh or revisit escalation report'], 'Expected Result': 'Escalated count increases by one (now 4 cases).', 'Dependent Module/Process': 'Reporting Engine, Case Escalation Process'}, {'Test Case ID': 'TC_CM_ESC_TRACK_003', 'EPIC': 'Case Reporting and Trends', 'Feature': 'Escalation Metrics', 'User Story': '22895845', 'Business Process': 'Case Management Reporting', 'Sub-Process Title': 'Urgency Trend Reporting', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Non-Case Manager is blocked from viewing escalation data', 'Precondition': 'User is not a Case Manager.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Clerk/Supervisor', 'Detailed Test Steps': ['Login as Clerk or Supervisor', 'Attempt to access escalation report/dashboard'], 'Expected Result': 'Access denied or data is not visible.', 'Dependent Module/Process': 'Role Permissions'}, {'Test Case ID': 'TC_CM_ESC_TRACK_004', 'EPIC': 'Case Reporting and Trends', 'Feature': 'Escalation Metrics Export', 'User Story': '22895845', 'Business Process': 'Case Management Reporting', 'Sub-Process Title': 'Urgency Trend Reporting', 'Activity Title': 'Export Escalation Metrics', 'Test Scenario Title': 'Case Manager exports escalation statistics', 'Precondition': 'Escalation metrics displayed on dashboard.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'Navigate to escalation metrics', 'Select export option (CSV, PDF, etc.)', 'Download exported file'], 'Expected Result': 'Exported file contains correct escalation data.', 'Dependent Module/Process': 'Reporting Engine, File Export'}]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>22895820</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Managers can view eligibility status of their clients for better service planning. Testing covers correct eligibility display, negative/edge cases (no status available), permissions, and regulatory or audit requirements around eligibility notifications.</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Verify sensitive information is detected and redacted in uploaded documents.', 'Check that non-sensitive documents are not altered.', 'Validate case worker can view redacted and original versions if permitted.', 'Ensure redaction is applied before document alerts are sent.']</t>
+          <t>22895813: As a Case Manager, I want to view the eligibility status of my clients so that I can plan services accordingly.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['Documents with unusual formats (handwritten, images).', 'Partially detected sensitive information.', 'Multiple types of sensitive data in one document.', 'Large/complex documents with many pages.']</t>
+          <t>Case Manager logs in, reviews client list, and sees eligibility status displayed clearly for each client.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['Redaction logic (shared with 22895815, 22895831).', 'End-to-end document upload and alert process.']</t>
+          <t>[{'Test Case ID': 'TC_CM_ELIG_VIEW_001', 'Brief Description': 'View eligibility status for clients on dashboard'}, {'Test Case ID': 'TC_CM_ELIG_VIEW_002', 'Brief Description': 'Eligibility status unavailable – error or placeholder displayed'}, {'Test Case ID': 'TC_CM_ELIG_VIEW_003', 'Brief Description': 'User without access cannot view client eligibility'}, {'Test Case ID': 'TC_CM_ELIG_VIEW_004', 'Brief Description': 'Audit logs include eligibility status viewing'}]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['22895815, 22895831: Redaction and privacy features.', 'Document upload, notification, and alert stories (22895824, 22895846).']</t>
+          <t>[{'Test Case ID': 'TC_CM_ELIG_VIEW_001', 'EPIC': 'Client Management', 'Feature': 'Eligibility Status Viewing', 'User Story': '22895813', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Eligibility Status', 'Activity Title': 'View Client Eligibility', 'Test Scenario Title': 'Case Manager sees client eligibility status', 'Precondition': 'Clients assigned to Case Manager; eligibility data available.', 'Test Data': 'Client IDs: CL555, CL666; Status: Eligible/Ineligible', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'View client list/dashboard', 'Check eligibility status for each client'], 'Expected Result': 'Eligibility status clearly displayed for each client.', 'Dependent Module/Process': 'Eligibility Data Feed'}, {'Test Case ID': 'TC_CM_ELIG_VIEW_002', 'EPIC': 'Client Management', 'Feature': 'Eligibility Status Viewing', 'User Story': '22895813', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Eligibility Status', 'Activity Title': 'Handle Missing Eligibility Data', 'Test Scenario Title': 'Status unavailable is handled gracefully', 'Precondition': 'Eligibility data is missing or corrupt for a client.', 'Test Data': 'Client ID: CL777; Status: NULL', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager', 'View client list', 'Check display for client CL777'], 'Expected Result': 'Placeholder or appropriate error message displayed instead of eligibility status.', 'Dependent Module/Process': 'Eligibility Data Feed'}, {'Test Case ID': 'TC_CM_ELIG_VIEW_003', 'EPIC': 'Client Management', 'Feature': 'Eligibility Status Viewing', 'User Story': '22895813', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Access Control', 'Activity Title': 'Permission Validation', 'Test Scenario Title': 'Unauthorized user cannot view eligibility status', 'Precondition': 'User role does not have eligibility access.', 'Test Data': 'Client ID: CL555', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Clerk/External User', 'Detailed Test Steps': ['Login as Clerk/External User', 'Attempt to view client dashboard/info'], 'Expected Result': 'Eligibility status is not accessible or visible.', 'Dependent Module/Process': 'Role &amp; Permissions'}, {'Test Case ID': 'TC_CM_ELIG_VIEW_004', 'EPIC': 'Client Management', 'Feature': 'Eligibility Status Viewing', 'User Story': '22895813', 'Business Process': 'Eligibility Management', 'Sub-Process Title': 'Eligibility Status Audit', 'Activity Title': 'Audit Viewing of Eligibility Status', 'Test Scenario Title': 'Audit log records eligibility status view', 'Precondition': 'Case Manager views client eligibility.', 'Test Data': 'Client ID: CL555', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Auditor/Case Manager', 'Detailed Test Steps': ['Login as Auditor or System Admin', 'Query audit logs for eligibility view actions', 'Verify entry for Case Manager viewing eligibility for CL555'], 'Expected Result': 'Audit log entry exists with user, client, timestamp.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>22895816</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>This user story enables Case Managers to view analytics on eligibility denials, supporting operational insight and systemic improvements.</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['Search by full name returns correct applicant(s)', 'Search by partial name returns appropriate results', 'Search by full SSN returns the correct applicant', 'Search with invalid or nonexistent SSN returns no results', 'Search with blank input returns appropriate message or all applicants (if designed)', 'Search results update if applicant data is changed', 'Ensure search prevents duplicate entries based on existing applicants']</t>
+          <t>As a Case Manager, I want to view trends in eligibility denials so that I can identify systemic issues.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['Search by name with leading, trailing, or multiple spaces', 'Search by name with different capitalizations', 'Search by name with special characters or accents', 'Search by SSN with dashes, spaces, or invalid formats', 'Multiple applicants with similar names', 'SSN with fewer/more than 9 digits']</t>
+          <t>Case Manager logs in, navigates to the analytics dashboard, applies filters, and reviews a graph/chart showing denial trends over time, broken down by category.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['Verify that applicant search functionality integrates with add/edit applicant workflows (related: 22895834, 22895838, 22895808)']</t>
+          <t>[{'Test Case ID': 'TC_CM_DENIAL_01', 'Brief Description': 'View eligibility denial trends with all filters applied'}, {'Test Case ID': 'TC_CM_DENIAL_02', 'Brief Description': 'View eligibility denial trends with no data returned'}, {'Test Case ID': 'TC_CM_DENIAL_03', 'Brief Description': 'Verify permission restrictions for other user roles'}, {'Test Case ID': 'TC_CM_DENIAL_04', 'Brief Description': 'Validate data accuracy between dashboard and underlying source'}, {'Test Case ID': 'TC_CM_DENIAL_05', 'Brief Description': 'Check for compliance with regulatory audit requirements (audit log, export)'}]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['22895834', '22895838', '22895808']</t>
+          <t>[{'Test Case ID': 'TC_CM_DENIAL_01', 'EPIC': 'Reporting and Analytics', 'Feature': 'Eligibility Denials Trend Analytics', 'User Story': '22895832', 'Business Process': 'Case Management Analytics', 'Sub-Process Title': 'View Denial Trend Charts', 'Activity Title': 'Trend Visualization', 'Test Scenario Title': 'Case Manager views denial trends with all filters', 'Precondition': 'User assigned Case Manager role. System contains denial data.', 'Test Data': 'Multiple denial events across categories and timeframes.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', "Navigate to the 'Eligibility Denials Analysis' dashboard.", 'Select various filters (date range, denial type, region, etc.).', "Click 'Generate Report'.", 'Observe chart/table generated.'], 'Expected Result': 'Updated charts/tables reflect accurate denial trends per filter selection.', 'Dependent Module/Process': 'Eligibility Engine, Reporting DB'}, {'Test Case ID': 'TC_CM_DENIAL_02', 'EPIC': 'Reporting and Analytics', 'Feature': 'Eligibility Denials Trend Analytics', 'User Story': '22895832', 'Business Process': 'Case Management Analytics', 'Sub-Process Title': 'View Denial Trend Charts', 'Activity Title': 'Trend Visualization', 'Test Scenario Title': 'No data returned for selected filters', 'Precondition': 'User is logged in as Case Manager. No matching denial data for selected filter.', 'Test Data': 'Filters set to period with no denials.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Apply a filter with a date range or criteria known to have zero denials.', "Click 'Generate Report'."], 'Expected Result': "Dashboard gracefully shows 'No data available' message, with empty chart.", 'Dependent Module/Process': 'Reporting DB'}, {'Test Case ID': 'TC_CM_DENIAL_03', 'EPIC': 'Reporting and Analytics', 'Feature': 'Eligibility Denials Trend Analytics', 'User Story': '22895832', 'Business Process': 'Case Management Analytics', 'Sub-Process Title': 'View Denial Trend Charts', 'Activity Title': 'Access Control', 'Test Scenario Title': 'Permission restricted for non-Case Managers', 'Precondition': 'User has a non-Case Manager role.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker/Other', 'Detailed Test Steps': ['Login as a user with a role such as Case Worker.', "Attempt to access the 'Eligibility Denials Analysis' dashboard."], 'Expected Result': 'Access denied. User receives appropriate error or is redirected.', 'Dependent Module/Process': 'User Permissions'}, {'Test Case ID': 'TC_CM_DENIAL_04', 'EPIC': 'Reporting and Analytics', 'Feature': 'Eligibility Denials Trend Analytics', 'User Story': '22895832', 'Business Process': 'Case Management Analytics', 'Sub-Process Title': 'View Denial Trend Charts', 'Activity Title': 'Data Accuracy', 'Test Scenario Title': 'Data accuracy between dashboard and DB', 'Precondition': 'Case Manager with access. Known set of denial events.', 'Test Data': 'Seeded denial transactions with expected values.', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Run a DB query for denials using same filters as dashboard.', 'Run dashboard report.', 'Compare results.'], 'Expected Result': 'Dashboard and DB data match exactly.', 'Dependent Module/Process': 'Reporting DB'}, {'Test Case ID': 'TC_CM_DENIAL_05', 'EPIC': 'Reporting and Analytics', 'Feature': 'Eligibility Denials Trend Analytics', 'User Story': '22895832', 'Business Process': 'Case Management Analytics', 'Sub-Process Title': 'View Denial Trend Charts', 'Activity Title': 'Audit/Compliance', 'Test Scenario Title': 'Regulatory compliance: Audit log and export', 'Precondition': 'Audit logging and export enabled per policy.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Generate denial trend report.', 'Export report as Excel/PDF.', 'Check system logs for audit entry (user, time, parameters).'], 'Expected Result': 'Export succeeds and logs meet compliance/audit standards.', 'Dependent Module/Process': 'Reporting DB, Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>22895818</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bulk document upload accelerates workflow for Case Workers and ensures accurate association of files to multiple cases.</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['Send document request to a single applicant', 'Send requests for multiple document types', 'Applicant receives notification for document request', 'Document request appears in applicant’s portal/dashboard', 'Case Worker sees status of document requests (pending/completed)', 'Error shown if trying to send request for unsupported document type']</t>
+          <t>As a Case Worker, I want to bulk upload documents for multiple cases so that I can save time.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['Send request to invalid or inactive applicant', 'Send duplicate requests for the same document', 'Request with blank or missing document types', 'Large batch of requests sent at once', 'Applicant with no email/contact info']</t>
+          <t>Case Worker selects multiple files, associates each with relevant cases, and uploads. All files are attached to the correct cases in the system.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['Test communication/notification logic (related: 22895819, 22895824, 22895826)']</t>
+          <t>[{'Test Case ID': 'TC_CW_BULKUPLOAD_01', 'Brief Description': 'Bulk upload valid documents to multiple cases'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_02', 'Brief Description': 'Attempt upload with unsupported file types'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_03', 'Brief Description': 'User tries to upload with missing case associations'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_04', 'Brief Description': 'Permissions validation: unauthorized role attempts upload'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_05', 'Brief Description': 'System handles partial upload success/failure gracefully'}]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['22895819', '22895824', '22895826']</t>
+          <t>[{'Test Case ID': 'TC_CW_BULKUPLOAD_01', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '22895831', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Bulk Upload', 'Test Scenario Title': 'Successful bulk upload of valid documents', 'Precondition': 'Case Worker with upload permissions. Multiple cases exist.', 'Test Data': ['documents: [doc1.pdf, doc2.jpg]', 'cases: [12345, 23456]'], 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Navigate to bulk upload interface.', 'Select multiple documents.', 'Assign each document to one or more cases.', "Click 'Upload'."], 'Expected Result': 'All documents are successfully linked to their respective cases.', 'Dependent Module/Process': 'Document Repository, Case Management'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_02', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '22895831', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Bulk Upload', 'Test Scenario Title': 'Attempt bulk upload with unsupported file types', 'Precondition': 'Case Worker logged in.', 'Test Data': ['documents: [malware.exe, largefile.mov, doc3.pdf]', 'cases: [34567, 45678]'], 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select mix of supported and unsupported file types.', 'Assign files to cases.', 'Attempt to upload.'], 'Expected Result': 'System rejects unsupported types, displays clear error, only allows valid types to upload.', 'Dependent Module/Process': 'Document Repository'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_03', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '22895831', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Bulk Upload', 'Test Scenario Title': 'Missing case association for some documents', 'Precondition': 'Case Worker logged in.', 'Test Data': ['documents: [doc4.pdf, doc5.pdf]', 'case associations: [doc4.pdf -&gt; 78901 | doc5.pdf -&gt; none]'], 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select multiple files.', 'Assign only some documents to cases.', "Click 'Upload'."], 'Expected Result': 'System prompts for missing associations; prevents upload until resolved.', 'Dependent Module/Process': 'Validation Engine'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_04', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '22895831', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Bulk Upload', 'Test Scenario Title': 'Permissions enforcement for bulk upload', 'Precondition': 'User role is NOT Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'External User', 'Detailed Test Steps': ['Login as an unauthorized user.', 'Attempt to access bulk upload feature.'], 'Expected Result': 'Access denied or bulk upload feature hidden for unauthorized roles.', 'Dependent Module/Process': 'User Roles/Permissions'}, {'Test Case ID': 'TC_CW_BULKUPLOAD_05', 'EPIC': 'Document Management', 'Feature': 'Bulk Upload', 'User Story': '22895831', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Bulk Upload', 'Test Scenario Title': 'Partial upload failure handling', 'Precondition': 'Case Worker with multiple cases.', 'Test Data': ['documents: [doc6.pdf (OK), doc7.pdf (corrupt)]', 'cases: [12345, 23456]'], 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Bulk upload multiple documents, some valid, some corrupted.', 'Assign to cases.', "Click 'Upload'."], 'Expected Result': 'Valid documents succeed, failed documents reported individually with reason.', 'Dependent Module/Process': 'Document Repository'}]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>22895815</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Supports Case Workers in accurate, compliant income eligibility checks utilizing wage datasets, aligning with determination requirements.</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Upload a single document to a case', 'Upload multiple documents to a single case', 'Support various file types (PDF, JPG, DOCX, etc.)', 'Restrict file upload size as per requirements', 'Case Worker can view uploaded documents after upload', 'Document upload fails gracefully with invalid file format']</t>
+          <t>As a Case Worker, I want to check income eligibility using wage data so that I can determine financial qualification.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['Upload with corrupted file', 'Upload extremely large file', 'Upload file with special characters in name', 'Simultaneous uploads of the same document', 'Upload to a non-existent or closed case']</t>
+          <t>Case Worker inputs applicant info, system accesses wage database, auto-calculates eligibility, and returns result explaining basis.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['Document view and retrieval (related: 22895831, 22895836, 22895820)']</t>
+          <t>[{'Test Case ID': 'TC_CW_ELIG_01', 'Brief Description': 'Eligibility verification with valid wage data'}, {'Test Case ID': 'TC_CW_ELIG_02', 'Brief Description': 'Applicant not found in wage database'}, {'Test Case ID': 'TC_CW_ELIG_03', 'Brief Description': 'Income eligibility calculation error due to missing data'}, {'Test Case ID': 'TC_CW_ELIG_04', 'Brief Description': 'Permissions check for wage data access'}, {'Test Case ID': 'TC_CW_ELIG_05', 'Brief Description': 'Audit log for eligibility decision'}]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['22895831', '22895836', '22895820']</t>
+          <t>[{'Test Case ID': 'TC_CW_ELIG_01', 'EPIC': 'Income Eligibility', 'Feature': 'Automated Wage Data Checks', 'User Story': '22895810', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Financial Eligibility', 'Activity Title': 'Income Verification', 'Test Scenario Title': 'Case Worker uses wage data to check eligibility', 'Precondition': 'Case Worker role; Applicant has wage data.', 'Test Data': {'applicant_id': 'A1234', 'wage_records': [{'quarter': 'Q1-2024', 'amount': 4500}, {'quarter': 'Q2-2024', 'amount': 4400}], 'threshold': 9000}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Access applicant eligibility screen.', 'Enter applicant ID (A1234).', 'Submit for wage data check.', 'System retrieves wage data and calculates income.', 'Eligibility result displayed.'], 'Expected Result': 'Eligibility status accurately reflects wage-based calculation.', 'Dependent Module/Process': 'Wage Data API, Eligibility Engine'}, {'Test Case ID': 'TC_CW_ELIG_02', 'EPIC': 'Income Eligibility', 'Feature': 'Automated Wage Data Checks', 'User Story': '22895810', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Financial Eligibility', 'Activity Title': 'Income Verification', 'Test Scenario Title': 'No wage data found for applicant', 'Precondition': 'Case Worker logged in; Applicant not in wage DB.', 'Test Data': {'applicant_id': 'B2345'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Input applicant ID not present in wage data.', 'Submit for eligibility check.'], 'Expected Result': "System displays 'No wage records found' and prompts for alternate verification.", 'Dependent Module/Process': 'Wage Data API'}, {'Test Case ID': 'TC_CW_ELIG_03', 'EPIC': 'Income Eligibility', 'Feature': 'Automated Wage Data Checks', 'User Story': '22895810', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Financial Eligibility', 'Activity Title': 'Income Verification', 'Test Scenario Title': 'Eligibility calculation error due to incomplete wage data', 'Precondition': 'Applicant record has partial/missing wage data.', 'Test Data': {'applicant_id': 'C3456', 'wage_records': []}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit eligibility check for applicant with missing wage details.'], 'Expected Result': 'System provides error/warning with clear guidance to user.', 'Dependent Module/Process': 'Wage Data API, Error Messaging'}, {'Test Case ID': 'TC_CW_ELIG_04', 'EPIC': 'Income Eligibility', 'Feature': 'Automated Wage Data Checks', 'User Story': '22895810', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Financial Eligibility', 'Activity Title': 'Access Control', 'Test Scenario Title': 'Permissions enforcement for wage data access', 'Precondition': 'User is not a Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Unauthorized User', 'Detailed Test Steps': ['Login as unauthorized user.', 'Attempt to access wage data check.'], 'Expected Result': 'Access denied—no wage data or calculation screen visible.', 'Dependent Module/Process': 'User Roles/Permissions'}, {'Test Case ID': 'TC_CW_ELIG_05', 'EPIC': 'Income Eligibility', 'Feature': 'Automated Wage Data Checks', 'User Story': '22895810', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Financial Eligibility', 'Activity Title': 'Audit/Compliance', 'Test Scenario Title': 'Eligibility audit log creation', 'Precondition': 'Audit logging enabled.', 'Test Data': {'applicant_id': 'A1234'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Perform eligibility check.', 'Query audit log for corresponding entry.'], 'Expected Result': 'Audit trail includes user, time, applicant, calculation result.', 'Dependent Module/Process': 'Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>22895809</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Case Workers can generate comprehensive summary reports on eligibility findings, supporting workflow documentation and review by supervisors.</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['Enter valid government ID returns verified status', 'Enter invalid or expired government ID returns error/failed status', 'Case Worker can review ID details before finalizing verification', 'Store verification status on applicant record', 'Attempt verification without required fields triggers error']</t>
+          <t>As a Case Worker, I want to generate a summary report of eligibility findings so that I can present it to supervisors.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['ID with special characters or unusual formats', 'Two applicants with the same government ID', 'Upload blurry or partial ID image', 'Very long or very short ID numbers', 'Verification when system is offline or external service fails']</t>
+          <t>Case Worker selects applicant/case, chooses ‘Generate Report’, and receives a formatted summary including eligibility status, rationale, and supporting data.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>['ID verification process consistency (related: 22895810)']</t>
+          <t>[{'Test Case ID': 'TC_CW_ELIGREP_01', 'Brief Description': 'Generate summary report successfully for eligible case'}, {'Test Case ID': 'TC_CW_ELIGREP_02', 'Brief Description': 'Generate summary report for ineligible case'}, {'Test Case ID': 'TC_CW_ELIGREP_03', 'Brief Description': 'Attempt to generate report with incomplete eligibility data'}, {'Test Case ID': 'TC_CW_ELIGREP_04', 'Brief Description': 'Role-based restriction on report generation'}, {'Test Case ID': 'TC_CW_ELIGREP_05', 'Brief Description': 'Compliance: export and audit log for generated report'}]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['22895810']</t>
+          <t>[{'Test Case ID': 'TC_CW_ELIGREP_01', 'EPIC': 'Reporting', 'Feature': 'Eligibility Summary Report', 'User Story': '22895823', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Reporting &amp; Documentation', 'Activity Title': 'Generate Report', 'Test Scenario Title': 'Generate correct summary report for eligible case', 'Precondition': 'Eligibility result is ‘Eligible’.', 'Test Data': {'case_id': 'E001', 'eligibility_status': 'Eligible'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Access case E001.', "Click 'Generate Eligibility Summary Report'.", 'View report.'], 'Expected Result': 'Report reflects eligibility result and supporting data, formatted correctly.', 'Dependent Module/Process': 'Reporting Engine'}, {'Test Case ID': 'TC_CW_ELIGREP_02', 'EPIC': 'Reporting', 'Feature': 'Eligibility Summary Report', 'User Story': '22895823', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Reporting &amp; Documentation', 'Activity Title': 'Generate Report', 'Test Scenario Title': 'Generate report for ineligible case', 'Precondition': "Case with 'Ineligible' result.", 'Test Data': {'case_id': 'E002', 'eligibility_status': 'Ineligible', 'reason': 'Income exceeds threshold'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Access case E002.', 'Generate summary report.'], 'Expected Result': 'Report states ineligible status and provides rationale.', 'Dependent Module/Process': 'Reporting Engine'}, {'Test Case ID': 'TC_CW_ELIGREP_03', 'EPIC': 'Reporting', 'Feature': 'Eligibility Summary Report', 'User Story': '22895823', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Reporting &amp; Documentation', 'Activity Title': 'Generate Report', 'Test Scenario Title': 'Attempt generation with incomplete data', 'Precondition': 'Case missing eligibility determination data.', 'Test Data': {'case_id': 'E003', 'eligibility_status': 'Pending'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select a case with partial/incomplete eligibility data.', 'Try to generate report.'], 'Expected Result': 'System notifies user that report cannot be generated until eligibility is finalized.', 'Dependent Module/Process': 'Validation'}, {'Test Case ID': 'TC_CW_ELIGREP_04', 'EPIC': 'Reporting', 'Feature': 'Eligibility Summary Report', 'User Story': '22895823', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Reporting &amp; Documentation', 'Activity Title': 'Access Control', 'Test Scenario Title': 'Permissions - different roles', 'Precondition': 'User role is not Case Worker.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'External User', 'Detailed Test Steps': ['Login as different role.', 'Access case and try to generate summary report.'], 'Expected Result': 'Report generation unavailable/hidden for this role.', 'Dependent Module/Process': 'Roles &amp; Permissions'}, {'Test Case ID': 'TC_CW_ELIGREP_05', 'EPIC': 'Reporting', 'Feature': 'Eligibility Summary Report', 'User Story': '22895823', 'Business Process': 'Eligibility Determination', 'Sub-Process Title': 'Reporting &amp; Documentation', 'Activity Title': 'Compliance', 'Test Scenario Title': 'Audit/Compliance for report export', 'Precondition': 'Compliance logging enabled.', 'Test Data': {'case_id': 'E004'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Generate summary report.', 'Export/download report.', 'Check logs for creation, export action.'], 'Expected Result': 'Both report actions are logged with all required info (user, case, timestamp).', 'Dependent Module/Process': 'Logging, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>22895835</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Document preview helps Case Workers verify file contents and metadata before uploading, reducing upload errors and ensuring accurate documentation.</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['Assign case based on specified language preference', 'Automatic assignment when multiple agents have matching language skills', 'Fallback assignment when no agent has matching language', 'Update language preference and re-assign case', 'Display case assignments with assigned language clearly to case managers']</t>
+          <t>As a Case Worker, I want to preview documents before uploading so that I can ensure accuracy.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['Applicant specifies a rare or unsupported language', 'No available case managers at time of assignment', 'Change in agent language skills after assignment', 'Simultaneous new cases with identical preferences', 'Applicant with multiple language preferences selected']</t>
+          <t>Case Worker selects file(s), clicks ‘Preview’, reviews content and metadata, and makes upload decision.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>['Case assignment rules consistency across case manager workflow (related: 22895817, 22895847)']</t>
+          <t>[{'Test Case ID': 'TC_CW_PREVIEW_01', 'Brief Description': 'Preview supported document type before upload'}, {'Test Case ID': 'TC_CW_PREVIEW_02', 'Brief Description': 'Attempt to preview unsupported document type'}, {'Test Case ID': 'TC_CW_PREVIEW_03', 'Brief Description': 'Ensure that document preview does not alter file'}, {'Test Case ID': 'TC_CW_PREVIEW_04', 'Brief Description': 'Permission restriction for unauthorized user'}, {'Test Case ID': 'TC_CW_PREVIEW_05', 'Brief Description': 'Preview corrupted or unreadable file'}]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['22895817', '22895847']</t>
+          <t>[{'Test Case ID': 'TC_CW_PREVIEW_01', 'EPIC': 'Document Management', 'Feature': 'Document Preview', 'User Story': '22895836', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Preview File', 'Test Scenario Title': 'Preview PDF document before upload', 'Precondition': 'User is logged in as Case Worker; document in supported format (.pdf).', 'Test Data': {'document': 'sample1.pdf'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select 'sample1.pdf' in upload dialog.", "Click 'Preview'."], 'Expected Result': 'Document content and metadata are shown in preview UI; user can make informed decision.', 'Dependent Module/Process': 'Preview Engine'}, {'Test Case ID': 'TC_CW_PREVIEW_02', 'EPIC': 'Document Management', 'Feature': 'Document Preview', 'User Story': '22895836', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Preview File', 'Test Scenario Title': 'Attempt preview on unsupported file type', 'Precondition': 'User is Case Worker; file is of unsupported type (e.g., .exe).', 'Test Data': {'document': 'malware.exe'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select 'malware.exe'.", 'Attempt to preview.'], 'Expected Result': "System shows message 'Preview unavailable for this file type'.", 'Dependent Module/Process': 'Preview Engine'}, {'Test Case ID': 'TC_CW_PREVIEW_03', 'EPIC': 'Document Management', 'Feature': 'Document Preview', 'User Story': '22895836', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Preview File', 'Test Scenario Title': 'Preview does not modify file', 'Precondition': 'File integrity is validated before and after preview.', 'Test Data': {'document': 'sample2.docx'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Preview 'sample2.docx'.", 'Check file hash before and after preview.'], 'Expected Result': 'File is identical (no modification on preview action).', 'Dependent Module/Process': 'Preview Engine'}, {'Test Case ID': 'TC_CW_PREVIEW_04', 'EPIC': 'Document Management', 'Feature': 'Document Preview', 'User Story': '22895836', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Preview File', 'Test Scenario Title': 'Unauthorized user attempts document preview', 'Precondition': 'User does not have Case Worker permissions.', 'Test Data': '', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'External User', 'Detailed Test Steps': ['Attempt to access document upload interface as unauthorized user.', 'Try to preview file.'], 'Expected Result': 'Preview feature inaccessible; access error displayed.', 'Dependent Module/Process': 'User Roles/Permissions'}, {'Test Case ID': 'TC_CW_PREVIEW_05', 'EPIC': 'Document Management', 'Feature': 'Document Preview', 'User Story': '22895836', 'Business Process': 'Case Documentation', 'Sub-Process Title': 'Document Upload', 'Activity Title': 'Preview File', 'Test Scenario Title': 'Preview corrupted/unreadable file', 'Precondition': 'File is corrupted/unreadable.', 'Test Data': {'document': 'corruptfile.pdf'}, 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select a corrupted PDF file.', "Click 'Preview'."], 'Expected Result': "System displays error message: 'File cannot be previewed.'", 'Dependent Module/Process': 'Preview Engine'}]</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>22895817</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>This user story covers the ability for Case Workers to generate and print a checklist of required documents tailored for walk-in clients, enabling efficient and consistent client onboarding.</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['Assign a new case to a team member with the lowest workload', 'Assign a case to a team member with manually adjusted workload', 'Attempt to assign a case when all members have reached their maximum case limit', 'Reassign an existing case to another team member', 'View summary of cases per team member post-assignment to verify workload balance']</t>
+          <t>22895826: As a Case Worker, I want to print a checklist of required documents so that I can provide it to walk-in clients.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['Assign case when one or more team members are marked as unavailable', 'Assign case when team workload information is incomplete or delayed', 'Assign multiple cases at once to test bulk assignment logic', 'Assign a case to a member with 0 workload versus those with several assignments']</t>
+          <t>Case Worker selects 'Print Checklist', system generates checklist based on case type, and produces a printable document.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>['Test interactions with story 22895827 (escalation) to ensure assigned cases can be escalated', 'Verify assignment changes for cases that are to be exported (story 22895837)', 'Test efficiency when cases are filtered by eligibility (story 22895830) prior to assignment']</t>
+          <t>[{'Test Case ID': '22895826-TC1', 'Brief Description': 'Print checklist for standard walk-in case'}, {'Test Case ID': '22895826-TC2', 'Brief Description': 'Attempt to print checklist with no case type selected (negative)'}, {'Test Case ID': '22895826-TC3', 'Brief Description': 'Print checklist for special case with unique requirements'}, {'Test Case ID': '22895826-TC4', 'Brief Description': 'API call to retrieve checklist data returns error (negative, integration)'}, {'Test Case ID': '22895826-TC5', 'Brief Description': 'Checklist printing audit log is created (compliance)'}, {'Test Case ID': '22895826-TC6', 'Brief Description': 'User without permission attempts to print checklist (permission)'}]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['22895827 (case escalation)', '22895837 (case export)', '22895825 (if relates to case reallocation/assignment logic)']</t>
+          <t>[{'Test Case ID': '22895826-TC1', 'EPIC': 'Document Management', 'Feature': 'Checklist Printing', 'User Story': '22895826', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Generation', 'Activity Title': 'Generate and Print Checklist', 'Test Scenario Title': 'Case Worker successfully prints checklist for walk-in client', 'Precondition': 'Case Worker has logged into the system; case type is selected.', 'Test Data': "{ case_type: 'Standard', client_id: '100123' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Intake Dashboard.', "Select 'Print Checklist' option.", 'Choose the relevant case type.', "Click 'Generate Checklist'.", 'Verify generated checklist contents.', "Click 'Print'.", 'Collect printed checklist.'], 'Expected Result': 'Checklist is generated and printed with correct documents listed for the selected case type.', 'Dependent Module/Process': 'Document Templates'}, {'Test Case ID': '22895826-TC2', 'EPIC': 'Document Management', 'Feature': 'Checklist Printing', 'User Story': '22895826', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Generation', 'Activity Title': 'Handle Missing Case Type', 'Test Scenario Title': 'System prevents checklist printing if no case type is selected', 'Precondition': 'Case Worker is on the checklist print page.', 'Test Data': "{ case_type: '' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Intake Dashboard.', "Select 'Print Checklist' option.", 'Leave case type unselected.', "Click 'Generate Checklist'."], 'Expected Result': 'System shows validation error and does not proceed to print.', 'Dependent Module/Process': None}, {'Test Case ID': '22895826-TC3', 'EPIC': 'Document Management', 'Feature': 'Checklist Printing for Special Case', 'User Story': '22895826', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Generation', 'Activity Title': 'Print Checklist for Special Requirement', 'Test Scenario Title': 'Successfully print checklist for a special case type', 'Precondition': 'Special case type is configured in system.', 'Test Data': "{ case_type: 'Foster Care', client_id: '100234' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Intake Dashboard.', "Select 'Print Checklist' option.", "Choose 'Foster Care' as case type.", "Click 'Generate Checklist'.", "Review checklist and click 'Print'."], 'Expected Result': 'Checklist includes Foster Care specific documents and prints successfully.', 'Dependent Module/Process': 'Document Templates'}, {'Test Case ID': '22895826-TC4', 'EPIC': 'Document Management', 'Feature': 'Checklist Printing', 'User Story': '22895826', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist API Integration', 'Activity Title': 'Handle Checklist API Failure', 'Test Scenario Title': 'Checklist data API returns error', 'Precondition': 'Checklist service API is unavailable.', 'Test Data': "{ case_type: 'Standard' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to Intake Dashboard.', "Select 'Print Checklist' option.", "Select 'Standard' case type.", "Click 'Generate Checklist'."], 'Expected Result': 'System displays error message; checklist not generated.', 'Dependent Module/Process': 'Document Templates API'}, {'Test Case ID': '22895826-TC5', 'EPIC': 'Document Management', 'Feature': 'Checklist Printing', 'User Story': '22895826', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Auditing', 'Activity Title': 'Record Checklist Print Event', 'Test Scenario Title': 'Printing a checklist triggers a compliance audit log', 'Precondition': 'Checklist printing functions as normal.', 'Test Data': "{ case_type: 'Standard', client_id: '100123' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Print a checklist as in TC1.', 'Check audit log entries for checklist print action.'], 'Expected Result': 'Audit log records user ID, client ID, timestamp, and checklist type.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': '22895826-TC6', 'EPIC': 'Document Management', 'Feature': 'Checklist Printing', 'User Story': '22895826', 'Business Process': 'Client Intake', 'Sub-Process Title': 'Checklist Permissions Validation', 'Activity Title': 'Restrict Printing by Role', 'Test Scenario Title': 'Prevent printing checklist without permission', 'Precondition': 'User without checklist printing permission is logged in.', 'Test Data': "{ user_role: 'Intern' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Intern', 'Detailed Test Steps': ["Attempt to access 'Print Checklist' option."], 'Expected Result': 'System disables or hides printing option; access is denied.', 'Dependent Module/Process': 'RBAC'}]</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>22895822</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>This user story encompasses functionality for Case Workers to print a formatted summary of case notes for inclusion in physical files, ensuring accurate record-keeping and compliance.</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Initiate coordination with another agency for a dual eligibility case', 'Log communication history with partnering agency for an eligible client', "Verify protocol followed for agencies' responses (accepted, declined, no response)"]</t>
+          <t>22895842: As a Case Worker, I want to print a summary of case notes so that I can include them in physical files.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['Coordinate with an agency that is not yet in the system', 'Coordinate when agency response times out or fails', 'Dual eligibility for more than two agencies']</t>
+          <t>Case Worker selects a case file, chooses 'Print Case Notes', reviews the summary, and successfully prints.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['Test filtering of dual eligible cases (shared with 22895830), then coordinating', 'Verify that exporting dual eligibility cases (22895837) includes coordination status']</t>
+          <t>[{'Test Case ID': '22895842-TC1', 'Brief Description': 'Print summary of case notes for a valid case'}, {'Test Case ID': '22895842-TC2', 'Brief Description': 'Attempt to print notes for case with no notes (negative)'}, {'Test Case ID': '22895842-TC3', 'Brief Description': 'API fails to fetch notes (integration negative)'}, {'Test Case ID': '22895842-TC4', 'Brief Description': 'Audit trail is created for printed notes (compliance)'}, {'Test Case ID': '22895842-TC5', 'Brief Description': 'User without permission attempts to print notes (permissions)'}]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['22895830 (filtering eligibility status)', '22895813 (related communication/coordination features)', '22895837 (case export including agency coordination details)']</t>
+          <t>[{'Test Case ID': '22895842-TC1', 'EPIC': 'Case Notes Management', 'Feature': 'Print Case Notes Summary', 'User Story': '22895842', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Print Case Notes Summary', 'Test Scenario Title': 'Case Worker prints notes summary for a case', 'Precondition': 'Case with notes exists; Case Worker logged in.', 'Test Data': "{ case_id: '200567', notes_count: '3' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Search for and open case 200567.', "Click 'Print Case Notes'.", 'Review generated summary.', "Click 'Print'."], 'Expected Result': 'Printable summary contains all notes with timestamps and worker info.', 'Dependent Module/Process': 'Notes API'}, {'Test Case ID': '22895842-TC2', 'EPIC': 'Case Notes Management', 'Feature': 'Print Case Notes Summary', 'User Story': '22895842', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Handle Empty Notes', 'Test Scenario Title': 'Prevent printing when no case notes are present', 'Precondition': 'Case exists without notes.', 'Test Data': "{ case_id: '200888', notes_count: '0' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Search for and open case 200888.', "Click 'Print Case Notes'."], 'Expected Result': "System displays message: 'No case notes to print.' and disables print option.", 'Dependent Module/Process': None}, {'Test Case ID': '22895842-TC3', 'EPIC': 'Case Notes Management', 'Feature': 'Print Case Notes Summary', 'User Story': '22895842', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Notes Handling', 'Activity Title': 'Notes API Failure', 'Test Scenario Title': 'API fails to fetch notes, system gracefully handles error', 'Precondition': 'API is down.', 'Test Data': "{ case_id: '200567' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to print notes for case 200567 while Notes service is unavailable.'], 'Expected Result': "System displays error message: 'Unable to retrieve notes at this time.'", 'Dependent Module/Process': 'Notes API'}, {'Test Case ID': '22895842-TC4', 'EPIC': 'Case Notes Management', 'Feature': 'Print Case Notes Summary', 'User Story': '22895842', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Notes Compliance', 'Activity Title': 'Audit Print Event', 'Test Scenario Title': 'Printing case notes triggers audit trail', 'Precondition': 'Printing process is successful.', 'Test Data': "{ case_id: '200567' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Print notes summary as in TC1.', 'Verify audit log for event: print, case ID, user ID, timestamp.'], 'Expected Result': 'Audit entry recorded with all relevant information.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': '22895842-TC5', 'EPIC': 'Case Notes Management', 'Feature': 'Print Case Notes Summary', 'User Story': '22895842', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case Notes Permissions', 'Activity Title': 'Enforce Role-Based Access', 'Test Scenario Title': 'User without print permission cannot print notes', 'Precondition': 'User with restricted role is logged in.', 'Test Data': "{ user_role: 'Receptionist' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Receptionist', 'Detailed Test Steps': ["Attempt to access 'Print Case Notes' for any case."], 'Expected Result': "'Print Case Notes' option is disabled or hidden.", 'Dependent Module/Process': 'RBAC'}]</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>22895827</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>This user story provides Case Workers automated alerts for duplicate applications, enabling prompt review and process improvement by supporting merges and reducing redundancy.</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Escalate an urgent case to a supervisor and verify notification', 'Track escalation status and resolution outcome', 'Attempt escalation for cases already handled or closed', 'Escalate both assigned and unassigned (or recently reassigned) cases']</t>
+          <t>22895838: As a Case Worker, I want to receive alerts for duplicate applications so that I can merge them.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['Escalate a case currently being assigned to another team member', 'Escalate multiple cases at once', 'Escalate a case with incomplete data']</t>
+          <t>Case Worker receives real-time alert for potential duplicates and initiates merge process.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>['Test with various case assignment conditions (22895817)', 'Verify escalation events are reflected in case data export (22895837)']</t>
+          <t>[{'Test Case ID': '22895838-TC1', 'Brief Description': 'Alert triggered when a duplicate is detected upon new application submission'}, {'Test Case ID': '22895838-TC2', 'Brief Description': 'No alert when no duplicates exist (positive control)'}, {'Test Case ID': '22895838-TC3', 'Brief Description': 'Case Worker merges detected duplicate'}, {'Test Case ID': '22895838-TC4', 'Brief Description': 'Duplicate detection engine fails (integration negative)'}, {'Test Case ID': '22895838-TC5', 'Brief Description': 'User without merge privileges attempts merge (permissions)'}, {'Test Case ID': '22895838-TC6', 'Brief Description': 'Audit log for duplicate alert and merge action (compliance)'}]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['22895817 (case assignment)', '22895825 (if case reassignment or escalation flows overlap)', '22895837 (case export including escalation status)']</t>
+          <t>[{'Test Case ID': '22895838-TC1', 'EPIC': 'Application Management', 'Feature': 'Duplicate Detection', 'User Story': '22895838', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicate Applications', 'Activity Title': 'Detect and Alert', 'Test Scenario Title': 'System alerts user about duplicate upon new application', 'Precondition': 'Similar application exists in system.', 'Test Data': "{ applicant_name: 'Jane Doe', dob: '1982-03-21', ssn: '123-45-6789' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit a new application with matching details.', 'System processes application and compares for duplicates.', "System displays alert: 'Potential duplicate found for Jane Doe'."], 'Expected Result': 'Duplicate alert appears with details of matching application(s).', 'Dependent Module/Process': 'Duplicate Detection Service'}, {'Test Case ID': '22895838-TC2', 'EPIC': 'Application Management', 'Feature': 'Duplicate Detection', 'User Story': '22895838', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicate Applications', 'Activity Title': 'Control Test for No Duplicate', 'Test Scenario Title': 'No alert when no duplicates present', 'Precondition': 'No existing applications with same data.', 'Test Data': "{ applicant_name: 'Stanley Smith', dob: '1999-12-11', ssn: '789-65-4321' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit a new application with unique data.'], 'Expected Result': 'No duplicate alert is displayed.', 'Dependent Module/Process': 'Duplicate Detection Service'}, {'Test Case ID': '22895838-TC3', 'EPIC': 'Application Management', 'Feature': 'Duplicate Merge', 'User Story': '22895838', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Duplicates Resolution', 'Activity Title': 'User-Initiated Merge', 'Test Scenario Title': 'Case Worker merges duplicate applications', 'Precondition': 'Duplicates detected and displayed with merge option.', 'Test Data': "{ duplicate_case_ids: ['300111', '302589'] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select 'Merge' for identified duplicates.", 'Follow prompts to confirm merge.', 'Merge process completes.'], 'Expected Result': 'Applications are merged; history retained.', 'Dependent Module/Process': 'Duplicate Merge Service'}, {'Test Case ID': '22895838-TC4', 'EPIC': 'Application Management', 'Feature': 'Duplicate Detection', 'User Story': '22895838', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Integration', 'Activity Title': 'Duplicate Service Failure', 'Test Scenario Title': 'Duplicate detection service fails/unreachable', 'Precondition': 'Duplicate detection service is down.', 'Test Data': "{ applicant_name: 'Test User' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to submit application when service is offline.'], 'Expected Result': "System displays error: 'Unable to check for duplicates at this time.'", 'Dependent Module/Process': 'Duplicate Detection Service'}, {'Test Case ID': '22895838-TC5', 'EPIC': 'Application Management', 'Feature': 'Duplicate Merge', 'User Story': '22895838', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Enforce Merge Privileges', 'Test Scenario Title': 'User without merge permission tries to merge', 'Precondition': 'Duplicates displayed to user with limited role.', 'Test Data': "{ user_role: 'Data Entry Clerk', duplicate_case_ids: ['300112', '300113'] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Data Entry Clerk', 'Detailed Test Steps': ['Attempt to initiate merge on detected duplicates.'], 'Expected Result': 'Merge option grayed out or access denied message shown.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': '22895838-TC6', 'EPIC': 'Application Management', 'Feature': 'Duplicate Detection', 'User Story': '22895838', 'Business Process': 'Application Intake', 'Sub-Process Title': 'Compliance', 'Activity Title': 'Audit Alert and Merge Event', 'Test Scenario Title': 'Audit log is generated on duplicate alert and merge', 'Precondition': 'Duplicate merge process is completed.', 'Test Data': "{ duplicate_case_ids: ['300111', '302589'] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Complete duplicate detection and merge as in TC3.', 'Verify audit logs for alert and merge action (user, date, case ids).'], 'Expected Result': 'Alerts and merges are logged with full audit trail.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>22895837</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>The user story ensures Case Workers receive timely alerts upon client document uploads, streamlining review processes and enabling prompt eligibility actions.</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Export single case data to Excel and verify format/fields', 'Export filtered case list (by eligibility, priority, assigned member, etc.)', 'Export large number of cases and verify performance/limits', 'Export during concurrent case assignment or escalation actions']</t>
+          <t>22895824: As a Case Worker, I want to receive alerts when a document is uploaded by a client so that I can review it promptly.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['Export when no cases are present or filtered set is empty', 'Export with cases containing non-ASCII/unusual characters', 'Export when connection is interrupted']</t>
+          <t>Case Worker is notified instantly of a new document upload and can click to open and review the file.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>['Ensure exported data includes assignment (22895817), escalation (22895827), and eligibility coordination (22895822, 22895830) statuses', 'Export after bulk updates or changes']</t>
+          <t>[{'Test Case ID': '22895824-TC1', 'Brief Description': 'Receive alert for new document uploaded by client'}, {'Test Case ID': '22895824-TC2', 'Brief Description': 'Alert links to correct case and document'}, {'Test Case ID': '22895824-TC3', 'Brief Description': 'Multiple case workers receive alert if assigned to client'}, {'Test Case ID': '22895824-TC4', 'Brief Description': 'Alert not sent for non-customer uploads (negative)'}, {'Test Case ID': '22895824-TC5', 'Brief Description': 'Document upload service fails, no alert generated (API/integration negative)'}, {'Test Case ID': '22895824-TC6', 'Brief Description': 'Regulatory/audit trail for who viewed document alerts'}]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['22895817, 22895827, 22895822, 22895830 (any field or status change should reflect in exported data)']</t>
+          <t>[{'Test Case ID': '22895824-TC1', 'EPIC': 'Document Management', 'Feature': 'Upload Notifications', 'User Story': '22895824', 'Business Process': 'Document Review', 'Sub-Process Title': 'Document Alerts', 'Activity Title': 'Notify Assigned Worker', 'Test Scenario Title': 'Case Worker receives alert when client uploads document', 'Precondition': 'Client uploads document online; case is assigned to Case Worker.', 'Test Data': "{ client_id: '500456', document_id: 'DOC123', assigned_worker: 'cwilliams' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client logs into portal and uploads document DOC123.', 'System triggers alert for assigned Case Worker.', 'Case Worker receives alert in dashboard/notification center.'], 'Expected Result': 'Case Worker receives timely alert with client/document/case references.', 'Dependent Module/Process': 'Document Upload Service'}, {'Test Case ID': '22895824-TC2', 'EPIC': 'Document Management', 'Feature': 'Upload Notifications', 'User Story': '22895824', 'Business Process': 'Document Review', 'Sub-Process Title': 'Alert Navigation', 'Activity Title': 'Link Alert to Document', 'Test Scenario Title': 'Alert links to correct case and document', 'Precondition': 'Case Worker receives document upload alert.', 'Test Data': "{ document_id: 'DOC124', case_id: '900321' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Click on document upload alert.', 'System navigates to case and highlights uploaded document.'], 'Expected Result': 'Clicking alert takes worker directly to associated file and case.', 'Dependent Module/Process': 'Case Navigation'}, {'Test Case ID': '22895824-TC3', 'EPIC': 'Document Management', 'Feature': 'Upload Notifications', 'User Story': '22895824', 'Business Process': 'Document Review', 'Sub-Process Title': 'Multiple User Assignment', 'Activity Title': 'Alert All Assigned Workers', 'Test Scenario Title': 'Multiple Case Workers receive alert for same document upload', 'Precondition': 'Case is assigned to multiple workers.', 'Test Data': "{ client_id: '500457', document_id: 'DOC125', assigned_workers: ['cwilliams', 'jjones'] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client uploads document DOC125.', 'System checks assigned users.', 'Both workers receive notification.'], 'Expected Result': 'All assigned workers are notified of the document upload.', 'Dependent Module/Process': 'Assignment Service'}, {'Test Case ID': '22895824-TC4', 'EPIC': 'Document Management', 'Feature': 'Upload Notifications', 'User Story': '22895824', 'Business Process': 'Document Review', 'Sub-Process Title': 'Negative/Edge Case', 'Activity Title': 'Non-Client Upload', 'Test Scenario Title': 'Alert not sent for document uploaded by admin/system', 'Precondition': 'System/admin user uploads document.', 'Test Data': "{ user_role: 'Admin', document_id: 'DOC126' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Admin', 'Detailed Test Steps': ['Admin uploads document to case.', 'Check whether alert is sent to Case Worker.'], 'Expected Result': 'No alert is generated for non-client submission.', 'Dependent Module/Process': 'Document Upload Service'}, {'Test Case ID': '22895824-TC5', 'EPIC': 'Document Management', 'Feature': 'Upload Notifications', 'User Story': '22895824', 'Business Process': 'Document Review', 'Sub-Process Title': 'Integration', 'Activity Title': 'Document Service Failure', 'Test Scenario Title': 'Document upload API fails; alert is not generated', 'Precondition': 'Document upload service is down.', 'Test Data': "{ client_id: '500458', document_id: 'DOC127' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client attempts to upload document while service is unavailable.'], 'Expected Result': 'Upload fails and no alert is created; user sees error.', 'Dependent Module/Process': 'Document Upload API'}, {'Test Case ID': '22895824-TC6', 'EPIC': 'Document Management', 'Feature': 'Upload Notifications', 'User Story': '22895824', 'Business Process': 'Document Review', 'Sub-Process Title': 'Audit &amp; Compliance', 'Activity Title': 'Audit Alert Views', 'Test Scenario Title': 'Viewing/documenting the alert is captured in audit trail (compliance)', 'Precondition': 'Alert is generated and worker clicks to view it.', 'Test Data': "{ worker_id: 'cwilliams', alert_id: 'ALRT001' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Worker clicks on document upload alert.', 'System records event in audit log.'], 'Expected Result': 'Audit log stores alert view with user, time, and document reference.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>22895830</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>This user story ensures Case Workers are able to record details of household composition, supporting eligibility assessments by providing actionable data on family size and relationships.</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['Filter clients by eligible status and verify result list', 'Filter by ineligible or pending status', 'Filter when no clients meet criteria', 'Combine filters (status + assigned case manager, etc.)']</t>
+          <t>22895811: As a Case Worker, I want to record household composition so that I can assess eligibility based on family size.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['Eligibility status is updated during filtering', 'Client with multiple eligibility types or pending changes', 'Filtering on very large client lists']</t>
+          <t>Case Worker enters household information; system stores and displays data for accurate eligibility checks.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>['Filtering followed by assignment (22895817)', 'Filtering for dual eligible cases and coordinating (22895822)', 'Filtering and exporting results (22895837)']</t>
+          <t>[{'Test Case ID': '22895811-TC1', 'Brief Description': 'Record household members with valid data'}, {'Test Case ID': '22895811-TC2', 'Brief Description': 'Attempt to save incomplete household (missing required fields; negative)'}, {'Test Case ID': '22895811-TC3', 'Brief Description': 'Edit existing household composition'}, {'Test Case ID': '22895811-TC4', 'Brief Description': 'Integration: API fails while saving household data (negative)'}, {'Test Case ID': '22895811-TC5', 'Brief Description': 'Verify user roles (only Case Workers/eligible roles can record household composition)'}]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['22895822 (dual eligibility coordination)', '22895837 (case export)', '22895817 (case assignment based on filter)']</t>
+          <t>[{'Test Case ID': '22895811-TC1', 'EPIC': 'Eligibility Assessment', 'Feature': 'Household Data Entry', 'User Story': '22895811', 'Business Process': 'Intake/Assessment', 'Sub-Process Title': 'Household Entry', 'Activity Title': 'Add Household Composition', 'Test Scenario Title': 'Case Worker records all household members with required details', 'Precondition': 'Case Worker logged in, relevant case selected.', 'Test Data': "{ case_id: '850012', household: [ { name: 'Sam Lee', dob: '1990-02-01', relationship: 'Head' }, { name: 'Pat Lee', dob: '2012-12-11', relationship: 'Child' } ] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open case 850012.', "Navigate to 'Household Composition' section.", "Click 'Add Member', enter all details for Sam Lee.", 'Add Pat Lee as child.', 'Save changes.'], 'Expected Result': 'Household list saved; all members show in system for eligibility rules.', 'Dependent Module/Process': 'Eligibility Engine'}, {'Test Case ID': '22895811-TC2', 'EPIC': 'Eligibility Assessment', 'Feature': 'Household Data Entry', 'User Story': '22895811', 'Business Process': 'Intake/Assessment', 'Sub-Process Title': 'Validation', 'Activity Title': 'Missing Required Fields', 'Test Scenario Title': 'System prevents save if required data missing', 'Precondition': 'Case Worker is in household entry page.', 'Test Data': "{ case_id: '850013', household: [ { name: '', dob: '2010-05-10', relationship: 'Child' } ] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to add household member with blank name.', "Click 'Save'."], 'Expected Result': 'System highlights error and blocks save until fields complete.', 'Dependent Module/Process': None}, {'Test Case ID': '22895811-TC3', 'EPIC': 'Eligibility Assessment', 'Feature': 'Household Data Entry', 'User Story': '22895811', 'Business Process': 'Intake/Assessment', 'Sub-Process Title': 'Editing', 'Activity Title': 'Edit Household', 'Test Scenario Title': 'Edit an existing household composition entry', 'Precondition': 'Household composition exists for selected case.', 'Test Data': "{ case_id: '850014', household: [ { name: 'Anna Lee', dob: '2009-09-09', relationship: 'Child' } ] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open case 850014.', "Navigate to existing household member 'Anna Lee'.", "Change relationship from 'Child' to 'Dependent'.", 'Save changes.'], 'Expected Result': 'Change saved and reflected in system.', 'Dependent Module/Process': 'Eligibility Engine'}, {'Test Case ID': '22895811-TC4', 'EPIC': 'Eligibility Assessment', 'Feature': 'Household Data Entry', 'User Story': '22895811', 'Business Process': 'Intake/Assessment', 'Sub-Process Title': 'Integration', 'Activity Title': 'API Failure on Save', 'Test Scenario Title': 'Saving household triggers API error', 'Precondition': 'Backend is down on save call.', 'Test Data': "{ case_id: '850015', household: [ { name: 'John Doe', dob: '2000-01-01', relationship: 'Head' } ] }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to save household data when backend is unavailable.'], 'Expected Result': 'System displays error message and does not lose unsaved data.', 'Dependent Module/Process': 'Household Data API'}, {'Test Case ID': '22895811-TC5', 'EPIC': 'Eligibility Assessment', 'Feature': 'Household Data Entry', 'User Story': '22895811', 'Business Process': 'Intake/Assessment', 'Sub-Process Title': 'Permissions', 'Activity Title': 'Enforce Entry Permission', 'Test Scenario Title': 'Only Case Worker or higher can add household composition', 'Precondition': 'User with restricted role logged in.', 'Test Data': "{ user_role: 'Receptionist', case_id: '850016' }", 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Receptionist', 'Detailed Test Steps': ['Attempt to add or edit household data.', 'Check if access is blocked.'], 'Expected Result': 'User cannot access add or edit options for household composition.', 'Dependent Module/Process': 'RBAC'}]</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>22895843</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>This user story enables Case Workers to redact sensitive information in uploaded documents to maintain privacy, comply with data protection regulations, and ensure only authorized data is retained.</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Verify alert is generated when a case is inactive for exactly 60 days.', 'Verify alert includes relevant case details and notification to the correct Case Manager.', 'Confirm alert is not triggered for cases with activity in the last 59 days.', 'Verify alert is sent only once per inactivity period per case.', 'Confirm alert method (email, UI notification, etc.) per requirements.', 'Verify correct handling of cases that become active after an alert.', 'Test alert generation for different Case Managers, with multiple assigned cases.']</t>
+          <t>As a Case Worker, I want to redact sensitive information in uploaded documents so that I can protect privacy.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['Case inactive for 59 days, activity occurs, then another period of inactivity.', 'Case with no recorded activity at opening.', 'System downtime on scheduled alert day.', 'Case closed before 60 days ends.']</t>
+          <t>A Case Worker successfully redacts sensitive information from an uploaded document and saves the redacted version, ensuring compliance with information privacy standards.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>['Test alert delivery and notification logic shared with 22895841 and 22895814 (alert mechanisms and recipient validation).', 'Test alert list filtering/multiple alert types together (relates to 22895841 and 22895814).']</t>
+          <t>[{'Test Case ID': 'TC_22895820_01', 'Brief Description': 'Successfully redact sensitive information in a supported document type.'}, {'Test Case ID': 'TC_22895820_02', 'Brief Description': 'Attempt to redact information with insufficient permissions.'}, {'Test Case ID': 'TC_22895820_03', 'Brief Description': 'Redact an unsupported file type and validate error handling.'}, {'Test Case ID': 'TC_22895820_04', 'Brief Description': 'Redact and then download/view the redacted document.'}, {'Test Case ID': 'TC_22895820_05', 'Brief Description': 'Audit trail is generated for all redaction actions.'}]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['22895841 (overdue redeterminations alert logic)', '22895814 (eligibility expiration alert logic)']</t>
+          <t>[{'Test Case ID': 'TC_22895820_01', 'EPIC': 'Case Document Management', 'Feature': 'Redaction of Sensitive Data', 'User Story': '22895820', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Document Redaction', 'Activity Title': 'Redact Document', 'Test Scenario Title': 'Redact sensitive information with permission', 'Precondition': 'Case Worker is logged in and has permission to redact documents; a supported document is uploaded to the case.', 'Test Data': 'PDF file containing PII (e.g., SSN, address)', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to the case document upload section.', 'Select a document containing sensitive information.', "Click 'Redact' and use the tool to highlight/confine the sensitive details.", 'Apply and save changes.'], 'Expected Result': 'The sensitive information is blacked out or masked in the document; the redacted version is saved and available for future use.', 'Dependent Module/Process': 'Document Storage'}, {'Test Case ID': 'TC_22895820_02', 'EPIC': 'Case Document Management', 'Feature': 'Redaction of Sensitive Data', 'User Story': '22895820', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Document Redaction', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Redact information with insufficient permissions', 'Precondition': 'User is logged in as a Viewer or with restricted permissions; document is present.', 'Test Data': 'Any supported document', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Viewer/Restricted Case Worker', 'Detailed Test Steps': ['Attempt to access the redaction feature as a user with insufficient permissions.'], 'Expected Result': 'User is denied access to redact and receives an appropriate error message or UI restriction.', 'Dependent Module/Process': 'Permissions/Role Management'}, {'Test Case ID': 'TC_22895820_03', 'EPIC': 'Case Document Management', 'Feature': 'Redaction of Sensitive Data', 'User Story': '22895820', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Document Redaction', 'Activity Title': 'Unsupported File Type Handling', 'Test Scenario Title': 'Redact unsupported file type', 'Precondition': 'Case Worker is logged in; an unsupported document is uploaded.', 'Test Data': 'Audio file or unsupported document format', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select an unsupported file type and attempt to use the redact feature.'], 'Expected Result': 'System blocks redaction and provides an error message indicating unsupported file type.', 'Dependent Module/Process': 'File Type Validation'}, {'Test Case ID': 'TC_22895820_04', 'EPIC': 'Case Document Management', 'Feature': 'Redaction of Sensitive Data', 'User Story': '22895820', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Document Redaction', 'Activity Title': 'Download/View Redacted Version', 'Test Scenario Title': 'View/download redacted document', 'Precondition': 'Document has been successfully redacted.', 'Test Data': 'Previously redacted PDF file', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Locate the redacted document.', 'Download and/or preview the document.'], 'Expected Result': 'Downloaded or previewed document does not display the redacted information.', 'Dependent Module/Process': 'Document Viewer'}, {'Test Case ID': 'TC_22895820_05', 'EPIC': 'Case Document Management', 'Feature': 'Redaction of Sensitive Data', 'User Story': '22895820', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Record Redaction Event', 'Test Scenario Title': 'Audit redaction activities', 'Precondition': 'System audit logging is enabled.', 'Test Data': 'Redaction activity', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Redact a document.', 'Access audit logs.'], 'Expected Result': 'Audit log contains user, time, redacted fields/areas, and document reference.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22895847</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>This story allows Case Workers to issue document requests to applicants, facilitating the collection of required documentation for case processing.</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>["Verify alert triggers when a caseworker's assigned cases meet or exceed the overload threshold.", 'Verify alerts are only sent to Case Managers, not caseworkers.', 'Confirm alert contains relevant details: overloaded caseworker, number of cases, list of case IDs.', 'Test alert triggers when crossing threshold due to reassignment or new cases.', 'Test for cases where multiple caseworkers become overloaded at once.', 'Ensure notifications stop if cases are reassigned below threshold.']</t>
+          <t>As a Case Worker, I want to send document requests to applicants so that they can upload missing items.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['Caseworker assigned just below threshold, receives several new cases at once.', 'Threshold changed in settings: verify system re-evaluates current assignments.', 'Caseworker becomes unavailable (on leave) while overloaded.', 'Multiple alerts for the same caseworker in short succession.']</t>
+          <t>A Case Worker sends a request for missing documents to an applicant, who then receives a notification and uploads the required items.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>['Test alert delivery &amp; notification channel logic shared with other alert stories (ensure consistent implementation across user roles).']</t>
+          <t>[{'Test Case ID': 'TC_22895818_01', 'Brief Description': 'Successfully send document request for missing documents.'}, {'Test Case ID': 'TC_22895818_02', 'Brief Description': 'Attempt to send a document request without specifying required documents.'}, {'Test Case ID': 'TC_22895818_03', 'Brief Description': 'Request sent to an invalid or inactive applicant.'}, {'Test Case ID': 'TC_22895818_04', 'Brief Description': 'Audit log generated for document request.'}]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['Related stories 22895817, 22895835 involving case assignment logic or caseworker workload.']</t>
+          <t>[{'Test Case ID': 'TC_22895818_01', 'EPIC': 'Document Request Management', 'Feature': 'Request Missing Documents', 'User Story': '22895818', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Send Document Request', 'Test Scenario Title': 'Send document request with all required fields', 'Precondition': 'Case Worker is logged in and applicant profile exists; missing documents identified.', 'Test Data': 'Applicant ID, required document list', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Select case and navigate to applicant's document section.", 'Choose missing documents to request.', 'Submit the request.'], 'Expected Result': 'Applicant receives a notification or email with requested documents listed.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_22895818_02', 'EPIC': 'Document Request Management', 'Feature': 'Request Missing Documents', 'User Story': '22895818', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Validation', 'Test Scenario Title': 'Send request without specifying document', 'Precondition': 'Case Worker is logged in and on request screen.', 'Test Data': 'Applicant ID, empty document list', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to send a request leaving the required documents field empty.'], 'Expected Result': 'System prevents the request and displays a validation error.', 'Dependent Module/Process': 'Form Validation'}, {'Test Case ID': 'TC_22895818_03', 'EPIC': 'Document Request Management', 'Feature': 'Request Missing Documents', 'User Story': '22895818', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Request Documents', 'Activity Title': 'Error Handling for Invalid Applicant', 'Test Scenario Title': 'Send request to invalid/inactive applicant', 'Precondition': 'Case Worker is logged in; applicant is marked as inactive or does not exist.', 'Test Data': 'Invalid or inactive Applicant ID', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to send a document request to an invalid/inactive applicant.'], 'Expected Result': 'Request is blocked, and an error is displayed indicating applicant status.', 'Dependent Module/Process': 'Applicant Validation'}, {'Test Case ID': 'TC_22895818_04', 'EPIC': 'Document Request Management', 'Feature': 'Request Missing Documents', 'User Story': '22895818', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Record Document Request Event', 'Test Scenario Title': 'Audit document request sent', 'Precondition': 'Audit logging enabled.', 'Test Data': 'Document request activity', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Send a document request.', 'Access audit logs.'], 'Expected Result': 'Audit log records sender, time, applicant, and requested documents.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>22895814</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>This story enables Case Workers to track the status of document submissions for each applicant, aiding workflow management and ensuring timely follow-ups.</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>["Verify alert triggers when client's eligibility is within notification window (e.g., 30 days before expiration).", 'Confirm alert includes client details, expiration date, and next steps.', 'Alert is sent only to relevant Case Manager.', 'No alert if eligibility already redetermined or extended.', 'Alert cancels if client eligibility is updated before expiration.', 'Multiple clients expiring simultaneously handled correctly.']</t>
+          <t>As a Case Worker, I want to track document submission status so that I can follow up on pending items.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['Client eligibility expiring on a holiday/weekend.', 'Eligibility extended minutes before alert is due.', 'Multiple eligibility windows per client (multiple programs).', 'Eligibility manually overridden by admin.']</t>
+          <t>Case Worker views a clear status dashboard showing pending, submitted, and missing documents for each applicant.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>['Test alert generation and recipient correctness shared with 22895841 and 22895843.', 'Multiple concurrent alerts of different types (test alert queue/rendering).']</t>
+          <t>[{'Test Case ID': 'TC_22895819_01', 'Brief Description': 'Status dashboard displays all document submission statuses correctly.'}, {'Test Case ID': 'TC_22895819_02', 'Brief Description': 'Status updates in real-time when applicant uploads documents.'}, {'Test Case ID': 'TC_22895819_03', 'Brief Description': 'Unauthorized user cannot access document status dashboard.'}, {'Test Case ID': 'TC_22895819_04', 'Brief Description': 'Audit trail logs document status changes.'}]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['22895841 (overdue redetermination and alert flow), 22895843 (alert mechanics).']</t>
+          <t>[{'Test Case ID': 'TC_22895819_01', 'EPIC': 'Document Submission Tracking', 'Feature': 'Document Status Tracking', 'User Story': '22895819', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Track Documents', 'Activity Title': 'View Submission Status', 'Test Scenario Title': 'Display all statuses correctly', 'Precondition': 'Applicant has submitted some documents; others are pending.', 'Test Data': 'Applicant profile with a mix of submitted and pending documents', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ["Navigate to applicant's case dashboard.", 'View the document submission status table.'], 'Expected Result': 'All status columns are accurate for submitted, pending, and missing documents.', 'Dependent Module/Process': 'Applicant Portal Integration'}, {'Test Case ID': 'TC_22895819_02', 'EPIC': 'Document Submission Tracking', 'Feature': 'Document Status Tracking', 'User Story': '22895819', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Track Documents', 'Activity Title': 'Status Refresh', 'Test Scenario Title': 'Real-time status update', 'Precondition': 'Applicant is uploading a document.', 'Test Data': 'Applicant uploads a pending document', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Monitor dashboard as applicant submits a document.', 'Verify the status refreshes in real-time.'], 'Expected Result': "Document is moved from 'pending' to 'submitted' instantly.", 'Dependent Module/Process': 'Real-Time Notifications'}, {'Test Case ID': 'TC_22895819_03', 'EPIC': 'Document Submission Tracking', 'Feature': 'Document Status Tracking', 'User Story': '22895819', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Track Documents', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Unauthorized access to document tracking', 'Precondition': 'User role does not have permission for tracking dashboard.', 'Test Data': "User with 'Guest' or restricted role", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest/Unauthorized Role', 'Detailed Test Steps': ['Attempt to access the document status dashboard.'], 'Expected Result': 'Access is denied and appropriate error message is displayed.', 'Dependent Module/Process': 'Permission Validation'}, {'Test Case ID': 'TC_22895819_04', 'EPIC': 'Document Submission Tracking', 'Feature': 'Document Status Tracking', 'User Story': '22895819', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Record Status Change', 'Test Scenario Title': 'Audit document status changes', 'Precondition': 'Audit logging enabled.', 'Test Data': 'Change in document status', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Trigger a document status change (e.g., document submission by applicant).', 'Access and review audit logs.'], 'Expected Result': 'Audit log includes user, time, action, and document details.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>22895841</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>This story lets Case Workers upload supporting documents to a case, ensuring cases have complete supporting documentation for administrative and legal compliance.</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Verify overdue redeterminations are correctly flagged after eligibility expiration.', 'Alert sent only once per client per overdue period.', 'Multiple overdue clients flagged in dashboard/report.', 'Redetermination completed should remove overdue flag.', 'Accurate calculation of overdue status based on eligibility date.']</t>
+          <t>As a Case Worker, I want to upload supporting documents to a case so that I can maintain complete records.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['Redetermination completed immediately after becoming overdue.', 'Multiple overdue periods tracked for same client.', 'Eligibility date modified after becoming overdue.', 'Client is transferred between Case Managers while overdue.']</t>
+          <t>A Case Worker uploads various supporting documents to a case, and they are properly stored, displayed, and linked within the case file.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>['Alerts tested for delivery, content, and recipient logic with 22895843 and 22895814.', 'Test updates to dashboard/status shared with other alerting stories.']</t>
+          <t>[{'Test Case ID': 'TC_22895815_01', 'Brief Description': 'Successfully upload supported document type.'}, {'Test Case ID': 'TC_22895815_02', 'Brief Description': 'Upload unsupported file type.'}, {'Test Case ID': 'TC_22895815_03', 'Brief Description': 'Upload large file exceeding size limit.'}, {'Test Case ID': 'TC_22895815_04', 'Brief Description': 'Audit trail for document upload.'}]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['22895814 (eligibility expiration alerts), 22895843 (inactivity alerts)']</t>
+          <t>[{'Test Case ID': 'TC_22895815_01', 'EPIC': 'Case Document Management', 'Feature': 'Document Upload', 'User Story': '22895815', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Upload Documents', 'Activity Title': 'Upload Supporting Document', 'Test Scenario Title': 'Upload supported document', 'Precondition': 'Case Worker is logged in, case is open.', 'Test Data': 'PDF, JPG document files under max file size', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Navigate to upload section of a case.', 'Select a supported document type.', 'Upload the file.'], 'Expected Result': 'Document is uploaded, linked to the case, and displayed within the case documentation section.', 'Dependent Module/Process': 'Document Storage'}, {'Test Case ID': 'TC_22895815_02', 'EPIC': 'Case Document Management', 'Feature': 'Document Upload', 'User Story': '22895815', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Upload Documents', 'Activity Title': 'Handle Unsupported File Type', 'Test Scenario Title': 'Attempt to upload unsupported file type', 'Precondition': 'Case Worker is logged in, case is open.', 'Test Data': 'EXE, ZIP, or other unsupported file formats', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to upload a file of an unsupported type.'], 'Expected Result': 'System rejects the upload and displays a validation error.', 'Dependent Module/Process': 'File Type Validation'}, {'Test Case ID': 'TC_22895815_03', 'EPIC': 'Case Document Management', 'Feature': 'Document Upload', 'User Story': '22895815', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Upload Documents', 'Activity Title': 'File Size Validation', 'Test Scenario Title': 'Upload file exceeding size limit', 'Precondition': 'Case Worker is logged in; large file available.', 'Test Data': 'PDF file &gt; maximum allowed size', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Select a file larger than the allowed size.', 'Attempt to upload.'], 'Expected Result': 'Upload is blocked, and user sees a size-limit validation error.', 'Dependent Module/Process': 'File Size Validation'}, {'Test Case ID': 'TC_22895815_04', 'EPIC': 'Case Document Management', 'Feature': 'Document Upload', 'User Story': '22895815', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Record Document Upload Event', 'Test Scenario Title': 'Audit document upload', 'Precondition': 'Audit trail enabled.', 'Test Data': 'Document upload event', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload a document.', 'Review audit trail.'], 'Expected Result': 'Upload event is recorded with user, document, timestamp, and case ID.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>22895845</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>This story ensures accurate record-keeping by allowing Case Workers to verify applicant identities using government-issued IDs, enhancing case integrity and reducing fraud.</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['Verify escalated case count matches number of cases with escalation flag.', 'Count and summary appear correctly on reporting dashboard.', 'Trend reporting accurately reflects changes in escalated case volume over time.', 'Cases can be escalated and de-escalated and counts update accordingly.', 'Multiple escalation reasons are handled correctly.']</t>
+          <t>As a Case Worker, I want to verify applicant identity using government ID so that I can ensure accurate records.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['Case escalated, de-escalated, then escalated again; ensure correct historical trends.', 'Bulk escalation or de-escalation events.', 'Escalated case is closed or reassigned.']</t>
+          <t>A Case Worker receives a scan or photo of a government ID, compares the details with the applicant record, and confirms the identity.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>['Test dashboard/reporting rendering and refresh across data changes (may overlap with related escalation/urgency stories).', 'Validation of escalation flag logic could be shared if escalation is used in other stories.']</t>
+          <t>[{'Test Case ID': 'TC_22895809_01', 'Brief Description': 'Successfully verify identity using valid government ID.'}, {'Test Case ID': 'TC_22895809_02', 'Brief Description': 'Attempt verification with expired or invalid ID.'}, {'Test Case ID': 'TC_22895809_03', 'Brief Description': 'Verify identity when government ID does not match applicant details.'}, {'Test Case ID': 'TC_22895809_04', 'Brief Description': 'Audit trail generated for each identity verification.'}]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['22895827 (if escalated case logic or reporting is reused), any reporting dashboards using escalated case count.']</t>
+          <t>[{'Test Case ID': 'TC_22895809_01', 'EPIC': 'Applicant Verification', 'Feature': 'Identity Verification', 'User Story': '22895809', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Applicant Verification', 'Activity Title': 'Verify Identity', 'Test Scenario Title': 'Verify identity with valid government ID', 'Precondition': 'Applicant government ID is uploaded; applicant details are present in the system.', 'Test Data': 'Valid government-issued ID (driver license, passport) matching applicant details', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open applicant record.', 'Access uploaded government ID.', 'Compare ID details with applicant record.', 'Confirm identity.'], 'Expected Result': 'Identity verification is marked as successful, and case progress continues.', 'Dependent Module/Process': 'Document Storage'}, {'Test Case ID': 'TC_22895809_02', 'EPIC': 'Applicant Verification', 'Feature': 'Identity Verification', 'User Story': '22895809', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Applicant Verification', 'Activity Title': 'Invalid/Expired ID Handling', 'Test Scenario Title': 'Verification with expired/invalid ID', 'Precondition': 'Uploaded government ID is expired or invalid.', 'Test Data': 'Expired driver license; fake document', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open applicant record.', 'Attempt verification using expired/invalid ID.'], 'Expected Result': 'Verification fails with a message indicating ID is expired/invalid. Case is flagged for further review.', 'Dependent Module/Process': 'Document Validation'}, {'Test Case ID': 'TC_22895809_03', 'EPIC': 'Applicant Verification', 'Feature': 'Identity Verification', 'User Story': '22895809', 'Business Process': 'Case Handling', 'Sub-Process Title': 'Applicant Verification', 'Activity Title': 'Mismatched ID Handling', 'Test Scenario Title': 'ID does not match applicant details', 'Precondition': 'Uploaded ID does not match applicant profile (e.g., name or date-of-birth mismatch).', 'Test Data': 'Government ID with non-matching details', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open applicant record.', 'Attempt verification, observe mismatch.', 'Document and flag for fraud review.'], 'Expected Result': 'System warns of mismatch; verification cannot proceed; fraud review is triggered.', 'Dependent Module/Process': 'Profile Validation, Fraud Module'}, {'Test Case ID': 'TC_22895809_04', 'EPIC': 'Applicant Verification', 'Feature': 'Identity Verification', 'User Story': '22895809', 'Business Process': 'Compliance &amp; Audit', 'Sub-Process Title': 'Audit Trail', 'Activity Title': 'Record Identity Verification', 'Test Scenario Title': 'Audit identity verification', 'Precondition': 'Audit logging enabled.', 'Test Data': 'Identity verification event', 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Perform any identity verification.', 'Open audit log/report.'], 'Expected Result': 'Audit shows user, applicant, ID type, time of action, and result of verification.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>22895825</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Validate that Case Managers can assign cases to team members appropriately, balancing responsibilities based on real-time workload and permissions.</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Start tracking time when a case is opened.', 'Pause and resume time tracking on a single case.', 'Stop time tracking when a case is closed.', 'Log manual time entry/edit for a case.', 'Access time reports filtered by case, case manager, and date range.', 'Validate that time records persist across sessions.']</t>
+          <t>22895817: As a Case Manager, I want to assign cases to team members based on workload so that we can balance responsibilities.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['Multiple cases open concurrently and time tracked simultaneously.', 'Unusually long or negative time entries.', 'Time tracking interrupted by system crash or logout.', 'Leap year and daylight saving time changes during tracking.']</t>
+          <t>Case Manager assigns available case to a team member after reviewing current workloads. The system validates assignments and updates workload counts in real time.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['Integration with workload reporting (potential overlap with related stories 22895817, 22895837).']</t>
+          <t>[{'Test Case ID': 'TC_22895817_01', 'Brief Description': 'Assign a case to the team member with the lowest current workload.'}, {'Test Case ID': 'TC_22895817_02', 'Brief Description': 'Attempt to assign a case to an already overloaded team member (negative).'}, {'Test Case ID': 'TC_22895817_03', 'Brief Description': "Verify that only users with 'Case Manager' role can assign cases (permissions)."}, {'Test Case ID': 'TC_22895817_04', 'Brief Description': 'System updates workload dashboard after assignment (integration/E2E).'}]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Any workload or time reporting features (related: 22895817, 22895837).']</t>
+          <t>[{'Test Case ID': 'TC_22895817_01', 'EPIC': 'Case Assignment', 'Feature': 'Workload-based Assignment', 'User Story': '22895817', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Case', 'Activity Title': 'Select Team Member and Assign', 'Test Scenario Title': 'Assign case to least loaded team member (positive)', 'Precondition': 'Case Manager is logged in; at least two team members with different workloads exist.', 'Test Data': {'CaseID': 'C10001', 'TeamMembers': [{'UserID': 'TM1', 'CurrentWorkload': 2}, {'UserID': 'TM2', 'CurrentWorkload': 5}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["Navigate to 'Cases Pending Assignment'.", 'Open details for CaseID C10001.', 'Review current workloads for all team members.', 'Select TM1 (least workload) as assignee.', "Click 'Assign'."], 'Expected Result': "CaseID C10001 is assigned to TM1. TM1's workload increases by one. Assignment is logged and visible in audit/report.", 'Dependent Module/Process': 'Workload Dashboard'}, {'Test Case ID': 'TC_22895817_02', 'EPIC': 'Case Assignment', 'Feature': 'Workload-based Assignment', 'User Story': '22895817', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Case', 'Activity Title': 'Select Team Member and Assign', 'Test Scenario Title': 'Prevent assignment to overloaded team member (negative)', 'Precondition': 'Case Manager is logged in; at least one team member exceeds allowed workload threshold.', 'Test Data': {'CaseID': 'C10002', 'TeamMembers': [{'UserID': 'TM3', 'CurrentWorkload': 8}, {'MaxAllowedWorkload': 7}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["Navigate to 'Cases Pending Assignment'.", 'Attempt to assign CaseID C10002 to TM3.', 'Confirm assignment.'], 'Expected Result': "System displays error: 'Cannot assign case. Workload for TM3 exceeds allowed maximum.' No assignment is made.", 'Dependent Module/Process': 'Workload Validation'}, {'Test Case ID': 'TC_22895817_03', 'EPIC': 'Case Assignment', 'Feature': 'Role-based Assignment', 'User Story': '22895817', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Case', 'Activity Title': 'Permissions Check', 'Test Scenario Title': 'Only Case Managers can assign cases', 'Precondition': 'User with non-Case Manager role is logged in.', 'Test Data': {'CaseID': 'C10003'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as a Case Worker.', "Navigate to 'Cases Pending Assignment'.", 'Attempt to assign CaseID C10003 to any team member.'], 'Expected Result': "'Assign' button is disabled or an error is displayed indicating insufficient permissions.", 'Dependent Module/Process': 'Role &amp; Permissions Management'}, {'Test Case ID': 'TC_22895817_04', 'EPIC': 'Case Assignment', 'Feature': 'Assignment Integration', 'User Story': '22895817', 'Business Process': 'Case Management', 'Sub-Process Title': 'Assign Case', 'Activity Title': 'Workload Update', 'Test Scenario Title': 'Dashboard reflects updated workload after assignment', 'Precondition': 'Case successfully assigned to a team member in prior step.', 'Test Data': {'CaseID': 'C10004', 'TeamMember': {'UserID': 'TM4', 'StartingWorkload': 3}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign CaseID C10004 to TM4.', "Navigate to 'Workload Dashboard'.", "Check TM4's workload count."], 'Expected Result': "TM4's workload increases by one and is displayed in real time. Dashboard refreshes automatically or after page reload.", 'Dependent Module/Process': 'Workload Dashboard'}]</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>22895832</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Validate that Case Managers can successfully coordinate with external agencies for cases involving dual eligibility, ensuring clients get full benefits, and that coordination is adequately tracked.</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['View eligibility denial trends over different time periods (week, month, year).', 'Filter trend data by case type, program, or region.', 'Export or print trend reports.', 'Identify ‘spikes’ or anomalies in denial trends.', 'Display systemic issues or common denial reasons.']</t>
+          <t>22895822: As a Case Manager, I want to coordinate with other agencies for dual eligibility cases so that clients receive all benefits.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Periods with zero denials.', 'Sudden unexplained surge or drop in denials.', 'Incomplete or corrupted trend data.', 'Very large data sets (performance).']</t>
+          <t>Case Manager identifies dual eligibility, initiates coordination with relevant agencies, and confirms client receives all intended benefits. Coordination is logged for audit.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>['Testing eligibility denial logic with stories 22895813, 22895823.']</t>
+          <t>[{'Test Case ID': 'TC_22895822_01', 'Brief Description': 'Initiate coordination for a dual eligible case.'}, {'Test Case ID': 'TC_22895822_02', 'Brief Description': 'System prevents duplication of agency outreach (negative).'}, {'Test Case ID': 'TC_22895822_03', 'Brief Description': 'Verify audit trail captures all coordination actions (compliance).'}]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['Eligibility logic and reporting (22895813, 22895823).']</t>
+          <t>[{'Test Case ID': 'TC_22895822_01', 'EPIC': 'Case Coordination', 'Feature': 'Dual Eligibility Handling', 'User Story': '22895822', 'Business Process': 'Case Management', 'Sub-Process Title': 'External Coordination', 'Activity Title': 'Initiate Coordination', 'Test Scenario Title': 'Positive coordination invocation', 'Precondition': 'Case is marked dual eligible; Case Manager is logged in.', 'Test Data': {'CaseID': 'D20001', 'ExternalAgencies': ['AgencyA', 'AgencyB']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open dual eligible case D20001.', "Select 'Initiate Coordination'.", 'Select agencies to notify: AgencyA, AgencyB.', 'Send coordination requests.'], 'Expected Result': "Coordination requests are sent; status updates appear in case record (e.g., 'Pending Agency Response').", 'Dependent Module/Process': 'Agency Interface, Notification Service'}, {'Test Case ID': 'TC_22895822_02', 'EPIC': 'Case Coordination', 'Feature': 'Dual Eligibility Handling', 'User Story': '22895822', 'Business Process': 'Case Management', 'Sub-Process Title': 'External Coordination', 'Activity Title': 'Initiate Coordination', 'Test Scenario Title': 'Duplicate outreach is prevented (negative)', 'Precondition': "Coordination status for at least one external agency is already 'Pending' or 'Completed'.", 'Test Data': {'CaseID': 'D20002', 'AgenciesPending': ['AgencyA']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open dual eligible case D20002.', 'Attempt to initiate coordination with AgencyA again.'], 'Expected Result': "System prevents duplicate notification; error message 'Coordination already in progress/completed with AgencyA'.", 'Dependent Module/Process': 'Agency Interface, Audit Trail'}, {'Test Case ID': 'TC_22895822_03', 'EPIC': 'Case Coordination', 'Feature': 'Compliance &amp; Audit', 'User Story': '22895822', 'Business Process': 'Case Management', 'Sub-Process Title': 'External Coordination', 'Activity Title': 'Audit Capture', 'Test Scenario Title': 'All coordination steps are logged for audit', 'Precondition': 'At least one coordination action has been taken on a dual eligible case.', 'Test Data': {'CaseID': 'D20003', 'ActionTaken': 'Coordination initiated with AgencyB'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Open audit log for CaseID D20003.', 'Review entries related to agency coordination.'], 'Expected Result': 'All coordination actions (time, agency, user) are recorded and visible for audit purposes.', 'Dependent Module/Process': 'Audit Trail, Compliance Reporting'}]</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>22895828</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Confirm that Case Managers can filter clients by eligibility status and that the UI provides prioritization tools for outreach, with correct permissions and accurate filtering.</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Upload a document and confirm it is auto-validated correctly.', 'Reject a clearly invalid/incorrect document.', 'Review validation results and override if necessary.', 'Log/document the validation process.', 'Display validation errors clearly to the user.']</t>
+          <t>22895830: As a Case Manager, I want to filter clients by eligibility status so that I can prioritize outreach.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['Unsupported or corrupted file formats.', 'Oversized files or files with ambiguous content.', 'Network interruption during upload.', 'Simultaneous uploads of multiple documents.']</t>
+          <t>Case Manager accesses client list, applies eligibility status filters, and the resulting list reflects the correct clients for targeted outreach.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>['Integration with document management features (see related: 22895831, 22895836).']</t>
+          <t>[{'Test Case ID': 'TC_22895830_01', 'Brief Description': "Filter clients by 'Eligible' status."}, {'Test Case ID': 'TC_22895830_02', 'Brief Description': "Filter clients by 'Ineligible' status."}, {'Test Case ID': 'TC_22895830_03', 'Brief Description': 'Invalid filter attempt returns correct errors/messages (negative).'}, {'Test Case ID': 'TC_22895830_04', 'Brief Description': 'Verify only authorized users can use filter controls.'}]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Document upload/validation flows, manual review features (22895831, 22895836).']</t>
+          <t>[{'Test Case ID': 'TC_22895830_01', 'EPIC': 'Client Management', 'Feature': 'Eligibility Filter', 'User Story': '22895830', 'Business Process': 'Outreach Prioritization', 'Sub-Process Title': 'Filter Clients', 'Activity Title': 'Apply Filters', 'Test Scenario Title': "Filter by 'Eligible' clients (positive)", 'Precondition': 'Case Manager is logged in; client list populated.', 'Test Data': {'EligibilityStatus': 'Eligible'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Go to client management module.', "Select filter by eligibility status: 'Eligible'.", 'View client list.'], 'Expected Result': "Client list displays only those with 'Eligible' status.", 'Dependent Module/Process': 'Eligibility Service'}, {'Test Case ID': 'TC_22895830_02', 'EPIC': 'Client Management', 'Feature': 'Eligibility Filter', 'User Story': '22895830', 'Business Process': 'Outreach Prioritization', 'Sub-Process Title': 'Filter Clients', 'Activity Title': 'Apply Filters', 'Test Scenario Title': "Filter by 'Ineligible' clients", 'Precondition': 'Case Manager is logged in; client list populated.', 'Test Data': {'EligibilityStatus': 'Ineligible'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Go to client management module.', "Select filter by eligibility status: 'Ineligible'.", 'View client list.'], 'Expected Result': "Client list displays only those with 'Ineligible' status.", 'Dependent Module/Process': 'Eligibility Service'}, {'Test Case ID': 'TC_22895830_03', 'EPIC': 'Client Management', 'Feature': 'Eligibility Filter', 'User Story': '22895830', 'Business Process': 'Outreach Prioritization', 'Sub-Process Title': 'Filter Clients', 'Activity Title': 'Error Management', 'Test Scenario Title': 'Invalid filter entry (negative)', 'Precondition': 'Case Manager is logged in.', 'Test Data': {'EligibilityStatus': 'UnknownStatus'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Enter an invalid eligibility status into filter field.', 'Attempt to apply filter.'], 'Expected Result': 'System displays error or does not apply filter; user is informed of invalid entry.', 'Dependent Module/Process': 'Input Validation'}, {'Test Case ID': 'TC_22895830_04', 'EPIC': 'Client Management', 'Feature': 'Eligibility Filter Permissions', 'User Story': '22895830', 'Business Process': 'Outreach Prioritization', 'Sub-Process Title': 'Filter Clients', 'Activity Title': 'Permissions Check', 'Test Scenario Title': 'Permissions restrict filter usage', 'Precondition': 'Logged in as a user with no case management privileges.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker (no filter permission)', 'Detailed Test Steps': ['Log in as a user without filter permissions.', 'Navigate to client management module.', 'Attempt to access or use eligibility filter control.'], 'Expected Result': 'Eligibility filter controls are disabled or not visible; unauthorized usage is prevented.', 'Dependent Module/Process': 'Role &amp; Permissions Management'}]</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>22895810</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ensure Case Managers can export case data to Excel accurately, with appropriate permissions and audit logging for data extraction activities.</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['Check income eligibility with valid wage data.', 'Handle missing or incomplete wage data gracefully.', 'Validate proper calculation per current eligibility rules.', 'View income eligibility history for a case.', 'Manual override or note addition to income eligibility determination.']</t>
+          <t>22895837: As a Case Manager, I want to export case data to Excel so that I can analyze it offline.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['Conflicting sources of wage data.', 'Applicants at edge of eligibility income limits.', 'Negative, zero, or extremely high wages.', 'Eligibility checks during year-end or policy changes.']</t>
+          <t>Case Manager exports filtered or full set of case data to Excel; exported file contains correct and complete data. Export action is audit-logged.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>['Eligibility processing (overlap with 22895813, 22895809, 22895811).']</t>
+          <t>[{'Test Case ID': 'TC_22895837_01', 'Brief Description': 'Export all case data to Excel.'}, {'Test Case ID': 'TC_22895837_02', 'Brief Description': 'Export filtered (subset) case data to Excel.'}, {'Test Case ID': 'TC_22895837_03', 'Brief Description': 'Verify users without export permission cannot access export function.'}, {'Test Case ID': 'TC_22895837_04', 'Brief Description': 'Export action is audit-trailed (compliance).'}]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['Eligibility and qualification modules (22895811, 22895809, 22895813).']</t>
+          <t>[{'Test Case ID': 'TC_22895837_01', 'EPIC': 'Data Export', 'Feature': 'Export to Excel', 'User Story': '22895837', 'Business Process': 'Reporting', 'Sub-Process Title': 'Export Data', 'Activity Title': 'Export All', 'Test Scenario Title': 'Export all cases (positive)', 'Precondition': 'Case Manager is logged in; case database populated.', 'Test Data': {'Cases': [{'CaseID': 'E30001', 'Status': 'Active'}, {'CaseID': 'E30002', 'Status': 'Closed'}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["Navigate to 'Case List'.", "Click 'Export to Excel' without applying filters.", 'Download and open exported file.'], 'Expected Result': 'Exported file contains all case data as displayed; columns/fields match those in system.', 'Dependent Module/Process': 'Export Service, Audit Trail'}, {'Test Case ID': 'TC_22895837_02', 'EPIC': 'Data Export', 'Feature': 'Export to Excel', 'User Story': '22895837', 'Business Process': 'Reporting', 'Sub-Process Title': 'Export Data', 'Activity Title': 'Export Filtered', 'Test Scenario Title': 'Export filtered cases', 'Precondition': 'Case Manager is logged in; filtered view applied.', 'Test Data': {'FilterCriteria': 'Status = Active'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ["Navigate to 'Case List'.", "Apply filter for 'Active' status.", "Click 'Export to Excel'.", 'Download and check exported file.'], 'Expected Result': 'Exported file reflects only filtered cases.', 'Dependent Module/Process': 'Export Service, Filters'}, {'Test Case ID': 'TC_22895837_03', 'EPIC': 'Data Export', 'Feature': 'Export to Excel Permissions', 'User Story': '22895837', 'Business Process': 'Reporting', 'Sub-Process Title': 'Export Data', 'Activity Title': 'Permissions Check', 'Test Scenario Title': 'Non-permitted user cannot export', 'Precondition': 'Logged in as a user without export permissions.', 'Test Data': None, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker (no export perm)', 'Detailed Test Steps': ['Log in as non-Case Manager.', "Navigate to 'Case List'.", 'Verify presence/absence of export button.'], 'Expected Result': 'Export option not displayed or disabled for unauthorized users.', 'Dependent Module/Process': 'Role &amp; Permissions Management'}, {'Test Case ID': 'TC_22895837_04', 'EPIC': 'Data Export', 'Feature': 'Export Audit', 'User Story': '22895837', 'Business Process': 'Reporting', 'Sub-Process Title': 'Export Data', 'Activity Title': 'Audit Trail', 'Test Scenario Title': 'Export is logged (compliance)', 'Precondition': 'Case Manager exports data.', 'Test Data': {'UserID': 'CM1', 'Action': 'Export', 'Timestamp': '2024-06-20T09:00:00Z'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['User (CM1) performs export to Excel.', 'Open audit log as Auditor.', 'Search for export action at the specified timestamp.'], 'Expected Result': 'Export event is present in the audit trail, with user ID, timestamp, data exported.', 'Dependent Module/Process': 'Audit Trail, Compliance'}]</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>22895812</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Verify Case Managers are alerted in real time when a caseworker's workload reaches or exceeds a threshold, enabling them to promptly reassign cases to avoid overload.</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Flag an application as incomplete when mandatory fields are missing.', 'Remove the incomplete flag when fields are filled.', 'Generate notifications or alerts for incomplete applications.', 'Case Worker can view, filter, and sort by incomplete status.', 'Report on incomplete applications over a time period.']</t>
+          <t>22895847: As a Case Manager, I want to receive alerts when a caseworker is overloaded so that I can reassign cases.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['Fields that become mandatory conditionally.', 'Rapid user edits (flag must update in real time).', 'Network or save failures after flagging.']</t>
+          <t>A caseworker's workload reaches the configured limit, and the Case Manager receives an alert notification, which lists overloaded caseworkers and enables quick reassignment.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>['Application completeness and notification features (related: 22895829, 22895818).']</t>
+          <t>[{'Test Case ID': 'TC_22895847_01', 'Brief Description': 'Alert sent when caseworker workload exceeds threshold.'}, {'Test Case ID': 'TC_22895847_02', 'Brief Description': 'Verify alert contains correct caseworker and case details.'}, {'Test Case ID': 'TC_22895847_03', 'Brief Description': 'No alert sent if overload threshold not reached (negative).'}, {'Test Case ID': 'TC_22895847_04', 'Brief Description': 'Security: Only Case Managers receive overload alerts.'}]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['Application processing, notification, and status features (22895829, 22895818).']</t>
+          <t>[{'Test Case ID': 'TC_22895847_01', 'EPIC': 'Workload Monitoring', 'Feature': 'Overload Alert', 'User Story': '22895847', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Send Alert', 'Test Scenario Title': 'Overload alert is triggered (positive)', 'Precondition': 'Case manager is logged in; configurable threshold is set (e.g., 7).', 'Test Data': {'CaseworkerID': 'CW1', 'Workload': 8, 'Threshold': 7}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign cases to CW1 until workload exceeds 7.', 'Monitor incoming notifications for Case Manager.'], 'Expected Result': "Case Manager receives alert for CW1's overload.", 'Dependent Module/Process': 'Notification Service, Workload Monitor'}, {'Test Case ID': 'TC_22895847_02', 'EPIC': 'Workload Monitoring', 'Feature': 'Alert Content', 'User Story': '22895847', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Alert Details', 'Test Scenario Title': 'Alert includes case and user details', 'Precondition': 'Overload alert triggered for CW1.', 'Test Data': {'Alert': {'CaseworkerID': 'CW1', 'Cases': ['C50001', 'C50002', 'C50003', 'C50004', 'C50005', 'C50006', 'C50007', 'C50008']}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Open received alert.', 'Review its details.'], 'Expected Result': 'Alert lists CW1, their current workload count, and open case IDs for reassignment.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_22895847_03', 'EPIC': 'Workload Monitoring', 'Feature': 'Alert Suppression', 'User Story': '22895847', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Suppress Alert', 'Test Scenario Title': 'No alert when threshold not met (negative)', 'Precondition': 'Case Manager is logged in; workload at or below threshold.', 'Test Data': {'CaseworkerID': 'CW2', 'Workload': 7, 'Threshold': 7}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Assign cases to CW2 so that workload is equal to threshold.', 'Check notifications.'], 'Expected Result': 'No overload alert is sent.', 'Dependent Module/Process': 'Notification Service, Workload Monitor'}, {'Test Case ID': 'TC_22895847_04', 'EPIC': 'Workload Monitoring', 'Feature': 'Alert Permissions', 'User Story': '22895847', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Alert Notification', 'Activity Title': 'Send Alert (Restricted)', 'Test Scenario Title': 'Alerts only go to authorized users', 'Precondition': 'Overload threshold exceeded for any caseworker.', 'Test Data': {'CaseworkerID': 'CW3', 'Workload': 9}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Assign cases to CW3 so their workload exceeds threshold.', 'Login as a Case Worker.', 'Monitor notifications.', 'Login as a Case Manager.', 'Monitor notifications.'], 'Expected Result': 'Only Case Manager receives overload alert; Case Workers do not receive such alerts.', 'Dependent Module/Process': 'Notification Service, Role Management'}]</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>22895808</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>This user story focuses on proactive eligibility management by alerting case managers before client eligibility expiration, supporting timely redeterminations to maintain service continuity.</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Verify that the Case Worker can access the Medicaid application intake screen.', 'Validate all required fields are presented and labeled correctly.', 'Test that fields accept and validate proper data formats (e.g. SSN, DOB, income).', 'Ensure successful saving/submission of a new Medicaid application.', 'Check that a new application record appears in the system after submission.', 'Ensure error messages display for required fields if left blank.']</t>
+          <t>22895814: As a Case Manager, I want to receive alerts when a client's eligibility is about to expire so that I can initiate redetermination.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['Submissions with special characters in name or address fields.', 'Very large numbers or out-of-range values for income, household size etc.', 'Simultaneous submissions for the same client.', 'Submitting incomplete or invalid application data.']</t>
+          <t>When a client's eligibility is set to expire within a predefined timeframe, the system automatically generates an alert visible to the assigned case manager, triggering the redetermination workflow.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>['Test creation of a new application (also relevant if intake triggers duplicate alerts, see 22895838).', 'Field validation (should be shared if 22895808 or 22895838 adjust the intake process).']</t>
+          <t>[{'Test Case ID': 'TC_22895814_1', 'Brief Description': 'Receive alert for impending eligibility expiration'}, {'Test Case ID': 'TC_22895814_2', 'Brief Description': 'Do not receive alert for clients whose eligibility is not expiring soon'}, {'Test Case ID': 'TC_22895814_3', 'Brief Description': 'Verify alert content and actionable link'}, {'Test Case ID': 'TC_22895814_4', 'Brief Description': 'No alert for unauthorized users'}, {'Test Case ID': 'TC_22895814_5', 'Brief Description': 'Audit trail records for alert delivery (compliance)'}]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['22895816 - If the intake process changes, any downstream steps related to the eligibility process.', '22895838 - Duplicate detection (alerts/merges).']</t>
+          <t>[{'Test Case ID': 'TC_22895814_1', 'EPIC': 'Eligibility Management', 'Feature': 'Automated Alerts', 'User Story': '22895814', 'Business Process': 'Client Management', 'Sub-Process Title': 'Ongoing Eligibility Tracking', 'Activity Title': 'Eligibility Expiry Alerts', 'Test Scenario Title': 'Receive alert for impending eligibility expiration', 'Precondition': 'A client assigned to the case manager has eligibility expiring within the alert threshold (e.g., 30 days). Case manager is logged in.', 'Test Data': "{ 'client_id': 'CL123', 'eligibility_end_date': '2024-07-01', 'alert_threshold': 30 }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to client list/dashboard.', 'Set or verify client eligibility end date to within 30 days.', 'Wait for system to process daily checks or trigger manually.', 'Check alert notification area.'], 'Expected Result': 'Alert for impending eligibility expiration is displayed, containing client information and action item (e.g., link to initiate redetermination).', 'Dependent Module/Process': 'Notification Service, Client Database'}, {'Test Case ID': 'TC_22895814_2', 'EPIC': 'Eligibility Management', 'Feature': 'Automated Alerts', 'User Story': '22895814', 'Business Process': 'Client Management', 'Sub-Process Title': 'Ongoing Eligibility Tracking', 'Activity Title': 'Eligibility Expiry Alerts', 'Test Scenario Title': 'Do not receive alert for clients whose eligibility is not expiring soon', 'Precondition': 'A client with eligibility end date outside alert window (&gt;30 days).', 'Test Data': "{ 'client_id': 'CL124', 'eligibility_end_date': '2024-10-01' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to client with eligibility beyond 30 days.', 'Review alert notification area.'], 'Expected Result': 'No alert received for client; alert area remains unchanged.', 'Dependent Module/Process': 'Notification Service'}, {'Test Case ID': 'TC_22895814_3', 'EPIC': 'Eligibility Management', 'Feature': 'Automated Alerts', 'User Story': '22895814', 'Business Process': 'Client Management', 'Sub-Process Title': 'Ongoing Eligibility Tracking', 'Activity Title': 'Eligibility Expiry Alerts', 'Test Scenario Title': 'Verify alert content and actionable link', 'Precondition': 'Alert generated for a client.', 'Test Data': "{ 'client_id': 'CL125', 'eligibility_end_date': '2024-06-20' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Locate and open the alert.', 'Review message content, expiry date, and client details.', 'Click actionable link/button in alert.'], 'Expected Result': 'Alert displays correct data; clickable element routes to redetermination initiation screen.', 'Dependent Module/Process': 'Eligibility Module, Redetermination Workflow'}, {'Test Case ID': 'TC_22895814_4', 'EPIC': 'Eligibility Management', 'Feature': 'Automated Alerts', 'User Story': '22895814', 'Business Process': 'Client Management', 'Sub-Process Title': 'Ongoing Eligibility Tracking', 'Activity Title': 'Eligibility Expiry Alerts', 'Test Scenario Title': 'No alert for unauthorized users', 'Precondition': 'User with no case manager role.', 'Test Data': "{ 'user_role': 'Intake Clerk', 'client_id': 'CL123' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Intake Clerk', 'Detailed Test Steps': ['Login as non-case manager user.', 'Check alert notification area.'], 'Expected Result': 'No eligibility expiration alert visible.', 'Dependent Module/Process': 'RBAC/Permissions'}, {'Test Case ID': 'TC_22895814_5', 'EPIC': 'Eligibility Management', 'Feature': 'Automated Alerts', 'User Story': '22895814', 'Business Process': 'Client Management', 'Sub-Process Title': 'Ongoing Eligibility Tracking', 'Activity Title': 'Eligibility Expiry Alerts', 'Test Scenario Title': 'Audit trail records for alert delivery (compliance)', 'Precondition': 'System audit logging enabled.', 'Test Data': "{ 'client_id': 'CL123', 'alert_id': 'ALRT001' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System Auditor', 'Detailed Test Steps': ['Trigger alert for eligibility expiration.', 'Access audit trail/logs.', 'Review entry for alert delivery with timestamp, recipient, client info.'], 'Expected Result': 'Audit log contains complete, immutable record of alert sent to proper user, supporting regulatory requirements.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>22895826</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>This user story enables time tracking per case, allowing case managers to monitor and report their workload accurately, improving resource allocation and compliance with reporting standards.</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['Verify availability of the print checklist function.', 'Ensure that checklist includes all document types and correct items based on application type.', 'Test printing from different browsers/OS.', 'Validate downloaded/printed checklist output format.', 'Check that user can print for different client scenarios (new/renewal application, household size variations).']</t>
+          <t>22895825: As a Case Manager, I want to track the time spent on each case so that I can report on workload.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['Checklist for applications with unusual requirements (e.g. multiple languages, guardianships).', 'Very large family or household size resulting in long lists.', 'Checklist printing attempts for incomplete or incorrect application data.']</t>
+          <t>A case manager starts a timer or logs time when working on a case. The system records and associates the time entry with the correct case, available for reports.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>['Print checklist UI and functionality (also applies to 22895842 for printing summary).']</t>
+          <t>[{'Test Case ID': 'TC_22895825_1', 'Brief Description': 'Log time spent on a case'}, {'Test Case ID': 'TC_22895825_2', 'Brief Description': 'Edit a previously logged time entry'}, {'Test Case ID': 'TC_22895825_3', 'Brief Description': 'Attempt to log time without proper permissions'}, {'Test Case ID': 'TC_22895825_4', 'Brief Description': 'Log time with invalid or negative duration (negative test)'}, {'Test Case ID': 'TC_22895825_5', 'Brief Description': 'View total time for each case in workload report'}]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['22895818 - If document requirements change, it might impact the checklist.', '22895842 - Shared print functionality.']</t>
+          <t>[{'Test Case ID': 'TC_22895825_1', 'EPIC': 'Case Productivity', 'Feature': 'Time Tracking', 'User Story': '22895825', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Time Entry', 'Activity Title': 'Log Time', 'Test Scenario Title': 'Log time spent on a case', 'Precondition': 'Case manager assigned to a case, system time tracking enabled.', 'Test Data': "{ 'case_id': 'CS100', 'duration': '2h', 'activity': 'Eligibility Review' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Open an assigned case.', "Click 'Log Time'.", 'Enter duration and description.', 'Submit time entry.'], 'Expected Result': 'Time entry is saved and linked to the case. Success message displayed.', 'Dependent Module/Process': 'Case Management, Reporting'}, {'Test Case ID': 'TC_22895825_2', 'EPIC': 'Case Productivity', 'Feature': 'Time Tracking', 'User Story': '22895825', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Time Entry', 'Activity Title': 'Edit Time', 'Test Scenario Title': 'Edit a previously logged time entry', 'Precondition': 'Existing time entry present.', 'Test Data': "{ 'case_id': 'CS100', 'time_entry_id': 'TE123', 'new_duration': '2.5h' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to case and view time entries.', 'Select time entry to edit.', 'Update duration and save.'], 'Expected Result': 'Time entry is updated and correctly reflected in reports.', 'Dependent Module/Process': 'Reporting'}, {'Test Case ID': 'TC_22895825_3', 'EPIC': 'Case Productivity', 'Feature': 'Time Tracking', 'User Story': '22895825', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Time Entry', 'Activity Title': 'Log Time', 'Test Scenario Title': 'Attempt to log time without proper permissions', 'Precondition': 'Logged in as user without Case Manager role.', 'Test Data': "{ 'user_role': 'Guest' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Guest', 'Detailed Test Steps': ['Login as non-case manager user.', 'Attempt to log time on any case.'], 'Expected Result': 'Access denied. No time entry is created.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': 'TC_22895825_4', 'EPIC': 'Case Productivity', 'Feature': 'Time Tracking', 'User Story': '22895825', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Time Entry', 'Activity Title': 'Log Time', 'Test Scenario Title': 'Log time with invalid or negative duration (negative test)', 'Precondition': 'User is a Case Manager.', 'Test Data': "{ 'case_id': 'CS200', 'duration': '-1h' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Select a case.', 'Attempt to log time with negative duration.', 'Submit entry.'], 'Expected Result': 'System rejects entry, displays validation error.', 'Dependent Module/Process': 'Input Validation'}, {'Test Case ID': 'TC_22895825_5', 'EPIC': 'Case Productivity', 'Feature': 'Time Tracking', 'User Story': '22895825', 'Business Process': 'Workload Management', 'Sub-Process Title': 'Reporting', 'Activity Title': 'Workload Report', 'Test Scenario Title': 'View total time for each case in workload report', 'Precondition': 'Multiple time entries for different cases.', 'Test Data': "{ 'user_id': 'CM123' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Manager', 'Detailed Test Steps': ['Login as Case Manager.', 'Navigate to reports &gt; workload.', 'Generate report for selected period.', 'Review time totals per case.'], 'Expected Result': 'Report accurately reflects time spent per case, matching logged entries.', 'Dependent Module/Process': 'Reporting'}]</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>22895842</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>This user story introduces automatic validation of uploaded documents for case workers, reducing manual review through backend validation logic and improving operational efficiency.</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['Verify user can select and print case notes summary for a given client.', 'Test that selected notes appear accurately and in order.', 'Check that formatting of printed summary is correct.', 'Ensure different note types (manual entries, system logs) display properly.', 'Test print from multiple browsers/OS.']</t>
+          <t>22895828: As a Case Worker, I want to auto-validate uploaded documents so that I can reduce manual review time.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['Notes for clients with a large number of entries.', 'Very long individual notes (multi-page).', 'Case with no notes.']</t>
+          <t>A case worker uploads a required document for a client or application. The system auto-validates content, file type, and completeness, and presents an acceptance or error message.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>['Print UI and compatibility testing (overlaps with 22895826 - printing checklist).']</t>
+          <t>[{'Test Case ID': 'TC_22895828_1', 'Brief Description': 'Valid document is auto-validated successfully'}, {'Test Case ID': 'TC_22895828_2', 'Brief Description': 'Invalid/unsupported file type is rejected (negative)'}, {'Test Case ID': 'TC_22895828_3', 'Brief Description': 'Incomplete/missing mandatory information in document triggers error'}, {'Test Case ID': 'TC_22895828_4', 'Brief Description': 'Multiple concurrent uploads correctly validated'}, {'Test Case ID': 'TC_22895828_5', 'Brief Description': 'Audit log for validation outcome'}]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['22895826 - Changes in print functionality.', 'Shared printing service or template module.']</t>
+          <t>[{'Test Case ID': 'TC_22895828_1', 'EPIC': 'Case Management', 'Feature': 'Document Upload', 'User Story': '22895828', 'Business Process': 'Intake and Verification', 'Sub-Process Title': 'Document Handling', 'Activity Title': 'Auto-Validation', 'Test Scenario Title': 'Valid document is auto-validated successfully', 'Precondition': 'User logged in as case worker. Document meets format and content requirements.', 'Test Data': "{ 'filename': 'id_card.pdf', 'filetype': 'pdf', 'content': 'Valid' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Initiate document upload for case.', 'Select valid document file.', 'Upload and wait for validation result.'], 'Expected Result': "Document is accepted, auto-validation status is 'success', no manual review required.", 'Dependent Module/Process': 'Document Validation Service'}, {'Test Case ID': 'TC_22895828_2', 'EPIC': 'Case Management', 'Feature': 'Document Upload', 'User Story': '22895828', 'Business Process': 'Intake and Verification', 'Sub-Process Title': 'Document Handling', 'Activity Title': 'Auto-Validation', 'Test Scenario Title': 'Invalid/unsupported file type is rejected (negative)', 'Precondition': 'User logged in as case worker. File type is not permitted.', 'Test Data': "{ 'filename': 'malware.exe', 'filetype': 'exe' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Upload document with disallowed file extension.', 'Observe system response to upload.'], 'Expected Result': 'System rejects upload, displays error stating unsupported file type.', 'Dependent Module/Process': 'Input Validation'}, {'Test Case ID': 'TC_22895828_3', 'EPIC': 'Case Management', 'Feature': 'Document Upload', 'User Story': '22895828', 'Business Process': 'Intake and Verification', 'Sub-Process Title': 'Document Handling', 'Activity Title': 'Auto-Validation', 'Test Scenario Title': 'Incomplete/missing mandatory information in document triggers error', 'Precondition': 'Document with missing fields or blurry/unreadable data.', 'Test Data': "{ 'filename': 'partial_id.jpg', 'filetype': 'jpg', 'content': 'missing fields' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload document missing required information.', 'Wait for auto-validation feedback.'], 'Expected Result': 'Validation fails; error details specify missing information.', 'Dependent Module/Process': 'Document Parsing/Validation Service'}, {'Test Case ID': 'TC_22895828_4', 'EPIC': 'Case Management', 'Feature': 'Document Upload', 'User Story': '22895828', 'Business Process': 'Intake and Verification', 'Sub-Process Title': 'Document Handling', 'Activity Title': 'Auto-Validation', 'Test Scenario Title': 'Multiple concurrent uploads correctly validated', 'Precondition': 'Case worker with multiple documents to upload.', 'Test Data': "[{ 'filename': 'proof1.pdf' }, { 'filename': 'proof2.pdf' }]", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Upload first valid document.', 'While validation in progress, upload second valid document.', 'Wait for both validations to complete.'], 'Expected Result': 'Both documents are individually validated and results are independent.', 'Dependent Module/Process': 'Document Validation Service'}, {'Test Case ID': 'TC_22895828_5', 'EPIC': 'Case Management', 'Feature': 'Document Upload', 'User Story': '22895828', 'Business Process': 'Intake and Verification', 'Sub-Process Title': 'Document Handling', 'Activity Title': 'Auto-Validation', 'Test Scenario Title': 'Audit log for validation outcome', 'Precondition': 'Audit logging enabled.', 'Test Data': "{ 'filename': 'id_card.pdf' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System Auditor', 'Detailed Test Steps': ['Upload document (successful or failed validation).', 'Access audit logs.', 'Review log for validation result with timestamp and user data.'], 'Expected Result': 'Validation action is recorded in audit trail (compliance).', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>22895838</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>This user story allows case workers to flag incomplete applications, enabling prompt follow-up and enhancing the completeness rate of applicant submissions.</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['Test inputting a duplicate Medicaid application and verify that the system triggers an alert.', 'Validate detection logic for variations in client names/IDs.', 'Check that alert allows the Case Worker to view/merge duplicates.', 'Ensure alert is not triggered for non-duplicate applications.', 'Confirm merge action results in a single, unified application.']</t>
+          <t>22895812: As a Case Worker, I want to flag incomplete applications so that I can follow up with applicants.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['Near-duplicates (typos, transposed digits in SSN).', 'Concurrency: Multiple workers submitting overlapping applications at the same time.', 'Merging applications with conflicting data.']</t>
+          <t>A case worker reviews an application, identifies it as incomplete, and flags it using the system. The application status updates and is visible in case worker and applicant queues.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>['Application intake and validation (shared with 22895808).']</t>
+          <t>[{'Test Case ID': 'TC_22895812_1', 'Brief Description': 'Flag an incomplete application successfully'}, {'Test Case ID': 'TC_22895812_2', 'Brief Description': 'Flag an already completed application (negative)'}, {'Test Case ID': 'TC_22895812_3', 'Brief Description': 'Application status updated upon flagging'}, {'Test Case ID': 'TC_22895812_4', 'Brief Description': 'Unauthorized user attempts to flag application'}, {'Test Case ID': 'TC_22895812_5', 'Brief Description': 'Audit log entry for application flag (compliance)'}]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['22895808 - Changes in intake could affect duplicate logic.', '22895816, 22895833 - Any workflow that relies on accurate unique application records.']</t>
+          <t>[{'Test Case ID': 'TC_22895812_1', 'EPIC': 'Application Processing', 'Feature': 'Application Review', 'User Story': '22895812', 'Business Process': 'Application Management', 'Sub-Process Title': 'Review', 'Activity Title': 'Flag Incomplete', 'Test Scenario Title': 'Flag an incomplete application successfully', 'Precondition': 'Application submitted but missing required fields/documents.', 'Test Data': "{ 'application_id': 'APP1001', 'status': 'Incomplete', 'missing': ['proof_of_income'] }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', 'Open the incomplete application.', "Select 'Flag as Incomplete' and provide missing item details.", 'Submit flag.'], 'Expected Result': "Application is flagged, status changes to 'Incomplete', applicant and case worker are notified.", 'Dependent Module/Process': 'Notification, Application Database'}, {'Test Case ID': 'TC_22895812_2', 'EPIC': 'Application Processing', 'Feature': 'Application Review', 'User Story': '22895812', 'Business Process': 'Application Management', 'Sub-Process Title': 'Review', 'Activity Title': 'Flag Incomplete', 'Test Scenario Title': 'Flag an already completed application (negative)', 'Precondition': "Application previously marked 'Completed'.", 'Test Data': "{ 'application_id': 'APP1002', 'status': 'Completed' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Open a completed application.', 'Attempt to flag as incomplete.'], 'Expected Result': 'System prevents flagging; displays appropriate error.', 'Dependent Module/Process': 'Input Validation'}, {'Test Case ID': 'TC_22895812_3', 'EPIC': 'Application Processing', 'Feature': 'Application Review', 'User Story': '22895812', 'Business Process': 'Application Management', 'Sub-Process Title': 'Review', 'Activity Title': 'Flag Incomplete', 'Test Scenario Title': 'Application status updated upon flagging', 'Precondition': 'A submitted but incomplete application.', 'Test Data': "{ 'application_id': 'APP1003' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Flag application as incomplete.', 'View application in case worker dashboard.', 'View application status in applicant portal.'], 'Expected Result': 'Status is updated and visible to all relevant parties.', 'Dependent Module/Process': 'Applicant Portal'}, {'Test Case ID': 'TC_22895812_4', 'EPIC': 'Application Processing', 'Feature': 'Application Review', 'User Story': '22895812', 'Business Process': 'Application Management', 'Sub-Process Title': 'Review', 'Activity Title': 'Flag Incomplete', 'Test Scenario Title': 'Unauthorized user attempts to flag application', 'Precondition': 'No case worker role.', 'Test Data': "{ 'user_role': 'Applicant' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Login as applicant.', 'Attempt to flag own application as incomplete.'], 'Expected Result': 'System denies access; action not allowed.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': 'TC_22895812_5', 'EPIC': 'Application Processing', 'Feature': 'Application Review', 'User Story': '22895812', 'Business Process': 'Application Management', 'Sub-Process Title': 'Review', 'Activity Title': 'Flag Incomplete', 'Test Scenario Title': 'Audit log entry for application flag (compliance)', 'Precondition': 'Audit log enabled.', 'Test Data': "{ 'application_id': 'APP1001' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'System Auditor', 'Detailed Test Steps': ['Flag an application as incomplete.', 'Review audit logs for application events.'], 'Expected Result': 'Flagging activity and user details recorded in immutable audit log.', 'Dependent Module/Process': 'Audit Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>22895844</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>This user story covers intake of new Medicaid applications, ensuring all required data is collected and application is initiated in the eligibility process.</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Submit application with conflicting income data and verify alert is presented.', 'Ensure alert content is clear and directs worker actions.', 'Test alert persistence and resolution process.', 'Check system identifies and flags all standard income data discrepancies.', 'Ensure no alert for consistent, valid data.']</t>
+          <t>22895808: As a Case Worker, I want to intake a new Medicaid application so that I can begin the eligibility process.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['Rapidly updated applications (income updated multiple times).', 'Clients with multiple sources of income.', 'Partial/incomplete income data resulting in ambiguous conflicts.']</t>
+          <t>A case worker logs in, selects 'New Application', enters required demographic and eligibility information, saves the application, and receives confirmation.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>['Alert UI and workflow for Case Workers (if similar approaches used for 22895838).']</t>
+          <t>[{'Test Case ID': 'TC_22895808_1', 'Brief Description': 'Successful intake of new Medicaid application'}, {'Test Case ID': 'TC_22895808_2', 'Brief Description': 'Attempt to submit application with missing mandatory fields (negative)'}, {'Test Case ID': 'TC_22895808_3', 'Brief Description': 'Unauthorized user attempts application intake (permissions/compliance)'}, {'Test Case ID': 'TC_22895808_4', 'Brief Description': 'APIs correctly create new application and return expected results'}, {'Test Case ID': 'TC_22895808_5', 'Brief Description': 'Integration with eligibility process is correctly triggered'}]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['22895834 - If income data definitions change.', '22895810 - If data ingestion logic changes.']</t>
+          <t>[{'Test Case ID': 'TC_22895808_1', 'EPIC': 'Application Intake', 'Feature': 'New Application', 'User Story': '22895808', 'Business Process': 'Enrollment', 'Sub-Process Title': 'Application Submission', 'Activity Title': 'Intake', 'Test Scenario Title': 'Successful intake of new Medicaid application', 'Precondition': 'User logged in as Case Worker.', 'Test Data': "{ 'first_name': 'Jane', 'last_name': 'Doe', 'DOB': '1990-01-01', 'SSN': '123-45-6789' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Login as Case Worker.', "Navigate to 'New Application'.", 'Enter all required information.', 'Review and submit the application.'], 'Expected Result': 'Application is created, case number assigned, confirmation message received, eligibility process begins.', 'Dependent Module/Process': 'Eligibility, Application Database'}, {'Test Case ID': 'TC_22895808_2', 'EPIC': 'Application Intake', 'Feature': 'New Application', 'User Story': '22895808', 'Business Process': 'Enrollment', 'Sub-Process Title': 'Application Submission', 'Activity Title': 'Intake', 'Test Scenario Title': 'Attempt to submit application with missing mandatory fields (negative)', 'Precondition': 'Application form left incomplete.', 'Test Data': "{ 'first_name': '', 'last_name': 'Doe' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Leave one or more required fields blank.', 'Attempt to submit application.'], 'Expected Result': 'System displays validation error; application not created.', 'Dependent Module/Process': 'Input Validation'}, {'Test Case ID': 'TC_22895808_3', 'EPIC': 'Application Intake', 'Feature': 'New Application', 'User Story': '22895808', 'Business Process': 'Enrollment', 'Sub-Process Title': 'Application Submission', 'Activity Title': 'Intake', 'Test Scenario Title': 'Unauthorized user attempts application intake (permissions/compliance)', 'Precondition': "User role lacks 'Case Worker' permission.", 'Test Data': "{ 'user_role': 'Applicant' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Applicant', 'Detailed Test Steps': ['Login as non-Case Worker.', 'Attempt to create new Medicaid application.'], 'Expected Result': 'System prevents application intake, displays permission error.', 'Dependent Module/Process': 'RBAC'}, {'Test Case ID': 'TC_22895808_4', 'EPIC': 'Application Intake', 'Feature': 'New Application API', 'User Story': '22895808', 'Business Process': 'Enrollment', 'Sub-Process Title': 'Application Submission', 'Activity Title': 'API Integration', 'Test Scenario Title': 'APIs correctly create new application and return expected results', 'Precondition': 'API endpoint operational; valid authentication.', 'Test Data': "{ 'POST /api/applications': {'first_name': 'Jane', 'last_name': 'Doe', 'DOB': '1990-01-01'} }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Service Account', 'Detailed Test Steps': ['Send POST request to application creation API with valid data.', 'Check response for application ID and status.'], 'Expected Result': 'API returns 201 Created; includes application ID and status.', 'Dependent Module/Process': 'API Gateway, Application Database'}, {'Test Case ID': 'TC_22895808_5', 'EPIC': 'Application Intake', 'Feature': 'Eligibility Integration', 'User Story': '22895808', 'Business Process': 'Enrollment', 'Sub-Process Title': 'Eligibility Process', 'Activity Title': 'Start Eligibility', 'Test Scenario Title': 'Integration with eligibility process is correctly triggered', 'Precondition': 'Successful application creation.', 'Test Data': "{ 'application_id': 'APP8001' }", 'T-Code': '', 'SAP Fiori Application ID': '', 'User Role': 'Case Worker', 'Detailed Test Steps': ['Complete new application intake.', 'Check eligibility module/process for new record.', 'Confirm eligibility process status.'], 'Expected Result': 'Eligibility module/process is automatically initiated, linked to new application.', 'Dependent Module/Process': 'Eligibility Module'}]</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>22895840</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>This user story ensures that case workers are alerted whenever clients submit conflicting income data, empowering timely investigation and improved data integrity.</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['Verify that a case worker receives an alert when an eligibility rule is changed.', 'Verify the alert contains information about what rule was changed and when.', 'Test if the alert is not sent for unrelated rule changes.', 'Check notification delivery (in-app, email, SMS if supported).', 'Verify that multiple eligibility rule changes trigger the correct number of alerts.', 'Check that dismissing/acknowledging an alert marks it as read.']</t>
+          <t>As a Case Worker, I want to receive alerts when a client submits conflicting income data so that I can investigate.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['Multiple eligibility rules changed simultaneously.', 'Eligibility rule changed and then reverted before alert delivery.', 'Case worker has notification settings disabled.', 'Old/inactive case worker accounts.']</t>
+          <t>A client submits an application with income data conflicting with previously recorded information; the system detects the conflict and automatically notifies the assigned case worker.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'Test Case ID': 'TC_22895844_01', 'Brief Description': 'Alert is triggered when a client submits conflicting income data.'}, {'Test Case ID': 'TC_22895844_02', 'Brief Description': 'System does not trigger alert when income is consistent with previous data.'}, {'Test Case ID': 'TC_22895844_03', 'Brief Description': 'Multiple conflicting submissions generate separate alerts.'}, {'Test Case ID': 'TC_22895844_04', 'Brief Description': 'Case worker without proper role does not receive alert.'}, {'Test Case ID': 'TC_22895844_05', 'Brief Description': 'Audit records are created for all alert events.'}, {'Test Case ID': 'TC_22895844_06', 'Brief Description': 'System behavior when alert notification service is down.'}]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['Alerts and notifications module.', 'Case assessment workflows depending on eligibility rules.']</t>
+          <t>[{'Test Case ID': 'TC_22895844_01', 'EPIC': 'Data Integrity and Alerts', 'Feature': 'Alert for Conflicting Income Data', 'User Story': '22895844', 'Business Process': 'Client Data Submission', 'Sub-Process Title': 'Income Data Entry', 'Activity Title': 'Data Validation and Alert Generation', 'Test Scenario Title': 'Receive Alert on Conflicting Income Submission', 'Precondition': 'Client has existing record with income data; Case Worker has notification permissions.', 'Test Data': {'ExistingIncome': '40000', 'SubmittedIncome': '60000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as client and submit new application with income data differing from previous record.', 'System performs validation and compares submitted income with existing data.', 'System flags conflicting data and generates alert.', "System delivers alert to assigned Case Worker's dashboard/notification center."], 'Expected Result': 'Case Worker receives alert for client with conflicting income data, showing relevant details.', 'Dependent Module/Process': 'Notification Service, Client Database'}, {'Test Case ID': 'TC_22895844_02', 'EPIC': 'Data Integrity and Alerts', 'Feature': 'Alert for Conflicting Income Data', 'User Story': '22895844', 'Business Process': 'Client Data Submission', 'Sub-Process Title': 'Income Data Entry', 'Activity Title': 'Data Validation', 'Test Scenario Title': 'No Alert for Matching Income Data', 'Precondition': 'Client has existing record with income data.', 'Test Data': {'ExistingIncome': '40000', 'SubmittedIncome': '40000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as client and submit application with income matching previous record.', 'System performs data validation.', 'No conflict is detected.', "Check Case Worker's alert feed."], 'Expected Result': "No alert is generated in Case Worker's dashboard.", 'Dependent Module/Process': 'Notification Service, Client Database'}, {'Test Case ID': 'TC_22895844_03', 'EPIC': 'Data Integrity and Alerts', 'Feature': 'Alert for Conflicting Income Data', 'User Story': '22895844', 'Business Process': 'Client Data Submission', 'Sub-Process Title': 'Income Data Entry', 'Activity Title': 'Multiple Submissions Handling', 'Test Scenario Title': 'Multiple Conflicting Submissions Generate Alerts', 'Precondition': 'Client has existing income data.', 'Test Data': [{'SubmittedIncome': '50000'}, {'SubmittedIncome': '70000'}], 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Client submits application with conflicting income (test #1).', 'System generates alert.', 'Client resubmits with another conflicting value (test #2).', 'System generates another alert.'], 'Expected Result': 'Case Worker receives separate alerts for each conflicting submission.', 'Dependent Module/Process': 'Notification Service, Client Database'}, {'Test Case ID': 'TC_22895844_04', 'EPIC': 'Access Control', 'Feature': 'Role-based Alert Delivery', 'User Story': '22895844', 'Business Process': 'Access Management', 'Sub-Process Title': 'Alert Delivery', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Unauthorized Role Does Not Receive Alert', 'Precondition': 'User is assigned a role other than Case Worker.', 'Test Data': {'ExistingIncome': '40000', 'SubmittedIncome': '70000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Viewer', 'Detailed Test Steps': ['Client submits conflicting income data.', 'System attempts to notify users.', 'Check alert notifications for Viewer role.'], 'Expected Result': 'Viewer does not receive alert; only Case Worker is notified.', 'Dependent Module/Process': 'Access Control, Notification Service'}, {'Test Case ID': 'TC_22895844_05', 'EPIC': 'Compliance &amp; Auditability', 'Feature': 'Alert and Audit Log', 'User Story': '22895844', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Alert Events', 'Activity Title': 'Audit Trail Creation', 'Test Scenario Title': 'Audit Log Created for Alert Event', 'Precondition': 'System audit logging is enabled.', 'Test Data': {'ClientID': '12345', 'ExistingIncome': '25000', 'SubmittedIncome': '10000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Client submits application with conflicting income.', 'System triggers alert to Case Worker.', 'Access audit log as Auditor role.', 'Verify alert event entry.'], 'Expected Result': 'Alert event is present in the audit log with timestamp and related user IDs.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}, {'Test Case ID': 'TC_22895844_06', 'EPIC': 'System Resilience', 'Feature': 'Alert for Conflicting Income Data', 'User Story': '22895844', 'Business Process': 'Notification Delivery', 'Sub-Process Title': 'Error Handling', 'Activity Title': 'Service Down Scenario', 'Test Scenario Title': 'Alert Notification Fails Gracefully', 'Precondition': 'Alert delivery service is offline.', 'Test Data': {'ExistingIncome': '25000', 'SubmittedIncome': '100000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Submit conflicting income data while alert notification service is down.', 'Check for error handling and logging.', 'Check later for pending alert delivery after service resumes.'], 'Expected Result': 'System logs alert failure and retries or queues alert for later delivery; no data loss.', 'Dependent Module/Process': 'Notification Service, System Logging'}]</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>22895819</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>This story equips case workers with real-time alerts when eligibility rules change, ensuring they maintain accurate and up-to-date client assessments.</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['Verify that a case worker can see the submission status of each required document per case.', 'Ensure the status updates immediately after a document is submitted.', 'Test filtering or sorting cases by document status.', 'Check that pending documents can be easily identified.', 'Verify that following up action can be triggered from status view.', 'Test notifications/reminders for pending items.']</t>
+          <t>As a Case Worker, I want to receive alerts when eligibility rules change so that I can adjust my assessments.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['Documents submitted partially (e.g., multiple required files for one item, only some uploaded).', 'Simultaneous updates by different users.', 'Large volume of pending documents.', 'Document submitted by error, then withdrawn.']</t>
+          <t>An admin updates eligibility rules; system generates an alert to all relevant Case Workers, including rule description and effective date.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['22895818: Any shared UI or API endpoints for document status.', '22895824: Interactions when document requirements change.', '22895846: Shared tracking or notification features for documents.']</t>
+          <t>[{'Test Case ID': 'TC_22895840_01', 'Brief Description': 'Alert sent to Case Workers when eligibility rule changes.'}, {'Test Case ID': 'TC_22895840_02', 'Brief Description': 'No alert sent if non-eligibility rules are updated.'}, {'Test Case ID': 'TC_22895840_03', 'Brief Description': 'Case Workers receive only relevant rule change alerts based on assigned caseload.'}, {'Test Case ID': 'TC_22895840_04', 'Brief Description': 'Audit log includes rule change and notification events.'}, {'Test Case ID': 'TC_22895840_05', 'Brief Description': 'Role or permission restriction: unauthorized users do not receive alerts.'}]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['Document management and uploads.', 'Case overview/dashboard.', 'Notification/reminder system for documents.']</t>
+          <t>[{'Test Case ID': 'TC_22895840_01', 'EPIC': 'Eligibility Rules &amp; Notifications', 'Feature': 'Eligibility Rule Change Notification', 'User Story': '22895840', 'Business Process': 'Rule Management', 'Sub-Process Title': 'Eligibility Rules Update', 'Activity Title': 'Rule Change Alert Generation', 'Test Scenario Title': 'Case Worker Receives Alert on Eligibility Rule Change', 'Precondition': 'Eligibility rule exists; user with Case Worker role is assigned to open cases affected by the rule.', 'Test Data': {'RuleID': 'ELIG-101', 'ChangeType': 'Threshold Change', 'OldValue': 'Income &lt; 20000', 'NewValue': 'Income &lt; 25000'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Admin logs in and changes the eligibility rule threshold.', 'System updates rule database.', 'System evaluates affected clients/cases and identifies assigned Case Workers.', 'System generates and sends alert detailing the rule change to each impacted Case Worker.'], 'Expected Result': 'Case Workers receive actionable alert containing summary, effective date, and change details.', 'Dependent Module/Process': 'Rule Management, Notification Service'}, {'Test Case ID': 'TC_22895840_02', 'EPIC': 'Eligibility Rules &amp; Notifications', 'Feature': 'Eligibility Rule Change Notification', 'User Story': '22895840', 'Business Process': 'Rule Management', 'Sub-Process Title': 'Config Change Non-eligibility', 'Activity Title': 'Config Change Alert Filtering', 'Test Scenario Title': 'No Alert on Non-Eligibility Rule Change', 'Precondition': 'Other (non-eligibility) rules exist.', 'Test Data': {'RuleID': 'OTHER-102', 'ChangeType': 'Minor Revision'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Admin updates a non-eligibility rule.', 'System processes config change.', 'System checks if notification needs to be sent.'], 'Expected Result': 'No eligibility rule change alert sent to Case Workers.', 'Dependent Module/Process': 'Rule Management, Notification Service'}, {'Test Case ID': 'TC_22895840_03', 'EPIC': 'Eligibility Rules &amp; Notifications', 'Feature': 'Eligibility Rule Change Notification', 'User Story': '22895840', 'Business Process': 'Rule Management', 'Sub-Process Title': 'Rule Change Alert Filtering', 'Activity Title': 'Filtering by Case Assignment', 'Test Scenario Title': 'Alert Sent Only to Impacted Case Workers', 'Precondition': 'Multiple Case Workers assigned to different cases/clients.', 'Test Data': {'RuleID': 'ELIG-102', 'AffectedCases': ['Case-201', 'Case-202']}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Admin changes eligibility rule affecting specific clients/cases.', 'System determines impacted cases.', 'System matches assigned Case Workers for these cases.', 'Only those Case Workers receive the alert.'], 'Expected Result': 'Unimpacted Case Workers do not receive irrelevant alerts; only relevant ones are notified.', 'Dependent Module/Process': 'Rule Management, Case Assignment, Notification Service'}, {'Test Case ID': 'TC_22895840_04', 'EPIC': 'Compliance &amp; Auditability', 'Feature': 'Eligibility Rule Change Notification', 'User Story': '22895840', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Rule Change Events', 'Activity Title': 'Audit Trail Recording', 'Test Scenario Title': 'Audit Log for Rule Change and Notification', 'Precondition': 'Audit logging is enabled.', 'Test Data': {'RuleID': 'ELIG-105'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Admin changes eligibility rule.', 'Notification is sent to relevant Case Workers.', 'Auditor checks audit log entries for both rule change and alert notifications.'], 'Expected Result': 'Audit log contains entries for rule change event and notification dispatch with timestamps.', 'Dependent Module/Process': 'Audit Logging, Notification Service'}, {'Test Case ID': 'TC_22895840_05', 'EPIC': 'Access Control', 'Feature': 'Eligibility Rule Change Notification', 'User Story': '22895840', 'Business Process': 'Permission Enforcement', 'Sub-Process Title': 'Alert Delivery', 'Activity Title': 'Role Restriction', 'Test Scenario Title': 'Unauthorized Users Do Not Receive Alert', 'Precondition': 'Non-Case Worker user logged in.', 'Test Data': {'RuleID': 'ELIG-110'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Client', 'Detailed Test Steps': ['Admin changes eligibility rule.', 'Check notification feed of a non-Case Worker user (e.g., client).'], 'Expected Result': 'Client or other non-Case Worker users do not receive alerts about rule changes.', 'Dependent Module/Process': 'Rule Management, Access Control'}]</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>22895839</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Enables Case Managers to produce monthly reports on case activity, facilitating oversight, team performance tracking, and compliance reporting.</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['Generate a monthly report for case activity and verify accuracy with raw data.', 'Confirm the report includes all relevant fields (e.g., case opened/closed, activity logs).', 'Check report formatting for readability and exports (e.g., PDF, CSV).', 'Test for correct team-based access and report visibility.', 'Verify filter options (e.g., by team member, date range).']</t>
+          <t>As a Case Manager, I want to generate monthly reports of case activity so that I can track team performance.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['Month with zero activity.', 'Large volume of activity data.', 'Cases transferred between managers or teams during the reporting period.']</t>
+          <t>Case Manager selects reporting period, generates report detailing case assignments, outcomes, and activity metrics for the month.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['22895837: Verify report data consistency if activity log format changes.', '22895823: Consistency with other case activity reports.']</t>
+          <t>[{'Test Case ID': 'TC_22895839_01', 'Brief Description': 'Case Manager successfully generates and views monthly report.'}, {'Test Case ID': 'TC_22895839_02', 'Brief Description': 'Generated report contains accurate data for the selected period.'}, {'Test Case ID': 'TC_22895839_03', 'Brief Description': 'Unauthorized users cannot generate or view reports.'}, {'Test Case ID': 'TC_22895839_04', 'Brief Description': 'Report generation is logged for audit purposes.'}, {'Test Case ID': 'TC_22895839_05', 'Brief Description': 'System handles report generation gracefully under high load.'}]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['Reporting module.', 'Case activity logging functionalities.']</t>
+          <t>[{'Test Case ID': 'TC_22895839_01', 'EPIC': 'Reporting and Analytics', 'Feature': 'Monthly Case Activity Report', 'User Story': '22895839', 'Business Process': 'Reporting', 'Sub-Process Title': 'Report Generation', 'Activity Title': 'Run Monthly Report', 'Test Scenario Title': 'Generate and View Monthly Report', 'Precondition': 'Case activities are present for the current month; Case Manager is logged in.', 'Test Data': {'Month': 'June 2024', 'Team': 'Team A'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Case Manager navigates to Reports section.', "Selects 'Monthly Case Activity' report.", 'Chooses the desired month and team.', "Clicks 'Generate.'", 'System processes report and displays results.'], 'Expected Result': 'Monthly report generated and displayed, including key case activity metrics for selected team.', 'Dependent Module/Process': 'Reporting Engine, Case Management DB'}, {'Test Case ID': 'TC_22895839_02', 'EPIC': 'Reporting and Analytics', 'Feature': 'Monthly Case Activity Report', 'User Story': '22895839', 'Business Process': 'Reporting', 'Sub-Process Title': 'Report Data Validation', 'Activity Title': 'Validate Report Content', 'Test Scenario Title': 'Generated Report Data Accuracy', 'Precondition': 'Case transactions occurred in reported month.', 'Test Data': {'ReportedMonth': 'June 2024'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Generate monthly report for June 2024.', 'Review report data, cross-verify against raw case activity logs.'], 'Expected Result': 'Report data matches actual case activity logs for reported month.', 'Dependent Module/Process': 'Reporting Engine, Case Management DB'}, {'Test Case ID': 'TC_22895839_03', 'EPIC': 'Security &amp; Permissions', 'Feature': 'Monthly Case Activity Report', 'User Story': '22895839', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role-based Access', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'Unauthorized User Cannot Generate/View Report', 'Precondition': 'User has role other than Case Manager.', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as non-Case Manager (e.g., Case Worker).', 'Navigate to Reports section, try to access or generate Monthly Case Activity report.'], 'Expected Result': 'Access is denied; user cannot generate or view report.', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'TC_22895839_04', 'EPIC': 'Compliance &amp; Auditability', 'Feature': 'Monthly Case Activity Report', 'User Story': '22895839', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Report Generation Events', 'Activity Title': 'Audit Trail Recording', 'Test Scenario Title': 'Report Generation Is Logged', 'Precondition': 'Audit logging enabled.', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Generate monthly report as Case Manager.', 'Log in as Auditor, check audit logs.'], 'Expected Result': 'Audit log contains entry documenting report generation event with user ID and timestamp.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC_22895839_05', 'EPIC': 'System Resilience', 'Feature': 'Monthly Case Activity Report', 'User Story': '22895839', 'Business Process': 'Reporting', 'Sub-Process Title': 'Performance Testing', 'Activity Title': 'High Load Scenario', 'Test Scenario Title': 'Handle High Load During Report Generation', 'Precondition': 'High number of concurrent report requests.', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Simulate concurrent report generation attempts by multiple Case Managers.', 'Observe system performance, error logs, and output.', 'Verify all responses.'], 'Expected Result': 'System does not crash, provides reports or user-friendly errors as needed.', 'Dependent Module/Process': 'Reporting Engine'}]</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>22895821</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Provides Case Managers with access to all client communication logs, promoting continuity in client interactions and informed case handling.</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['Verify that case managers can access and view all communication logs for a case.', 'Ensure sorting/filtering of logs by date, client, or type is correct.', 'Test visibility permissions (only authorized users can view certain logs).', 'Check if attachment and message contents are displayed correctly.', 'Confirm integration with other case history records.']</t>
+          <t>As a Case Manager, I want to view communication logs with clients so that I can understand case history.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['Very large number of communications in a single case.', 'Corrupted or missing log entries.', 'Communication logs linked to merged/split cases.']</t>
+          <t>Case Manager accesses a case and successfully views full communication history chronologically.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'Test Case ID': 'TC_22895821_01', 'Brief Description': 'Case Manager views complete communication log for a client.'}, {'Test Case ID': 'TC_22895821_02', 'Brief Description': 'Audit log captures access to communication history.'}, {'Test Case ID': 'TC_22895821_03', 'Brief Description': 'Non-authorized users cannot access communication logs.'}, {'Test Case ID': 'TC_22895821_04', 'Brief Description': 'System handles lack of messages gracefully (empty log).'}]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['Communication logging features.', 'Case history aggregation and display.']</t>
+          <t>[{'Test Case ID': 'TC_22895821_01', 'EPIC': 'Client Interaction History', 'Feature': 'Communication Logs View', 'User Story': '22895821', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case History', 'Activity Title': 'View Communication Logs', 'Test Scenario Title': 'Case Manager Views Communication Log', 'Precondition': 'Case Manager assigned to case; communication log data present.', 'Test Data': {'ClientID': 'C-111', 'Messages': [{'Type': 'Email', 'Content': 'First contact established.'}, {'Type': 'Phone Call', 'Content': 'Discussed case options.'}]}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Navigate to assigned case.', "Open 'Communication Log' tab.", 'Scroll through and review messages.'], 'Expected Result': 'Case Manager sees all communication events in order with type, date, and content.', 'Dependent Module/Process': 'Communication Service, Case Database'}, {'Test Case ID': 'TC_22895821_02', 'EPIC': 'Compliance &amp; Auditability', 'Feature': 'Communication Logs View', 'User Story': '22895821', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'View Events', 'Activity Title': 'Audit Trail Recording for Viewing', 'Test Scenario Title': 'Access to Communication Log Is Audited', 'Precondition': 'Audit logging enabled.', 'Test Data': {'CaseID': 'CASE-2024-ABC'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Case Manager views communication log.', 'Auditor logs in and checks audit log.', 'Search for record of log access.'], 'Expected Result': "Audit log contains entry for Case Manager's access to communication log with timestamp and user info.", 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC_22895821_03', 'EPIC': 'Security &amp; Permissions', 'Feature': 'Communication Logs View', 'User Story': '22895821', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role-based Access', 'Activity Title': 'Unauthorized Access Prevention', 'Test Scenario Title': 'Unauthorized User Cannot View Communication Logs', 'Precondition': 'User is not assigned to case or does not have Case Manager/Worker role.', 'Test Data': {'UserRole': 'Client'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Client', 'Detailed Test Steps': ['Log in as a client.', 'Attempt to navigate to communication logs for a case.', 'Observe response.'], 'Expected Result': 'Client receives access denied message; communication logs not displayed.', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'TC_22895821_04', 'EPIC': 'Client Interaction History', 'Feature': 'Communication Logs View', 'User Story': '22895821', 'Business Process': 'Case Management', 'Sub-Process Title': 'Case History', 'Activity Title': 'Handle No Communications', 'Test Scenario Title': 'Display for Cases with No Communication Logs', 'Precondition': 'No messages/communications exist for selected case.', 'Test Data': {'ClientID': 'C-222', 'Messages': []}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Manager', 'Detailed Test Steps': ['Log in as Case Manager.', 'Select case with no communication log.', "Open 'Communication Log' tab."], 'Expected Result': "System displays appropriate 'No communications found' message; interface remains functional.", 'Dependent Module/Process': 'Communication Service'}]</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>22895833</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Allows Case Workers to pre-fill application forms with data from previous cases, reducing manual entry, increasing efficiency, and minimizing errors.</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['Verify that a case worker can select and pre-fill data from previous cases into a new application.', 'Check that only authorized/eligible data is pre-filled.', 'Test the ability to edit or override pre-filled fields.', 'Ensure proper loading and performance for large historical datasets.', 'Check error handling if previous case data is inconsistent or missing.']</t>
+          <t>As a Case Worker, I want to pre-fill application data from previous cases so that I can reduce data entry.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['Previous case data contains invalid or outdated fields.', 'Multiple previous cases for the same client with conflicting information.', 'No previous cases available for pre-fill.']</t>
+          <t>Case Worker starts a new application, system offers option to import/prefill data from a previous case, pre-filling relevant fields.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['22895829: Shared code/data fetching for historical records.', '22895838: Data transformation and mapping logic.']</t>
+          <t>[{'Test Case ID': 'TC_22895833_01', 'Brief Description': 'Case Worker pre-fills application data from a selected past case.'}, {'Test Case ID': 'TC_22895833_02', 'Brief Description': 'System restricts pre-filling if user lacks permissions.'}, {'Test Case ID': 'TC_22895833_03', 'Brief Description': 'System handles incompatible data gracefully.'}, {'Test Case ID': 'TC_22895833_04', 'Brief Description': 'Audit trail logs all pre-fill actions.'}, {'Test Case ID': 'TC_22895833_05', 'Brief Description': 'System prevents pre-fill from unrelated cases (different client).'}]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['New case/application workflows.', 'Historical data management.', 'Data privacy and authorization.']</t>
+          <t>[{'Test Case ID': 'TC_22895833_01', 'EPIC': 'Application Entry Optimization', 'Feature': 'Pre-fill from Previous Case', 'User Story': '22895833', 'Business Process': 'Application Management', 'Sub-Process Title': 'Data Entry', 'Activity Title': 'Pre-fill Application Data', 'Test Scenario Title': 'Pre-fill Data from Previous Case', 'Precondition': 'Case Worker has access to both previous case and new application.', 'Test Data': {'PreviousCaseID': 'CASE-1001', 'ClientID': 'CL-777', 'DataSet': {'Address': '12 Main St', 'Income': '50000', 'HouseholdSize': '3'}}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Log in as Case Worker.', 'Start new application for client CL-777.', 'Select option to pre-fill data from previous case CASE-1001.', 'System retrieves and fills data into new application.', 'Review pre-filled fields for accuracy.'], 'Expected Result': 'All relevant data from previous case is correctly populated in new application form.', 'Dependent Module/Process': 'Case Management Service, Application Service'}, {'Test Case ID': 'TC_22895833_02', 'EPIC': 'Security &amp; Permissions', 'Feature': 'Pre-fill from Previous Case', 'User Story': '22895833', 'Business Process': 'Access Control', 'Sub-Process Title': 'Role-based Access', 'Activity Title': 'Permission Enforcement', 'Test Scenario Title': 'User Without Permission Cannot Pre-fill', 'Precondition': 'User has no pre-fill permission.', 'Test Data': {'UserRole': 'External Consultant'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'External Consultant', 'Detailed Test Steps': ['Log in as External Consultant.', 'Attempt to start new application and pre-fill from previous case.', 'Observe response.'], 'Expected Result': 'Pre-fill option is disabled or access denied message is shown.', 'Dependent Module/Process': 'Access Control'}, {'Test Case ID': 'TC_22895833_03', 'EPIC': 'Application Entry Optimization', 'Feature': 'Pre-fill from Previous Case', 'User Story': '22895833', 'Business Process': 'Application Management', 'Sub-Process Title': 'Data Entry', 'Activity Title': 'Handle Incompatible Data', 'Test Scenario Title': 'System Handles Incompatible Data Formats Gracefully', 'Precondition': 'Previous and current application forms have mismatched fields.', 'Test Data': {'PreviousCaseID': 'CASE-1002', 'IncompatibleField': 'EmploymentStatus'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Start new application with form that differs from previous case structure.', 'Select to pre-fill from previous case.', 'System attempts to map fields.'], 'Expected Result': 'System imports compatible fields; unmapped fields are left blank with a warning/info message.', 'Dependent Module/Process': 'Case Management Service'}, {'Test Case ID': 'TC_22895833_04', 'EPIC': 'Compliance &amp; Auditability', 'Feature': 'Pre-fill from Previous Case', 'User Story': '22895833', 'Business Process': 'Audit Logging', 'Sub-Process Title': 'Pre-fill Events', 'Activity Title': 'Audit Trail Recording', 'Test Scenario Title': 'Pre-fill Action Audited', 'Precondition': 'Audit logging enabled.', 'Test Data': {}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Auditor', 'Detailed Test Steps': ['Case Worker uses pre-fill on a new application.', 'Auditor accesses audit log to verify event.', 'Search for pre-fill related log entries.'], 'Expected Result': 'Audit log contains clear record of pre-fill action, including user, timestamp, and source case/application.', 'Dependent Module/Process': 'Audit Logging'}, {'Test Case ID': 'TC_22895833_05', 'EPIC': 'Security &amp; Data Integrity', 'Feature': 'Pre-fill from Previous Case', 'User Story': '22895833', 'Business Process': 'Application Management', 'Sub-Process Title': 'Pre-fill Data', 'Activity Title': 'Prevent Pre-fill from Unrelated Cases', 'Test Scenario Title': 'Pre-fill Blocked from Unrelated Client Cases', 'Precondition': 'Previous case belongs to a different client.', 'Test Data': {'PreviousCaseID': 'CASE-2001', 'PreviousClientID': 'CL-888', 'CurrentClientID': 'CL-777'}, 'T-Code': None, 'SAP Fiori Application ID': None, 'User Role': 'Case Worker', 'Detailed Test Steps': ['Attempt to start application for client CL-777.', 'Try to pre-fill using data from CASE-2001 (belongs to CL-888).'], 'Expected Result': 'System prevents pre-filling; error or warning presented to user.', 'Dependent Module/Process': 'Case Management Service, Access Control'}]</t>
         </is>
       </c>
     </row>

--- a/output_test_cases.xlsx
+++ b/output_test_cases.xlsx
@@ -457,1001 +457,1001 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22895813</v>
+        <v>22895835</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['Verify that the Case Manager can access the eligibility status view for assigned clients.', 'Verify the eligibility status is displayed accurately for each client (eligible, ineligible, pending).', 'Verify filtering/sorting of clients by eligibility status.', 'Verify the date/time of the eligibility status is shown (if present).', 'Verify that eligibility status updates are reflected in real-time or after refresh.', 'Verify proper access control so only the Case Manager can view his/her clients.']</t>
+          <t>["Assign a case to a case manager whose language preference matches the client's.", 'Attempt to assign a case with no language specified for the client.', 'Assign a case where multiple case managers are eligible for the language.', "Assign a case where no case manager matches the client's language preference."]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Clients with no eligibility assessment data.', 'Clients with multiple or conflicting eligibility statuses.', 'Rapid changes in eligibility (simultaneous updates).', 'Case Manager with a very large number of clients.']</t>
+          <t>['Client has a rare or unsupported language preference.', 'Case manager profile is missing a language setting.', 'Case is updated with a new language preference after assignment.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Test eligibility data rendering, as shared with 22895823 (report generation), 22895814, and 22895832.', 'Verify consistency between eligibility status view and summary report (22895823).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['Eligibility data model (shared with 22895823, 22895832, 22895814, 22895841).', 'Case/Client access controls.']</t>
+          <t>['Case assignment logic in general', 'Case manager profile management', 'Case assignment UI']</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22895831</v>
+        <v>22895817</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['Verify that the Case Worker can select multiple cases for document upload.', 'Verify that multiple document files can be selected and are associated with the correct cases.', 'Verify progress/status indicator during bulk upload.', 'Verify successful upload displays confirmation.', 'Verify failed uploads display error information per case/file.', 'Verify uploaded documents are retrievable under the correct cases.']</t>
+          <t>['Assign a case to the team member with the lowest workload.', 'Assign a case when all team members have equal workloads.', 'Manually override assignment and select a specific team member.', 'Simulate team member workload changes and assign multiple cases to check balancing.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['Uploading documents with invalid file types.', 'Uploading more documents/files than allowed limit.', 'Files with duplicate names across different cases.', 'Case is locked or not found during upload.', 'Network failure during bulk upload.']</t>
+          <t>['All team members have the maximum workload possible.', 'Only one team member is available.', "A team member's workload data becomes corrupted or is missing."]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['File upload validation and association with cases (shared with 22895836: document preview before upload).']</t>
+          <t>['Assignment logic related to team member attributes (shared with 22895847 if it exists)']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['Document management and storage components (shared with 22895836, 22895828, 22895815).', "Cases' document association logic."]</t>
+          <t>['Case assignment logic', 'Team member workload tracking', 'Case distribution algorithms']</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22895823</v>
+        <v>22895822</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['Verify Case Worker can generate summary report for selected cases/clients.', 'Verify report includes accurate eligibility findings for all selected clients.', 'Verify report format (fields, layout) matches requirements.', 'Verify report export/download (PDF, Excel, etc.) is available.', 'Verify permission checks on report generation.']</t>
+          <t>['Initiate agency coordination on a dual eligibility case.', 'Receive confirmation of coordination from external agency.', 'Attempt coordination for a case not marked as dual eligible.', 'Track communication status for dual eligibility cases.']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['Generating a report for clients with no eligibility data.', 'Huge number of clients in report.', 'Eligibility data updates during/after report is running.']</t>
+          <t>['Agency response is delayed or not received.', 'Case changes eligibility status during coordination.', 'External agency system is down or unreachable.']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['Test eligibility data integrity and consistency (shared with 22895813, 22895832).', 'Test report export/download process.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['Eligibility calculation logic (shared with 22895813, 22895832, 22895839).', 'Eligibility summary report features.']</t>
+          <t>['Case eligibility criteria logic', 'Agency communication modules']</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22895836</v>
+        <v>22895827</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Verify that Case Worker can initiate document preview before upload.', 'Verify correct rendering of supported file types (PDF, images, docs).', 'Verify error message upon trying to preview unsupported/corrupted files.', 'Verify preview matches the actual document content.', 'Verify ability to cancel upload after preview.']</t>
+          <t>['Escalate an urgent case to the supervisor.', 'Attempt to escalate a case already marked as urgent.', 'Verify notification sent to supervisor upon escalation.', 'Supervisor resolves escalated case and marks it as handled.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['Attempting preview of large files or files with unsupported formats.', 'Previewing files with malware or embedded scripts.', 'Multiple previews in quick succession.']</t>
+          <t>['Supervisor is unavailable or on leave.', 'Multiple escalations occur simultaneously.', 'Case is de-escalated (if possible).']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['File type/size validation logic (shared with 22895831, 22895828, 22895815).']</t>
+          <t>['Notification logic between case manager and supervisor (shared with 22895845 if it exists)', 'Escalation status updates']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['Document upload component (shared with 22895831, 22895828, 22895815).', 'Preview rendering component.']</t>
+          <t>['Supervisor notification system', 'Urgency flag handling', 'Case status lifecycle']</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22895834</v>
+        <v>22895837</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Verify Case Worker is notified when household data is conflicting.', 'Verify conflicting fields (e.g., addresses, relationships) are clearly highlighted.', 'Verify alert message is clear and actionable.', 'Verify notifications trigger only for actual conflicts.', 'Verify resolution instructions or links are provided.']</t>
+          <t>['Export all case data to Excel and verify content.', 'Export filtered case list and verify correct records are exported.', 'Export when there are no cases.', 'Verify column headings and formatting in the exported file.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['Multiple conflicts in a single household.', 'Rapid updates causing intermittent or resolved conflicts.', 'Edge case where conflict is due to data from external system.']</t>
+          <t>['Case data contains special characters, emojis, or very long text.', 'Large volume export (thousands of cases).', 'User cancels export midway through process.']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['Testing notification/alert mechanism (shared with related stories 22895811, 22895844, 22895816 as per notification pattern).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['Household data model and validation rules.', 'Notification/alert infrastructure affecting related stories.']</t>
+          <t>['Data extraction module', 'Case data display/filter logic', 'Excel export utilities']</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22895846</v>
+        <v>22895830</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Verify that an alert is sent to the case worker when a client uploads a document after business hours.', 'Check that the alert includes client, document, and timestamp information.', 'Ensure an alert is NOT sent if a document is uploaded during business hours.', 'Validate the business hours definition (e.g., 9am-5pm configurable).', 'Review alert delivery mechanisms (email, dashboard, etc.).']</t>
+          <t>['Filter client list by single eligibility status and verify returned clients match selected status.', 'Select multiple eligibility statuses and verify that filtered results include only matching clients.', 'Verify default view (no filter applied) shows all clients.', 'Filter resets when user navigates away and returns.', 'Check that filtering works on paginated client lists.', 'Verify filter persists on page reload, if intended.']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['Document uploaded at exactly the start or end of business hours.', 'Case worker divided across multiple time zones.', 'Multiple documents uploaded in quick succession after hours.', 'Document upload crosses business hours threshold (e.g., starts upload before, finishes after hours).']</t>
+          <t>['No clients match selected eligibility status (empty result).', 'All clients match filter (entire list returned).', 'Client with missing eligibility data.', 'Rapidly changing filter selections.', 'Very large numbers of clients (performance).']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['Check that alerts are triggered for document upload (shared with 22895824).', 'Test alert notifications for clients uploading documents during or after business hours.']</t>
+          <t>['Verify filter integration with stories 22895813 and 22895832 for consistent client listing and filtering behavior.']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['22895824: Document upload alerting.', 'Any notification infrastructure (e.g., alert delivery used in other features).']</t>
+          <t>['22895813', '22895832']</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22895824</v>
+        <v>22895839</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['Verify that an alert is sent to a case worker whenever a client uploads a document.', 'Check the alert contains correct document, client, and timestamp details.', 'Ensure alerts are sent regardless of business hours.', 'Validate the system handles simultaneous uploads by multiple clients.']</t>
+          <t>['Generate a monthly case activity report and verify data correctness.', 'Select different months and verify reports update appropriately.', 'Attempt to generate a report when no activity occurred in that month.', 'Verify report export functionality (PDF/CSV etc., if available).', 'Report includes key metrics (cases opened/closed, activities logged, etc.).']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['Document uploaded by two clients at nearly the same time.', 'Upload fails halfway—no alert should be sent.', 'Document metadata is incomplete.']</t>
+          <t>['Month with zero case activity.', 'Edge of month (cases opened/closed at month boundary).', 'Very large volumes of case activity.', 'Incorrect or partial date selection.']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['Validate alert notification format and delivery (shared with 22895846).', 'Test alert batching/deduplication logic (if any).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['22895846: After-hours alerting.', 'Notification systems used across application.']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22895829</v>
+        <v>22895843</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['Verify that missing required fields in an application are detected.', 'Check that suggestions for completing missing fields are accurate and actionable.', 'Validate that case workers can access and apply suggestions easily.', 'Ensure suggestions do not expose sensitive information.']</t>
+          <t>['Case status flagged as inactive at exactly 60 days; alert generated to Case Manager.', 'Alert accurately references client and inactivity duration.', 'Alert for inactivity is not generated before 60 days.', 'Dismiss alert and verify it is removed from alert queue.', 'Multiple inactive cases: verify all generate separate alerts.']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['Applications with all fields completed—no suggestion shown.', 'Application missing multiple required fields.', 'Unrecognized or unexpected application fields.']</t>
+          <t>['Case reactivated just before 60 days (no alert triggered).', 'Case becomes inactive, alert is triggered, then case is reactivated (alert removed or updated).', 'Multiple cases become inactive at same time.', 'Case never has any activity.']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['Suggestion mechanism for data input (potentially shared with 22895812, 22895833).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['22895812, 22895833: If suggestion or field-checking logic changes.', 'Data validation components.']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>22895811</v>
+        <v>22895847</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Verify that household composition can be recorded and saved for a case.', 'Check that family size calculations are accurate and include all designated members.', 'Ensure household changes are tracked historically.', 'Validate that eligibility logic uses household composition correctly.']</t>
+          <t>['Caseworker exceeds overload threshold; alert is generated to Case Manager.', 'Alert includes information linking to overloaded caseworker’s cases.', 'Caseworker drops below threshold; alert is resolved or removed.', 'Threshold is customizable, and updates reflect immediately.', 'Multiple caseworkers exceed threshold, multiple alerts generated.']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['Household with zero members.', 'Large household (maximum supported size).', 'Editing/removing members after initial entry.', 'Duplicate household member entries.']</t>
+          <t>['Threshold set to 0 (all caseworkers overloaded).', 'High number of cases and simultaneous threshold breaches.', 'Case(s) assigned/unassigned rapidly around threshold.']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['Eligibility assessment based on composition (possibly shared with eligibility stories 22895834, 22895810).']</t>
+          <t>['Verify alert notification behaviors with related story 22895817 for consistency in alert delivery and removal.']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['22895834, 22895810: Eligibility determination features.', 'Client information data structures.']</t>
+          <t>['22895817']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22895820</v>
+        <v>22895814</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Verify sensitive information is detected and redacted in uploaded documents.', 'Check that non-sensitive documents are not altered.', 'Validate case worker can view redacted and original versions if permitted.', 'Ensure redaction is applied before document alerts are sent.']</t>
+          <t>['Eligibility about to expire triggers alert to Case Manager.', 'Alert clearly indicates client and expiration date.', 'Change in eligibility after alert generated updates or removes alert.', 'Multiple clients with expiring eligibility generate separate alerts.', 'User can dismiss alert and it does not reappear unless status changes again.']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['Documents with unusual formats (handwritten, images).', 'Partially detected sensitive information.', 'Multiple types of sensitive data in one document.', 'Large/complex documents with many pages.']</t>
+          <t>['Eligibility extended at last moment before expiration.', 'Eligibility expires on weekend/holiday.', 'Client with missing or malformed eligibility expiration data.']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['Redaction logic (shared with 22895815, 22895831).', 'End-to-end document upload and alert process.']</t>
+          <t>['Verify alert delivery pattern with story 22895841 for consistent notification about eligibility status.']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['22895815, 22895831: Redaction and privacy features.', 'Document upload, notification, and alert stories (22895824, 22895846).']</t>
+          <t>['22895841']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22895816</v>
+        <v>22895841</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['Search by full name returns correct applicant(s)', 'Search by partial name returns appropriate results', 'Search by full SSN returns the correct applicant', 'Search with invalid or nonexistent SSN returns no results', 'Search with blank input returns appropriate message or all applicants (if designed)', 'Search results update if applicant data is changed', 'Ensure search prevents duplicate entries based on existing applicants']</t>
+          <t>['Verify overdue redeterminations are listed for all clients when due date exceeds current date', 'Check due dates are correctly calculated and presented', 'Verify an overdue status is visually distinct', 'Test filtering and sorting of overdue redetermination list', 'Confirm only relevant cases (assigned to the user) are displayed', 'Ensure notifications/reminders for overdue redeterminations are triggered if implemented']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['Search by name with leading, trailing, or multiple spaces', 'Search by name with different capitalizations', 'Search by name with special characters or accents', 'Search by SSN with dashes, spaces, or invalid formats', 'Multiple applicants with similar names', 'SSN with fewer/more than 9 digits']</t>
+          <t>['Clients with redeterminations due today (boundary case)', 'Redetermination dates set far in the past or future', 'No overdue redeterminations for a user', 'Multiple overdue redeterminations for a single client']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>['Verify that applicant search functionality integrates with add/edit applicant workflows (related: 22895834, 22895838, 22895808)']</t>
+          <t>['Test user assignment logic (also impacts case ownership across stories)', 'Test date-based filtering (relevant for time tracking, story 22895825)']</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['22895834', '22895838', '22895808']</t>
+          <t>['22895814 - any changes in tracking logic may affect how related overdue notifications/aggregation work']</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22895818</v>
+        <v>22895845</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['Send document request to a single applicant', 'Send requests for multiple document types', 'Applicant receives notification for document request', 'Document request appears in applicant’s portal/dashboard', 'Case Worker sees status of document requests (pending/completed)', 'Error shown if trying to send request for unsupported document type']</t>
+          <t>['Verify escalated cases are counted accurately according to escalation status', 'Test reporting accuracy for number of escalated cases over time', 'Ensure escalation triggers status change and updates the count', 'Verify UI reflects current escalated cases total', 'Test data export/report functionality if available']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['Send request to invalid or inactive applicant', 'Send duplicate requests for the same document', 'Request with blank or missing document types', 'Large batch of requests sent at once', 'Applicant with no email/contact info']</t>
+          <t>['Escalated case returned to normal status', 'All or no cases escalated', 'Rapid escalate/de-escalate actions in succession']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>['Test communication/notification logic (related: 22895819, 22895824, 22895826)']</t>
+          <t>['Status change triggers workflow—test with other status-based stories (overlap with overdue, 22895841)', 'Case assignment logic applies here as well']</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['22895819', '22895824', '22895826']</t>
+          <t>["22895827 - Since it's listed as related, changes in how escalation is tracked may impact both stories"]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22895815</v>
+        <v>22895825</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Upload a single document to a case', 'Upload multiple documents to a single case', 'Support various file types (PDF, JPG, DOCX, etc.)', 'Restrict file upload size as per requirements', 'Case Worker can view uploaded documents after upload', 'Document upload fails gracefully with invalid file format']</t>
+          <t>['Verify timer/tracking starts upon opening a case and pauses/stops as expected', 'Confirm time spent matches user actions and activity', 'Check time logs are correctly attributed to cases/users', 'Test reporting calculations for average and total time', 'Verify time tracking accuracy for long-running sessions']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['Upload with corrupted file', 'Upload extremely large file', 'Upload file with special characters in name', 'Simultaneous uploads of the same document', 'Upload to a non-existent or closed case']</t>
+          <t>['Case left open/active overnight', 'Multiple users working on the same case consecutively', 'Network/session disruption impacts timing']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>['Document view and retrieval (related: 22895831, 22895836, 22895820)']</t>
+          <t>['Date/time field formatting (also relevant to overdue redetermination, 22895841)']</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['22895831', '22895836', '22895820']</t>
+          <t>['None directly, unless time-based calculations are reused in other features']</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22895809</v>
+        <v>22895821</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['Enter valid government ID returns verified status', 'Enter invalid or expired government ID returns error/failed status', 'Case Worker can review ID details before finalizing verification', 'Store verification status on applicant record', 'Attempt verification without required fields triggers error']</t>
+          <t>['Verify all client communications are correctly displayed for a case', 'Test chronological order and timestamp accuracy', 'Check for presence of all message types (SMS, email, notes, etc.)', 'Ensure secure/redacted display of sensitive information', 'Test searching/filtering log entries by keyword or date']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['ID with special characters or unusual formats', 'Two applicants with the same government ID', 'Upload blurry or partial ID image', 'Very long or very short ID numbers', 'Verification when system is offline or external service fails']</t>
+          <t>['Large volume of communication logs', 'No communication logged for a client', 'Mixed-format (text, attachments) communication entries']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>['ID verification process consistency (related: 22895810)']</t>
+          <t>['Case assignment/ownership logic', 'Date/time formatting as for other logs (see time spent, 22895825)']</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['22895810']</t>
+          <t>['None directly, unless communication data is used in other features']</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22895835</v>
+        <v>22895813</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['Assign case based on specified language preference', 'Automatic assignment when multiple agents have matching language skills', 'Fallback assignment when no agent has matching language', 'Update language preference and re-assign case', 'Display case assignments with assigned language clearly to case managers']</t>
+          <t>['Verify eligibility status displays correctly for all clients', 'Test for accurate status based on data inputs or calculations', 'Check UI accurately summarizes eligibility reasons/notes', 'Validate planned services change based on eligibility status updates', 'Confirm user permissions control visibility of eligibility details']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['Applicant specifies a rare or unsupported language', 'No available case managers at time of assignment', 'Change in agent language skills after assignment', 'Simultaneous new cases with identical preferences', 'Applicant with multiple language preferences selected']</t>
+          <t>['Clients with pending/indeterminate eligibility', 'Rapid status changes (e.g., eligible -&gt; ineligible -&gt; eligible)', 'Missing/incomplete eligibility data']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>['Case assignment rules consistency across case manager workflow (related: 22895817, 22895847)']</t>
+          <t>['User permission and access controls (general for case manager features)', 'Data refresh/sync with other client attributes (potential overlap with 22895830 if shared data model)']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['22895817', '22895847']</t>
+          <t>['22895830 - Changes in eligibility logic may impact related stories that consume/include eligibility status']</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22895817</v>
+        <v>22895832</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['Assign a new case to a team member with the lowest workload', 'Assign a case to a team member with manually adjusted workload', 'Attempt to assign a case when all members have reached their maximum case limit', 'Reassign an existing case to another team member', 'View summary of cases per team member post-assignment to verify workload balance']</t>
+          <t>['Verify that the eligibility denial trends view displays for Case Managers.', 'Check that denial reasons are aggregated and summarized accurately.', 'Test filtering trends by different time ranges (e.g., week, month, year).', 'Confirm exporting/printing of trend reports works as expected.', 'Validate that clicking on a specific denial reason drills down to relevant case lists or details.']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['Assign case when one or more team members are marked as unavailable', 'Assign case when team workload information is incomplete or delayed', 'Assign multiple cases at once to test bulk assignment logic', 'Assign a case to a member with 0 workload versus those with several assignments']</t>
+          <t>['No denials present for selected time period.', 'All denials for one reason (monocausal).', 'Rapid influx of denial data (system performance with large datasets).', 'Denials tied to edge-case reasons (typos, unexpected values).']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>['Test interactions with story 22895827 (escalation) to ensure assigned cases can be escalated', 'Verify assignment changes for cases that are to be exported (story 22895837)', 'Test efficiency when cases are filtered by eligibility (story 22895830) prior to assignment']</t>
+          <t>['Test trend-related visualizations in story 22895830, if it administers related eligibility data and reporting.']</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['22895827 (case escalation)', '22895837 (case export)', '22895825 (if relates to case reallocation/assignment logic)']</t>
+          <t>['Eligibility denial data processing (impacts 22895830).', 'Reporting and analytics components shared across the admin dashboard.']</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22895822</v>
+        <v>22895828</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Initiate coordination with another agency for a dual eligibility case', 'Log communication history with partnering agency for an eligible client', "Verify protocol followed for agencies' responses (accepted, declined, no response)"]</t>
+          <t>['Upload a valid document and verify auto-validation passes.', 'Upload a document with missing fields and verify auto-validation fails.', 'Test various supported file types (e.g., PDF, JPEG, PNG).', 'Confirm the correct error is displayed for corrupted/unsupported file uploads.', 'Check the system flags for suspected fraudulent or altered documents.']</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['Coordinate with an agency that is not yet in the system', 'Coordinate when agency response times out or fails', 'Dual eligibility for more than two agencies']</t>
+          <t>['Upload a zero-byte file.', 'Upload a document with borderline/ambiguous content (e.g., blurry scan).', 'Upload a document larger than maximum allowed size.', 'Mass upload of documents in quick succession.']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>['Test filtering of dual eligible cases (shared with 22895830), then coordinating', 'Verify that exporting dual eligibility cases (22895837) includes coordination status']</t>
+          <t>['Document upload validation (partially shared with 22895831 for upload mechanics, but validation logic is distinct).']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['22895830 (filtering eligibility status)', '22895813 (related communication/coordination features)', '22895837 (case export including agency coordination details)']</t>
+          <t>['Document management system (especially upload and metadata processing).']</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22895827</v>
+        <v>22895831</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Escalate an urgent case to a supervisor and verify notification', 'Track escalation status and resolution outcome', 'Attempt escalation for cases already handled or closed', 'Escalate both assigned and unassigned (or recently reassigned) cases']</t>
+          <t>['Bulk upload valid documents for multiple cases and confirm association with each case.', 'Attempt to upload a mixed batch (some valid, some invalid documents) and verify partial success/failure handling.', 'Validate user can see the status/results for each upload in the batch.', 'Test system response to duplicate documents within a batch.', 'Upload a very large batch and assess performance.']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['Escalate a case currently being assigned to another team member', 'Escalate multiple cases at once', 'Escalate a case with incomplete data']</t>
+          <t>['Upload a batch where all documents are invalid.', 'Uploading documents for nonexistent or closed cases.', 'Uploading identical documents to multiple cases in one batch.', 'Network interruption during bulk upload.']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>['Test with various case assignment conditions (22895817)', 'Verify escalation events are reflected in case data export (22895837)']</t>
+          <t>['Document upload mechanics (shared with 22895828).']</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['22895817 (case assignment)', '22895825 (if case reassignment or escalation flows overlap)', '22895837 (case export including escalation status)']</t>
+          <t>['Case document association logic.', 'Document upload infrastructure (shared with 22895828).']</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22895837</v>
+        <v>22895810</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Export single case data to Excel and verify format/fields', 'Export filtered case list (by eligibility, priority, assigned member, etc.)', 'Export large number of cases and verify performance/limits', 'Export during concurrent case assignment or escalation actions']</t>
+          <t>['Enter valid wage data and verify income eligibility result is calculated correctly.', 'Enter wage data at exactly the eligibility threshold.', 'Test with missing, zero, or negative wage inputs.', 'Validate recalculation when wage data is updated.', 'Check that the ineligibility reasons are displayed for non-qualifying results.']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['Export when no cases are present or filtered set is empty', 'Export with cases containing non-ASCII/unusual characters', 'Export when connection is interrupted']</t>
+          <t>['Multiple sources of wage data for same applicant.', 'Rapid updates to wage data from external sources.', 'Wage data with odd formats (e.g., foreign currency, thousands separator).', 'Test with extremely high or low wages.']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>['Ensure exported data includes assignment (22895817), escalation (22895827), and eligibility coordination (22895822, 22895830) statuses', 'Export after bulk updates or changes']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['22895817, 22895827, 22895822, 22895830 (any field or status change should reflect in exported data)']</t>
+          <t>['Applicant eligibility processing across modules.', 'Any downstream module relying on eligibility decision (e.g., denial reporting, application status).']</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22895830</v>
+        <v>22895812</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['Filter clients by eligible status and verify result list', 'Filter by ineligible or pending status', 'Filter when no clients meet criteria', 'Combine filters (status + assigned case manager, etc.)']</t>
+          <t>["Submit a fully completed application and verify it's not flagged as incomplete.", 'Submit an application missing required fields and ensure it is flagged.', 'Validate that the Case Worker receives notification or can see flagged applications.', 'Check capability to sort or filter applications by completion status.', 'Resubmit or update an application and ensure flagged status updates accordingly.']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['Eligibility status is updated during filtering', 'Client with multiple eligibility types or pending changes', 'Filtering on very large client lists']</t>
+          <t>['Application updated in partial increments (slow save).', 'Intentional omission of optional vs. required fields.', 'Large number of incomplete applications in the queue.', 'Changing required field definition during processing.']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>['Filtering followed by assignment (22895817)', 'Filtering for dual eligible cases and coordinating (22895822)', 'Filtering and exporting results (22895837)']</t>
+          <t>['Flagged/incomplete status handling with related story 22895829 (if it handles incomplete flows for applicants).']</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['22895822 (dual eligibility coordination)', '22895837 (case export)', '22895817 (case assignment based on filter)']</t>
+          <t>['Application submission and editing.', 'Notifications and dashboard filtering.']</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22895843</v>
+        <v>22895823</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Verify alert is generated when a case is inactive for exactly 60 days.', 'Verify alert includes relevant case details and notification to the correct Case Manager.', 'Confirm alert is not triggered for cases with activity in the last 59 days.', 'Verify alert is sent only once per inactivity period per case.', 'Confirm alert method (email, UI notification, etc.) per requirements.', 'Verify correct handling of cases that become active after an alert.', 'Test alert generation for different Case Managers, with multiple assigned cases.']</t>
+          <t>['Generate summary report for completed eligibility findings', 'Verify report includes all relevant fields (e.g., client info, eligibility status, dates)', 'Check PDF/print preview format if applicable', 'Download summary report', 'Present summary report to supervisor (e.g., share, email, print)', 'Ensure only finalized findings are included (exclude drafts/in-progress)']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['Case inactive for 59 days, activity occurs, then another period of inactivity.', 'Case with no recorded activity at opening.', 'System downtime on scheduled alert day.', 'Case closed before 60 days ends.']</t>
+          <t>['Generate report when no eligibility findings are available', 'Generate report for a very large set of findings', 'Attempt to generate report with incomplete/in-progress findings', 'Eligibility findings with missing or unusual data']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>['Test alert delivery and notification logic shared with 22895841 and 22895814 (alert mechanisms and recipient validation).', 'Test alert list filtering/multiple alert types together (relates to 22895841 and 22895814).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['22895841 (overdue redeterminations alert logic)', '22895814 (eligibility expiration alert logic)']</t>
+          <t>['Eligibility findings calculation logic', 'Any export, download, or print features related to findings']</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22895847</v>
+        <v>22895808</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>["Verify alert triggers when a caseworker's assigned cases meet or exceed the overload threshold.", 'Verify alerts are only sent to Case Managers, not caseworkers.', 'Confirm alert contains relevant details: overloaded caseworker, number of cases, list of case IDs.', 'Test alert triggers when crossing threshold due to reassignment or new cases.', 'Test for cases where multiple caseworkers become overloaded at once.', 'Ensure notifications stop if cases are reassigned below threshold.']</t>
+          <t>['Successfully intake a new Medicaid application with valid data', 'Field validation for all required inputs (e.g., SSN, DOB, address)', 'Verify new application appears in system after submission', 'Duplicate applications for the same individual are prevented/handled', 'System saves progress of partially completed application']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['Caseworker assigned just below threshold, receives several new cases at once.', 'Threshold changed in settings: verify system re-evaluates current assignments.', 'Caseworker becomes unavailable (on leave) while overloaded.', 'Multiple alerts for the same caseworker in short succession.']</t>
+          <t>['Submit application with missing mandatory fields', 'Intake application with special characters or extremely long text', 'Attempt intake during system outage or connection loss', 'Application for person already active in system']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>['Test alert delivery &amp; notification channel logic shared with other alert stories (ensure consistent implementation across user roles).']</t>
+          <t>['Field validation (shared with data prefill, if data is loaded into fields)', 'Save and resume functionality (shared with document preview if incorporated in workflow)']</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['Related stories 22895817, 22895835 involving case assignment logic or caseworker workload.']</t>
+          <t>['Eligibility process initiation', 'Application database storage', 'Duplicate application detection']</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22895814</v>
+        <v>22895833</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>["Verify alert triggers when client's eligibility is within notification window (e.g., 30 days before expiration).", 'Confirm alert includes client details, expiration date, and next steps.', 'Alert is sent only to relevant Case Manager.', 'No alert if eligibility already redetermined or extended.', 'Alert cancels if client eligibility is updated before expiration.', 'Multiple clients expiring simultaneously handled correctly.']</t>
+          <t>['Pre-fill new application using previous case data', 'Manually override pre-filled fields and save changes', 'Pre-fill works for cases from different time periods', 'Pre-fill skips irrelevant/outdated data', 'Verify audit/history of pre-filled versus edited fields']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['Client eligibility expiring on a holiday/weekend.', 'Eligibility extended minutes before alert is due.', 'Multiple eligibility windows per client (multiple programs).', 'Eligibility manually overridden by admin.']</t>
+          <t>['No previous cases available for the individual', 'Previous cases with missing or corrupt data', 'Conflicting data in multiple previous cases', 'Pre-fill for applicant with a name change']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>['Test alert generation and recipient correctness shared with 22895841 and 22895843.', 'Multiple concurrent alerts of different types (test alert queue/rendering).']</t>
+          <t>['Field validation (shared with new application intake)', 'Save and resume functionality (shared with application intake)']</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['22895841 (overdue redetermination and alert flow), 22895843 (alert mechanics).']</t>
+          <t>['Application intake flow (to ensure pre-fill does not break manual entry)', 'Previous case data storage']</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22895841</v>
+        <v>22895836</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Verify overdue redeterminations are correctly flagged after eligibility expiration.', 'Alert sent only once per client per overdue period.', 'Multiple overdue clients flagged in dashboard/report.', 'Redetermination completed should remove overdue flag.', 'Accurate calculation of overdue status based on eligibility date.']</t>
+          <t>['Upload a valid document and preview its content', 'Preview supported document formats (PDF, JPEG, PNG, etc.)', 'Cancel upload after preview', 'Upload and preview multiple documents', 'Verify image quality and document orientation in preview', 'Preview reflects corrections if document is re-uploaded']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['Redetermination completed immediately after becoming overdue.', 'Multiple overdue periods tracked for same client.', 'Eligibility date modified after becoming overdue.', 'Client is transferred between Case Managers while overdue.']</t>
+          <t>['Upload a corrupted or unsupported file type', 'Upload a very large document size', 'Rapid upload/removal actions', 'Preview for multi-page documents']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>['Alerts tested for delivery, content, and recipient logic with 22895843 and 22895814.', 'Test updates to dashboard/status shared with other alerting stories.']</t>
+          <t>['File upload validation (shared with document requirements checklist)']</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['22895814 (eligibility expiration alerts), 22895843 (inactivity alerts)']</t>
+          <t>['Document upload backend', 'Document management UI']</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22895845</v>
+        <v>22895826</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['Verify escalated case count matches number of cases with escalation flag.', 'Count and summary appear correctly on reporting dashboard.', 'Trend reporting accurately reflects changes in escalated case volume over time.', 'Cases can be escalated and de-escalated and counts update accordingly.', 'Multiple escalation reasons are handled correctly.']</t>
+          <t>['Print checklist when all required documents are present', 'Checklist updates based on applicant type (e.g., adult, child, family)', 'Download/print a blank checklist', 'Checklist displays in correct print layout', 'Checklist includes only needed documents (no extras)']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['Case escalated, de-escalated, then escalated again; ensure correct historical trends.', 'Bulk escalation or de-escalation events.', 'Escalated case is closed or reassigned.']</t>
+          <t>['Checklist with zero required documents', 'Checklist for applicant with unusual document requirements', 'Printing errors (out of range paper size, missing printer)', 'Special document names/characters']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>['Test dashboard/reporting rendering and refresh across data changes (may overlap with related escalation/urgency stories).', 'Validation of escalation flag logic could be shared if escalation is used in other stories.']</t>
+          <t>['Document requirements logic (shared with document upload validation)']</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['22895827 (if escalated case logic or reporting is reused), any reporting dashboards using escalated case count.']</t>
+          <t>['Document listing/generation features', 'Document requirements configuration']</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22895825</v>
+        <v>22895842</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Start tracking time when a case is opened.', 'Pause and resume time tracking on a single case.', 'Stop time tracking when a case is closed.', 'Log manual time entry/edit for a case.', 'Access time reports filtered by case, case manager, and date range.', 'Validate that time records persist across sessions.']</t>
+          <t>['Verify that the print summary option is available on the case notes page.', 'Verify that selecting print summary generates a document containing all relevant case notes.', 'Verify that the summary contains accurate and complete case notes information.', 'Verify the presence of key details such as time, date, and author within the printed summary.', 'Verify that the print formatting is compatible with standard printers.', 'Verify that confidential data is appropriately displayed or hidden as per policy.']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['Multiple cases open concurrently and time tracked simultaneously.', 'Unusually long or negative time entries.', 'Time tracking interrupted by system crash or logout.', 'Leap year and daylight saving time changes during tracking.']</t>
+          <t>['Printing summary when there are no case notes.', 'Case notes with special or non-ASCII characters.', 'Case notes with extensive length or attachments.', 'Large number of case notes (printable summary pagination or truncation).', 'User permission: attempt by user without print privilege.']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['Integration with workload reporting (potential overlap with related stories 22895817, 22895837).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Any workload or time reporting features (related: 22895817, 22895837).']</t>
+          <t>['Any existing case notes display or export features.', 'Case notes permission and confidentiality logic.']</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22895832</v>
+        <v>22895834</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['View eligibility denial trends over different time periods (week, month, year).', 'Filter trend data by case type, program, or region.', 'Export or print trend reports.', 'Identify ‘spikes’ or anomalies in denial trends.', 'Display systemic issues or common denial reasons.']</t>
+          <t>['Verify that an alert is triggered upon entry or detection of conflicting household data.', 'Verify alert content includes enough detail for investigation.', 'Verify the alert is visible to the assigned case worker.', 'Verify that resolving the data conflict (editing data) causes the alert to clear or update.', 'Verify that the alert system does not trigger false positives.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Periods with zero denials.', 'Sudden unexplained surge or drop in denials.', 'Incomplete or corrupted trend data.', 'Very large data sets (performance).']</t>
+          <t>['Multiple simultaneous conflicting fields in household data.', 'Data entered by two users at the same time creating a race condition.', 'Archived or deleted household data records during conflict detection.', 'Very large/complex household records triggering performance or missing alerts.']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>['Testing eligibility denial logic with stories 22895813, 22895823.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['Eligibility logic and reporting (22895813, 22895823).']</t>
+          <t>['Household data entry module.', 'Other alerting functionality.']</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22895828</v>
+        <v>22895838</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Upload a document and confirm it is auto-validated correctly.', 'Reject a clearly invalid/incorrect document.', 'Review validation results and override if necessary.', 'Log/document the validation process.', 'Display validation errors clearly to the user.']</t>
+          <t>['Verify that an alert is triggered when duplicate application data is detected.', 'Verify alert contains actionable information to merge applications.', 'Verify ability for a case worker to review and act upon the alert.', 'Verify the alert is not raised for legitimate non-duplicate cases.', 'If merge is performed, verify resultant application integrity.']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['Unsupported or corrupted file formats.', 'Oversized files or files with ambiguous content.', 'Network interruption during upload.', 'Simultaneous uploads of multiple documents.']</t>
+          <t>['Applications with slight variants (typos, casing differences) in personal data.', 'Multiple (3+) duplicates detected at once.', 'Applications in mid-processing when alert/deduping runs.', 'Deleted or already-merged applications.']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>['Integration with document management features (see related: 22895831, 22895836).']</t>
+          <t>['Test alert rendering and notification mechanisms shared with 22895834, 22895844, 22895846.']</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Document upload/validation flows, manual review features (22895831, 22895836).']</t>
+          <t>['Application intake/entry module.', 'Any merge/de-duplication features.', 'Related story 22895816: may require retesting to ensure integrity if deduping logic changes.']</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22895810</v>
+        <v>22895844</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['Check income eligibility with valid wage data.', 'Handle missing or incomplete wage data gracefully.', 'Validate proper calculation per current eligibility rules.', 'View income eligibility history for a case.', 'Manual override or note addition to income eligibility determination.']</t>
+          <t>['Verify alert displays when conflicting income data is submitted.', 'Verify alert details are sufficient for investigation.', 'Verify that editing income data to resolve conflict clears or updates the alert.', 'Confirm alert is sent to the correct case worker.', 'Verify alerts are not generated for valid data updates without conflict.']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['Conflicting sources of wage data.', 'Applicants at edge of eligibility income limits.', 'Negative, zero, or extremely high wages.', 'Eligibility checks during year-end or policy changes.']</t>
+          <t>['Multiple conflicting income submissions in a short period.', 'Income data from multiple external sources uploaded simultaneously.', 'Edge cases with formatting inconsistencies (e.g., currency, rounding).']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>['Eligibility processing (overlap with 22895813, 22895809, 22895811).']</t>
+          <t>['Test alert rendering and notification mechanisms shared with 22895834, 22895838, 22895846.']</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['Eligibility and qualification modules (22895811, 22895809, 22895813).']</t>
+          <t>['Income data entry and validation modules.', 'Alerting system.']</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22895812</v>
+        <v>22895846</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Flag an application as incomplete when mandatory fields are missing.', 'Remove the incomplete flag when fields are filled.', 'Generate notifications or alerts for incomplete applications.', 'Case Worker can view, filter, and sort by incomplete status.', 'Report on incomplete applications over a time period.']</t>
+          <t>['Verify alert is sent when a document is uploaded outside of business hours.', 'Verify proper identification of business hours based on locale/time zone.', 'Verify alert includes relevant document and client details.', 'Test alert visibility to correct case worker.', 'Confirm that uploads within business hours do not trigger the alert.']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['Fields that become mandatory conditionally.', 'Rapid user edits (flag must update in real time).', 'Network or save failures after flagging.']</t>
+          <t>['Daylight savings time transitions.', 'Uploads occurring exactly at the boundary of business hours (e.g., 5:00 PM sharp).', 'Simultaneous uploads by multiple clients after hours.', 'Uploads with incorrect or missing timestamps.']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>['Application completeness and notification features (related: 22895829, 22895818).']</t>
+          <t>['Test alert rendering and notification mechanisms shared with 22895834, 22895838, 22895844.', 'Document upload error handling shareable with related story 22895824.']</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['Application processing, notification, and status features (22895829, 22895818).']</t>
+          <t>['Document upload functionality.', 'Time/date handling and business hours logic.', 'Alert/notification system.']</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22895808</v>
+        <v>22895824</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Verify that the Case Worker can access the Medicaid application intake screen.', 'Validate all required fields are presented and labeled correctly.', 'Test that fields accept and validate proper data formats (e.g. SSN, DOB, income).', 'Ensure successful saving/submission of a new Medicaid application.', 'Check that a new application record appears in the system after submission.', 'Ensure error messages display for required fields if left blank.']</t>
+          <t>['Upload a document as a client; verify that assigned case worker receives alert.', 'Verify the content of the alert includes document details (uploader, doc name, timestamp).', 'Check alert delivery via all supported channels (email, in-app, SMS as applicable).', 'Ensure alert is only sent to the assigned case worker, not others.', 'Verify alert is not sent to the client uploading the document.', 'Check that repeated uploads trigger separate alerts.', 'Confirm link in alert navigates to the uploaded document.']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['Submissions with special characters in name or address fields.', 'Very large numbers or out-of-range values for income, household size etc.', 'Simultaneous submissions for the same client.', 'Submitting incomplete or invalid application data.']</t>
+          <t>['Uploading a document with the same name as an existing one.', 'Uploading an unsupported file format.', 'Uploading a document by a client not assigned to any case worker.', 'Simultaneously uploading multiple documents by the same client.', 'Uploading a very large file.', 'Network outage during upload or alert delivery.']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>['Test creation of a new application (also relevant if intake triggers duplicate alerts, see 22895838).', 'Field validation (should be shared if 22895808 or 22895838 adjust the intake process).']</t>
+          <t>[{'with': 22895846, 'cases': ['Alert delivery system: ensure alerts are properly formatted and delivered for all triggers.', 'Permissions: ensure alerts only sent to the correct users.']}]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['22895816 - If the intake process changes, any downstream steps related to the eligibility process.', '22895838 - Duplicate detection (alerts/merges).']</t>
+          <t>['22895846 (Other alerts to case workers; alert delivery system)', 'Document upload workflows']</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>22895826</v>
+        <v>22895840</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['Verify availability of the print checklist function.', 'Ensure that checklist includes all document types and correct items based on application type.', 'Test printing from different browsers/OS.', 'Validate downloaded/printed checklist output format.', 'Check that user can print for different client scenarios (new/renewal application, household size variations).']</t>
+          <t>['Trigger a change in eligibility rules; verify case worker alert is sent.', 'Verify alert includes relevant rule change details (rule name, what changed, date).', 'Ensure only affected case workers receive the alert.', 'Test alert delivery on all supported channels.', 'Verify alert not sent if rules do not change.', 'Check dismiss/defer capability in alert if applicable.']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['Checklist for applications with unusual requirements (e.g. multiple languages, guardianships).', 'Very large family or household size resulting in long lists.', 'Checklist printing attempts for incomplete or incorrect application data.']</t>
+          <t>['Changing multiple eligibility rules simultaneously.', 'Eligibility rule changes affecting no current cases.', 'Frequent rule changes in quick succession.', 'Rule change initiated and reverted quickly.', 'Case worker not assigned to any current cases.']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>['Print checklist UI and functionality (also applies to 22895842 for printing summary).']</t>
+          <t>[{'with': 22895824, 'cases': ['Alert delivery mechanism behaves consistently regardless of trigger event.', 'Only authorized users receive alerts.']}]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['22895818 - If document requirements change, it might impact the checklist.', '22895842 - Shared print functionality.']</t>
+          <t>['Alert system for all sources (including document upload alerts in 22895824)', 'Eligibility assessment workflows']</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>22895842</v>
+        <v>22895829</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['Verify user can select and print case notes summary for a given client.', 'Test that selected notes appear accurately and in order.', 'Check that formatting of printed summary is correct.', 'Ensure different note types (manual entries, system logs) display properly.', 'Test print from multiple browsers/OS.']</t>
+          <t>['Create an incomplete application; verify suggestions for all missing required fields.', 'Ensure suggestions are contextually appropriate based on the application type.', 'Suggestions update dynamically as fields are completed.', 'Suggestions display only for fields the user has permission to complete.', 'Verify suggestions are accurate when multiple fields are missing.', 'Suggestions persist after application save and reload.', 'Test suggestions on initial creation and subsequent edit.']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['Notes for clients with a large number of entries.', 'Very long individual notes (multi-page).', 'Case with no notes.']</t>
+          <t>['All required fields missing.', 'All fields complete except one.', 'Application with optional missing fields only.', 'Rapidly toggling field completion status.', 'Field data entered but fails validation (still triggers suggestion).']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>['Print UI and compatibility testing (overlaps with 22895826 - printing checklist).']</t>
+          <t>[{'with': 22895812, 'cases': ['Suggestion engine generates notifications for missing data in application forms.', 'Field-level validation and completion triggers.']}]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['22895826 - Changes in print functionality.', 'Shared printing service or template module.']</t>
+          <t>['Suggestion engine (shared with 22895812)', 'Application form validation and completion tracking']</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>22895838</v>
+        <v>22895811</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['Test inputting a duplicate Medicaid application and verify that the system triggers an alert.', 'Validate detection logic for variations in client names/IDs.', 'Check that alert allows the Case Worker to view/merge duplicates.', 'Ensure alert is not triggered for non-duplicate applications.', 'Confirm merge action results in a single, unified application.']</t>
+          <t>['Add household members and verify they are recorded correctly.', 'Edit and remove household members; changes persist and are accurate.', 'Check information is stored and retrievable for eligibility assessment.', 'Test with zero, one, and multiple household members.', 'Verify data validation for household member information (age, relationship, etc.).', 'Check that eligibility results update as composition changes.', 'Permissions: Only case workers can edit household composition.']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['Near-duplicates (typos, transposed digits in SSN).', 'Concurrency: Multiple workers submitting overlapping applications at the same time.', 'Merging applications with conflicting data.']</t>
+          <t>['Household with zero members.', 'Household member with missing information.', 'Exceedingly large household (stress test).', 'Simultaneous edits by two users.', 'Changing household composition after eligibility decisions made.']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>['Application intake and validation (shared with 22895808).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['22895808 - Changes in intake could affect duplicate logic.', '22895816, 22895833 - Any workflow that relies on accurate unique application records.']</t>
+          <t>['Eligibility assessment (family size factor)', 'Household member data storage and retrieval']</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22895844</v>
+        <v>22895820</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Submit application with conflicting income data and verify alert is presented.', 'Ensure alert content is clear and directs worker actions.', 'Test alert persistence and resolution process.', 'Check system identifies and flags all standard income data discrepancies.', 'Ensure no alert for consistent, valid data.']</t>
+          <t>['Upload a document with sensitive information; verify redacted version is viewable.', 'Ensure sensitive fields (e.g., SSN, address) are fully redacted.', 'Test manual and automated redaction approaches if both exist.', 'Verify original (unredacted) document is not accessible to unauthorized users.', 'Check redaction persists across downloads and views.', 'Redact multiple sensitive pieces of information in the same document.', 'Attempt viewing document as various user roles; only redacted version visible to case worker.']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['Rapidly updated applications (income updated multiple times).', 'Clients with multiple sources of income.', 'Partial/incomplete income data resulting in ambiguous conflicts.']</t>
+          <t>['Uploading non-standard document formats.', 'Documents with edge-case sensitive info (e.g., partial SSN, handwritten text).', 'Large documents with many sensitive fields.', 'Sensitive information in images or scanned docs (OCR challenges).', 'Sensitive info accidentally not redacted.']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>['Alert UI and workflow for Case Workers (if similar approaches used for 22895838).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['22895834 - If income data definitions change.', '22895810 - If data ingestion logic changes.']</t>
+          <t>['Document upload and viewing workflows', 'User access control for document content']</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22895840</v>
+        <v>22895816</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['Verify that a case worker receives an alert when an eligibility rule is changed.', 'Verify the alert contains information about what rule was changed and when.', 'Test if the alert is not sent for unrelated rule changes.', 'Check notification delivery (in-app, email, SMS if supported).', 'Verify that multiple eligibility rule changes trigger the correct number of alerts.', 'Check that dismissing/acknowledging an alert marks it as read.']</t>
+          <t>['Search by full name returns correct applicant(s).', 'Search by partial name returns matching applicants.', 'Search by exact SSN returns correct applicant.', 'Searching with no matching name or SSN returns no results.', 'Case insensitive search by name returns expected results.', 'Search handles leading/trailing whitespace input.']</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['Multiple eligibility rules changed simultaneously.', 'Eligibility rule changed and then reverted before alert delivery.', 'Case worker has notification settings disabled.', 'Old/inactive case worker accounts.']</t>
+          <t>['Names with special characters (hyphens, apostrophes, etc.)', 'SSN with/without dashes', 'Multiple applicants with the same name', 'Invalid SSN format', 'Very long name strings', 'Empty search input']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Duplicate detection logic (with 22895838)']</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['Alerts and notifications module.', 'Case assessment workflows depending on eligibility rules.']</t>
+          <t>['Applicant search functionality', 'Duplicate entry prevention', 'Potential downstream processes that rely on applicant lookup (22895838)']</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22895819</v>
+        <v>22895818</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['Verify that a case worker can see the submission status of each required document per case.', 'Ensure the status updates immediately after a document is submitted.', 'Test filtering or sorting cases by document status.', 'Check that pending documents can be easily identified.', 'Verify that following up action can be triggered from status view.', 'Test notifications/reminders for pending items.']</t>
+          <t>['Send document request to applicant successfully.', 'Request specifies correct list of required documents.', 'Applicant receives notification of document request.', "Request logs appear in applicant's communication history.", 'Duplicate document request is handled appropriately.']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['Documents submitted partially (e.g., multiple required files for one item, only some uploaded).', 'Simultaneous updates by different users.', 'Large volume of pending documents.', 'Document submitted by error, then withdrawn.']</t>
+          <t>['Request with empty document list', 'Request to applicant with no email/notification settings', 'Resending document request after status update']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['22895818: Any shared UI or API endpoints for document status.', '22895824: Interactions when document requirements change.', '22895846: Shared tracking or notification features for documents.']</t>
+          <t>['Document workflow initiation (with 22895819)']</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['Document management and uploads.', 'Case overview/dashboard.', 'Notification/reminder system for documents.']</t>
+          <t>['Applicant communication module', 'Document submission workflow (22895819)']</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>22895839</v>
+        <v>22895819</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['Generate a monthly report for case activity and verify accuracy with raw data.', 'Confirm the report includes all relevant fields (e.g., case opened/closed, activity logs).', 'Check report formatting for readability and exports (e.g., PDF, CSV).', 'Test for correct team-based access and report visibility.', 'Verify filter options (e.g., by team member, date range).']</t>
+          <t>['Display correct submission status for all requested documents.', 'Status updates in real time when applicant uploads documents.', 'Pending, submitted, and overdue states are represented accurately.', 'Automated reminders triggered for pending items.', 'Follow-up actions available for overdue submissions.']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['Month with zero activity.', 'Large volume of activity data.', 'Cases transferred between managers or teams during the reporting period.']</t>
+          <t>['Multiple document requests sent sequentially', 'Simultaneous uploads from applicant and staff', 'Status update for partially completed document set']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['22895837: Verify report data consistency if activity log format changes.', '22895823: Consistency with other case activity reports.']</t>
+          <t>['Document workflow status updates (with 22895818)']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['Reporting module.', 'Case activity logging functionalities.']</t>
+          <t>['Document submission tracking', 'Applicant notifications/reminders', 'Staff alerting']</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>22895821</v>
+        <v>22895815</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['Verify that case managers can access and view all communication logs for a case.', 'Ensure sorting/filtering of logs by date, client, or type is correct.', 'Test visibility permissions (only authorized users can view certain logs).', 'Check if attachment and message contents are displayed correctly.', 'Confirm integration with other case history records.']</t>
+          <t>['Upload single supporting document to a case.', 'Upload multiple documents at once.', 'Supported file types accepted and saved correctly.', 'Unsupported file types are rejected with correct error message.', 'Uploaded documents are linked to correct case records.', 'Verify that user cannot upload documents without correct permissions.']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['Very large number of communications in a single case.', 'Corrupted or missing log entries.', 'Communication logs linked to merged/split cases.']</t>
+          <t>['Attempt to upload very large file', 'Simultaneous uploads from multiple users', 'Duplicate file upload handling', 'File name with special characters']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Document attachment and upload process (with 22895831)']</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['Communication logging features.', 'Case history aggregation and display.']</t>
+          <t>['Document management system', 'Case record updates', 'Potential link to document status tracking (22895819/22895831)']</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>22895833</v>
+        <v>22895809</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['Verify that a case worker can select and pre-fill data from previous cases into a new application.', 'Check that only authorized/eligible data is pre-filled.', 'Test the ability to edit or override pre-filled fields.', 'Ensure proper loading and performance for large historical datasets.', 'Check error handling if previous case data is inconsistent or missing.']</t>
+          <t>["Verify identity using valid government ID (driver's license, passport, etc.).", 'Invalid ID data is rejected with appropriate error message.', 'System matches submitted ID with applicant information.', 'ID images/files are stored securely and linked to applicant record.', 'Audit trail for identity verification process is recorded.']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['Previous case data contains invalid or outdated fields.', 'Multiple previous cases for the same client with conflicting information.', 'No previous cases available for pre-fill.']</t>
+          <t>['ID with damaged image or incomplete data', 'Expired government ID', 'Different names on ID and applicant record', 'Multiple IDs submitted']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['22895829: Shared code/data fetching for historical records.', '22895838: Data transformation and mapping logic.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['New case/application workflows.', 'Historical data management.', 'Data privacy and authorization.']</t>
+          <t>['Applicant onboarding/verification process', 'Document upload and storage module', 'Identity-related workflows in the system']</t>
         </is>
       </c>
     </row>
